--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="2262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2263" uniqueCount="2263">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,40 +47,40 @@
     <t xml:space="preserve">4.13119506835938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91636347770691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7879581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63239049911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757326126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71881651878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66942977905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37804841995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28421401977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1879096031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26939749717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06197357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25705099105835</t>
+    <t xml:space="preserve">3.91636323928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78795719146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63239026069641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757278442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71881580352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66943001747131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37804818153381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28421378135681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18790912628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2693977355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06197333335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25705122947693</t>
   </si>
   <si>
     <t xml:space="preserve">3.3261923789978</t>
@@ -89,25 +89,25 @@
     <t xml:space="preserve">3.26198959350586</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46200585365295</t>
+    <t xml:space="preserve">3.46200609207153</t>
   </si>
   <si>
     <t xml:space="preserve">3.43237352371216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18544101715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16321587562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16074705123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07679033279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95332264900208</t>
+    <t xml:space="preserve">3.18544054031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16321635246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16074657440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07678961753845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9533224105835</t>
   </si>
   <si>
     <t xml:space="preserve">2.91628289222717</t>
@@ -119,115 +119,115 @@
     <t xml:space="preserve">2.65700316429138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58292317390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7335524559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5927996635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68416571617126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80269336700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75824594497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89899802207947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87924313545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81010127067566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92616057395935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83973383903503</t>
+    <t xml:space="preserve">2.58292269706726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73355269432068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59280014038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68416595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80269384384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75824570655823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89899754524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87924337387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81010150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92616009712219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83973336219788</t>
   </si>
   <si>
     <t xml:space="preserve">2.72614407539368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0051794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13358449935913</t>
+    <t xml:space="preserve">3.00517916679382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13358402252197</t>
   </si>
   <si>
     <t xml:space="preserve">3.29902982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45212864875793</t>
+    <t xml:space="preserve">3.45212912559509</t>
   </si>
   <si>
     <t xml:space="preserve">3.46447467803955</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44225168228149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2891526222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30643820762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21013331413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35088539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.447190284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36076283454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44472026824951</t>
+    <t xml:space="preserve">3.44225096702576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28915238380432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30643796920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21013355255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35088562965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44718956947327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36076307296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44471979141235</t>
   </si>
   <si>
     <t xml:space="preserve">3.42496609687805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51633095741272</t>
+    <t xml:space="preserve">3.5163311958313</t>
   </si>
   <si>
     <t xml:space="preserve">3.50151515007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51386117935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47682166099548</t>
+    <t xml:space="preserve">3.51386141777039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4768214225769</t>
   </si>
   <si>
     <t xml:space="preserve">3.33360075950623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57559514045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5064537525177</t>
+    <t xml:space="preserve">3.57559466362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50645351409912</t>
   </si>
   <si>
     <t xml:space="preserve">3.33606958389282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34841632843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18050241470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13852262496948</t>
+    <t xml:space="preserve">3.34841656684875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18050217628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13852286338806</t>
   </si>
   <si>
     <t xml:space="preserve">3.01505637168884</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">3.21260333061218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16815543174744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31878447532654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35335493087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40274167060852</t>
+    <t xml:space="preserve">3.16815519332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31878423690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35335516929626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4027419090271</t>
   </si>
   <si>
     <t xml:space="preserve">3.56571793556213</t>
@@ -257,31 +257,31 @@
     <t xml:space="preserve">3.54596328735352</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56818675994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47435283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53361630439758</t>
+    <t xml:space="preserve">3.56818747520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47435235977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53361654281616</t>
   </si>
   <si>
     <t xml:space="preserve">3.41015005111694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38298678398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29656004905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26692843437195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3657021522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3163149356842</t>
+    <t xml:space="preserve">3.3829870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29655981063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26692819595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36570143699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31631541252136</t>
   </si>
   <si>
     <t xml:space="preserve">3.38051795959473</t>
@@ -290,25 +290,25 @@
     <t xml:space="preserve">3.33113098144531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.108891248703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11382985115051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10148286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629915237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97801661491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06938171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12370681762695</t>
+    <t xml:space="preserve">3.10889101028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11382961273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10148334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629867553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97801637649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06938195228577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12370705604553</t>
   </si>
   <si>
     <t xml:space="preserve">3.07185125350952</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">3.03974962234497</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14840006828308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1212375164032</t>
+    <t xml:space="preserve">3.14840054512024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12123775482178</t>
   </si>
   <si>
     <t xml:space="preserve">2.9310986995697</t>
@@ -338,28 +338,28 @@
     <t xml:space="preserve">2.87677335739136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89652848243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86195731163025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93356847763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09407496452332</t>
+    <t xml:space="preserve">2.89652872085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86195778846741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93356823921204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09407448768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.08666706085205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04962754249573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11136054992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.819979429245</t>
+    <t xml:space="preserve">3.04962682723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11136031150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81997895240784</t>
   </si>
   <si>
     <t xml:space="preserve">2.64465665817261</t>
@@ -368,10 +368,10 @@
     <t xml:space="preserve">2.66194176673889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7137975692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77059245109558</t>
+    <t xml:space="preserve">2.71379733085632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.770592212677</t>
   </si>
   <si>
     <t xml:space="preserve">2.533536195755</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">2.52365875244141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54835176467896</t>
+    <t xml:space="preserve">2.54835200309753</t>
   </si>
   <si>
     <t xml:space="preserve">2.8471417427063</t>
@@ -389,31 +389,31 @@
     <t xml:space="preserve">2.96320009231567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91134452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99777126312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00270986557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95826148986816</t>
+    <t xml:space="preserve">2.91134428977966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9977707862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00270962715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95826125144958</t>
   </si>
   <si>
     <t xml:space="preserve">3.08913612365723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09901428222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12617659568787</t>
+    <t xml:space="preserve">3.09901356697083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12617635726929</t>
   </si>
   <si>
     <t xml:space="preserve">3.06691217422485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84467267990112</t>
+    <t xml:space="preserve">2.84467244148254</t>
   </si>
   <si>
     <t xml:space="preserve">2.81257104873657</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">2.69157361984253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91381335258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88665103912354</t>
+    <t xml:space="preserve">2.913813829422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88665080070496</t>
   </si>
   <si>
     <t xml:space="preserve">3.05703473091125</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">2.98789381980896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96073150634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97307801246643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88418197631836</t>
+    <t xml:space="preserve">2.96073126792908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97307777404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88418173789978</t>
   </si>
   <si>
     <t xml:space="preserve">2.91875267028809</t>
@@ -452,49 +452,49 @@
     <t xml:space="preserve">3.02987217903137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0446879863739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99283266067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05950474739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97554707527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95085406303406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96813917160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90393614768982</t>
+    <t xml:space="preserve">3.04468774795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99283218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05950450897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97554683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95085334777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96813941001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90393590927124</t>
   </si>
   <si>
     <t xml:space="preserve">2.86442732810974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87430477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81504034996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90146708488464</t>
+    <t xml:space="preserve">2.87430453300476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81504058837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90146684646606</t>
   </si>
   <si>
     <t xml:space="preserve">2.83232545852661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8668966293335</t>
+    <t xml:space="preserve">2.86689639091492</t>
   </si>
   <si>
     <t xml:space="preserve">2.74096012115479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70885872840881</t>
+    <t xml:space="preserve">2.70885896682739</t>
   </si>
   <si>
     <t xml:space="preserve">2.79034686088562</t>
@@ -506,61 +506,61 @@
     <t xml:space="preserve">2.84220337867737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8915901184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87183523178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90887498855591</t>
+    <t xml:space="preserve">2.89158964157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87183475494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90887475013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.76812291145325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82244849205017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85948777198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9385073184967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25211238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29409122467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25952076911926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03234195709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02740359306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16568565368652</t>
+    <t xml:space="preserve">2.82244801521301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85948801040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93850684165955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25211262702942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29409146308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2595202922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03234171867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02740287780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16568517684937</t>
   </si>
   <si>
     <t xml:space="preserve">3.5237398147583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39780306816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47188305854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45953607559204</t>
+    <t xml:space="preserve">3.39780330657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47188258171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45953631401062</t>
   </si>
   <si>
     <t xml:space="preserve">3.47929120063782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49410724639893</t>
+    <t xml:space="preserve">3.4941074848175</t>
   </si>
   <si>
     <t xml:space="preserve">3.55584049224854</t>
@@ -569,19 +569,19 @@
     <t xml:space="preserve">3.58547234535217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57065606117249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56077933311462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6002893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62251281738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55830979347229</t>
+    <t xml:space="preserve">3.57065582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56077909469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60028862953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62251257896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55831003189087</t>
   </si>
   <si>
     <t xml:space="preserve">3.72128558158875</t>
@@ -593,22 +593,22 @@
     <t xml:space="preserve">3.85709953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93364858627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93117880821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97315764427185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525903701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99044370651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15341901779175</t>
+    <t xml:space="preserve">3.93364882469177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9311785697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97315740585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99044275283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15341949462891</t>
   </si>
   <si>
     <t xml:space="preserve">4.19539785385132</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">4.31392621994019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30898809432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27935552597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42257738113403</t>
+    <t xml:space="preserve">4.30898714065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27935457229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42257690429688</t>
   </si>
   <si>
     <t xml:space="preserve">4.5065336227417</t>
@@ -650,22 +650,22 @@
     <t xml:space="preserve">4.5707368850708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88928031921387</t>
+    <t xml:space="preserve">4.88927984237671</t>
   </si>
   <si>
     <t xml:space="preserve">4.95842266082764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01274824142456</t>
+    <t xml:space="preserve">5.0127477645874</t>
   </si>
   <si>
     <t xml:space="preserve">5.17078495025635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33615064620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53616619110107</t>
+    <t xml:space="preserve">4.33615016937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53616571426392</t>
   </si>
   <si>
     <t xml:space="preserve">4.34602689743042</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.41516828536987</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62753105163574</t>
+    <t xml:space="preserve">4.62753057479858</t>
   </si>
   <si>
     <t xml:space="preserve">4.64234781265259</t>
@@ -686,25 +686,25 @@
     <t xml:space="preserve">4.71889734268188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99793100357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04237842559814</t>
+    <t xml:space="preserve">4.99793195724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04237937927246</t>
   </si>
   <si>
     <t xml:space="preserve">5.10164356231689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12633657455444</t>
+    <t xml:space="preserve">5.12633562088013</t>
   </si>
   <si>
     <t xml:space="preserve">4.95348405838013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98805332183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99299240112305</t>
+    <t xml:space="preserve">4.98805284500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99299287796021</t>
   </si>
   <si>
     <t xml:space="preserve">5.00287055969238</t>
@@ -713,40 +713,40 @@
     <t xml:space="preserve">5.04731750488281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92385149002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78063011169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89915895462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02756357192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33869934082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34363746643066</t>
+    <t xml:space="preserve">4.92385101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78062915802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89915800094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02756309509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33870029449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34363698959351</t>
   </si>
   <si>
     <t xml:space="preserve">5.32388353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25474214553833</t>
+    <t xml:space="preserve">5.25474262237549</t>
   </si>
   <si>
     <t xml:space="preserve">5.32882261276245</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1757230758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14609098434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18560028076172</t>
+    <t xml:space="preserve">5.17572355270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14609050750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18560075759888</t>
   </si>
   <si>
     <t xml:space="preserve">5.18066215515137</t>
@@ -755,25 +755,25 @@
     <t xml:space="preserve">5.13127565383911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13621425628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16584730148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09670352935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14115190505981</t>
+    <t xml:space="preserve">5.13621377944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16584587097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09670448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14115285873413</t>
   </si>
   <si>
     <t xml:space="preserve">5.22511053085327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30412769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21029472351074</t>
+    <t xml:space="preserve">5.30412817001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21029376983643</t>
   </si>
   <si>
     <t xml:space="preserve">4.98311519622803</t>
@@ -782,55 +782,55 @@
     <t xml:space="preserve">4.94360589981079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96336126327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93372821807861</t>
+    <t xml:space="preserve">4.96336078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93372774124146</t>
   </si>
   <si>
     <t xml:space="preserve">5.07695055007935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07201099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06213474273682</t>
+    <t xml:space="preserve">5.07201147079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0621337890625</t>
   </si>
   <si>
     <t xml:space="preserve">4.81026220321655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83248615264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74358940124512</t>
+    <t xml:space="preserve">4.83248662948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74358987808228</t>
   </si>
   <si>
     <t xml:space="preserve">4.78556823730469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73371315002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71642684936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70655012130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69420337677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51888036727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45220851898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64728689193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7040810585022</t>
+    <t xml:space="preserve">4.7337121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71642732620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70654964447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69420289993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51888084411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45220899581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64728593826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70408058166504</t>
   </si>
   <si>
     <t xml:space="preserve">4.63000059127808</t>
@@ -839,22 +839,22 @@
     <t xml:space="preserve">4.79297685623169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78803777694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23498678207397</t>
+    <t xml:space="preserve">4.78803825378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23498773574829</t>
   </si>
   <si>
     <t xml:space="preserve">4.91644287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97323751449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05225706100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03744029998779</t>
+    <t xml:space="preserve">4.97323846817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0522575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03744077682495</t>
   </si>
   <si>
     <t xml:space="preserve">4.91891241073608</t>
@@ -866,61 +866,61 @@
     <t xml:space="preserve">5.02262449264526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76828336715698</t>
+    <t xml:space="preserve">4.76828384399414</t>
   </si>
   <si>
     <t xml:space="preserve">4.62012386322021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80038547515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72383642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68926525115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66210222244263</t>
+    <t xml:space="preserve">4.80038404464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72383594512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68926429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66210174560547</t>
   </si>
   <si>
     <t xml:space="preserve">4.67197942733765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59049129486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.583083152771</t>
+    <t xml:space="preserve">4.59049081802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58308362960815</t>
   </si>
   <si>
     <t xml:space="preserve">4.61518526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84730243682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83001613616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75346708297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8053240776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75099849700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79544639587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8176703453064</t>
+    <t xml:space="preserve">4.84730195999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83001661300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75346660614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80532312393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75099754333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79544687271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81766986846924</t>
   </si>
   <si>
     <t xml:space="preserve">4.78309917449951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72136545181274</t>
+    <t xml:space="preserve">4.7213659286499</t>
   </si>
   <si>
     <t xml:space="preserve">4.68432569503784</t>
@@ -929,85 +929,85 @@
     <t xml:space="preserve">4.85224056243896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.778160572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76087522506714</t>
+    <t xml:space="preserve">4.77816104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7608757019043</t>
   </si>
   <si>
     <t xml:space="preserve">4.55838966369629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85507869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8600378036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78564977645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82532405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80548572540283</t>
+    <t xml:space="preserve">4.85507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86003732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78564882278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82532358169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80548620223999</t>
   </si>
   <si>
     <t xml:space="preserve">4.87243509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95922183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99889612197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19230556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15263175964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17246770858765</t>
+    <t xml:space="preserve">4.95922231674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9988956451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19230508804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15263223648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1724681854248</t>
   </si>
   <si>
     <t xml:space="preserve">5.10799884796143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17742776870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97409915924072</t>
+    <t xml:space="preserve">5.17742729187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97410011291504</t>
   </si>
   <si>
     <t xml:space="preserve">4.97905921936035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98897695541382</t>
+    <t xml:space="preserve">4.98897743225098</t>
   </si>
   <si>
     <t xml:space="preserve">5.03856992721558</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03361034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05840587615967</t>
+    <t xml:space="preserve">5.03360986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05840635299683</t>
   </si>
   <si>
     <t xml:space="preserve">5.07328462600708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02865171432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07824277877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06336545944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95178318023682</t>
+    <t xml:space="preserve">5.02865123748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07824230194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0633659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95178365707397</t>
   </si>
   <si>
     <t xml:space="preserve">4.95426273345947</t>
@@ -1016,52 +1016,52 @@
     <t xml:space="preserve">4.86995601654053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26669359207153</t>
+    <t xml:space="preserve">5.26669406890869</t>
   </si>
   <si>
     <t xml:space="preserve">5.40555238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34604120254517</t>
+    <t xml:space="preserve">5.34604167938232</t>
   </si>
   <si>
     <t xml:space="preserve">5.30636787414551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67335033416748</t>
+    <t xml:space="preserve">5.67334985733032</t>
   </si>
   <si>
     <t xml:space="preserve">5.68822765350342</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01553678512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19406843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14943552017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16431283950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07008838653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13951683044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27341651916504</t>
+    <t xml:space="preserve">6.01553630828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19406938552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14943504333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1643123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07008695602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13951635360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27341508865356</t>
   </si>
   <si>
     <t xml:space="preserve">6.61560249328613</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53129577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50649976730347</t>
+    <t xml:space="preserve">6.53129482269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50649929046631</t>
   </si>
   <si>
     <t xml:space="preserve">6.78421592712402</t>
@@ -1070,37 +1070,37 @@
     <t xml:space="preserve">6.70982789993286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72470474243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76933860778809</t>
+    <t xml:space="preserve">6.7247052192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76933813095093</t>
   </si>
   <si>
     <t xml:space="preserve">6.80405282974243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96770668029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88340091705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99250268936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07680940628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14623880386353</t>
+    <t xml:space="preserve">6.96770763397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88340044021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99250221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07680988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14623975753784</t>
   </si>
   <si>
     <t xml:space="preserve">7.18095350265503</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46362924575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31485271453857</t>
+    <t xml:space="preserve">7.46362972259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31485223770142</t>
   </si>
   <si>
     <t xml:space="preserve">7.33468914031982</t>
@@ -1109,31 +1109,31 @@
     <t xml:space="preserve">7.38428211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36444568634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51818084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58265018463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56281328201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53801727294922</t>
+    <t xml:space="preserve">7.36444520950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51818037033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58265066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56281423568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53801870346069</t>
   </si>
   <si>
     <t xml:space="preserve">7.49338483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40907764434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52313995361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41403675079346</t>
+    <t xml:space="preserve">7.4090781211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52313947677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41403722763062</t>
   </si>
   <si>
     <t xml:space="preserve">7.50330352783203</t>
@@ -1142,52 +1142,52 @@
     <t xml:space="preserve">7.42395639419556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45866966247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41899633407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30989408493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37932395935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93795204162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05697298049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02225828170776</t>
+    <t xml:space="preserve">7.45867013931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41899538040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30989456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37932252883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93795299530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05697345733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02225923538208</t>
   </si>
   <si>
     <t xml:space="preserve">7.14128017425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34956741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35948610305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5132212638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76614093780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73142671585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66199779510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45371055603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28013753890991</t>
+    <t xml:space="preserve">7.34956789016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35948514938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51322174072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76614141464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73142719268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6619987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45371150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28013706207275</t>
   </si>
   <si>
     <t xml:space="preserve">7.33964872360229</t>
@@ -1199,103 +1199,103 @@
     <t xml:space="preserve">7.25038242340088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4338755607605</t>
+    <t xml:space="preserve">7.43387508392334</t>
   </si>
   <si>
     <t xml:space="preserve">7.55785417556763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24046421051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20078945159912</t>
+    <t xml:space="preserve">7.2404637336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20078992843628</t>
   </si>
   <si>
     <t xml:space="preserve">7.1710352897644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.151198387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00738191604614</t>
+    <t xml:space="preserve">7.15119886398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00738096237183</t>
   </si>
   <si>
     <t xml:space="preserve">7.23550415039062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1908712387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53305959701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52809953689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50826215744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43883371353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44875192642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63720178604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65208005905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64216184616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69175338745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67191648483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297780990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39420032501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71159076690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35628890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88692569732666</t>
+    <t xml:space="preserve">7.19087171554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53305864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52809810638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50826263427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43883323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44875144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63720226287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65207958221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64216136932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69175243377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67191743850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297685623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39419984817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71159029006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35628986358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88692760467529</t>
   </si>
   <si>
     <t xml:space="preserve">8.98115062713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15968227386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2142333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42252159118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48699188232422</t>
+    <t xml:space="preserve">9.15968322753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21423435211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42252063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48699283599854</t>
   </si>
   <si>
     <t xml:space="preserve">9.69032001495361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28862190246582</t>
+    <t xml:space="preserve">9.28862285614014</t>
   </si>
   <si>
     <t xml:space="preserve">9.32829761505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50186920166016</t>
+    <t xml:space="preserve">9.50187015533447</t>
   </si>
   <si>
     <t xml:space="preserve">9.69528007507324</t>
@@ -1304,34 +1304,34 @@
     <t xml:space="preserve">9.76470756530762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70519733428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64072704315186</t>
+    <t xml:space="preserve">9.70519638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64072799682617</t>
   </si>
   <si>
     <t xml:space="preserve">9.63080787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81925868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84108066558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68337821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65163803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53856754302979</t>
+    <t xml:space="preserve">9.81925964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84107971191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68337917327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65163898468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5385684967041</t>
   </si>
   <si>
     <t xml:space="preserve">9.31937026977539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75798606872559</t>
+    <t xml:space="preserve">8.7579870223999</t>
   </si>
   <si>
     <t xml:space="preserve">9.35111045837402</t>
@@ -1343,25 +1343,25 @@
     <t xml:space="preserve">8.63698196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75302791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57548713684082</t>
+    <t xml:space="preserve">8.75302696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57548809051514</t>
   </si>
   <si>
     <t xml:space="preserve">8.77782249450684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82741546630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0039644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83733367919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94643592834473</t>
+    <t xml:space="preserve">8.82741451263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00396537780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83733463287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94643497467041</t>
   </si>
   <si>
     <t xml:space="preserve">8.98908615112305</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">8.80956268310547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73815059661865</t>
+    <t xml:space="preserve">8.73814868927002</t>
   </si>
   <si>
     <t xml:space="preserve">8.6905403137207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8055944442749</t>
+    <t xml:space="preserve">8.80559539794922</t>
   </si>
   <si>
     <t xml:space="preserve">8.71434497833252</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">8.47431945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98930644989014</t>
+    <t xml:space="preserve">7.98930740356445</t>
   </si>
   <si>
     <t xml:space="preserve">8.01410293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46836853027344</t>
+    <t xml:space="preserve">8.46836757659912</t>
   </si>
   <si>
     <t xml:space="preserve">8.55664253234863</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">8.51597690582275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52787780761719</t>
+    <t xml:space="preserve">8.52787971496582</t>
   </si>
   <si>
     <t xml:space="preserve">8.53085422515869</t>
@@ -1418,28 +1418,28 @@
     <t xml:space="preserve">8.52589416503906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3592643737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56457710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71732044219971</t>
+    <t xml:space="preserve">8.35926532745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56457805633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71732139587402</t>
   </si>
   <si>
     <t xml:space="preserve">8.42175006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25115299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1886682510376</t>
+    <t xml:space="preserve">8.25115489959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18866729736328</t>
   </si>
   <si>
     <t xml:space="preserve">8.32554244995117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15792083740234</t>
+    <t xml:space="preserve">8.15791988372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.18370914459229</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">9.15869140625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07438564300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18943977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31342029571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22613620758057</t>
+    <t xml:space="preserve">9.07438468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18943881988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31341934204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2261381149292</t>
   </si>
   <si>
     <t xml:space="preserve">9.40764427185059</t>
@@ -1472,22 +1472,22 @@
     <t xml:space="preserve">9.43640804290771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36301231384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70916652679443</t>
+    <t xml:space="preserve">9.36301136016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7091646194458</t>
   </si>
   <si>
     <t xml:space="preserve">9.76768398284912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63180065155029</t>
+    <t xml:space="preserve">9.63180160522461</t>
   </si>
   <si>
     <t xml:space="preserve">9.55840492248535</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75974750518799</t>
+    <t xml:space="preserve">9.75974941253662</t>
   </si>
   <si>
     <t xml:space="preserve">9.79148769378662</t>
@@ -1496,16 +1496,16 @@
     <t xml:space="preserve">9.49393558502197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68635272979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41458702087402</t>
+    <t xml:space="preserve">9.68635368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41458797454834</t>
   </si>
   <si>
     <t xml:space="preserve">9.20927715301514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43739986419678</t>
+    <t xml:space="preserve">9.43739891052246</t>
   </si>
   <si>
     <t xml:space="preserve">9.21820259094238</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">9.5355920791626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4800500869751</t>
+    <t xml:space="preserve">9.48004817962646</t>
   </si>
   <si>
     <t xml:space="preserve">9.29556655883789</t>
@@ -1526,46 +1526,46 @@
     <t xml:space="preserve">9.3084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42946434020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41756248474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36697864532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30746936798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36796951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19935703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43938446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59609413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48600196838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31143665313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3054838180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10810852050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06446552276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42748069763184</t>
+    <t xml:space="preserve">9.42946529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41756343841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36697769165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30746841430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36797046661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1993579864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4393835067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59609508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31143474578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30548477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1081075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06446647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42748260498047</t>
   </si>
   <si>
     <t xml:space="preserve">9.62089157104492</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.85221195220947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87601566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86213111877441</t>
+    <t xml:space="preserve">8.87601661682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8621301651001</t>
   </si>
   <si>
     <t xml:space="preserve">9.13984680175781</t>
@@ -1589,22 +1589,22 @@
     <t xml:space="preserve">8.90676307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98313617706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92659950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85022735595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04462814331055</t>
+    <t xml:space="preserve">8.98313522338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92660045623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85022830963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04462909698486</t>
   </si>
   <si>
     <t xml:space="preserve">8.87403297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92461681365967</t>
+    <t xml:space="preserve">8.92461585998535</t>
   </si>
   <si>
     <t xml:space="preserve">8.79666900634766</t>
@@ -1616,19 +1616,19 @@
     <t xml:space="preserve">8.38505268096924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18172454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92979621887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15296077728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24123573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95558547973633</t>
+    <t xml:space="preserve">8.18172359466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92979574203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15296268463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24123668670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95558452606201</t>
   </si>
   <si>
     <t xml:space="preserve">8.10039329528809</t>
@@ -1637,49 +1637,49 @@
     <t xml:space="preserve">8.10237789154053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03889846801758</t>
+    <t xml:space="preserve">8.03889942169189</t>
   </si>
   <si>
     <t xml:space="preserve">8.50506687164307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40687274932861</t>
+    <t xml:space="preserve">8.40687465667725</t>
   </si>
   <si>
     <t xml:space="preserve">8.46935939788818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52291965484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2630558013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21346282958984</t>
+    <t xml:space="preserve">8.52291870117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26305675506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21346378326416</t>
   </si>
   <si>
     <t xml:space="preserve">8.25214576721191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19957733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24917030334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22239112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33347702026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14105796813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01906394958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21048927307129</t>
+    <t xml:space="preserve">8.19957828521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24916934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22239017486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33347606658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14105987548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01906299591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21048736572266</t>
   </si>
   <si>
     <t xml:space="preserve">7.16111707687378</t>
@@ -1688,160 +1688,160 @@
     <t xml:space="preserve">7.26426839828491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23947334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04804563522339</t>
+    <t xml:space="preserve">7.23947286605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04804706573486</t>
   </si>
   <si>
     <t xml:space="preserve">7.04209566116333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24343967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23352098464966</t>
+    <t xml:space="preserve">7.2434401512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23352146148682</t>
   </si>
   <si>
     <t xml:space="preserve">7.20277404785156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24839973449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17500257492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04408025741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97663402557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80801963806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79909420013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01729965209961</t>
+    <t xml:space="preserve">7.2483983039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1750020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04407930374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97663497924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80802059173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79909324645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01729917526245</t>
   </si>
   <si>
     <t xml:space="preserve">7.12243509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0371356010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95977163314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18591260910034</t>
+    <t xml:space="preserve">7.03713655471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95977115631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1859130859375</t>
   </si>
   <si>
     <t xml:space="preserve">7.43486642837524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42693090438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36146926879883</t>
+    <t xml:space="preserve">7.42693185806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36146879196167</t>
   </si>
   <si>
     <t xml:space="preserve">7.220627784729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26823568344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39320802688599</t>
+    <t xml:space="preserve">7.26823663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39320850372314</t>
   </si>
   <si>
     <t xml:space="preserve">7.22657918930054</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21566915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16706800460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48247528076172</t>
+    <t xml:space="preserve">7.21566820144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.167067527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4824743270874</t>
   </si>
   <si>
     <t xml:space="preserve">7.40610218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42792320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45767784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48346567153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61934852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73341178894043</t>
+    <t xml:space="preserve">7.42792367935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.457679271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48346519470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61934900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73341131210327</t>
   </si>
   <si>
     <t xml:space="preserve">7.66001462936401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70266437530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66795015335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51024532318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68282842636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69373750686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64017724990845</t>
+    <t xml:space="preserve">7.70266389846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66794919967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51024580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68282604217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6937370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64017772674561</t>
   </si>
   <si>
     <t xml:space="preserve">7.57769155502319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52016401290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34460735321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42197227478027</t>
+    <t xml:space="preserve">7.52016448974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34460878372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42197179794312</t>
   </si>
   <si>
     <t xml:space="preserve">7.01035690307617</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9627480506897</t>
+    <t xml:space="preserve">6.96274757385254</t>
   </si>
   <si>
     <t xml:space="preserve">6.92803335189819</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94588613510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17797708511353</t>
+    <t xml:space="preserve">6.94588708877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.177978515625</t>
   </si>
   <si>
     <t xml:space="preserve">6.87744951248169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82587289810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66618680953979</t>
+    <t xml:space="preserve">6.82587337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66618633270264</t>
   </si>
   <si>
     <t xml:space="preserve">6.86455488204956</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">6.95183801651001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78024959564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0470552444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81992149353027</t>
+    <t xml:space="preserve">6.78024864196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04705476760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81992244720459</t>
   </si>
   <si>
     <t xml:space="preserve">6.67015409469604</t>
@@ -1868,121 +1868,121 @@
     <t xml:space="preserve">7.02920150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11251640319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09664726257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26129293441772</t>
+    <t xml:space="preserve">7.11251592636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09664630889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26129341125488</t>
   </si>
   <si>
     <t xml:space="preserve">7.28708124160767</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08672857284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30394268035889</t>
+    <t xml:space="preserve">7.08672714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30394315719604</t>
   </si>
   <si>
     <t xml:space="preserve">7.23054552078247</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13334465026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12838697433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94291067123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0123405456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93001651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99052000045776</t>
+    <t xml:space="preserve">7.13334512710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12838649749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94291210174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01234006881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93001699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99051952362061</t>
   </si>
   <si>
     <t xml:space="preserve">7.33865594863892</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34758329391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30493402481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49635982513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3485746383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23451280593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86554718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82488203048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61064291000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78322458267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91613149642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9220814704895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86852312088013</t>
+    <t xml:space="preserve">7.34758424758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30493450164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49635934829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34857606887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2345118522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86554765701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8248815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61064338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78322505950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9161319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92208194732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86852264404297</t>
   </si>
   <si>
     <t xml:space="preserve">6.82884836196899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82289791107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72272109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50848388671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25754737854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28928470611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23175811767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15736961364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5025315284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55113172531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62849569320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87645721435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01134872436523</t>
+    <t xml:space="preserve">6.82289838790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72272205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50848197937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25754690170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28928518295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23175859451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1573691368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50253295898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55113220214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62849617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87645673751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01134920120239</t>
   </si>
   <si>
     <t xml:space="preserve">7.16012525558472</t>
@@ -1991,52 +1991,52 @@
     <t xml:space="preserve">7.2444314956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21070909500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32080507278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10557317733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26724433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18690586090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18987941741943</t>
+    <t xml:space="preserve">7.21070766448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32080411911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1055736541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2672438621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18690538406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18987989425659</t>
   </si>
   <si>
     <t xml:space="preserve">7.28509712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39816761016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47354698181152</t>
+    <t xml:space="preserve">7.3981671333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47354793548584</t>
   </si>
   <si>
     <t xml:space="preserve">7.52710723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6354398727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44302177429199</t>
+    <t xml:space="preserve">6.63543891906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44302082061768</t>
   </si>
   <si>
     <t xml:space="preserve">6.41822481155396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3973970413208</t>
+    <t xml:space="preserve">6.39739608764648</t>
   </si>
   <si>
     <t xml:space="preserve">6.4975733757019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40731430053711</t>
+    <t xml:space="preserve">6.40731525421143</t>
   </si>
   <si>
     <t xml:space="preserve">6.45988273620605</t>
@@ -2045,46 +2045,46 @@
     <t xml:space="preserve">6.44897317886353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45194721221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57692003250122</t>
+    <t xml:space="preserve">6.4519476890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57692098617554</t>
   </si>
   <si>
     <t xml:space="preserve">6.50154066085815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51145935058594</t>
+    <t xml:space="preserve">6.51145887374878</t>
   </si>
   <si>
     <t xml:space="preserve">6.54617404937744</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45591592788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43806171417236</t>
+    <t xml:space="preserve">6.45591497421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43806123733521</t>
   </si>
   <si>
     <t xml:space="preserve">6.41227388381958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3626823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41524982452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6493239402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32697486877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36664962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35871458053589</t>
+    <t xml:space="preserve">6.36268281936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41525030136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64932584762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32697629928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36665010452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35871315002441</t>
   </si>
   <si>
     <t xml:space="preserve">6.30416297912598</t>
@@ -2096,52 +2096,52 @@
     <t xml:space="preserve">6.26548147201538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32003307342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63643169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46980142593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49658012390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33590269088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46385049819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49162149429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66122722625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52633666992188</t>
+    <t xml:space="preserve">6.32003211975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6364312171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46980047225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49658060073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33590316772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46384954452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49162197113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6612286567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52633619308472</t>
   </si>
   <si>
     <t xml:space="preserve">6.58188009262085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73958301544189</t>
+    <t xml:space="preserve">6.73958349227905</t>
   </si>
   <si>
     <t xml:space="preserve">6.8060359954834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80901098251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81000423431396</t>
+    <t xml:space="preserve">6.80901193618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81000375747681</t>
   </si>
   <si>
     <t xml:space="preserve">6.9389443397522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86157989501953</t>
+    <t xml:space="preserve">6.86157941818237</t>
   </si>
   <si>
     <t xml:space="preserve">6.89133453369141</t>
@@ -2153,46 +2153,46 @@
     <t xml:space="preserve">7.04308700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09367084503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607570648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29303169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28431129455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20211410522461</t>
+    <t xml:space="preserve">7.0936713218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607618331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29303216934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28431224822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20211505889893</t>
   </si>
   <si>
     <t xml:space="preserve">7.14384794235229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20939826965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19170999526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14488887786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04916715621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3737907409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11263513565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07205629348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80673694610596</t>
+    <t xml:space="preserve">7.20939874649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19170951843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14488935470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04916620254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11263465881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07205677032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80673742294312</t>
   </si>
   <si>
     <t xml:space="preserve">6.73806619644165</t>
@@ -2201,157 +2201,157 @@
     <t xml:space="preserve">6.61112928390503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71309423446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81401920318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88997411727905</t>
+    <t xml:space="preserve">6.71309566497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81402015686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88997364044189</t>
   </si>
   <si>
     <t xml:space="preserve">6.95448350906372</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93350172042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88365411758423</t>
+    <t xml:space="preserve">6.93350219726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88365459442139</t>
   </si>
   <si>
     <t xml:space="preserve">6.82684993743896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62166309356689</t>
+    <t xml:space="preserve">6.62166213989258</t>
   </si>
   <si>
     <t xml:space="preserve">6.64021015167236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16998958587646</t>
+    <t xml:space="preserve">7.16999006271362</t>
   </si>
   <si>
     <t xml:space="preserve">7.10623073577881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.019287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96132373809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6297779083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59268188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84771633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78164005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78743457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7642502784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88133573532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94625377655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83728313446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8952465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86278676986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92422676086426</t>
+    <t xml:space="preserve">7.01928663253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96132278442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62977695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59268045425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84771680831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78163909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78743600845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76425075531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88133525848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94625329971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83728361129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89524602890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8627872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92422866821289</t>
   </si>
   <si>
     <t xml:space="preserve">6.98566818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06449747085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15028238296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13521289825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14216804504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02160549163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03319787979126</t>
+    <t xml:space="preserve">7.06449699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15028142929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13521146774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14216709136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02160453796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0331974029541</t>
   </si>
   <si>
     <t xml:space="preserve">7.08072662353516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10970783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15723752975464</t>
+    <t xml:space="preserve">7.10970878601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15723848342896</t>
   </si>
   <si>
     <t xml:space="preserve">7.13057518005371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33112716674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35315227508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32532930374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28939342498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20940542221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20476675033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28707504272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28591442108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05986166000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07493019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95900392532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17578554153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3114185333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19433403015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08768320083618</t>
+    <t xml:space="preserve">7.33112621307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35315275192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3253288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28939294815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20940446853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20476627349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28707408905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28591394424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05986070632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0749306678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9590048789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17578506469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31141901016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19433355331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08768272399902</t>
   </si>
   <si>
     <t xml:space="preserve">6.976393699646</t>
@@ -2360,64 +2360,64 @@
     <t xml:space="preserve">6.99842023849487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76540946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81873655319214</t>
+    <t xml:space="preserve">6.76540994644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81873559951782</t>
   </si>
   <si>
     <t xml:space="preserve">6.8685827255249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72715377807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72367572784424</t>
+    <t xml:space="preserve">6.72715473175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7236762046814</t>
   </si>
   <si>
     <t xml:space="preserve">6.82569074630737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58572435379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40719938278198</t>
+    <t xml:space="preserve">6.5857253074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40719985961914</t>
   </si>
   <si>
     <t xml:space="preserve">6.52660274505615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46632194519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194389343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69005870819092</t>
+    <t xml:space="preserve">6.4663233757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194341659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6900577545166</t>
   </si>
   <si>
     <t xml:space="preserve">6.54515075683594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63557291030884</t>
+    <t xml:space="preserve">6.63557386398315</t>
   </si>
   <si>
     <t xml:space="preserve">6.74454259872437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80482387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86162853240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86394691467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0830454826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29055213928223</t>
+    <t xml:space="preserve">6.80482339859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86162805557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86394643783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08304500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29055166244507</t>
   </si>
   <si>
     <t xml:space="preserve">7.30562257766724</t>
@@ -2426,16 +2426,16 @@
     <t xml:space="preserve">7.37285900115967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28243637084961</t>
+    <t xml:space="preserve">7.28243684768677</t>
   </si>
   <si>
     <t xml:space="preserve">7.28127765655518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29287052154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18158197402954</t>
+    <t xml:space="preserve">7.29287147521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1815824508667</t>
   </si>
   <si>
     <t xml:space="preserve">7.1873779296875</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">7.07029342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9265456199646</t>
+    <t xml:space="preserve">6.92654705047607</t>
   </si>
   <si>
     <t xml:space="preserve">6.83148813247681</t>
@@ -2453,13 +2453,13 @@
     <t xml:space="preserve">6.84539794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87785768508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525754928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63093614578247</t>
+    <t xml:space="preserve">6.87785720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525707244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63093566894531</t>
   </si>
   <si>
     <t xml:space="preserve">6.54051446914673</t>
@@ -2468,13 +2468,13 @@
     <t xml:space="preserve">6.53239917755127</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57529306411743</t>
+    <t xml:space="preserve">6.57529163360596</t>
   </si>
   <si>
     <t xml:space="preserve">6.50921487808228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54862928390503</t>
+    <t xml:space="preserve">6.54862880706787</t>
   </si>
   <si>
     <t xml:space="preserve">6.73410987854004</t>
@@ -2483,22 +2483,22 @@
     <t xml:space="preserve">6.87553930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91843128204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07145214080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03899383544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87206125259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95668601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90915679931641</t>
+    <t xml:space="preserve">6.91843175888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07145357131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03899335861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87206172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95668745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90915632247925</t>
   </si>
   <si>
     <t xml:space="preserve">6.87321996688843</t>
@@ -2507,10 +2507,10 @@
     <t xml:space="preserve">6.86742353439331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90336132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81062126159668</t>
+    <t xml:space="preserve">6.90336084365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81062030792236</t>
   </si>
   <si>
     <t xml:space="preserve">7.45980310440063</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">8.07304954528809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12057781219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32808494567871</t>
+    <t xml:space="preserve">8.12057685852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32808589935303</t>
   </si>
   <si>
     <t xml:space="preserve">8.37561416625977</t>
@@ -2531,13 +2531,13 @@
     <t xml:space="preserve">8.38025188446045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40691566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48226547241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41039180755615</t>
+    <t xml:space="preserve">8.40691375732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48226642608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41039085388184</t>
   </si>
   <si>
     <t xml:space="preserve">8.51124668121338</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">8.41386985778809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40807342529297</t>
+    <t xml:space="preserve">8.40807437896729</t>
   </si>
   <si>
     <t xml:space="preserve">8.42198467254639</t>
@@ -2558,34 +2558,34 @@
     <t xml:space="preserve">8.19245147705078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09623432159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79019021987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74613952636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88177299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87713479995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89104604721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82033109664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77859878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70440530776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65223979949951</t>
+    <t xml:space="preserve">8.09623336791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79018974304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74613857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8817720413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87713575363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89104413986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82033157348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77859926223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70440578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65223932266235</t>
   </si>
   <si>
     <t xml:space="preserve">7.74845790863037</t>
@@ -2594,10 +2594,10 @@
     <t xml:space="preserve">7.68238067626953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68701648712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62093925476074</t>
+    <t xml:space="preserve">7.6870174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62094020843506</t>
   </si>
   <si>
     <t xml:space="preserve">7.57920598983765</t>
@@ -2606,28 +2606,28 @@
     <t xml:space="preserve">7.46328115463257</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6476035118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72411346435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80757904052734</t>
+    <t xml:space="preserve">7.64760160446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72411298751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80757999420166</t>
   </si>
   <si>
     <t xml:space="preserve">7.88524961471558</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88409090042114</t>
+    <t xml:space="preserve">7.88408994674683</t>
   </si>
   <si>
     <t xml:space="preserve">7.91191244125366</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82844591140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78439474105835</t>
+    <t xml:space="preserve">7.82844638824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78439426422119</t>
   </si>
   <si>
     <t xml:space="preserve">7.7415018081665</t>
@@ -2639,115 +2639,115 @@
     <t xml:space="preserve">7.47719192504883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51197004318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41691112518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43777656555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43661785125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39024686813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36822271347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22911167144775</t>
+    <t xml:space="preserve">7.51196908950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41691064834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43777847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43661880493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39024782180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3682222366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22911214828491</t>
   </si>
   <si>
     <t xml:space="preserve">7.21867799758911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20592641830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22099733352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14680528640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98219013214111</t>
+    <t xml:space="preserve">7.20592594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22099685668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14680433273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98219060897827</t>
   </si>
   <si>
     <t xml:space="preserve">7.03783416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96364164352417</t>
+    <t xml:space="preserve">6.96364259719849</t>
   </si>
   <si>
     <t xml:space="preserve">7.03087949752808</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91263437271118</t>
+    <t xml:space="preserve">6.91263580322266</t>
   </si>
   <si>
     <t xml:space="preserve">6.80018711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85235357284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19317436218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07608985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03203821182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29403018951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10739040374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1410083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11086750030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11550521850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00189733505249</t>
+    <t xml:space="preserve">6.85235404968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19317579269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07609081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03203868865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29402923583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1073899269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14100790023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11086702346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1155047416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00189781188965</t>
   </si>
   <si>
     <t xml:space="preserve">6.57297372817993</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52544355392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70165061950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51616907119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27620458602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3411226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37126445770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28431844711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.096519947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.438063621521</t>
+    <t xml:space="preserve">6.52544403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70165014266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51616954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27620363235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34112215042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37126302719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2843189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09651947021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43806314468384</t>
   </si>
   <si>
     <t xml:space="preserve">5.40676259994507</t>
@@ -2756,19 +2756,19 @@
     <t xml:space="preserve">5.51921081542969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53326463699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85785627365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15534782409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9791407585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54731965065002</t>
+    <t xml:space="preserve">4.53326511383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85785579681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15534830093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97914171218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54731893539429</t>
   </si>
   <si>
     <t xml:space="preserve">3.36531543731689</t>
@@ -2777,58 +2777,58 @@
     <t xml:space="preserve">3.56123042106628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40994739532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84872460365295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96117305755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99421119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75482535362244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65744781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80931043624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66498351097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64295721054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83481383323669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08289480209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12636709213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33503198623657</t>
+    <t xml:space="preserve">3.40994763374329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84872508049011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96117353439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99421143531799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75482511520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65744853019714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8093101978302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66498374938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64295697212219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368872642517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83481407165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08289527893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12636661529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33503150939941</t>
   </si>
   <si>
     <t xml:space="preserve">4.32401990890503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10434007644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12056970596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24403095245361</t>
+    <t xml:space="preserve">4.10434055328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12056922912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24403142929077</t>
   </si>
   <si>
     <t xml:space="preserve">4.30663061141968</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">4.20229768753052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35010242462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26026010513306</t>
+    <t xml:space="preserve">4.35010194778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26026058197021</t>
   </si>
   <si>
     <t xml:space="preserve">4.46197128295898</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">4.57383871078491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74135208129883</t>
+    <t xml:space="preserve">4.74135160446167</t>
   </si>
   <si>
     <t xml:space="preserve">4.64629220962524</t>
@@ -2861,10 +2861,10 @@
     <t xml:space="preserve">4.38430070877075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4486403465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42139720916748</t>
+    <t xml:space="preserve">4.44863986968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42139673233032</t>
   </si>
   <si>
     <t xml:space="preserve">4.40516757965088</t>
@@ -2879,28 +2879,28 @@
     <t xml:space="preserve">4.4005298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27475118637085</t>
+    <t xml:space="preserve">4.27475070953369</t>
   </si>
   <si>
     <t xml:space="preserve">4.15476846694946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1750545501709</t>
+    <t xml:space="preserve">4.17505502700806</t>
   </si>
   <si>
     <t xml:space="preserve">4.51703548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31242704391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25388383865356</t>
+    <t xml:space="preserve">4.31242752075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25388479232788</t>
   </si>
   <si>
     <t xml:space="preserve">4.29851627349854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59934234619141</t>
+    <t xml:space="preserve">4.59934282302856</t>
   </si>
   <si>
     <t xml:space="preserve">4.72859954833984</t>
@@ -2909,16 +2909,16 @@
     <t xml:space="preserve">4.78192567825317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60339975357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76511573791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83293199539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08217191696167</t>
+    <t xml:space="preserve">4.60340023040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7651162147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83293151855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08217239379883</t>
   </si>
   <si>
     <t xml:space="preserve">5.04449605941772</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">5.39748907089233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45255422592163</t>
+    <t xml:space="preserve">5.45255327224731</t>
   </si>
   <si>
     <t xml:space="preserve">5.21316814422607</t>
@@ -2936,49 +2936,49 @@
     <t xml:space="preserve">5.07231855392456</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68164968490601</t>
+    <t xml:space="preserve">4.68165016174316</t>
   </si>
   <si>
     <t xml:space="preserve">4.74888610839844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7506251335144</t>
+    <t xml:space="preserve">4.75062465667725</t>
   </si>
   <si>
     <t xml:space="preserve">4.88625812530518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86770963668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85263919830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89958906173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96624660491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25374174118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02246999740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09550333023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00508117675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1169490814209</t>
+    <t xml:space="preserve">4.86771011352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85264015197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89958953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96624612808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25374221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02247047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09550285339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00508213043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11694955825806</t>
   </si>
   <si>
     <t xml:space="preserve">5.18418645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09260511398315</t>
+    <t xml:space="preserve">5.09260606765747</t>
   </si>
   <si>
     <t xml:space="preserve">5.21606588363647</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">5.15868234634399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21896409988403</t>
+    <t xml:space="preserve">5.21896457672119</t>
   </si>
   <si>
     <t xml:space="preserve">5.20679187774658</t>
@@ -2999,28 +2999,28 @@
     <t xml:space="preserve">5.00276327133179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11984872817993</t>
+    <t xml:space="preserve">5.11984825134277</t>
   </si>
   <si>
     <t xml:space="preserve">5.24910449981689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20447301864624</t>
+    <t xml:space="preserve">5.2044734954834</t>
   </si>
   <si>
     <t xml:space="preserve">5.25721979141235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31692171096802</t>
+    <t xml:space="preserve">5.3169207572937</t>
   </si>
   <si>
     <t xml:space="preserve">5.31054544448853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34184455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35401678085327</t>
+    <t xml:space="preserve">5.34184503555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35401725769043</t>
   </si>
   <si>
     <t xml:space="preserve">5.30822706222534</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">5.3412652015686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26069784164429</t>
+    <t xml:space="preserve">5.26069736480713</t>
   </si>
   <si>
     <t xml:space="preserve">5.25895833969116</t>
@@ -3038,16 +3038,16 @@
     <t xml:space="preserve">5.37488412857056</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30764675140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99638700485229</t>
+    <t xml:space="preserve">5.30764770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99638652801514</t>
   </si>
   <si>
     <t xml:space="preserve">5.23693227767944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44270133972168</t>
+    <t xml:space="preserve">5.44270038604736</t>
   </si>
   <si>
     <t xml:space="preserve">5.44733715057373</t>
@@ -3062,76 +3062,76 @@
     <t xml:space="preserve">5.47457933425903</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76323318481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74178743362427</t>
+    <t xml:space="preserve">5.76323366165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74178838729858</t>
   </si>
   <si>
     <t xml:space="preserve">5.65716218948364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61658763885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59340333938599</t>
+    <t xml:space="preserve">5.6165885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59340286254883</t>
   </si>
   <si>
     <t xml:space="preserve">5.56847953796387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58065176010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47631931304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40618324279785</t>
+    <t xml:space="preserve">5.58065128326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47631883621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40618371963501</t>
   </si>
   <si>
     <t xml:space="preserve">5.5800724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51631212234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54703330993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47747802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45719146728516</t>
+    <t xml:space="preserve">5.51631259918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54703283309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47747850418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.457190990448</t>
   </si>
   <si>
     <t xml:space="preserve">5.35053968429565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28736019134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31750106811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37836217880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46646499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58470821380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57079839706421</t>
+    <t xml:space="preserve">5.28736066818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31750011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37836122512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46646451950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58470869064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57079744338989</t>
   </si>
   <si>
     <t xml:space="preserve">5.57137775421143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73019599914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74642419815063</t>
+    <t xml:space="preserve">5.73019552230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74642467498779</t>
   </si>
   <si>
     <t xml:space="preserve">5.78641891479492</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">6.30750465393066</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26693058013916</t>
+    <t xml:space="preserve">6.266930103302</t>
   </si>
   <si>
     <t xml:space="preserve">6.23910808563232</t>
@@ -3158,16 +3158,16 @@
     <t xml:space="preserve">6.02232789993286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01189422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92958641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16491556167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02116823196411</t>
+    <t xml:space="preserve">6.01189470291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92958736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16491508483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02116870880127</t>
   </si>
   <si>
     <t xml:space="preserve">6.06753873825073</t>
@@ -3176,37 +3176,37 @@
     <t xml:space="preserve">5.99914216995239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07681274414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18578243255615</t>
+    <t xml:space="preserve">6.07681226730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18578290939331</t>
   </si>
   <si>
     <t xml:space="preserve">6.20317125320435</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19042015075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10463523864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16375637054443</t>
+    <t xml:space="preserve">6.19041967391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10463428497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16375732421875</t>
   </si>
   <si>
     <t xml:space="preserve">6.06058263778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12666130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99566459655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24954032897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22867441177368</t>
+    <t xml:space="preserve">6.12665939331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99566555023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24954175949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22867488861084</t>
   </si>
   <si>
     <t xml:space="preserve">6.24722242355347</t>
@@ -3215,109 +3215,109 @@
     <t xml:space="preserve">6.20548963546753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35735130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43386173248291</t>
+    <t xml:space="preserve">6.35735177993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43386220932007</t>
   </si>
   <si>
     <t xml:space="preserve">6.48023366928101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37242269515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12550067901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12318277359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11043167114258</t>
+    <t xml:space="preserve">6.37242317199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12550115585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12318229675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11043119430542</t>
   </si>
   <si>
     <t xml:space="preserve">6.27156686782837</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3793773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47443723678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51269197463989</t>
+    <t xml:space="preserve">6.37937784194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47443675994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51269340515137</t>
   </si>
   <si>
     <t xml:space="preserve">6.91031694412231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99146461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07840776443481</t>
+    <t xml:space="preserve">6.99146413803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07840871810913</t>
   </si>
   <si>
     <t xml:space="preserve">7.29750776290894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31837463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34851551055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5003776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46560001373291</t>
+    <t xml:space="preserve">7.31837368011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34851503372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50037717819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46559953689575</t>
   </si>
   <si>
     <t xml:space="preserve">7.44705104827881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58963966369629</t>
+    <t xml:space="preserve">7.58964061737061</t>
   </si>
   <si>
     <t xml:space="preserve">7.64180707931519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58616161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66614961624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.573410987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66730928421021</t>
+    <t xml:space="preserve">7.58616209030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66615104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57341051101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66730976104736</t>
   </si>
   <si>
     <t xml:space="preserve">7.63948774337769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66846799850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85395097732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80294227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77048301696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98494529724121</t>
+    <t xml:space="preserve">7.6684684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85394954681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80294275283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77048349380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98494482040405</t>
   </si>
   <si>
     <t xml:space="preserve">8.01624584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90611600875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01044940948486</t>
+    <t xml:space="preserve">7.9061164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01045036315918</t>
   </si>
   <si>
     <t xml:space="preserve">8.18781471252441</t>
@@ -3326,22 +3326,22 @@
     <t xml:space="preserve">8.29678535461426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.348952293396</t>
+    <t xml:space="preserve">8.34895133972168</t>
   </si>
   <si>
     <t xml:space="preserve">8.42082500457764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25968933105469</t>
+    <t xml:space="preserve">8.259690284729</t>
   </si>
   <si>
     <t xml:space="preserve">8.46139907836914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51588439941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57036972045898</t>
+    <t xml:space="preserve">8.51588535308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57036876678467</t>
   </si>
   <si>
     <t xml:space="preserve">8.51356506347656</t>
@@ -3350,46 +3350,46 @@
     <t xml:space="preserve">8.49733543395996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62485408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60166931152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57152843475342</t>
+    <t xml:space="preserve">8.62485504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60166835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5715274810791</t>
   </si>
   <si>
     <t xml:space="preserve">8.41271018981934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33504009246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50545120239258</t>
+    <t xml:space="preserve">8.33503913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50545024871826</t>
   </si>
   <si>
     <t xml:space="preserve">8.46951389312744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78281116485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40054130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27200603485107</t>
+    <t xml:space="preserve">8.78280925750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40054225921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27200698852539</t>
   </si>
   <si>
     <t xml:space="preserve">9.32146167755127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11963272094727</t>
+    <t xml:space="preserve">9.11963367462158</t>
   </si>
   <si>
     <t xml:space="preserve">8.84830284118652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43663024902344</t>
+    <t xml:space="preserve">8.43662929534912</t>
   </si>
   <si>
     <t xml:space="preserve">8.60236835479736</t>
@@ -3398,25 +3398,25 @@
     <t xml:space="preserve">8.30564308166504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49945163726807</t>
+    <t xml:space="preserve">8.49944972991943</t>
   </si>
   <si>
     <t xml:space="preserve">8.37380981445312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42460155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68122863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69726848602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76142406463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93117332458496</t>
+    <t xml:space="preserve">8.42460060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.681227684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69726753234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76142501831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93117237091064</t>
   </si>
   <si>
     <t xml:space="preserve">9.08889198303223</t>
@@ -3425,10 +3425,10 @@
     <t xml:space="preserve">9.01805305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84295654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79484081268311</t>
+    <t xml:space="preserve">8.84295749664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79483890533447</t>
   </si>
   <si>
     <t xml:space="preserve">8.86567878723145</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">8.95790481567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02206134796143</t>
+    <t xml:space="preserve">9.02206230163574</t>
   </si>
   <si>
     <t xml:space="preserve">8.82825469970703</t>
@@ -3446,22 +3446,22 @@
     <t xml:space="preserve">8.87770843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94186496734619</t>
+    <t xml:space="preserve">8.94186401367188</t>
   </si>
   <si>
     <t xml:space="preserve">8.82424545288086</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86968994140625</t>
+    <t xml:space="preserve">8.86969089508057</t>
   </si>
   <si>
     <t xml:space="preserve">9.07552623748779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06082344055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97795486450195</t>
+    <t xml:space="preserve">9.06082248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97795391082764</t>
   </si>
   <si>
     <t xml:space="preserve">9.30542182922363</t>
@@ -3473,25 +3473,25 @@
     <t xml:space="preserve">9.2679967880249</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25062084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14369297027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6796703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85610198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0579271316528</t>
+    <t xml:space="preserve">9.25061988830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14369201660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67967128753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85610103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0579290390015</t>
   </si>
   <si>
     <t xml:space="preserve">10.1755485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3158922195435</t>
+    <t xml:space="preserve">10.3158931732178</t>
   </si>
   <si>
     <t xml:space="preserve">10.6027088165283</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">10.5399112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6655054092407</t>
+    <t xml:space="preserve">10.665506362915</t>
   </si>
   <si>
     <t xml:space="preserve">10.9837713241577</t>
@@ -3515,55 +3515,55 @@
     <t xml:space="preserve">10.1288757324219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1374387741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2801599502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4457139968872</t>
+    <t xml:space="preserve">10.1374397277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2801609039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4457149505615</t>
   </si>
   <si>
     <t xml:space="preserve">10.4628419876099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7754001617432</t>
+    <t xml:space="preserve">10.7753992080688</t>
   </si>
   <si>
     <t xml:space="preserve">10.7639818191528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8010902404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.912410736084</t>
+    <t xml:space="preserve">10.8010892868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9124116897583</t>
   </si>
   <si>
     <t xml:space="preserve">10.9109840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6526613235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5613193511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6597957611084</t>
+    <t xml:space="preserve">10.652660369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5613203048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6597967147827</t>
   </si>
   <si>
     <t xml:space="preserve">10.8082256317139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7397184371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7340106964111</t>
+    <t xml:space="preserve">10.7397193908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7340097427368</t>
   </si>
   <si>
     <t xml:space="preserve">10.8910036087036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7816696166992</t>
+    <t xml:space="preserve">10.7816715240479</t>
   </si>
   <si>
     <t xml:space="preserve">10.3457984924316</t>
@@ -3578,28 +3578,28 @@
     <t xml:space="preserve">10.4886598587036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4667921066284</t>
+    <t xml:space="preserve">10.4667930603027</t>
   </si>
   <si>
     <t xml:space="preserve">10.4288902282715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4901161193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0906887054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0761098861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2204303741455</t>
+    <t xml:space="preserve">10.4901170730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0906867980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0761108398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2204294204712</t>
   </si>
   <si>
     <t xml:space="preserve">10.1227588653564</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8312339782715</t>
+    <t xml:space="preserve">10.8312349319458</t>
   </si>
   <si>
     <t xml:space="preserve">10.8705949783325</t>
@@ -3614,13 +3614,13 @@
     <t xml:space="preserve">10.686915397644</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7306489944458</t>
+    <t xml:space="preserve">10.7306480407715</t>
   </si>
   <si>
     <t xml:space="preserve">10.678168296814</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8283185958862</t>
+    <t xml:space="preserve">10.8283195495605</t>
   </si>
   <si>
     <t xml:space="preserve">11.0047092437744</t>
@@ -3632,34 +3632,34 @@
     <t xml:space="preserve">10.7364797592163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9376525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1636056900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2160873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2787704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2583608627319</t>
+    <t xml:space="preserve">10.9376516342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1636066436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2160863876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2787714004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2583618164062</t>
   </si>
   <si>
     <t xml:space="preserve">11.7190160751343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7394275665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8502159118652</t>
+    <t xml:space="preserve">11.739426612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8502149581909</t>
   </si>
   <si>
     <t xml:space="preserve">11.9143590927124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0338954925537</t>
+    <t xml:space="preserve">12.0338945388794</t>
   </si>
   <si>
     <t xml:space="preserve">12.1709260940552</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">12.7219648361206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.737998008728</t>
+    <t xml:space="preserve">12.7379989624023</t>
   </si>
   <si>
     <t xml:space="preserve">12.5601511001587</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">12.5003824234009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677244186401</t>
+    <t xml:space="preserve">12.3677253723145</t>
   </si>
   <si>
     <t xml:space="preserve">12.3167037963867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3181600570679</t>
+    <t xml:space="preserve">12.3181610107422</t>
   </si>
   <si>
     <t xml:space="preserve">12.3604373931885</t>
@@ -3710,22 +3710,22 @@
     <t xml:space="preserve">12.3852186203003</t>
   </si>
   <si>
-    <t xml:space="preserve">12.436240196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2758855819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2613086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0659666061401</t>
+    <t xml:space="preserve">12.4362392425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2758846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2613077163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0659675598145</t>
   </si>
   <si>
     <t xml:space="preserve">12.1738414764404</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3414840698242</t>
+    <t xml:space="preserve">12.3414850234985</t>
   </si>
   <si>
     <t xml:space="preserve">12.1942501068115</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">12.0164022445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429269790649</t>
+    <t xml:space="preserve">11.8429279327393</t>
   </si>
   <si>
     <t xml:space="preserve">11.8370971679688</t>
@@ -3752,13 +3752,13 @@
     <t xml:space="preserve">11.4332942962646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0222034454346</t>
+    <t xml:space="preserve">11.0222024917603</t>
   </si>
   <si>
     <t xml:space="preserve">11.049901008606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4289207458496</t>
+    <t xml:space="preserve">11.4289216995239</t>
   </si>
   <si>
     <t xml:space="preserve">11.3633213043213</t>
@@ -3767,19 +3767,19 @@
     <t xml:space="preserve">11.4814004898071</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5790710449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4347515106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5324211120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9201889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8006534576416</t>
+    <t xml:space="preserve">11.5790700912476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4347524642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5324220657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9201898574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">11.9318523406982</t>
@@ -3788,31 +3788,31 @@
     <t xml:space="preserve">12.7175903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7146739959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0280952453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1170196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0834903717041</t>
+    <t xml:space="preserve">12.714674949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0280961990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.117018699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0834913253784</t>
   </si>
   <si>
     <t xml:space="preserve">13.1330547332764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4829196929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5645561218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.369213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0062284469604</t>
+    <t xml:space="preserve">13.4829187393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5645551681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3692121505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0062294006348</t>
   </si>
   <si>
     <t xml:space="preserve">13.1053562164307</t>
@@ -3821,13 +3821,13 @@
     <t xml:space="preserve">12.6388702392578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4930925369263</t>
+    <t xml:space="preserve">12.4930934906006</t>
   </si>
   <si>
     <t xml:space="preserve">12.5411996841431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5732698440552</t>
+    <t xml:space="preserve">12.5732707977295</t>
   </si>
   <si>
     <t xml:space="preserve">12.6024265289307</t>
@@ -3836,25 +3836,25 @@
     <t xml:space="preserve">12.485803604126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5105857849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4041690826416</t>
+    <t xml:space="preserve">12.5105867385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4041700363159</t>
   </si>
   <si>
     <t xml:space="preserve">12.2744283676147</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4814310073853</t>
+    <t xml:space="preserve">12.4814319610596</t>
   </si>
   <si>
     <t xml:space="preserve">12.567440032959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4537334442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0980367660522</t>
+    <t xml:space="preserve">12.4537343978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0980377197266</t>
   </si>
   <si>
     <t xml:space="preserve">12.1636371612549</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">12.6898918151855</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2525615692139</t>
+    <t xml:space="preserve">12.2525596618652</t>
   </si>
   <si>
     <t xml:space="preserve">11.7044401168823</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">11.6854887008667</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0645084381104</t>
+    <t xml:space="preserve">12.0645093917847</t>
   </si>
   <si>
     <t xml:space="preserve">12.2219486236572</t>
@@ -3887,37 +3887,37 @@
     <t xml:space="preserve">12.2365255355835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3444004058838</t>
+    <t xml:space="preserve">12.3444013595581</t>
   </si>
   <si>
     <t xml:space="preserve">11.9770421981812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1432285308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0426416397095</t>
+    <t xml:space="preserve">12.1432275772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">11.8575048446655</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7627506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0674238204956</t>
+    <t xml:space="preserve">11.762749671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0674247741699</t>
   </si>
   <si>
     <t xml:space="preserve">11.6373825073242</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0790872573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.153431892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2642240524292</t>
+    <t xml:space="preserve">12.0790863037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1534328460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2642230987549</t>
   </si>
   <si>
     <t xml:space="preserve">12.2860908508301</t>
@@ -3926,10 +3926,10 @@
     <t xml:space="preserve">12.2671394348145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4114589691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3123292922974</t>
+    <t xml:space="preserve">12.4114580154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3123302459717</t>
   </si>
   <si>
     <t xml:space="preserve">12.2292366027832</t>
@@ -3938,31 +3938,31 @@
     <t xml:space="preserve">12.2598495483398</t>
   </si>
   <si>
-    <t xml:space="preserve">12.284631729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2817163467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7656955718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8079719543457</t>
+    <t xml:space="preserve">12.2846326828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.281717300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.765697479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.80797290802</t>
   </si>
   <si>
     <t xml:space="preserve">12.7992248535156</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5995092391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7190494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7321672439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7904787063599</t>
+    <t xml:space="preserve">12.5995101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.719048500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7321681976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7904777526855</t>
   </si>
   <si>
     <t xml:space="preserve">12.857536315918</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">12.9143896102905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7817325592041</t>
+    <t xml:space="preserve">12.7817316055298</t>
   </si>
   <si>
     <t xml:space="preserve">12.7117595672607</t>
@@ -3983,10 +3983,10 @@
     <t xml:space="preserve">13.0368423461914</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0295515060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1855354309082</t>
+    <t xml:space="preserve">13.0295524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1855344772339</t>
   </si>
   <si>
     <t xml:space="preserve">13.0878639221191</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">13.093695640564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248802185059</t>
+    <t xml:space="preserve">12.7248792648315</t>
   </si>
   <si>
     <t xml:space="preserve">12.3983383178711</t>
@@ -4010,22 +4010,22 @@
     <t xml:space="preserve">11.3458280563354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3472852706909</t>
+    <t xml:space="preserve">11.3472862243652</t>
   </si>
   <si>
     <t xml:space="preserve">11.0353231430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.662163734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6096849441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4755697250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8749990463257</t>
+    <t xml:space="preserve">11.6621646881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6096839904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4755687713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8749980926514</t>
   </si>
   <si>
     <t xml:space="preserve">12.2977523803711</t>
@@ -4037,25 +4037,25 @@
     <t xml:space="preserve">11.9887046813965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0193185806274</t>
+    <t xml:space="preserve">12.0193176269531</t>
   </si>
   <si>
     <t xml:space="preserve">11.9289360046387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8589639663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8924913406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.963921546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5309638977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8866624832153</t>
+    <t xml:space="preserve">11.8589630126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8924922943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9639234542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5309648513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.886661529541</t>
   </si>
   <si>
     <t xml:space="preserve">11.9916200637817</t>
@@ -4067,22 +4067,22 @@
     <t xml:space="preserve">12.1621799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301221847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9114751815796</t>
+    <t xml:space="preserve">12.6301231384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9114742279053</t>
   </si>
   <si>
     <t xml:space="preserve">13.4318971633911</t>
   </si>
   <si>
-    <t xml:space="preserve">13.299241065979</t>
+    <t xml:space="preserve">13.2992401123047</t>
   </si>
   <si>
     <t xml:space="preserve">13.1213932037354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.020806312561</t>
+    <t xml:space="preserve">13.0208053588867</t>
   </si>
   <si>
     <t xml:space="preserve">13.1490907669067</t>
@@ -4097,7 +4097,7 @@
     <t xml:space="preserve">13.8298692703247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9508628845215</t>
+    <t xml:space="preserve">13.9508638381958</t>
   </si>
   <si>
     <t xml:space="preserve">13.9173345565796</t>
@@ -4106,13 +4106,13 @@
     <t xml:space="preserve">13.8415307998657</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6986694335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2132320404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1009521484375</t>
+    <t xml:space="preserve">13.6986684799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2132329940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1009531021118</t>
   </si>
   <si>
     <t xml:space="preserve">12.6855192184448</t>
@@ -4124,7 +4124,7 @@
     <t xml:space="preserve">12.4406147003174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3691816329956</t>
+    <t xml:space="preserve">12.3691825866699</t>
   </si>
   <si>
     <t xml:space="preserve">12.6417856216431</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">12.4683122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3618936538696</t>
+    <t xml:space="preserve">12.3618927001953</t>
   </si>
   <si>
     <t xml:space="preserve">12.223406791687</t>
@@ -4160,7 +4160,7 @@
     <t xml:space="preserve">12.5149602890015</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665534973145</t>
+    <t xml:space="preserve">12.1665515899658</t>
   </si>
   <si>
     <t xml:space="preserve">11.8837461471558</t>
@@ -4169,10 +4169,10 @@
     <t xml:space="preserve">12.4391555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6869468688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3065004348755</t>
+    <t xml:space="preserve">11.6869478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3064994812012</t>
   </si>
   <si>
     <t xml:space="preserve">11.1052961349487</t>
@@ -4184,13 +4184,13 @@
     <t xml:space="preserve">10.9041242599487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0746517181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43031692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42594337463379</t>
+    <t xml:space="preserve">10.074652671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43031787872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42594432830811</t>
   </si>
   <si>
     <t xml:space="preserve">10.5834140777588</t>
@@ -4199,13 +4199,13 @@
     <t xml:space="preserve">9.81808471679688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83703517913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2043943405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3181009292603</t>
+    <t xml:space="preserve">9.8370361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2043933868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3180999755859</t>
   </si>
   <si>
     <t xml:space="preserve">10.9770126342773</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">10.7262754440308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6883726119995</t>
+    <t xml:space="preserve">10.6883735656738</t>
   </si>
   <si>
     <t xml:space="preserve">10.6475563049316</t>
@@ -4226,7 +4226,7 @@
     <t xml:space="preserve">10.6373510360718</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5046949386597</t>
+    <t xml:space="preserve">10.5046939849854</t>
   </si>
   <si>
     <t xml:space="preserve">10.5207300186157</t>
@@ -4235,10 +4235,10 @@
     <t xml:space="preserve">10.5323915481567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2321214675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0542736053467</t>
+    <t xml:space="preserve">11.2321224212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.054274559021</t>
   </si>
   <si>
     <t xml:space="preserve">10.7875022888184</t>
@@ -4250,7 +4250,7 @@
     <t xml:space="preserve">10.8516435623169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4522142410278</t>
+    <t xml:space="preserve">10.4522151947021</t>
   </si>
   <si>
     <t xml:space="preserve">9.98718547821045</t>
@@ -4259,10 +4259,10 @@
     <t xml:space="preserve">9.86910629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0338354110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1475410461426</t>
+    <t xml:space="preserve">10.0338344573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1475400924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.1358785629272</t>
@@ -4271,16 +4271,16 @@
     <t xml:space="preserve">10.1854429244995</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2583312988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5054626464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5621299743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6644458770752</t>
+    <t xml:space="preserve">10.2583322525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5054616928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5621309280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6644449234009</t>
   </si>
   <si>
     <t xml:space="preserve">10.3197212219238</t>
@@ -4292,16 +4292,16 @@
     <t xml:space="preserve">9.75304889678955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94823551177979</t>
+    <t xml:space="preserve">9.9482364654541</t>
   </si>
   <si>
     <t xml:space="preserve">10.0710134506226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2174053192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9088830947876</t>
+    <t xml:space="preserve">10.2174043655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90888404846191</t>
   </si>
   <si>
     <t xml:space="preserve">10.2237005233765</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">9.99545764923096</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1119403839111</t>
+    <t xml:space="preserve">10.1119394302368</t>
   </si>
   <si>
     <t xml:space="preserve">10.4125909805298</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">10.6817607879639</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3386087417603</t>
+    <t xml:space="preserve">10.3386096954346</t>
   </si>
   <si>
     <t xml:space="preserve">10.5306482315063</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">11.064263343811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9304656982422</t>
+    <t xml:space="preserve">10.9304666519165</t>
   </si>
   <si>
     <t xml:space="preserve">11.0249118804932</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">9.56415843963623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63027095794678</t>
+    <t xml:space="preserve">9.63027000427246</t>
   </si>
   <si>
     <t xml:space="preserve">9.74990081787109</t>
@@ -4415,13 +4415,13 @@
     <t xml:space="preserve">9.82230758666992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61295509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78138256072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77508544921875</t>
+    <t xml:space="preserve">9.61295413970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78138160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77508640289307</t>
   </si>
   <si>
     <t xml:space="preserve">9.86953067779541</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">8.81804084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44295406341553</t>
+    <t xml:space="preserve">9.44295310974121</t>
   </si>
   <si>
     <t xml:space="preserve">9.80499362945557</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">9.60193634033203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67906761169434</t>
+    <t xml:space="preserve">9.67906665802002</t>
   </si>
   <si>
     <t xml:space="preserve">9.4445276260376</t>
@@ -4472,10 +4472,10 @@
     <t xml:space="preserve">10.014347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94981002807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89156723022461</t>
+    <t xml:space="preserve">9.94980907440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89156913757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.9545316696167</t>
@@ -4502,16 +4502,16 @@
     <t xml:space="preserve">11.2405614852905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3523216247559</t>
+    <t xml:space="preserve">11.3523225784302</t>
   </si>
   <si>
     <t xml:space="preserve">11.2736177444458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2799139022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6340837478638</t>
+    <t xml:space="preserve">11.2799129486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6340827941895</t>
   </si>
   <si>
     <t xml:space="preserve">11.3381547927856</t>
@@ -4520,40 +4520,40 @@
     <t xml:space="preserve">11.4971380233765</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5585279464722</t>
+    <t xml:space="preserve">11.5585269927979</t>
   </si>
   <si>
     <t xml:space="preserve">11.673436164856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7269554138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5223236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7049179077148</t>
+    <t xml:space="preserve">11.726954460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5223226547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7049169540405</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9021320343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0500965118408</t>
+    <t xml:space="preserve">10.9021329879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0500974655151</t>
   </si>
   <si>
     <t xml:space="preserve">11.1681537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.089448928833</t>
+    <t xml:space="preserve">11.0894498825073</t>
   </si>
   <si>
     <t xml:space="preserve">10.8139839172363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8265771865845</t>
+    <t xml:space="preserve">10.8265762329102</t>
   </si>
   <si>
     <t xml:space="preserve">10.7195386886597</t>
@@ -4589,13 +4589,13 @@
     <t xml:space="preserve">10.6597232818604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7557439804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7699098587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5463886260986</t>
+    <t xml:space="preserve">10.7557430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7699089050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5463876724243</t>
   </si>
   <si>
     <t xml:space="preserve">10.6329641342163</t>
@@ -4610,37 +4610,37 @@
     <t xml:space="preserve">10.237868309021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0111989974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1009216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0946264266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65860462188721</t>
+    <t xml:space="preserve">10.0111999511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1009225845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0946254730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65860366821289</t>
   </si>
   <si>
     <t xml:space="preserve">9.84906768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93564224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86480903625488</t>
+    <t xml:space="preserve">9.93564319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8648099899292</t>
   </si>
   <si>
     <t xml:space="preserve">9.68064117431641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5893440246582</t>
+    <t xml:space="preserve">9.58934307098389</t>
   </si>
   <si>
     <t xml:space="preserve">9.69638156890869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5972146987915</t>
+    <t xml:space="preserve">9.59721374511719</t>
   </si>
   <si>
     <t xml:space="preserve">9.82703113555908</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">10.2488870620728</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2063865661621</t>
+    <t xml:space="preserve">10.2063856124878</t>
   </si>
   <si>
     <t xml:space="preserve">10.3685169219971</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">10.6487045288086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.744725227356</t>
+    <t xml:space="preserve">10.7447233200073</t>
   </si>
   <si>
     <t xml:space="preserve">10.7305574417114</t>
@@ -4679,10 +4679,10 @@
     <t xml:space="preserve">10.7510204315186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8092622756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4566669464111</t>
+    <t xml:space="preserve">10.8092613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4566659927368</t>
   </si>
   <si>
     <t xml:space="preserve">10.8297252655029</t>
@@ -4694,19 +4694,19 @@
     <t xml:space="preserve">11.1429681777954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1980609893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.339729309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4247303009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2153759002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1036157608032</t>
+    <t xml:space="preserve">11.1980619430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3397302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.424729347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2153768539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1036167144775</t>
   </si>
   <si>
     <t xml:space="preserve">11.3413028717041</t>
@@ -4715,16 +4715,16 @@
     <t xml:space="preserve">11.4451932907104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5553789138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3838033676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5333423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5301942825317</t>
+    <t xml:space="preserve">11.5553798675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3838043212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5333414077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5301933288574</t>
   </si>
   <si>
     <t xml:space="preserve">11.4546375274658</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">11.5774164199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206583023071</t>
+    <t xml:space="preserve">11.7206592559814</t>
   </si>
   <si>
     <t xml:space="preserve">11.7332515716553</t>
@@ -4760,10 +4760,10 @@
     <t xml:space="preserve">10.8486137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8612060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9336137771606</t>
+    <t xml:space="preserve">10.8612070083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.933614730835</t>
   </si>
   <si>
     <t xml:space="preserve">10.6675939559937</t>
@@ -4775,31 +4775,31 @@
     <t xml:space="preserve">10.3811092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3559236526489</t>
+    <t xml:space="preserve">10.3559246063232</t>
   </si>
   <si>
     <t xml:space="preserve">10.32444190979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5290746688843</t>
+    <t xml:space="preserve">10.52907371521</t>
   </si>
   <si>
     <t xml:space="preserve">10.4393510818481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7415761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8816690444946</t>
+    <t xml:space="preserve">10.7415752410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8816699981689</t>
   </si>
   <si>
     <t xml:space="preserve">11.1697282791138</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2862100601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3696365356445</t>
+    <t xml:space="preserve">11.2862110137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3696374893188</t>
   </si>
   <si>
     <t xml:space="preserve">11.5427865982056</t>
@@ -4811,19 +4811,19 @@
     <t xml:space="preserve">11.6246395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1996355056763</t>
+    <t xml:space="preserve">11.199634552002</t>
   </si>
   <si>
     <t xml:space="preserve">11.2673206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3035259246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2295427322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9477806091309</t>
+    <t xml:space="preserve">11.3035249710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2295417785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9477815628052</t>
   </si>
   <si>
     <t xml:space="preserve">11.037504196167</t>
@@ -4832,7 +4832,7 @@
     <t xml:space="preserve">11.0312070846558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0343570709229</t>
+    <t xml:space="preserve">11.0343561172485</t>
   </si>
   <si>
     <t xml:space="preserve">10.95250415802</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">11.0611152648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1728754043579</t>
+    <t xml:space="preserve">11.1728763580322</t>
   </si>
   <si>
     <t xml:space="preserve">11.3145446777344</t>
@@ -4850,43 +4850,43 @@
     <t xml:space="preserve">11.4026927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9693651199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9630689620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8686227798462</t>
+    <t xml:space="preserve">11.9693641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9630680084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8686237335205</t>
   </si>
   <si>
     <t xml:space="preserve">11.8749198913574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9016790390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3392753601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1299209594727</t>
+    <t xml:space="preserve">11.9016780853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3392763137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.129921913147</t>
   </si>
   <si>
     <t xml:space="preserve">12.2054777145386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2589960098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4903879165649</t>
+    <t xml:space="preserve">12.258996963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4903869628906</t>
   </si>
   <si>
     <t xml:space="preserve">12.517147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5533514022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7013158798218</t>
+    <t xml:space="preserve">12.5533504486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7013149261475</t>
   </si>
   <si>
     <t xml:space="preserve">12.4888134002686</t>
@@ -4895,7 +4895,7 @@
     <t xml:space="preserve">12.7642793655396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2254867553711</t>
+    <t xml:space="preserve">13.2254877090454</t>
   </si>
   <si>
     <t xml:space="preserve">12.946873664856</t>
@@ -4907,25 +4907,25 @@
     <t xml:space="preserve">13.0287265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4238204956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.515118598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9054918289185</t>
+    <t xml:space="preserve">13.4238214492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5151195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9054927825928</t>
   </si>
   <si>
     <t xml:space="preserve">13.8330850601196</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7968807220459</t>
+    <t xml:space="preserve">13.7968816757202</t>
   </si>
   <si>
     <t xml:space="preserve">13.7653980255127</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5387296676636</t>
+    <t xml:space="preserve">13.5387306213379</t>
   </si>
   <si>
     <t xml:space="preserve">13.2915983200073</t>
@@ -4934,19 +4934,19 @@
     <t xml:space="preserve">12.7532606124878</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9027986526489</t>
+    <t xml:space="preserve">12.9027976989746</t>
   </si>
   <si>
     <t xml:space="preserve">12.4305725097656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265913009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4714984893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7390947341919</t>
+    <t xml:space="preserve">12.5265922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4714994430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7390937805176</t>
   </si>
   <si>
     <t xml:space="preserve">12.7469635009766</t>
@@ -4955,34 +4955,34 @@
     <t xml:space="preserve">12.7343711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7737226486206</t>
+    <t xml:space="preserve">12.5155725479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7737236022949</t>
   </si>
   <si>
     <t xml:space="preserve">12.7910394668579</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9153919219971</t>
+    <t xml:space="preserve">12.9153909683228</t>
   </si>
   <si>
     <t xml:space="preserve">13.050763130188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1719675064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.120023727417</t>
+    <t xml:space="preserve">13.171968460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1200227737427</t>
   </si>
   <si>
     <t xml:space="preserve">12.9390029907227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6824264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7878894805908</t>
+    <t xml:space="preserve">12.682427406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7878904342651</t>
   </si>
   <si>
     <t xml:space="preserve">13.1829862594604</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">13.2191896438599</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2443752288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5088214874268</t>
+    <t xml:space="preserve">13.2443742752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5088224411011</t>
   </si>
   <si>
     <t xml:space="preserve">13.3624324798584</t>
@@ -5006,7 +5006,7 @@
     <t xml:space="preserve">13.3545618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6320543289185</t>
+    <t xml:space="preserve">12.6320552825928</t>
   </si>
   <si>
     <t xml:space="preserve">12.5486288070679</t>
@@ -5054,13 +5054,13 @@
     <t xml:space="preserve">12.770318031311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6242437362671</t>
+    <t xml:space="preserve">12.6242446899414</t>
   </si>
   <si>
     <t xml:space="preserve">12.7514142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0143480300903</t>
+    <t xml:space="preserve">13.014347076416</t>
   </si>
   <si>
     <t xml:space="preserve">13.2600955963135</t>
@@ -5069,13 +5069,13 @@
     <t xml:space="preserve">13.1655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0934000015259</t>
+    <t xml:space="preserve">13.0933990478516</t>
   </si>
   <si>
     <t xml:space="preserve">12.5623769760132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4334878921509</t>
+    <t xml:space="preserve">12.4334888458252</t>
   </si>
   <si>
     <t xml:space="preserve">12.6929845809937</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">13.5470886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5178737640381</t>
+    <t xml:space="preserve">13.5178747177124</t>
   </si>
   <si>
     <t xml:space="preserve">13.6261405944824</t>
@@ -5132,13 +5132,13 @@
     <t xml:space="preserve">13.2033843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0813703536987</t>
+    <t xml:space="preserve">13.0813694000244</t>
   </si>
   <si>
     <t xml:space="preserve">12.9885702133179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0469999313354</t>
+    <t xml:space="preserve">13.0469989776611</t>
   </si>
   <si>
     <t xml:space="preserve">13.1587028503418</t>
@@ -5153,7 +5153,7 @@
     <t xml:space="preserve">13.8254890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.999059677124</t>
+    <t xml:space="preserve">13.9990587234497</t>
   </si>
   <si>
     <t xml:space="preserve">13.9681262969971</t>
@@ -5171,7 +5171,7 @@
     <t xml:space="preserve">13.9767189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0437412261963</t>
+    <t xml:space="preserve">14.043740272522</t>
   </si>
   <si>
     <t xml:space="preserve">14.3736963272095</t>
@@ -5180,52 +5180,52 @@
     <t xml:space="preserve">14.4458742141724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3547925949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2671489715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2551193237305</t>
+    <t xml:space="preserve">14.3547916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2671480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2551183700562</t>
   </si>
   <si>
     <t xml:space="preserve">14.3152666091919</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1863784790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4149408340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4235334396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8050441741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.593846321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650459289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0200386047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192983627319</t>
+    <t xml:space="preserve">14.1863775253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4149398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4235324859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8050451278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5938453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650449752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0200366973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192974090576</t>
   </si>
   <si>
     <t xml:space="preserve">15.5147933959961</t>
   </si>
   <si>
-    <t xml:space="preserve">15.373875617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3446598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2982606887817</t>
+    <t xml:space="preserve">15.3738746643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3446588516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2982597351074</t>
   </si>
   <si>
     <t xml:space="preserve">15.0834455490112</t>
@@ -5243,31 +5243,31 @@
     <t xml:space="preserve">14.5197706222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3221406936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1571636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0523338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3015184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3633852005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.378851890564</t>
+    <t xml:space="preserve">14.3221397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1571626663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0523328781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3015174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3633842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3788509368896</t>
   </si>
   <si>
     <t xml:space="preserve">14.2173109054565</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3668222427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5489845275879</t>
+    <t xml:space="preserve">14.3668212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5489854812622</t>
   </si>
   <si>
     <t xml:space="preserve">14.7964515686035</t>
@@ -5276,10 +5276,10 @@
     <t xml:space="preserve">14.7500524520874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7586450576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4355630874634</t>
+    <t xml:space="preserve">14.7586460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4355621337891</t>
   </si>
   <si>
     <t xml:space="preserve">14.4493112564087</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">14.5386743545532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5661697387695</t>
+    <t xml:space="preserve">14.5661706924438</t>
   </si>
   <si>
     <t xml:space="preserve">14.6074151992798</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">15.2673263549805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1006298065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3859052658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2827930450439</t>
+    <t xml:space="preserve">15.1006288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3859033584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2827920913696</t>
   </si>
   <si>
     <t xml:space="preserve">15.5113563537598</t>
@@ -5321,43 +5321,43 @@
     <t xml:space="preserve">15.9959783554077</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6058759689331</t>
+    <t xml:space="preserve">15.6058750152588</t>
   </si>
   <si>
     <t xml:space="preserve">15.712423324585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5251054763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4512090682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.607593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6471185684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.55260181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999782562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.231237411499</t>
+    <t xml:space="preserve">15.5251045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4512071609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6075925827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6471195220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5526008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2312364578247</t>
   </si>
   <si>
     <t xml:space="preserve">15.3137273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4649562835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9444236755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2726612091064</t>
+    <t xml:space="preserve">15.464955329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9444227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2726593017578</t>
   </si>
   <si>
     <t xml:space="preserve">16.246883392334</t>
@@ -5369,25 +5369,25 @@
     <t xml:space="preserve">16.0681571960449</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2348537445068</t>
+    <t xml:space="preserve">16.2348518371582</t>
   </si>
   <si>
     <t xml:space="preserve">16.1300239562988</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5405721664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1642160415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4855785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2759189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1848382949829</t>
+    <t xml:space="preserve">15.5405702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1642150878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.485577583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.275918006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1848392486572</t>
   </si>
   <si>
     <t xml:space="preserve">14.8806600570679</t>
@@ -5396,16 +5396,16 @@
     <t xml:space="preserve">14.6417865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.122971534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4168376922607</t>
+    <t xml:space="preserve">15.1229705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4168367385864</t>
   </si>
   <si>
     <t xml:space="preserve">15.7553873062134</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0647201538086</t>
+    <t xml:space="preserve">16.06471824646</t>
   </si>
   <si>
     <t xml:space="preserve">15.7467937469482</t>
@@ -5417,16 +5417,16 @@
     <t xml:space="preserve">15.5749416351318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7364816665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0440998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2211036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.894585609436</t>
+    <t xml:space="preserve">15.7364826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0440979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2211055755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8945846557617</t>
   </si>
   <si>
     <t xml:space="preserve">15.8705272674561</t>
@@ -5441,7 +5441,7 @@
     <t xml:space="preserve">16.1094017028809</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0939350128174</t>
+    <t xml:space="preserve">16.0939331054688</t>
   </si>
   <si>
     <t xml:space="preserve">16.9394454956055</t>
@@ -5450,7 +5450,7 @@
     <t xml:space="preserve">17.1009864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2754154205322</t>
+    <t xml:space="preserve">17.2754173278809</t>
   </si>
   <si>
     <t xml:space="preserve">17.4472694396973</t>
@@ -5459,7 +5459,7 @@
     <t xml:space="preserve">17.5847511291504</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0960102081299</t>
+    <t xml:space="preserve">18.0960083007812</t>
   </si>
   <si>
     <t xml:space="preserve">17.9714183807373</t>
@@ -5471,7 +5471,7 @@
     <t xml:space="preserve">18.0530471801758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0186767578125</t>
+    <t xml:space="preserve">18.0186748504639</t>
   </si>
   <si>
     <t xml:space="preserve">17.9671211242676</t>
@@ -5489,28 +5489,28 @@
     <t xml:space="preserve">18.289342880249</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2506771087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2549743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2377891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2420845031738</t>
+    <t xml:space="preserve">18.250675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2549724578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2377872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2420825958252</t>
   </si>
   <si>
     <t xml:space="preserve">18.2034168243408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1733436584473</t>
+    <t xml:space="preserve">18.1733417510986</t>
   </si>
   <si>
     <t xml:space="preserve">18.19482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5718612670898</t>
+    <t xml:space="preserve">17.5718631744385</t>
   </si>
   <si>
     <t xml:space="preserve">17.5503787994385</t>
@@ -5522,7 +5522,7 @@
     <t xml:space="preserve">17.7608985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620845794678</t>
+    <t xml:space="preserve">17.6620826721191</t>
   </si>
   <si>
     <t xml:space="preserve">17.8554172515869</t>
@@ -5534,7 +5534,7 @@
     <t xml:space="preserve">17.5761566162109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3011951446533</t>
+    <t xml:space="preserve">17.3011932373047</t>
   </si>
   <si>
     <t xml:space="preserve">17.11301612854</t>
@@ -5543,13 +5543,13 @@
     <t xml:space="preserve">16.8741416931152</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0459938049316</t>
+    <t xml:space="preserve">17.045991897583</t>
   </si>
   <si>
     <t xml:space="preserve">16.9016380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9274158477783</t>
+    <t xml:space="preserve">16.927417755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.8122749328613</t>
@@ -5561,7 +5561,7 @@
     <t xml:space="preserve">16.6885433197021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7761859893799</t>
+    <t xml:space="preserve">16.7761878967285</t>
   </si>
   <si>
     <t xml:space="preserve">16.7332248687744</t>
@@ -5570,7 +5570,7 @@
     <t xml:space="preserve">17.374231338501</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6105289459229</t>
+    <t xml:space="preserve">17.6105270385742</t>
   </si>
   <si>
     <t xml:space="preserve">17.8468246459961</t>
@@ -5588,16 +5588,16 @@
     <t xml:space="preserve">18.624454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0197124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3032684326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4536380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2388229370117</t>
+    <t xml:space="preserve">19.0197143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3032703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4536399841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2388248443604</t>
   </si>
   <si>
     <t xml:space="preserve">19.3977890014648</t>
@@ -5621,10 +5621,10 @@
     <t xml:space="preserve">20.8198623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1463832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8843078613281</t>
+    <t xml:space="preserve">21.1463813781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8843059539795</t>
   </si>
   <si>
     <t xml:space="preserve">20.8327522277832</t>
@@ -5636,13 +5636,13 @@
     <t xml:space="preserve">20.7382335662842</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9960117340088</t>
+    <t xml:space="preserve">20.9960098266602</t>
   </si>
   <si>
     <t xml:space="preserve">21.1592712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2494926452637</t>
+    <t xml:space="preserve">21.249490737915</t>
   </si>
   <si>
     <t xml:space="preserve">21.4814929962158</t>
@@ -5663,7 +5663,7 @@
     <t xml:space="preserve">21.8552703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7994194030762</t>
+    <t xml:space="preserve">21.7994213104248</t>
   </si>
   <si>
     <t xml:space="preserve">22.3665313720703</t>
@@ -5672,7 +5672,7 @@
     <t xml:space="preserve">22.4696407318115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8649024963379</t>
+    <t xml:space="preserve">22.8649005889893</t>
   </si>
   <si>
     <t xml:space="preserve">22.9078636169434</t>
@@ -5681,19 +5681,19 @@
     <t xml:space="preserve">23.1269760131836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1441612243652</t>
+    <t xml:space="preserve">23.1441593170166</t>
   </si>
   <si>
     <t xml:space="preserve">23.3331985473633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8391227722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9293460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6371974945068</t>
+    <t xml:space="preserve">22.8391246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9293441772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6371955871582</t>
   </si>
   <si>
     <t xml:space="preserve">21.8939361572266</t>
@@ -5702,10 +5702,10 @@
     <t xml:space="preserve">21.4943809509277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5244541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1377906799316</t>
+    <t xml:space="preserve">21.5244560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.137788772583</t>
   </si>
   <si>
     <t xml:space="preserve">21.3912696838379</t>
@@ -5714,25 +5714,25 @@
     <t xml:space="preserve">21.5459365844727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6791210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6619358062744</t>
+    <t xml:space="preserve">21.6791229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.661937713623</t>
   </si>
   <si>
     <t xml:space="preserve">20.9530487060547</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4771957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8370494842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8542346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9229755401611</t>
+    <t xml:space="preserve">21.4771976470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8370475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8542327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9229736328125</t>
   </si>
   <si>
     <t xml:space="preserve">21.2375450134277</t>
@@ -6798,6 +6798,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.3730001449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64200019836426</t>
   </si>
 </sst>
 </file>
@@ -71824,7 +71827,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6502777778</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>31615917</v>
@@ -71845,6 +71848,32 @@
         <v>2261</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6518634259</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>23049984</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>8.73700046539307</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>8.50699996948242</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>8.69999980926514</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>8.64200019836426</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>2262</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2263" uniqueCount="2263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="2264">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">4.13119506835938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91636323928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78795719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63239026069641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757278442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71881580352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66943001747131</t>
+    <t xml:space="preserve">3.91636347770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7879581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63238978385925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757349967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71881675720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66942977905273</t>
   </si>
   <si>
     <t xml:space="preserve">3.37804818153381</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">3.25705122947693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3261923789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26198959350586</t>
+    <t xml:space="preserve">3.32619214057922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26198983192444</t>
   </si>
   <si>
     <t xml:space="preserve">3.46200609207153</t>
@@ -95,19 +95,19 @@
     <t xml:space="preserve">3.43237352371216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18544054031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16321635246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16074657440186</t>
+    <t xml:space="preserve">3.18544030189514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16321611404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16074681282043</t>
   </si>
   <si>
     <t xml:space="preserve">3.07678961753845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9533224105835</t>
+    <t xml:space="preserve">2.95332336425781</t>
   </si>
   <si>
     <t xml:space="preserve">2.91628289222717</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">2.65700316429138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58292269706726</t>
+    <t xml:space="preserve">2.58292293548584</t>
   </si>
   <si>
     <t xml:space="preserve">2.73355269432068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59280014038086</t>
+    <t xml:space="preserve">2.59279990196228</t>
   </si>
   <si>
     <t xml:space="preserve">2.68416595458984</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">2.89899754524231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87924337387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81010150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92616009712219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83973336219788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72614407539368</t>
+    <t xml:space="preserve">2.87924265861511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81010174751282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92616033554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83973360061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72614431381226</t>
   </si>
   <si>
     <t xml:space="preserve">3.00517916679382</t>
@@ -161,19 +161,19 @@
     <t xml:space="preserve">3.13358402252197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29902982711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45212912559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46447467803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44225096702576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28915238380432</t>
+    <t xml:space="preserve">3.2990300655365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45212841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46447539329529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44225144386292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2891526222229</t>
   </si>
   <si>
     <t xml:space="preserve">3.30643796920776</t>
@@ -185,58 +185,58 @@
     <t xml:space="preserve">3.35088562965393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44718956947327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36076307296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44471979141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42496609687805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5163311958313</t>
+    <t xml:space="preserve">3.44719004631042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36076378822327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472026824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42496585845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51633095741272</t>
   </si>
   <si>
     <t xml:space="preserve">3.50151515007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51386141777039</t>
+    <t xml:space="preserve">3.51386165618896</t>
   </si>
   <si>
     <t xml:space="preserve">3.4768214225769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33360075950623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57559466362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50645351409912</t>
+    <t xml:space="preserve">3.33360028266907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57559490203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5064537525177</t>
   </si>
   <si>
     <t xml:space="preserve">3.33606958389282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34841656684875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18050217628479</t>
+    <t xml:space="preserve">3.3484160900116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18050169944763</t>
   </si>
   <si>
     <t xml:space="preserve">3.13852286338806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01505637168884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13605380058289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21260333061218</t>
+    <t xml:space="preserve">3.01505661010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13605427742004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21260261535645</t>
   </si>
   <si>
     <t xml:space="preserve">3.16815519332886</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">3.31878423690796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35335516929626</t>
+    <t xml:space="preserve">3.35335493087769</t>
   </si>
   <si>
     <t xml:space="preserve">3.4027419090271</t>
@@ -254,136 +254,136 @@
     <t xml:space="preserve">3.56571793556213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54596328735352</t>
+    <t xml:space="preserve">3.54596352577209</t>
   </si>
   <si>
     <t xml:space="preserve">3.56818747520447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47435235977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53361654281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41015005111694</t>
+    <t xml:space="preserve">3.47435259819031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53361678123474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41015028953552</t>
   </si>
   <si>
     <t xml:space="preserve">3.3829870223999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29655981063843</t>
+    <t xml:space="preserve">3.29656028747559</t>
   </si>
   <si>
     <t xml:space="preserve">3.26692819595337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36570143699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31631541252136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38051795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33113098144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10889101028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11382961273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10148334503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629867553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97801637649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06938195228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12370705604553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07185125350952</t>
+    <t xml:space="preserve">3.36570167541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31631517410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38051819801331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33113121986389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.108891248703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11383008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10148286819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629939079285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97801661491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06938147544861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12370681762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07185077667236</t>
   </si>
   <si>
     <t xml:space="preserve">3.15827775001526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0743203163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0422191619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03974962234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14840054512024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12123775482178</t>
+    <t xml:space="preserve">3.07432055473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04221868515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03974914550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14840006828308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1212375164032</t>
   </si>
   <si>
     <t xml:space="preserve">2.9310986995697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87677335739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89652872085571</t>
+    <t xml:space="preserve">2.87677311897278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8965277671814</t>
   </si>
   <si>
     <t xml:space="preserve">2.86195778846741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93356823921204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09407448768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08666706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04962682723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11136031150818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81997895240784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64465665817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66194176673889</t>
+    <t xml:space="preserve">2.93356871604919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09407496452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08666729927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04962754249573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1113600730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.819979429245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64465641975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66194200515747</t>
   </si>
   <si>
     <t xml:space="preserve">2.71379733085632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.770592212677</t>
+    <t xml:space="preserve">2.77059268951416</t>
   </si>
   <si>
     <t xml:space="preserve">2.533536195755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52365875244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54835200309753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8471417427063</t>
+    <t xml:space="preserve">2.52365899085999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54835176467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84714198112488</t>
   </si>
   <si>
     <t xml:space="preserve">2.96320009231567</t>
@@ -392,40 +392,40 @@
     <t xml:space="preserve">2.91134428977966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9977707862854</t>
+    <t xml:space="preserve">2.99777054786682</t>
   </si>
   <si>
     <t xml:space="preserve">3.00270962715149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95826125144958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08913612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09901356697083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12617635726929</t>
+    <t xml:space="preserve">2.95826148986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08913636207581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09901404380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12617683410645</t>
   </si>
   <si>
     <t xml:space="preserve">3.06691217422485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84467244148254</t>
+    <t xml:space="preserve">2.84467220306396</t>
   </si>
   <si>
     <t xml:space="preserve">2.81257104873657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69157361984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.913813829422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88665080070496</t>
+    <t xml:space="preserve">2.69157338142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91381359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88665056228638</t>
   </si>
   <si>
     <t xml:space="preserve">3.05703473091125</t>
@@ -434,43 +434,43 @@
     <t xml:space="preserve">2.98789381980896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96073126792908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97307777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88418173789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91875267028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0348105430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02987217903137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04468774795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99283218383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05950450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97554683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95085334777832</t>
+    <t xml:space="preserve">2.9607310295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97307801246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88418197631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91875243186951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03481078147888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02987194061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04468822479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99283242225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05950427055359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97554707527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9508535861969</t>
   </si>
   <si>
     <t xml:space="preserve">2.96813941001892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90393590927124</t>
+    <t xml:space="preserve">2.90393614768982</t>
   </si>
   <si>
     <t xml:space="preserve">2.86442732810974</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">2.81504058837891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90146684646606</t>
+    <t xml:space="preserve">2.90146660804749</t>
   </si>
   <si>
     <t xml:space="preserve">2.83232545852661</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">2.74096012115479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70885896682739</t>
+    <t xml:space="preserve">2.70885920524597</t>
   </si>
   <si>
     <t xml:space="preserve">2.79034686088562</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">2.82491779327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84220337867737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89158964157104</t>
+    <t xml:space="preserve">2.84220361709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89158987998962</t>
   </si>
   <si>
     <t xml:space="preserve">2.87183475494385</t>
@@ -521,19 +521,19 @@
     <t xml:space="preserve">2.82244801521301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85948801040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93850684165955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25211262702942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29409146308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2595202922821</t>
+    <t xml:space="preserve">2.85948824882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93850708007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25211215019226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29409122467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25952053070068</t>
   </si>
   <si>
     <t xml:space="preserve">3.03234171867371</t>
@@ -542,73 +542,73 @@
     <t xml:space="preserve">3.02740287780762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16568517684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5237398147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39780330657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47188258171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45953631401062</t>
+    <t xml:space="preserve">3.16568541526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52373909950256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39780306816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47188305854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45953583717346</t>
   </si>
   <si>
     <t xml:space="preserve">3.47929120063782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4941074848175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55584049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58547234535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57065582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56077909469604</t>
+    <t xml:space="preserve">3.49410676956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55584096908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58547258377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57065606117249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56077933311462</t>
   </si>
   <si>
     <t xml:space="preserve">3.60028862953186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62251257896423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55831003189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72128558158875</t>
+    <t xml:space="preserve">3.62251281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55830955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72128534317017</t>
   </si>
   <si>
     <t xml:space="preserve">3.81265163421631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85709953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93364882469177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9311785697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97315740585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99044275283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15341949462891</t>
+    <t xml:space="preserve">3.85709977149963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93364858627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93117928504944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97315788269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525903701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99044346809387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15341901779175</t>
   </si>
   <si>
     <t xml:space="preserve">4.19539785385132</t>
@@ -617,31 +617,31 @@
     <t xml:space="preserve">4.21762228012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29664039611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30651807785034</t>
+    <t xml:space="preserve">4.29664087295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30651760101318</t>
   </si>
   <si>
     <t xml:space="preserve">4.17564296722412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26453971862793</t>
+    <t xml:space="preserve">4.26453876495361</t>
   </si>
   <si>
     <t xml:space="preserve">4.31392621994019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30898714065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27935457229614</t>
+    <t xml:space="preserve">4.30898809432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27935552597046</t>
   </si>
   <si>
     <t xml:space="preserve">4.42257690429688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5065336227417</t>
+    <t xml:space="preserve">4.50653409957886</t>
   </si>
   <si>
     <t xml:space="preserve">4.53863525390625</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">4.5707368850708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88927984237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95842266082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0127477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17078495025635</t>
+    <t xml:space="preserve">4.88928031921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95842170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01274728775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17078447341919</t>
   </si>
   <si>
     <t xml:space="preserve">4.33615016937256</t>
@@ -668,55 +668,55 @@
     <t xml:space="preserve">4.53616571426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34602689743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39047527313232</t>
+    <t xml:space="preserve">4.34602737426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39047574996948</t>
   </si>
   <si>
     <t xml:space="preserve">4.41516828536987</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62753057479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64234781265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71889734268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99793195724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04237937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10164356231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12633562088013</t>
+    <t xml:space="preserve">4.62753105163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64234733581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71889686584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99793100357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0423789024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10164308547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12633657455444</t>
   </si>
   <si>
     <t xml:space="preserve">4.95348405838013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98805284500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99299287796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00287055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04731750488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92385101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78062915802002</t>
+    <t xml:space="preserve">4.98805332183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99299192428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00287103652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04731798171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92385196685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78062963485718</t>
   </si>
   <si>
     <t xml:space="preserve">4.89915800094604</t>
@@ -725,112 +725,112 @@
     <t xml:space="preserve">5.02756309509277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33870029449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34363698959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32388353347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25474262237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32882261276245</t>
+    <t xml:space="preserve">5.33869981765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34363746643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32388401031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25474309921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32882213592529</t>
   </si>
   <si>
     <t xml:space="preserve">5.17572355270386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14609050750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18560075759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18066215515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13127565383911</t>
+    <t xml:space="preserve">5.14609146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18560028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18066167831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13127613067627</t>
   </si>
   <si>
     <t xml:space="preserve">5.13621377944946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16584587097168</t>
+    <t xml:space="preserve">5.165846824646</t>
   </si>
   <si>
     <t xml:space="preserve">5.09670448303223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14115285873413</t>
+    <t xml:space="preserve">5.14115190505981</t>
   </si>
   <si>
     <t xml:space="preserve">5.22511053085327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30412817001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21029376983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98311519622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94360589981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96336078643799</t>
+    <t xml:space="preserve">5.30412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21029424667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98311424255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94360542297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96336126327515</t>
   </si>
   <si>
     <t xml:space="preserve">4.93372774124146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07695055007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07201147079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0621337890625</t>
+    <t xml:space="preserve">5.07695007324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07201194763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06213474273682</t>
   </si>
   <si>
     <t xml:space="preserve">4.81026220321655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83248662948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74358987808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78556823730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7337121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71642732620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70654964447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69420289993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51888084411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45220899581909</t>
+    <t xml:space="preserve">4.83248567581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74359035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78556871414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73371267318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71642780303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70655012130737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69420337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51888036727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45220947265625</t>
   </si>
   <si>
     <t xml:space="preserve">4.64728593826294</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70408058166504</t>
+    <t xml:space="preserve">4.70408010482788</t>
   </si>
   <si>
     <t xml:space="preserve">4.63000059127808</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">4.79297685623169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78803825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23498773574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91644287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97323846817017</t>
+    <t xml:space="preserve">4.78803777694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23498725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91644239425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97323799133301</t>
   </si>
   <si>
     <t xml:space="preserve">5.0522575378418</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">4.91891241073608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94854497909546</t>
+    <t xml:space="preserve">4.9485445022583</t>
   </si>
   <si>
     <t xml:space="preserve">5.02262449264526</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">4.62012386322021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80038404464722</t>
+    <t xml:space="preserve">4.80038547515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.72383594512939</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">4.67197942733765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59049081802368</t>
+    <t xml:space="preserve">4.59049129486084</t>
   </si>
   <si>
     <t xml:space="preserve">4.58308362960815</t>
@@ -896,34 +896,34 @@
     <t xml:space="preserve">4.61518526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84730195999146</t>
+    <t xml:space="preserve">4.8473014831543</t>
   </si>
   <si>
     <t xml:space="preserve">4.83001661300659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75346660614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80532312393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75099754333496</t>
+    <t xml:space="preserve">4.75346708297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80532264709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75099849700928</t>
   </si>
   <si>
     <t xml:space="preserve">4.79544687271118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81766986846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78309917449951</t>
+    <t xml:space="preserve">4.81767129898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78310012817383</t>
   </si>
   <si>
     <t xml:space="preserve">4.7213659286499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68432569503784</t>
+    <t xml:space="preserve">4.684326171875</t>
   </si>
   <si>
     <t xml:space="preserve">4.85224056243896</t>
@@ -935,22 +935,22 @@
     <t xml:space="preserve">4.7608757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55838966369629</t>
+    <t xml:space="preserve">4.55839014053345</t>
   </si>
   <si>
     <t xml:space="preserve">4.85507822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86003732681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78564882278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82532358169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80548620223999</t>
+    <t xml:space="preserve">4.86003828048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78564929962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82532262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80548572540283</t>
   </si>
   <si>
     <t xml:space="preserve">4.87243509292603</t>
@@ -959,22 +959,22 @@
     <t xml:space="preserve">4.95922231674194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9988956451416</t>
+    <t xml:space="preserve">4.99889612197876</t>
   </si>
   <si>
     <t xml:space="preserve">5.19230508804321</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15263223648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1724681854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10799884796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17742729187012</t>
+    <t xml:space="preserve">5.15263175964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17246866226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10799789428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17742776870728</t>
   </si>
   <si>
     <t xml:space="preserve">4.97410011291504</t>
@@ -983,106 +983,106 @@
     <t xml:space="preserve">4.97905921936035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98897743225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03856992721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03360986709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05840635299683</t>
+    <t xml:space="preserve">4.98897647857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03856897354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03361034393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05840587615967</t>
   </si>
   <si>
     <t xml:space="preserve">5.07328462600708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02865123748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07824230194092</t>
+    <t xml:space="preserve">5.02865076065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07824325561523</t>
   </si>
   <si>
     <t xml:space="preserve">5.0633659362793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95178365707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95426273345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86995601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26669406890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40555238723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34604167938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30636787414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67334985733032</t>
+    <t xml:space="preserve">4.95178270339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95426225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86995649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26669502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40555286407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34604120254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30636739730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67335033416748</t>
   </si>
   <si>
     <t xml:space="preserve">5.68822765350342</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01553630828857</t>
+    <t xml:space="preserve">6.01553535461426</t>
   </si>
   <si>
     <t xml:space="preserve">6.19406938552856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14943504333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1643123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07008695602417</t>
+    <t xml:space="preserve">6.14943552017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16431283950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07008743286133</t>
   </si>
   <si>
     <t xml:space="preserve">6.13951635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27341508865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61560249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53129482269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50649929046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78421592712402</t>
+    <t xml:space="preserve">6.27341604232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61560297012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53129434585571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50650024414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78421688079834</t>
   </si>
   <si>
     <t xml:space="preserve">6.70982789993286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7247052192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76933813095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80405282974243</t>
+    <t xml:space="preserve">6.72470569610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76933860778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80405330657959</t>
   </si>
   <si>
     <t xml:space="preserve">6.96770763397217</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88340044021606</t>
+    <t xml:space="preserve">6.88339948654175</t>
   </si>
   <si>
     <t xml:space="preserve">6.99250221252441</t>
@@ -1094,58 +1094,58 @@
     <t xml:space="preserve">7.14623975753784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18095350265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46362972259521</t>
+    <t xml:space="preserve">7.18095302581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4636287689209</t>
   </si>
   <si>
     <t xml:space="preserve">7.31485223770142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33468914031982</t>
+    <t xml:space="preserve">7.33469009399414</t>
   </si>
   <si>
     <t xml:space="preserve">7.38428211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36444520950317</t>
+    <t xml:space="preserve">7.36444568634033</t>
   </si>
   <si>
     <t xml:space="preserve">7.51818037033081</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58265066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56281423568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53801870346069</t>
+    <t xml:space="preserve">7.58264970779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56281328201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53801822662354</t>
   </si>
   <si>
     <t xml:space="preserve">7.49338483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4090781211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52313947677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41403722763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50330352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42395639419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45867013931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41899538040161</t>
+    <t xml:space="preserve">7.40907764434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52314043045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41403770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50330400466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42395544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4586706161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41899681091309</t>
   </si>
   <si>
     <t xml:space="preserve">7.30989456176758</t>
@@ -1154,13 +1154,13 @@
     <t xml:space="preserve">7.37932252883911</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93795299530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05697345733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02225923538208</t>
+    <t xml:space="preserve">6.93795156478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05697250366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02225780487061</t>
   </si>
   <si>
     <t xml:space="preserve">7.14128017425537</t>
@@ -1169,106 +1169,106 @@
     <t xml:space="preserve">7.34956789016724</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35948514938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51322174072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76614141464233</t>
+    <t xml:space="preserve">7.35948610305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5132212638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76614236831665</t>
   </si>
   <si>
     <t xml:space="preserve">7.73142719268799</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6619987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45371150970459</t>
+    <t xml:space="preserve">7.66199779510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45371103286743</t>
   </si>
   <si>
     <t xml:space="preserve">7.28013706207275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33964872360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3743634223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25038242340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43387508392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55785417556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2404637336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20078992843628</t>
+    <t xml:space="preserve">7.33964824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37436246871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25038146972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43387460708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55785512924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24046421051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20079040527344</t>
   </si>
   <si>
     <t xml:space="preserve">7.1710352897644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15119886398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00738096237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23550415039062</t>
+    <t xml:space="preserve">7.15119791030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00738143920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23550510406494</t>
   </si>
   <si>
     <t xml:space="preserve">7.19087171554565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53305864334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52809810638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50826263427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43883323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44875144958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63720226287842</t>
+    <t xml:space="preserve">7.53305912017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52809906005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50826215744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43883371353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4487509727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63720178604126</t>
   </si>
   <si>
     <t xml:space="preserve">7.65207958221436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64216136932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69175243377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67191743850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297685623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39419984817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71159029006958</t>
+    <t xml:space="preserve">7.64216279983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69175386428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67191600799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297733306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39420032501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7115912437439</t>
   </si>
   <si>
     <t xml:space="preserve">8.35628986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88692760467529</t>
+    <t xml:space="preserve">8.88692665100098</t>
   </si>
   <si>
     <t xml:space="preserve">8.98115062713623</t>
@@ -1280,16 +1280,16 @@
     <t xml:space="preserve">9.21423435211182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42252063751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48699283599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69032001495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28862285614014</t>
+    <t xml:space="preserve">9.42252159118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48699188232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6903190612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28862380981445</t>
   </si>
   <si>
     <t xml:space="preserve">9.32829761505127</t>
@@ -1298,31 +1298,31 @@
     <t xml:space="preserve">9.50187015533447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69528007507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76470756530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70519638061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64072799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63080787658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81925964355469</t>
+    <t xml:space="preserve">9.69527912139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76470851898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70519828796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64072895050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63080883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.819260597229</t>
   </si>
   <si>
     <t xml:space="preserve">9.84107971191406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68337917327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65163898468018</t>
+    <t xml:space="preserve">9.68337726593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65163993835449</t>
   </si>
   <si>
     <t xml:space="preserve">9.5385684967041</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">8.7579870223999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35111045837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89982032775879</t>
+    <t xml:space="preserve">9.35110855102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89982128143311</t>
   </si>
   <si>
     <t xml:space="preserve">8.63698196411133</t>
@@ -1346,43 +1346,43 @@
     <t xml:space="preserve">8.75302696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57548809051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77782249450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82741451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00396537780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83733463287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94643497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98908615112305</t>
+    <t xml:space="preserve">8.57548713684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77782440185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82741546630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00396347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83733367919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94643592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98908710479736</t>
   </si>
   <si>
     <t xml:space="preserve">8.80956268310547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73814868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6905403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80559539794922</t>
+    <t xml:space="preserve">8.73814964294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69054126739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8055944442749</t>
   </si>
   <si>
     <t xml:space="preserve">8.71434497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47431945800781</t>
+    <t xml:space="preserve">8.4743185043335</t>
   </si>
   <si>
     <t xml:space="preserve">7.98930740356445</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">8.01410293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46836757659912</t>
+    <t xml:space="preserve">8.4683666229248</t>
   </si>
   <si>
     <t xml:space="preserve">8.55664253234863</t>
@@ -1400,37 +1400,37 @@
     <t xml:space="preserve">8.56259250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51597690582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52787971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53085422515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43266201019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53184509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52589416503906</t>
+    <t xml:space="preserve">8.51597595214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52787685394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53085327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43266105651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53184604644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52589511871338</t>
   </si>
   <si>
     <t xml:space="preserve">8.35926532745361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56457805633545</t>
+    <t xml:space="preserve">8.56457710266113</t>
   </si>
   <si>
     <t xml:space="preserve">8.71732139587402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42175006866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25115489959717</t>
+    <t xml:space="preserve">8.42175102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25115394592285</t>
   </si>
   <si>
     <t xml:space="preserve">8.18866729736328</t>
@@ -1442,10 +1442,10 @@
     <t xml:space="preserve">8.15791988372803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18370914459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78278350830078</t>
+    <t xml:space="preserve">8.18370819091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78278255462646</t>
   </si>
   <si>
     <t xml:space="preserve">8.73517227172852</t>
@@ -1454,10 +1454,10 @@
     <t xml:space="preserve">9.15869140625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07438468933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18943881988525</t>
+    <t xml:space="preserve">9.07438373565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18943977355957</t>
   </si>
   <si>
     <t xml:space="preserve">9.31341934204102</t>
@@ -1466,28 +1466,28 @@
     <t xml:space="preserve">9.2261381149292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40764427185059</t>
+    <t xml:space="preserve">9.4076452255249</t>
   </si>
   <si>
     <t xml:space="preserve">9.43640804290771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36301136016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7091646194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76768398284912</t>
+    <t xml:space="preserve">9.36301040649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70916652679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76768207550049</t>
   </si>
   <si>
     <t xml:space="preserve">9.63180160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55840492248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75974941253662</t>
+    <t xml:space="preserve">9.55840587615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7597484588623</t>
   </si>
   <si>
     <t xml:space="preserve">9.79148769378662</t>
@@ -1496,28 +1496,28 @@
     <t xml:space="preserve">9.49393558502197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68635368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41458797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20927715301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43739891052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21820259094238</t>
+    <t xml:space="preserve">9.686354637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41458606719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20927619934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43739986419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21820163726807</t>
   </si>
   <si>
     <t xml:space="preserve">9.51674652099609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5355920791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48004817962646</t>
+    <t xml:space="preserve">9.53559303283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4800500869751</t>
   </si>
   <si>
     <t xml:space="preserve">9.29556655883789</t>
@@ -1526,61 +1526,61 @@
     <t xml:space="preserve">9.3084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42946529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41756343841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36697769165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30746841430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36797046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1993579864502</t>
+    <t xml:space="preserve">9.42946434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41756439208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36697864532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30747032165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36797142028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19935703277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.4393835067749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59609508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48600006103516</t>
+    <t xml:space="preserve">9.59609413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48600196838379</t>
   </si>
   <si>
     <t xml:space="preserve">9.31143474578857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30548477172852</t>
+    <t xml:space="preserve">9.3054838180542</t>
   </si>
   <si>
     <t xml:space="preserve">9.1081075668335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06446647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42748260498047</t>
+    <t xml:space="preserve">9.06446552276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42748165130615</t>
   </si>
   <si>
     <t xml:space="preserve">9.62089157104492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.185471534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85221195220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87601661682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8621301651001</t>
+    <t xml:space="preserve">9.18547344207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85221099853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87601470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86212921142578</t>
   </si>
   <si>
     <t xml:space="preserve">9.13984680175781</t>
@@ -1595,43 +1595,43 @@
     <t xml:space="preserve">8.92660045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85022830963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04462909698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87403297424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92461585998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79666900634766</t>
+    <t xml:space="preserve">8.85022640228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04463005065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87403202056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92461681365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79666805267334</t>
   </si>
   <si>
     <t xml:space="preserve">8.75005149841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38505268096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18172359466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92979574203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15296268463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24123668670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95558452606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10039329528809</t>
+    <t xml:space="preserve">8.38505363464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18172454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92979621887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15296173095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24123764038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95558500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10039234161377</t>
   </si>
   <si>
     <t xml:space="preserve">8.10237789154053</t>
@@ -1643,28 +1643,28 @@
     <t xml:space="preserve">8.50506687164307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40687465667725</t>
+    <t xml:space="preserve">8.40687274932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.46935939788818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52291870117188</t>
+    <t xml:space="preserve">8.52291965484619</t>
   </si>
   <si>
     <t xml:space="preserve">8.26305675506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21346378326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25214576721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19957828521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24916934967041</t>
+    <t xml:space="preserve">8.21346282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25214672088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19957733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24917030334473</t>
   </si>
   <si>
     <t xml:space="preserve">8.22239017486572</t>
@@ -1673,67 +1673,67 @@
     <t xml:space="preserve">8.33347606658936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14105987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01906299591064</t>
+    <t xml:space="preserve">8.14105796813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01906108856201</t>
   </si>
   <si>
     <t xml:space="preserve">8.21048736572266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16111707687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26426839828491</t>
+    <t xml:space="preserve">7.16111660003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26426792144775</t>
   </si>
   <si>
     <t xml:space="preserve">7.23947286605835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04804706573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04209566116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2434401512146</t>
+    <t xml:space="preserve">7.04804515838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04209423065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24343967437744</t>
   </si>
   <si>
     <t xml:space="preserve">7.23352146148682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20277404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2483983039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1750020980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04407930374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97663497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80802059173584</t>
+    <t xml:space="preserve">7.20277500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24839973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17500257492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04407978057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97663402557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80802011489868</t>
   </si>
   <si>
     <t xml:space="preserve">6.79909324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01729917526245</t>
+    <t xml:space="preserve">7.01729965209961</t>
   </si>
   <si>
     <t xml:space="preserve">7.12243509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03713655471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95977115631104</t>
+    <t xml:space="preserve">7.03713703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95977210998535</t>
   </si>
   <si>
     <t xml:space="preserve">7.1859130859375</t>
@@ -1742,22 +1742,22 @@
     <t xml:space="preserve">7.43486642837524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42693185806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36146879196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.220627784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26823663711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39320850372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22657918930054</t>
+    <t xml:space="preserve">7.42693090438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36147022247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22062730789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26823568344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39320707321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22657871246338</t>
   </si>
   <si>
     <t xml:space="preserve">7.21566820144653</t>
@@ -1766,91 +1766,91 @@
     <t xml:space="preserve">7.167067527771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4824743270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40610218048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42792367935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.457679271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48346519470215</t>
+    <t xml:space="preserve">7.48247528076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40610265731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42792177200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45767831802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48346614837646</t>
   </si>
   <si>
     <t xml:space="preserve">7.61934900283813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73341131210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66001462936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70266389846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66794919967651</t>
+    <t xml:space="preserve">7.73341083526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66001415252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7026629447937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66794872283936</t>
   </si>
   <si>
     <t xml:space="preserve">7.51024580001831</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68282604217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6937370300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64017772674561</t>
+    <t xml:space="preserve">7.68282651901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69373750686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64017820358276</t>
   </si>
   <si>
     <t xml:space="preserve">7.57769155502319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52016448974609</t>
+    <t xml:space="preserve">7.52016401290894</t>
   </si>
   <si>
     <t xml:space="preserve">7.34460878372192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42197179794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01035690307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96274757385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92803335189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94588708877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.177978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87744951248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82587337493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66618633270264</t>
+    <t xml:space="preserve">7.42197227478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01035737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96274852752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92803430557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94588613510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17797708511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87744903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82587289810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66618585586548</t>
   </si>
   <si>
     <t xml:space="preserve">6.86455488204956</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95183801651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78024864196777</t>
+    <t xml:space="preserve">6.95183658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78024959564209</t>
   </si>
   <si>
     <t xml:space="preserve">7.04705476760864</t>
@@ -1862,25 +1862,25 @@
     <t xml:space="preserve">6.67015409469604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75247573852539</t>
+    <t xml:space="preserve">6.75247621536255</t>
   </si>
   <si>
     <t xml:space="preserve">7.02920150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11251592636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09664630889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26129341125488</t>
+    <t xml:space="preserve">7.11251735687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09664726257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26129388809204</t>
   </si>
   <si>
     <t xml:space="preserve">7.28708124160767</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08672714233398</t>
+    <t xml:space="preserve">7.08672857284546</t>
   </si>
   <si>
     <t xml:space="preserve">7.30394315719604</t>
@@ -1889,13 +1889,13 @@
     <t xml:space="preserve">7.23054552078247</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13334512710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12838649749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94291210174561</t>
+    <t xml:space="preserve">7.13334608078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1283860206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94291067123413</t>
   </si>
   <si>
     <t xml:space="preserve">7.01234006881714</t>
@@ -1907,40 +1907,40 @@
     <t xml:space="preserve">6.99051952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33865594863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34758424758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30493450164795</t>
+    <t xml:space="preserve">7.33865737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34758329391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30493307113647</t>
   </si>
   <si>
     <t xml:space="preserve">7.49635934829712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34857606887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2345118522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86554765701294</t>
+    <t xml:space="preserve">7.34857416152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23451375961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86554670333862</t>
   </si>
   <si>
     <t xml:space="preserve">6.8248815536499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61064338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78322505950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9161319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92208194732666</t>
+    <t xml:space="preserve">6.61064291000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78322458267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91613245010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92208290100098</t>
   </si>
   <si>
     <t xml:space="preserve">6.86852264404297</t>
@@ -1955,22 +1955,22 @@
     <t xml:space="preserve">6.72272205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50848197937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25754690170288</t>
+    <t xml:space="preserve">6.50848388671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25754642486572</t>
   </si>
   <si>
     <t xml:space="preserve">6.28928518295288</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23175859451294</t>
+    <t xml:space="preserve">6.23175811767578</t>
   </si>
   <si>
     <t xml:space="preserve">6.1573691368103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50253295898438</t>
+    <t xml:space="preserve">6.50253248214722</t>
   </si>
   <si>
     <t xml:space="preserve">6.55113220214844</t>
@@ -1982,52 +1982,52 @@
     <t xml:space="preserve">6.87645673751831</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01134920120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16012525558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2444314956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21070766448975</t>
+    <t xml:space="preserve">7.01134872436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16012477874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24443197250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21070909500122</t>
   </si>
   <si>
     <t xml:space="preserve">7.32080411911011</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1055736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2672438621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18690538406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18987989425659</t>
+    <t xml:space="preserve">7.10557460784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26724481582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18690490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18987941741943</t>
   </si>
   <si>
     <t xml:space="preserve">7.28509712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3981671333313</t>
+    <t xml:space="preserve">7.39816761016846</t>
   </si>
   <si>
     <t xml:space="preserve">7.47354793548584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52710723876953</t>
+    <t xml:space="preserve">7.52710819244385</t>
   </si>
   <si>
     <t xml:space="preserve">6.63543891906738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44302082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41822481155396</t>
+    <t xml:space="preserve">6.44302129745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41822528839111</t>
   </si>
   <si>
     <t xml:space="preserve">6.39739608764648</t>
@@ -2036,124 +2036,124 @@
     <t xml:space="preserve">6.4975733757019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40731525421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45988273620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44897317886353</t>
+    <t xml:space="preserve">6.40731477737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45988321304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44897222518921</t>
   </si>
   <si>
     <t xml:space="preserve">6.4519476890564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57692098617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50154066085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51145887374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54617404937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45591497421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43806123733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41227388381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36268281936646</t>
+    <t xml:space="preserve">6.57692050933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.501540184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51145839691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54617309570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4559154510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43806171417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4122748374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36268186569214</t>
   </si>
   <si>
     <t xml:space="preserve">6.41525030136108</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64932584762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32697629928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36665010452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35871315002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30416297912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2585391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26548147201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32003211975098</t>
+    <t xml:space="preserve">6.64932441711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32697582244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36664915084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35871458053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30416345596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25853776931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26548051834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32003307342529</t>
   </si>
   <si>
     <t xml:space="preserve">6.6364312171936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46980047225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49658060073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33590316772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46384954452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49162197113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6612286567688</t>
+    <t xml:space="preserve">6.46980142593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49658012390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33590221405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46384906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49162149429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66122722625732</t>
   </si>
   <si>
     <t xml:space="preserve">6.52633619308472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58188009262085</t>
+    <t xml:space="preserve">6.58188104629517</t>
   </si>
   <si>
     <t xml:space="preserve">6.73958349227905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8060359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80901193618774</t>
+    <t xml:space="preserve">6.80603742599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8090124130249</t>
   </si>
   <si>
     <t xml:space="preserve">6.81000375747681</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9389443397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86157941818237</t>
+    <t xml:space="preserve">6.93894386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86158037185669</t>
   </si>
   <si>
     <t xml:space="preserve">6.89133453369141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89232778549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04308700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0936713218689</t>
+    <t xml:space="preserve">6.89232683181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04308748245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09367084503174</t>
   </si>
   <si>
     <t xml:space="preserve">7.16607618331909</t>
@@ -2162,109 +2162,109 @@
     <t xml:space="preserve">7.29303216934204</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28431224822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20211505889893</t>
+    <t xml:space="preserve">7.28431129455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20211458206177</t>
   </si>
   <si>
     <t xml:space="preserve">7.14384794235229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20939874649048</t>
+    <t xml:space="preserve">7.20939779281616</t>
   </si>
   <si>
     <t xml:space="preserve">7.19170951843262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14488935470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04916620254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379169464111</t>
+    <t xml:space="preserve">7.14488840103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04916667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379217147827</t>
   </si>
   <si>
     <t xml:space="preserve">7.11263465881348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07205677032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80673742294312</t>
+    <t xml:space="preserve">7.07205581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80673789978027</t>
   </si>
   <si>
     <t xml:space="preserve">6.73806619644165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61112928390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71309566497803</t>
+    <t xml:space="preserve">6.61112976074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71309518814087</t>
   </si>
   <si>
     <t xml:space="preserve">6.81402015686035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88997364044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95448350906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93350219726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88365459442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82684993743896</t>
+    <t xml:space="preserve">6.88997507095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95448303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93350172042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88365411758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82685089111328</t>
   </si>
   <si>
     <t xml:space="preserve">6.62166213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64021015167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16999006271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10623073577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01928663253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96132278442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62977695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59268045425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84771680831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78163909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78743600845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76425075531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88133525848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94625329971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83728361129761</t>
+    <t xml:space="preserve">6.64020967483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16999101638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10622978210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.019287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96132373809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6297779083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59268140792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84771633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78163957595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78743410110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7642502784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8813362121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94625377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83728313446045</t>
   </si>
   <si>
     <t xml:space="preserve">6.89524602890015</t>
@@ -2273,34 +2273,34 @@
     <t xml:space="preserve">6.8627872467041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92422866821289</t>
+    <t xml:space="preserve">6.92422771453857</t>
   </si>
   <si>
     <t xml:space="preserve">6.98566818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06449699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15028142929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13521146774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14216709136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02160453796387</t>
+    <t xml:space="preserve">7.0644965171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15028238296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13521242141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14216756820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02160501480103</t>
   </si>
   <si>
     <t xml:space="preserve">7.0331974029541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08072662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10970878601074</t>
+    <t xml:space="preserve">7.08072710037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10970783233643</t>
   </si>
   <si>
     <t xml:space="preserve">7.15723848342896</t>
@@ -2309,10 +2309,10 @@
     <t xml:space="preserve">7.13057518005371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33112621307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35315275192261</t>
+    <t xml:space="preserve">7.33112573623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35315132141113</t>
   </si>
   <si>
     <t xml:space="preserve">7.3253288269043</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">7.28939294815063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20940446853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20476627349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28707408905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28591394424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05986070632935</t>
+    <t xml:space="preserve">7.20940351486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20476675033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28707456588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2859148979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0598611831665</t>
   </si>
   <si>
     <t xml:space="preserve">7.0749306678772</t>
@@ -2342,10 +2342,10 @@
     <t xml:space="preserve">6.9590048789978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17578506469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31141901016235</t>
+    <t xml:space="preserve">7.17578601837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31141805648804</t>
   </si>
   <si>
     <t xml:space="preserve">7.19433355331421</t>
@@ -2357,19 +2357,19 @@
     <t xml:space="preserve">6.976393699646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99842023849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76540994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81873559951782</t>
+    <t xml:space="preserve">6.99841928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76541090011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81873512268066</t>
   </si>
   <si>
     <t xml:space="preserve">6.8685827255249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72715473175049</t>
+    <t xml:space="preserve">6.72715330123901</t>
   </si>
   <si>
     <t xml:space="preserve">6.7236762046814</t>
@@ -2378,49 +2378,49 @@
     <t xml:space="preserve">6.82569074630737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5857253074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40719985961914</t>
+    <t xml:space="preserve">6.58572435379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4072003364563</t>
   </si>
   <si>
     <t xml:space="preserve">6.52660274505615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4663233757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194341659546</t>
+    <t xml:space="preserve">6.46632242202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194389343262</t>
   </si>
   <si>
     <t xml:space="preserve">6.6900577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54515075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63557386398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74454259872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80482339859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86162805557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86394643783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08304500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29055166244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30562257766724</t>
+    <t xml:space="preserve">6.54515027999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63557291030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74454307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8048243522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86162757873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86394691467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0830454826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29055213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30562210083008</t>
   </si>
   <si>
     <t xml:space="preserve">7.37285900115967</t>
@@ -2432,49 +2432,49 @@
     <t xml:space="preserve">7.28127765655518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29287147521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1815824508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1873779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07029342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92654705047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83148813247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84539794921875</t>
+    <t xml:space="preserve">7.29287099838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18158292770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18737936019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07029390335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92654657363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83148670196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84539842605591</t>
   </si>
   <si>
     <t xml:space="preserve">6.87785720825195</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81525707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63093566894531</t>
+    <t xml:space="preserve">6.81525754928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63093614578247</t>
   </si>
   <si>
     <t xml:space="preserve">6.54051446914673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53239917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57529163360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50921487808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54862880706787</t>
+    <t xml:space="preserve">6.53239965438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57529258728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50921440124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54862976074219</t>
   </si>
   <si>
     <t xml:space="preserve">6.73410987854004</t>
@@ -2483,70 +2483,70 @@
     <t xml:space="preserve">6.87553930282593</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91843175888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07145357131958</t>
+    <t xml:space="preserve">6.91843223571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07145261764526</t>
   </si>
   <si>
     <t xml:space="preserve">7.03899335861206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87206172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95668745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90915632247925</t>
+    <t xml:space="preserve">6.87206077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95668697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90915584564209</t>
   </si>
   <si>
     <t xml:space="preserve">6.87321996688843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86742353439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90336084365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81062030792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45980310440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07304954528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12057685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32808589935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37561416625977</t>
+    <t xml:space="preserve">6.86742305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90335988998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81062078475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45980167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07304859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12057876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32808399200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37561511993408</t>
   </si>
   <si>
     <t xml:space="preserve">8.38025188446045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40691375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48226642608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41039085388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51124668121338</t>
+    <t xml:space="preserve">8.40691471099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48226547241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41039180755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5112476348877</t>
   </si>
   <si>
     <t xml:space="preserve">8.41386985778809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40807437896729</t>
+    <t xml:space="preserve">8.40807247161865</t>
   </si>
   <si>
     <t xml:space="preserve">8.42198467254639</t>
@@ -2555,88 +2555,88 @@
     <t xml:space="preserve">8.18433666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19245147705078</t>
+    <t xml:space="preserve">8.1924524307251</t>
   </si>
   <si>
     <t xml:space="preserve">8.09623336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79018974304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74613857269287</t>
+    <t xml:space="preserve">7.79019117355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74613952636719</t>
   </si>
   <si>
     <t xml:space="preserve">7.8817720413208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87713575363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89104413986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82033157348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77859926223755</t>
+    <t xml:space="preserve">7.87713432312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89104652404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82033014297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77859830856323</t>
   </si>
   <si>
     <t xml:space="preserve">7.70440578460693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65223932266235</t>
+    <t xml:space="preserve">7.65224123001099</t>
   </si>
   <si>
     <t xml:space="preserve">7.74845790863037</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68238067626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6870174407959</t>
+    <t xml:space="preserve">7.68238019943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68701601028442</t>
   </si>
   <si>
     <t xml:space="preserve">7.62094020843506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57920598983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46328115463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64760160446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72411298751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80757999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88524961471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88408994674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91191244125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82844638824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78439426422119</t>
+    <t xml:space="preserve">7.5792064666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46328067779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6476035118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72411346435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80757856369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88525009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88409042358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91191291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82844686508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78439569473267</t>
   </si>
   <si>
     <t xml:space="preserve">7.7415018081665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5803656578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47719192504883</t>
+    <t xml:space="preserve">7.58036518096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47719287872314</t>
   </si>
   <si>
     <t xml:space="preserve">7.51196908950806</t>
@@ -2651,19 +2651,19 @@
     <t xml:space="preserve">7.43661880493164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39024782180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3682222366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22911214828491</t>
+    <t xml:space="preserve">7.39024686813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36822175979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22911167144775</t>
   </si>
   <si>
     <t xml:space="preserve">7.21867799758911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20592594146729</t>
+    <t xml:space="preserve">7.2059268951416</t>
   </si>
   <si>
     <t xml:space="preserve">7.22099685668945</t>
@@ -2672,61 +2672,61 @@
     <t xml:space="preserve">7.14680433273315</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98219060897827</t>
+    <t xml:space="preserve">6.98219013214111</t>
   </si>
   <si>
     <t xml:space="preserve">7.03783416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96364259719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03087949752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91263580322266</t>
+    <t xml:space="preserve">6.96364164352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03087854385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9126353263855</t>
   </si>
   <si>
     <t xml:space="preserve">6.80018711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85235404968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19317579269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07609081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03203868865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29402923583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1073899269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14100790023804</t>
+    <t xml:space="preserve">6.8523530960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19317483901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07608985900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03203916549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29403018951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10739040374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14100742340088</t>
   </si>
   <si>
     <t xml:space="preserve">7.11086702346802</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1155047416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00189781188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57297372817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52544403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70165014266968</t>
+    <t xml:space="preserve">7.11550521850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00189828872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57297325134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52544355392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70165061950684</t>
   </si>
   <si>
     <t xml:space="preserve">6.51616954803467</t>
@@ -2741,13 +2741,13 @@
     <t xml:space="preserve">6.37126302719116</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2843189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09651947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43806314468384</t>
+    <t xml:space="preserve">6.28431987762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09651899337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.438063621521</t>
   </si>
   <si>
     <t xml:space="preserve">5.40676259994507</t>
@@ -2765,91 +2765,91 @@
     <t xml:space="preserve">4.15534830093384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97914171218872</t>
+    <t xml:space="preserve">3.97914099693298</t>
   </si>
   <si>
     <t xml:space="preserve">3.54731893539429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36531543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56123042106628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40994763374329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84872508049011</t>
+    <t xml:space="preserve">3.36531567573547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56122994422913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40994739532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84872436523438</t>
   </si>
   <si>
     <t xml:space="preserve">3.96117353439331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99421143531799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75482511520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65744853019714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8093101978302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66498374938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64295697212219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368872642517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83481407165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08289527893066</t>
+    <t xml:space="preserve">3.99421119689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75482583045959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65744829177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80930972099304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66498351097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64295744895935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368968009949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83481431007385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08289480209351</t>
   </si>
   <si>
     <t xml:space="preserve">4.12636661529541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33503150939941</t>
+    <t xml:space="preserve">4.33503246307373</t>
   </si>
   <si>
     <t xml:space="preserve">4.32401990890503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10434055328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12056922912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24403142929077</t>
+    <t xml:space="preserve">4.10434007644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12057018280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24403095245361</t>
   </si>
   <si>
     <t xml:space="preserve">4.30663061141968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11419439315796</t>
+    <t xml:space="preserve">4.11419486999512</t>
   </si>
   <si>
     <t xml:space="preserve">4.20229768753052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35010194778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26026058197021</t>
+    <t xml:space="preserve">4.35010242462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26026105880737</t>
   </si>
   <si>
     <t xml:space="preserve">4.46197128295898</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57383871078491</t>
+    <t xml:space="preserve">4.57383823394775</t>
   </si>
   <si>
     <t xml:space="preserve">4.74135160446167</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">4.38430070877075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44863986968994</t>
+    <t xml:space="preserve">4.44863939285278</t>
   </si>
   <si>
     <t xml:space="preserve">4.42139673233032</t>
@@ -2870,52 +2870,52 @@
     <t xml:space="preserve">4.40516757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50370359420776</t>
+    <t xml:space="preserve">4.50370407104492</t>
   </si>
   <si>
     <t xml:space="preserve">4.42429494857788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4005298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27475070953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15476846694946</t>
+    <t xml:space="preserve">4.40053033828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27475166320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1547679901123</t>
   </si>
   <si>
     <t xml:space="preserve">4.17505502700806</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51703548431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31242752075195</t>
+    <t xml:space="preserve">4.51703500747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31242704391479</t>
   </si>
   <si>
     <t xml:space="preserve">4.25388479232788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29851627349854</t>
+    <t xml:space="preserve">4.29851579666138</t>
   </si>
   <si>
     <t xml:space="preserve">4.59934282302856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72859954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78192567825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60340023040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7651162147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83293151855469</t>
+    <t xml:space="preserve">4.72859907150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78192520141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60339975357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76511526107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83293199539185</t>
   </si>
   <si>
     <t xml:space="preserve">5.08217239379883</t>
@@ -2927,34 +2927,34 @@
     <t xml:space="preserve">5.39748907089233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45255327224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21316814422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07231855392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68165016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74888610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75062465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88625812530518</t>
+    <t xml:space="preserve">5.45255279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21316766738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0723180770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68164968490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7488865852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75062561035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88625764846802</t>
   </si>
   <si>
     <t xml:space="preserve">4.86771011352539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85264015197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89958953857422</t>
+    <t xml:space="preserve">4.85263919830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89958906173706</t>
   </si>
   <si>
     <t xml:space="preserve">4.96624612808228</t>
@@ -2963,22 +2963,22 @@
     <t xml:space="preserve">5.25374221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02247047424316</t>
+    <t xml:space="preserve">5.02246999740601</t>
   </si>
   <si>
     <t xml:space="preserve">5.09550285339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00508213043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11694955825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18418645858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09260606765747</t>
+    <t xml:space="preserve">5.00508165359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1169490814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18418598175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09260559082031</t>
   </si>
   <si>
     <t xml:space="preserve">5.21606588363647</t>
@@ -2987,16 +2987,16 @@
     <t xml:space="preserve">5.15868234634399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21896457672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20679187774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09840154647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00276327133179</t>
+    <t xml:space="preserve">5.21896409988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20679235458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00276279449463</t>
   </si>
   <si>
     <t xml:space="preserve">5.11984825134277</t>
@@ -3005,31 +3005,31 @@
     <t xml:space="preserve">5.24910449981689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2044734954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25721979141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3169207572937</t>
+    <t xml:space="preserve">5.20447301864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2572193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31692123413086</t>
   </si>
   <si>
     <t xml:space="preserve">5.31054544448853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34184503555298</t>
+    <t xml:space="preserve">5.34184455871582</t>
   </si>
   <si>
     <t xml:space="preserve">5.35401725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30822706222534</t>
+    <t xml:space="preserve">5.30822658538818</t>
   </si>
   <si>
     <t xml:space="preserve">5.3412652015686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26069736480713</t>
+    <t xml:space="preserve">5.26069688796997</t>
   </si>
   <si>
     <t xml:space="preserve">5.25895833969116</t>
@@ -3038,28 +3038,28 @@
     <t xml:space="preserve">5.37488412857056</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30764770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99638652801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23693227767944</t>
+    <t xml:space="preserve">5.30764722824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99638605117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2369327545166</t>
   </si>
   <si>
     <t xml:space="preserve">5.44270038604736</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44733715057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38937425613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38183975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47457933425903</t>
+    <t xml:space="preserve">5.44733762741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38937473297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38183879852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47457885742188</t>
   </si>
   <si>
     <t xml:space="preserve">5.76323366165161</t>
@@ -3068,37 +3068,37 @@
     <t xml:space="preserve">5.74178838729858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65716218948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6165885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59340286254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56847953796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58065128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47631883621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40618371963501</t>
+    <t xml:space="preserve">5.65716171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61658811569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59340381622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56848001480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58065223693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.476318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40618276596069</t>
   </si>
   <si>
     <t xml:space="preserve">5.5800724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51631259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54703283309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47747850418091</t>
+    <t xml:space="preserve">5.51631307601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54703330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47747755050659</t>
   </si>
   <si>
     <t xml:space="preserve">5.457190990448</t>
@@ -3107,55 +3107,55 @@
     <t xml:space="preserve">5.35053968429565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28736066818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31750011444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37836122512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46646451950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58470869064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57079744338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57137775421143</t>
+    <t xml:space="preserve">5.28736019134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31750059127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37836265563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46646499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58470916748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57079792022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57137727737427</t>
   </si>
   <si>
     <t xml:space="preserve">5.73019552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74642467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78641891479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30750465393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.266930103302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23910808563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01537179946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75975656509399</t>
+    <t xml:space="preserve">5.74642515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641939163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30750370025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26693058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23910856246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01537227630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75975608825684</t>
   </si>
   <si>
     <t xml:space="preserve">5.92263126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02232789993286</t>
+    <t xml:space="preserve">6.0223274230957</t>
   </si>
   <si>
     <t xml:space="preserve">6.01189470291138</t>
@@ -3164,13 +3164,13 @@
     <t xml:space="preserve">5.92958736419678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16491508483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02116870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06753873825073</t>
+    <t xml:space="preserve">6.16491556167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02116775512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06753921508789</t>
   </si>
   <si>
     <t xml:space="preserve">5.99914216995239</t>
@@ -3179,136 +3179,136 @@
     <t xml:space="preserve">6.07681226730347</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18578290939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20317125320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19041967391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10463428497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16375732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06058263778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12665939331055</t>
+    <t xml:space="preserve">6.18578243255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20317077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19042015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10463523864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16375589370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06058216094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12666034698486</t>
   </si>
   <si>
     <t xml:space="preserve">5.99566555023193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24954175949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22867488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24722242355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20548963546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35735177993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43386220932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48023366928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37242317199707</t>
+    <t xml:space="preserve">6.24954080581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22867441177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24722290039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20549011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3573522567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43386268615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48023414611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37242269515991</t>
   </si>
   <si>
     <t xml:space="preserve">6.12550115585327</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12318229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11043119430542</t>
+    <t xml:space="preserve">6.12318325042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11043071746826</t>
   </si>
   <si>
     <t xml:space="preserve">6.27156686782837</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37937784194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47443675994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51269340515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91031694412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99146413803101</t>
+    <t xml:space="preserve">6.3793773651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47443723678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51269245147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91031646728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99146509170532</t>
   </si>
   <si>
     <t xml:space="preserve">7.07840871810913</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29750776290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31837368011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34851503372192</t>
+    <t xml:space="preserve">7.29750871658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31837463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34851455688477</t>
   </si>
   <si>
     <t xml:space="preserve">7.50037717819214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46559953689575</t>
+    <t xml:space="preserve">7.46559906005859</t>
   </si>
   <si>
     <t xml:space="preserve">7.44705104827881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58964061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64180707931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58616209030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66615104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57341051101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66730976104736</t>
+    <t xml:space="preserve">7.58963966369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64180612564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58616256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66615056991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.573410987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66730928421021</t>
   </si>
   <si>
     <t xml:space="preserve">7.63948774337769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6684684753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85394954681396</t>
+    <t xml:space="preserve">7.66846895217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85395097732544</t>
   </si>
   <si>
     <t xml:space="preserve">7.80294275283813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77048349380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98494482040405</t>
+    <t xml:space="preserve">7.77048254013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98494529724121</t>
   </si>
   <si>
     <t xml:space="preserve">8.01624584197998</t>
@@ -3317,25 +3317,25 @@
     <t xml:space="preserve">7.9061164855957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01045036315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18781471252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29678535461426</t>
+    <t xml:space="preserve">8.01044845581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1878137588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29678440093994</t>
   </si>
   <si>
     <t xml:space="preserve">8.34895133972168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42082500457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.259690284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46139907836914</t>
+    <t xml:space="preserve">8.42082595825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25968837738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46139812469482</t>
   </si>
   <si>
     <t xml:space="preserve">8.51588535308838</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">8.49733543395996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62485504150391</t>
+    <t xml:space="preserve">8.62485408782959</t>
   </si>
   <si>
     <t xml:space="preserve">8.60166835784912</t>
@@ -3359,19 +3359,19 @@
     <t xml:space="preserve">8.5715274810791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41271018981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33503913879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50545024871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46951389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78280925750732</t>
+    <t xml:space="preserve">8.41271114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33504009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50545120239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46951484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78281116485596</t>
   </si>
   <si>
     <t xml:space="preserve">8.40054225921631</t>
@@ -3380,52 +3380,52 @@
     <t xml:space="preserve">9.27200698852539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32146167755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11963367462158</t>
+    <t xml:space="preserve">9.32146072387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1196346282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.84830284118652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43662929534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60236835479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30564308166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49944972991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37380981445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42460060119629</t>
+    <t xml:space="preserve">8.43663024902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60236930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30564403533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49945163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37381076812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42460155487061</t>
   </si>
   <si>
     <t xml:space="preserve">8.681227684021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69726753234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76142501831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93117237091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08889198303223</t>
+    <t xml:space="preserve">8.69726848602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76142406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93117332458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08889293670654</t>
   </si>
   <si>
     <t xml:space="preserve">9.01805305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84295749664307</t>
+    <t xml:space="preserve">8.84295654296875</t>
   </si>
   <si>
     <t xml:space="preserve">8.79483890533447</t>
@@ -3434,28 +3434,28 @@
     <t xml:space="preserve">8.86567878723145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95790481567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02206230163574</t>
+    <t xml:space="preserve">8.95790386199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02206039428711</t>
   </si>
   <si>
     <t xml:space="preserve">8.82825469970703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87770843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94186401367188</t>
+    <t xml:space="preserve">8.87770938873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94186687469482</t>
   </si>
   <si>
     <t xml:space="preserve">8.82424545288086</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86969089508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07552623748779</t>
+    <t xml:space="preserve">8.86968994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07552719116211</t>
   </si>
   <si>
     <t xml:space="preserve">9.06082248687744</t>
@@ -3464,28 +3464,28 @@
     <t xml:space="preserve">8.97795391082764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30542182922363</t>
+    <t xml:space="preserve">9.30542087554932</t>
   </si>
   <si>
     <t xml:space="preserve">9.28537178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2679967880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25061988830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14369201660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67967128753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85610103607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0579290390015</t>
+    <t xml:space="preserve">9.26799583435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25061893463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14369297027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6796703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85610008239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0579271316528</t>
   </si>
   <si>
     <t xml:space="preserve">10.1755485534668</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">10.3158931732178</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6027088165283</t>
+    <t xml:space="preserve">10.602707862854</t>
   </si>
   <si>
     <t xml:space="preserve">10.5399112701416</t>
@@ -3512,13 +3512,13 @@
     <t xml:space="preserve">10.4785413742065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1288757324219</t>
+    <t xml:space="preserve">10.1288766860962</t>
   </si>
   <si>
     <t xml:space="preserve">10.1374397277832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2801609039307</t>
+    <t xml:space="preserve">10.2801599502563</t>
   </si>
   <si>
     <t xml:space="preserve">10.4457149505615</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">10.4628419876099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7753992080688</t>
+    <t xml:space="preserve">10.7754001617432</t>
   </si>
   <si>
     <t xml:space="preserve">10.7639818191528</t>
@@ -3545,10 +3545,10 @@
     <t xml:space="preserve">10.652660369873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5613203048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6597967147827</t>
+    <t xml:space="preserve">10.5613193511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6597957611084</t>
   </si>
   <si>
     <t xml:space="preserve">10.8082256317139</t>
@@ -6801,6 +6801,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.64200019836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83800029754639</t>
   </si>
 </sst>
 </file>
@@ -71853,7 +71856,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6518634259</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>23049984</v>
@@ -71874,6 +71877,32 @@
         <v>2262</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6514236111</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>20363194</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>8.85599994659424</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>8.60700035095215</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>8.69200038909912</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>8.83800029754639</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>2263</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="2264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="2265">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02501392364502</t>
+    <t xml:space="preserve">4.02501440048218</t>
   </si>
   <si>
     <t xml:space="preserve">STLAM.MI</t>
@@ -50,76 +50,76 @@
     <t xml:space="preserve">3.91636323928833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78795766830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63238954544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757326126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71881651878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66942954063416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37804889678955</t>
+    <t xml:space="preserve">3.78795742988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63239002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757349967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71881604194641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66942930221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37804818153381</t>
   </si>
   <si>
     <t xml:space="preserve">3.28421401977539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18790984153748</t>
+    <t xml:space="preserve">3.18790936470032</t>
   </si>
   <si>
     <t xml:space="preserve">3.2693977355957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06197309494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25705122947693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32619214057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26199007034302</t>
+    <t xml:space="preserve">3.06197333335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25705170631409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32619285583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26198935508728</t>
   </si>
   <si>
     <t xml:space="preserve">3.46200561523438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43237328529358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18543982505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16321682929993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16074705123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07679009437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95332312583923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91628336906433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94838428497314</t>
+    <t xml:space="preserve">3.4323742389679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1854407787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16321611404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16074657440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07678961753845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95332264900208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91628289222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94838380813599</t>
   </si>
   <si>
     <t xml:space="preserve">2.65700316429138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58292269706726</t>
+    <t xml:space="preserve">2.58292293548584</t>
   </si>
   <si>
     <t xml:space="preserve">2.7335524559021</t>
@@ -128,70 +128,70 @@
     <t xml:space="preserve">2.59280014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68416571617126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80269360542297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75824594497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89899778366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87924361228943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81010150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92616009712219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83973360061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72614431381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00517892837524</t>
+    <t xml:space="preserve">2.68416619300842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80269336700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75824546813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89899802207947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87924313545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81010127067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92616033554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83973407745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72614407539368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00517916679382</t>
   </si>
   <si>
     <t xml:space="preserve">3.13358426094055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29902958869934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45212864875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46447587013245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44225096702576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28915286064148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30643796920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21013331413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35088586807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44719004631042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36076307296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44471979141235</t>
+    <t xml:space="preserve">3.29902935028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45212817192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46447515487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44225144386292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2891526222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30643749237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21013355255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35088539123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44719052314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36076354980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472002983093</t>
   </si>
   <si>
     <t xml:space="preserve">3.42496585845947</t>
@@ -203,25 +203,25 @@
     <t xml:space="preserve">3.50151538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51386189460754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4768214225769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33360028266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57559514045715</t>
+    <t xml:space="preserve">3.51386141777039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47682166099548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33360052108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57559466362</t>
   </si>
   <si>
     <t xml:space="preserve">3.50645351409912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33606934547424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841656684875</t>
+    <t xml:space="preserve">3.33606958389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841561317444</t>
   </si>
   <si>
     <t xml:space="preserve">3.18050193786621</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">3.01505637168884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13605427742004</t>
+    <t xml:space="preserve">3.13605380058289</t>
   </si>
   <si>
     <t xml:space="preserve">3.2126030921936</t>
@@ -242,49 +242,49 @@
     <t xml:space="preserve">3.16815519332886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31878352165222</t>
+    <t xml:space="preserve">3.31878399848938</t>
   </si>
   <si>
     <t xml:space="preserve">3.35335493087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40274214744568</t>
+    <t xml:space="preserve">3.40274167060852</t>
   </si>
   <si>
     <t xml:space="preserve">3.56571745872498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54596304893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56818747520447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47435212135315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.533616065979</t>
+    <t xml:space="preserve">3.54596257209778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56818699836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47435283660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53361630439758</t>
   </si>
   <si>
     <t xml:space="preserve">3.41014981269836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38298678398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29655981063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26692819595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36570143699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31631565093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38051772117615</t>
+    <t xml:space="preserve">3.38298654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29656004905701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26692867279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36570167541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31631517410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38051748275757</t>
   </si>
   <si>
     <t xml:space="preserve">3.33113098144531</t>
@@ -296,19 +296,19 @@
     <t xml:space="preserve">3.11382985115051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10148286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629915237427</t>
+    <t xml:space="preserve">3.10148334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629891395569</t>
   </si>
   <si>
     <t xml:space="preserve">2.97801637649536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06938171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12370681762695</t>
+    <t xml:space="preserve">3.06938195228577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12370657920837</t>
   </si>
   <si>
     <t xml:space="preserve">3.07185125350952</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">3.07432007789612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04221940040588</t>
+    <t xml:space="preserve">3.0422191619873</t>
   </si>
   <si>
     <t xml:space="preserve">3.03974962234497</t>
@@ -329,34 +329,34 @@
     <t xml:space="preserve">3.14840006828308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12123775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9310986995697</t>
+    <t xml:space="preserve">3.1212375164032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93109822273254</t>
   </si>
   <si>
     <t xml:space="preserve">2.87677359580994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89652872085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86195755004883</t>
+    <t xml:space="preserve">2.89652848243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86195731163025</t>
   </si>
   <si>
     <t xml:space="preserve">2.93356823921204</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09407496452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08666706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04962754249573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11135983467102</t>
+    <t xml:space="preserve">3.09407520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08666658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04962730407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11136031150818</t>
   </si>
   <si>
     <t xml:space="preserve">2.81997919082642</t>
@@ -371,40 +371,40 @@
     <t xml:space="preserve">2.71379733085632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77059245109558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53353595733643</t>
+    <t xml:space="preserve">2.77059268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.533536195755</t>
   </si>
   <si>
     <t xml:space="preserve">2.52365875244141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54835200309753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8471417427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96320056915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91134405136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9977707862854</t>
+    <t xml:space="preserve">2.54835176467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84714150428772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96320033073425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91134452819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99777102470398</t>
   </si>
   <si>
     <t xml:space="preserve">3.00270962715149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95826101303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08913636207581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09901356697083</t>
+    <t xml:space="preserve">2.95826125144958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08913612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09901452064514</t>
   </si>
   <si>
     <t xml:space="preserve">3.12617659568787</t>
@@ -413,22 +413,22 @@
     <t xml:space="preserve">3.06691217422485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84467220306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81257128715515</t>
+    <t xml:space="preserve">2.84467196464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81257057189941</t>
   </si>
   <si>
     <t xml:space="preserve">2.69157338142395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91381335258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88665080070496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05703496932983</t>
+    <t xml:space="preserve">2.91381311416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88665056228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05703473091125</t>
   </si>
   <si>
     <t xml:space="preserve">2.98789358139038</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">2.96073126792908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97307777404785</t>
+    <t xml:space="preserve">2.97307729721069</t>
   </si>
   <si>
     <t xml:space="preserve">2.88418173789978</t>
@@ -446,166 +446,166 @@
     <t xml:space="preserve">2.91875219345093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03481078147888</t>
+    <t xml:space="preserve">3.03481101989746</t>
   </si>
   <si>
     <t xml:space="preserve">3.02987194061279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04468774795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99283218383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05950403213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97554659843445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95085310935974</t>
+    <t xml:space="preserve">3.0446879863739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99283242225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05950427055359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97554683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95085382461548</t>
   </si>
   <si>
     <t xml:space="preserve">2.96813917160034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90393567085266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86442685127258</t>
+    <t xml:space="preserve">2.90393590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86442708969116</t>
   </si>
   <si>
     <t xml:space="preserve">2.87430453300476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81504011154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90146684646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83232522010803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86689615249634</t>
+    <t xml:space="preserve">2.81504034996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90146708488464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83232545852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86689639091492</t>
   </si>
   <si>
     <t xml:space="preserve">2.74096012115479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70885896682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7903470993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82491707801819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84220361709595</t>
+    <t xml:space="preserve">2.70885872840881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79034733772278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8249180316925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84220337867737</t>
   </si>
   <si>
     <t xml:space="preserve">2.89158987998962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87183451652527</t>
+    <t xml:space="preserve">2.87183475494385</t>
   </si>
   <si>
     <t xml:space="preserve">2.90887475013733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76812267303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82244825363159</t>
+    <t xml:space="preserve">2.76812314987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82244849205017</t>
   </si>
   <si>
     <t xml:space="preserve">2.85948848724365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93850684165955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25211215019226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29409098625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25952005386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03234124183655</t>
+    <t xml:space="preserve">2.93850708007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25211238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29409122467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25952076911926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03234195709229</t>
   </si>
   <si>
     <t xml:space="preserve">3.0274031162262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16568517684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52373933792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39780306816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47188282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4595353603363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47929120063782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49410676956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55584049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58547210693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57065629959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56077861785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6002881526947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62251234054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55830979347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72128510475159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81265139579773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8570990562439</t>
+    <t xml:space="preserve">3.16568541526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52373909950256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39780354499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47188305854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45953583717346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4792914390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49410653114319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55584096908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58547258377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57065677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56077933311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60028886795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62251210212708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55830955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72128486633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81265115737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85709977149963</t>
   </si>
   <si>
     <t xml:space="preserve">3.93364882469177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93117904663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97315788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99044322967529</t>
+    <t xml:space="preserve">3.93117880821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97315812110901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525903701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99044346809387</t>
   </si>
   <si>
     <t xml:space="preserve">4.15341901779175</t>
@@ -620,46 +620,46 @@
     <t xml:space="preserve">4.29664039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30651807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17564249038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26453971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31392669677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30898761749268</t>
+    <t xml:space="preserve">4.30651760101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17564344406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26453924179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31392621994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30898714065552</t>
   </si>
   <si>
     <t xml:space="preserve">4.2793550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42257690429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5065336227417</t>
+    <t xml:space="preserve">4.42257642745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50653409957886</t>
   </si>
   <si>
     <t xml:space="preserve">4.53863525390625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5707368850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88928079605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95842218399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01274728775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17078542709351</t>
+    <t xml:space="preserve">4.57073640823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88928031921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95842170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0127477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17078495025635</t>
   </si>
   <si>
     <t xml:space="preserve">4.33615016937256</t>
@@ -668,34 +668,34 @@
     <t xml:space="preserve">4.53616571426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34602689743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39047527313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41516876220703</t>
+    <t xml:space="preserve">4.34602785110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39047574996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41516828536987</t>
   </si>
   <si>
     <t xml:space="preserve">4.62753057479858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64234781265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71889686584473</t>
+    <t xml:space="preserve">4.64234733581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71889734268188</t>
   </si>
   <si>
     <t xml:space="preserve">4.99793195724487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0423789024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10164260864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12633657455444</t>
+    <t xml:space="preserve">5.04237985610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10164356231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1263370513916</t>
   </si>
   <si>
     <t xml:space="preserve">4.95348358154297</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">4.98805332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99299192428589</t>
+    <t xml:space="preserve">4.99299240112305</t>
   </si>
   <si>
     <t xml:space="preserve">5.00287055969238</t>
@@ -716,25 +716,25 @@
     <t xml:space="preserve">4.92385149002075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78062915802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8991584777832</t>
+    <t xml:space="preserve">4.78062963485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89915800094604</t>
   </si>
   <si>
     <t xml:space="preserve">5.02756309509277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33869934082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34363842010498</t>
+    <t xml:space="preserve">5.33869886398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34363794326782</t>
   </si>
   <si>
     <t xml:space="preserve">5.32388401031494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25474214553833</t>
+    <t xml:space="preserve">5.25474166870117</t>
   </si>
   <si>
     <t xml:space="preserve">5.32882261276245</t>
@@ -743,61 +743,61 @@
     <t xml:space="preserve">5.1757230758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14609050750732</t>
+    <t xml:space="preserve">5.14609098434448</t>
   </si>
   <si>
     <t xml:space="preserve">5.18560028076172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18066215515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13127565383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13621377944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16584587097168</t>
+    <t xml:space="preserve">5.18066167831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13127517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13621425628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16584634780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.09670400619507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14115285873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22511053085327</t>
+    <t xml:space="preserve">5.14115190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22511100769043</t>
   </si>
   <si>
     <t xml:space="preserve">5.30412817001343</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21029424667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98311519622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94360589981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96336078643799</t>
+    <t xml:space="preserve">5.21029472351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98311567306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94360542297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96336126327515</t>
   </si>
   <si>
     <t xml:space="preserve">4.93372821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07695055007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07201099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0621337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81026220321655</t>
+    <t xml:space="preserve">5.07694959640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07201147079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06213426589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81026172637939</t>
   </si>
   <si>
     <t xml:space="preserve">4.83248615264893</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">4.74358987808228</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78556776046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73371315002441</t>
+    <t xml:space="preserve">4.78556823730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7337121963501</t>
   </si>
   <si>
     <t xml:space="preserve">4.71642732620239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70654964447021</t>
+    <t xml:space="preserve">4.70655012130737</t>
   </si>
   <si>
     <t xml:space="preserve">4.69420289993286</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">4.51888036727905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45220899581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6472864151001</t>
+    <t xml:space="preserve">4.45220851898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64728593826294</t>
   </si>
   <si>
     <t xml:space="preserve">4.70408010482788</t>
@@ -836,25 +836,25 @@
     <t xml:space="preserve">4.63000106811523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79297685623169</t>
+    <t xml:space="preserve">4.79297637939453</t>
   </si>
   <si>
     <t xml:space="preserve">4.78803777694702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23498773574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91644382476807</t>
+    <t xml:space="preserve">5.23498725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91644287109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.97323799133301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05225658416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03744077682495</t>
+    <t xml:space="preserve">5.05225706100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03744029998779</t>
   </si>
   <si>
     <t xml:space="preserve">4.91891288757324</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">4.94854497909546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02262496948242</t>
+    <t xml:space="preserve">5.02262449264526</t>
   </si>
   <si>
     <t xml:space="preserve">4.76828384399414</t>
@@ -872,25 +872,25 @@
     <t xml:space="preserve">4.62012386322021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80038452148438</t>
+    <t xml:space="preserve">4.80038404464722</t>
   </si>
   <si>
     <t xml:space="preserve">4.72383546829224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68926382064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66210126876831</t>
+    <t xml:space="preserve">4.68926477432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66210222244263</t>
   </si>
   <si>
     <t xml:space="preserve">4.67197895050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59049129486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.583083152771</t>
+    <t xml:space="preserve">4.59049081802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58308362960815</t>
   </si>
   <si>
     <t xml:space="preserve">4.61518478393555</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">4.8473014831543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83001613616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75346660614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8053240776062</t>
+    <t xml:space="preserve">4.83001661300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75346755981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80532360076904</t>
   </si>
   <si>
     <t xml:space="preserve">4.75099802017212</t>
@@ -914,82 +914,82 @@
     <t xml:space="preserve">4.79544639587402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8176703453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78309965133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72136545181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68432664871216</t>
+    <t xml:space="preserve">4.81767082214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78309917449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72136688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.684326171875</t>
   </si>
   <si>
     <t xml:space="preserve">4.85224056243896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77816152572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7608757019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55839014053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85507774353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86003732681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78564977645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8253231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80548620223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87243509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95922231674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99889612197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19230556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15263175964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1724681854248</t>
+    <t xml:space="preserve">4.77816104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76087474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55838966369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85507869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8600378036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78564882278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82532262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80548572540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87243556976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95922183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99889516830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19230508804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1526312828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17246866226196</t>
   </si>
   <si>
     <t xml:space="preserve">5.10799884796143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17742729187012</t>
+    <t xml:space="preserve">5.17742776870728</t>
   </si>
   <si>
     <t xml:space="preserve">4.97410011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97905921936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98897695541382</t>
+    <t xml:space="preserve">4.97905969619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98897743225098</t>
   </si>
   <si>
     <t xml:space="preserve">5.03856992721558</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03360939025879</t>
+    <t xml:space="preserve">5.03360986709595</t>
   </si>
   <si>
     <t xml:space="preserve">5.05840587615967</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">5.07824373245239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06336545944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95178365707397</t>
+    <t xml:space="preserve">5.0633659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95178318023682</t>
   </si>
   <si>
     <t xml:space="preserve">4.95426273345947</t>
@@ -1016,43 +1016,43 @@
     <t xml:space="preserve">4.86995601654053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26669359207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40555238723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34604167938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30636739730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67334985733032</t>
+    <t xml:space="preserve">5.26669502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40555286407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34604215621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30636882781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67335081100464</t>
   </si>
   <si>
     <t xml:space="preserve">5.68822717666626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01553583145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19406795501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14943552017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16431331634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07008743286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13951683044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27341604232788</t>
+    <t xml:space="preserve">6.01553678512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19406843185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1494345664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16431188583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0700888633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13951778411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27341651916504</t>
   </si>
   <si>
     <t xml:space="preserve">6.61560201644897</t>
@@ -1064,28 +1064,28 @@
     <t xml:space="preserve">6.50649929046631</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78421688079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70982837677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72470474243164</t>
+    <t xml:space="preserve">6.78421545028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70982694625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7247052192688</t>
   </si>
   <si>
     <t xml:space="preserve">6.76933813095093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80405330657959</t>
+    <t xml:space="preserve">6.80405282974243</t>
   </si>
   <si>
     <t xml:space="preserve">6.96770668029785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88339948654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99250221252441</t>
+    <t xml:space="preserve">6.88339996337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99250411987305</t>
   </si>
   <si>
     <t xml:space="preserve">7.07680988311768</t>
@@ -1097,97 +1097,97 @@
     <t xml:space="preserve">7.18095397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46362924575806</t>
+    <t xml:space="preserve">7.4636287689209</t>
   </si>
   <si>
     <t xml:space="preserve">7.31485271453857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33469009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38428163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36444520950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51818180084229</t>
+    <t xml:space="preserve">7.33468866348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38428258895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36444473266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51818227767944</t>
   </si>
   <si>
     <t xml:space="preserve">7.58265066146851</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5628137588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53801870346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49338531494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4090781211853</t>
+    <t xml:space="preserve">7.56281328201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53801727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49338483810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40907716751099</t>
   </si>
   <si>
     <t xml:space="preserve">7.52314043045044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41403722763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50330400466919</t>
+    <t xml:space="preserve">7.4140362739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50330352783203</t>
   </si>
   <si>
     <t xml:space="preserve">7.4239559173584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4586706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41899681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30989408493042</t>
+    <t xml:space="preserve">7.45867013931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41899585723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30989503860474</t>
   </si>
   <si>
     <t xml:space="preserve">7.37932300567627</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93795299530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05697202682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02225923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14127969741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34956836700439</t>
+    <t xml:space="preserve">6.93795251846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05697345733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02225828170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14127922058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34956789016724</t>
   </si>
   <si>
     <t xml:space="preserve">7.3594856262207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51322221755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76614141464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73142576217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66199779510498</t>
+    <t xml:space="preserve">7.51322174072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76614236831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73142719268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66199827194214</t>
   </si>
   <si>
     <t xml:space="preserve">7.45371103286743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28013753890991</t>
+    <t xml:space="preserve">7.28013801574707</t>
   </si>
   <si>
     <t xml:space="preserve">7.33964872360229</t>
@@ -1196,100 +1196,100 @@
     <t xml:space="preserve">7.37436294555664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25038242340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43387413024902</t>
+    <t xml:space="preserve">7.25038385391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43387508392334</t>
   </si>
   <si>
     <t xml:space="preserve">7.55785417556763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24046325683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20079040527344</t>
+    <t xml:space="preserve">7.24046421051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2007908821106</t>
   </si>
   <si>
     <t xml:space="preserve">7.17103624343872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15119791030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00738143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23550319671631</t>
+    <t xml:space="preserve">7.15119743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00738048553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23550415039062</t>
   </si>
   <si>
     <t xml:space="preserve">7.19087219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53305816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52810001373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50826215744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43883371353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44875335693359</t>
+    <t xml:space="preserve">7.53305864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52809810638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5082631111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43883323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44875192642212</t>
   </si>
   <si>
     <t xml:space="preserve">7.63720178604126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6520791053772</t>
+    <t xml:space="preserve">7.65208005905151</t>
   </si>
   <si>
     <t xml:space="preserve">7.64216136932373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69175338745117</t>
+    <t xml:space="preserve">7.69175434112549</t>
   </si>
   <si>
     <t xml:space="preserve">7.67191648483276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54297733306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39419984817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71158981323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35628890991211</t>
+    <t xml:space="preserve">7.54297637939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39420080184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71159029006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35628986358643</t>
   </si>
   <si>
     <t xml:space="preserve">8.88692665100098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98114967346191</t>
+    <t xml:space="preserve">8.98115158081055</t>
   </si>
   <si>
     <t xml:space="preserve">9.15968322753906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2142333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42252159118652</t>
+    <t xml:space="preserve">9.21423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42252254486084</t>
   </si>
   <si>
     <t xml:space="preserve">9.48699188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6903190612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28862285614014</t>
+    <t xml:space="preserve">9.69032096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28862190246582</t>
   </si>
   <si>
     <t xml:space="preserve">9.32829761505127</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">9.50187015533447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69527912139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76470947265625</t>
+    <t xml:space="preserve">9.69527816772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76470851898193</t>
   </si>
   <si>
     <t xml:space="preserve">9.70519828796387</t>
@@ -1310,22 +1310,22 @@
     <t xml:space="preserve">9.64072799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63081073760986</t>
+    <t xml:space="preserve">9.63080883026123</t>
   </si>
   <si>
     <t xml:space="preserve">9.81925964355469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84107971191406</t>
+    <t xml:space="preserve">9.84108066558838</t>
   </si>
   <si>
     <t xml:space="preserve">9.68337821960449</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65163993835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53856754302979</t>
+    <t xml:space="preserve">9.65163898468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5385684967041</t>
   </si>
   <si>
     <t xml:space="preserve">9.31937026977539</t>
@@ -1334,22 +1334,22 @@
     <t xml:space="preserve">8.75798606872559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35111045837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89982032775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63698196411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75302791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57548809051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77782344818115</t>
+    <t xml:space="preserve">9.35110950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89982128143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63698101043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75302696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57548713684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77782249450684</t>
   </si>
   <si>
     <t xml:space="preserve">8.82741546630859</t>
@@ -1361,31 +1361,31 @@
     <t xml:space="preserve">8.83733367919922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94643592834473</t>
+    <t xml:space="preserve">8.94643688201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.98908710479736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80956268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73814868927002</t>
+    <t xml:space="preserve">8.80956363677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73814964294434</t>
   </si>
   <si>
     <t xml:space="preserve">8.6905403137207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80559539794922</t>
+    <t xml:space="preserve">8.8055944442749</t>
   </si>
   <si>
     <t xml:space="preserve">8.71434497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47432041168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98930549621582</t>
+    <t xml:space="preserve">8.47431945800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98930644989014</t>
   </si>
   <si>
     <t xml:space="preserve">8.01410293579102</t>
@@ -1394,37 +1394,37 @@
     <t xml:space="preserve">8.46836757659912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55664157867432</t>
+    <t xml:space="preserve">8.55664348602295</t>
   </si>
   <si>
     <t xml:space="preserve">8.56259250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51597595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52787780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53085422515869</t>
+    <t xml:space="preserve">8.51597690582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5278787612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53085517883301</t>
   </si>
   <si>
     <t xml:space="preserve">8.43266201019287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53184604644775</t>
+    <t xml:space="preserve">8.53184509277344</t>
   </si>
   <si>
     <t xml:space="preserve">8.52589416503906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35926532745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56457710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71732139587402</t>
+    <t xml:space="preserve">8.35926628112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56457614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71732044219971</t>
   </si>
   <si>
     <t xml:space="preserve">8.42175102233887</t>
@@ -1433,22 +1433,22 @@
     <t xml:space="preserve">8.25115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1886682510376</t>
+    <t xml:space="preserve">8.18866634368896</t>
   </si>
   <si>
     <t xml:space="preserve">8.32554340362549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15791988372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18370914459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78278350830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73517322540283</t>
+    <t xml:space="preserve">8.15792083740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18370819091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78278255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73517417907715</t>
   </si>
   <si>
     <t xml:space="preserve">9.15869140625</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">9.07438468933105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18943977355957</t>
+    <t xml:space="preserve">9.18943881988525</t>
   </si>
   <si>
     <t xml:space="preserve">9.31341934204102</t>
@@ -1466,13 +1466,13 @@
     <t xml:space="preserve">9.22613716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4076452255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43640804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36301136016846</t>
+    <t xml:space="preserve">9.40764331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43640899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36301231384277</t>
   </si>
   <si>
     <t xml:space="preserve">9.70916557312012</t>
@@ -1484,19 +1484,19 @@
     <t xml:space="preserve">9.63180255889893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55840492248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75974941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79148864746094</t>
+    <t xml:space="preserve">9.55840396881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75975036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79149055480957</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393463134766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68635368347168</t>
+    <t xml:space="preserve">9.68635272979736</t>
   </si>
   <si>
     <t xml:space="preserve">9.41458797454834</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">9.20927619934082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43739986419678</t>
+    <t xml:space="preserve">9.43739891052246</t>
   </si>
   <si>
     <t xml:space="preserve">9.21820259094238</t>
@@ -1520,19 +1520,19 @@
     <t xml:space="preserve">9.4800500869751</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29556560516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30845832824707</t>
+    <t xml:space="preserve">9.29556655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30846118927002</t>
   </si>
   <si>
     <t xml:space="preserve">9.42946434020996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41756343841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36697769165039</t>
+    <t xml:space="preserve">9.41756248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36697864532471</t>
   </si>
   <si>
     <t xml:space="preserve">9.30746936798096</t>
@@ -1541,28 +1541,28 @@
     <t xml:space="preserve">9.36796951293945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19935607910156</t>
+    <t xml:space="preserve">9.19935703277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.43938446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59609603881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48600196838379</t>
+    <t xml:space="preserve">9.59609413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48600101470947</t>
   </si>
   <si>
     <t xml:space="preserve">9.31143569946289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30548477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1081075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06446552276611</t>
+    <t xml:space="preserve">9.3054838180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10810852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06446647644043</t>
   </si>
   <si>
     <t xml:space="preserve">9.42748165130615</t>
@@ -1586,28 +1586,28 @@
     <t xml:space="preserve">9.13984680175781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90676307678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98313617706299</t>
+    <t xml:space="preserve">8.90676212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98313426971436</t>
   </si>
   <si>
     <t xml:space="preserve">8.92660045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85022830963135</t>
+    <t xml:space="preserve">8.85022735595703</t>
   </si>
   <si>
     <t xml:space="preserve">9.04462909698486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87403202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92461681365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79666805267334</t>
+    <t xml:space="preserve">8.87403297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92461490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79666996002197</t>
   </si>
   <si>
     <t xml:space="preserve">8.75005149841309</t>
@@ -1625,58 +1625,58 @@
     <t xml:space="preserve">8.15296173095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24123668670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95558547973633</t>
+    <t xml:space="preserve">8.24123573303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95558404922485</t>
   </si>
   <si>
     <t xml:space="preserve">8.10039329528809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10237693786621</t>
+    <t xml:space="preserve">8.10237598419189</t>
   </si>
   <si>
     <t xml:space="preserve">8.03889942169189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50506687164307</t>
+    <t xml:space="preserve">8.50506782531738</t>
   </si>
   <si>
     <t xml:space="preserve">8.40687370300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4693603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52291870117188</t>
+    <t xml:space="preserve">8.46935939788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52291965484619</t>
   </si>
   <si>
     <t xml:space="preserve">8.26305675506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21346473693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25214672088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19957733154297</t>
+    <t xml:space="preserve">8.21346378326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25214576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19957828521729</t>
   </si>
   <si>
     <t xml:space="preserve">8.24917030334473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22239017486572</t>
+    <t xml:space="preserve">8.22239112854004</t>
   </si>
   <si>
     <t xml:space="preserve">8.33347606658936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14105796813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01906299591064</t>
+    <t xml:space="preserve">8.14105987548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01906394958496</t>
   </si>
   <si>
     <t xml:space="preserve">8.21048831939697</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">7.16111707687378</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2642674446106</t>
+    <t xml:space="preserve">7.26426839828491</t>
   </si>
   <si>
     <t xml:space="preserve">7.23947286605835</t>
@@ -1694,79 +1694,79 @@
     <t xml:space="preserve">7.04804563522339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04209566116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24344062805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23352098464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20277500152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24839878082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17500305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04407930374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97663450241089</t>
+    <t xml:space="preserve">7.04209518432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2434401512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23352146148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2027759552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24839925765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17500257492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04407978057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97663307189941</t>
   </si>
   <si>
     <t xml:space="preserve">6.80801963806152</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79909324645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01729965209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12243556976318</t>
+    <t xml:space="preserve">6.7990927696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01729869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12243461608887</t>
   </si>
   <si>
     <t xml:space="preserve">7.03713655471802</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95977210998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18591356277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43486595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42692995071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36146831512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22062635421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26823568344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3932089805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2265796661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21566772460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16706800460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4824743270874</t>
+    <t xml:space="preserve">6.95977258682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18591213226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4348669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42693138122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36146879196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22062730789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26823616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39320755004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22657871246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21566915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.167067527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48247528076172</t>
   </si>
   <si>
     <t xml:space="preserve">7.40610265731812</t>
@@ -1778,115 +1778,115 @@
     <t xml:space="preserve">7.45767831802368</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48346710205078</t>
+    <t xml:space="preserve">7.48346614837646</t>
   </si>
   <si>
     <t xml:space="preserve">7.61934947967529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73341131210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66001510620117</t>
+    <t xml:space="preserve">7.73341178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66001462936401</t>
   </si>
   <si>
     <t xml:space="preserve">7.70266389846802</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66794919967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51024627685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68282651901245</t>
+    <t xml:space="preserve">7.66794872283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51024580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68282699584961</t>
   </si>
   <si>
     <t xml:space="preserve">7.6937370300293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64017820358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57769107818604</t>
+    <t xml:space="preserve">7.64017772674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57769203186035</t>
   </si>
   <si>
     <t xml:space="preserve">7.52016401290894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34460878372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42197179794312</t>
+    <t xml:space="preserve">7.34460830688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42197275161743</t>
   </si>
   <si>
     <t xml:space="preserve">7.01035690307617</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96274757385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92803382873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94588708877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17797803878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87744903564453</t>
+    <t xml:space="preserve">6.9627480506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92803287506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94588756561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17797899246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87744951248169</t>
   </si>
   <si>
     <t xml:space="preserve">6.82587289810181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66618633270264</t>
+    <t xml:space="preserve">6.66618680953979</t>
   </si>
   <si>
     <t xml:space="preserve">6.86455535888672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95183753967285</t>
+    <t xml:space="preserve">6.95183706283569</t>
   </si>
   <si>
     <t xml:space="preserve">6.78024816513062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04705476760864</t>
+    <t xml:space="preserve">7.04705429077148</t>
   </si>
   <si>
     <t xml:space="preserve">6.81992244720459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67015409469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75247573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02920007705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11251640319824</t>
+    <t xml:space="preserve">6.67015314102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75247669219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02920198440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1125168800354</t>
   </si>
   <si>
     <t xml:space="preserve">7.09664630889893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26129341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28708076477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08672904968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30394172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23054504394531</t>
+    <t xml:space="preserve">7.26129293441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28708124160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0867280960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30394268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23054599761963</t>
   </si>
   <si>
     <t xml:space="preserve">7.13334560394287</t>
@@ -1895,52 +1895,52 @@
     <t xml:space="preserve">7.1283860206604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94291162490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01234102249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93001747131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99051904678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33865642547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34758377075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30493307113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49635934829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34857606887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23451328277588</t>
+    <t xml:space="preserve">6.94291019439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01233959197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.930016040802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99051856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33865690231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34758329391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30493402481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49636030197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3485746383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23451280593872</t>
   </si>
   <si>
     <t xml:space="preserve">6.86554718017578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82488203048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6106424331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7832236289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9161319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92208194732666</t>
+    <t xml:space="preserve">6.8248815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61064291000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78322458267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91613149642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92208290100098</t>
   </si>
   <si>
     <t xml:space="preserve">6.86852216720581</t>
@@ -1949,76 +1949,76 @@
     <t xml:space="preserve">6.82884883880615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82289838790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72272157669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50848245620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25754690170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2892861366272</t>
+    <t xml:space="preserve">6.82289791107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72272253036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50848340988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25754737854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28928518295288</t>
   </si>
   <si>
     <t xml:space="preserve">6.2317590713501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15736961364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50253343582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55113220214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62849712371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87645816802979</t>
+    <t xml:space="preserve">6.15737009048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50253200531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5511326789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62849617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87645769119263</t>
   </si>
   <si>
     <t xml:space="preserve">7.01134920120239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16012525558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24443197250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2107081413269</t>
+    <t xml:space="preserve">7.16012477874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24443244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21070861816406</t>
   </si>
   <si>
     <t xml:space="preserve">7.32080411911011</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10557413101196</t>
+    <t xml:space="preserve">7.1055736541748</t>
   </si>
   <si>
     <t xml:space="preserve">7.26724481582642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18690490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18987941741943</t>
+    <t xml:space="preserve">7.1869044303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18987989425659</t>
   </si>
   <si>
     <t xml:space="preserve">7.28509712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39816856384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.473548412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52710819244385</t>
+    <t xml:space="preserve">7.39816665649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47354793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52710723876953</t>
   </si>
   <si>
     <t xml:space="preserve">6.63543939590454</t>
@@ -2027,52 +2027,52 @@
     <t xml:space="preserve">6.44302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41822481155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39739608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4975733757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40731430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4598822593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44897317886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45194864273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57692003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50153923034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51145887374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54617309570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45591449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43806266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41227388381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36268329620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41524934768677</t>
+    <t xml:space="preserve">6.4182243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3973970413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49757289886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40731477737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45988273620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44897222518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45194721221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57692050933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50154113769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51145839691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54617357254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4559154510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43806219100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41227436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3626823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41524982452393</t>
   </si>
   <si>
     <t xml:space="preserve">6.64932537078857</t>
@@ -2081,25 +2081,25 @@
     <t xml:space="preserve">6.32697582244873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36664962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35871458053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30416297912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25853872299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26548099517822</t>
+    <t xml:space="preserve">6.36664915084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35871410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30416393280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25853824615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26548051834106</t>
   </si>
   <si>
     <t xml:space="preserve">6.32003259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6364312171936</t>
+    <t xml:space="preserve">6.63643074035645</t>
   </si>
   <si>
     <t xml:space="preserve">6.46980094909668</t>
@@ -2108,91 +2108,91 @@
     <t xml:space="preserve">6.49658012390137</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33590173721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4638500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49162149429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66122817993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52633619308472</t>
+    <t xml:space="preserve">6.33590078353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46385049819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49162244796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66122674942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52633571624756</t>
   </si>
   <si>
     <t xml:space="preserve">6.58187961578369</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73958253860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80603694915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80901145935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81000423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93894386291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86157941818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89133453369141</t>
+    <t xml:space="preserve">6.73958206176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80603742599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80901193618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81000280380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93894481658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86158037185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89133548736572</t>
   </si>
   <si>
     <t xml:space="preserve">6.89232683181763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04308652877808</t>
+    <t xml:space="preserve">7.04308795928955</t>
   </si>
   <si>
     <t xml:space="preserve">7.09367227554321</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16607618331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29303169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28431177139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20211458206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14384841918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20939874649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19170951843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14488840103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04916667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379026412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11263513565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07205533981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80673694610596</t>
+    <t xml:space="preserve">7.16607570648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29303216934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28431129455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20211505889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14384698867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20939826965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19170999526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14488887786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04916715621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11263418197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07205629348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80673742294312</t>
   </si>
   <si>
     <t xml:space="preserve">6.73806619644165</t>
@@ -2201,73 +2201,73 @@
     <t xml:space="preserve">6.61112976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71309471130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81402063369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88997459411621</t>
+    <t xml:space="preserve">6.71309566497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81402015686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88997364044189</t>
   </si>
   <si>
     <t xml:space="preserve">6.95448350906372</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93350124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88365411758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82685041427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62166213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64020967483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16999053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10622978210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.019287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96132373809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62977695465088</t>
+    <t xml:space="preserve">6.93350172042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88365316390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82684993743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62166261672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64021015167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16998958587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10623073577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01928615570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96132326126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62977838516235</t>
   </si>
   <si>
     <t xml:space="preserve">6.59268140792847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84771680831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78163862228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78743457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7642502784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88133478164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94625377655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83728313446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89524602890015</t>
+    <t xml:space="preserve">6.84771728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78163909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78743553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76424980163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88133525848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94625329971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83728361129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89524507522583</t>
   </si>
   <si>
     <t xml:space="preserve">6.86278676986694</t>
@@ -2276,106 +2276,106 @@
     <t xml:space="preserve">6.92422819137573</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98566865921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06449747085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15028190612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13521194458008</t>
+    <t xml:space="preserve">6.98566818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06449699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15028142929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13521242141724</t>
   </si>
   <si>
     <t xml:space="preserve">7.14216756820679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02160406112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03319692611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.080726146698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10970878601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15723752975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13057518005371</t>
+    <t xml:space="preserve">7.02160453796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03319787979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08072662353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10970830917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1572380065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13057470321655</t>
   </si>
   <si>
     <t xml:space="preserve">7.33112621307373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35315179824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32532930374146</t>
+    <t xml:space="preserve">7.35315227508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32533025741577</t>
   </si>
   <si>
     <t xml:space="preserve">7.28939342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20940399169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20476770401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28707408905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28591442108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0598611831665</t>
+    <t xml:space="preserve">7.20940494537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20476627349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28707456588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28591585159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05986022949219</t>
   </si>
   <si>
     <t xml:space="preserve">7.07493114471436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95900535583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17578506469727</t>
+    <t xml:space="preserve">6.95900583267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17578649520874</t>
   </si>
   <si>
     <t xml:space="preserve">7.3114185333252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19433355331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08768320083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97639417648315</t>
+    <t xml:space="preserve">7.19433403015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08768272399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.976393699646</t>
   </si>
   <si>
     <t xml:space="preserve">6.99842023849487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76541042327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81873607635498</t>
+    <t xml:space="preserve">6.76541090011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81873464584351</t>
   </si>
   <si>
     <t xml:space="preserve">6.86858320236206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72715425491333</t>
+    <t xml:space="preserve">6.72715520858765</t>
   </si>
   <si>
     <t xml:space="preserve">6.72367715835571</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82569074630737</t>
+    <t xml:space="preserve">6.82569122314453</t>
   </si>
   <si>
     <t xml:space="preserve">6.5857253074646</t>
@@ -2387,58 +2387,58 @@
     <t xml:space="preserve">6.52660322189331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4663233757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194389343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69005727767944</t>
+    <t xml:space="preserve">6.46632242202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194341659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69005823135376</t>
   </si>
   <si>
     <t xml:space="preserve">6.5451512336731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63557243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74454355239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80482530593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86162805557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86394643783569</t>
+    <t xml:space="preserve">6.635573387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74454307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80482387542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86162757873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86394691467285</t>
   </si>
   <si>
     <t xml:space="preserve">7.08304595947266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29055213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30562210083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37285900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28243732452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28127717971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29286956787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1815824508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1873779296875</t>
+    <t xml:space="preserve">7.29055166244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30562162399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37285852432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28243684768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28127765655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29287052154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18158292770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18737745285034</t>
   </si>
   <si>
     <t xml:space="preserve">7.07029342651367</t>
@@ -2447,28 +2447,28 @@
     <t xml:space="preserve">6.92654657363892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83148765563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84539937973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87785720825195</t>
+    <t xml:space="preserve">6.83148670196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84539747238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87785673141479</t>
   </si>
   <si>
     <t xml:space="preserve">6.81525707244873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63093519210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54051399230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53239870071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57529163360596</t>
+    <t xml:space="preserve">6.63093709945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54051351547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53239917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57529306411743</t>
   </si>
   <si>
     <t xml:space="preserve">6.50921440124512</t>
@@ -2477,13 +2477,13 @@
     <t xml:space="preserve">6.54862976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73410892486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87553882598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9184308052063</t>
+    <t xml:space="preserve">6.73410940170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87553930282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91843128204346</t>
   </si>
   <si>
     <t xml:space="preserve">7.07145357131958</t>
@@ -2492,151 +2492,151 @@
     <t xml:space="preserve">7.03899383544922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87206125259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95668697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90915632247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87322092056274</t>
+    <t xml:space="preserve">6.87206172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95668840408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90915584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87321996688843</t>
   </si>
   <si>
     <t xml:space="preserve">6.86742353439331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90336084365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81062030792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45980310440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0730504989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12057781219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32808494567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37561321258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38025188446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40691375732422</t>
+    <t xml:space="preserve">6.90336132049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81062078475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45980215072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07304859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12057876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32808399200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37561416625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38025093078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40691471099854</t>
   </si>
   <si>
     <t xml:space="preserve">8.48226642608643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41039180755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5112476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41386985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40807437896729</t>
+    <t xml:space="preserve">8.41038990020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51124572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41386890411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40807342529297</t>
   </si>
   <si>
     <t xml:space="preserve">8.42198467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18433666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1924524307251</t>
+    <t xml:space="preserve">8.1843376159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19245147705078</t>
   </si>
   <si>
     <t xml:space="preserve">8.09623432159424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79019212722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74614000320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88177251815796</t>
+    <t xml:space="preserve">7.79019069671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74613952636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88177299499512</t>
   </si>
   <si>
     <t xml:space="preserve">7.87713479995728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89104557037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82033109664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77859878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70440578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65223932266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74845838546753</t>
+    <t xml:space="preserve">7.89104509353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82033157348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77859830856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70440530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65224075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74845743179321</t>
   </si>
   <si>
     <t xml:space="preserve">7.68238067626953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68701648712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6209397315979</t>
+    <t xml:space="preserve">7.68701696395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62093925476074</t>
   </si>
   <si>
     <t xml:space="preserve">7.57920598983765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46328067779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64760255813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72411346435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80758047103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88524961471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88409090042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91191244125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82844638824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78439426422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74150228500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58036470413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47719144821167</t>
+    <t xml:space="preserve">7.46328163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72411298751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80757999420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88525009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88409042358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91191291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82844495773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78439378738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7415018081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5803656578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47719240188599</t>
   </si>
   <si>
     <t xml:space="preserve">7.51196956634521</t>
@@ -2648,76 +2648,76 @@
     <t xml:space="preserve">7.43777751922607</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43661880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39024829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3682222366333</t>
+    <t xml:space="preserve">7.43661832809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39024782180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36822319030762</t>
   </si>
   <si>
     <t xml:space="preserve">7.22911214828491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21867752075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20592641830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22099637985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.146803855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98219013214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03783512115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96364259719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03087854385376</t>
+    <t xml:space="preserve">7.21867704391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2059268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22099685668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14680480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98218965530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03783464431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96364164352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03087902069092</t>
   </si>
   <si>
     <t xml:space="preserve">6.91263580322266</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80018711090088</t>
+    <t xml:space="preserve">6.80018758773804</t>
   </si>
   <si>
     <t xml:space="preserve">6.85235452651978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19317483901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07609128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03203916549683</t>
+    <t xml:space="preserve">7.19317531585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07608985900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03203773498535</t>
   </si>
   <si>
     <t xml:space="preserve">7.294029712677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1073899269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14100742340088</t>
+    <t xml:space="preserve">7.10739040374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14100933074951</t>
   </si>
   <si>
     <t xml:space="preserve">7.11086750030518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11550426483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00189781188965</t>
+    <t xml:space="preserve">7.1155047416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00189828872681</t>
   </si>
   <si>
     <t xml:space="preserve">6.57297277450562</t>
@@ -2726,19 +2726,19 @@
     <t xml:space="preserve">6.52544403076172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70164966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51616907119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27620363235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3411226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37126350402832</t>
+    <t xml:space="preserve">6.70165109634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51617002487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27620410919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34112167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37126302719116</t>
   </si>
   <si>
     <t xml:space="preserve">6.2843189239502</t>
@@ -2750,10 +2750,10 @@
     <t xml:space="preserve">5.43806314468384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40676259994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51921033859253</t>
+    <t xml:space="preserve">5.40676355361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51921081542969</t>
   </si>
   <si>
     <t xml:space="preserve">4.53326463699341</t>
@@ -2762,16 +2762,16 @@
     <t xml:space="preserve">4.85785627365112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15534782409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9791407585144</t>
+    <t xml:space="preserve">4.15534830093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97914123535156</t>
   </si>
   <si>
     <t xml:space="preserve">3.54731917381287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36531543731689</t>
+    <t xml:space="preserve">3.36531519889832</t>
   </si>
   <si>
     <t xml:space="preserve">3.56123042106628</t>
@@ -2780,40 +2780,40 @@
     <t xml:space="preserve">3.40994739532471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84872460365295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96117305755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99421191215515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75482559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65744781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8093101978302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66498374938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64295721054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368848800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83481407165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08289432525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12636709213257</t>
+    <t xml:space="preserve">3.84872531890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96117281913757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99421143531799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75482511520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65744829177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80931043624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66498327255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64295792579651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368872642517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83481383323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08289480209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12636661529541</t>
   </si>
   <si>
     <t xml:space="preserve">4.33503198623657</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">4.12057018280029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24403095245361</t>
+    <t xml:space="preserve">4.24403190612793</t>
   </si>
   <si>
     <t xml:space="preserve">4.30663061141968</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">4.11419486999512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20229768753052</t>
+    <t xml:space="preserve">4.20229721069336</t>
   </si>
   <si>
     <t xml:space="preserve">4.35010242462158</t>
@@ -2846,55 +2846,55 @@
     <t xml:space="preserve">4.26026058197021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46197128295898</t>
+    <t xml:space="preserve">4.46197080612183</t>
   </si>
   <si>
     <t xml:space="preserve">4.57383871078491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74135112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64629220962524</t>
+    <t xml:space="preserve">4.74135160446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6462926864624</t>
   </si>
   <si>
     <t xml:space="preserve">4.38430070877075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44863939285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42139720916748</t>
+    <t xml:space="preserve">4.44863986968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42139673233032</t>
   </si>
   <si>
     <t xml:space="preserve">4.40516757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50370359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42429542541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40053033828735</t>
+    <t xml:space="preserve">4.50370454788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42429494857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4005298614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.27475118637085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15476846694946</t>
+    <t xml:space="preserve">4.15476894378662</t>
   </si>
   <si>
     <t xml:space="preserve">4.17505502700806</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51703548431396</t>
+    <t xml:space="preserve">4.51703596115112</t>
   </si>
   <si>
     <t xml:space="preserve">4.31242704391479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25388431549072</t>
+    <t xml:space="preserve">4.25388383865356</t>
   </si>
   <si>
     <t xml:space="preserve">4.29851579666138</t>
@@ -2906,16 +2906,16 @@
     <t xml:space="preserve">4.72859954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78192520141602</t>
+    <t xml:space="preserve">4.78192567825317</t>
   </si>
   <si>
     <t xml:space="preserve">4.60339975357056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76511573791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83293199539185</t>
+    <t xml:space="preserve">4.76511526107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.832932472229</t>
   </si>
   <si>
     <t xml:space="preserve">5.08217191696167</t>
@@ -2924,37 +2924,37 @@
     <t xml:space="preserve">5.04449558258057</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39748954772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45255374908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21316814422607</t>
+    <t xml:space="preserve">5.39748907089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45255327224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21316909790039</t>
   </si>
   <si>
     <t xml:space="preserve">5.0723180770874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68164920806885</t>
+    <t xml:space="preserve">4.68164968490601</t>
   </si>
   <si>
     <t xml:space="preserve">4.74888610839844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75062465667725</t>
+    <t xml:space="preserve">4.7506251335144</t>
   </si>
   <si>
     <t xml:space="preserve">4.88625812530518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86771011352539</t>
+    <t xml:space="preserve">4.86770963668823</t>
   </si>
   <si>
     <t xml:space="preserve">4.85263967514038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89958953857422</t>
+    <t xml:space="preserve">4.89958906173706</t>
   </si>
   <si>
     <t xml:space="preserve">4.96624660491943</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">5.02247047424316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09550333023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00508213043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1169490814209</t>
+    <t xml:space="preserve">5.09550285339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00508165359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11694955825806</t>
   </si>
   <si>
     <t xml:space="preserve">5.18418645858765</t>
@@ -2981,16 +2981,16 @@
     <t xml:space="preserve">5.09260559082031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21606540679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15868234634399</t>
+    <t xml:space="preserve">5.21606588363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15868282318115</t>
   </si>
   <si>
     <t xml:space="preserve">5.21896409988403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20679187774658</t>
+    <t xml:space="preserve">5.20679235458374</t>
   </si>
   <si>
     <t xml:space="preserve">5.09840154647827</t>
@@ -3002,34 +3002,34 @@
     <t xml:space="preserve">5.11984825134277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24910497665405</t>
+    <t xml:space="preserve">5.24910449981689</t>
   </si>
   <si>
     <t xml:space="preserve">5.20447301864624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25721883773804</t>
+    <t xml:space="preserve">5.25721979141235</t>
   </si>
   <si>
     <t xml:space="preserve">5.31692123413086</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31054544448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34184455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35401725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30822658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34126567840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26069688796997</t>
+    <t xml:space="preserve">5.31054496765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34184503555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35401678085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30822706222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3412652015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26069736480713</t>
   </si>
   <si>
     <t xml:space="preserve">5.25895833969116</t>
@@ -3041,22 +3041,22 @@
     <t xml:space="preserve">5.30764770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99638652801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23693227767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44270086288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44733667373657</t>
+    <t xml:space="preserve">4.99638700485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23693180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44270038604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44733715057373</t>
   </si>
   <si>
     <t xml:space="preserve">5.38937425613403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38183975219727</t>
+    <t xml:space="preserve">5.38183879852295</t>
   </si>
   <si>
     <t xml:space="preserve">5.47457933425903</t>
@@ -3065,22 +3065,22 @@
     <t xml:space="preserve">5.76323366165161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74178838729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65716171264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6165885925293</t>
+    <t xml:space="preserve">5.74178791046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65716218948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61658811569214</t>
   </si>
   <si>
     <t xml:space="preserve">5.59340333938599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56847906112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58065176010132</t>
+    <t xml:space="preserve">5.56847953796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58065223693848</t>
   </si>
   <si>
     <t xml:space="preserve">5.47631883621216</t>
@@ -3092,10 +3092,10 @@
     <t xml:space="preserve">5.5800724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51631307601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54703235626221</t>
+    <t xml:space="preserve">5.51631212234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54703330993652</t>
   </si>
   <si>
     <t xml:space="preserve">5.47747802734375</t>
@@ -3107,28 +3107,28 @@
     <t xml:space="preserve">5.35053968429565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28735971450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31750106811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37836217880249</t>
+    <t xml:space="preserve">5.28736019134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31750011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37836170196533</t>
   </si>
   <si>
     <t xml:space="preserve">5.46646499633789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58470821380615</t>
+    <t xml:space="preserve">5.58470869064331</t>
   </si>
   <si>
     <t xml:space="preserve">5.57079792022705</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57137775421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73019599914551</t>
+    <t xml:space="preserve">5.57137727737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73019504547119</t>
   </si>
   <si>
     <t xml:space="preserve">5.74642467498779</t>
@@ -3137,22 +3137,22 @@
     <t xml:space="preserve">5.78641891479492</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30750465393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26693058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23910856246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01537227630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75975608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92263126373291</t>
+    <t xml:space="preserve">6.30750417709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.266930103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23910760879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01537179946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75975704193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92263174057007</t>
   </si>
   <si>
     <t xml:space="preserve">6.0223274230957</t>
@@ -3161,16 +3161,16 @@
     <t xml:space="preserve">6.01189470291138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92958641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16491556167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02116870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06753873825073</t>
+    <t xml:space="preserve">5.92958736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16491508483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02116775512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06753826141357</t>
   </si>
   <si>
     <t xml:space="preserve">5.99914264678955</t>
@@ -3179,142 +3179,142 @@
     <t xml:space="preserve">6.07681274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18578243255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20317077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19041967391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1046347618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16375684738159</t>
+    <t xml:space="preserve">6.18578290939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20317125320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19041919708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10463523864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16375732421875</t>
   </si>
   <si>
     <t xml:space="preserve">6.06058263778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12666082382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99566507339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24954080581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22867488861084</t>
+    <t xml:space="preserve">6.12666034698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99566459655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24954175949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22867441177368</t>
   </si>
   <si>
     <t xml:space="preserve">6.24722242355347</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20548915863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35735273361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43386363983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48023414611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37242317199707</t>
+    <t xml:space="preserve">6.20548963546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35735177993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43386316299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48023319244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37242269515991</t>
   </si>
   <si>
     <t xml:space="preserve">6.12550115585327</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12318277359009</t>
+    <t xml:space="preserve">6.12318229675293</t>
   </si>
   <si>
     <t xml:space="preserve">6.11043119430542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27156782150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37937831878662</t>
+    <t xml:space="preserve">6.27156686782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37937688827515</t>
   </si>
   <si>
     <t xml:space="preserve">6.47443675994873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51269292831421</t>
+    <t xml:space="preserve">6.51269245147705</t>
   </si>
   <si>
     <t xml:space="preserve">6.91031742095947</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99146556854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07840824127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29750728607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31837463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34851503372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50037670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46560001373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705009460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58963918685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64180660247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58616209030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66615152359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57340908050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66731023788452</t>
+    <t xml:space="preserve">6.99146413803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07840776443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29750823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31837368011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34851455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50037717819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46559953689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705057144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58963871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64180612564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58616161346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66615009307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57341003417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66731119155884</t>
   </si>
   <si>
     <t xml:space="preserve">7.63948774337769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66846895217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85395002365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80294227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77048254013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98494529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0162467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9061164855957</t>
+    <t xml:space="preserve">7.66846942901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8539514541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80294322967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77048397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98494482040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01624488830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90611696243286</t>
   </si>
   <si>
     <t xml:space="preserve">8.01045036315918</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">8.29678440093994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.348952293396</t>
+    <t xml:space="preserve">8.34895133972168</t>
   </si>
   <si>
     <t xml:space="preserve">8.42082500457764</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">8.46140003204346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51588439941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57036876678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51356506347656</t>
+    <t xml:space="preserve">8.51588535308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57036972045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51356601715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.49733543395996</t>
@@ -3362,7 +3362,7 @@
     <t xml:space="preserve">8.41271018981934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33504009246826</t>
+    <t xml:space="preserve">8.33504104614258</t>
   </si>
   <si>
     <t xml:space="preserve">8.50545120239258</t>
@@ -3374,52 +3374,52 @@
     <t xml:space="preserve">8.78281116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40054130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27200603485107</t>
+    <t xml:space="preserve">8.40054225921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27200698852539</t>
   </si>
   <si>
     <t xml:space="preserve">9.32146072387695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11963367462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84830284118652</t>
+    <t xml:space="preserve">9.1196346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84830379486084</t>
   </si>
   <si>
     <t xml:space="preserve">8.43663024902344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60236740112305</t>
+    <t xml:space="preserve">8.60236835479736</t>
   </si>
   <si>
     <t xml:space="preserve">8.30564308166504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49945068359375</t>
+    <t xml:space="preserve">8.49945163726807</t>
   </si>
   <si>
     <t xml:space="preserve">8.37380981445312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42460060119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.681227684021</t>
+    <t xml:space="preserve">8.42460155487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68122863769531</t>
   </si>
   <si>
     <t xml:space="preserve">8.69726848602295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76142501831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93117332458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08889198303223</t>
+    <t xml:space="preserve">8.76142406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93117237091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08889293670654</t>
   </si>
   <si>
     <t xml:space="preserve">9.01805114746094</t>
@@ -3431,25 +3431,25 @@
     <t xml:space="preserve">8.79483890533447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86567974090576</t>
+    <t xml:space="preserve">8.86567878723145</t>
   </si>
   <si>
     <t xml:space="preserve">8.95790481567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02206230163574</t>
+    <t xml:space="preserve">9.02206134796143</t>
   </si>
   <si>
     <t xml:space="preserve">8.82825469970703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87770843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94186592102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82424449920654</t>
+    <t xml:space="preserve">8.87770938873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94186496734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82424545288086</t>
   </si>
   <si>
     <t xml:space="preserve">8.86968898773193</t>
@@ -3461,28 +3461,28 @@
     <t xml:space="preserve">9.06082248687744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97795295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30542087554932</t>
+    <t xml:space="preserve">8.97795486450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30542182922363</t>
   </si>
   <si>
     <t xml:space="preserve">9.28537178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26799583435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25061988830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14369297027588</t>
+    <t xml:space="preserve">9.2679967880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25062084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14369201660156</t>
   </si>
   <si>
     <t xml:space="preserve">9.6796703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85610198974609</t>
+    <t xml:space="preserve">9.85610103607178</t>
   </si>
   <si>
     <t xml:space="preserve">10.0579290390015</t>
@@ -3491,28 +3491,28 @@
     <t xml:space="preserve">10.1755485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3158941268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.602707862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5399122238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6655054092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.983772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.596999168396</t>
+    <t xml:space="preserve">10.3158922195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6027088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5399112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6655044555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9837713241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5970001220703</t>
   </si>
   <si>
     <t xml:space="preserve">10.4785413742065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1288757324219</t>
+    <t xml:space="preserve">10.1288747787476</t>
   </si>
   <si>
     <t xml:space="preserve">10.1374397277832</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">10.4457149505615</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4628410339355</t>
+    <t xml:space="preserve">10.4628419876099</t>
   </si>
   <si>
     <t xml:space="preserve">10.7754001617432</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">10.8010892868042</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9124116897583</t>
+    <t xml:space="preserve">10.9124126434326</t>
   </si>
   <si>
     <t xml:space="preserve">10.9109840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">10.652660369873</t>
+    <t xml:space="preserve">10.6526613235474</t>
   </si>
   <si>
     <t xml:space="preserve">10.5613193511963</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">10.8082256317139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7397193908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7340097427368</t>
+    <t xml:space="preserve">10.7397203445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7340106964111</t>
   </si>
   <si>
     <t xml:space="preserve">10.8910045623779</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">10.3457975387573</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4551305770874</t>
+    <t xml:space="preserve">10.4551296234131</t>
   </si>
   <si>
     <t xml:space="preserve">10.481369972229</t>
@@ -3596,25 +3596,25 @@
     <t xml:space="preserve">10.2204294204712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1227588653564</t>
+    <t xml:space="preserve">10.1227579116821</t>
   </si>
   <si>
     <t xml:space="preserve">10.8312349319458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8705940246582</t>
+    <t xml:space="preserve">10.8705949783325</t>
   </si>
   <si>
     <t xml:space="preserve">11.0061683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6869144439697</t>
+    <t xml:space="preserve">10.686915397644</t>
   </si>
   <si>
     <t xml:space="preserve">10.7306489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.678168296814</t>
+    <t xml:space="preserve">10.6781692504883</t>
   </si>
   <si>
     <t xml:space="preserve">10.8283195495605</t>
@@ -3626,25 +3626,25 @@
     <t xml:space="preserve">11.0003366470337</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7364797592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9376516342163</t>
+    <t xml:space="preserve">10.736478805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9376525878906</t>
   </si>
   <si>
     <t xml:space="preserve">11.1636066436768</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2160873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2787704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2583608627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7190160751343</t>
+    <t xml:space="preserve">11.2160863876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2787714004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2583618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7190170288086</t>
   </si>
   <si>
     <t xml:space="preserve">11.739426612854</t>
@@ -3653,10 +3653,10 @@
     <t xml:space="preserve">11.8502168655396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9143581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0338954925537</t>
+    <t xml:space="preserve">11.9143590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.033896446228</t>
   </si>
   <si>
     <t xml:space="preserve">12.1709260940552</t>
@@ -3665,13 +3665,13 @@
     <t xml:space="preserve">12.5120449066162</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7219648361206</t>
+    <t xml:space="preserve">12.7219638824463</t>
   </si>
   <si>
     <t xml:space="preserve">12.7379989624023</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5601511001587</t>
+    <t xml:space="preserve">12.5601501464844</t>
   </si>
   <si>
     <t xml:space="preserve">12.3910493850708</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">12.3167037963867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3181600570679</t>
+    <t xml:space="preserve">12.3181610107422</t>
   </si>
   <si>
     <t xml:space="preserve">12.3604364395142</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">12.0003681182861</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4056282043457</t>
+    <t xml:space="preserve">12.4056272506714</t>
   </si>
   <si>
     <t xml:space="preserve">12.3808450698853</t>
@@ -3713,10 +3713,10 @@
     <t xml:space="preserve">12.2758855819702</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2613086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0659675598145</t>
+    <t xml:space="preserve">12.2613077163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0659685134888</t>
   </si>
   <si>
     <t xml:space="preserve">12.1738414764404</t>
@@ -3725,10 +3725,10 @@
     <t xml:space="preserve">12.3414850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1942501068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0936632156372</t>
+    <t xml:space="preserve">12.1942510604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0936641693115</t>
   </si>
   <si>
     <t xml:space="preserve">11.688404083252</t>
@@ -3743,10 +3743,10 @@
     <t xml:space="preserve">11.8370971679688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6679944992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4332933425903</t>
+    <t xml:space="preserve">11.6679954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4332942962646</t>
   </si>
   <si>
     <t xml:space="preserve">11.0222034454346</t>
@@ -3755,10 +3755,10 @@
     <t xml:space="preserve">11.049901008606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4289216995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3633222579956</t>
+    <t xml:space="preserve">11.4289207458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3633213043213</t>
   </si>
   <si>
     <t xml:space="preserve">11.4814004898071</t>
@@ -3779,28 +3779,28 @@
     <t xml:space="preserve">11.8006534576416</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9318523406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7175903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7146739959717</t>
+    <t xml:space="preserve">11.9318532943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7175893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.714674949646</t>
   </si>
   <si>
     <t xml:space="preserve">13.0280961990356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.117018699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0834903717041</t>
+    <t xml:space="preserve">13.1170196533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0834913253784</t>
   </si>
   <si>
     <t xml:space="preserve">13.1330547332764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4829196929932</t>
+    <t xml:space="preserve">13.4829187393188</t>
   </si>
   <si>
     <t xml:space="preserve">13.5645561218262</t>
@@ -3812,16 +3812,16 @@
     <t xml:space="preserve">13.0062284469604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1053562164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6388692855835</t>
+    <t xml:space="preserve">13.105357170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6388702392578</t>
   </si>
   <si>
     <t xml:space="preserve">12.4930925369263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5412006378174</t>
+    <t xml:space="preserve">12.5411996841431</t>
   </si>
   <si>
     <t xml:space="preserve">12.5732698440552</t>
@@ -3857,10 +3857,10 @@
     <t xml:space="preserve">12.1636371612549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1753005981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2656812667847</t>
+    <t xml:space="preserve">12.1752996444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2656803131104</t>
   </si>
   <si>
     <t xml:space="preserve">12.6898918151855</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">11.7044401168823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6854887008667</t>
+    <t xml:space="preserve">11.6854877471924</t>
   </si>
   <si>
     <t xml:space="preserve">12.0645084381104</t>
@@ -3887,22 +3887,22 @@
     <t xml:space="preserve">12.3444013595581</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9770421981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1432275772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0426416397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8575038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7627506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0674238204956</t>
+    <t xml:space="preserve">11.9770412445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1432285308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0426425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8575048446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7627515792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0674247741699</t>
   </si>
   <si>
     <t xml:space="preserve">11.6373815536499</t>
@@ -3911,31 +3911,31 @@
     <t xml:space="preserve">12.0790863037109</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1534328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2642240524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2860908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2671394348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4114589691162</t>
+    <t xml:space="preserve">12.1534337997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2642230987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2860898971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2671384811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4114580154419</t>
   </si>
   <si>
     <t xml:space="preserve">12.3123302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2292366027832</t>
+    <t xml:space="preserve">12.2292356491089</t>
   </si>
   <si>
     <t xml:space="preserve">12.2598505020142</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2846326828003</t>
+    <t xml:space="preserve">12.284631729126</t>
   </si>
   <si>
     <t xml:space="preserve">12.281717300415</t>
@@ -3944,46 +3944,46 @@
     <t xml:space="preserve">12.7656965255737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8079719543457</t>
+    <t xml:space="preserve">12.80797290802</t>
   </si>
   <si>
     <t xml:space="preserve">12.7992248535156</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5995092391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7190494537354</t>
+    <t xml:space="preserve">12.5995101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.719048500061</t>
   </si>
   <si>
     <t xml:space="preserve">12.7321672439575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7904796600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.857536315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9143896102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7817325592041</t>
+    <t xml:space="preserve">12.7904787063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8575353622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9143886566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7817316055298</t>
   </si>
   <si>
     <t xml:space="preserve">12.7117595672607</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0339260101318</t>
+    <t xml:space="preserve">13.0339269638062</t>
   </si>
   <si>
     <t xml:space="preserve">13.0368413925171</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0295515060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1855354309082</t>
+    <t xml:space="preserve">13.0295534133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1855344772339</t>
   </si>
   <si>
     <t xml:space="preserve">13.0878639221191</t>
@@ -3992,13 +3992,13 @@
     <t xml:space="preserve">13.093695640564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248802185059</t>
+    <t xml:space="preserve">12.7248792648315</t>
   </si>
   <si>
     <t xml:space="preserve">12.3983383178711</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2511034011841</t>
+    <t xml:space="preserve">12.2511024475098</t>
   </si>
   <si>
     <t xml:space="preserve">12.1782150268555</t>
@@ -4013,7 +4013,7 @@
     <t xml:space="preserve">11.0353240966797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.662163734436</t>
+    <t xml:space="preserve">11.6621646881104</t>
   </si>
   <si>
     <t xml:space="preserve">11.6096849441528</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">12.2977514266968</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1592636108398</t>
+    <t xml:space="preserve">12.1592645645142</t>
   </si>
   <si>
     <t xml:space="preserve">11.9887046813965</t>
@@ -4040,13 +4040,13 @@
     <t xml:space="preserve">11.9289360046387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8589630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8924913406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.963921546936</t>
+    <t xml:space="preserve">11.8589639663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8924922943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9639225006104</t>
   </si>
   <si>
     <t xml:space="preserve">11.5309648513794</t>
@@ -4064,10 +4064,10 @@
     <t xml:space="preserve">12.1621799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301221847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9114751815796</t>
+    <t xml:space="preserve">12.6301231384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9114742279053</t>
   </si>
   <si>
     <t xml:space="preserve">13.4318971633911</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">13.299241065979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1213941574097</t>
+    <t xml:space="preserve">13.1213932037354</t>
   </si>
   <si>
     <t xml:space="preserve">13.020806312561</t>
@@ -4088,22 +4088,22 @@
     <t xml:space="preserve">13.3969106674194</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8561096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.829870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9508628845215</t>
+    <t xml:space="preserve">13.8561086654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8298692703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9508619308472</t>
   </si>
   <si>
     <t xml:space="preserve">13.9173345565796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8415307998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6986694335938</t>
+    <t xml:space="preserve">13.8415298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6986703872681</t>
   </si>
   <si>
     <t xml:space="preserve">13.2132320404053</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">12.6855182647705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7861042022705</t>
+    <t xml:space="preserve">12.7861051559448</t>
   </si>
   <si>
     <t xml:space="preserve">12.4406147003174</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">12.6417856216431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6636524200439</t>
+    <t xml:space="preserve">12.6636533737183</t>
   </si>
   <si>
     <t xml:space="preserve">11.998908996582</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">12.4683122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3618936538696</t>
+    <t xml:space="preserve">12.3618927001953</t>
   </si>
   <si>
     <t xml:space="preserve">12.2234058380127</t>
@@ -4169,19 +4169,19 @@
     <t xml:space="preserve">11.6869468688965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3065004348755</t>
+    <t xml:space="preserve">12.3064994812012</t>
   </si>
   <si>
     <t xml:space="preserve">11.1052961349487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2190027236938</t>
+    <t xml:space="preserve">11.2190017700195</t>
   </si>
   <si>
     <t xml:space="preserve">10.9041242599487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.074652671814</t>
+    <t xml:space="preserve">10.0746517181396</t>
   </si>
   <si>
     <t xml:space="preserve">9.43031692504883</t>
@@ -4199,10 +4199,10 @@
     <t xml:space="preserve">9.83703517913818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2043943405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3180999755859</t>
+    <t xml:space="preserve">10.2043933868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3180990219116</t>
   </si>
   <si>
     <t xml:space="preserve">10.9770126342773</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">10.7262754440308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6883726119995</t>
+    <t xml:space="preserve">10.6883735656738</t>
   </si>
   <si>
     <t xml:space="preserve">10.6475563049316</t>
@@ -4226,10 +4226,10 @@
     <t xml:space="preserve">10.5046939849854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5207300186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5323915481567</t>
+    <t xml:space="preserve">10.5207290649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5323925018311</t>
   </si>
   <si>
     <t xml:space="preserve">11.2321214675903</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">9.98718547821045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86910629272461</t>
+    <t xml:space="preserve">9.86910724639893</t>
   </si>
   <si>
     <t xml:space="preserve">10.0338344573975</t>
@@ -4265,7 +4265,7 @@
     <t xml:space="preserve">10.1358785629272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1854438781738</t>
+    <t xml:space="preserve">10.1854429244995</t>
   </si>
   <si>
     <t xml:space="preserve">10.2583312988281</t>
@@ -6804,6 +6804,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.91499996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11699962615967</t>
   </si>
 </sst>
 </file>
@@ -71908,7 +71911,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6512268519</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>23916483</v>
@@ -71929,6 +71932,32 @@
         <v>2263</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6501388889</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>23267996</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>8.85400009155273</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>9.00699996948242</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>9.11699962615967</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>2264</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="2265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2266" uniqueCount="2266">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02501440048218</t>
+    <t xml:space="preserve">4.02501392364502</t>
   </si>
   <si>
     <t xml:space="preserve">STLAM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13119459152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91636323928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78795742988586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63239002227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757349967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71881604194641</t>
+    <t xml:space="preserve">4.13119506835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91636347770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78795766830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63238978385925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757326126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71881699562073</t>
   </si>
   <si>
     <t xml:space="preserve">3.66942930221558</t>
@@ -68,43 +68,43 @@
     <t xml:space="preserve">3.37804818153381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28421401977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18790936470032</t>
+    <t xml:space="preserve">3.28421378135681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18790984153748</t>
   </si>
   <si>
     <t xml:space="preserve">3.2693977355957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06197333335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25705170631409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32619285583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26198935508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46200561523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4323742389679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1854407787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16321611404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16074657440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07678961753845</t>
+    <t xml:space="preserve">3.06197357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25705122947693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32619214057922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26198959350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46200609207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43237376213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18544030189514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16321635246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16074705123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07679009437561</t>
   </si>
   <si>
     <t xml:space="preserve">2.95332264900208</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">2.65700316429138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58292293548584</t>
+    <t xml:space="preserve">2.58292269706726</t>
   </si>
   <si>
     <t xml:space="preserve">2.7335524559021</t>
@@ -128,16 +128,16 @@
     <t xml:space="preserve">2.59280014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68416619300842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80269336700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75824546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89899802207947</t>
+    <t xml:space="preserve">2.68416571617126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80269432067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75824570655823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89899730682373</t>
   </si>
   <si>
     <t xml:space="preserve">2.87924313545227</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">2.92616033554077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83973407745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72614407539368</t>
+    <t xml:space="preserve">2.83973383903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72614431381226</t>
   </si>
   <si>
     <t xml:space="preserve">3.00517916679382</t>
@@ -161,34 +161,34 @@
     <t xml:space="preserve">3.13358426094055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29902935028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45212817192078</t>
+    <t xml:space="preserve">3.29902958869934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45212888717651</t>
   </si>
   <si>
     <t xml:space="preserve">3.46447515487671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44225144386292</t>
+    <t xml:space="preserve">3.44225120544434</t>
   </si>
   <si>
     <t xml:space="preserve">3.2891526222229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30643749237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21013355255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35088539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44719052314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36076354980469</t>
+    <t xml:space="preserve">3.30643773078918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21013331413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35088562965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.447190284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36076307296753</t>
   </si>
   <si>
     <t xml:space="preserve">3.44472002983093</t>
@@ -197,10 +197,10 @@
     <t xml:space="preserve">3.42496585845947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51633071899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50151538848877</t>
+    <t xml:space="preserve">3.51633143424988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50151515007019</t>
   </si>
   <si>
     <t xml:space="preserve">3.51386141777039</t>
@@ -212,28 +212,28 @@
     <t xml:space="preserve">3.33360052108765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57559466362</t>
+    <t xml:space="preserve">3.57559514045715</t>
   </si>
   <si>
     <t xml:space="preserve">3.50645351409912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33606958389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841561317444</t>
+    <t xml:space="preserve">3.33606934547424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841704368591</t>
   </si>
   <si>
     <t xml:space="preserve">3.18050193786621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13852262496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01505637168884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13605380058289</t>
+    <t xml:space="preserve">3.13852310180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01505661010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13605451583862</t>
   </si>
   <si>
     <t xml:space="preserve">3.2126030921936</t>
@@ -245,19 +245,19 @@
     <t xml:space="preserve">3.31878399848938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35335493087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40274167060852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56571745872498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54596257209778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56818699836731</t>
+    <t xml:space="preserve">3.35335516929626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4027419090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56571769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54596328735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56818747520447</t>
   </si>
   <si>
     <t xml:space="preserve">3.47435283660889</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">3.41014981269836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38298654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29656004905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26692867279053</t>
+    <t xml:space="preserve">3.38298678398132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29656076431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26692843437195</t>
   </si>
   <si>
     <t xml:space="preserve">3.36570167541504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31631517410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38051748275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33113098144531</t>
+    <t xml:space="preserve">3.3163149356842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38051772117615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33113074302673</t>
   </si>
   <si>
     <t xml:space="preserve">3.10889101028442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11382985115051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10148334503174</t>
+    <t xml:space="preserve">3.11383008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10148310661316</t>
   </si>
   <si>
     <t xml:space="preserve">3.11629891395569</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">2.97801637649536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06938195228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12370657920837</t>
+    <t xml:space="preserve">3.06938147544861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12370705604553</t>
   </si>
   <si>
     <t xml:space="preserve">3.07185125350952</t>
@@ -317,64 +317,64 @@
     <t xml:space="preserve">3.15827775001526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07432007789612</t>
+    <t xml:space="preserve">3.0743203163147</t>
   </si>
   <si>
     <t xml:space="preserve">3.0422191619873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03974962234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14840006828308</t>
+    <t xml:space="preserve">3.03974938392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14840030670166</t>
   </si>
   <si>
     <t xml:space="preserve">3.1212375164032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93109822273254</t>
+    <t xml:space="preserve">2.93109846115112</t>
   </si>
   <si>
     <t xml:space="preserve">2.87677359580994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89652848243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86195731163025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93356823921204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09407520294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08666658401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04962730407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11136031150818</t>
+    <t xml:space="preserve">2.89652824401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86195802688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93356847763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09407472610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08666682243347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04962682723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11135983467102</t>
   </si>
   <si>
     <t xml:space="preserve">2.81997919082642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64465618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66194200515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71379733085632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77059268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.533536195755</t>
+    <t xml:space="preserve">2.64465641975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66194152832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7137975692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77059245109558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53353595733643</t>
   </si>
   <si>
     <t xml:space="preserve">2.52365875244141</t>
@@ -383,28 +383,28 @@
     <t xml:space="preserve">2.54835176467896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84714150428772</t>
+    <t xml:space="preserve">2.84714198112488</t>
   </si>
   <si>
     <t xml:space="preserve">2.96320033073425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91134452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99777102470398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00270962715149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95826125144958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08913612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09901452064514</t>
+    <t xml:space="preserve">2.91134428977966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99777054786682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00270938873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95826148986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08913636207581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09901428222656</t>
   </si>
   <si>
     <t xml:space="preserve">3.12617659568787</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">3.06691217422485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84467196464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81257057189941</t>
+    <t xml:space="preserve">2.84467267990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81257128715515</t>
   </si>
   <si>
     <t xml:space="preserve">2.69157338142395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91381311416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88665056228638</t>
+    <t xml:space="preserve">2.91381287574768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88665103912354</t>
   </si>
   <si>
     <t xml:space="preserve">3.05703473091125</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">2.98789358139038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96073126792908</t>
+    <t xml:space="preserve">2.96073079109192</t>
   </si>
   <si>
     <t xml:space="preserve">2.97307729721069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88418173789978</t>
+    <t xml:space="preserve">2.8841814994812</t>
   </si>
   <si>
     <t xml:space="preserve">2.91875219345093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03481101989746</t>
+    <t xml:space="preserve">3.03481030464172</t>
   </si>
   <si>
     <t xml:space="preserve">3.02987194061279</t>
@@ -455,31 +455,31 @@
     <t xml:space="preserve">3.0446879863739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99283242225647</t>
+    <t xml:space="preserve">2.99283218383789</t>
   </si>
   <si>
     <t xml:space="preserve">3.05950427055359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97554683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95085382461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96813917160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90393590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86442708969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87430453300476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81504034996033</t>
+    <t xml:space="preserve">2.97554659843445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9508535861969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96813941001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90393567085266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86442756652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8743040561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81504082679749</t>
   </si>
   <si>
     <t xml:space="preserve">2.90146708488464</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">2.83232545852661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86689639091492</t>
+    <t xml:space="preserve">2.86689615249634</t>
   </si>
   <si>
     <t xml:space="preserve">2.74096012115479</t>
@@ -497,118 +497,118 @@
     <t xml:space="preserve">2.70885872840881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79034733772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8249180316925</t>
+    <t xml:space="preserve">2.79034686088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82491779327393</t>
   </si>
   <si>
     <t xml:space="preserve">2.84220337867737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89158987998962</t>
+    <t xml:space="preserve">2.8915901184082</t>
   </si>
   <si>
     <t xml:space="preserve">2.87183475494385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90887475013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76812314987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82244849205017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85948848724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93850708007812</t>
+    <t xml:space="preserve">2.90887451171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76812267303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82244777679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85948824882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9385073184967</t>
   </si>
   <si>
     <t xml:space="preserve">3.25211238861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29409122467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25952076911926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03234195709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0274031162262</t>
+    <t xml:space="preserve">3.29409098625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2595202922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03234171867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02740287780762</t>
   </si>
   <si>
     <t xml:space="preserve">3.16568541526794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52373909950256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39780354499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47188305854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45953583717346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4792914390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49410653114319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55584096908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58547258377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57065677642822</t>
+    <t xml:space="preserve">3.52373933792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39780306816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47188282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45953607559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47929167747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49410724639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55584049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58547210693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57065606117249</t>
   </si>
   <si>
     <t xml:space="preserve">3.56077933311462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60028886795044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62251210212708</t>
+    <t xml:space="preserve">3.60028910636902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62251257896423</t>
   </si>
   <si>
     <t xml:space="preserve">3.55830955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72128486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81265115737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85709977149963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93364882469177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93117880821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97315812110901</t>
+    <t xml:space="preserve">3.72128558158875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81265163421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85709929466248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93364906311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93117928504944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97315764427185</t>
   </si>
   <si>
     <t xml:space="preserve">4.00525903701782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99044346809387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15341901779175</t>
+    <t xml:space="preserve">3.99044299125671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15341854095459</t>
   </si>
   <si>
     <t xml:space="preserve">4.19539785385132</t>
@@ -617,16 +617,16 @@
     <t xml:space="preserve">4.21762180328369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29664039611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30651760101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17564344406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26453924179077</t>
+    <t xml:space="preserve">4.29664087295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30651807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17564296722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26453971862793</t>
   </si>
   <si>
     <t xml:space="preserve">4.31392621994019</t>
@@ -638,25 +638,25 @@
     <t xml:space="preserve">4.2793550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42257642745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50653409957886</t>
+    <t xml:space="preserve">4.42257690429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5065336227417</t>
   </si>
   <si>
     <t xml:space="preserve">4.53863525390625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57073640823364</t>
+    <t xml:space="preserve">4.57073736190796</t>
   </si>
   <si>
     <t xml:space="preserve">4.88928031921387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95842170715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0127477645874</t>
+    <t xml:space="preserve">4.95842266082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01274728775024</t>
   </si>
   <si>
     <t xml:space="preserve">5.17078495025635</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.53616571426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34602785110474</t>
+    <t xml:space="preserve">4.34602689743042</t>
   </si>
   <si>
     <t xml:space="preserve">4.39047574996948</t>
@@ -683,13 +683,13 @@
     <t xml:space="preserve">4.64234733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71889734268188</t>
+    <t xml:space="preserve">4.71889686584473</t>
   </si>
   <si>
     <t xml:space="preserve">4.99793195724487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04237985610962</t>
+    <t xml:space="preserve">5.0423789024353</t>
   </si>
   <si>
     <t xml:space="preserve">5.10164356231689</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">5.1263370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95348358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98805332183838</t>
+    <t xml:space="preserve">4.95348405838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9880542755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.99299240112305</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">5.04731750488281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92385149002075</t>
+    <t xml:space="preserve">4.92385101318359</t>
   </si>
   <si>
     <t xml:space="preserve">4.78062963485718</t>
@@ -722,25 +722,25 @@
     <t xml:space="preserve">4.89915800094604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02756309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33869886398315</t>
+    <t xml:space="preserve">5.02756404876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33869934082031</t>
   </si>
   <si>
     <t xml:space="preserve">5.34363794326782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32388401031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25474166870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32882261276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1757230758667</t>
+    <t xml:space="preserve">5.32388305664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25474262237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32882213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17572402954102</t>
   </si>
   <si>
     <t xml:space="preserve">5.14609098434448</t>
@@ -749,28 +749,28 @@
     <t xml:space="preserve">5.18560028076172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18066167831421</t>
+    <t xml:space="preserve">5.18066215515137</t>
   </si>
   <si>
     <t xml:space="preserve">5.13127517700195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13621425628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16584634780884</t>
+    <t xml:space="preserve">5.13621377944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16584539413452</t>
   </si>
   <si>
     <t xml:space="preserve">5.09670400619507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14115190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22511100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30412817001343</t>
+    <t xml:space="preserve">5.14115238189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22511005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30412864685059</t>
   </si>
   <si>
     <t xml:space="preserve">5.21029472351074</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.98311567306519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94360542297363</t>
+    <t xml:space="preserve">4.94360589981079</t>
   </si>
   <si>
     <t xml:space="preserve">4.96336126327515</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">4.93372821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07694959640503</t>
+    <t xml:space="preserve">5.0769510269165</t>
   </si>
   <si>
     <t xml:space="preserve">5.07201147079468</t>
@@ -797,28 +797,28 @@
     <t xml:space="preserve">5.06213426589966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81026172637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83248615264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74358987808228</t>
+    <t xml:space="preserve">4.81026220321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83248662948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74359035491943</t>
   </si>
   <si>
     <t xml:space="preserve">4.78556823730469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7337121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71642732620239</t>
+    <t xml:space="preserve">4.73371267318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71642684936523</t>
   </si>
   <si>
     <t xml:space="preserve">4.70655012130737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69420289993286</t>
+    <t xml:space="preserve">4.69420337677002</t>
   </si>
   <si>
     <t xml:space="preserve">4.51888036727905</t>
@@ -830,34 +830,34 @@
     <t xml:space="preserve">4.64728593826294</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70408010482788</t>
+    <t xml:space="preserve">4.70407962799072</t>
   </si>
   <si>
     <t xml:space="preserve">4.63000106811523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79297637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78803777694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23498725891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91644287109375</t>
+    <t xml:space="preserve">4.79297685623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78803825378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23498678207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91644239425659</t>
   </si>
   <si>
     <t xml:space="preserve">4.97323799133301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05225706100464</t>
+    <t xml:space="preserve">5.0522575378418</t>
   </si>
   <si>
     <t xml:space="preserve">5.03744029998779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91891288757324</t>
+    <t xml:space="preserve">4.91891241073608</t>
   </si>
   <si>
     <t xml:space="preserve">4.94854497909546</t>
@@ -872,10 +872,10 @@
     <t xml:space="preserve">4.62012386322021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80038404464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72383546829224</t>
+    <t xml:space="preserve">4.80038452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72383594512939</t>
   </si>
   <si>
     <t xml:space="preserve">4.68926477432251</t>
@@ -887,40 +887,40 @@
     <t xml:space="preserve">4.67197895050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59049081802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58308362960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61518478393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8473014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83001661300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75346755981445</t>
+    <t xml:space="preserve">4.590491771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.583083152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61518526077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84730243682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83001613616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75346708297729</t>
   </si>
   <si>
     <t xml:space="preserve">4.80532360076904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75099802017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79544639587402</t>
+    <t xml:space="preserve">4.75099849700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79544591903687</t>
   </si>
   <si>
     <t xml:space="preserve">4.81767082214355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78309917449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72136688232422</t>
+    <t xml:space="preserve">4.78309965133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72136545181274</t>
   </si>
   <si>
     <t xml:space="preserve">4.684326171875</t>
@@ -932,37 +932,37 @@
     <t xml:space="preserve">4.77816104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76087474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55838966369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85507869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8600378036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78564882278442</t>
+    <t xml:space="preserve">4.76087522506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55839014053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86003732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78564929962158</t>
   </si>
   <si>
     <t xml:space="preserve">4.82532262802124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80548572540283</t>
+    <t xml:space="preserve">4.80548620223999</t>
   </si>
   <si>
     <t xml:space="preserve">4.87243556976318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95922183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99889516830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19230508804321</t>
+    <t xml:space="preserve">4.95922231674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99889612197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19230556488037</t>
   </si>
   <si>
     <t xml:space="preserve">5.1526312828064</t>
@@ -971,34 +971,34 @@
     <t xml:space="preserve">5.17246866226196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10799884796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17742776870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97410011291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97905969619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98897743225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03856992721558</t>
+    <t xml:space="preserve">5.10799837112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17742729187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97409963607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97905874252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98897790908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03856945037842</t>
   </si>
   <si>
     <t xml:space="preserve">5.03360986709595</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05840587615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07328414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02865076065063</t>
+    <t xml:space="preserve">5.05840682983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07328462600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02865123748779</t>
   </si>
   <si>
     <t xml:space="preserve">5.07824373245239</t>
@@ -1007,85 +1007,85 @@
     <t xml:space="preserve">5.0633659362793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95178318023682</t>
+    <t xml:space="preserve">4.95178270339966</t>
   </si>
   <si>
     <t xml:space="preserve">4.95426273345947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86995601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26669502258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40555286407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34604215621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30636882781982</t>
+    <t xml:space="preserve">4.86995649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26669406890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40555191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34604167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30636692047119</t>
   </si>
   <si>
     <t xml:space="preserve">5.67335081100464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68822717666626</t>
+    <t xml:space="preserve">5.68822765350342</t>
   </si>
   <si>
     <t xml:space="preserve">6.01553678512573</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19406843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1494345664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16431188583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0700888633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13951778411865</t>
+    <t xml:space="preserve">6.19406795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14943552017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1643123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07008838653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13951635360718</t>
   </si>
   <si>
     <t xml:space="preserve">6.27341651916504</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61560201644897</t>
+    <t xml:space="preserve">6.61560344696045</t>
   </si>
   <si>
     <t xml:space="preserve">6.53129482269287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50649929046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78421545028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70982694625854</t>
+    <t xml:space="preserve">6.50649976730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78421640396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7098274230957</t>
   </si>
   <si>
     <t xml:space="preserve">6.7247052192688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76933813095093</t>
+    <t xml:space="preserve">6.76933860778809</t>
   </si>
   <si>
     <t xml:space="preserve">6.80405282974243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96770668029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88339996337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99250411987305</t>
+    <t xml:space="preserve">6.96770715713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88340091705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99250364303589</t>
   </si>
   <si>
     <t xml:space="preserve">7.07680988311768</t>
@@ -1094,73 +1094,73 @@
     <t xml:space="preserve">7.14623928070068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18095397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4636287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31485271453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33468866348267</t>
+    <t xml:space="preserve">7.18095350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46362924575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31485223770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33469104766846</t>
   </si>
   <si>
     <t xml:space="preserve">7.38428258895874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36444473266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51818227767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58265066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56281328201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53801727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49338483810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40907716751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52314043045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4140362739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50330352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4239559173584</t>
+    <t xml:space="preserve">7.36444568634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51818037033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58264923095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56281423568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53801822662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49338626861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4090781211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52313947677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41403722763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50330448150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42395544052124</t>
   </si>
   <si>
     <t xml:space="preserve">7.45867013931274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41899585723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30989503860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37932300567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93795251846313</t>
+    <t xml:space="preserve">7.41899633407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30989360809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37932348251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93795204162598</t>
   </si>
   <si>
     <t xml:space="preserve">7.05697345733643</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02225828170776</t>
+    <t xml:space="preserve">7.02225875854492</t>
   </si>
   <si>
     <t xml:space="preserve">7.14127922058105</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">7.76614236831665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73142719268799</t>
+    <t xml:space="preserve">7.73142766952515</t>
   </si>
   <si>
     <t xml:space="preserve">7.66199827194214</t>
@@ -1187,52 +1187,52 @@
     <t xml:space="preserve">7.45371103286743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28013801574707</t>
+    <t xml:space="preserve">7.28013849258423</t>
   </si>
   <si>
     <t xml:space="preserve">7.33964872360229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37436294555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25038385391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43387508392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55785417556763</t>
+    <t xml:space="preserve">7.3743634223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25038290023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43387413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55785512924194</t>
   </si>
   <si>
     <t xml:space="preserve">7.24046421051025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2007908821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17103624343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15119743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00738048553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23550415039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19087219238281</t>
+    <t xml:space="preserve">7.20078992843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17103576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15119791030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00738096237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23550510406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19087171554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.53305864334106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52809810638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5082631111145</t>
+    <t xml:space="preserve">7.52809953689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50826358795166</t>
   </si>
   <si>
     <t xml:space="preserve">7.43883323669434</t>
@@ -1241,34 +1241,34 @@
     <t xml:space="preserve">7.44875192642212</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63720178604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65208005905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64216136932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69175434112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67191648483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39420080184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71159029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35628986358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88692665100098</t>
+    <t xml:space="preserve">7.63720273971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65208053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64216041564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69175338745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67191743850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297733306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39420127868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71159076690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35628890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88692760467529</t>
   </si>
   <si>
     <t xml:space="preserve">8.98115158081055</t>
@@ -1280,43 +1280,43 @@
     <t xml:space="preserve">9.21423530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42252254486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48699188232422</t>
+    <t xml:space="preserve">9.42252159118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48699378967285</t>
   </si>
   <si>
     <t xml:space="preserve">9.69032096862793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28862190246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32829761505127</t>
+    <t xml:space="preserve">9.28862285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32829666137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.50187015533447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69527816772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76470851898193</t>
+    <t xml:space="preserve">9.69527912139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76470947265625</t>
   </si>
   <si>
     <t xml:space="preserve">9.70519828796387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64072799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63080883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81925964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84108066558838</t>
+    <t xml:space="preserve">9.64072704315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63081073760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81925868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84107971191406</t>
   </si>
   <si>
     <t xml:space="preserve">9.68337821960449</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">9.65163898468018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5385684967041</t>
+    <t xml:space="preserve">9.53856754302979</t>
   </si>
   <si>
     <t xml:space="preserve">9.31937026977539</t>
@@ -1337,25 +1337,25 @@
     <t xml:space="preserve">9.35110950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89982128143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63698101043701</t>
+    <t xml:space="preserve">8.89982032775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63698291778564</t>
   </si>
   <si>
     <t xml:space="preserve">8.75302696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57548713684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77782249450684</t>
+    <t xml:space="preserve">8.5754861831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77782344818115</t>
   </si>
   <si>
     <t xml:space="preserve">8.82741546630859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0039644241333</t>
+    <t xml:space="preserve">9.00396347045898</t>
   </si>
   <si>
     <t xml:space="preserve">8.83733367919922</t>
@@ -1364,28 +1364,28 @@
     <t xml:space="preserve">8.94643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98908710479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80956363677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73814964294434</t>
+    <t xml:space="preserve">8.98908805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80956172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73814868927002</t>
   </si>
   <si>
     <t xml:space="preserve">8.6905403137207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8055944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71434497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47431945800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98930644989014</t>
+    <t xml:space="preserve">8.80559539794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7143440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47432041168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98930692672729</t>
   </si>
   <si>
     <t xml:space="preserve">8.01410293579102</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">8.46836757659912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55664348602295</t>
+    <t xml:space="preserve">8.556640625</t>
   </si>
   <si>
     <t xml:space="preserve">8.56259250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51597690582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5278787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53085517883301</t>
+    <t xml:space="preserve">8.51597595214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52787685394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53085422515869</t>
   </si>
   <si>
     <t xml:space="preserve">8.43266201019287</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">8.53184509277344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52589416503906</t>
+    <t xml:space="preserve">8.5258960723877</t>
   </si>
   <si>
     <t xml:space="preserve">8.35926628112793</t>
@@ -1424,55 +1424,55 @@
     <t xml:space="preserve">8.56457614898682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71732044219971</t>
+    <t xml:space="preserve">8.71732139587402</t>
   </si>
   <si>
     <t xml:space="preserve">8.42175102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25115394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18866634368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32554340362549</t>
+    <t xml:space="preserve">8.25115489959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18866729736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32554149627686</t>
   </si>
   <si>
     <t xml:space="preserve">8.15792083740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18370819091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78278255462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73517417907715</t>
+    <t xml:space="preserve">8.18370723724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78278350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73517322540283</t>
   </si>
   <si>
     <t xml:space="preserve">9.15869140625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07438468933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18943881988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31341934204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22613716125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40764331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43640899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36301231384277</t>
+    <t xml:space="preserve">9.07438373565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18943977355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31342029571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2261381149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4076452255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43640804290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36301136016846</t>
   </si>
   <si>
     <t xml:space="preserve">9.70916557312012</t>
@@ -1481,25 +1481,25 @@
     <t xml:space="preserve">9.76768398284912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63180255889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55840396881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75975036621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79149055480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393463134766</t>
+    <t xml:space="preserve">9.63180160522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55840492248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7597484588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79148864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393558502197</t>
   </si>
   <si>
     <t xml:space="preserve">9.68635272979736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41458797454834</t>
+    <t xml:space="preserve">9.41458702087402</t>
   </si>
   <si>
     <t xml:space="preserve">9.20927619934082</t>
@@ -1511,25 +1511,25 @@
     <t xml:space="preserve">9.21820259094238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51674842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5355920791626</t>
+    <t xml:space="preserve">9.51674747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53559398651123</t>
   </si>
   <si>
     <t xml:space="preserve">9.4800500869751</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29556655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30846118927002</t>
+    <t xml:space="preserve">9.29556560516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3084602355957</t>
   </si>
   <si>
     <t xml:space="preserve">9.42946434020996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41756248474121</t>
+    <t xml:space="preserve">9.41756439208984</t>
   </si>
   <si>
     <t xml:space="preserve">9.36697864532471</t>
@@ -1538,19 +1538,19 @@
     <t xml:space="preserve">9.30746936798096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36796951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19935703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43938446044922</t>
+    <t xml:space="preserve">9.36797046661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1993579864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4393835067749</t>
   </si>
   <si>
     <t xml:space="preserve">9.59609413146973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48600101470947</t>
+    <t xml:space="preserve">9.48600006103516</t>
   </si>
   <si>
     <t xml:space="preserve">9.31143569946289</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">9.3054838180542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10810852050781</t>
+    <t xml:space="preserve">9.1081075668335</t>
   </si>
   <si>
     <t xml:space="preserve">9.06446647644043</t>
@@ -1568,46 +1568,46 @@
     <t xml:space="preserve">9.42748165130615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62089061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.185471534729</t>
+    <t xml:space="preserve">9.62089157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18547058105469</t>
   </si>
   <si>
     <t xml:space="preserve">8.85221195220947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87601566314697</t>
+    <t xml:space="preserve">8.87601661682129</t>
   </si>
   <si>
     <t xml:space="preserve">8.8621301651001</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13984680175781</t>
+    <t xml:space="preserve">9.13984775543213</t>
   </si>
   <si>
     <t xml:space="preserve">8.90676212310791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98313426971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92660045623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85022735595703</t>
+    <t xml:space="preserve">8.9831371307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92659950256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85022830963135</t>
   </si>
   <si>
     <t xml:space="preserve">9.04462909698486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87403297424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92461490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79666996002197</t>
+    <t xml:space="preserve">8.87403202056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92461681365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79666900634766</t>
   </si>
   <si>
     <t xml:space="preserve">8.75005149841309</t>
@@ -1619,64 +1619,64 @@
     <t xml:space="preserve">8.18172454833984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92979574203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15296173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24123573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95558404922485</t>
+    <t xml:space="preserve">7.92979621887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15296268463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24123668670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95558452606201</t>
   </si>
   <si>
     <t xml:space="preserve">8.10039329528809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10237598419189</t>
+    <t xml:space="preserve">8.10237693786621</t>
   </si>
   <si>
     <t xml:space="preserve">8.03889942169189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50506782531738</t>
+    <t xml:space="preserve">8.50506687164307</t>
   </si>
   <si>
     <t xml:space="preserve">8.40687370300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46935939788818</t>
+    <t xml:space="preserve">8.4693603515625</t>
   </si>
   <si>
     <t xml:space="preserve">8.52291965484619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26305675506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21346378326416</t>
+    <t xml:space="preserve">8.2630558013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21346473693848</t>
   </si>
   <si>
     <t xml:space="preserve">8.25214576721191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19957828521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24917030334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22239112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33347606658936</t>
+    <t xml:space="preserve">8.19957733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24916934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22239208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33347702026367</t>
   </si>
   <si>
     <t xml:space="preserve">8.14105987548828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01906394958496</t>
+    <t xml:space="preserve">8.01906204223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.21048831939697</t>
@@ -1685,52 +1685,52 @@
     <t xml:space="preserve">7.16111707687378</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26426839828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23947286605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04804563522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04209518432617</t>
+    <t xml:space="preserve">7.2642674446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23947238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04804658889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04209470748901</t>
   </si>
   <si>
     <t xml:space="preserve">7.2434401512146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23352146148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2027759552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24839925765991</t>
+    <t xml:space="preserve">7.23352098464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20277452468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24839878082275</t>
   </si>
   <si>
     <t xml:space="preserve">7.17500257492065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04407978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97663307189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80801963806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7990927696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01729869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12243461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03713655471802</t>
+    <t xml:space="preserve">7.04407930374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97663402557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80802011489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79909324645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01729917526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12243509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0371356010437</t>
   </si>
   <si>
     <t xml:space="preserve">6.95977258682251</t>
@@ -1739,67 +1739,67 @@
     <t xml:space="preserve">7.18591213226318</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4348669052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42693138122559</t>
+    <t xml:space="preserve">7.43486642837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42693042755127</t>
   </si>
   <si>
     <t xml:space="preserve">7.36146879196167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22062730789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26823616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39320755004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22657871246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21566915512085</t>
+    <t xml:space="preserve">7.220627784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26823663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39320802688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22657918930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21566820144653</t>
   </si>
   <si>
     <t xml:space="preserve">7.167067527771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48247528076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40610265731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42792272567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45767831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48346614837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61934947967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73341178894043</t>
+    <t xml:space="preserve">7.4824743270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40610218048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42792177200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.457679271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48346567153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61934852600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73341083526611</t>
   </si>
   <si>
     <t xml:space="preserve">7.66001462936401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70266389846802</t>
+    <t xml:space="preserve">7.70266437530518</t>
   </si>
   <si>
     <t xml:space="preserve">7.66794872283936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51024580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68282699584961</t>
+    <t xml:space="preserve">7.51024436950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68282556533813</t>
   </si>
   <si>
     <t xml:space="preserve">7.6937370300293</t>
@@ -1808,85 +1808,85 @@
     <t xml:space="preserve">7.64017772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57769203186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52016401290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34460830688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42197275161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01035690307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9627480506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92803287506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94588756561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17797899246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87744951248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82587289810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66618680953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86455535888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95183706283569</t>
+    <t xml:space="preserve">7.57769107818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52016448974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34460878372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42197132110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0103554725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96274852752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92803335189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94588613510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17797756195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87744855880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82587432861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66618585586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86455488204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95183897018433</t>
   </si>
   <si>
     <t xml:space="preserve">6.78024816513062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04705429077148</t>
+    <t xml:space="preserve">7.0470552444458</t>
   </si>
   <si>
     <t xml:space="preserve">6.81992244720459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67015314102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75247669219971</t>
+    <t xml:space="preserve">6.67015361785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75247621536255</t>
   </si>
   <si>
     <t xml:space="preserve">7.02920198440552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1125168800354</t>
+    <t xml:space="preserve">7.11251640319824</t>
   </si>
   <si>
     <t xml:space="preserve">7.09664630889893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26129293441772</t>
+    <t xml:space="preserve">7.26129388809204</t>
   </si>
   <si>
     <t xml:space="preserve">7.28708124160767</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0867280960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30394268035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23054599761963</t>
+    <t xml:space="preserve">7.08672857284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30394124984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23054695129395</t>
   </si>
   <si>
     <t xml:space="preserve">7.13334560394287</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">7.1283860206604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94291019439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01233959197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.930016040802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99051856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33865690231323</t>
+    <t xml:space="preserve">6.94291210174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01234006881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93001747131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99051952362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33865737915039</t>
   </si>
   <si>
     <t xml:space="preserve">7.34758329391479</t>
@@ -1916,10 +1916,10 @@
     <t xml:space="preserve">7.30493402481079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49636030197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3485746383667</t>
+    <t xml:space="preserve">7.49635982513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34857559204102</t>
   </si>
   <si>
     <t xml:space="preserve">7.23451280593872</t>
@@ -1928,49 +1928,49 @@
     <t xml:space="preserve">6.86554718017578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8248815536499</t>
+    <t xml:space="preserve">6.82488250732422</t>
   </si>
   <si>
     <t xml:space="preserve">6.61064291000366</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78322458267212</t>
+    <t xml:space="preserve">6.78322410583496</t>
   </si>
   <si>
     <t xml:space="preserve">6.91613149642944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92208290100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86852216720581</t>
+    <t xml:space="preserve">6.92208242416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86852121353149</t>
   </si>
   <si>
     <t xml:space="preserve">6.82884883880615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82289791107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72272253036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50848340988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25754737854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28928518295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2317590713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15737009048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50253200531006</t>
+    <t xml:space="preserve">6.82289838790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72272109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50848293304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25754642486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28928470611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23175811767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15736961364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50253248214722</t>
   </si>
   <si>
     <t xml:space="preserve">6.5511326789856</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">6.62849617004395</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87645769119263</t>
+    <t xml:space="preserve">6.87645673751831</t>
   </si>
   <si>
     <t xml:space="preserve">7.01134920120239</t>
@@ -1988,31 +1988,31 @@
     <t xml:space="preserve">7.16012477874756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24443244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21070861816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32080411911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1055736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26724481582642</t>
+    <t xml:space="preserve">7.24443101882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21070909500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32080459594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10557317733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26724338531494</t>
   </si>
   <si>
     <t xml:space="preserve">7.1869044303894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18987989425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28509712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39816665649414</t>
+    <t xml:space="preserve">7.18988084793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28509759902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3981671333313</t>
   </si>
   <si>
     <t xml:space="preserve">7.47354793548584</t>
@@ -2021,16 +2021,16 @@
     <t xml:space="preserve">7.52710723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63543939590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44302082061768</t>
+    <t xml:space="preserve">6.63543891906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44302177429199</t>
   </si>
   <si>
     <t xml:space="preserve">6.4182243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3973970413208</t>
+    <t xml:space="preserve">6.39739656448364</t>
   </si>
   <si>
     <t xml:space="preserve">6.49757289886475</t>
@@ -2039,214 +2039,214 @@
     <t xml:space="preserve">6.40731477737427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45988273620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44897222518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45194721221924</t>
+    <t xml:space="preserve">6.4598822593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44897270202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4519476890564</t>
   </si>
   <si>
     <t xml:space="preserve">6.57692050933838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50154113769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51145839691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54617357254028</t>
+    <t xml:space="preserve">6.501540184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51145887374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54617261886597</t>
   </si>
   <si>
     <t xml:space="preserve">6.4559154510498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43806219100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41227436065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3626823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41524982452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64932537078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32697582244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36664915084839</t>
+    <t xml:space="preserve">6.43806266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41227340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36268186569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41524934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64932489395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32697534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36664962768555</t>
   </si>
   <si>
     <t xml:space="preserve">6.35871410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30416393280029</t>
+    <t xml:space="preserve">6.30416297912598</t>
   </si>
   <si>
     <t xml:space="preserve">6.25853824615479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26548051834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32003259658813</t>
+    <t xml:space="preserve">6.26548147201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32003307342529</t>
   </si>
   <si>
     <t xml:space="preserve">6.63643074035645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46980094909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49658012390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33590078353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46385049819946</t>
+    <t xml:space="preserve">6.46980142593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49658107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33590269088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4638500213623</t>
   </si>
   <si>
     <t xml:space="preserve">6.49162244796753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66122674942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52633571624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58187961578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73958206176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80603742599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80901193618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81000280380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93894481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86158037185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89133548736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89232683181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04308795928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09367227554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607570648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29303216934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28431129455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20211505889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14384698867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20939826965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19170999526978</t>
+    <t xml:space="preserve">6.66122770309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5263352394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58188009262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73958349227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80603694915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80901145935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81000471115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93894338607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86157989501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89133405685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89232778549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04308748245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09367179870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607618331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29303169250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28431081771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20211458206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14384841918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.209397315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19171094894409</t>
   </si>
   <si>
     <t xml:space="preserve">7.14488887786865</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04916715621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11263418197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07205629348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80673742294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73806619644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61112976074219</t>
+    <t xml:space="preserve">7.04916667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3737907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11263465881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07205581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80673789978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73806571960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61112833023071</t>
   </si>
   <si>
     <t xml:space="preserve">6.71309566497803</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81402015686035</t>
+    <t xml:space="preserve">6.81402063369751</t>
   </si>
   <si>
     <t xml:space="preserve">6.88997364044189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95448350906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93350172042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88365316390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82684993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62166261672974</t>
+    <t xml:space="preserve">6.95448398590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93350124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88365411758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82684946060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62166309356689</t>
   </si>
   <si>
     <t xml:space="preserve">6.64021015167236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16998958587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10623073577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01928615570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96132326126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62977838516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59268140792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84771728515625</t>
+    <t xml:space="preserve">7.16999053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10623025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01928758621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9613242149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62977695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59268093109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84771585464478</t>
   </si>
   <si>
     <t xml:space="preserve">6.78163909912109</t>
@@ -2255,130 +2255,130 @@
     <t xml:space="preserve">6.78743553161621</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76424980163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88133525848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94625329971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83728361129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89524507522583</t>
+    <t xml:space="preserve">6.7642502784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88133573532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94625377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83728408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89524555206299</t>
   </si>
   <si>
     <t xml:space="preserve">6.86278676986694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92422819137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98566818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06449699401855</t>
+    <t xml:space="preserve">6.92422771453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98566770553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06449747085571</t>
   </si>
   <si>
     <t xml:space="preserve">7.15028142929077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13521242141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14216756820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02160453796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03319787979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08072662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10970830917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1572380065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13057470321655</t>
+    <t xml:space="preserve">7.13521194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14216804504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02160501480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0331974029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.080726146698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10970783233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15723896026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13057565689087</t>
   </si>
   <si>
     <t xml:space="preserve">7.33112621307373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35315227508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32533025741577</t>
+    <t xml:space="preserve">7.35315275192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32532930374146</t>
   </si>
   <si>
     <t xml:space="preserve">7.28939342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20940494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20476627349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28707456588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28591585159302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05986022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07493114471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95900583267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17578649520874</t>
+    <t xml:space="preserve">7.20940399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20476722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28707504272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28591537475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05986070632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07493162155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95900440216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17578601837158</t>
   </si>
   <si>
     <t xml:space="preserve">7.3114185333252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19433403015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08768272399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.976393699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99842023849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76541090011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81873464584351</t>
+    <t xml:space="preserve">7.19433355331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08768367767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97639417648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99841928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76541042327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81873512268066</t>
   </si>
   <si>
     <t xml:space="preserve">6.86858320236206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72715520858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72367715835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82569122314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5857253074646</t>
+    <t xml:space="preserve">6.72715377807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7236762046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82569169998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58572435379028</t>
   </si>
   <si>
     <t xml:space="preserve">6.40719985961914</t>
@@ -2390,16 +2390,16 @@
     <t xml:space="preserve">6.46632242202759</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68194341659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69005823135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5451512336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.635573387146</t>
+    <t xml:space="preserve">6.68194389343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6900577545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54515075683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63557386398315</t>
   </si>
   <si>
     <t xml:space="preserve">6.74454307556152</t>
@@ -2408,166 +2408,166 @@
     <t xml:space="preserve">6.80482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86162757873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86394691467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08304595947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29055166244507</t>
+    <t xml:space="preserve">6.86162710189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86394643783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0830454826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29055213928223</t>
   </si>
   <si>
     <t xml:space="preserve">7.30562162399292</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37285852432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28243684768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28127765655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29287052154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18158292770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18737745285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07029342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92654657363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83148670196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84539747238159</t>
+    <t xml:space="preserve">7.37285947799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28243637084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28127813339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29287099838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1815824508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18737888336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07029294967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92654705047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83148717880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84539842605591</t>
   </si>
   <si>
     <t xml:space="preserve">6.87785673141479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81525707244873</t>
+    <t xml:space="preserve">6.81525754928589</t>
   </si>
   <si>
     <t xml:space="preserve">6.63093709945679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54051351547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53239917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57529306411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50921440124512</t>
+    <t xml:space="preserve">6.54051399230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53240013122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57529258728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5092134475708</t>
   </si>
   <si>
     <t xml:space="preserve">6.54862976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73410940170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87553930282593</t>
+    <t xml:space="preserve">6.73410987854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87553882598877</t>
   </si>
   <si>
     <t xml:space="preserve">6.91843128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07145357131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03899383544922</t>
+    <t xml:space="preserve">7.07145309448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03899335861206</t>
   </si>
   <si>
     <t xml:space="preserve">6.87206172943115</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95668840408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90915584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87321996688843</t>
+    <t xml:space="preserve">6.95668649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90915679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87321949005127</t>
   </si>
   <si>
     <t xml:space="preserve">6.86742353439331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90336132049561</t>
+    <t xml:space="preserve">6.90336036682129</t>
   </si>
   <si>
     <t xml:space="preserve">6.81062078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45980215072632</t>
+    <t xml:space="preserve">7.45980310440063</t>
   </si>
   <si>
     <t xml:space="preserve">8.07304859161377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12057876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32808399200439</t>
+    <t xml:space="preserve">8.12057781219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32808494567871</t>
   </si>
   <si>
     <t xml:space="preserve">8.37561416625977</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38025093078613</t>
+    <t xml:space="preserve">8.38025188446045</t>
   </si>
   <si>
     <t xml:space="preserve">8.40691471099854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48226642608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41038990020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51124572753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41386890411377</t>
+    <t xml:space="preserve">8.48226547241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41039180755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51124668121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41386985778809</t>
   </si>
   <si>
     <t xml:space="preserve">8.40807342529297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42198467254639</t>
+    <t xml:space="preserve">8.42198371887207</t>
   </si>
   <si>
     <t xml:space="preserve">8.1843376159668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19245147705078</t>
+    <t xml:space="preserve">8.1924524307251</t>
   </si>
   <si>
     <t xml:space="preserve">8.09623432159424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79019069671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74613952636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88177299499512</t>
+    <t xml:space="preserve">7.79019165039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74613857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88177251815796</t>
   </si>
   <si>
     <t xml:space="preserve">7.87713479995728</t>
@@ -2576,136 +2576,136 @@
     <t xml:space="preserve">7.89104509353638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82033157348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77859830856323</t>
+    <t xml:space="preserve">7.82033061981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77859878540039</t>
   </si>
   <si>
     <t xml:space="preserve">7.70440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65224075317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74845743179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68238067626953</t>
+    <t xml:space="preserve">7.65224027633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74845790863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68238019943237</t>
   </si>
   <si>
     <t xml:space="preserve">7.68701696395874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62093925476074</t>
+    <t xml:space="preserve">7.62094020843506</t>
   </si>
   <si>
     <t xml:space="preserve">7.57920598983765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46328163146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64760112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72411298751831</t>
+    <t xml:space="preserve">7.46328115463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64760255813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72411394119263</t>
   </si>
   <si>
     <t xml:space="preserve">7.80757999420166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88525009155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88409042358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91191291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82844495773315</t>
+    <t xml:space="preserve">7.88524913787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88409090042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91191148757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82844543457031</t>
   </si>
   <si>
     <t xml:space="preserve">7.78439378738403</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7415018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5803656578064</t>
+    <t xml:space="preserve">7.74150228500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58036518096924</t>
   </si>
   <si>
     <t xml:space="preserve">7.47719240188599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51196956634521</t>
+    <t xml:space="preserve">7.51196908950806</t>
   </si>
   <si>
     <t xml:space="preserve">7.41691112518311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43777751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43661832809448</t>
+    <t xml:space="preserve">7.43777704238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43661975860596</t>
   </si>
   <si>
     <t xml:space="preserve">7.39024782180786</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36822319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22911214828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21867704391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2059268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22099685668945</t>
+    <t xml:space="preserve">7.36822080612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22911071777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21867752075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20592594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22099637985229</t>
   </si>
   <si>
     <t xml:space="preserve">7.14680480957031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98218965530396</t>
+    <t xml:space="preserve">6.98219060897827</t>
   </si>
   <si>
     <t xml:space="preserve">7.03783464431763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96364164352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03087902069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91263580322266</t>
+    <t xml:space="preserve">6.96364212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03087949752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91263484954834</t>
   </si>
   <si>
     <t xml:space="preserve">6.80018758773804</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85235452651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19317531585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07608985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03203773498535</t>
+    <t xml:space="preserve">6.85235404968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19317483901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07609033584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03203916549683</t>
   </si>
   <si>
     <t xml:space="preserve">7.294029712677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10739040374756</t>
+    <t xml:space="preserve">7.10738945007324</t>
   </si>
   <si>
     <t xml:space="preserve">7.14100933074951</t>
@@ -2714,97 +2714,97 @@
     <t xml:space="preserve">7.11086750030518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1155047416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00189828872681</t>
+    <t xml:space="preserve">7.11550521850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00189733505249</t>
   </si>
   <si>
     <t xml:space="preserve">6.57297277450562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52544403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70165109634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51617002487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27620410919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34112167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37126302719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2843189239502</t>
+    <t xml:space="preserve">6.52544355392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70165061950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51616907119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27620315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3411226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37126398086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28431844711304</t>
   </si>
   <si>
     <t xml:space="preserve">6.09651947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43806314468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40676355361938</t>
+    <t xml:space="preserve">5.43806266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40676259994507</t>
   </si>
   <si>
     <t xml:space="preserve">5.51921081542969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53326463699341</t>
+    <t xml:space="preserve">4.53326511383057</t>
   </si>
   <si>
     <t xml:space="preserve">4.85785627365112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15534830093384</t>
+    <t xml:space="preserve">4.15534782409668</t>
   </si>
   <si>
     <t xml:space="preserve">3.97914123535156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54731917381287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36531519889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56123042106628</t>
+    <t xml:space="preserve">3.54731941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36531543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56123018264771</t>
   </si>
   <si>
     <t xml:space="preserve">3.40994739532471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84872531890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96117281913757</t>
+    <t xml:space="preserve">3.84872508049011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96117305755615</t>
   </si>
   <si>
     <t xml:space="preserve">3.99421143531799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75482511520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65744829177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80931043624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66498327255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64295792579651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368872642517</t>
+    <t xml:space="preserve">3.75482535362244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65744805335999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80930995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66498351097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64295768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368896484375</t>
   </si>
   <si>
     <t xml:space="preserve">3.83481383323669</t>
@@ -2819,16 +2819,16 @@
     <t xml:space="preserve">4.33503198623657</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32401990890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10434007644653</t>
+    <t xml:space="preserve">4.32402038574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10434055328369</t>
   </si>
   <si>
     <t xml:space="preserve">4.12057018280029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24403190612793</t>
+    <t xml:space="preserve">4.24403142929077</t>
   </si>
   <si>
     <t xml:space="preserve">4.30663061141968</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">4.35010242462158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26026058197021</t>
+    <t xml:space="preserve">4.26026105880737</t>
   </si>
   <si>
     <t xml:space="preserve">4.46197080612183</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">4.74135160446167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6462926864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38430070877075</t>
+    <t xml:space="preserve">4.64629220962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38430023193359</t>
   </si>
   <si>
     <t xml:space="preserve">4.44863986968994</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">4.42139673233032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40516757965088</t>
+    <t xml:space="preserve">4.40516710281372</t>
   </si>
   <si>
     <t xml:space="preserve">4.50370454788208</t>
@@ -2876,13 +2876,13 @@
     <t xml:space="preserve">4.42429494857788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4005298614502</t>
+    <t xml:space="preserve">4.40053033828735</t>
   </si>
   <si>
     <t xml:space="preserve">4.27475118637085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15476894378662</t>
+    <t xml:space="preserve">4.1547679901123</t>
   </si>
   <si>
     <t xml:space="preserve">4.17505502700806</t>
@@ -2891,34 +2891,34 @@
     <t xml:space="preserve">4.51703596115112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31242704391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25388383865356</t>
+    <t xml:space="preserve">4.31242752075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25388431549072</t>
   </si>
   <si>
     <t xml:space="preserve">4.29851579666138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59934282302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72859954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78192567825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60339975357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76511526107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.832932472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08217191696167</t>
+    <t xml:space="preserve">4.59934234619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72859907150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78192520141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6033992767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76511573791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83293199539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08217239379883</t>
   </si>
   <si>
     <t xml:space="preserve">5.04449558258057</t>
@@ -2930,25 +2930,25 @@
     <t xml:space="preserve">5.45255327224731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21316909790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0723180770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68164968490601</t>
+    <t xml:space="preserve">5.21316814422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07231855392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68164920806885</t>
   </si>
   <si>
     <t xml:space="preserve">4.74888610839844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7506251335144</t>
+    <t xml:space="preserve">4.75062465667725</t>
   </si>
   <si>
     <t xml:space="preserve">4.88625812530518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86770963668823</t>
+    <t xml:space="preserve">4.86771059036255</t>
   </si>
   <si>
     <t xml:space="preserve">4.85263967514038</t>
@@ -2963,13 +2963,13 @@
     <t xml:space="preserve">5.25374221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02247047424316</t>
+    <t xml:space="preserve">5.02246999740601</t>
   </si>
   <si>
     <t xml:space="preserve">5.09550285339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00508165359497</t>
+    <t xml:space="preserve">5.00508117675781</t>
   </si>
   <si>
     <t xml:space="preserve">5.11694955825806</t>
@@ -2984,40 +2984,40 @@
     <t xml:space="preserve">5.21606588363647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15868282318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21896409988403</t>
+    <t xml:space="preserve">5.15868234634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21896457672119</t>
   </si>
   <si>
     <t xml:space="preserve">5.20679235458374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09840154647827</t>
+    <t xml:space="preserve">5.09840202331543</t>
   </si>
   <si>
     <t xml:space="preserve">5.00276327133179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11984825134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24910449981689</t>
+    <t xml:space="preserve">5.11984872817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24910497665405</t>
   </si>
   <si>
     <t xml:space="preserve">5.20447301864624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25721979141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31692123413086</t>
+    <t xml:space="preserve">5.2572193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3169207572937</t>
   </si>
   <si>
     <t xml:space="preserve">5.31054496765137</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34184503555298</t>
+    <t xml:space="preserve">5.34184408187866</t>
   </si>
   <si>
     <t xml:space="preserve">5.35401678085327</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">5.30822706222534</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3412652015686</t>
+    <t xml:space="preserve">5.34126567840576</t>
   </si>
   <si>
     <t xml:space="preserve">5.26069736480713</t>
@@ -3035,16 +3035,16 @@
     <t xml:space="preserve">5.25895833969116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37488412857056</t>
+    <t xml:space="preserve">5.37488460540771</t>
   </si>
   <si>
     <t xml:space="preserve">5.30764770507812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99638700485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23693180084229</t>
+    <t xml:space="preserve">4.99638652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23693227767944</t>
   </si>
   <si>
     <t xml:space="preserve">5.44270038604736</t>
@@ -3056,52 +3056,52 @@
     <t xml:space="preserve">5.38937425613403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38183879852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47457933425903</t>
+    <t xml:space="preserve">5.38183927536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47457981109619</t>
   </si>
   <si>
     <t xml:space="preserve">5.76323366165161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74178791046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65716218948364</t>
+    <t xml:space="preserve">5.74178838729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65716171264648</t>
   </si>
   <si>
     <t xml:space="preserve">5.61658811569214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59340333938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56847953796387</t>
+    <t xml:space="preserve">5.59340381622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56848001480103</t>
   </si>
   <si>
     <t xml:space="preserve">5.58065223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47631883621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40618371963501</t>
+    <t xml:space="preserve">5.476318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40618276596069</t>
   </si>
   <si>
     <t xml:space="preserve">5.5800724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51631212234497</t>
+    <t xml:space="preserve">5.51631259918213</t>
   </si>
   <si>
     <t xml:space="preserve">5.54703330993652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47747802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45719051361084</t>
+    <t xml:space="preserve">5.47747850418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.457190990448</t>
   </si>
   <si>
     <t xml:space="preserve">5.35053968429565</t>
@@ -3110,25 +3110,25 @@
     <t xml:space="preserve">5.28736019134521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31750011444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37836170196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46646499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58470869064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57079792022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57137727737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73019504547119</t>
+    <t xml:space="preserve">5.31750059127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37836217880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46646451950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58470916748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57079839706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57137680053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73019599914551</t>
   </si>
   <si>
     <t xml:space="preserve">5.74642467498779</t>
@@ -3137,43 +3137,43 @@
     <t xml:space="preserve">5.78641891479492</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30750417709351</t>
+    <t xml:space="preserve">6.30750465393066</t>
   </si>
   <si>
     <t xml:space="preserve">6.266930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23910760879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01537179946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75975704193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92263174057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0223274230957</t>
+    <t xml:space="preserve">6.23910856246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01537132263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75975608825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92263126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02232694625854</t>
   </si>
   <si>
     <t xml:space="preserve">6.01189470291138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92958736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16491508483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02116775512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06753826141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99914264678955</t>
+    <t xml:space="preserve">5.92958688735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16491556167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02116727828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06753921508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99914216995239</t>
   </si>
   <si>
     <t xml:space="preserve">6.07681274414062</t>
@@ -3182,61 +3182,61 @@
     <t xml:space="preserve">6.18578290939331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20317125320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19041919708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10463523864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16375732421875</t>
+    <t xml:space="preserve">6.20317077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19041967391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1046347618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16375637054443</t>
   </si>
   <si>
     <t xml:space="preserve">6.06058263778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12666034698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99566459655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24954175949097</t>
+    <t xml:space="preserve">6.12666082382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99566507339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24954032897949</t>
   </si>
   <si>
     <t xml:space="preserve">6.22867441177368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24722242355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20548963546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35735177993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43386316299438</t>
+    <t xml:space="preserve">6.24722194671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20549058914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3573522567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43386268615723</t>
   </si>
   <si>
     <t xml:space="preserve">6.48023319244385</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37242269515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12550115585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12318229675293</t>
+    <t xml:space="preserve">6.37242317199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12550067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12318277359009</t>
   </si>
   <si>
     <t xml:space="preserve">6.11043119430542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27156686782837</t>
+    <t xml:space="preserve">6.27156734466553</t>
   </si>
   <si>
     <t xml:space="preserve">6.37937688827515</t>
@@ -3251,19 +3251,19 @@
     <t xml:space="preserve">6.91031742095947</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99146413803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07840776443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29750823974609</t>
+    <t xml:space="preserve">6.99146509170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07840919494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29750776290894</t>
   </si>
   <si>
     <t xml:space="preserve">7.31837368011475</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34851455688477</t>
+    <t xml:space="preserve">7.34851503372192</t>
   </si>
   <si>
     <t xml:space="preserve">7.50037717819214</t>
@@ -3272,25 +3272,25 @@
     <t xml:space="preserve">7.46559953689575</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44705057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58963871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64180612564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58616161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66615009307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57341003417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66731119155884</t>
+    <t xml:space="preserve">7.44705152511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58964014053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64180707931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58616256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66615104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.573410987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66731023788452</t>
   </si>
   <si>
     <t xml:space="preserve">7.63948774337769</t>
@@ -3299,25 +3299,25 @@
     <t xml:space="preserve">7.66846942901611</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8539514541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80294322967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77048397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98494482040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01624488830566</t>
+    <t xml:space="preserve">7.85395097732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80294227600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77048301696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98494529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01624584197998</t>
   </si>
   <si>
     <t xml:space="preserve">7.90611696243286</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01045036315918</t>
+    <t xml:space="preserve">8.01044845581055</t>
   </si>
   <si>
     <t xml:space="preserve">8.18781471252441</t>
@@ -3326,13 +3326,13 @@
     <t xml:space="preserve">8.29678440093994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34895133972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42082500457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25968933105469</t>
+    <t xml:space="preserve">8.348952293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42082595825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25968837738037</t>
   </si>
   <si>
     <t xml:space="preserve">8.46140003204346</t>
@@ -3341,16 +3341,16 @@
     <t xml:space="preserve">8.51588535308838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57036972045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51356601715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49733543395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62485408782959</t>
+    <t xml:space="preserve">8.57036876678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51356506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49733638763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62485504150391</t>
   </si>
   <si>
     <t xml:space="preserve">8.60166931152344</t>
@@ -3359,43 +3359,43 @@
     <t xml:space="preserve">8.57152843475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41271018981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33504104614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50545120239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46951293945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78281116485596</t>
+    <t xml:space="preserve">8.41271114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33504009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50545024871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46951484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78281021118164</t>
   </si>
   <si>
     <t xml:space="preserve">8.40054225921631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27200698852539</t>
+    <t xml:space="preserve">9.27200603485107</t>
   </si>
   <si>
     <t xml:space="preserve">9.32146072387695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1196346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84830379486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43663024902344</t>
+    <t xml:space="preserve">9.11963367462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84830284118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43662929534912</t>
   </si>
   <si>
     <t xml:space="preserve">8.60236835479736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30564308166504</t>
+    <t xml:space="preserve">8.30564403533936</t>
   </si>
   <si>
     <t xml:space="preserve">8.49945163726807</t>
@@ -3404,28 +3404,28 @@
     <t xml:space="preserve">8.37380981445312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42460155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68122863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69726848602295</t>
+    <t xml:space="preserve">8.42460060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.681227684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69726753234863</t>
   </si>
   <si>
     <t xml:space="preserve">8.76142406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93117237091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08889293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01805114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84295749664307</t>
+    <t xml:space="preserve">8.93117427825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08889198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01805210113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84295558929443</t>
   </si>
   <si>
     <t xml:space="preserve">8.79483890533447</t>
@@ -3440,31 +3440,31 @@
     <t xml:space="preserve">9.02206134796143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82825469970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87770938873291</t>
+    <t xml:space="preserve">8.82825374603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87770843505859</t>
   </si>
   <si>
     <t xml:space="preserve">8.94186496734619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82424545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86968898773193</t>
+    <t xml:space="preserve">8.82424449920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86968994140625</t>
   </si>
   <si>
     <t xml:space="preserve">9.07552623748779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06082248687744</t>
+    <t xml:space="preserve">9.06082439422607</t>
   </si>
   <si>
     <t xml:space="preserve">8.97795486450195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30542182922363</t>
+    <t xml:space="preserve">9.30542087554932</t>
   </si>
   <si>
     <t xml:space="preserve">9.28537178039551</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">9.2679967880249</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25062084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14369201660156</t>
+    <t xml:space="preserve">9.25061988830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14369297027588</t>
   </si>
   <si>
     <t xml:space="preserve">9.6796703338623</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">9.85610103607178</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0579290390015</t>
+    <t xml:space="preserve">10.0579280853271</t>
   </si>
   <si>
     <t xml:space="preserve">10.1755485534668</t>
@@ -3500,10 +3500,10 @@
     <t xml:space="preserve">10.5399112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6655044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9837713241577</t>
+    <t xml:space="preserve">10.6655054092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.983772277832</t>
   </si>
   <si>
     <t xml:space="preserve">10.5970001220703</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">10.4785413742065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1288747787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1374397277832</t>
+    <t xml:space="preserve">10.1288757324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1374387741089</t>
   </si>
   <si>
     <t xml:space="preserve">10.2801599502563</t>
@@ -3527,22 +3527,22 @@
     <t xml:space="preserve">10.4628419876099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7754001617432</t>
+    <t xml:space="preserve">10.7753992080688</t>
   </si>
   <si>
     <t xml:space="preserve">10.7639818191528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8010892868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9124126434326</t>
+    <t xml:space="preserve">10.8010902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9124116897583</t>
   </si>
   <si>
     <t xml:space="preserve">10.9109840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6526613235474</t>
+    <t xml:space="preserve">10.652660369873</t>
   </si>
   <si>
     <t xml:space="preserve">10.5613193511963</t>
@@ -3554,13 +3554,13 @@
     <t xml:space="preserve">10.8082256317139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7397203445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7340106964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8910045623779</t>
+    <t xml:space="preserve">10.7397184371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7340097427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8910036087036</t>
   </si>
   <si>
     <t xml:space="preserve">10.7816705703735</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">10.3457975387573</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4551296234131</t>
+    <t xml:space="preserve">10.4551305770874</t>
   </si>
   <si>
     <t xml:space="preserve">10.481369972229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4886598587036</t>
+    <t xml:space="preserve">10.4886589050293</t>
   </si>
   <si>
     <t xml:space="preserve">10.4667921066284</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">10.4288902282715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4901170730591</t>
+    <t xml:space="preserve">10.4901161193848</t>
   </si>
   <si>
     <t xml:space="preserve">10.09068775177</t>
@@ -3593,19 +3593,19 @@
     <t xml:space="preserve">10.0761108398438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2204294204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1227579116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312349319458</t>
+    <t xml:space="preserve">10.2204303741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1227588653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312339782715</t>
   </si>
   <si>
     <t xml:space="preserve">10.8705949783325</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0061683654785</t>
+    <t xml:space="preserve">11.0061674118042</t>
   </si>
   <si>
     <t xml:space="preserve">10.686915397644</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">10.7306489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6781692504883</t>
+    <t xml:space="preserve">10.678168296814</t>
   </si>
   <si>
     <t xml:space="preserve">10.8283195495605</t>
@@ -3626,31 +3626,31 @@
     <t xml:space="preserve">11.0003366470337</t>
   </si>
   <si>
-    <t xml:space="preserve">10.736478805542</t>
+    <t xml:space="preserve">10.7364797592163</t>
   </si>
   <si>
     <t xml:space="preserve">10.9376525878906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1636066436768</t>
+    <t xml:space="preserve">11.1636056900024</t>
   </si>
   <si>
     <t xml:space="preserve">11.2160863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2787714004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2583618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7190170288086</t>
+    <t xml:space="preserve">11.2787704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2583608627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7190160751343</t>
   </si>
   <si>
     <t xml:space="preserve">11.739426612854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502168655396</t>
+    <t xml:space="preserve">11.8502159118652</t>
   </si>
   <si>
     <t xml:space="preserve">11.9143590927124</t>
@@ -3668,16 +3668,16 @@
     <t xml:space="preserve">12.7219638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7379989624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5601501464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3910493850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5003824234009</t>
+    <t xml:space="preserve">12.737998008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5601511001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3910484313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5003814697266</t>
   </si>
   <si>
     <t xml:space="preserve">12.3677253723145</t>
@@ -3692,19 +3692,19 @@
     <t xml:space="preserve">12.3604364395142</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0003681182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4056272506714</t>
+    <t xml:space="preserve">12.0003671646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4056282043457</t>
   </si>
   <si>
     <t xml:space="preserve">12.3808450698853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3560628890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3852186203003</t>
+    <t xml:space="preserve">12.3560619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.385217666626</t>
   </si>
   <si>
     <t xml:space="preserve">12.436240196228</t>
@@ -3713,10 +3713,10 @@
     <t xml:space="preserve">12.2758855819702</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2613077163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0659685134888</t>
+    <t xml:space="preserve">12.2613086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0659666061401</t>
   </si>
   <si>
     <t xml:space="preserve">12.1738414764404</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">12.3414850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1942510604858</t>
+    <t xml:space="preserve">12.1942501068115</t>
   </si>
   <si>
     <t xml:space="preserve">12.0936641693115</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">11.688404083252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0164031982422</t>
+    <t xml:space="preserve">12.0164022445679</t>
   </si>
   <si>
     <t xml:space="preserve">11.8429269790649</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">11.8370971679688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6679954528809</t>
+    <t xml:space="preserve">11.6679935455322</t>
   </si>
   <si>
     <t xml:space="preserve">11.4332942962646</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">11.0222034454346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.049901008606</t>
+    <t xml:space="preserve">11.0499000549316</t>
   </si>
   <si>
     <t xml:space="preserve">11.4289207458496</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">11.3633213043213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4814004898071</t>
+    <t xml:space="preserve">11.4813995361328</t>
   </si>
   <si>
     <t xml:space="preserve">11.5790710449219</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">11.5324220657349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9201889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8006534576416</t>
+    <t xml:space="preserve">11.9201898574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8006525039673</t>
   </si>
   <si>
     <t xml:space="preserve">11.9318532943726</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">12.7175893783569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.714674949646</t>
+    <t xml:space="preserve">12.7146739959717</t>
   </si>
   <si>
     <t xml:space="preserve">13.0280961990356</t>
@@ -3797,22 +3797,22 @@
     <t xml:space="preserve">13.0834913253784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1330547332764</t>
+    <t xml:space="preserve">13.1330537796021</t>
   </si>
   <si>
     <t xml:space="preserve">13.4829187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5645561218262</t>
+    <t xml:space="preserve">13.5645551681519</t>
   </si>
   <si>
     <t xml:space="preserve">13.369213104248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0062284469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.105357170105</t>
+    <t xml:space="preserve">13.0062274932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1053562164307</t>
   </si>
   <si>
     <t xml:space="preserve">12.6388702392578</t>
@@ -3821,19 +3821,19 @@
     <t xml:space="preserve">12.4930925369263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5411996841431</t>
+    <t xml:space="preserve">12.5412006378174</t>
   </si>
   <si>
     <t xml:space="preserve">12.5732698440552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6024265289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.485803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5105857849121</t>
+    <t xml:space="preserve">12.6024255752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4858045578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5105867385864</t>
   </si>
   <si>
     <t xml:space="preserve">12.4041690826416</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">12.2744283676147</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4814319610596</t>
+    <t xml:space="preserve">12.4814310073853</t>
   </si>
   <si>
     <t xml:space="preserve">12.567440032959</t>
@@ -3872,28 +3872,28 @@
     <t xml:space="preserve">11.7044401168823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6854877471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0645084381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2219486236572</t>
+    <t xml:space="preserve">11.6854887008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0645093917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2219476699829</t>
   </si>
   <si>
     <t xml:space="preserve">12.2365255355835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3444013595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9770412445068</t>
+    <t xml:space="preserve">12.3444004058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9770421981812</t>
   </si>
   <si>
     <t xml:space="preserve">12.1432285308838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0426425933838</t>
+    <t xml:space="preserve">12.0426416397095</t>
   </si>
   <si>
     <t xml:space="preserve">11.8575048446655</t>
@@ -3905,34 +3905,34 @@
     <t xml:space="preserve">12.0674247741699</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6373815536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0790863037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1534337997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2642230987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2860898971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2671384811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4114580154419</t>
+    <t xml:space="preserve">11.6373825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0790872573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1534328460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2642240524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2860908508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2671394348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4114589691162</t>
   </si>
   <si>
     <t xml:space="preserve">12.3123302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2292356491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2598505020142</t>
+    <t xml:space="preserve">12.2292366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2598495483398</t>
   </si>
   <si>
     <t xml:space="preserve">12.284631729126</t>
@@ -3941,19 +3941,19 @@
     <t xml:space="preserve">12.281717300415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7656965255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.80797290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7992248535156</t>
+    <t xml:space="preserve">12.7656955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8079719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7992258071899</t>
   </si>
   <si>
     <t xml:space="preserve">12.5995101928711</t>
   </si>
   <si>
-    <t xml:space="preserve">12.719048500061</t>
+    <t xml:space="preserve">12.7190494537354</t>
   </si>
   <si>
     <t xml:space="preserve">12.7321672439575</t>
@@ -3962,28 +3962,28 @@
     <t xml:space="preserve">12.7904787063599</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8575353622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9143886566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7817316055298</t>
+    <t xml:space="preserve">12.857536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9143896102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7817325592041</t>
   </si>
   <si>
     <t xml:space="preserve">12.7117595672607</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0339269638062</t>
+    <t xml:space="preserve">13.0339260101318</t>
   </si>
   <si>
     <t xml:space="preserve">13.0368413925171</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0295534133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1855344772339</t>
+    <t xml:space="preserve">13.0295524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1855354309082</t>
   </si>
   <si>
     <t xml:space="preserve">13.0878639221191</t>
@@ -3992,43 +3992,43 @@
     <t xml:space="preserve">13.093695640564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248792648315</t>
+    <t xml:space="preserve">12.7248802185059</t>
   </si>
   <si>
     <t xml:space="preserve">12.3983383178711</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2511024475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1782150268555</t>
+    <t xml:space="preserve">12.2511043548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1782159805298</t>
   </si>
   <si>
     <t xml:space="preserve">11.3458280563354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3472852706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0353240966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6621646881104</t>
+    <t xml:space="preserve">11.3472862243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0353231430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.662163734436</t>
   </si>
   <si>
     <t xml:space="preserve">11.6096849441528</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4755706787109</t>
+    <t xml:space="preserve">11.4755697250366</t>
   </si>
   <si>
     <t xml:space="preserve">11.8749990463257</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2977514266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1592645645142</t>
+    <t xml:space="preserve">12.2977523803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1592636108398</t>
   </si>
   <si>
     <t xml:space="preserve">11.9887046813965</t>
@@ -4046,10 +4046,10 @@
     <t xml:space="preserve">11.8924922943115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9639225006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5309648513794</t>
+    <t xml:space="preserve">11.963921546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5309638977051</t>
   </si>
   <si>
     <t xml:space="preserve">11.886661529541</t>
@@ -4064,16 +4064,16 @@
     <t xml:space="preserve">12.1621799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301231384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9114742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4318971633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.299241065979</t>
+    <t xml:space="preserve">12.6301221847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9114751815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4318981170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2992420196533</t>
   </si>
   <si>
     <t xml:space="preserve">13.1213932037354</t>
@@ -4088,13 +4088,13 @@
     <t xml:space="preserve">13.3969106674194</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8561086654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8298692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9508619308472</t>
+    <t xml:space="preserve">13.8561096191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8298683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9508628845215</t>
   </si>
   <si>
     <t xml:space="preserve">13.9173345565796</t>
@@ -4103,16 +4103,16 @@
     <t xml:space="preserve">13.8415298461914</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6986703872681</t>
+    <t xml:space="preserve">13.6986694335938</t>
   </si>
   <si>
     <t xml:space="preserve">13.2132320404053</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1009531021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6855182647705</t>
+    <t xml:space="preserve">12.1009521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6855192184448</t>
   </si>
   <si>
     <t xml:space="preserve">12.7861051559448</t>
@@ -4127,25 +4127,25 @@
     <t xml:space="preserve">12.6417856216431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6636533737183</t>
+    <t xml:space="preserve">12.6636524200439</t>
   </si>
   <si>
     <t xml:space="preserve">11.998908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8822870254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9814167022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4683122634888</t>
+    <t xml:space="preserve">11.882287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9814157485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4683132171631</t>
   </si>
   <si>
     <t xml:space="preserve">12.3618927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2234058380127</t>
+    <t xml:space="preserve">12.223406791687</t>
   </si>
   <si>
     <t xml:space="preserve">11.9099855422974</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">12.5149602890015</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665525436401</t>
+    <t xml:space="preserve">12.1665534973145</t>
   </si>
   <si>
     <t xml:space="preserve">11.8837461471558</t>
@@ -4166,25 +4166,25 @@
     <t xml:space="preserve">12.4391555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6869468688965</t>
+    <t xml:space="preserve">11.6869459152222</t>
   </si>
   <si>
     <t xml:space="preserve">12.3064994812012</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1052961349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2190017700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9041242599487</t>
+    <t xml:space="preserve">11.1052951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2190027236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9041233062744</t>
   </si>
   <si>
     <t xml:space="preserve">10.0746517181396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43031692504883</t>
+    <t xml:space="preserve">9.43031787872314</t>
   </si>
   <si>
     <t xml:space="preserve">9.42594432830811</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">10.2043933868408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3180990219116</t>
+    <t xml:space="preserve">10.3180999755859</t>
   </si>
   <si>
     <t xml:space="preserve">10.9770126342773</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">10.6475563049316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8035373687744</t>
+    <t xml:space="preserve">10.8035364151001</t>
   </si>
   <si>
     <t xml:space="preserve">10.6373510360718</t>
@@ -4226,13 +4226,13 @@
     <t xml:space="preserve">10.5046939849854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5207290649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5323925018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2321214675903</t>
+    <t xml:space="preserve">10.5207300186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5323915481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2321224212646</t>
   </si>
   <si>
     <t xml:space="preserve">11.0542736053467</t>
@@ -4244,7 +4244,7 @@
     <t xml:space="preserve">10.7802124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8516426086426</t>
+    <t xml:space="preserve">10.8516435623169</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522142410278</t>
@@ -4253,25 +4253,25 @@
     <t xml:space="preserve">9.98718547821045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86910724639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0338344573975</t>
+    <t xml:space="preserve">9.86910629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0338354110718</t>
   </si>
   <si>
     <t xml:space="preserve">10.1475410461426</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1358785629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1854429244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2583312988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5054616928101</t>
+    <t xml:space="preserve">10.1358795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1854419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2583303451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5054626464844</t>
   </si>
   <si>
     <t xml:space="preserve">10.5621299743652</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">9.94823551177979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0710144042969</t>
+    <t xml:space="preserve">10.0710134506226</t>
   </si>
   <si>
     <t xml:space="preserve">10.2174043655396</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">10.2237005233765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0914764404297</t>
+    <t xml:space="preserve">10.091477394104</t>
   </si>
   <si>
     <t xml:space="preserve">10.0190687179565</t>
@@ -4337,7 +4337,7 @@
     <t xml:space="preserve">10.6313905715942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6030569076538</t>
+    <t xml:space="preserve">10.6030559539795</t>
   </si>
   <si>
     <t xml:space="preserve">10.6565752029419</t>
@@ -4349,28 +4349,28 @@
     <t xml:space="preserve">10.3386087417603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5306482315063</t>
+    <t xml:space="preserve">10.5306491851807</t>
   </si>
   <si>
     <t xml:space="preserve">10.7903728485107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8202810287476</t>
+    <t xml:space="preserve">10.8202800750732</t>
   </si>
   <si>
     <t xml:space="preserve">11.0186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9666700363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1571340560913</t>
+    <t xml:space="preserve">10.9666709899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1571350097656</t>
   </si>
   <si>
     <t xml:space="preserve">11.2263946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8549098968506</t>
+    <t xml:space="preserve">10.8549108505249</t>
   </si>
   <si>
     <t xml:space="preserve">11.064263343811</t>
@@ -4385,13 +4385,13 @@
     <t xml:space="preserve">10.7919464111328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2252740859985</t>
+    <t xml:space="preserve">10.2252750396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.82388305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82073307037354</t>
+    <t xml:space="preserve">9.82073497772217</t>
   </si>
   <si>
     <t xml:space="preserve">10.0977735519409</t>
@@ -4403,25 +4403,25 @@
     <t xml:space="preserve">9.63027000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74989986419678</t>
+    <t xml:space="preserve">9.74990081787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.99388408660889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82230854034424</t>
+    <t xml:space="preserve">9.82230758666992</t>
   </si>
   <si>
     <t xml:space="preserve">9.61295509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78138160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77508640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86953067779541</t>
+    <t xml:space="preserve">9.78138256072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77508544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86953163146973</t>
   </si>
   <si>
     <t xml:space="preserve">9.59406566619873</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">9.28082180023193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22415542602539</t>
+    <t xml:space="preserve">9.22415447235107</t>
   </si>
   <si>
     <t xml:space="preserve">9.12656116485596</t>
@@ -4439,28 +4439,28 @@
     <t xml:space="preserve">8.84637355804443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.818039894104</t>
+    <t xml:space="preserve">8.81804084777832</t>
   </si>
   <si>
     <t xml:space="preserve">9.44295406341553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80499267578125</t>
+    <t xml:space="preserve">9.80499362945557</t>
   </si>
   <si>
     <t xml:space="preserve">9.60193634033203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67906665802002</t>
+    <t xml:space="preserve">9.67906761169434</t>
   </si>
   <si>
     <t xml:space="preserve">9.4445276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20211887359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40989875793457</t>
+    <t xml:space="preserve">9.20211791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40989780426025</t>
   </si>
   <si>
     <t xml:space="preserve">9.64443683624268</t>
@@ -4478,13 +4478,13 @@
     <t xml:space="preserve">9.9545316696167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1150884628296</t>
+    <t xml:space="preserve">10.1150894165039</t>
   </si>
   <si>
     <t xml:space="preserve">10.0348100662231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1764783859253</t>
+    <t xml:space="preserve">10.176477432251</t>
   </si>
   <si>
     <t xml:space="preserve">10.677038192749</t>
@@ -4493,10 +4493,10 @@
     <t xml:space="preserve">10.9572257995605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0548181533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2405614852905</t>
+    <t xml:space="preserve">11.0548191070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2405605316162</t>
   </si>
   <si>
     <t xml:space="preserve">11.3523216247559</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">11.2799139022827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6340827941895</t>
+    <t xml:space="preserve">11.6340837478638</t>
   </si>
   <si>
     <t xml:space="preserve">11.3381547927856</t>
@@ -4526,16 +4526,16 @@
     <t xml:space="preserve">11.726954460144</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223236083984</t>
+    <t xml:space="preserve">11.5223245620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.7049179077148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680629730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9021320343018</t>
+    <t xml:space="preserve">11.3680639266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9021329879761</t>
   </si>
   <si>
     <t xml:space="preserve">11.0500965118408</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">10.8139839172363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8265771865845</t>
+    <t xml:space="preserve">10.8265762329102</t>
   </si>
   <si>
     <t xml:space="preserve">10.7195386886597</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">10.6046304702759</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0961999893188</t>
+    <t xml:space="preserve">10.0961990356445</t>
   </si>
   <si>
     <t xml:space="preserve">10.2315711975098</t>
@@ -4574,10 +4574,10 @@
     <t xml:space="preserve">10.3401832580566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4613885879517</t>
+    <t xml:space="preserve">10.3323125839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4613876342773</t>
   </si>
   <si>
     <t xml:space="preserve">10.8124103546143</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">10.7699098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5463895797729</t>
+    <t xml:space="preserve">10.5463886260986</t>
   </si>
   <si>
     <t xml:space="preserve">10.6329641342163</t>
@@ -4601,10 +4601,10 @@
     <t xml:space="preserve">10.4047212600708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4912967681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.237868309021</t>
+    <t xml:space="preserve">10.4912958145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2378673553467</t>
   </si>
   <si>
     <t xml:space="preserve">10.0111989974976</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">10.0946264266968</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65860366821289</t>
+    <t xml:space="preserve">9.65860462188721</t>
   </si>
   <si>
     <t xml:space="preserve">9.84906768798828</t>
@@ -4628,10 +4628,10 @@
     <t xml:space="preserve">9.86480903625488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68064117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5893440246582</t>
+    <t xml:space="preserve">9.68064022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58934307098389</t>
   </si>
   <si>
     <t xml:space="preserve">9.69638156890869</t>
@@ -4640,10 +4640,10 @@
     <t xml:space="preserve">9.5972146987915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82703018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83647441864014</t>
+    <t xml:space="preserve">9.82703113555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83647537231445</t>
   </si>
   <si>
     <t xml:space="preserve">10.0851812362671</t>
@@ -4655,10 +4655,10 @@
     <t xml:space="preserve">10.2063865661621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3685169219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.289813041687</t>
+    <t xml:space="preserve">10.3685178756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2898120880127</t>
   </si>
   <si>
     <t xml:space="preserve">10.6487045288086</t>
@@ -4679,19 +4679,19 @@
     <t xml:space="preserve">10.8092622756958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4566659927368</t>
+    <t xml:space="preserve">10.4566669464111</t>
   </si>
   <si>
     <t xml:space="preserve">10.8297252655029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7872257232666</t>
+    <t xml:space="preserve">10.7872247695923</t>
   </si>
   <si>
     <t xml:space="preserve">11.1429681777954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1980600357056</t>
+    <t xml:space="preserve">11.1980609893799</t>
   </si>
   <si>
     <t xml:space="preserve">11.339729309082</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">11.4247303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2153768539429</t>
+    <t xml:space="preserve">11.2153759002686</t>
   </si>
   <si>
     <t xml:space="preserve">11.1036157608032</t>
@@ -4718,10 +4718,10 @@
     <t xml:space="preserve">11.3838033676147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5333423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5301933288574</t>
+    <t xml:space="preserve">11.5333433151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5301942825317</t>
   </si>
   <si>
     <t xml:space="preserve">11.4546375274658</t>
@@ -4730,19 +4730,19 @@
     <t xml:space="preserve">11.5774164199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206592559814</t>
+    <t xml:space="preserve">11.7206583023071</t>
   </si>
   <si>
     <t xml:space="preserve">11.7332515716553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4924154281616</t>
+    <t xml:space="preserve">11.4924163818359</t>
   </si>
   <si>
     <t xml:space="preserve">11.5364904403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3712110519409</t>
+    <t xml:space="preserve">11.3712120056152</t>
   </si>
   <si>
     <t xml:space="preserve">11.3979711532593</t>
@@ -4757,10 +4757,10 @@
     <t xml:space="preserve">10.8486137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8612060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9336137771606</t>
+    <t xml:space="preserve">10.8612070083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.933614730835</t>
   </si>
   <si>
     <t xml:space="preserve">10.6675939559937</t>
@@ -4775,13 +4775,13 @@
     <t xml:space="preserve">10.3559246063232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3244428634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.52907371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4393510818481</t>
+    <t xml:space="preserve">10.32444190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5290746688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4393520355225</t>
   </si>
   <si>
     <t xml:space="preserve">10.7415761947632</t>
@@ -4790,13 +4790,13 @@
     <t xml:space="preserve">10.8816699981689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1697282791138</t>
+    <t xml:space="preserve">11.1697273254395</t>
   </si>
   <si>
     <t xml:space="preserve">11.2862100601196</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3696365356445</t>
+    <t xml:space="preserve">11.3696374893188</t>
   </si>
   <si>
     <t xml:space="preserve">11.5427875518799</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">11.5286197662354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6246395111084</t>
+    <t xml:space="preserve">11.6246404647827</t>
   </si>
   <si>
     <t xml:space="preserve">11.1996355056763</t>
@@ -4814,7 +4814,7 @@
     <t xml:space="preserve">11.2673206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3035259246826</t>
+    <t xml:space="preserve">11.3035249710083</t>
   </si>
   <si>
     <t xml:space="preserve">11.2295427322388</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">11.0312070846558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0343561172485</t>
+    <t xml:space="preserve">11.0343570709229</t>
   </si>
   <si>
     <t xml:space="preserve">10.95250415802</t>
@@ -4850,16 +4850,16 @@
     <t xml:space="preserve">11.9693651199341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9630689620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8686237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8749189376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9016790390015</t>
+    <t xml:space="preserve">11.9630680084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8686218261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8749198913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9016780853271</t>
   </si>
   <si>
     <t xml:space="preserve">12.3392753601074</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">12.2054777145386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.258996963501</t>
+    <t xml:space="preserve">12.2589960098267</t>
   </si>
   <si>
     <t xml:space="preserve">12.4903879165649</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">12.946873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0901155471802</t>
+    <t xml:space="preserve">13.0901145935059</t>
   </si>
   <si>
     <t xml:space="preserve">13.0287265777588</t>
@@ -4913,31 +4913,31 @@
     <t xml:space="preserve">13.9054918289185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8330850601196</t>
+    <t xml:space="preserve">13.8330841064453</t>
   </si>
   <si>
     <t xml:space="preserve">13.7968807220459</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7653980255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5387296676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2915992736816</t>
+    <t xml:space="preserve">13.765398979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5387306213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2915983200073</t>
   </si>
   <si>
     <t xml:space="preserve">12.7532606124878</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9027986526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4305715560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5265913009644</t>
+    <t xml:space="preserve">12.9027976989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4305725097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5265922546387</t>
   </si>
   <si>
     <t xml:space="preserve">12.4714984893799</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">12.7737226486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7910394668579</t>
+    <t xml:space="preserve">12.7910385131836</t>
   </si>
   <si>
     <t xml:space="preserve">12.9153909683228</t>
@@ -4991,19 +4991,19 @@
     <t xml:space="preserve">13.2443752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5088224411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3624324798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4049320220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3545618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6320552825928</t>
+    <t xml:space="preserve">13.5088214874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3624334335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.404932975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3545627593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6320543289185</t>
   </si>
   <si>
     <t xml:space="preserve">12.5486288070679</t>
@@ -5051,13 +5051,13 @@
     <t xml:space="preserve">12.770318031311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6242437362671</t>
+    <t xml:space="preserve">12.6242446899414</t>
   </si>
   <si>
     <t xml:space="preserve">12.7514142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0143480300903</t>
+    <t xml:space="preserve">13.014347076416</t>
   </si>
   <si>
     <t xml:space="preserve">13.2600955963135</t>
@@ -5066,13 +5066,13 @@
     <t xml:space="preserve">13.1655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0934000015259</t>
+    <t xml:space="preserve">13.0933990478516</t>
   </si>
   <si>
     <t xml:space="preserve">12.5623769760132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4334878921509</t>
+    <t xml:space="preserve">12.4334888458252</t>
   </si>
   <si>
     <t xml:space="preserve">12.6929845809937</t>
@@ -5114,7 +5114,7 @@
     <t xml:space="preserve">13.5470886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5178737640381</t>
+    <t xml:space="preserve">13.5178747177124</t>
   </si>
   <si>
     <t xml:space="preserve">13.6261405944824</t>
@@ -5129,13 +5129,13 @@
     <t xml:space="preserve">13.2033843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0813703536987</t>
+    <t xml:space="preserve">13.0813694000244</t>
   </si>
   <si>
     <t xml:space="preserve">12.9885702133179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0469999313354</t>
+    <t xml:space="preserve">13.0469989776611</t>
   </si>
   <si>
     <t xml:space="preserve">13.1587028503418</t>
@@ -5150,7 +5150,7 @@
     <t xml:space="preserve">13.8254890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.999059677124</t>
+    <t xml:space="preserve">13.9990587234497</t>
   </si>
   <si>
     <t xml:space="preserve">13.9681262969971</t>
@@ -5168,7 +5168,7 @@
     <t xml:space="preserve">13.9767189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0437412261963</t>
+    <t xml:space="preserve">14.043740272522</t>
   </si>
   <si>
     <t xml:space="preserve">14.3736963272095</t>
@@ -5177,52 +5177,52 @@
     <t xml:space="preserve">14.4458742141724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3547925949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2671489715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2551193237305</t>
+    <t xml:space="preserve">14.3547916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2671480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2551183700562</t>
   </si>
   <si>
     <t xml:space="preserve">14.3152666091919</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1863784790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4149408340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4235334396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8050441741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.593846321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650459289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0200386047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192983627319</t>
+    <t xml:space="preserve">14.1863775253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4149398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4235324859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8050451278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5938453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650449752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0200366973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192974090576</t>
   </si>
   <si>
     <t xml:space="preserve">15.5147933959961</t>
   </si>
   <si>
-    <t xml:space="preserve">15.373875617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3446598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2982606887817</t>
+    <t xml:space="preserve">15.3738746643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3446588516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2982597351074</t>
   </si>
   <si>
     <t xml:space="preserve">15.0834455490112</t>
@@ -5240,31 +5240,31 @@
     <t xml:space="preserve">14.5197706222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3221406936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1571636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0523338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3015184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3633852005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.378851890564</t>
+    <t xml:space="preserve">14.3221397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1571626663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0523328781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3015174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3633842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3788509368896</t>
   </si>
   <si>
     <t xml:space="preserve">14.2173109054565</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3668222427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5489845275879</t>
+    <t xml:space="preserve">14.3668212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5489854812622</t>
   </si>
   <si>
     <t xml:space="preserve">14.7964515686035</t>
@@ -5273,10 +5273,10 @@
     <t xml:space="preserve">14.7500524520874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7586450576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4355630874634</t>
+    <t xml:space="preserve">14.7586460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4355621337891</t>
   </si>
   <si>
     <t xml:space="preserve">14.4493112564087</t>
@@ -5288,7 +5288,7 @@
     <t xml:space="preserve">14.5386743545532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5661697387695</t>
+    <t xml:space="preserve">14.5661706924438</t>
   </si>
   <si>
     <t xml:space="preserve">14.6074151992798</t>
@@ -5303,13 +5303,13 @@
     <t xml:space="preserve">15.2673263549805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1006298065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3859052658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2827930450439</t>
+    <t xml:space="preserve">15.1006288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3859033584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2827920913696</t>
   </si>
   <si>
     <t xml:space="preserve">15.5113563537598</t>
@@ -5318,43 +5318,43 @@
     <t xml:space="preserve">15.9959783554077</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6058759689331</t>
+    <t xml:space="preserve">15.6058750152588</t>
   </si>
   <si>
     <t xml:space="preserve">15.712423324585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5251054763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4512090682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.607593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6471185684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.55260181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999782562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.231237411499</t>
+    <t xml:space="preserve">15.5251045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4512071609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6075925827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6471195220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5526008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2312364578247</t>
   </si>
   <si>
     <t xml:space="preserve">15.3137273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4649562835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9444236755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2726612091064</t>
+    <t xml:space="preserve">15.464955329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9444227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2726593017578</t>
   </si>
   <si>
     <t xml:space="preserve">16.246883392334</t>
@@ -5366,25 +5366,25 @@
     <t xml:space="preserve">16.0681571960449</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2348537445068</t>
+    <t xml:space="preserve">16.2348518371582</t>
   </si>
   <si>
     <t xml:space="preserve">16.1300239562988</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5405721664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1642160415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4855785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2759189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1848382949829</t>
+    <t xml:space="preserve">15.5405702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1642150878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.485577583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.275918006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1848392486572</t>
   </si>
   <si>
     <t xml:space="preserve">14.8806600570679</t>
@@ -5393,16 +5393,16 @@
     <t xml:space="preserve">14.6417865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.122971534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4168376922607</t>
+    <t xml:space="preserve">15.1229705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4168367385864</t>
   </si>
   <si>
     <t xml:space="preserve">15.7553873062134</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0647201538086</t>
+    <t xml:space="preserve">16.06471824646</t>
   </si>
   <si>
     <t xml:space="preserve">15.7467937469482</t>
@@ -5414,16 +5414,16 @@
     <t xml:space="preserve">15.5749416351318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7364816665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0440998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2211036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.894585609436</t>
+    <t xml:space="preserve">15.7364826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0440979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2211055755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8945846557617</t>
   </si>
   <si>
     <t xml:space="preserve">15.8705272674561</t>
@@ -5438,7 +5438,7 @@
     <t xml:space="preserve">16.1094017028809</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0939350128174</t>
+    <t xml:space="preserve">16.0939331054688</t>
   </si>
   <si>
     <t xml:space="preserve">16.9394454956055</t>
@@ -5447,7 +5447,7 @@
     <t xml:space="preserve">17.1009864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2754154205322</t>
+    <t xml:space="preserve">17.2754173278809</t>
   </si>
   <si>
     <t xml:space="preserve">17.4472694396973</t>
@@ -5456,7 +5456,7 @@
     <t xml:space="preserve">17.5847511291504</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0960102081299</t>
+    <t xml:space="preserve">18.0960083007812</t>
   </si>
   <si>
     <t xml:space="preserve">17.9714183807373</t>
@@ -5468,7 +5468,7 @@
     <t xml:space="preserve">18.0530471801758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0186767578125</t>
+    <t xml:space="preserve">18.0186748504639</t>
   </si>
   <si>
     <t xml:space="preserve">17.9671211242676</t>
@@ -5486,28 +5486,28 @@
     <t xml:space="preserve">18.289342880249</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2506771087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2549743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2377891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2420845031738</t>
+    <t xml:space="preserve">18.250675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2549724578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2377872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2420825958252</t>
   </si>
   <si>
     <t xml:space="preserve">18.2034168243408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1733436584473</t>
+    <t xml:space="preserve">18.1733417510986</t>
   </si>
   <si>
     <t xml:space="preserve">18.19482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5718612670898</t>
+    <t xml:space="preserve">17.5718631744385</t>
   </si>
   <si>
     <t xml:space="preserve">17.5503787994385</t>
@@ -5519,7 +5519,7 @@
     <t xml:space="preserve">17.7608985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620845794678</t>
+    <t xml:space="preserve">17.6620826721191</t>
   </si>
   <si>
     <t xml:space="preserve">17.8554172515869</t>
@@ -5531,7 +5531,7 @@
     <t xml:space="preserve">17.5761566162109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3011951446533</t>
+    <t xml:space="preserve">17.3011932373047</t>
   </si>
   <si>
     <t xml:space="preserve">17.11301612854</t>
@@ -5540,13 +5540,13 @@
     <t xml:space="preserve">16.8741416931152</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0459938049316</t>
+    <t xml:space="preserve">17.045991897583</t>
   </si>
   <si>
     <t xml:space="preserve">16.9016380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9274158477783</t>
+    <t xml:space="preserve">16.927417755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.8122749328613</t>
@@ -5558,7 +5558,7 @@
     <t xml:space="preserve">16.6885433197021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7761859893799</t>
+    <t xml:space="preserve">16.7761878967285</t>
   </si>
   <si>
     <t xml:space="preserve">16.7332248687744</t>
@@ -5567,7 +5567,7 @@
     <t xml:space="preserve">17.374231338501</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6105289459229</t>
+    <t xml:space="preserve">17.6105270385742</t>
   </si>
   <si>
     <t xml:space="preserve">17.8468246459961</t>
@@ -5585,16 +5585,16 @@
     <t xml:space="preserve">18.624454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0197124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3032684326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4536380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2388229370117</t>
+    <t xml:space="preserve">19.0197143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3032703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4536399841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2388248443604</t>
   </si>
   <si>
     <t xml:space="preserve">19.3977890014648</t>
@@ -5618,10 +5618,10 @@
     <t xml:space="preserve">20.8198623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1463832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8843078613281</t>
+    <t xml:space="preserve">21.1463813781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8843059539795</t>
   </si>
   <si>
     <t xml:space="preserve">20.8327522277832</t>
@@ -5633,13 +5633,13 @@
     <t xml:space="preserve">20.7382335662842</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9960117340088</t>
+    <t xml:space="preserve">20.9960098266602</t>
   </si>
   <si>
     <t xml:space="preserve">21.1592712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2494926452637</t>
+    <t xml:space="preserve">21.249490737915</t>
   </si>
   <si>
     <t xml:space="preserve">21.4814929962158</t>
@@ -5660,7 +5660,7 @@
     <t xml:space="preserve">21.8552703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7994194030762</t>
+    <t xml:space="preserve">21.7994213104248</t>
   </si>
   <si>
     <t xml:space="preserve">22.3665313720703</t>
@@ -5669,7 +5669,7 @@
     <t xml:space="preserve">22.4696407318115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8649024963379</t>
+    <t xml:space="preserve">22.8649005889893</t>
   </si>
   <si>
     <t xml:space="preserve">22.9078636169434</t>
@@ -5678,19 +5678,19 @@
     <t xml:space="preserve">23.1269760131836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1441612243652</t>
+    <t xml:space="preserve">23.1441593170166</t>
   </si>
   <si>
     <t xml:space="preserve">23.3331985473633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8391227722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9293460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6371974945068</t>
+    <t xml:space="preserve">22.8391246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9293441772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6371955871582</t>
   </si>
   <si>
     <t xml:space="preserve">21.8939361572266</t>
@@ -5699,10 +5699,10 @@
     <t xml:space="preserve">21.4943809509277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5244541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1377906799316</t>
+    <t xml:space="preserve">21.5244560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.137788772583</t>
   </si>
   <si>
     <t xml:space="preserve">21.3912696838379</t>
@@ -5711,25 +5711,25 @@
     <t xml:space="preserve">21.5459365844727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6791210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6619358062744</t>
+    <t xml:space="preserve">21.6791229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.661937713623</t>
   </si>
   <si>
     <t xml:space="preserve">20.9530487060547</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4771957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8370494842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8542346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9229755401611</t>
+    <t xml:space="preserve">21.4771976470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8370475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8542327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9229736328125</t>
   </si>
   <si>
     <t xml:space="preserve">21.2375450134277</t>
@@ -6807,6 +6807,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.11699962615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55000019073486</t>
   </si>
 </sst>
 </file>
@@ -71937,7 +71940,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6501388889</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>23267996</v>
@@ -71958,6 +71961,32 @@
         <v>2264</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6495833333</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>34368060</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>9.5959997177124</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>9.13300037384033</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>9.55000019073486</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>2265</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="2268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="2269">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02501392364502</t>
+    <t xml:space="preserve">4.02501344680786</t>
   </si>
   <si>
     <t xml:space="preserve">STLAM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13119506835938</t>
+    <t xml:space="preserve">4.13119459152222</t>
   </si>
   <si>
     <t xml:space="preserve">3.91636347770691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78795790672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63238978385925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757349967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71881604194641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66942977905273</t>
+    <t xml:space="preserve">3.78795719146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63238954544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757326126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71881651878357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66942954063416</t>
   </si>
   <si>
     <t xml:space="preserve">3.37804841995239</t>
@@ -71,34 +71,34 @@
     <t xml:space="preserve">3.28421401977539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1879096031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2693977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06197333335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25705122947693</t>
+    <t xml:space="preserve">3.18790936470032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26939749717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06197309494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25705146789551</t>
   </si>
   <si>
     <t xml:space="preserve">3.32619261741638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2619903087616</t>
+    <t xml:space="preserve">3.26198959350586</t>
   </si>
   <si>
     <t xml:space="preserve">3.46200561523438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43237400054932</t>
+    <t xml:space="preserve">3.43237376213074</t>
   </si>
   <si>
     <t xml:space="preserve">3.18544054031372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16321635246277</t>
+    <t xml:space="preserve">3.16321611404419</t>
   </si>
   <si>
     <t xml:space="preserve">3.16074705123901</t>
@@ -107,49 +107,49 @@
     <t xml:space="preserve">3.07678961753845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95332264900208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91628336906433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94838380813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65700364112854</t>
+    <t xml:space="preserve">2.95332288742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91628289222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94838428497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65700316429138</t>
   </si>
   <si>
     <t xml:space="preserve">2.58292293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73355269432068</t>
+    <t xml:space="preserve">2.7335524559021</t>
   </si>
   <si>
     <t xml:space="preserve">2.59280014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68416571617126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80269312858582</t>
+    <t xml:space="preserve">2.68416595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80269336700439</t>
   </si>
   <si>
     <t xml:space="preserve">2.75824546813965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89899706840515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87924242019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81010103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92615962028503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83973383903503</t>
+    <t xml:space="preserve">2.89899778366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87924289703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81010150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92616009712219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83973360061646</t>
   </si>
   <si>
     <t xml:space="preserve">2.72614431381226</t>
@@ -158,52 +158,52 @@
     <t xml:space="preserve">3.00517916679382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13358402252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2990300655365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45212864875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46447515487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44225096702576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28915214538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30643796920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21013379096985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35088562965393</t>
+    <t xml:space="preserve">3.13358426094055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29902982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45212841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46447467803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44225144386292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28915238380432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30643820762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21013331413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35088515281677</t>
   </si>
   <si>
     <t xml:space="preserve">3.44719004631042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36076307296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44472026824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42496609687805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51633095741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50151562690735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386117935181</t>
+    <t xml:space="preserve">3.36076331138611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472050666809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42496633529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5163311958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50151538848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386189460754</t>
   </si>
   <si>
     <t xml:space="preserve">3.47682166099548</t>
@@ -212,40 +212,40 @@
     <t xml:space="preserve">3.33360052108765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57559466362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50645422935486</t>
+    <t xml:space="preserve">3.57559514045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50645399093628</t>
   </si>
   <si>
     <t xml:space="preserve">3.3360698223114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34841704368591</t>
+    <t xml:space="preserve">3.3484160900116</t>
   </si>
   <si>
     <t xml:space="preserve">3.18050193786621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13852286338806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01505661010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13605427742004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21260333061218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1681547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31878399848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35335516929626</t>
+    <t xml:space="preserve">3.13852214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01505589485168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13605356216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21260285377502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16815519332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31878471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35335469245911</t>
   </si>
   <si>
     <t xml:space="preserve">3.40274214744568</t>
@@ -254,28 +254,28 @@
     <t xml:space="preserve">3.56571745872498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54596304893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56818771362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47435307502747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.533616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41014957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3829870223999</t>
+    <t xml:space="preserve">3.54596328735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56818723678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47435283660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53361630439758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41015005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38298654556274</t>
   </si>
   <si>
     <t xml:space="preserve">3.29656004905701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26692795753479</t>
+    <t xml:space="preserve">3.26692843437195</t>
   </si>
   <si>
     <t xml:space="preserve">3.36570143699646</t>
@@ -284,61 +284,61 @@
     <t xml:space="preserve">3.3163149356842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38051795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33113121986389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10889077186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11383008956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10148286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629891395569</t>
+    <t xml:space="preserve">3.38051748275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33113098144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.108891248703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11382961273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.101482629776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629843711853</t>
   </si>
   <si>
     <t xml:space="preserve">2.97801661491394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06938123703003</t>
+    <t xml:space="preserve">3.06938195228577</t>
   </si>
   <si>
     <t xml:space="preserve">3.12370705604553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07185125350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15827775001526</t>
+    <t xml:space="preserve">3.0718514919281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15827751159668</t>
   </si>
   <si>
     <t xml:space="preserve">3.0743203163147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04221940040588</t>
+    <t xml:space="preserve">3.0422191619873</t>
   </si>
   <si>
     <t xml:space="preserve">3.03974962234497</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14840030670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1212375164032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93109893798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87677311897278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89652800559998</t>
+    <t xml:space="preserve">3.1483998298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12123727798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93109846115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87677359580994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89652848243713</t>
   </si>
   <si>
     <t xml:space="preserve">2.86195778846741</t>
@@ -347,22 +347,22 @@
     <t xml:space="preserve">2.93356823921204</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09407472610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08666706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04962754249573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11136031150818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.819979429245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64465641975403</t>
+    <t xml:space="preserve">3.09407520294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08666682243347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04962730407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11135983467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81997895240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64465618133545</t>
   </si>
   <si>
     <t xml:space="preserve">2.66194176673889</t>
@@ -371,22 +371,22 @@
     <t xml:space="preserve">2.7137975692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.770592212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.533536195755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52365899085999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54835200309753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8471417427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96320033073425</t>
+    <t xml:space="preserve">2.77059292793274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53353595733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52365875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54835152626038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84714198112488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96319985389709</t>
   </si>
   <si>
     <t xml:space="preserve">2.91134452819824</t>
@@ -401,40 +401,40 @@
     <t xml:space="preserve">2.95826148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08913636207581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0990138053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12617659568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06691265106201</t>
+    <t xml:space="preserve">3.08913612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09901404380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12617707252502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06691217422485</t>
   </si>
   <si>
     <t xml:space="preserve">2.84467244148254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81257104873657</t>
+    <t xml:space="preserve">2.81257081031799</t>
   </si>
   <si>
     <t xml:space="preserve">2.69157338142395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91381335258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88665080070496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05703473091125</t>
+    <t xml:space="preserve">2.91381311416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88665056228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05703520774841</t>
   </si>
   <si>
     <t xml:space="preserve">2.98789381980896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96073150634766</t>
+    <t xml:space="preserve">2.96073079109192</t>
   </si>
   <si>
     <t xml:space="preserve">2.97307777404785</t>
@@ -443,25 +443,25 @@
     <t xml:space="preserve">2.88418197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91875219345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03481078147888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02987194061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0446879863739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99283266067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05950450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97554659843445</t>
+    <t xml:space="preserve">2.91875267028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03481030464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02987217903137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04468822479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99283242225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05950474739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97554731369019</t>
   </si>
   <si>
     <t xml:space="preserve">2.95085382461548</t>
@@ -473,49 +473,49 @@
     <t xml:space="preserve">2.90393614768982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86442732810974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8743040561676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81504058837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90146684646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83232522010803</t>
+    <t xml:space="preserve">2.86442708969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87430453300476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81504034996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9014675617218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83232498168945</t>
   </si>
   <si>
     <t xml:space="preserve">2.86689615249634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74096012115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70885848999023</t>
+    <t xml:space="preserve">2.74095988273621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70885920524597</t>
   </si>
   <si>
     <t xml:space="preserve">2.7903470993042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82491731643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84220337867737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89159035682678</t>
+    <t xml:space="preserve">2.82491827011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84220314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89158987998962</t>
   </si>
   <si>
     <t xml:space="preserve">2.87183499336243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90887498855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76812314987183</t>
+    <t xml:space="preserve">2.90887475013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76812267303467</t>
   </si>
   <si>
     <t xml:space="preserve">2.82244849205017</t>
@@ -524,88 +524,88 @@
     <t xml:space="preserve">2.85948824882507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9385073184967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25211262702942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29409146308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25952053070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03234195709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02740359306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16568541526794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52373957633972</t>
+    <t xml:space="preserve">2.93850684165955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25211215019226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29409122467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25952005386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03234171867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02740287780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16568517684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5237398147583</t>
   </si>
   <si>
     <t xml:space="preserve">3.39780354499817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47188305854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45953559875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47929167747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49410700798035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55584073066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58547210693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57065653800964</t>
+    <t xml:space="preserve">3.47188282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45953607559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47929120063782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49410676956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55584049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58547186851501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57065677642822</t>
   </si>
   <si>
     <t xml:space="preserve">3.56077909469604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60028886795044</t>
+    <t xml:space="preserve">3.60028839111328</t>
   </si>
   <si>
     <t xml:space="preserve">3.62251234054565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55830907821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72128510475159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81265068054199</t>
+    <t xml:space="preserve">3.55830955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72128558158875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81265115737915</t>
   </si>
   <si>
     <t xml:space="preserve">3.8570990562439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93364858627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93117928504944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97315716743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525856018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99044322967529</t>
+    <t xml:space="preserve">3.93364882469177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93117904663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97315812110901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525808334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99044299125671</t>
   </si>
   <si>
     <t xml:space="preserve">4.15341901779175</t>
@@ -626,22 +626,22 @@
     <t xml:space="preserve">4.17564249038696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26453971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31392574310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30898809432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27935552597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42257642745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5065336227417</t>
+    <t xml:space="preserve">4.26453924179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31392669677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30898761749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2793550491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42257738113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50653409957886</t>
   </si>
   <si>
     <t xml:space="preserve">4.53863573074341</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">4.5707368850708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88928127288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95842218399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01274824142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17078447341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33615064620972</t>
+    <t xml:space="preserve">4.88928031921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95842170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01274728775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17078495025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33615016937256</t>
   </si>
   <si>
     <t xml:space="preserve">4.53616619110107</t>
@@ -674,43 +674,43 @@
     <t xml:space="preserve">4.39047574996948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41516828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62753105163574</t>
+    <t xml:space="preserve">4.41516876220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62753057479858</t>
   </si>
   <si>
     <t xml:space="preserve">4.64234733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71889686584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99793243408203</t>
+    <t xml:space="preserve">4.71889734268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99793195724487</t>
   </si>
   <si>
     <t xml:space="preserve">5.04237937927246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10164308547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12633657455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95348405838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9880542755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99299240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00287055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04731798171997</t>
+    <t xml:space="preserve">5.10164260864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1263370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95348358154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98805379867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99299144744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00287103652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04731750488281</t>
   </si>
   <si>
     <t xml:space="preserve">4.92385101318359</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">4.8991584777832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02756309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33869934082031</t>
+    <t xml:space="preserve">5.02756261825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33869886398315</t>
   </si>
   <si>
     <t xml:space="preserve">5.34363794326782</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">5.32388353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25474214553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32882308959961</t>
+    <t xml:space="preserve">5.25474166870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32882165908813</t>
   </si>
   <si>
     <t xml:space="preserve">5.1757230758667</t>
@@ -746,25 +746,25 @@
     <t xml:space="preserve">5.14609098434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18560075759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18066215515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13127517700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13621425628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16584634780884</t>
+    <t xml:space="preserve">5.18560028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18066167831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13127565383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13621377944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.165846824646</t>
   </si>
   <si>
     <t xml:space="preserve">5.09670400619507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14115285873413</t>
+    <t xml:space="preserve">5.14115238189697</t>
   </si>
   <si>
     <t xml:space="preserve">5.22511005401611</t>
@@ -773,67 +773,67 @@
     <t xml:space="preserve">5.30412864685059</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21029424667358</t>
+    <t xml:space="preserve">5.21029472351074</t>
   </si>
   <si>
     <t xml:space="preserve">4.98311567306519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94360542297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96336078643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93372869491577</t>
+    <t xml:space="preserve">4.94360494613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96336030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93372917175293</t>
   </si>
   <si>
     <t xml:space="preserve">5.07695007324219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07201099395752</t>
+    <t xml:space="preserve">5.07201147079468</t>
   </si>
   <si>
     <t xml:space="preserve">5.06213426589966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81026220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83248567581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74359035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78556776046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73371362686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71642732620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70654964447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69420337677002</t>
+    <t xml:space="preserve">4.81026172637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83248615264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74358940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78556823730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73371315002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71642637252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70655012130737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69420289993286</t>
   </si>
   <si>
     <t xml:space="preserve">4.51888036727905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45220851898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64728593826294</t>
+    <t xml:space="preserve">4.45220804214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6472864151001</t>
   </si>
   <si>
     <t xml:space="preserve">4.70408058166504</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63000059127808</t>
+    <t xml:space="preserve">4.63000106811523</t>
   </si>
   <si>
     <t xml:space="preserve">4.79297685623169</t>
@@ -842,37 +842,37 @@
     <t xml:space="preserve">4.78803777694702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23498773574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91644287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97323751449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05225706100464</t>
+    <t xml:space="preserve">5.23498725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91644239425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97323799133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05225658416748</t>
   </si>
   <si>
     <t xml:space="preserve">5.03744077682495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91891241073608</t>
+    <t xml:space="preserve">4.91891288757324</t>
   </si>
   <si>
     <t xml:space="preserve">4.94854497909546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02262496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7682843208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62012386322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80038547515869</t>
+    <t xml:space="preserve">5.02262449264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76828384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62012338638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80038499832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.72383546829224</t>
@@ -884,22 +884,22 @@
     <t xml:space="preserve">4.66210174560547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67197942733765</t>
+    <t xml:space="preserve">4.67197895050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.59049129486084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.583083152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61518478393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84730195999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83001565933228</t>
+    <t xml:space="preserve">4.58308267593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61518526077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8473014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83001708984375</t>
   </si>
   <si>
     <t xml:space="preserve">4.75346660614014</t>
@@ -908,43 +908,43 @@
     <t xml:space="preserve">4.80532360076904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75099897384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79544734954834</t>
+    <t xml:space="preserve">4.75099802017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79544687271118</t>
   </si>
   <si>
     <t xml:space="preserve">4.8176703453064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78309917449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7213659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.684326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85224008560181</t>
+    <t xml:space="preserve">4.78309965133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72136545181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68432664871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85224056243896</t>
   </si>
   <si>
     <t xml:space="preserve">4.77816104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76087522506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55839014053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85507869720459</t>
+    <t xml:space="preserve">4.7608757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55839061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85507917404175</t>
   </si>
   <si>
     <t xml:space="preserve">4.86003732681274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78564929962158</t>
+    <t xml:space="preserve">4.78564977645874</t>
   </si>
   <si>
     <t xml:space="preserve">4.82532262802124</t>
@@ -953,46 +953,46 @@
     <t xml:space="preserve">4.80548620223999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87243509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9592227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99889612197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19230556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15263175964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17246770858765</t>
+    <t xml:space="preserve">4.87243556976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95922231674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99889516830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19230461120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1526312828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1724681854248</t>
   </si>
   <si>
     <t xml:space="preserve">5.10799884796143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17742776870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97409963607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97905874252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98897647857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03856945037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03361034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05840635299683</t>
+    <t xml:space="preserve">5.17742729187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97410011291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97905969619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98897695541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03857040405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03360986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05840587615967</t>
   </si>
   <si>
     <t xml:space="preserve">5.07328414916992</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">5.02865123748779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07824373245239</t>
+    <t xml:space="preserve">5.07824420928955</t>
   </si>
   <si>
     <t xml:space="preserve">5.0633659362793</t>
@@ -1010,124 +1010,124 @@
     <t xml:space="preserve">4.95178365707397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95426273345947</t>
+    <t xml:space="preserve">4.95426321029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.86995601654053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26669406890869</t>
+    <t xml:space="preserve">5.26669502258301</t>
   </si>
   <si>
     <t xml:space="preserve">5.40555238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34604120254517</t>
+    <t xml:space="preserve">5.34604167938232</t>
   </si>
   <si>
     <t xml:space="preserve">5.30636787414551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67334938049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68822765350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01553630828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19406843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14943647384644</t>
+    <t xml:space="preserve">5.67334985733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68822717666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01553726196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19406938552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14943599700928</t>
   </si>
   <si>
     <t xml:space="preserve">6.1643123626709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07008838653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13951683044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2734169960022</t>
+    <t xml:space="preserve">6.07008790969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13951635360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27341604232788</t>
   </si>
   <si>
     <t xml:space="preserve">6.61560297012329</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53129577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50649976730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78421640396118</t>
+    <t xml:space="preserve">6.53129529953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50649881362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78421545028687</t>
   </si>
   <si>
     <t xml:space="preserve">6.70982789993286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72470474243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76933813095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80405235290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96770715713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88340044021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99250268936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07681083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14623928070068</t>
+    <t xml:space="preserve">6.72470569610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76933717727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80405330657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96770763397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88339996337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99250316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07681035995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14623880386353</t>
   </si>
   <si>
     <t xml:space="preserve">7.18095350265503</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46362829208374</t>
+    <t xml:space="preserve">7.4636287689209</t>
   </si>
   <si>
     <t xml:space="preserve">7.31485271453857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33468914031982</t>
+    <t xml:space="preserve">7.33469009399414</t>
   </si>
   <si>
     <t xml:space="preserve">7.38428211212158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36444568634033</t>
+    <t xml:space="preserve">7.36444520950317</t>
   </si>
   <si>
     <t xml:space="preserve">7.51818180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58265018463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56281423568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53801822662354</t>
+    <t xml:space="preserve">7.58265113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56281280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53801774978638</t>
   </si>
   <si>
     <t xml:space="preserve">7.49338483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40907764434814</t>
+    <t xml:space="preserve">7.40907907485962</t>
   </si>
   <si>
     <t xml:space="preserve">7.52313947677612</t>
@@ -1136,139 +1136,139 @@
     <t xml:space="preserve">7.41403675079346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50330352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4239559173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4586706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41899538040161</t>
+    <t xml:space="preserve">7.50330305099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42395639419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45867204666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41899681091309</t>
   </si>
   <si>
     <t xml:space="preserve">7.30989408493042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37932300567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93795251846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05697250366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02225875854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14128017425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34956836700439</t>
+    <t xml:space="preserve">7.37932205200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93795204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05697345733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02225828170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14127922058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34956693649292</t>
   </si>
   <si>
     <t xml:space="preserve">7.35948610305786</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51322221755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76614141464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73142671585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6619987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45371103286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28013753890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33964872360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3743634223938</t>
+    <t xml:space="preserve">7.5132212638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76614189147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73142576217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66199827194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45371055603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28013706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33964967727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37436437606812</t>
   </si>
   <si>
     <t xml:space="preserve">7.25038242340088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43387460708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55785417556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24046516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2007908821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17103481292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15119743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00738096237183</t>
+    <t xml:space="preserve">7.43387413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55785512924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24046468734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20079040527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17103672027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.151198387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00738143920898</t>
   </si>
   <si>
     <t xml:space="preserve">7.23550415039062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1908712387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53305816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52809762954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50826120376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43883323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44875288009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63720178604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65207815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64216184616089</t>
+    <t xml:space="preserve">7.19087219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53305912017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52809953689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5082631111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43883275985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44875240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63720226287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65208005905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64216136932373</t>
   </si>
   <si>
     <t xml:space="preserve">7.69175434112549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67191600799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297685623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39420032501221</t>
+    <t xml:space="preserve">7.67191743850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297733306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39420080184937</t>
   </si>
   <si>
     <t xml:space="preserve">7.71159029006958</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35628890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88692665100098</t>
+    <t xml:space="preserve">8.35628986358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88692569732666</t>
   </si>
   <si>
     <t xml:space="preserve">8.98115158081055</t>
@@ -1277,22 +1277,22 @@
     <t xml:space="preserve">9.15968322753906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21423435211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42252159118652</t>
+    <t xml:space="preserve">9.21423530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42252254486084</t>
   </si>
   <si>
     <t xml:space="preserve">9.48699283599854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69032001495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28862380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32829666137695</t>
+    <t xml:space="preserve">9.69032096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28862285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32829761505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.50187015533447</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">9.76470851898193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70519638061523</t>
+    <t xml:space="preserve">9.70519733428955</t>
   </si>
   <si>
     <t xml:space="preserve">9.64072895050049</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">9.53856754302979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31937026977539</t>
+    <t xml:space="preserve">9.31936931610107</t>
   </si>
   <si>
     <t xml:space="preserve">8.75798606872559</t>
@@ -1346,28 +1346,28 @@
     <t xml:space="preserve">8.75302696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57548713684082</t>
+    <t xml:space="preserve">8.57548809051514</t>
   </si>
   <si>
     <t xml:space="preserve">8.77782249450684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82741451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0039644241333</t>
+    <t xml:space="preserve">8.82741355895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00396347045898</t>
   </si>
   <si>
     <t xml:space="preserve">8.83733367919922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94643497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98908519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80956363677979</t>
+    <t xml:space="preserve">8.94643592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98908710479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80956268310547</t>
   </si>
   <si>
     <t xml:space="preserve">8.73814964294434</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">8.6905403137207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8055944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7143440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47432041168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98930644989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01410293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46836757659912</t>
+    <t xml:space="preserve">8.80559539794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71434688568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4743185043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98930692672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01410388946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4683666229248</t>
   </si>
   <si>
     <t xml:space="preserve">8.55664253234863</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">8.53085422515869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43266201019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53184509277344</t>
+    <t xml:space="preserve">8.43266105651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53184604644775</t>
   </si>
   <si>
     <t xml:space="preserve">8.52589416503906</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">8.35926532745361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56457710266113</t>
+    <t xml:space="preserve">8.56457614898682</t>
   </si>
   <si>
     <t xml:space="preserve">8.71732044219971</t>
@@ -1430,28 +1430,28 @@
     <t xml:space="preserve">8.42175102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25115299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18866729736328</t>
+    <t xml:space="preserve">8.25115394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1886682510376</t>
   </si>
   <si>
     <t xml:space="preserve">8.32554244995117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15792083740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18370819091797</t>
+    <t xml:space="preserve">8.15791988372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18370914459229</t>
   </si>
   <si>
     <t xml:space="preserve">8.78278350830078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73517227172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15869045257568</t>
+    <t xml:space="preserve">8.73517322540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15869140625</t>
   </si>
   <si>
     <t xml:space="preserve">9.07438468933105</t>
@@ -1463,43 +1463,43 @@
     <t xml:space="preserve">9.31342029571533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22613716125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40764427185059</t>
+    <t xml:space="preserve">9.2261381149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4076452255249</t>
   </si>
   <si>
     <t xml:space="preserve">9.43640804290771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36301231384277</t>
+    <t xml:space="preserve">9.36301136016846</t>
   </si>
   <si>
     <t xml:space="preserve">9.70916557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7676830291748</t>
+    <t xml:space="preserve">9.76768398284912</t>
   </si>
   <si>
     <t xml:space="preserve">9.63180255889893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55840492248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7597484588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79148864746094</t>
+    <t xml:space="preserve">9.55840396881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75975036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79148960113525</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393463134766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68635272979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41458797454834</t>
+    <t xml:space="preserve">9.686354637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41458606719971</t>
   </si>
   <si>
     <t xml:space="preserve">9.20927619934082</t>
@@ -1511,94 +1511,94 @@
     <t xml:space="preserve">9.21820259094238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51674652099609</t>
+    <t xml:space="preserve">9.51674747467041</t>
   </si>
   <si>
     <t xml:space="preserve">9.53559303283691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48005104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29556655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30845928192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42946434020996</t>
+    <t xml:space="preserve">9.4800500869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29556560516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30846118927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42946529388428</t>
   </si>
   <si>
     <t xml:space="preserve">9.41756248474121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36697864532471</t>
+    <t xml:space="preserve">9.36697959899902</t>
   </si>
   <si>
     <t xml:space="preserve">9.30746841430664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36796951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19935607910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43938446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59609508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48600006103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31143665313721</t>
+    <t xml:space="preserve">9.36797046661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19935703277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4393835067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59609413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48600101470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31143474578857</t>
   </si>
   <si>
     <t xml:space="preserve">9.3054838180542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1081075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06446647644043</t>
+    <t xml:space="preserve">9.10810661315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06446552276611</t>
   </si>
   <si>
     <t xml:space="preserve">9.42748165130615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62088966369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18547248840332</t>
+    <t xml:space="preserve">9.62089061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.185471534729</t>
   </si>
   <si>
     <t xml:space="preserve">8.85221195220947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87601566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86213111877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1398458480835</t>
+    <t xml:space="preserve">8.87601470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86212825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13984680175781</t>
   </si>
   <si>
     <t xml:space="preserve">8.90676307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98313617706299</t>
+    <t xml:space="preserve">8.98313522338867</t>
   </si>
   <si>
     <t xml:space="preserve">8.92659950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85022735595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04462814331055</t>
+    <t xml:space="preserve">8.85022830963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04462909698486</t>
   </si>
   <si>
     <t xml:space="preserve">8.87403202056885</t>
@@ -1607,31 +1607,31 @@
     <t xml:space="preserve">8.92461585998535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79666805267334</t>
+    <t xml:space="preserve">8.79666996002197</t>
   </si>
   <si>
     <t xml:space="preserve">8.7500524520874</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38505268096924</t>
+    <t xml:space="preserve">8.38505363464355</t>
   </si>
   <si>
     <t xml:space="preserve">8.18172454833984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92979526519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15296077728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24123573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95558547973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10039329528809</t>
+    <t xml:space="preserve">7.92979669570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15296173095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24123477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95558452606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10039234161377</t>
   </si>
   <si>
     <t xml:space="preserve">8.10237693786621</t>
@@ -1640,196 +1640,196 @@
     <t xml:space="preserve">8.03889942169189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50506687164307</t>
+    <t xml:space="preserve">8.50506591796875</t>
   </si>
   <si>
     <t xml:space="preserve">8.40687370300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46935844421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52291870117188</t>
+    <t xml:space="preserve">8.4693603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52291965484619</t>
   </si>
   <si>
     <t xml:space="preserve">8.26305675506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21346282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25214672088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19957733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24916934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22239208221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33347606658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14105796813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01906299591064</t>
+    <t xml:space="preserve">8.21346378326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25214767456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19957828521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24917125701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22239112854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33347702026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14105987548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01906108856201</t>
   </si>
   <si>
     <t xml:space="preserve">8.21048831939697</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16111707687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26426839828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23947238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04804658889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04209518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24343967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23352098464966</t>
+    <t xml:space="preserve">7.16111660003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26426887512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23947191238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04804611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04209613800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2434401512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23352146148682</t>
   </si>
   <si>
     <t xml:space="preserve">7.20277500152588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2483983039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17500305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0440788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97663307189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80802011489868</t>
+    <t xml:space="preserve">7.24839878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1750020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04407978057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97663354873657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80801963806152</t>
   </si>
   <si>
     <t xml:space="preserve">6.79909372329712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01729917526245</t>
+    <t xml:space="preserve">7.01729869842529</t>
   </si>
   <si>
     <t xml:space="preserve">7.12243509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0371356010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95977210998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18591356277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43486595153809</t>
+    <t xml:space="preserve">7.03713703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95977258682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18591260910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43486642837524</t>
   </si>
   <si>
     <t xml:space="preserve">7.42693090438843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36146926879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22062683105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26823663711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39320755004883</t>
+    <t xml:space="preserve">7.36146879196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22062730789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26823616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39320850372314</t>
   </si>
   <si>
     <t xml:space="preserve">7.22657918930054</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21566820144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16706705093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48247480392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40610313415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42792224884033</t>
+    <t xml:space="preserve">7.21566772460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.167067527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48247385025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40610265731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42792320251465</t>
   </si>
   <si>
     <t xml:space="preserve">7.45767879486084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48346662521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61934900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73341178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66001462936401</t>
+    <t xml:space="preserve">7.48346710205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61934947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73341131210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6600136756897</t>
   </si>
   <si>
     <t xml:space="preserve">7.70266342163086</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6679482460022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51024627685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68282651901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69373655319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64017772674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57769250869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52016496658325</t>
+    <t xml:space="preserve">7.66795015335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51024675369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68282604217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6937370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64017868041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57769155502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52016544342041</t>
   </si>
   <si>
     <t xml:space="preserve">7.34460830688477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42197227478027</t>
+    <t xml:space="preserve">7.42197179794312</t>
   </si>
   <si>
     <t xml:space="preserve">7.01035642623901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96274709701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92803430557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94588756561279</t>
+    <t xml:space="preserve">6.96274900436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92803335189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94588661193848</t>
   </si>
   <si>
     <t xml:space="preserve">7.17797803878784</t>
@@ -1838,25 +1838,25 @@
     <t xml:space="preserve">6.87744951248169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82587289810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66618680953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86455488204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95183801651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78024959564209</t>
+    <t xml:space="preserve">6.82587385177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66618633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86455535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95183706283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78024864196777</t>
   </si>
   <si>
     <t xml:space="preserve">7.04705476760864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81992244720459</t>
+    <t xml:space="preserve">6.81992197036743</t>
   </si>
   <si>
     <t xml:space="preserve">6.67015361785889</t>
@@ -1865,22 +1865,22 @@
     <t xml:space="preserve">6.75247573852539</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02920055389404</t>
+    <t xml:space="preserve">7.02920150756836</t>
   </si>
   <si>
     <t xml:space="preserve">7.11251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09664726257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26129293441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28708219528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08672761917114</t>
+    <t xml:space="preserve">7.09664583206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26129341125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28708171844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0867280960083</t>
   </si>
   <si>
     <t xml:space="preserve">7.30394268035889</t>
@@ -1889,49 +1889,49 @@
     <t xml:space="preserve">7.23054552078247</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13334465026855</t>
+    <t xml:space="preserve">7.13334608078003</t>
   </si>
   <si>
     <t xml:space="preserve">7.12838649749756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94291019439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01234102249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93001794815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99052047729492</t>
+    <t xml:space="preserve">6.94291114807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01234006881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93001651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99051904678345</t>
   </si>
   <si>
     <t xml:space="preserve">7.33865737915039</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34758329391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30493402481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49635982513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34857559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2345118522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86554718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82488107681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61064291000366</t>
+    <t xml:space="preserve">7.34758377075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30493354797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49636077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34857606887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23451280593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86554670333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82488059997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61064338684082</t>
   </si>
   <si>
     <t xml:space="preserve">6.78322410583496</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">6.9161319732666</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92208194732666</t>
+    <t xml:space="preserve">6.92208290100098</t>
   </si>
   <si>
     <t xml:space="preserve">6.86852216720581</t>
@@ -1949,28 +1949,28 @@
     <t xml:space="preserve">6.82884931564331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82289886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72272109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50848340988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25754642486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28928470611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23175954818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15736961364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50253248214722</t>
+    <t xml:space="preserve">6.82289743423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72272157669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50848293304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25754594802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28928518295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2317590713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15737056732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50253200531006</t>
   </si>
   <si>
     <t xml:space="preserve">6.55113220214844</t>
@@ -1979,13 +1979,13 @@
     <t xml:space="preserve">6.62849569320679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87645721435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01134920120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16012525558472</t>
+    <t xml:space="preserve">6.87645626068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01134967803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16012477874756</t>
   </si>
   <si>
     <t xml:space="preserve">7.2444314956665</t>
@@ -2000,139 +2000,139 @@
     <t xml:space="preserve">7.10557317733765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26724433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18690490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18987989425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28509712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39816665649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47354888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52710723876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63543891906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44302225112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4182243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39739608764648</t>
+    <t xml:space="preserve">7.26724481582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18690538406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18987894058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28509759902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3981671333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47354745864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52710771560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6354398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44302082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41822481155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3973970413208</t>
   </si>
   <si>
     <t xml:space="preserve">6.49757289886475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40731525421143</t>
+    <t xml:space="preserve">6.40731430053711</t>
   </si>
   <si>
     <t xml:space="preserve">6.4598822593689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44897270202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4519476890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57692050933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50153923034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51145839691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54617357254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4559154510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43806219100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41227388381958</t>
+    <t xml:space="preserve">6.44897317886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45194816589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57692098617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.501540184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51145887374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54617309570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45591592788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43806266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41227436065674</t>
   </si>
   <si>
     <t xml:space="preserve">6.36268186569214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41524887084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64932489395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32697677612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36665010452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35871458053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30416250228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25853824615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26548147201538</t>
+    <t xml:space="preserve">6.41525077819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64932441711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32697582244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36664915084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35871362686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30416345596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25853872299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26548004150391</t>
   </si>
   <si>
     <t xml:space="preserve">6.32003259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6364312171936</t>
+    <t xml:space="preserve">6.63643026351929</t>
   </si>
   <si>
     <t xml:space="preserve">6.46980142593384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49658012390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33590221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46385097503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49162197113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66122770309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52633714675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58188009262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73958301544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8060359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8090124130249</t>
+    <t xml:space="preserve">6.49658060073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33590269088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46385049819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49162149429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66122722625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52633619308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58187961578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73958349227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80603742599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80901145935059</t>
   </si>
   <si>
     <t xml:space="preserve">6.81000375747681</t>
@@ -2144,31 +2144,31 @@
     <t xml:space="preserve">6.86157989501953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89133358001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89232730865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04308652877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0936713218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607570648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29303169250488</t>
+    <t xml:space="preserve">6.89133453369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89232683181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04308748245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09367179870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607522964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29303216934204</t>
   </si>
   <si>
     <t xml:space="preserve">7.28431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20211315155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14384889602661</t>
+    <t xml:space="preserve">7.20211410522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14384841918945</t>
   </si>
   <si>
     <t xml:space="preserve">7.20939826965332</t>
@@ -2177,49 +2177,49 @@
     <t xml:space="preserve">7.19170999526978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14488887786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04916572570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3737907409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11263561248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07205533981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80673789978027</t>
+    <t xml:space="preserve">7.14488840103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04916667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11263465881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07205629348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80673694610596</t>
   </si>
   <si>
     <t xml:space="preserve">6.73806619644165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61112880706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71309566497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81401968002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88997459411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95448398590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93350172042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88365459442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82684946060181</t>
+    <t xml:space="preserve">6.61112976074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71309518814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81402111053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88997411727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95448303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93350219726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88365411758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82684993743896</t>
   </si>
   <si>
     <t xml:space="preserve">6.62166213989258</t>
@@ -2228,34 +2228,34 @@
     <t xml:space="preserve">6.64021015167236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16999006271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10623121261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.019287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9613242149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62977743148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59268093109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84771633148193</t>
+    <t xml:space="preserve">7.16999053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10623073577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01928663253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96132326126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6297779083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59268140792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84771680831909</t>
   </si>
   <si>
     <t xml:space="preserve">6.78163909912109</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78743553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7642502784729</t>
+    <t xml:space="preserve">6.78743505477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76424932479858</t>
   </si>
   <si>
     <t xml:space="preserve">6.88133573532104</t>
@@ -2264,70 +2264,70 @@
     <t xml:space="preserve">6.94625329971313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83728456497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89524555206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86278676986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92422771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98566770553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06449699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15028285980225</t>
+    <t xml:space="preserve">6.83728408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89524602890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86278629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92422723770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98566818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06449747085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15028142929077</t>
   </si>
   <si>
     <t xml:space="preserve">7.13521194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14216661453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02160549163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03319787979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08072710037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10970878601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15723752975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13057470321655</t>
+    <t xml:space="preserve">7.14216756820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02160501480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03319883346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08072757720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10970830917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1572380065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13057374954224</t>
   </si>
   <si>
     <t xml:space="preserve">7.33112621307373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35315179824829</t>
+    <t xml:space="preserve">7.35315275192261</t>
   </si>
   <si>
     <t xml:space="preserve">7.32532930374146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28939294815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20940446853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20476770401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28707456588745</t>
+    <t xml:space="preserve">7.28939247131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20940494537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20476675033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28707408905029</t>
   </si>
   <si>
     <t xml:space="preserve">7.28591442108154</t>
@@ -2336,16 +2336,16 @@
     <t xml:space="preserve">7.0598611831665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07493114471436</t>
+    <t xml:space="preserve">7.0749306678772</t>
   </si>
   <si>
     <t xml:space="preserve">6.9590048789978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17578554153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31141805648804</t>
+    <t xml:space="preserve">7.17578601837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3114185333252</t>
   </si>
   <si>
     <t xml:space="preserve">7.19433450698853</t>
@@ -2354,16 +2354,16 @@
     <t xml:space="preserve">7.08768320083618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.976393699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99842071533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76541042327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81873655319214</t>
+    <t xml:space="preserve">6.97639322280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99842023849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76541090011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81873559951782</t>
   </si>
   <si>
     <t xml:space="preserve">6.8685827255249</t>
@@ -2372,76 +2372,76 @@
     <t xml:space="preserve">6.72715473175049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72367715835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82569026947021</t>
+    <t xml:space="preserve">6.72367668151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82569122314453</t>
   </si>
   <si>
     <t xml:space="preserve">6.58572483062744</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40719985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52660322189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4663233757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194341659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69005870819092</t>
+    <t xml:space="preserve">6.40719890594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52660417556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46632242202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194389343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69005823135376</t>
   </si>
   <si>
     <t xml:space="preserve">6.5451512336731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63557243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74454259872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80482387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86162805557251</t>
+    <t xml:space="preserve">6.63557291030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74454307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8048243522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86162757873535</t>
   </si>
   <si>
     <t xml:space="preserve">6.86394691467285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0830454826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29055213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30562305450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37285947799683</t>
+    <t xml:space="preserve">7.08304595947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29055261611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30562257766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37285852432251</t>
   </si>
   <si>
     <t xml:space="preserve">7.28243684768677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28127717971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29287147521973</t>
+    <t xml:space="preserve">7.28127813339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29287099838257</t>
   </si>
   <si>
     <t xml:space="preserve">7.18158197402954</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18737840652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07029294967651</t>
+    <t xml:space="preserve">7.18737888336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07029342651367</t>
   </si>
   <si>
     <t xml:space="preserve">6.92654657363892</t>
@@ -2450,67 +2450,67 @@
     <t xml:space="preserve">6.83148717880249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84539794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87785673141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525707244873</t>
+    <t xml:space="preserve">6.84539842605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87785720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525802612305</t>
   </si>
   <si>
     <t xml:space="preserve">6.63093614578247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54051446914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53239917755127</t>
+    <t xml:space="preserve">6.54051399230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53240013122559</t>
   </si>
   <si>
     <t xml:space="preserve">6.57529163360596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50921487808228</t>
+    <t xml:space="preserve">6.50921535491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.54862976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73410987854004</t>
+    <t xml:space="preserve">6.73410940170288</t>
   </si>
   <si>
     <t xml:space="preserve">6.87553977966309</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9184308052063</t>
+    <t xml:space="preserve">6.91843032836914</t>
   </si>
   <si>
     <t xml:space="preserve">7.07145309448242</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03899335861206</t>
+    <t xml:space="preserve">7.03899383544922</t>
   </si>
   <si>
     <t xml:space="preserve">6.87206172943115</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95668649673462</t>
+    <t xml:space="preserve">6.95668745040894</t>
   </si>
   <si>
     <t xml:space="preserve">6.90915679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87321996688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86742353439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90335988998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81062030792236</t>
+    <t xml:space="preserve">6.87322092056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86742401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90336084365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81062078475952</t>
   </si>
   <si>
     <t xml:space="preserve">7.45980262756348</t>
@@ -2519,76 +2519,76 @@
     <t xml:space="preserve">8.07304954528809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12057781219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32808399200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37561321258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38025283813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40691375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48226642608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41039085388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5112476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41386985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40807342529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42198371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18433856964111</t>
+    <t xml:space="preserve">8.12057876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32808494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37561416625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38025188446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40691471099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48226451873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41039180755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51124668121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41386890411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40807437896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4219856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1843376159668</t>
   </si>
   <si>
     <t xml:space="preserve">8.1924524307251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09623527526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79019069671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74614000320435</t>
+    <t xml:space="preserve">8.09623336791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79019165039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74613857269287</t>
   </si>
   <si>
     <t xml:space="preserve">7.8817720413208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87713479995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89104700088501</t>
+    <t xml:space="preserve">7.87713384628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89104604721069</t>
   </si>
   <si>
     <t xml:space="preserve">7.82033157348633</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77859830856323</t>
+    <t xml:space="preserve">7.77859878540039</t>
   </si>
   <si>
     <t xml:space="preserve">7.70440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65224075317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74845838546753</t>
+    <t xml:space="preserve">7.65224027633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74845743179321</t>
   </si>
   <si>
     <t xml:space="preserve">7.68237972259521</t>
@@ -2597,61 +2597,61 @@
     <t xml:space="preserve">7.68701696395874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62094020843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57920598983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46328067779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64760208129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72411346435547</t>
+    <t xml:space="preserve">7.62093925476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5792064666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46328163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64760303497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72411394119263</t>
   </si>
   <si>
     <t xml:space="preserve">7.80757999420166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88524913787842</t>
+    <t xml:space="preserve">7.88524866104126</t>
   </si>
   <si>
     <t xml:space="preserve">7.88409042358398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9119119644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82844686508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78439474105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7415018081665</t>
+    <t xml:space="preserve">7.91191148757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82844543457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78439426422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74150228500366</t>
   </si>
   <si>
     <t xml:space="preserve">7.5803656578064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47719144821167</t>
+    <t xml:space="preserve">7.47719287872314</t>
   </si>
   <si>
     <t xml:space="preserve">7.51197052001953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41691017150879</t>
+    <t xml:space="preserve">7.41691064834595</t>
   </si>
   <si>
     <t xml:space="preserve">7.43777799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43661689758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3902473449707</t>
+    <t xml:space="preserve">7.43661785125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39024782180786</t>
   </si>
   <si>
     <t xml:space="preserve">7.3682222366333</t>
@@ -2660,16 +2660,16 @@
     <t xml:space="preserve">7.2291111946106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21867752075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20592546463013</t>
+    <t xml:space="preserve">7.21867704391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20592737197876</t>
   </si>
   <si>
     <t xml:space="preserve">7.22099685668945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14680480957031</t>
+    <t xml:space="preserve">7.146803855896</t>
   </si>
   <si>
     <t xml:space="preserve">6.98219060897827</t>
@@ -2678,31 +2678,31 @@
     <t xml:space="preserve">7.03783416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96364259719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03087902069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91263580322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80018711090088</t>
+    <t xml:space="preserve">6.96364116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03087949752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9126353263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80018758773804</t>
   </si>
   <si>
     <t xml:space="preserve">6.85235404968262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19317436218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07609081268311</t>
+    <t xml:space="preserve">7.19317579269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07609033584595</t>
   </si>
   <si>
     <t xml:space="preserve">7.03203725814819</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29402923583984</t>
+    <t xml:space="preserve">7.294029712677</t>
   </si>
   <si>
     <t xml:space="preserve">7.1073899269104</t>
@@ -2711,19 +2711,19 @@
     <t xml:space="preserve">7.14100885391235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11086702346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11550521850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00189733505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57297325134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52544355392456</t>
+    <t xml:space="preserve">7.11086797714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11550426483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00189781188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57297277450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52544403076172</t>
   </si>
   <si>
     <t xml:space="preserve">6.70165014266968</t>
@@ -2732,13 +2732,13 @@
     <t xml:space="preserve">6.51617002487183</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27620315551758</t>
+    <t xml:space="preserve">6.27620363235474</t>
   </si>
   <si>
     <t xml:space="preserve">6.3411226272583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37126398086548</t>
+    <t xml:space="preserve">6.37126302719116</t>
   </si>
   <si>
     <t xml:space="preserve">6.28431844711304</t>
@@ -2747,10 +2747,10 @@
     <t xml:space="preserve">6.09651947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.438063621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40676307678223</t>
+    <t xml:space="preserve">5.43806266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40676355361938</t>
   </si>
   <si>
     <t xml:space="preserve">5.51921081542969</t>
@@ -2759,16 +2759,16 @@
     <t xml:space="preserve">4.53326511383057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85785627365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15534830093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97914099693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54731845855713</t>
+    <t xml:space="preserve">4.85785675048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.155348777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97914147377014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54731893539429</t>
   </si>
   <si>
     <t xml:space="preserve">3.36531496047974</t>
@@ -2780,58 +2780,58 @@
     <t xml:space="preserve">3.40994715690613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84872484207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96117329597473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99421167373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75482559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65744853019714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80931043624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66498351097107</t>
+    <t xml:space="preserve">3.84872508049011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96117353439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99421143531799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75482511520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65744805335999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8093101978302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66498327255249</t>
   </si>
   <si>
     <t xml:space="preserve">3.64295721054077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59368872642517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83481383323669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08289527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12636613845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33503198623657</t>
+    <t xml:space="preserve">3.59368944168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83481407165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08289480209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12636709213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33503246307373</t>
   </si>
   <si>
     <t xml:space="preserve">4.32401990890503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10434055328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12057018280029</t>
+    <t xml:space="preserve">4.10434103012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12056970596313</t>
   </si>
   <si>
     <t xml:space="preserve">4.24403142929077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30663061141968</t>
+    <t xml:space="preserve">4.30663013458252</t>
   </si>
   <si>
     <t xml:space="preserve">4.11419486999512</t>
@@ -2849,34 +2849,34 @@
     <t xml:space="preserve">4.46197080612183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57383823394775</t>
+    <t xml:space="preserve">4.57383918762207</t>
   </si>
   <si>
     <t xml:space="preserve">4.74135112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64629173278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38430118560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44863986968994</t>
+    <t xml:space="preserve">4.64629220962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38430023193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44863891601562</t>
   </si>
   <si>
     <t xml:space="preserve">4.42139673233032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40516757965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50370407104492</t>
+    <t xml:space="preserve">4.40516710281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50370454788208</t>
   </si>
   <si>
     <t xml:space="preserve">4.42429494857788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4005298614502</t>
+    <t xml:space="preserve">4.40053033828735</t>
   </si>
   <si>
     <t xml:space="preserve">4.27475118637085</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">4.1547679901123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1750545501709</t>
+    <t xml:space="preserve">4.17505502700806</t>
   </si>
   <si>
     <t xml:space="preserve">4.51703548431396</t>
@@ -2900,31 +2900,31 @@
     <t xml:space="preserve">4.29851627349854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59934234619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.728600025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78192472457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6033992767334</t>
+    <t xml:space="preserve">4.59934186935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72859954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78192567825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60340023040771</t>
   </si>
   <si>
     <t xml:space="preserve">4.76511526107788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83293199539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08217239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04449558258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39748954772949</t>
+    <t xml:space="preserve">4.83293151855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08217191696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04449605941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39748907089233</t>
   </si>
   <si>
     <t xml:space="preserve">5.45255327224731</t>
@@ -2933,10 +2933,10 @@
     <t xml:space="preserve">5.21316814422607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07231855392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68164968490601</t>
+    <t xml:space="preserve">5.0723180770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68165016174316</t>
   </si>
   <si>
     <t xml:space="preserve">4.74888563156128</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">4.75062465667725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88625812530518</t>
+    <t xml:space="preserve">4.88625717163086</t>
   </si>
   <si>
     <t xml:space="preserve">4.86770963668823</t>
@@ -2960,13 +2960,13 @@
     <t xml:space="preserve">4.96624660491943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25374221801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02246999740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09550333023071</t>
+    <t xml:space="preserve">5.25374174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02247047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09550285339355</t>
   </si>
   <si>
     <t xml:space="preserve">5.00508165359497</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">5.09260559082031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21606588363647</t>
+    <t xml:space="preserve">5.21606540679932</t>
   </si>
   <si>
     <t xml:space="preserve">5.15868234634399</t>
@@ -2993,13 +2993,13 @@
     <t xml:space="preserve">5.20679235458374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09840106964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00276279449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11984872817993</t>
+    <t xml:space="preserve">5.09840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00276327133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11984825134277</t>
   </si>
   <si>
     <t xml:space="preserve">5.24910449981689</t>
@@ -3014,16 +3014,16 @@
     <t xml:space="preserve">5.3169207572937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31054496765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34184455871582</t>
+    <t xml:space="preserve">5.31054544448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34184503555298</t>
   </si>
   <si>
     <t xml:space="preserve">5.35401773452759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30822706222534</t>
+    <t xml:space="preserve">5.30822658538818</t>
   </si>
   <si>
     <t xml:space="preserve">5.3412652015686</t>
@@ -3035,10 +3035,10 @@
     <t xml:space="preserve">5.25895881652832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3748836517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30764770507812</t>
+    <t xml:space="preserve">5.37488460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30764675140381</t>
   </si>
   <si>
     <t xml:space="preserve">4.99638700485229</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">5.23693227767944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44270086288452</t>
+    <t xml:space="preserve">5.44270038604736</t>
   </si>
   <si>
     <t xml:space="preserve">5.44733715057373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38937425613403</t>
+    <t xml:space="preserve">5.38937473297119</t>
   </si>
   <si>
     <t xml:space="preserve">5.38183975219727</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">5.74178791046143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65716171264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61658811569214</t>
+    <t xml:space="preserve">5.65716218948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6165885925293</t>
   </si>
   <si>
     <t xml:space="preserve">5.59340333938599</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">5.56847953796387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58065223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47631883621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40618419647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58007287979126</t>
+    <t xml:space="preserve">5.58065128326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47631931304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40618324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5800724029541</t>
   </si>
   <si>
     <t xml:space="preserve">5.51631259918213</t>
@@ -3098,16 +3098,16 @@
     <t xml:space="preserve">5.54703330993652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47747850418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45719051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35054016113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28735971450806</t>
+    <t xml:space="preserve">5.47747802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.457190990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35053968429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28736019134521</t>
   </si>
   <si>
     <t xml:space="preserve">5.31750059127808</t>
@@ -3116,16 +3116,16 @@
     <t xml:space="preserve">5.37836217880249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46646547317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58470821380615</t>
+    <t xml:space="preserve">5.46646451950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58470869064331</t>
   </si>
   <si>
     <t xml:space="preserve">5.57079792022705</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57137775421143</t>
+    <t xml:space="preserve">5.57137680053711</t>
   </si>
   <si>
     <t xml:space="preserve">5.73019552230835</t>
@@ -3134,16 +3134,16 @@
     <t xml:space="preserve">5.74642467498779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78641891479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30750465393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.266930103302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23910760879517</t>
+    <t xml:space="preserve">5.78641843795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30750417709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26693058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23910713195801</t>
   </si>
   <si>
     <t xml:space="preserve">6.01537179946899</t>
@@ -3152,43 +3152,43 @@
     <t xml:space="preserve">5.75975656509399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92263174057007</t>
+    <t xml:space="preserve">5.92263031005859</t>
   </si>
   <si>
     <t xml:space="preserve">6.02232694625854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01189470291138</t>
+    <t xml:space="preserve">6.01189422607422</t>
   </si>
   <si>
     <t xml:space="preserve">5.92958736419678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16491603851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02116918563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06753873825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99914264678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07681274414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18578243255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2031717300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19041967391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1046347618103</t>
+    <t xml:space="preserve">6.16491556167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02116823196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06753778457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99914216995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07681226730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18578338623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20317125320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19042015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10463523864746</t>
   </si>
   <si>
     <t xml:space="preserve">6.16375684738159</t>
@@ -3203,28 +3203,28 @@
     <t xml:space="preserve">5.99566507339478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24954080581665</t>
+    <t xml:space="preserve">6.24954128265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.22867441177368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24722290039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20548915863037</t>
+    <t xml:space="preserve">6.24722242355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20548963546753</t>
   </si>
   <si>
     <t xml:space="preserve">6.3573522567749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43386316299438</t>
+    <t xml:space="preserve">6.43386268615723</t>
   </si>
   <si>
     <t xml:space="preserve">6.48023366928101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37242269515991</t>
+    <t xml:space="preserve">6.37242317199707</t>
   </si>
   <si>
     <t xml:space="preserve">6.12550115585327</t>
@@ -3233,28 +3233,28 @@
     <t xml:space="preserve">6.12318277359009</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11043071746826</t>
+    <t xml:space="preserve">6.1104302406311</t>
   </si>
   <si>
     <t xml:space="preserve">6.27156686782837</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3793773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47443628311157</t>
+    <t xml:space="preserve">6.37937831878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47443723678589</t>
   </si>
   <si>
     <t xml:space="preserve">6.51269245147705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91031789779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99146509170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07840824127197</t>
+    <t xml:space="preserve">6.91031742095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99146461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07840871810913</t>
   </si>
   <si>
     <t xml:space="preserve">7.29750728607178</t>
@@ -3263,28 +3263,28 @@
     <t xml:space="preserve">7.3183741569519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34851503372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50037622451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46559953689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705104827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58964061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64180517196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58616161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66615104675293</t>
+    <t xml:space="preserve">7.34851551055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50037860870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46560001373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705152511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58964014053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64180612564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5861611366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6661524772644</t>
   </si>
   <si>
     <t xml:space="preserve">7.57341003417969</t>
@@ -3293,55 +3293,55 @@
     <t xml:space="preserve">7.66730976104736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63948678970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66846942901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85394954681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80294227600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77048349380493</t>
+    <t xml:space="preserve">7.63948774337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66846895217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85394906997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80294275283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77048301696777</t>
   </si>
   <si>
     <t xml:space="preserve">7.98494577407837</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0162467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90611696243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01044940948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18781471252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29678440093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.348952293396</t>
+    <t xml:space="preserve">8.01624584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90611505508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01044845581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18781566619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29678535461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34895133972168</t>
   </si>
   <si>
     <t xml:space="preserve">8.42082500457764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.259690284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46139907836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51588439941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57036972045898</t>
+    <t xml:space="preserve">8.25968837738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46139812469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51588535308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57036876678467</t>
   </si>
   <si>
     <t xml:space="preserve">8.51356601715088</t>
@@ -3368,16 +3368,16 @@
     <t xml:space="preserve">8.50545120239258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46951389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78281116485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40054130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27200603485107</t>
+    <t xml:space="preserve">8.46951484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78281021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40054225921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27200508117676</t>
   </si>
   <si>
     <t xml:space="preserve">9.32146072387695</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">9.11963367462158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84830379486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43663120269775</t>
+    <t xml:space="preserve">8.84830284118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43663215637207</t>
   </si>
   <si>
     <t xml:space="preserve">8.60236835479736</t>
@@ -3398,13 +3398,13 @@
     <t xml:space="preserve">8.30564403533936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49945163726807</t>
+    <t xml:space="preserve">8.49945068359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.37381076812744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42460060119629</t>
+    <t xml:space="preserve">8.42460155487061</t>
   </si>
   <si>
     <t xml:space="preserve">8.681227684021</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">8.69726753234863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76142406463623</t>
+    <t xml:space="preserve">8.76142501831055</t>
   </si>
   <si>
     <t xml:space="preserve">8.93117332458496</t>
@@ -3422,25 +3422,25 @@
     <t xml:space="preserve">9.08889293670654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01805114746094</t>
+    <t xml:space="preserve">9.01805210113525</t>
   </si>
   <si>
     <t xml:space="preserve">8.84295749664307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79483985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86567783355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95790386199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02206230163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82825374603271</t>
+    <t xml:space="preserve">8.79483890533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86567878723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95790481567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02206134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82825469970703</t>
   </si>
   <si>
     <t xml:space="preserve">8.87770843505859</t>
@@ -3449,10 +3449,10 @@
     <t xml:space="preserve">8.94186592102051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82424545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86968898773193</t>
+    <t xml:space="preserve">8.82424449920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86968994140625</t>
   </si>
   <si>
     <t xml:space="preserve">9.07552623748779</t>
@@ -3461,61 +3461,61 @@
     <t xml:space="preserve">9.06082344055176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97795486450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30542087554932</t>
+    <t xml:space="preserve">8.97795391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30542182922363</t>
   </si>
   <si>
     <t xml:space="preserve">9.28537273406982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2679967880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25061988830566</t>
+    <t xml:space="preserve">9.26799583435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25062084197998</t>
   </si>
   <si>
     <t xml:space="preserve">9.14369201660156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6796703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85610198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0579290390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1755495071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3158922195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.602707862854</t>
+    <t xml:space="preserve">9.67966938018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85610103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0579280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1755485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3158931732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6027069091797</t>
   </si>
   <si>
     <t xml:space="preserve">10.5399112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6655054092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9837732315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5970001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4785423278809</t>
+    <t xml:space="preserve">10.665506362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.983772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.596999168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4785413742065</t>
   </si>
   <si>
     <t xml:space="preserve">10.1288757324219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1374397277832</t>
+    <t xml:space="preserve">10.1374387741089</t>
   </si>
   <si>
     <t xml:space="preserve">10.2801599502563</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">10.4457149505615</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4628410339355</t>
+    <t xml:space="preserve">10.4628400802612</t>
   </si>
   <si>
     <t xml:space="preserve">10.7754001617432</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">10.9124116897583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9109840393066</t>
+    <t xml:space="preserve">10.9109830856323</t>
   </si>
   <si>
     <t xml:space="preserve">10.6526594161987</t>
@@ -3548,67 +3548,67 @@
     <t xml:space="preserve">10.5613193511963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6597967147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8082256317139</t>
+    <t xml:space="preserve">10.6597957611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8082246780396</t>
   </si>
   <si>
     <t xml:space="preserve">10.7397193908691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7340097427368</t>
+    <t xml:space="preserve">10.7340106964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8910026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7816705703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3457975387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4551305770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.481369972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4886598587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4667921066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4288902282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4901161193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0906867980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0761098861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2204303741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1227588653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8312349319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8705940246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.8910036087036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7816705703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3457975387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4551305770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.481369972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4886598587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4667921066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4288902282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4901170730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.09068775177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0761108398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2204294204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1227588653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8312349319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8705940246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8910045623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0061683654785</t>
+    <t xml:space="preserve">11.0061674118042</t>
   </si>
   <si>
     <t xml:space="preserve">10.6869144439697</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">10.7306489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.678168296814</t>
+    <t xml:space="preserve">10.6781692504883</t>
   </si>
   <si>
     <t xml:space="preserve">10.8283195495605</t>
@@ -3626,25 +3626,25 @@
     <t xml:space="preserve">11.0047092437744</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0003366470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7364797592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9376516342163</t>
+    <t xml:space="preserve">11.0003356933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7364807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9376525878906</t>
   </si>
   <si>
     <t xml:space="preserve">11.1636066436768</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2160873413086</t>
+    <t xml:space="preserve">11.2160863876343</t>
   </si>
   <si>
     <t xml:space="preserve">11.2787704467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2583608627319</t>
+    <t xml:space="preserve">11.2583618164062</t>
   </si>
   <si>
     <t xml:space="preserve">11.7190160751343</t>
@@ -3659,19 +3659,19 @@
     <t xml:space="preserve">11.9143581390381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0338954925537</t>
+    <t xml:space="preserve">12.033896446228</t>
   </si>
   <si>
     <t xml:space="preserve">12.1709260940552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5120449066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7219648361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7379989624023</t>
+    <t xml:space="preserve">12.5120439529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7219638824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.737998008728</t>
   </si>
   <si>
     <t xml:space="preserve">12.5601511001587</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">12.3167037963867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3181600570679</t>
+    <t xml:space="preserve">12.3181610107422</t>
   </si>
   <si>
     <t xml:space="preserve">12.3604364395142</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0003681182861</t>
+    <t xml:space="preserve">12.0003671646118</t>
   </si>
   <si>
     <t xml:space="preserve">12.4056282043457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3808450698853</t>
+    <t xml:space="preserve">12.3808441162109</t>
   </si>
   <si>
     <t xml:space="preserve">12.3560628890991</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">12.436240196228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2758855819702</t>
+    <t xml:space="preserve">12.2758846282959</t>
   </si>
   <si>
     <t xml:space="preserve">12.2613086700439</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">12.1738414764404</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3414850234985</t>
+    <t xml:space="preserve">12.3414840698242</t>
   </si>
   <si>
     <t xml:space="preserve">12.1942501068115</t>
@@ -3734,13 +3734,13 @@
     <t xml:space="preserve">12.0936632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.688404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0164031982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429269790649</t>
+    <t xml:space="preserve">11.6884031295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0164012908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429279327393</t>
   </si>
   <si>
     <t xml:space="preserve">11.8370971679688</t>
@@ -3749,19 +3749,19 @@
     <t xml:space="preserve">11.6679944992065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4332933425903</t>
+    <t xml:space="preserve">11.4332942962646</t>
   </si>
   <si>
     <t xml:space="preserve">11.0222034454346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.049901008606</t>
+    <t xml:space="preserve">11.0499000549316</t>
   </si>
   <si>
     <t xml:space="preserve">11.4289216995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3633222579956</t>
+    <t xml:space="preserve">11.3633213043213</t>
   </si>
   <si>
     <t xml:space="preserve">11.4814004898071</t>
@@ -3770,31 +3770,31 @@
     <t xml:space="preserve">11.5790710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4347515106201</t>
+    <t xml:space="preserve">11.4347524642944</t>
   </si>
   <si>
     <t xml:space="preserve">11.5324220657349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9201889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8006534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9318523406982</t>
+    <t xml:space="preserve">11.9201898574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8006525039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9318532943726</t>
   </si>
   <si>
     <t xml:space="preserve">12.7175903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7146739959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0280961990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.117018699646</t>
+    <t xml:space="preserve">12.714674949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0280952453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1170177459717</t>
   </si>
   <si>
     <t xml:space="preserve">13.0834903717041</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">13.5645561218262</t>
   </si>
   <si>
-    <t xml:space="preserve">13.369213104248</t>
+    <t xml:space="preserve">13.3692140579224</t>
   </si>
   <si>
     <t xml:space="preserve">13.0062284469604</t>
@@ -3818,16 +3818,16 @@
     <t xml:space="preserve">13.1053562164307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6388692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4930925369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5412006378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5732698440552</t>
+    <t xml:space="preserve">12.6388702392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4930934906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5411996841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5732707977295</t>
   </si>
   <si>
     <t xml:space="preserve">12.6024265289307</t>
@@ -3836,7 +3836,7 @@
     <t xml:space="preserve">12.485803604126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5105857849121</t>
+    <t xml:space="preserve">12.5105867385864</t>
   </si>
   <si>
     <t xml:space="preserve">12.4041690826416</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">12.2744283676147</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4814319610596</t>
+    <t xml:space="preserve">12.4814310073853</t>
   </si>
   <si>
     <t xml:space="preserve">12.567440032959</t>
@@ -3854,16 +3854,16 @@
     <t xml:space="preserve">12.4537343978882</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0980367660522</t>
+    <t xml:space="preserve">12.0980377197266</t>
   </si>
   <si>
     <t xml:space="preserve">12.1636371612549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1753005981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2656812667847</t>
+    <t xml:space="preserve">12.1752996444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2656803131104</t>
   </si>
   <si>
     <t xml:space="preserve">12.6898918151855</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">11.7044401168823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6854887008667</t>
+    <t xml:space="preserve">11.6854877471924</t>
   </si>
   <si>
     <t xml:space="preserve">12.0645084381104</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">12.2219486236572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2365255355835</t>
+    <t xml:space="preserve">12.2365264892578</t>
   </si>
   <si>
     <t xml:space="preserve">12.3444013595581</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">12.0426416397095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8575038909912</t>
+    <t xml:space="preserve">11.8575048446655</t>
   </si>
   <si>
     <t xml:space="preserve">11.7627506256104</t>
@@ -3914,31 +3914,31 @@
     <t xml:space="preserve">12.0790863037109</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1534328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2642240524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2860908508301</t>
+    <t xml:space="preserve">12.153431892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2642230987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2860898971558</t>
   </si>
   <si>
     <t xml:space="preserve">12.2671394348145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4114589691162</t>
+    <t xml:space="preserve">12.4114580154419</t>
   </si>
   <si>
     <t xml:space="preserve">12.3123302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2292366027832</t>
+    <t xml:space="preserve">12.2292375564575</t>
   </si>
   <si>
     <t xml:space="preserve">12.2598505020142</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2846326828003</t>
+    <t xml:space="preserve">12.284631729126</t>
   </si>
   <si>
     <t xml:space="preserve">12.281717300415</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">12.7190494537354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7321672439575</t>
+    <t xml:space="preserve">12.7321681976318</t>
   </si>
   <si>
     <t xml:space="preserve">12.7904796600342</t>
@@ -3968,10 +3968,10 @@
     <t xml:space="preserve">12.857536315918</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9143896102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7817325592041</t>
+    <t xml:space="preserve">12.9143905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7817316055298</t>
   </si>
   <si>
     <t xml:space="preserve">12.7117595672607</t>
@@ -3989,40 +3989,40 @@
     <t xml:space="preserve">13.1855354309082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0878639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.093695640564</t>
+    <t xml:space="preserve">13.0878629684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0936946868896</t>
   </si>
   <si>
     <t xml:space="preserve">12.7248802185059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3983383178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2511034011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1782150268555</t>
+    <t xml:space="preserve">12.3983392715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2511043548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1782159805298</t>
   </si>
   <si>
     <t xml:space="preserve">11.3458280563354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3472852706909</t>
+    <t xml:space="preserve">11.3472862243652</t>
   </si>
   <si>
     <t xml:space="preserve">11.0353240966797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.662163734436</t>
+    <t xml:space="preserve">11.6621646881104</t>
   </si>
   <si>
     <t xml:space="preserve">11.6096849441528</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4755706787109</t>
+    <t xml:space="preserve">11.4755697250366</t>
   </si>
   <si>
     <t xml:space="preserve">11.8749990463257</t>
@@ -4034,28 +4034,28 @@
     <t xml:space="preserve">12.1592636108398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9887046813965</t>
+    <t xml:space="preserve">11.9887056350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.0193185806274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9289360046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8589630126953</t>
+    <t xml:space="preserve">11.9289350509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8589639663696</t>
   </si>
   <si>
     <t xml:space="preserve">11.8924913406372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.963921546936</t>
+    <t xml:space="preserve">11.9639225006104</t>
   </si>
   <si>
     <t xml:space="preserve">11.5309648513794</t>
   </si>
   <si>
-    <t xml:space="preserve">11.886661529541</t>
+    <t xml:space="preserve">11.8866624832153</t>
   </si>
   <si>
     <t xml:space="preserve">11.9916200637817</t>
@@ -4064,10 +4064,10 @@
     <t xml:space="preserve">12.2685976028442</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1621799468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6301221847534</t>
+    <t xml:space="preserve">12.1621789932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6301231384277</t>
   </si>
   <si>
     <t xml:space="preserve">12.9114751815796</t>
@@ -4091,13 +4091,13 @@
     <t xml:space="preserve">13.3969106674194</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8561096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.829870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9508628845215</t>
+    <t xml:space="preserve">13.8561105728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8298692703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9508638381958</t>
   </si>
   <si>
     <t xml:space="preserve">13.9173345565796</t>
@@ -4106,19 +4106,19 @@
     <t xml:space="preserve">13.8415307998657</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6986694335938</t>
+    <t xml:space="preserve">13.6986703872681</t>
   </si>
   <si>
     <t xml:space="preserve">13.2132320404053</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1009531021118</t>
+    <t xml:space="preserve">12.1009521484375</t>
   </si>
   <si>
     <t xml:space="preserve">12.6855182647705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7861042022705</t>
+    <t xml:space="preserve">12.7861051559448</t>
   </si>
   <si>
     <t xml:space="preserve">12.4406147003174</t>
@@ -4127,10 +4127,10 @@
     <t xml:space="preserve">12.3691825866699</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6417856216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6636524200439</t>
+    <t xml:space="preserve">12.6417846679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6636533737183</t>
   </si>
   <si>
     <t xml:space="preserve">11.998908996582</t>
@@ -4142,13 +4142,13 @@
     <t xml:space="preserve">11.9814167022705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4683122634888</t>
+    <t xml:space="preserve">12.4683113098145</t>
   </si>
   <si>
     <t xml:space="preserve">12.3618936538696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2234058380127</t>
+    <t xml:space="preserve">12.223406791687</t>
   </si>
   <si>
     <t xml:space="preserve">11.9099855422974</t>
@@ -4169,10 +4169,10 @@
     <t xml:space="preserve">12.4391555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6869468688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3065004348755</t>
+    <t xml:space="preserve">11.6869459152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3064994812012</t>
   </si>
   <si>
     <t xml:space="preserve">11.1052961349487</t>
@@ -4181,28 +4181,28 @@
     <t xml:space="preserve">11.2190027236938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9041242599487</t>
+    <t xml:space="preserve">10.9041233062744</t>
   </si>
   <si>
     <t xml:space="preserve">10.074652671814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43031692504883</t>
+    <t xml:space="preserve">9.43031787872314</t>
   </si>
   <si>
     <t xml:space="preserve">9.42594432830811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5834140777588</t>
+    <t xml:space="preserve">10.5834150314331</t>
   </si>
   <si>
     <t xml:space="preserve">9.81808471679688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83703517913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2043943405151</t>
+    <t xml:space="preserve">9.8370361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2043933868408</t>
   </si>
   <si>
     <t xml:space="preserve">10.3180999755859</t>
@@ -4229,13 +4229,13 @@
     <t xml:space="preserve">10.5046939849854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5207300186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5323915481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2321214675903</t>
+    <t xml:space="preserve">10.5207290649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5323925018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2321224212646</t>
   </si>
   <si>
     <t xml:space="preserve">11.0542736053467</t>
@@ -4244,10 +4244,10 @@
     <t xml:space="preserve">10.7875022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7802124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8516426086426</t>
+    <t xml:space="preserve">10.7802133560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8516445159912</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522142410278</t>
@@ -4259,16 +4259,16 @@
     <t xml:space="preserve">9.86910629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0338344573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1475410461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1358785629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1854438781738</t>
+    <t xml:space="preserve">10.0338354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1475400924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1358795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1854419708252</t>
   </si>
   <si>
     <t xml:space="preserve">10.2583312988281</t>
@@ -4277,13 +4277,13 @@
     <t xml:space="preserve">10.5054616928101</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5621299743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6644458770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3197202682495</t>
+    <t xml:space="preserve">10.5621309280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6644449234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3197212219238</t>
   </si>
   <si>
     <t xml:space="preserve">10.0741624832153</t>
@@ -4292,22 +4292,22 @@
     <t xml:space="preserve">9.75304889678955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94823551177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0710144042969</t>
+    <t xml:space="preserve">9.9482364654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0710134506226</t>
   </si>
   <si>
     <t xml:space="preserve">10.2174043655396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9088830947876</t>
+    <t xml:space="preserve">9.90888404846191</t>
   </si>
   <si>
     <t xml:space="preserve">10.2237005233765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0914764404297</t>
+    <t xml:space="preserve">10.091477394104</t>
   </si>
   <si>
     <t xml:space="preserve">10.0190687179565</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">9.99545764923096</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1119403839111</t>
+    <t xml:space="preserve">10.1119394302368</t>
   </si>
   <si>
     <t xml:space="preserve">10.4125909805298</t>
@@ -4340,7 +4340,7 @@
     <t xml:space="preserve">10.6313905715942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6030569076538</t>
+    <t xml:space="preserve">10.6030559539795</t>
   </si>
   <si>
     <t xml:space="preserve">10.6565752029419</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">10.6817607879639</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3386087417603</t>
+    <t xml:space="preserve">10.3386096954346</t>
   </si>
   <si>
     <t xml:space="preserve">10.5306482315063</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">10.7903728485107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8202810287476</t>
+    <t xml:space="preserve">10.8202800750732</t>
   </si>
   <si>
     <t xml:space="preserve">11.0186147689819</t>
@@ -4367,19 +4367,19 @@
     <t xml:space="preserve">10.9666700363159</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1571340560913</t>
+    <t xml:space="preserve">11.1571350097656</t>
   </si>
   <si>
     <t xml:space="preserve">11.2263946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8549098968506</t>
+    <t xml:space="preserve">10.8549108505249</t>
   </si>
   <si>
     <t xml:space="preserve">11.064263343811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9304656982422</t>
+    <t xml:space="preserve">10.9304666519165</t>
   </si>
   <si>
     <t xml:space="preserve">11.0249118804932</t>
@@ -4388,13 +4388,13 @@
     <t xml:space="preserve">10.7919464111328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2252740859985</t>
+    <t xml:space="preserve">10.2252750396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.82388305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82073307037354</t>
+    <t xml:space="preserve">9.82073402404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.0977735519409</t>
@@ -4406,16 +4406,16 @@
     <t xml:space="preserve">9.63027000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74989986419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99388408660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82230854034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61295509338379</t>
+    <t xml:space="preserve">9.74990081787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99388313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82230758666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61295413970947</t>
   </si>
   <si>
     <t xml:space="preserve">9.78138160705566</t>
@@ -4442,13 +4442,13 @@
     <t xml:space="preserve">8.84637355804443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.818039894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44295406341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80499267578125</t>
+    <t xml:space="preserve">8.81804084777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44295310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80499362945557</t>
   </si>
   <si>
     <t xml:space="preserve">9.60193634033203</t>
@@ -4460,10 +4460,10 @@
     <t xml:space="preserve">9.4445276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20211887359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40989875793457</t>
+    <t xml:space="preserve">9.20211791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40989780426025</t>
   </si>
   <si>
     <t xml:space="preserve">9.64443683624268</t>
@@ -4472,16 +4472,16 @@
     <t xml:space="preserve">10.014347076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94981002807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89156818389893</t>
+    <t xml:space="preserve">9.94980907440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89156913757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.9545316696167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1150884628296</t>
+    <t xml:space="preserve">10.1150894165039</t>
   </si>
   <si>
     <t xml:space="preserve">10.0348100662231</t>
@@ -4496,19 +4496,19 @@
     <t xml:space="preserve">10.9572257995605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0548181533813</t>
+    <t xml:space="preserve">11.0548191070557</t>
   </si>
   <si>
     <t xml:space="preserve">11.2405614852905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3523216247559</t>
+    <t xml:space="preserve">11.3523225784302</t>
   </si>
   <si>
     <t xml:space="preserve">11.2736177444458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2799139022827</t>
+    <t xml:space="preserve">11.2799129486084</t>
   </si>
   <si>
     <t xml:space="preserve">11.6340827941895</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">11.4971380233765</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5585279464722</t>
+    <t xml:space="preserve">11.5585269927979</t>
   </si>
   <si>
     <t xml:space="preserve">11.673436164856</t>
@@ -4529,31 +4529,31 @@
     <t xml:space="preserve">11.726954460144</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7049179077148</t>
+    <t xml:space="preserve">11.5223226547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7049169540405</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9021320343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0500965118408</t>
+    <t xml:space="preserve">10.9021329879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0500974655151</t>
   </si>
   <si>
     <t xml:space="preserve">11.1681537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.089448928833</t>
+    <t xml:space="preserve">11.0894498825073</t>
   </si>
   <si>
     <t xml:space="preserve">10.8139839172363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8265771865845</t>
+    <t xml:space="preserve">10.8265762329102</t>
   </si>
   <si>
     <t xml:space="preserve">10.7195386886597</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">10.3323135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4613885879517</t>
+    <t xml:space="preserve">10.4613876342773</t>
   </si>
   <si>
     <t xml:space="preserve">10.8124103546143</t>
@@ -4592,10 +4592,10 @@
     <t xml:space="preserve">10.7557430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7699098587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5463895797729</t>
+    <t xml:space="preserve">10.7699089050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5463876724243</t>
   </si>
   <si>
     <t xml:space="preserve">10.6329641342163</t>
@@ -4604,19 +4604,19 @@
     <t xml:space="preserve">10.4047212600708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4912967681885</t>
+    <t xml:space="preserve">10.4912958145142</t>
   </si>
   <si>
     <t xml:space="preserve">10.237868309021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0111989974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1009216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0946264266968</t>
+    <t xml:space="preserve">10.0111999511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1009225845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0946254730225</t>
   </si>
   <si>
     <t xml:space="preserve">9.65860366821289</t>
@@ -4625,37 +4625,37 @@
     <t xml:space="preserve">9.84906768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93564224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86480903625488</t>
+    <t xml:space="preserve">9.93564319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8648099899292</t>
   </si>
   <si>
     <t xml:space="preserve">9.68064117431641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5893440246582</t>
+    <t xml:space="preserve">9.58934307098389</t>
   </si>
   <si>
     <t xml:space="preserve">9.69638156890869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5972146987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82703018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83647441864014</t>
+    <t xml:space="preserve">9.59721374511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82703113555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83647537231445</t>
   </si>
   <si>
     <t xml:space="preserve">10.0851812362671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2488861083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2063865661621</t>
+    <t xml:space="preserve">10.2488870620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2063856124878</t>
   </si>
   <si>
     <t xml:space="preserve">10.3685169219971</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">10.6487045288086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7447242736816</t>
+    <t xml:space="preserve">10.7447233200073</t>
   </si>
   <si>
     <t xml:space="preserve">10.7305574417114</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">10.7510204315186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8092622756958</t>
+    <t xml:space="preserve">10.8092613220215</t>
   </si>
   <si>
     <t xml:space="preserve">10.4566659927368</t>
@@ -4694,19 +4694,19 @@
     <t xml:space="preserve">11.1429681777954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1980600357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.339729309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4247303009033</t>
+    <t xml:space="preserve">11.1980619430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3397302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.424729347229</t>
   </si>
   <si>
     <t xml:space="preserve">11.2153768539429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1036157608032</t>
+    <t xml:space="preserve">11.1036167144775</t>
   </si>
   <si>
     <t xml:space="preserve">11.3413028717041</t>
@@ -4715,13 +4715,13 @@
     <t xml:space="preserve">11.4451932907104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5553789138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3838033676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5333423614502</t>
+    <t xml:space="preserve">11.5553798675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3838043212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5333414077759</t>
   </si>
   <si>
     <t xml:space="preserve">11.5301933288574</t>
@@ -4748,7 +4748,7 @@
     <t xml:space="preserve">11.3712110519409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979711532593</t>
+    <t xml:space="preserve">11.397970199585</t>
   </si>
   <si>
     <t xml:space="preserve">11.0831527709961</t>
@@ -4760,10 +4760,10 @@
     <t xml:space="preserve">10.8486137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8612060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9336137771606</t>
+    <t xml:space="preserve">10.8612070083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.933614730835</t>
   </si>
   <si>
     <t xml:space="preserve">10.6675939559937</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">10.3559246063232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3244428634644</t>
+    <t xml:space="preserve">10.32444190979</t>
   </si>
   <si>
     <t xml:space="preserve">10.52907371521</t>
@@ -4787,7 +4787,7 @@
     <t xml:space="preserve">10.4393510818481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7415761947632</t>
+    <t xml:space="preserve">10.7415752410889</t>
   </si>
   <si>
     <t xml:space="preserve">10.8816699981689</t>
@@ -4796,13 +4796,13 @@
     <t xml:space="preserve">11.1697282791138</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2862100601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3696365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5427875518799</t>
+    <t xml:space="preserve">11.2862110137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3696374893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5427865982056</t>
   </si>
   <si>
     <t xml:space="preserve">11.5286197662354</t>
@@ -4811,19 +4811,19 @@
     <t xml:space="preserve">11.6246395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1996355056763</t>
+    <t xml:space="preserve">11.199634552002</t>
   </si>
   <si>
     <t xml:space="preserve">11.2673206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3035259246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2295427322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9477806091309</t>
+    <t xml:space="preserve">11.3035249710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2295417785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9477815628052</t>
   </si>
   <si>
     <t xml:space="preserve">11.037504196167</t>
@@ -4841,34 +4841,34 @@
     <t xml:space="preserve">11.0611152648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1728754043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3145437240601</t>
+    <t xml:space="preserve">11.1728763580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3145446777344</t>
   </si>
   <si>
     <t xml:space="preserve">11.4026927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9693651199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9630689620972</t>
+    <t xml:space="preserve">11.9693641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9630680084229</t>
   </si>
   <si>
     <t xml:space="preserve">11.8686237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8749189376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9016790390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3392753601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1299209594727</t>
+    <t xml:space="preserve">11.8749198913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9016780853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3392763137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.129921913147</t>
   </si>
   <si>
     <t xml:space="preserve">12.2054777145386</t>
@@ -4877,16 +4877,16 @@
     <t xml:space="preserve">12.258996963501</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4903879165649</t>
+    <t xml:space="preserve">12.4903869628906</t>
   </si>
   <si>
     <t xml:space="preserve">12.517147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5533514022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7013158798218</t>
+    <t xml:space="preserve">12.5533504486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7013149261475</t>
   </si>
   <si>
     <t xml:space="preserve">12.4888134002686</t>
@@ -4895,7 +4895,7 @@
     <t xml:space="preserve">12.7642793655396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2254867553711</t>
+    <t xml:space="preserve">13.2254877090454</t>
   </si>
   <si>
     <t xml:space="preserve">12.946873664856</t>
@@ -4913,37 +4913,37 @@
     <t xml:space="preserve">13.5151195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9054918289185</t>
+    <t xml:space="preserve">13.9054927825928</t>
   </si>
   <si>
     <t xml:space="preserve">13.8330850601196</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7968807220459</t>
+    <t xml:space="preserve">13.7968816757202</t>
   </si>
   <si>
     <t xml:space="preserve">13.7653980255127</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5387296676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2915992736816</t>
+    <t xml:space="preserve">13.5387306213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2915983200073</t>
   </si>
   <si>
     <t xml:space="preserve">12.7532606124878</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9027986526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4305715560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5265913009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4714984893799</t>
+    <t xml:space="preserve">12.9027976989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4305725097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5265922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4714994430542</t>
   </si>
   <si>
     <t xml:space="preserve">12.7390937805176</t>
@@ -4955,10 +4955,10 @@
     <t xml:space="preserve">12.7343711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7737226486206</t>
+    <t xml:space="preserve">12.5155725479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7737236022949</t>
   </si>
   <si>
     <t xml:space="preserve">12.7910394668579</t>
@@ -4970,7 +4970,7 @@
     <t xml:space="preserve">13.050763130188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1719675064087</t>
+    <t xml:space="preserve">13.171968460083</t>
   </si>
   <si>
     <t xml:space="preserve">13.1200227737427</t>
@@ -4979,10 +4979,10 @@
     <t xml:space="preserve">12.9390029907227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6824264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7878894805908</t>
+    <t xml:space="preserve">12.682427406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7878904342651</t>
   </si>
   <si>
     <t xml:space="preserve">13.1829862594604</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">13.2191896438599</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2443752288818</t>
+    <t xml:space="preserve">13.2443742752075</t>
   </si>
   <si>
     <t xml:space="preserve">13.5088224411011</t>
@@ -5054,13 +5054,13 @@
     <t xml:space="preserve">12.770318031311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6242437362671</t>
+    <t xml:space="preserve">12.6242446899414</t>
   </si>
   <si>
     <t xml:space="preserve">12.7514142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0143480300903</t>
+    <t xml:space="preserve">13.014347076416</t>
   </si>
   <si>
     <t xml:space="preserve">13.2600955963135</t>
@@ -5069,13 +5069,13 @@
     <t xml:space="preserve">13.1655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0934000015259</t>
+    <t xml:space="preserve">13.0933990478516</t>
   </si>
   <si>
     <t xml:space="preserve">12.5623769760132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4334878921509</t>
+    <t xml:space="preserve">12.4334888458252</t>
   </si>
   <si>
     <t xml:space="preserve">12.6929845809937</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">13.5470886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5178737640381</t>
+    <t xml:space="preserve">13.5178747177124</t>
   </si>
   <si>
     <t xml:space="preserve">13.6261405944824</t>
@@ -5132,13 +5132,13 @@
     <t xml:space="preserve">13.2033843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0813703536987</t>
+    <t xml:space="preserve">13.0813694000244</t>
   </si>
   <si>
     <t xml:space="preserve">12.9885702133179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0469999313354</t>
+    <t xml:space="preserve">13.0469989776611</t>
   </si>
   <si>
     <t xml:space="preserve">13.1587028503418</t>
@@ -5153,7 +5153,7 @@
     <t xml:space="preserve">13.8254890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.999059677124</t>
+    <t xml:space="preserve">13.9990587234497</t>
   </si>
   <si>
     <t xml:space="preserve">13.9681262969971</t>
@@ -5171,7 +5171,7 @@
     <t xml:space="preserve">13.9767189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0437412261963</t>
+    <t xml:space="preserve">14.043740272522</t>
   </si>
   <si>
     <t xml:space="preserve">14.3736963272095</t>
@@ -5180,52 +5180,52 @@
     <t xml:space="preserve">14.4458742141724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3547925949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2671489715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2551193237305</t>
+    <t xml:space="preserve">14.3547916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2671480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2551183700562</t>
   </si>
   <si>
     <t xml:space="preserve">14.3152666091919</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1863784790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4149408340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4235334396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8050441741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.593846321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650459289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0200386047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192983627319</t>
+    <t xml:space="preserve">14.1863775253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4149398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4235324859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8050451278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5938453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650449752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0200366973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192974090576</t>
   </si>
   <si>
     <t xml:space="preserve">15.5147933959961</t>
   </si>
   <si>
-    <t xml:space="preserve">15.373875617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3446598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2982606887817</t>
+    <t xml:space="preserve">15.3738746643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3446588516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2982597351074</t>
   </si>
   <si>
     <t xml:space="preserve">15.0834455490112</t>
@@ -5243,31 +5243,31 @@
     <t xml:space="preserve">14.5197706222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3221406936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1571636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0523338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3015184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3633852005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.378851890564</t>
+    <t xml:space="preserve">14.3221397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1571626663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0523328781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3015174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3633842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3788509368896</t>
   </si>
   <si>
     <t xml:space="preserve">14.2173109054565</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3668222427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5489845275879</t>
+    <t xml:space="preserve">14.3668212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5489854812622</t>
   </si>
   <si>
     <t xml:space="preserve">14.7964515686035</t>
@@ -5276,10 +5276,10 @@
     <t xml:space="preserve">14.7500524520874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7586450576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4355630874634</t>
+    <t xml:space="preserve">14.7586460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4355621337891</t>
   </si>
   <si>
     <t xml:space="preserve">14.4493112564087</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">14.5386743545532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5661697387695</t>
+    <t xml:space="preserve">14.5661706924438</t>
   </si>
   <si>
     <t xml:space="preserve">14.6074151992798</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">15.2673263549805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1006298065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3859052658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2827930450439</t>
+    <t xml:space="preserve">15.1006288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3859033584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2827920913696</t>
   </si>
   <si>
     <t xml:space="preserve">15.5113563537598</t>
@@ -5321,43 +5321,43 @@
     <t xml:space="preserve">15.9959783554077</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6058759689331</t>
+    <t xml:space="preserve">15.6058750152588</t>
   </si>
   <si>
     <t xml:space="preserve">15.712423324585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5251054763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4512090682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.607593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6471185684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.55260181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999782562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.231237411499</t>
+    <t xml:space="preserve">15.5251045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4512071609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6075925827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6471195220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5526008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2312364578247</t>
   </si>
   <si>
     <t xml:space="preserve">15.3137273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4649562835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9444236755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2726612091064</t>
+    <t xml:space="preserve">15.464955329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9444227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2726593017578</t>
   </si>
   <si>
     <t xml:space="preserve">16.246883392334</t>
@@ -5369,25 +5369,25 @@
     <t xml:space="preserve">16.0681571960449</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2348537445068</t>
+    <t xml:space="preserve">16.2348518371582</t>
   </si>
   <si>
     <t xml:space="preserve">16.1300239562988</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5405721664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1642160415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4855785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2759189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1848382949829</t>
+    <t xml:space="preserve">15.5405702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1642150878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.485577583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.275918006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1848392486572</t>
   </si>
   <si>
     <t xml:space="preserve">14.8806600570679</t>
@@ -5396,16 +5396,16 @@
     <t xml:space="preserve">14.6417865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.122971534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4168376922607</t>
+    <t xml:space="preserve">15.1229705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4168367385864</t>
   </si>
   <si>
     <t xml:space="preserve">15.7553873062134</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0647201538086</t>
+    <t xml:space="preserve">16.06471824646</t>
   </si>
   <si>
     <t xml:space="preserve">15.7467937469482</t>
@@ -5417,16 +5417,16 @@
     <t xml:space="preserve">15.5749416351318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7364816665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0440998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2211036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.894585609436</t>
+    <t xml:space="preserve">15.7364826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0440979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2211055755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8945846557617</t>
   </si>
   <si>
     <t xml:space="preserve">15.8705272674561</t>
@@ -5441,7 +5441,7 @@
     <t xml:space="preserve">16.1094017028809</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0939350128174</t>
+    <t xml:space="preserve">16.0939331054688</t>
   </si>
   <si>
     <t xml:space="preserve">16.9394454956055</t>
@@ -5450,7 +5450,7 @@
     <t xml:space="preserve">17.1009864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2754154205322</t>
+    <t xml:space="preserve">17.2754173278809</t>
   </si>
   <si>
     <t xml:space="preserve">17.4472694396973</t>
@@ -5459,7 +5459,7 @@
     <t xml:space="preserve">17.5847511291504</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0960102081299</t>
+    <t xml:space="preserve">18.0960083007812</t>
   </si>
   <si>
     <t xml:space="preserve">17.9714183807373</t>
@@ -5471,7 +5471,7 @@
     <t xml:space="preserve">18.0530471801758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0186767578125</t>
+    <t xml:space="preserve">18.0186748504639</t>
   </si>
   <si>
     <t xml:space="preserve">17.9671211242676</t>
@@ -5489,28 +5489,28 @@
     <t xml:space="preserve">18.289342880249</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2506771087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2549743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2377891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2420845031738</t>
+    <t xml:space="preserve">18.250675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2549724578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2377872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2420825958252</t>
   </si>
   <si>
     <t xml:space="preserve">18.2034168243408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1733436584473</t>
+    <t xml:space="preserve">18.1733417510986</t>
   </si>
   <si>
     <t xml:space="preserve">18.19482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5718612670898</t>
+    <t xml:space="preserve">17.5718631744385</t>
   </si>
   <si>
     <t xml:space="preserve">17.5503787994385</t>
@@ -5522,7 +5522,7 @@
     <t xml:space="preserve">17.7608985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620845794678</t>
+    <t xml:space="preserve">17.6620826721191</t>
   </si>
   <si>
     <t xml:space="preserve">17.8554172515869</t>
@@ -5534,7 +5534,7 @@
     <t xml:space="preserve">17.5761566162109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3011951446533</t>
+    <t xml:space="preserve">17.3011932373047</t>
   </si>
   <si>
     <t xml:space="preserve">17.11301612854</t>
@@ -5543,13 +5543,13 @@
     <t xml:space="preserve">16.8741416931152</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0459938049316</t>
+    <t xml:space="preserve">17.045991897583</t>
   </si>
   <si>
     <t xml:space="preserve">16.9016380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9274158477783</t>
+    <t xml:space="preserve">16.927417755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.8122749328613</t>
@@ -5561,7 +5561,7 @@
     <t xml:space="preserve">16.6885433197021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7761859893799</t>
+    <t xml:space="preserve">16.7761878967285</t>
   </si>
   <si>
     <t xml:space="preserve">16.7332248687744</t>
@@ -5570,7 +5570,7 @@
     <t xml:space="preserve">17.374231338501</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6105289459229</t>
+    <t xml:space="preserve">17.6105270385742</t>
   </si>
   <si>
     <t xml:space="preserve">17.8468246459961</t>
@@ -5588,16 +5588,16 @@
     <t xml:space="preserve">18.624454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0197124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3032684326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4536380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2388229370117</t>
+    <t xml:space="preserve">19.0197143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3032703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4536399841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2388248443604</t>
   </si>
   <si>
     <t xml:space="preserve">19.3977890014648</t>
@@ -5621,10 +5621,10 @@
     <t xml:space="preserve">20.8198623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1463832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8843078613281</t>
+    <t xml:space="preserve">21.1463813781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8843059539795</t>
   </si>
   <si>
     <t xml:space="preserve">20.8327522277832</t>
@@ -5636,13 +5636,13 @@
     <t xml:space="preserve">20.7382335662842</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9960117340088</t>
+    <t xml:space="preserve">20.9960098266602</t>
   </si>
   <si>
     <t xml:space="preserve">21.1592712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2494926452637</t>
+    <t xml:space="preserve">21.249490737915</t>
   </si>
   <si>
     <t xml:space="preserve">21.4814929962158</t>
@@ -5663,7 +5663,7 @@
     <t xml:space="preserve">21.8552703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7994194030762</t>
+    <t xml:space="preserve">21.7994213104248</t>
   </si>
   <si>
     <t xml:space="preserve">22.3665313720703</t>
@@ -5672,7 +5672,7 @@
     <t xml:space="preserve">22.4696407318115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8649024963379</t>
+    <t xml:space="preserve">22.8649005889893</t>
   </si>
   <si>
     <t xml:space="preserve">22.9078636169434</t>
@@ -5681,19 +5681,19 @@
     <t xml:space="preserve">23.1269760131836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1441612243652</t>
+    <t xml:space="preserve">23.1441593170166</t>
   </si>
   <si>
     <t xml:space="preserve">23.3331985473633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8391227722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9293460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6371974945068</t>
+    <t xml:space="preserve">22.8391246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9293441772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6371955871582</t>
   </si>
   <si>
     <t xml:space="preserve">21.8939361572266</t>
@@ -5702,10 +5702,10 @@
     <t xml:space="preserve">21.4943809509277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5244541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1377906799316</t>
+    <t xml:space="preserve">21.5244560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.137788772583</t>
   </si>
   <si>
     <t xml:space="preserve">21.3912696838379</t>
@@ -5714,25 +5714,25 @@
     <t xml:space="preserve">21.5459365844727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6791210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6619358062744</t>
+    <t xml:space="preserve">21.6791229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.661937713623</t>
   </si>
   <si>
     <t xml:space="preserve">20.9530487060547</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4771957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8370494842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8542346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9229755401611</t>
+    <t xml:space="preserve">21.4771976470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8370475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8542327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9229736328125</t>
   </si>
   <si>
     <t xml:space="preserve">21.2375450134277</t>
@@ -6816,6 +6816,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.35200023651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22900009155273</t>
   </si>
 </sst>
 </file>
@@ -71998,7 +72001,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6509606481</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>24181371</v>
@@ -72019,6 +72022,32 @@
         <v>2267</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6506712963</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>18482396</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>9.36499977111816</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>9.16399955749512</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>9.30900001525879</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>9.22900009155273</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>2268</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="2269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="2270">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02501440048218</t>
+    <t xml:space="preserve">4.02501392364502</t>
   </si>
   <si>
     <t xml:space="preserve">STLAM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13119506835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91636371612549</t>
+    <t xml:space="preserve">4.13119459152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91636300086975</t>
   </si>
   <si>
     <t xml:space="preserve">3.78795790672302</t>
@@ -56,40 +56,40 @@
     <t xml:space="preserve">3.63238978385925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61757326126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71881675720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66943001747131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37804865837097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28421401977539</t>
+    <t xml:space="preserve">3.61757349967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71881604194641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66943025588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37804841995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28421354293823</t>
   </si>
   <si>
     <t xml:space="preserve">3.18790936470032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26939797401428</t>
+    <t xml:space="preserve">3.2693977355957</t>
   </si>
   <si>
     <t xml:space="preserve">3.06197357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25705075263977</t>
+    <t xml:space="preserve">3.25705099105835</t>
   </si>
   <si>
     <t xml:space="preserve">3.32619261741638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2619903087616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46200561523438</t>
+    <t xml:space="preserve">3.26199007034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46200609207153</t>
   </si>
   <si>
     <t xml:space="preserve">3.43237352371216</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">3.16321659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16074728965759</t>
+    <t xml:space="preserve">3.16074657440186</t>
   </si>
   <si>
     <t xml:space="preserve">3.07678985595703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95332288742065</t>
+    <t xml:space="preserve">2.95332264900208</t>
   </si>
   <si>
     <t xml:space="preserve">2.91628313064575</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">2.94838428497314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65700364112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58292317390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73355293273926</t>
+    <t xml:space="preserve">2.65700316429138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58292293548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73355269432068</t>
   </si>
   <si>
     <t xml:space="preserve">2.59280014038086</t>
@@ -134,31 +134,31 @@
     <t xml:space="preserve">2.80269360542297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75824594497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89899778366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87924337387085</t>
+    <t xml:space="preserve">2.75824522972107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89899754524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87924289703369</t>
   </si>
   <si>
     <t xml:space="preserve">2.81010150909424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92616009712219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83973336219788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72614431381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00517892837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13358473777771</t>
+    <t xml:space="preserve">2.92615985870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83973383903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72614455223083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00517916679382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13358426094055</t>
   </si>
   <si>
     <t xml:space="preserve">3.2990300655365</t>
@@ -167,19 +167,19 @@
     <t xml:space="preserve">3.45212817192078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46447515487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44225120544434</t>
+    <t xml:space="preserve">3.46447587013245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44225072860718</t>
   </si>
   <si>
     <t xml:space="preserve">3.28915238380432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30643796920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21013331413269</t>
+    <t xml:space="preserve">3.30643820762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21013402938843</t>
   </si>
   <si>
     <t xml:space="preserve">3.35088539123535</t>
@@ -188,124 +188,124 @@
     <t xml:space="preserve">3.44718980789185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36076307296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44472002983093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42496633529663</t>
+    <t xml:space="preserve">3.36076331138611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472026824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42496609687805</t>
   </si>
   <si>
     <t xml:space="preserve">3.51633095741272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50151491165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386117935181</t>
+    <t xml:space="preserve">3.50151515007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386141777039</t>
   </si>
   <si>
     <t xml:space="preserve">3.47682189941406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33360052108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57559490203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50645327568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3360698223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841656684875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18050169944763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1385223865509</t>
+    <t xml:space="preserve">3.33360075950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57559514045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5064537525177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33606958389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841632843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18050193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13852262496948</t>
   </si>
   <si>
     <t xml:space="preserve">3.01505637168884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13605356216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21260333061218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1681547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3187837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35335493087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4027419090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56571793556213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54596304893494</t>
+    <t xml:space="preserve">3.13605380058289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21260285377502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16815495491028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31878399848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35335564613342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40274167060852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56571769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54596281051636</t>
   </si>
   <si>
     <t xml:space="preserve">3.56818747520447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47435212135315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53361678123474</t>
+    <t xml:space="preserve">3.47435283660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53361630439758</t>
   </si>
   <si>
     <t xml:space="preserve">3.41014957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38298678398132</t>
+    <t xml:space="preserve">3.38298654556274</t>
   </si>
   <si>
     <t xml:space="preserve">3.29656004905701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26692771911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36570143699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31631565093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38051700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33113121986389</t>
+    <t xml:space="preserve">3.26692843437195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36570167541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31631469726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38051795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33113098144531</t>
   </si>
   <si>
     <t xml:space="preserve">3.108891248703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11383032798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10148310661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629867553711</t>
+    <t xml:space="preserve">3.11382961273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10148334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629939079285</t>
   </si>
   <si>
     <t xml:space="preserve">2.97801637649536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06938195228577</t>
+    <t xml:space="preserve">3.06938219070435</t>
   </si>
   <si>
     <t xml:space="preserve">3.12370681762695</t>
@@ -314,88 +314,88 @@
     <t xml:space="preserve">3.07185125350952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15827751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07431983947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04221963882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03974986076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14840006828308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12123775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9310986995697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87677335739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89652824401855</t>
+    <t xml:space="preserve">3.15827775001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07432055473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0422191619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03974914550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14840030670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1212375164032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93109822273254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87677383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89652848243713</t>
   </si>
   <si>
     <t xml:space="preserve">2.86195755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93356823921204</t>
+    <t xml:space="preserve">2.93356847763062</t>
   </si>
   <si>
     <t xml:space="preserve">3.09407472610474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08666682243347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04962754249573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1113600730896</t>
+    <t xml:space="preserve">3.08666706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04962706565857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11136031150818</t>
   </si>
   <si>
     <t xml:space="preserve">2.81997919082642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64465618133545</t>
+    <t xml:space="preserve">2.64465594291687</t>
   </si>
   <si>
     <t xml:space="preserve">2.66194176673889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71379780769348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77059268951416</t>
+    <t xml:space="preserve">2.7137975692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77059245109558</t>
   </si>
   <si>
     <t xml:space="preserve">2.533536195755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52365899085999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54835200309753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8471417427063</t>
+    <t xml:space="preserve">2.52365851402283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54835176467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84714198112488</t>
   </si>
   <si>
     <t xml:space="preserve">2.96320009231567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91134428977966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99777102470398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00270938873291</t>
+    <t xml:space="preserve">2.91134452819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99777150154114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00270915031433</t>
   </si>
   <si>
     <t xml:space="preserve">2.95826125144958</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">3.08913588523865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0990138053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12617659568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06691193580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84467172622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81257128715515</t>
+    <t xml:space="preserve">3.09901356697083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12617707252502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06691217422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84467244148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81257104873657</t>
   </si>
   <si>
     <t xml:space="preserve">2.69157338142395</t>
@@ -425,10 +425,10 @@
     <t xml:space="preserve">2.91381335258484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88665080070496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05703496932983</t>
+    <t xml:space="preserve">2.88665127754211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05703520774841</t>
   </si>
   <si>
     <t xml:space="preserve">2.98789381980896</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">2.96073126792908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97307753562927</t>
+    <t xml:space="preserve">2.97307777404785</t>
   </si>
   <si>
     <t xml:space="preserve">2.88418197631836</t>
@@ -446,40 +446,40 @@
     <t xml:space="preserve">2.91875219345093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03481101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02987194061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04468774795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99283242225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05950403213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97554659843445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9508535861969</t>
+    <t xml:space="preserve">3.0348105430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02987217903137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04468822479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99283194541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05950450897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97554683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95085382461548</t>
   </si>
   <si>
     <t xml:space="preserve">2.96813941001892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90393567085266</t>
+    <t xml:space="preserve">2.9039363861084</t>
   </si>
   <si>
     <t xml:space="preserve">2.86442756652832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87430453300476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81504058837891</t>
+    <t xml:space="preserve">2.8743040561676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81504034996033</t>
   </si>
   <si>
     <t xml:space="preserve">2.90146684646606</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">2.8668966293335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74095988273621</t>
+    <t xml:space="preserve">2.74096012115479</t>
   </si>
   <si>
     <t xml:space="preserve">2.70885896682739</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">2.82491755485535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84220337867737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89158964157104</t>
+    <t xml:space="preserve">2.84220314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8915901184082</t>
   </si>
   <si>
     <t xml:space="preserve">2.87183475494385</t>
@@ -515,94 +515,94 @@
     <t xml:space="preserve">2.90887451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76812291145325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82244849205017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85948824882507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93850708007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25211215019226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29409074783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2595202922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03234171867371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02740287780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16568493843079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52373933792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39780354499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47188282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45953607559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4792914390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49410676956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55584073066711</t>
+    <t xml:space="preserve">2.76812314987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82244825363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85948801040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93850755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25211191177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29409193992615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25952053070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03234148025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0274031162262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16568517684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5237398147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39780330657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47188305854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4595365524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47929096221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49410629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55584096908569</t>
   </si>
   <si>
     <t xml:space="preserve">3.58547210693359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57065653800964</t>
+    <t xml:space="preserve">3.57065582275391</t>
   </si>
   <si>
     <t xml:space="preserve">3.56077909469604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60028862953186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62251257896423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55830979347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72128534317017</t>
+    <t xml:space="preserve">3.60028839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62251281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55830955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72128558158875</t>
   </si>
   <si>
     <t xml:space="preserve">3.81265115737915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8570990562439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93364882469177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93117904663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97315764427185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525951385498</t>
+    <t xml:space="preserve">3.85709953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93364810943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93117952346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97315716743469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525903701782</t>
   </si>
   <si>
     <t xml:space="preserve">3.99044322967529</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">4.19539785385132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21762132644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29664087295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30651807785034</t>
+    <t xml:space="preserve">4.21762180328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29664039611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30651760101318</t>
   </si>
   <si>
     <t xml:space="preserve">4.17564296722412</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">4.31392621994019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30898714065552</t>
+    <t xml:space="preserve">4.30898761749268</t>
   </si>
   <si>
     <t xml:space="preserve">4.27935457229614</t>
@@ -653,22 +653,22 @@
     <t xml:space="preserve">4.88928031921387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95842218399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0127477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17078495025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33615016937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53616619110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34602689743042</t>
+    <t xml:space="preserve">4.95842266082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01274824142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17078447341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3361496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53616666793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34602737426758</t>
   </si>
   <si>
     <t xml:space="preserve">4.39047574996948</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.41516828536987</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62753057479858</t>
+    <t xml:space="preserve">4.62753105163574</t>
   </si>
   <si>
     <t xml:space="preserve">4.64234733581543</t>
@@ -686,34 +686,34 @@
     <t xml:space="preserve">4.71889734268188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99793243408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0423789024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10164308547974</t>
+    <t xml:space="preserve">4.99793195724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04237842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10164403915405</t>
   </si>
   <si>
     <t xml:space="preserve">5.12633657455444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95348358154297</t>
+    <t xml:space="preserve">4.95348405838013</t>
   </si>
   <si>
     <t xml:space="preserve">4.98805332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99299192428589</t>
+    <t xml:space="preserve">4.99299287796021</t>
   </si>
   <si>
     <t xml:space="preserve">5.00287055969238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04731798171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92385101318359</t>
+    <t xml:space="preserve">5.04731702804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92385149002075</t>
   </si>
   <si>
     <t xml:space="preserve">4.78062963485718</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">5.02756309509277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33869981765747</t>
+    <t xml:space="preserve">5.33869934082031</t>
   </si>
   <si>
     <t xml:space="preserve">5.34363794326782</t>
@@ -737,19 +737,19 @@
     <t xml:space="preserve">5.25474214553833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32882261276245</t>
+    <t xml:space="preserve">5.32882213592529</t>
   </si>
   <si>
     <t xml:space="preserve">5.1757230758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14609098434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18560123443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18066215515137</t>
+    <t xml:space="preserve">5.14609050750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18560075759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18066263198853</t>
   </si>
   <si>
     <t xml:space="preserve">5.13127517700195</t>
@@ -758,19 +758,19 @@
     <t xml:space="preserve">5.1362133026123</t>
   </si>
   <si>
-    <t xml:space="preserve">5.165846824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09670400619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14115285873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22511005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30412817001343</t>
+    <t xml:space="preserve">5.16584634780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09670448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14115238189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22511053085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30412864685059</t>
   </si>
   <si>
     <t xml:space="preserve">5.21029424667358</t>
@@ -785,52 +785,52 @@
     <t xml:space="preserve">4.96336078643799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93372821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07695007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07201194763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06213426589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81026268005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83248615264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74359035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78556776046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73371315002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71642780303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70654964447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69420289993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51887989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45220851898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64728593826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70408010482788</t>
+    <t xml:space="preserve">4.93372774124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07695055007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07201147079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06213331222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81026172637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83248662948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74358987808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78556823730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73371267318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71642732620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70654916763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69420337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51888036727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45220899581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64728689193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70408058166504</t>
   </si>
   <si>
     <t xml:space="preserve">4.63000106811523</t>
@@ -839,25 +839,25 @@
     <t xml:space="preserve">4.79297637939453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78803777694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23498725891113</t>
+    <t xml:space="preserve">4.78803825378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23498773574829</t>
   </si>
   <si>
     <t xml:space="preserve">4.91644287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97323846817017</t>
+    <t xml:space="preserve">4.97323799133301</t>
   </si>
   <si>
     <t xml:space="preserve">5.05225706100464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03744029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9189133644104</t>
+    <t xml:space="preserve">5.03744077682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91891241073608</t>
   </si>
   <si>
     <t xml:space="preserve">4.94854497909546</t>
@@ -866,52 +866,52 @@
     <t xml:space="preserve">5.02262449264526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76828336715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62012338638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80038499832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72383546829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68926477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66210222244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67197942733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59049129486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58308362960815</t>
+    <t xml:space="preserve">4.76828384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62012434005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80038452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72383594512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68926429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66210126876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67197895050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59049081802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.583083152771</t>
   </si>
   <si>
     <t xml:space="preserve">4.61518526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8473014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83001613616943</t>
+    <t xml:space="preserve">4.84730195999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83001661300659</t>
   </si>
   <si>
     <t xml:space="preserve">4.75346660614014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8053240776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75099754333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79544639587402</t>
+    <t xml:space="preserve">4.80532312393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75099849700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79544591903687</t>
   </si>
   <si>
     <t xml:space="preserve">4.8176703453064</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">4.78309917449951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72136545181274</t>
+    <t xml:space="preserve">4.72136640548706</t>
   </si>
   <si>
     <t xml:space="preserve">4.68432569503784</t>
@@ -929,46 +929,46 @@
     <t xml:space="preserve">4.85224008560181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77816104888916</t>
+    <t xml:space="preserve">4.77816152572632</t>
   </si>
   <si>
     <t xml:space="preserve">4.76087522506714</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55838966369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85507822036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8600378036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78564929962158</t>
+    <t xml:space="preserve">4.55839014053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85507774353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86003732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78564977645874</t>
   </si>
   <si>
     <t xml:space="preserve">4.8253231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80548620223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87243556976318</t>
+    <t xml:space="preserve">4.80548572540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87243461608887</t>
   </si>
   <si>
     <t xml:space="preserve">4.95922231674194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9988956451416</t>
+    <t xml:space="preserve">4.99889516830444</t>
   </si>
   <si>
     <t xml:space="preserve">5.19230556488037</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15263175964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17246866226196</t>
+    <t xml:space="preserve">5.15263223648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17246770858765</t>
   </si>
   <si>
     <t xml:space="preserve">5.10799884796143</t>
@@ -977,19 +977,19 @@
     <t xml:space="preserve">5.17742776870728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97409963607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97905921936035</t>
+    <t xml:space="preserve">4.97409915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97905969619751</t>
   </si>
   <si>
     <t xml:space="preserve">4.98897695541382</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03857040405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03360986709595</t>
+    <t xml:space="preserve">5.03856897354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03361034393311</t>
   </si>
   <si>
     <t xml:space="preserve">5.05840635299683</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">5.07328414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02865076065063</t>
+    <t xml:space="preserve">5.02865171432495</t>
   </si>
   <si>
     <t xml:space="preserve">5.07824325561523</t>
@@ -1007,25 +1007,25 @@
     <t xml:space="preserve">5.06336545944214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95178413391113</t>
+    <t xml:space="preserve">4.95178318023682</t>
   </si>
   <si>
     <t xml:space="preserve">4.95426273345947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86995649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26669406890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40555286407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34604072570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30636787414551</t>
+    <t xml:space="preserve">4.86995601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26669454574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40555238723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34604120254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30636739730835</t>
   </si>
   <si>
     <t xml:space="preserve">5.67334985733032</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">5.68822717666626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01553630828857</t>
+    <t xml:space="preserve">6.01553678512573</t>
   </si>
   <si>
     <t xml:space="preserve">6.19406795501709</t>
@@ -1043,106 +1043,106 @@
     <t xml:space="preserve">6.14943599700928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16431283950806</t>
+    <t xml:space="preserve">6.16431331634521</t>
   </si>
   <si>
     <t xml:space="preserve">6.07008838653564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13951635360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27341651916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61560201644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53129434585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50649976730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78421688079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70982885360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7247052192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76933765411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80405330657959</t>
+    <t xml:space="preserve">6.13951683044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27341604232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61560249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53129577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50649881362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78421545028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7098274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72470569610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76933860778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80405282974243</t>
   </si>
   <si>
     <t xml:space="preserve">6.96770763397217</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88340139389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99250364303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07681131362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.146240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18095397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4636287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31485366821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33468961715698</t>
+    <t xml:space="preserve">6.88340091705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99250268936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07681035995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14623975753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1809549331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46363019943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31485271453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33469009399414</t>
   </si>
   <si>
     <t xml:space="preserve">7.38428163528442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36444520950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51818084716797</t>
+    <t xml:space="preserve">7.36444568634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51818180084229</t>
   </si>
   <si>
     <t xml:space="preserve">7.58265018463135</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5628137588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53801870346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49338579177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4090781211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52314043045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41403675079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50330305099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42395687103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45867109298706</t>
+    <t xml:space="preserve">7.56281423568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53801727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49338483810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40907859802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52313995361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41403770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50330352783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42395639419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4586706161499</t>
   </si>
   <si>
     <t xml:space="preserve">7.41899633407593</t>
@@ -1151,19 +1151,19 @@
     <t xml:space="preserve">7.30989408493042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37932348251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93795251846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05697250366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02225923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1412787437439</t>
+    <t xml:space="preserve">7.37932300567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93795204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05697298049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02225875854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14128065109253</t>
   </si>
   <si>
     <t xml:space="preserve">7.34956741333008</t>
@@ -1172,16 +1172,16 @@
     <t xml:space="preserve">7.3594856262207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51322031021118</t>
+    <t xml:space="preserve">7.51322221755981</t>
   </si>
   <si>
     <t xml:space="preserve">7.76614141464233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73142623901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66199827194214</t>
+    <t xml:space="preserve">7.73142671585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66199779510498</t>
   </si>
   <si>
     <t xml:space="preserve">7.45371055603027</t>
@@ -1190,58 +1190,58 @@
     <t xml:space="preserve">7.28013753890991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33964920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3743634223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25038242340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43387413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55785417556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24046325683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20079040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17103338241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15119886398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0073823928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2355055809021</t>
+    <t xml:space="preserve">7.33964776992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37436294555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25038290023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43387365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55785512924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24046516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2007908821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17103481292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.151198387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00738143920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23550415039062</t>
   </si>
   <si>
     <t xml:space="preserve">7.19087219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53305864334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52810001373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50826263427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43883466720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44875288009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63720226287842</t>
+    <t xml:space="preserve">7.53305912017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52809953689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50826215744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43883323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44875192642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63720178604126</t>
   </si>
   <si>
     <t xml:space="preserve">7.6520791053772</t>
@@ -1250,25 +1250,25 @@
     <t xml:space="preserve">7.64216041564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69175386428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67191553115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297590255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39419984817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71159076690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35629081726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88692665100098</t>
+    <t xml:space="preserve">7.69175338745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67191648483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297685623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39420032501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71159029006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35628986358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88692474365234</t>
   </si>
   <si>
     <t xml:space="preserve">8.98115062713623</t>
@@ -1277,10 +1277,10 @@
     <t xml:space="preserve">9.15968322753906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21423530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42252254486084</t>
+    <t xml:space="preserve">9.21423435211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42252159118652</t>
   </si>
   <si>
     <t xml:space="preserve">9.48699188232422</t>
@@ -1289,31 +1289,31 @@
     <t xml:space="preserve">9.69032001495361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28862285614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32829856872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50186920166016</t>
+    <t xml:space="preserve">9.28862380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32829666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50187015533447</t>
   </si>
   <si>
     <t xml:space="preserve">9.69528007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76470947265625</t>
+    <t xml:space="preserve">9.76470851898193</t>
   </si>
   <si>
     <t xml:space="preserve">9.70519733428955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64072799682617</t>
+    <t xml:space="preserve">9.64072704315186</t>
   </si>
   <si>
     <t xml:space="preserve">9.63080883026123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.819260597229</t>
+    <t xml:space="preserve">9.81926155090332</t>
   </si>
   <si>
     <t xml:space="preserve">9.84108066558838</t>
@@ -1325,34 +1325,34 @@
     <t xml:space="preserve">9.65163898468018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53856754302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31937026977539</t>
+    <t xml:space="preserve">9.5385684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31936836242676</t>
   </si>
   <si>
     <t xml:space="preserve">8.7579870223999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35110950469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89982032775879</t>
+    <t xml:space="preserve">9.35110855102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89982128143311</t>
   </si>
   <si>
     <t xml:space="preserve">8.63698196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75302600860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57548809051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77782344818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82741641998291</t>
+    <t xml:space="preserve">8.75302696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57548713684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77782249450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82741451263428</t>
   </si>
   <si>
     <t xml:space="preserve">9.0039644241333</t>
@@ -1364,37 +1364,37 @@
     <t xml:space="preserve">8.94643592834473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98908615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80956172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73814868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69054222106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80559349060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71434593200684</t>
+    <t xml:space="preserve">8.98908710479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80956363677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73814964294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6905403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8055944442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71434497833252</t>
   </si>
   <si>
     <t xml:space="preserve">8.47431945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98930644989014</t>
+    <t xml:space="preserve">7.98930740356445</t>
   </si>
   <si>
     <t xml:space="preserve">8.01410293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46836757659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55664157867432</t>
+    <t xml:space="preserve">8.46836853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55664253234863</t>
   </si>
   <si>
     <t xml:space="preserve">8.56259250640869</t>
@@ -1403,10 +1403,10 @@
     <t xml:space="preserve">8.51597595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52787685394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53085517883301</t>
+    <t xml:space="preserve">8.52787780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53085422515869</t>
   </si>
   <si>
     <t xml:space="preserve">8.43266201019287</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">8.52589416503906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3592643737793</t>
+    <t xml:space="preserve">8.35926532745361</t>
   </si>
   <si>
     <t xml:space="preserve">8.56457710266113</t>
@@ -1430,25 +1430,25 @@
     <t xml:space="preserve">8.42175102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25115394592285</t>
+    <t xml:space="preserve">8.25115299224854</t>
   </si>
   <si>
     <t xml:space="preserve">8.1886682510376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32554244995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15791988372803</t>
+    <t xml:space="preserve">8.32554149627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15792083740234</t>
   </si>
   <si>
     <t xml:space="preserve">8.18370914459229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78278255462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73517513275146</t>
+    <t xml:space="preserve">8.78278160095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73517322540283</t>
   </si>
   <si>
     <t xml:space="preserve">9.15869045257568</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">9.07438373565674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18943977355957</t>
+    <t xml:space="preserve">9.18943881988525</t>
   </si>
   <si>
     <t xml:space="preserve">9.31342029571533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22613716125488</t>
+    <t xml:space="preserve">9.22613620758057</t>
   </si>
   <si>
     <t xml:space="preserve">9.40764427185059</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">9.4364070892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36301231384277</t>
+    <t xml:space="preserve">9.36301136016846</t>
   </si>
   <si>
     <t xml:space="preserve">9.70916652679443</t>
@@ -1484,40 +1484,40 @@
     <t xml:space="preserve">9.63180160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55840396881104</t>
+    <t xml:space="preserve">9.55840492248535</t>
   </si>
   <si>
     <t xml:space="preserve">9.7597484588623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79148864746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.686354637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41458797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20927715301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43740081787109</t>
+    <t xml:space="preserve">9.79148769378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393367767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68635272979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41458606719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20927619934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43739891052246</t>
   </si>
   <si>
     <t xml:space="preserve">9.21820259094238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51674842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53559303283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4800500869751</t>
+    <t xml:space="preserve">9.51674747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5355920791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48004913330078</t>
   </si>
   <si>
     <t xml:space="preserve">9.29556560516357</t>
@@ -1526,16 +1526,16 @@
     <t xml:space="preserve">9.3084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42946529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41756153106689</t>
+    <t xml:space="preserve">9.42946434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41756343841553</t>
   </si>
   <si>
     <t xml:space="preserve">9.36697864532471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30746936798096</t>
+    <t xml:space="preserve">9.30746841430664</t>
   </si>
   <si>
     <t xml:space="preserve">9.36797046661377</t>
@@ -1544,10 +1544,10 @@
     <t xml:space="preserve">9.19935703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43938446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59609603881836</t>
+    <t xml:space="preserve">9.4393835067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59609508514404</t>
   </si>
   <si>
     <t xml:space="preserve">9.48600101470947</t>
@@ -1556,16 +1556,16 @@
     <t xml:space="preserve">9.31143569946289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30548477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10810852050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06446552276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42748165130615</t>
+    <t xml:space="preserve">9.3054838180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1081075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06446647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42747974395752</t>
   </si>
   <si>
     <t xml:space="preserve">9.62089061737061</t>
@@ -1574,76 +1574,76 @@
     <t xml:space="preserve">9.185471534729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85221004486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87601566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86212921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13984680175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90676212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98313426971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92659950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85022735595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04462909698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87403202056885</t>
+    <t xml:space="preserve">8.85221195220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87601470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86213111877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13984775543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90676307678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98313617706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92660045623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85022830963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04462814331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87403297424316</t>
   </si>
   <si>
     <t xml:space="preserve">8.92461585998535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79666805267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7500524520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38505268096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18172454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92979669570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15296173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24123573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9555835723877</t>
+    <t xml:space="preserve">8.79666900634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75005149841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38505172729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18172550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92979526519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15296077728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24123668670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95558595657349</t>
   </si>
   <si>
     <t xml:space="preserve">8.10039329528809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10237789154053</t>
+    <t xml:space="preserve">8.10237884521484</t>
   </si>
   <si>
     <t xml:space="preserve">8.03889942169189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50506591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40687465667725</t>
+    <t xml:space="preserve">8.50506687164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40687370300293</t>
   </si>
   <si>
     <t xml:space="preserve">8.46935939788818</t>
@@ -1652,52 +1652,52 @@
     <t xml:space="preserve">8.52291965484619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26305770874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21346282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25214576721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19957733154297</t>
+    <t xml:space="preserve">8.26305675506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21346378326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25214672088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19957828521729</t>
   </si>
   <si>
     <t xml:space="preserve">8.24916934967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22239017486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33347702026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14105987548828</t>
+    <t xml:space="preserve">8.22239112854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33347606658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14105796813965</t>
   </si>
   <si>
     <t xml:space="preserve">8.01906204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21048736572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16111707687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26426887512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23947238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04804515838623</t>
+    <t xml:space="preserve">8.21048831939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1611156463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26426935195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23947334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04804611206055</t>
   </si>
   <si>
     <t xml:space="preserve">7.04209566116333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2434401512146</t>
+    <t xml:space="preserve">7.24344062805176</t>
   </si>
   <si>
     <t xml:space="preserve">7.23352098464966</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">7.20277500152588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24839878082275</t>
+    <t xml:space="preserve">7.24839925765991</t>
   </si>
   <si>
     <t xml:space="preserve">7.17500305175781</t>
@@ -1718,109 +1718,109 @@
     <t xml:space="preserve">6.97663402557373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80802011489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79909420013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01729869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12243413925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03713655471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95977067947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1859130859375</t>
+    <t xml:space="preserve">6.808021068573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79909372329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01730012893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12243509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03713703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95977115631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18591260910034</t>
   </si>
   <si>
     <t xml:space="preserve">7.43486595153809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42693042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36146831512451</t>
+    <t xml:space="preserve">7.42693090438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36146926879883</t>
   </si>
   <si>
     <t xml:space="preserve">7.22062683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26823711395264</t>
+    <t xml:space="preserve">7.26823568344116</t>
   </si>
   <si>
     <t xml:space="preserve">7.39320802688599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2265796661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21566820144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.167067527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4824743270874</t>
+    <t xml:space="preserve">7.22657918930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21566915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16706705093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48247480392456</t>
   </si>
   <si>
     <t xml:space="preserve">7.40610218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42792272567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45767974853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48346614837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61934852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73341083526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66001558303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70266437530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66795015335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51024627685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68282699584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6937370300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64017772674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57769250869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52016258239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34460783004761</t>
+    <t xml:space="preserve">7.42792224884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.457679271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48346662521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61934900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73341178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66001653671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70266342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66794919967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51024532318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68282556533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69373750686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64017724990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57769155502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52016401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34460735321045</t>
   </si>
   <si>
     <t xml:space="preserve">7.42197179794312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01035642623901</t>
+    <t xml:space="preserve">7.01035737991333</t>
   </si>
   <si>
     <t xml:space="preserve">6.96274852752686</t>
@@ -1832,19 +1832,19 @@
     <t xml:space="preserve">6.94588613510132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17797756195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87744903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82587242126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66618633270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86455488204956</t>
+    <t xml:space="preserve">7.17797803878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87744951248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82587337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66618680953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86455583572388</t>
   </si>
   <si>
     <t xml:space="preserve">6.95183849334717</t>
@@ -1853,160 +1853,160 @@
     <t xml:space="preserve">6.78024864196777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04705429077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81992197036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6701545715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75247621536255</t>
+    <t xml:space="preserve">7.04705476760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81992244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67015361785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75247573852539</t>
   </si>
   <si>
     <t xml:space="preserve">7.02920055389404</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1125168800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09664678573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26129245758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28708171844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08672761917114</t>
+    <t xml:space="preserve">7.11251592636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09664630889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26129293441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28708028793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0867280960083</t>
   </si>
   <si>
     <t xml:space="preserve">7.30394172668457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23054695129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13334512710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12838554382324</t>
+    <t xml:space="preserve">7.23054647445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13334465026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1283860206604</t>
   </si>
   <si>
     <t xml:space="preserve">6.94291114807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01234102249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93001747131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99052000045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33865594863892</t>
+    <t xml:space="preserve">7.01233959197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93001699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99051952362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33865737915039</t>
   </si>
   <si>
     <t xml:space="preserve">7.34758329391479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30493354797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49635934829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34857511520386</t>
+    <t xml:space="preserve">7.30493402481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49635982513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34857559204102</t>
   </si>
   <si>
     <t xml:space="preserve">7.23451375961304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86554670333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82488107681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61064195632935</t>
+    <t xml:space="preserve">6.86554574966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82488203048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6106424331665</t>
   </si>
   <si>
     <t xml:space="preserve">6.78322410583496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9161319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92208242416382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86852216720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82884883880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82289838790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72272109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50848245620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25754594802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28928565979004</t>
+    <t xml:space="preserve">6.91613101959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92208194732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86852312088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82884931564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82289791107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72272157669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50848340988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25754642486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28928661346436</t>
   </si>
   <si>
     <t xml:space="preserve">6.23175859451294</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15737104415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50253295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55113172531128</t>
+    <t xml:space="preserve">6.15736961364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50253248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5511326789856</t>
   </si>
   <si>
     <t xml:space="preserve">6.62849712371826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87645673751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01134824752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1601243019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24443197250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2107081413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32080459594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10557413101196</t>
+    <t xml:space="preserve">6.87645721435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01134777069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16012573242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24443101882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21070909500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32080411911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10557270050049</t>
   </si>
   <si>
     <t xml:space="preserve">7.26724529266357</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18690538406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18987989425659</t>
+    <t xml:space="preserve">7.18690490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18988084793091</t>
   </si>
   <si>
     <t xml:space="preserve">7.28509712219238</t>
@@ -2015,46 +2015,46 @@
     <t xml:space="preserve">7.39816761016846</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47354698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52710819244385</t>
+    <t xml:space="preserve">7.47354793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52710723876953</t>
   </si>
   <si>
     <t xml:space="preserve">6.63543891906738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44301986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41822528839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39739656448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4975733757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40731430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4598822593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44897413253784</t>
+    <t xml:space="preserve">6.44302082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4182243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39739608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49757289886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40731477737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45988321304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44897317886353</t>
   </si>
   <si>
     <t xml:space="preserve">6.45194864273071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57692050933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50153970718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51145887374878</t>
+    <t xml:space="preserve">6.57692003250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.501540184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51145839691162</t>
   </si>
   <si>
     <t xml:space="preserve">6.54617309570312</t>
@@ -2063,37 +2063,37 @@
     <t xml:space="preserve">6.4559154510498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43806266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41227531433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36268186569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41524982452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64932441711426</t>
+    <t xml:space="preserve">6.43806123733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41227436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3626823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41525030136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64932489395142</t>
   </si>
   <si>
     <t xml:space="preserve">6.32697629928589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36665010452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35871362686157</t>
+    <t xml:space="preserve">6.36664962768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35871410369873</t>
   </si>
   <si>
     <t xml:space="preserve">6.30416297912598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25854015350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26548051834106</t>
+    <t xml:space="preserve">6.25853872299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26548004150391</t>
   </si>
   <si>
     <t xml:space="preserve">6.32003259658813</t>
@@ -2102,88 +2102,88 @@
     <t xml:space="preserve">6.63643074035645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46980142593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49658060073853</t>
+    <t xml:space="preserve">6.46980094909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49658107757568</t>
   </si>
   <si>
     <t xml:space="preserve">6.33590221405029</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46385049819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49162149429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66122722625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52633666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58188056945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73958253860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80603647232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80901145935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81000423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93894338607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86157941818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89133453369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89232730865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04308795928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09367227554321</t>
+    <t xml:space="preserve">6.46385145187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49162244796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66122770309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52633619308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58188009262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73958301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80603694915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80901288986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81000280380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9389443397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86157989501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89133405685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89232778549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04308700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09367275238037</t>
   </si>
   <si>
     <t xml:space="preserve">7.16607570648193</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29303121566772</t>
+    <t xml:space="preserve">7.29303169250488</t>
   </si>
   <si>
     <t xml:space="preserve">7.28431129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20211410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14384794235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20939874649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19171047210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14488840103149</t>
+    <t xml:space="preserve">7.20211315155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14384746551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.209397315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19170999526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14488983154297</t>
   </si>
   <si>
     <t xml:space="preserve">7.04916667938232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37379121780396</t>
+    <t xml:space="preserve">7.3737907409668</t>
   </si>
   <si>
     <t xml:space="preserve">7.11263513565063</t>
@@ -2192,142 +2192,142 @@
     <t xml:space="preserve">7.07205581665039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80673742294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73806619644165</t>
+    <t xml:space="preserve">6.80673885345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73806667327881</t>
   </si>
   <si>
     <t xml:space="preserve">6.61112928390503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71309518814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81402015686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88997316360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95448350906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93350172042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88365459442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82685041427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62166213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64021015167236</t>
+    <t xml:space="preserve">6.71309471130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81401920318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88997459411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95448303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93350124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88365411758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82684946060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62166261672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64021062850952</t>
   </si>
   <si>
     <t xml:space="preserve">7.16999053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10623073577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01928615570068</t>
+    <t xml:space="preserve">7.10623121261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.019287109375</t>
   </si>
   <si>
     <t xml:space="preserve">6.96132373809814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62977647781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59268188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84771728515625</t>
+    <t xml:space="preserve">6.62977695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59268140792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84771680831909</t>
   </si>
   <si>
     <t xml:space="preserve">6.78163909912109</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78743505477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76424980163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88133573532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94625377655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83728313446045</t>
+    <t xml:space="preserve">6.78743410110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76425123214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88133525848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94625329971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83728408813477</t>
   </si>
   <si>
     <t xml:space="preserve">6.89524555206299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86278676986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92422771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98566913604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06449699401855</t>
+    <t xml:space="preserve">6.86278629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92422676086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98566865921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0644965171814</t>
   </si>
   <si>
     <t xml:space="preserve">7.15028142929077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13521194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14216804504395</t>
+    <t xml:space="preserve">7.13521146774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14216709136963</t>
   </si>
   <si>
     <t xml:space="preserve">7.02160501480103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03319692611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08072662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10970878601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15723705291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13057518005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33112668991089</t>
+    <t xml:space="preserve">7.03319835662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08072710037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10970830917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1572380065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13057470321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33112573623657</t>
   </si>
   <si>
     <t xml:space="preserve">7.35315132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32532930374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28939342498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20940446853638</t>
+    <t xml:space="preserve">7.3253288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28939294815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20940494537354</t>
   </si>
   <si>
     <t xml:space="preserve">7.20476722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28707504272461</t>
+    <t xml:space="preserve">7.28707408905029</t>
   </si>
   <si>
     <t xml:space="preserve">7.28591442108154</t>
@@ -2339,40 +2339,40 @@
     <t xml:space="preserve">7.07493114471436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95900535583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17578458786011</t>
+    <t xml:space="preserve">6.95900583267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17578554153442</t>
   </si>
   <si>
     <t xml:space="preserve">7.3114185333252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19433307647705</t>
+    <t xml:space="preserve">7.19433450698853</t>
   </si>
   <si>
     <t xml:space="preserve">7.08768320083618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97639417648315</t>
+    <t xml:space="preserve">6.97639322280884</t>
   </si>
   <si>
     <t xml:space="preserve">6.99841928482056</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76541042327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81873559951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86858320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72715377807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72367763519287</t>
+    <t xml:space="preserve">6.76540994644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81873607635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8685827255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72715520858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72367668151855</t>
   </si>
   <si>
     <t xml:space="preserve">6.82569074630737</t>
@@ -2381,64 +2381,64 @@
     <t xml:space="preserve">6.58572483062744</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40719985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52660417556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4663233757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194341659546</t>
+    <t xml:space="preserve">6.4072003364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52660322189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46632242202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194389343262</t>
   </si>
   <si>
     <t xml:space="preserve">6.6900577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54515075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.635573387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74454259872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80482482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86162805557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86394691467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08304452896118</t>
+    <t xml:space="preserve">6.5451512336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63557291030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74454355239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8048243522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86162853240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86394739151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08304595947266</t>
   </si>
   <si>
     <t xml:space="preserve">7.29055213928223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30562162399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37285900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28243732452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28127765655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29287052154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18158388137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18737840652466</t>
+    <t xml:space="preserve">7.30562257766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37285947799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28243684768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28127813339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29287099838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18158197402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18737888336182</t>
   </si>
   <si>
     <t xml:space="preserve">7.07029342651367</t>
@@ -2447,16 +2447,16 @@
     <t xml:space="preserve">6.92654657363892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83148813247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84539890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87785768508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525850296021</t>
+    <t xml:space="preserve">6.83148765563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84539794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87785720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525707244873</t>
   </si>
   <si>
     <t xml:space="preserve">6.63093566894531</t>
@@ -2465,43 +2465,43 @@
     <t xml:space="preserve">6.54051399230957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53239917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5752911567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50921440124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54862928390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73410940170288</t>
+    <t xml:space="preserve">6.53239965438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57529163360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50921392440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54862976074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73410987854004</t>
   </si>
   <si>
     <t xml:space="preserve">6.87553882598877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91843128204346</t>
+    <t xml:space="preserve">6.91843175888062</t>
   </si>
   <si>
     <t xml:space="preserve">7.07145214080811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03899383544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87206125259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95668601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90915632247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87321996688843</t>
+    <t xml:space="preserve">7.03899431228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87206172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95668697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90915679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87322044372559</t>
   </si>
   <si>
     <t xml:space="preserve">6.86742401123047</t>
@@ -2510,22 +2510,22 @@
     <t xml:space="preserve">6.90336036682129</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81062078475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45980310440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07304954528809</t>
+    <t xml:space="preserve">6.81062030792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45980262756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07304859161377</t>
   </si>
   <si>
     <t xml:space="preserve">8.12057876586914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32808494567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37561321258545</t>
+    <t xml:space="preserve">8.32808589935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37561511993408</t>
   </si>
   <si>
     <t xml:space="preserve">8.38025093078613</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">8.41039180755615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51124668121338</t>
+    <t xml:space="preserve">8.5112476348877</t>
   </si>
   <si>
     <t xml:space="preserve">8.41386985778809</t>
@@ -2549,82 +2549,82 @@
     <t xml:space="preserve">8.40807437896729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42198467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18433666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19245338439941</t>
+    <t xml:space="preserve">8.42198371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1843376159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19245147705078</t>
   </si>
   <si>
     <t xml:space="preserve">8.09623432159424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79019117355347</t>
+    <t xml:space="preserve">7.79019212722778</t>
   </si>
   <si>
     <t xml:space="preserve">7.74613952636719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88177251815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87713479995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89104604721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82033109664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77859973907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70440530776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65224075317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74845790863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68238067626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68701648712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62093925476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57920694351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46328067779541</t>
+    <t xml:space="preserve">7.88177299499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87713527679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89104557037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82033205032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77859830856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70440578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65224123001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74845695495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68238115310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68701696395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62093830108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5792064666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46328163146973</t>
   </si>
   <si>
     <t xml:space="preserve">7.64760255813599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72411346435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80757904052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88524961471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88409090042114</t>
+    <t xml:space="preserve">7.72411251068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8075795173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88525009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8840913772583</t>
   </si>
   <si>
     <t xml:space="preserve">7.91191244125366</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82844591140747</t>
+    <t xml:space="preserve">7.82844686508179</t>
   </si>
   <si>
     <t xml:space="preserve">7.78439474105835</t>
@@ -2633,16 +2633,16 @@
     <t xml:space="preserve">7.7415018081665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58036470413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47719144821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51197004318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41691064834595</t>
+    <t xml:space="preserve">7.58036613464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47719192504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51196908950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41691160202026</t>
   </si>
   <si>
     <t xml:space="preserve">7.43777751922607</t>
@@ -2651,37 +2651,37 @@
     <t xml:space="preserve">7.43661880493164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39024782180786</t>
+    <t xml:space="preserve">7.39024686813354</t>
   </si>
   <si>
     <t xml:space="preserve">7.36822271347046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22911071777344</t>
+    <t xml:space="preserve">7.22911214828491</t>
   </si>
   <si>
     <t xml:space="preserve">7.21867799758911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2059268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22099733352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14680528640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9821891784668</t>
+    <t xml:space="preserve">7.20592546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22099685668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14680433273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98218965530396</t>
   </si>
   <si>
     <t xml:space="preserve">7.03783464431763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96364259719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03087854385376</t>
+    <t xml:space="preserve">6.96364164352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03087949752808</t>
   </si>
   <si>
     <t xml:space="preserve">6.91263484954834</t>
@@ -2690,43 +2690,43 @@
     <t xml:space="preserve">6.80018711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85235404968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19317436218262</t>
+    <t xml:space="preserve">6.85235357284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19317483901978</t>
   </si>
   <si>
     <t xml:space="preserve">7.07608985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03203821182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29402923583984</t>
+    <t xml:space="preserve">7.03203868865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29403066635132</t>
   </si>
   <si>
     <t xml:space="preserve">7.10739040374756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14100790023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11086702346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1155047416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00189733505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57297277450562</t>
+    <t xml:space="preserve">7.1410083770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11086750030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11550521850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00189828872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57297325134277</t>
   </si>
   <si>
     <t xml:space="preserve">6.52544355392456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70165061950684</t>
+    <t xml:space="preserve">6.70165157318115</t>
   </si>
   <si>
     <t xml:space="preserve">6.51616954803467</t>
@@ -2735,28 +2735,28 @@
     <t xml:space="preserve">6.27620363235474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34112310409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37126398086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28431940078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.096519947052</t>
+    <t xml:space="preserve">6.3411226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37126302719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2843189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09651947021484</t>
   </si>
   <si>
     <t xml:space="preserve">5.438063621521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40676307678223</t>
+    <t xml:space="preserve">5.40676259994507</t>
   </si>
   <si>
     <t xml:space="preserve">5.51921033859253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53326463699341</t>
+    <t xml:space="preserve">4.53326511383057</t>
   </si>
   <si>
     <t xml:space="preserve">4.85785627365112</t>
@@ -2765,40 +2765,40 @@
     <t xml:space="preserve">4.15534782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97914123535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54731917381287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36531543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56122994422913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40994787216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84872460365295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96117329597473</t>
+    <t xml:space="preserve">3.9791419506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54731941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36531567573547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56123042106628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40994739532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84872484207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96117281913757</t>
   </si>
   <si>
     <t xml:space="preserve">3.99421167373657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75482606887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65744829177856</t>
+    <t xml:space="preserve">3.75482487678528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65744805335999</t>
   </si>
   <si>
     <t xml:space="preserve">3.80931043624878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66498351097107</t>
+    <t xml:space="preserve">3.66498398780823</t>
   </si>
   <si>
     <t xml:space="preserve">3.64295721054077</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">3.83481431007385</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08289432525635</t>
+    <t xml:space="preserve">4.08289480209351</t>
   </si>
   <si>
     <t xml:space="preserve">4.12636661529541</t>
@@ -2822,28 +2822,28 @@
     <t xml:space="preserve">4.32401990890503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10434055328369</t>
+    <t xml:space="preserve">4.10434007644653</t>
   </si>
   <si>
     <t xml:space="preserve">4.12057018280029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24403047561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30663061141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11419486999512</t>
+    <t xml:space="preserve">4.24403142929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30663013458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11419439315796</t>
   </si>
   <si>
     <t xml:space="preserve">4.20229768753052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35010242462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26026010513306</t>
+    <t xml:space="preserve">4.35010194778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26026105880737</t>
   </si>
   <si>
     <t xml:space="preserve">4.46197128295898</t>
@@ -2852,28 +2852,28 @@
     <t xml:space="preserve">4.57383871078491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74135160446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64629220962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38430118560791</t>
+    <t xml:space="preserve">4.74135208129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64629173278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38430070877075</t>
   </si>
   <si>
     <t xml:space="preserve">4.44863939285278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42139720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40516805648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50370359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42429447174072</t>
+    <t xml:space="preserve">4.42139673233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40516757965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50370407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42429494857788</t>
   </si>
   <si>
     <t xml:space="preserve">4.40053081512451</t>
@@ -2888,58 +2888,58 @@
     <t xml:space="preserve">4.17505502700806</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51703548431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31242752075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25388383865356</t>
+    <t xml:space="preserve">4.51703500747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31242704391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25388431549072</t>
   </si>
   <si>
     <t xml:space="preserve">4.29851627349854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59934282302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72859954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78192520141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6033992767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7651162147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83293199539185</t>
+    <t xml:space="preserve">4.59934186935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72859907150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78192472457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60340023040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76511573791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83293151855469</t>
   </si>
   <si>
     <t xml:space="preserve">5.08217191696167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04449558258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39749002456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45255374908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21316814422607</t>
+    <t xml:space="preserve">5.04449605941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39748907089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45255327224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21316766738892</t>
   </si>
   <si>
     <t xml:space="preserve">5.0723180770874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68164920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74888610839844</t>
+    <t xml:space="preserve">4.68165016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7488865852356</t>
   </si>
   <si>
     <t xml:space="preserve">4.7506251335144</t>
@@ -2948,22 +2948,22 @@
     <t xml:space="preserve">4.88625812530518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86771011352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85263919830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89958906173706</t>
+    <t xml:space="preserve">4.86770963668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85263967514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8995885848999</t>
   </si>
   <si>
     <t xml:space="preserve">4.96624708175659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25374221801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02246999740601</t>
+    <t xml:space="preserve">5.25374174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02247047424316</t>
   </si>
   <si>
     <t xml:space="preserve">5.09550285339355</t>
@@ -2972,10 +2972,10 @@
     <t xml:space="preserve">5.00508165359497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11694955825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18418598175049</t>
+    <t xml:space="preserve">5.1169490814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18418645858765</t>
   </si>
   <si>
     <t xml:space="preserve">5.09260559082031</t>
@@ -2984,13 +2984,13 @@
     <t xml:space="preserve">5.21606588363647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15868186950684</t>
+    <t xml:space="preserve">5.15868234634399</t>
   </si>
   <si>
     <t xml:space="preserve">5.21896409988403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20679187774658</t>
+    <t xml:space="preserve">5.20679140090942</t>
   </si>
   <si>
     <t xml:space="preserve">5.09840154647827</t>
@@ -2999,16 +2999,16 @@
     <t xml:space="preserve">5.00276279449463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11984872817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24910449981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20447301864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25721883773804</t>
+    <t xml:space="preserve">5.11984825134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24910497665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2044734954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2572193145752</t>
   </si>
   <si>
     <t xml:space="preserve">5.31692123413086</t>
@@ -3020,28 +3020,28 @@
     <t xml:space="preserve">5.34184503555298</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35401725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30822706222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3412652015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26069688796997</t>
+    <t xml:space="preserve">5.35401678085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30822658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34126567840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26069641113281</t>
   </si>
   <si>
     <t xml:space="preserve">5.25895833969116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3748836517334</t>
+    <t xml:space="preserve">5.37488412857056</t>
   </si>
   <si>
     <t xml:space="preserve">5.30764722824097</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99638652801514</t>
+    <t xml:space="preserve">4.99638605117798</t>
   </si>
   <si>
     <t xml:space="preserve">5.23693227767944</t>
@@ -3050,16 +3050,16 @@
     <t xml:space="preserve">5.44270133972168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44733667373657</t>
+    <t xml:space="preserve">5.44733715057373</t>
   </si>
   <si>
     <t xml:space="preserve">5.38937425613403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38183879852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47457885742188</t>
+    <t xml:space="preserve">5.38183975219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47457933425903</t>
   </si>
   <si>
     <t xml:space="preserve">5.76323366165161</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">5.65716171264648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61658811569214</t>
+    <t xml:space="preserve">5.61658763885498</t>
   </si>
   <si>
     <t xml:space="preserve">5.59340381622314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56847953796387</t>
+    <t xml:space="preserve">5.56848001480103</t>
   </si>
   <si>
     <t xml:space="preserve">5.58065176010132</t>
@@ -3086,19 +3086,19 @@
     <t xml:space="preserve">5.47631931304932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40618419647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5800724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51631307601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54703283309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47747850418091</t>
+    <t xml:space="preserve">5.40618371963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58007287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51631259918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54703330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47747802734375</t>
   </si>
   <si>
     <t xml:space="preserve">5.45719051361084</t>
@@ -3110,43 +3110,43 @@
     <t xml:space="preserve">5.28736019134521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31750106811523</t>
+    <t xml:space="preserve">5.31750059127808</t>
   </si>
   <si>
     <t xml:space="preserve">5.37836217880249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46646499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58470821380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57079744338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57137727737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73019599914551</t>
+    <t xml:space="preserve">5.46646451950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58470916748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57079792022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57137775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73019647598267</t>
   </si>
   <si>
     <t xml:space="preserve">5.74642467498779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78641939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30750465393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26693058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23910903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01537227630615</t>
+    <t xml:space="preserve">5.78641891479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30750417709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.266930103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23910856246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01537179946899</t>
   </si>
   <si>
     <t xml:space="preserve">5.75975608825684</t>
@@ -3155,28 +3155,28 @@
     <t xml:space="preserve">5.92263126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02232694625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01189422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92958641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16491556167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02116870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06753826141357</t>
+    <t xml:space="preserve">6.02232789993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01189517974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92958688735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16491508483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02116823196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06753778457642</t>
   </si>
   <si>
     <t xml:space="preserve">5.99914216995239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07681274414062</t>
+    <t xml:space="preserve">6.07681322097778</t>
   </si>
   <si>
     <t xml:space="preserve">6.18578290939331</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">6.1046347618103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16375684738159</t>
+    <t xml:space="preserve">6.16375637054443</t>
   </si>
   <si>
     <t xml:space="preserve">6.06058263778687</t>
@@ -3209,13 +3209,13 @@
     <t xml:space="preserve">6.22867488861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24722194671631</t>
+    <t xml:space="preserve">6.24722242355347</t>
   </si>
   <si>
     <t xml:space="preserve">6.20548915863037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35735321044922</t>
+    <t xml:space="preserve">6.35735130310059</t>
   </si>
   <si>
     <t xml:space="preserve">6.43386268615723</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">6.48023366928101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37242317199707</t>
+    <t xml:space="preserve">6.37242221832275</t>
   </si>
   <si>
     <t xml:space="preserve">6.12550115585327</t>
@@ -3233,19 +3233,19 @@
     <t xml:space="preserve">6.12318277359009</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11043167114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27156686782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3793773651123</t>
+    <t xml:space="preserve">6.11043071746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27156734466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37937784194946</t>
   </si>
   <si>
     <t xml:space="preserve">6.47443723678589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51269197463989</t>
+    <t xml:space="preserve">6.51269292831421</t>
   </si>
   <si>
     <t xml:space="preserve">6.91031694412231</t>
@@ -3254,55 +3254,55 @@
     <t xml:space="preserve">6.99146461486816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07840824127197</t>
+    <t xml:space="preserve">7.07840871810913</t>
   </si>
   <si>
     <t xml:space="preserve">7.29750776290894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31837368011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34851551055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5003776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46560001373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58963966369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64180612564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58616161346436</t>
+    <t xml:space="preserve">7.3183741569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34851503372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50037717819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46559906005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705104827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58964061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64180660247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58616065979004</t>
   </si>
   <si>
     <t xml:space="preserve">7.66615152359009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57341051101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66731023788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63948678970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66846990585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85395002365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80294227600098</t>
+    <t xml:space="preserve">7.573410987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66730928421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63948774337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66846799850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85395050048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80294275283813</t>
   </si>
   <si>
     <t xml:space="preserve">7.77048301696777</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">8.01624584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90611600875854</t>
+    <t xml:space="preserve">7.9061164855957</t>
   </si>
   <si>
     <t xml:space="preserve">8.01044940948486</t>
@@ -3326,10 +3326,10 @@
     <t xml:space="preserve">8.29678440093994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.348952293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42082405090332</t>
+    <t xml:space="preserve">8.34895133972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42082595825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.25968933105469</t>
@@ -3338,10 +3338,10 @@
     <t xml:space="preserve">8.46139907836914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51588439941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57036972045898</t>
+    <t xml:space="preserve">8.51588535308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57036876678467</t>
   </si>
   <si>
     <t xml:space="preserve">8.51356601715088</t>
@@ -3350,19 +3350,19 @@
     <t xml:space="preserve">8.49733543395996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62485504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60166931152344</t>
+    <t xml:space="preserve">8.62485408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60166835784912</t>
   </si>
   <si>
     <t xml:space="preserve">8.57152843475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41271114349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33504104614258</t>
+    <t xml:space="preserve">8.41271018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33503913879395</t>
   </si>
   <si>
     <t xml:space="preserve">8.50545120239258</t>
@@ -3371,28 +3371,28 @@
     <t xml:space="preserve">8.46951389312744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78281116485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40054130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27200603485107</t>
+    <t xml:space="preserve">8.78281021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40054321289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27200698852539</t>
   </si>
   <si>
     <t xml:space="preserve">9.32146167755127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11963272094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84830284118652</t>
+    <t xml:space="preserve">9.1196346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84830379486084</t>
   </si>
   <si>
     <t xml:space="preserve">8.43663024902344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60236835479736</t>
+    <t xml:space="preserve">8.60236930847168</t>
   </si>
   <si>
     <t xml:space="preserve">8.30564308166504</t>
@@ -3401,55 +3401,55 @@
     <t xml:space="preserve">8.49945068359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37380981445312</t>
+    <t xml:space="preserve">8.37381076812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.42460060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.681227684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69726753234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76142501831055</t>
+    <t xml:space="preserve">8.68122863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69726943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76142406463623</t>
   </si>
   <si>
     <t xml:space="preserve">8.93117332458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08889198303223</t>
+    <t xml:space="preserve">9.08889293670654</t>
   </si>
   <si>
     <t xml:space="preserve">9.01805114746094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84295749664307</t>
+    <t xml:space="preserve">8.84295654296875</t>
   </si>
   <si>
     <t xml:space="preserve">8.79483890533447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86567878723145</t>
+    <t xml:space="preserve">8.86567974090576</t>
   </si>
   <si>
     <t xml:space="preserve">8.95790481567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02206230163574</t>
+    <t xml:space="preserve">9.02206134796143</t>
   </si>
   <si>
     <t xml:space="preserve">8.82825469970703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87770843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94186496734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82424545288086</t>
+    <t xml:space="preserve">8.87770938873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94186592102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82424449920654</t>
   </si>
   <si>
     <t xml:space="preserve">8.86968994140625</t>
@@ -3458,19 +3458,19 @@
     <t xml:space="preserve">9.07552623748779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06082248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97795391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30542182922363</t>
+    <t xml:space="preserve">9.06082344055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97795486450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30542278289795</t>
   </si>
   <si>
     <t xml:space="preserve">9.28537178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26799583435059</t>
+    <t xml:space="preserve">9.2679967880249</t>
   </si>
   <si>
     <t xml:space="preserve">9.25061988830566</t>
@@ -3482,16 +3482,16 @@
     <t xml:space="preserve">9.6796703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85610198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0579290390015</t>
+    <t xml:space="preserve">9.85610103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0579280853271</t>
   </si>
   <si>
     <t xml:space="preserve">10.1755485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3158931732178</t>
+    <t xml:space="preserve">10.3158922195435</t>
   </si>
   <si>
     <t xml:space="preserve">10.602707862854</t>
@@ -3500,10 +3500,10 @@
     <t xml:space="preserve">10.5399112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6655054092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.983772277832</t>
+    <t xml:space="preserve">10.6655044555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9837713241577</t>
   </si>
   <si>
     <t xml:space="preserve">10.596999168396</t>
@@ -3512,34 +3512,34 @@
     <t xml:space="preserve">10.4785413742065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1288757324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1374397277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2801599502563</t>
+    <t xml:space="preserve">10.1288747787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1374387741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2801609039307</t>
   </si>
   <si>
     <t xml:space="preserve">10.4457149505615</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4628410339355</t>
+    <t xml:space="preserve">10.4628419876099</t>
   </si>
   <si>
     <t xml:space="preserve">10.7753992080688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7639808654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8010892868042</t>
+    <t xml:space="preserve">10.7639818191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8010902404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.912410736084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9109830856323</t>
+    <t xml:space="preserve">10.9109840393066</t>
   </si>
   <si>
     <t xml:space="preserve">10.652660369873</t>
@@ -3548,22 +3548,22 @@
     <t xml:space="preserve">10.5613193511963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6597967147827</t>
+    <t xml:space="preserve">10.6597957611084</t>
   </si>
   <si>
     <t xml:space="preserve">10.8082256317139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7397193908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7340097427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8910045623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7816705703735</t>
+    <t xml:space="preserve">10.7397203445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7340106964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8910036087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7816715240479</t>
   </si>
   <si>
     <t xml:space="preserve">10.3457975387573</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">10.4551305770874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4813709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4886598587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4667930603027</t>
+    <t xml:space="preserve">10.481369972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4886589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4667921066284</t>
   </si>
   <si>
     <t xml:space="preserve">10.4288902282715</t>
@@ -3587,16 +3587,16 @@
     <t xml:space="preserve">10.4901161193848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.09068775177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0761108398438</t>
+    <t xml:space="preserve">10.0906867980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0761098861694</t>
   </si>
   <si>
     <t xml:space="preserve">10.2204294204712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1227588653564</t>
+    <t xml:space="preserve">10.1227579116821</t>
   </si>
   <si>
     <t xml:space="preserve">10.8312349319458</t>
@@ -3605,22 +3605,22 @@
     <t xml:space="preserve">10.8705940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0061674118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6869144439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7306489944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6781692504883</t>
+    <t xml:space="preserve">11.0061683654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.686915397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7306480407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.678168296814</t>
   </si>
   <si>
     <t xml:space="preserve">10.8283195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0047082901001</t>
+    <t xml:space="preserve">11.0047092437744</t>
   </si>
   <si>
     <t xml:space="preserve">11.0003366470337</t>
@@ -3629,16 +3629,16 @@
     <t xml:space="preserve">10.7364797592163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9376525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1636066436768</t>
+    <t xml:space="preserve">10.9376516342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1636056900024</t>
   </si>
   <si>
     <t xml:space="preserve">11.2160863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2787704467773</t>
+    <t xml:space="preserve">11.2787714004517</t>
   </si>
   <si>
     <t xml:space="preserve">11.2583618164062</t>
@@ -3647,22 +3647,22 @@
     <t xml:space="preserve">11.7190160751343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739426612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8502168655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9143581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.033896446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1709260940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5120449066162</t>
+    <t xml:space="preserve">11.7394275665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8502159118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9143590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0338945388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1709251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5120439529419</t>
   </si>
   <si>
     <t xml:space="preserve">12.7219638824463</t>
@@ -3671,10 +3671,10 @@
     <t xml:space="preserve">12.7379989624023</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5601511001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3910503387451</t>
+    <t xml:space="preserve">12.560152053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3910493850708</t>
   </si>
   <si>
     <t xml:space="preserve">12.5003824234009</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">12.3181610107422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3604364395142</t>
+    <t xml:space="preserve">12.3604373931885</t>
   </si>
   <si>
     <t xml:space="preserve">12.0003681182861</t>
@@ -3698,22 +3698,22 @@
     <t xml:space="preserve">12.4056282043457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3808450698853</t>
+    <t xml:space="preserve">12.3808441162109</t>
   </si>
   <si>
     <t xml:space="preserve">12.3560628890991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.385217666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.436240196228</t>
+    <t xml:space="preserve">12.3852186203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4362392425537</t>
   </si>
   <si>
     <t xml:space="preserve">12.2758855819702</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2613086700439</t>
+    <t xml:space="preserve">12.2613077163696</t>
   </si>
   <si>
     <t xml:space="preserve">12.0659675598145</t>
@@ -3722,25 +3722,25 @@
     <t xml:space="preserve">12.1738414764404</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3414840698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1942510604858</t>
+    <t xml:space="preserve">12.3414850234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1942501068115</t>
   </si>
   <si>
     <t xml:space="preserve">12.0936632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.688404083252</t>
+    <t xml:space="preserve">11.6884031295776</t>
   </si>
   <si>
     <t xml:space="preserve">12.0164022445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429269790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8370971679688</t>
+    <t xml:space="preserve">11.8429279327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8370962142944</t>
   </si>
   <si>
     <t xml:space="preserve">11.6679944992065</t>
@@ -3749,25 +3749,25 @@
     <t xml:space="preserve">11.4332933425903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0222034454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0499000549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4289216995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3633222579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4814014434814</t>
+    <t xml:space="preserve">11.0222024917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.049901008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4289207458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3633213043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4814004898071</t>
   </si>
   <si>
     <t xml:space="preserve">11.5790710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4347524642944</t>
+    <t xml:space="preserve">11.4347515106201</t>
   </si>
   <si>
     <t xml:space="preserve">11.5324220657349</t>
@@ -3776,16 +3776,16 @@
     <t xml:space="preserve">11.9201898574829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8006534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9318532943726</t>
+    <t xml:space="preserve">11.8006525039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9318523406982</t>
   </si>
   <si>
     <t xml:space="preserve">12.7175893783569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.714674949646</t>
+    <t xml:space="preserve">12.7146739959717</t>
   </si>
   <si>
     <t xml:space="preserve">13.0280961990356</t>
@@ -3794,49 +3794,49 @@
     <t xml:space="preserve">13.117018699646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0834903717041</t>
+    <t xml:space="preserve">13.0834922790527</t>
   </si>
   <si>
     <t xml:space="preserve">13.1330547332764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4829196929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5645561218262</t>
+    <t xml:space="preserve">13.4829187393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5645551681519</t>
   </si>
   <si>
     <t xml:space="preserve">13.369213104248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0062284469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1053562164307</t>
+    <t xml:space="preserve">13.0062294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.105357170105</t>
   </si>
   <si>
     <t xml:space="preserve">12.6388702392578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4930934906006</t>
+    <t xml:space="preserve">12.4930925369263</t>
   </si>
   <si>
     <t xml:space="preserve">12.5412006378174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5732707977295</t>
+    <t xml:space="preserve">12.5732698440552</t>
   </si>
   <si>
     <t xml:space="preserve">12.6024265289307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.485803604126</t>
+    <t xml:space="preserve">12.4858045578003</t>
   </si>
   <si>
     <t xml:space="preserve">12.5105857849121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4041690826416</t>
+    <t xml:space="preserve">12.4041700363159</t>
   </si>
   <si>
     <t xml:space="preserve">12.2744283676147</t>
@@ -3845,13 +3845,13 @@
     <t xml:space="preserve">12.4814319610596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.567440032959</t>
+    <t xml:space="preserve">12.5674390792847</t>
   </si>
   <si>
     <t xml:space="preserve">12.4537343978882</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0980367660522</t>
+    <t xml:space="preserve">12.0980377197266</t>
   </si>
   <si>
     <t xml:space="preserve">12.1636371612549</t>
@@ -3860,10 +3860,10 @@
     <t xml:space="preserve">12.1752996444702</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2656803131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6898918151855</t>
+    <t xml:space="preserve">12.2656812667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6898927688599</t>
   </si>
   <si>
     <t xml:space="preserve">12.2525606155396</t>
@@ -3872,10 +3872,10 @@
     <t xml:space="preserve">11.704439163208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6854877471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0645084381104</t>
+    <t xml:space="preserve">11.6854887008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0645093917847</t>
   </si>
   <si>
     <t xml:space="preserve">12.2219476699829</t>
@@ -3890,25 +3890,25 @@
     <t xml:space="preserve">11.9770421981812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1432275772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0426416397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8575038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7627506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0674238204956</t>
+    <t xml:space="preserve">12.1432285308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0426425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8575048446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.762749671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0674247741699</t>
   </si>
   <si>
     <t xml:space="preserve">11.6373825073242</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0790863037109</t>
+    <t xml:space="preserve">12.0790872573853</t>
   </si>
   <si>
     <t xml:space="preserve">12.1534328460693</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">12.2860908508301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2671384811401</t>
+    <t xml:space="preserve">12.2671394348145</t>
   </si>
   <si>
     <t xml:space="preserve">12.4114580154419</t>
@@ -3929,10 +3929,10 @@
     <t xml:space="preserve">12.3123302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2292366027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2598505020142</t>
+    <t xml:space="preserve">12.2292375564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2598495483398</t>
   </si>
   <si>
     <t xml:space="preserve">12.2846326828003</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">12.281717300415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7656965255737</t>
+    <t xml:space="preserve">12.765697479248</t>
   </si>
   <si>
     <t xml:space="preserve">12.8079719543457</t>
@@ -3950,19 +3950,19 @@
     <t xml:space="preserve">12.7992248535156</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5995092391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7190494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7321672439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7904796600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8575353622437</t>
+    <t xml:space="preserve">12.5995111465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.719048500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7321681976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7904787063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.857536315918</t>
   </si>
   <si>
     <t xml:space="preserve">12.9143896102905</t>
@@ -3980,10 +3980,10 @@
     <t xml:space="preserve">13.0368413925171</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0295515060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1855354309082</t>
+    <t xml:space="preserve">13.0295524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1855335235596</t>
   </si>
   <si>
     <t xml:space="preserve">13.0878639221191</t>
@@ -3998,10 +3998,10 @@
     <t xml:space="preserve">12.3983383178711</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2511034011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1782159805298</t>
+    <t xml:space="preserve">12.2511043548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1782150268555</t>
   </si>
   <si>
     <t xml:space="preserve">11.3458280563354</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">11.3472862243652</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0353240966797</t>
+    <t xml:space="preserve">11.0353231430054</t>
   </si>
   <si>
     <t xml:space="preserve">11.6621646881104</t>
@@ -4022,19 +4022,19 @@
     <t xml:space="preserve">11.4755697250366</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8749990463257</t>
+    <t xml:space="preserve">11.8749980926514</t>
   </si>
   <si>
     <t xml:space="preserve">12.2977514266968</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1592636108398</t>
+    <t xml:space="preserve">12.1592626571655</t>
   </si>
   <si>
     <t xml:space="preserve">11.9887046813965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0193185806274</t>
+    <t xml:space="preserve">12.0193176269531</t>
   </si>
   <si>
     <t xml:space="preserve">11.9289360046387</t>
@@ -4043,10 +4043,10 @@
     <t xml:space="preserve">11.8589630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8924922943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.963921546936</t>
+    <t xml:space="preserve">11.8924913406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9639225006104</t>
   </si>
   <si>
     <t xml:space="preserve">11.5309648513794</t>
@@ -4064,31 +4064,31 @@
     <t xml:space="preserve">12.1621799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301221847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9114751815796</t>
+    <t xml:space="preserve">12.6301231384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9114742279053</t>
   </si>
   <si>
     <t xml:space="preserve">13.4318971633911</t>
   </si>
   <si>
-    <t xml:space="preserve">13.299241065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1213941574097</t>
+    <t xml:space="preserve">13.2992401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1213932037354</t>
   </si>
   <si>
     <t xml:space="preserve">13.020806312561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1490917205811</t>
+    <t xml:space="preserve">13.1490907669067</t>
   </si>
   <si>
     <t xml:space="preserve">13.3969106674194</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8561105728149</t>
+    <t xml:space="preserve">13.8561096191406</t>
   </si>
   <si>
     <t xml:space="preserve">13.8298692703247</t>
@@ -4100,52 +4100,52 @@
     <t xml:space="preserve">13.9173345565796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8415298461914</t>
+    <t xml:space="preserve">13.8415307998657</t>
   </si>
   <si>
     <t xml:space="preserve">13.6986703872681</t>
   </si>
   <si>
-    <t xml:space="preserve">13.213231086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1009531021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6855182647705</t>
+    <t xml:space="preserve">13.2132329940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1009521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6855192184448</t>
   </si>
   <si>
     <t xml:space="preserve">12.7861051559448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4406147003174</t>
+    <t xml:space="preserve">12.4406137466431</t>
   </si>
   <si>
     <t xml:space="preserve">12.3691825866699</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6417846679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6636533737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.998908996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8822870254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9814167022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4683122634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3618936538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2234058380127</t>
+    <t xml:space="preserve">12.6417856216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6636524200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9989099502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.882287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9814157485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4683132171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3618927001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.223406791687</t>
   </si>
   <si>
     <t xml:space="preserve">11.9099855422974</t>
@@ -4154,40 +4154,40 @@
     <t xml:space="preserve">12.3997955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5149602890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1665525436401</t>
+    <t xml:space="preserve">12.5149593353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1665515899658</t>
   </si>
   <si>
     <t xml:space="preserve">11.8837461471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4391555786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869459152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3065004348755</t>
+    <t xml:space="preserve">12.439154624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869468688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3064985275269</t>
   </si>
   <si>
     <t xml:space="preserve">11.1052961349487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2190027236938</t>
+    <t xml:space="preserve">11.2190017700195</t>
   </si>
   <si>
     <t xml:space="preserve">10.9041242599487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.074652671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43031692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42594528198242</t>
+    <t xml:space="preserve">10.0746517181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43031787872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42594432830811</t>
   </si>
   <si>
     <t xml:space="preserve">10.5834140777588</t>
@@ -4196,7 +4196,7 @@
     <t xml:space="preserve">9.81808471679688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83703517913818</t>
+    <t xml:space="preserve">9.8370361328125</t>
   </si>
   <si>
     <t xml:space="preserve">10.2043933868408</t>
@@ -4211,10 +4211,10 @@
     <t xml:space="preserve">10.7262754440308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6883726119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.647557258606</t>
+    <t xml:space="preserve">10.6883735656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6475563049316</t>
   </si>
   <si>
     <t xml:space="preserve">10.8035373687744</t>
@@ -4226,49 +4226,49 @@
     <t xml:space="preserve">10.5046939849854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5207290649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5323925018311</t>
+    <t xml:space="preserve">10.52073097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5323915481567</t>
   </si>
   <si>
     <t xml:space="preserve">11.2321224212646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0542736053467</t>
+    <t xml:space="preserve">11.054274559021</t>
   </si>
   <si>
     <t xml:space="preserve">10.7875022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7802124023438</t>
+    <t xml:space="preserve">10.7802133560181</t>
   </si>
   <si>
     <t xml:space="preserve">10.8516435623169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4522142410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98718547821045</t>
+    <t xml:space="preserve">10.4522151947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98718643188477</t>
   </si>
   <si>
     <t xml:space="preserve">9.86910629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0338344573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1475410461426</t>
+    <t xml:space="preserve">10.0338354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1475400924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.1358785629272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1854429244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2583312988281</t>
+    <t xml:space="preserve">10.1854419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2583322525024</t>
   </si>
   <si>
     <t xml:space="preserve">10.5054616928101</t>
@@ -4292,13 +4292,13 @@
     <t xml:space="preserve">9.94823551177979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0710144042969</t>
+    <t xml:space="preserve">10.0710134506226</t>
   </si>
   <si>
     <t xml:space="preserve">10.2174043655396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9088830947876</t>
+    <t xml:space="preserve">9.90888404846191</t>
   </si>
   <si>
     <t xml:space="preserve">10.2237005233765</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">10.091477394104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0190687179565</t>
+    <t xml:space="preserve">10.0190696716309</t>
   </si>
   <si>
     <t xml:space="preserve">10.3449058532715</t>
@@ -4322,10 +4322,10 @@
     <t xml:space="preserve">10.4125909805298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4314804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8375949859619</t>
+    <t xml:space="preserve">10.4314794540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8375959396362</t>
   </si>
   <si>
     <t xml:space="preserve">10.7683353424072</t>
@@ -4346,13 +4346,13 @@
     <t xml:space="preserve">10.6817607879639</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3386087417603</t>
+    <t xml:space="preserve">10.3386096954346</t>
   </si>
   <si>
     <t xml:space="preserve">10.5306482315063</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7903718948364</t>
+    <t xml:space="preserve">10.7903728485107</t>
   </si>
   <si>
     <t xml:space="preserve">10.8202800750732</t>
@@ -4364,19 +4364,19 @@
     <t xml:space="preserve">10.9666700363159</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1571340560913</t>
+    <t xml:space="preserve">11.1571350097656</t>
   </si>
   <si>
     <t xml:space="preserve">11.2263946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8549098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9304666519165</t>
+    <t xml:space="preserve">10.8549108505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.064263343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9304656982422</t>
   </si>
   <si>
     <t xml:space="preserve">11.0249118804932</t>
@@ -4385,40 +4385,40 @@
     <t xml:space="preserve">10.7919464111328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2252740859985</t>
+    <t xml:space="preserve">10.2252750396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.82388305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0977745056152</t>
+    <t xml:space="preserve">9.82073497772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0977735519409</t>
   </si>
   <si>
     <t xml:space="preserve">9.56415843963623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63027000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74989986419678</t>
+    <t xml:space="preserve">9.63026905059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74990081787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.99388408660889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82230854034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61295509338379</t>
+    <t xml:space="preserve">9.82230758666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61295413970947</t>
   </si>
   <si>
     <t xml:space="preserve">9.78138160705566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77508640289307</t>
+    <t xml:space="preserve">9.77508544921875</t>
   </si>
   <si>
     <t xml:space="preserve">9.86953067779541</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">9.28082180023193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22415447235107</t>
+    <t xml:space="preserve">9.22415542602539</t>
   </si>
   <si>
     <t xml:space="preserve">9.12656116485596</t>
@@ -4448,22 +4448,22 @@
     <t xml:space="preserve">9.80499362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60193538665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67906665802002</t>
+    <t xml:space="preserve">9.60193634033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67906761169434</t>
   </si>
   <si>
     <t xml:space="preserve">9.4445276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20211887359619</t>
+    <t xml:space="preserve">9.20211791992188</t>
   </si>
   <si>
     <t xml:space="preserve">9.40989780426025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64443683624268</t>
+    <t xml:space="preserve">9.64443588256836</t>
   </si>
   <si>
     <t xml:space="preserve">10.014347076416</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">9.94981002807617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89156818389893</t>
+    <t xml:space="preserve">9.89156913757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.9545316696167</t>
@@ -4490,16 +4490,16 @@
     <t xml:space="preserve">10.677038192749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9572257995605</t>
+    <t xml:space="preserve">10.9572248458862</t>
   </si>
   <si>
     <t xml:space="preserve">11.0548191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2405614852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3523225784302</t>
+    <t xml:space="preserve">11.2405605316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3523216247559</t>
   </si>
   <si>
     <t xml:space="preserve">11.2736177444458</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">11.2799139022827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6340827941895</t>
+    <t xml:space="preserve">11.6340837478638</t>
   </si>
   <si>
     <t xml:space="preserve">11.33815574646</t>
@@ -4517,10 +4517,10 @@
     <t xml:space="preserve">11.4971380233765</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5585269927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6734352111816</t>
+    <t xml:space="preserve">11.5585279464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.673436164856</t>
   </si>
   <si>
     <t xml:space="preserve">11.726954460144</t>
@@ -4529,25 +4529,25 @@
     <t xml:space="preserve">11.5223236083984</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7049169540405</t>
+    <t xml:space="preserve">11.7049179077148</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9021329879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0500965118408</t>
+    <t xml:space="preserve">10.9021339416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0500974655151</t>
   </si>
   <si>
     <t xml:space="preserve">11.1681537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0894498825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.813982963562</t>
+    <t xml:space="preserve">11.089448928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8139839172363</t>
   </si>
   <si>
     <t xml:space="preserve">10.8265762329102</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">10.5101852416992</t>
   </si>
   <si>
-    <t xml:space="preserve">10.333888053894</t>
+    <t xml:space="preserve">10.3338871002197</t>
   </si>
   <si>
     <t xml:space="preserve">10.6046304702759</t>
@@ -4571,16 +4571,16 @@
     <t xml:space="preserve">10.2315711975098</t>
   </si>
   <si>
-    <t xml:space="preserve">10.340184211731</t>
+    <t xml:space="preserve">10.3401832580566</t>
   </si>
   <si>
     <t xml:space="preserve">10.3323135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4613885879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8124103546143</t>
+    <t xml:space="preserve">10.4613876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8124094009399</t>
   </si>
   <si>
     <t xml:space="preserve">10.6597232818604</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">10.5463886260986</t>
   </si>
   <si>
-    <t xml:space="preserve">10.632963180542</t>
+    <t xml:space="preserve">10.6329641342163</t>
   </si>
   <si>
     <t xml:space="preserve">10.4047212600708</t>
@@ -4604,31 +4604,31 @@
     <t xml:space="preserve">10.4912958145142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.237868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0111999511719</t>
+    <t xml:space="preserve">10.2378673553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0111989974976</t>
   </si>
   <si>
     <t xml:space="preserve">10.1009225845337</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0946264266968</t>
+    <t xml:space="preserve">10.0946254730225</t>
   </si>
   <si>
     <t xml:space="preserve">9.65860366821289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8490686416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93564319610596</t>
+    <t xml:space="preserve">9.84906768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93564224243164</t>
   </si>
   <si>
     <t xml:space="preserve">9.86480903625488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68064117431641</t>
+    <t xml:space="preserve">9.68064022064209</t>
   </si>
   <si>
     <t xml:space="preserve">9.58934307098389</t>
@@ -4637,19 +4637,19 @@
     <t xml:space="preserve">9.69638156890869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59721374511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82703018188477</t>
+    <t xml:space="preserve">9.5972146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82703113555908</t>
   </si>
   <si>
     <t xml:space="preserve">9.83647537231445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0851821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2488861083984</t>
+    <t xml:space="preserve">10.0851812362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2488870620728</t>
   </si>
   <si>
     <t xml:space="preserve">10.2063865661621</t>
@@ -4658,7 +4658,7 @@
     <t xml:space="preserve">10.3685169219971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.289813041687</t>
+    <t xml:space="preserve">10.2898120880127</t>
   </si>
   <si>
     <t xml:space="preserve">10.6487045288086</t>
@@ -4673,10 +4673,10 @@
     <t xml:space="preserve">10.675464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7510194778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8092622756958</t>
+    <t xml:space="preserve">10.7510204315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8092613220215</t>
   </si>
   <si>
     <t xml:space="preserve">10.4566659927368</t>
@@ -4685,37 +4685,37 @@
     <t xml:space="preserve">10.8297252655029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7872257232666</t>
+    <t xml:space="preserve">10.7872247695923</t>
   </si>
   <si>
     <t xml:space="preserve">11.1429681777954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1980609893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.339729309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4247303009033</t>
+    <t xml:space="preserve">11.1980619430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3397302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.424729347229</t>
   </si>
   <si>
     <t xml:space="preserve">11.2153768539429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1036167144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3413028717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4451932907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5553789138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3838043212891</t>
+    <t xml:space="preserve">11.1036157608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3413038253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4451923370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5553798675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3838033676147</t>
   </si>
   <si>
     <t xml:space="preserve">11.5333423614502</t>
@@ -4730,22 +4730,22 @@
     <t xml:space="preserve">11.5774164199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206583023071</t>
+    <t xml:space="preserve">11.7206592559814</t>
   </si>
   <si>
     <t xml:space="preserve">11.7332515716553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4924154281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5364904403687</t>
+    <t xml:space="preserve">11.4924163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5364894866943</t>
   </si>
   <si>
     <t xml:space="preserve">11.3712110519409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3979711532593</t>
+    <t xml:space="preserve">11.397970199585</t>
   </si>
   <si>
     <t xml:space="preserve">11.0831527709961</t>
@@ -4763,10 +4763,10 @@
     <t xml:space="preserve">10.933614730835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6675939559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3291635513306</t>
+    <t xml:space="preserve">10.6675930023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3291645050049</t>
   </si>
   <si>
     <t xml:space="preserve">10.3811092376709</t>
@@ -4790,16 +4790,16 @@
     <t xml:space="preserve">10.8816699981689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1697282791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2862100601196</t>
+    <t xml:space="preserve">11.1697273254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2862110137939</t>
   </si>
   <si>
     <t xml:space="preserve">11.3696374893188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5427875518799</t>
+    <t xml:space="preserve">11.5427865982056</t>
   </si>
   <si>
     <t xml:space="preserve">11.5286197662354</t>
@@ -4811,52 +4811,52 @@
     <t xml:space="preserve">11.1996355056763</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2673206329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3035259246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2295417785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9477815628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.037504196167</t>
+    <t xml:space="preserve">11.2673215866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3035249710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2295427322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9477806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0375032424927</t>
   </si>
   <si>
     <t xml:space="preserve">11.0312070846558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0343570709229</t>
+    <t xml:space="preserve">11.0343561172485</t>
   </si>
   <si>
     <t xml:space="preserve">10.95250415802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0611162185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1728763580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3145446777344</t>
+    <t xml:space="preserve">11.0611152648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1728754043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3145437240601</t>
   </si>
   <si>
     <t xml:space="preserve">11.4026927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9693641662598</t>
+    <t xml:space="preserve">11.9693651199341</t>
   </si>
   <si>
     <t xml:space="preserve">11.9630680084229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8686237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8749189376831</t>
+    <t xml:space="preserve">11.8686227798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8749198913574</t>
   </si>
   <si>
     <t xml:space="preserve">11.9016780853271</t>
@@ -4865,7 +4865,7 @@
     <t xml:space="preserve">12.3392753601074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.129921913147</t>
+    <t xml:space="preserve">12.1299209594727</t>
   </si>
   <si>
     <t xml:space="preserve">12.2054777145386</t>
@@ -4886,10 +4886,10 @@
     <t xml:space="preserve">12.7013149261475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4888143539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7642784118652</t>
+    <t xml:space="preserve">12.4888124465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7642793655396</t>
   </si>
   <si>
     <t xml:space="preserve">13.2254867553711</t>
@@ -4898,10 +4898,10 @@
     <t xml:space="preserve">12.946873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0901145935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0287256240845</t>
+    <t xml:space="preserve">13.0901155471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0287265777588</t>
   </si>
   <si>
     <t xml:space="preserve">13.4238214492798</t>
@@ -4913,13 +4913,13 @@
     <t xml:space="preserve">13.9054927825928</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8330860137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7968816757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7653980255127</t>
+    <t xml:space="preserve">13.8330841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7968807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.765398979187</t>
   </si>
   <si>
     <t xml:space="preserve">13.5387306213379</t>
@@ -4934,7 +4934,7 @@
     <t xml:space="preserve">12.9027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4305715560913</t>
+    <t xml:space="preserve">12.4305725097656</t>
   </si>
   <si>
     <t xml:space="preserve">12.5265922546387</t>
@@ -4946,19 +4946,19 @@
     <t xml:space="preserve">12.7390937805176</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7469625473022</t>
+    <t xml:space="preserve">12.7469635009766</t>
   </si>
   <si>
     <t xml:space="preserve">12.7343711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155725479126</t>
+    <t xml:space="preserve">12.5155735015869</t>
   </si>
   <si>
     <t xml:space="preserve">12.7737226486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7910394668579</t>
+    <t xml:space="preserve">12.7910385131836</t>
   </si>
   <si>
     <t xml:space="preserve">12.9153909683228</t>
@@ -4967,7 +4967,7 @@
     <t xml:space="preserve">13.050763130188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1719675064087</t>
+    <t xml:space="preserve">13.171968460083</t>
   </si>
   <si>
     <t xml:space="preserve">13.1200227737427</t>
@@ -4976,10 +4976,10 @@
     <t xml:space="preserve">12.9390029907227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.682427406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7878894805908</t>
+    <t xml:space="preserve">12.6824264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7878904342651</t>
   </si>
   <si>
     <t xml:space="preserve">13.1829862594604</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">13.2443752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5088224411011</t>
+    <t xml:space="preserve">13.5088214874268</t>
   </si>
   <si>
     <t xml:space="preserve">13.3624324798584</t>
@@ -5003,7 +5003,7 @@
     <t xml:space="preserve">13.3545618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6320552825928</t>
+    <t xml:space="preserve">12.6320543289185</t>
   </si>
   <si>
     <t xml:space="preserve">12.5486288070679</t>
@@ -5051,13 +5051,13 @@
     <t xml:space="preserve">12.770318031311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6242437362671</t>
+    <t xml:space="preserve">12.6242446899414</t>
   </si>
   <si>
     <t xml:space="preserve">12.7514142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0143480300903</t>
+    <t xml:space="preserve">13.014347076416</t>
   </si>
   <si>
     <t xml:space="preserve">13.2600955963135</t>
@@ -5066,13 +5066,13 @@
     <t xml:space="preserve">13.1655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0934000015259</t>
+    <t xml:space="preserve">13.0933990478516</t>
   </si>
   <si>
     <t xml:space="preserve">12.5623769760132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4334878921509</t>
+    <t xml:space="preserve">12.4334888458252</t>
   </si>
   <si>
     <t xml:space="preserve">12.6929845809937</t>
@@ -5114,7 +5114,7 @@
     <t xml:space="preserve">13.5470886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5178737640381</t>
+    <t xml:space="preserve">13.5178747177124</t>
   </si>
   <si>
     <t xml:space="preserve">13.6261405944824</t>
@@ -5129,13 +5129,13 @@
     <t xml:space="preserve">13.2033843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0813703536987</t>
+    <t xml:space="preserve">13.0813694000244</t>
   </si>
   <si>
     <t xml:space="preserve">12.9885702133179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0469999313354</t>
+    <t xml:space="preserve">13.0469989776611</t>
   </si>
   <si>
     <t xml:space="preserve">13.1587028503418</t>
@@ -5150,7 +5150,7 @@
     <t xml:space="preserve">13.8254890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.999059677124</t>
+    <t xml:space="preserve">13.9990587234497</t>
   </si>
   <si>
     <t xml:space="preserve">13.9681262969971</t>
@@ -5168,7 +5168,7 @@
     <t xml:space="preserve">13.9767189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0437412261963</t>
+    <t xml:space="preserve">14.043740272522</t>
   </si>
   <si>
     <t xml:space="preserve">14.3736963272095</t>
@@ -5177,52 +5177,52 @@
     <t xml:space="preserve">14.4458742141724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3547925949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2671489715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2551193237305</t>
+    <t xml:space="preserve">14.3547916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2671480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2551183700562</t>
   </si>
   <si>
     <t xml:space="preserve">14.3152666091919</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1863784790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4149408340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4235334396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8050441741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.593846321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650459289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0200386047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192983627319</t>
+    <t xml:space="preserve">14.1863775253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4149398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4235324859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8050451278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5938453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650449752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0200366973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192974090576</t>
   </si>
   <si>
     <t xml:space="preserve">15.5147933959961</t>
   </si>
   <si>
-    <t xml:space="preserve">15.373875617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3446598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2982606887817</t>
+    <t xml:space="preserve">15.3738746643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3446588516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2982597351074</t>
   </si>
   <si>
     <t xml:space="preserve">15.0834455490112</t>
@@ -5240,31 +5240,31 @@
     <t xml:space="preserve">14.5197706222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3221406936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1571636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0523338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3015184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3633852005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.378851890564</t>
+    <t xml:space="preserve">14.3221397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1571626663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0523328781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3015174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3633842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3788509368896</t>
   </si>
   <si>
     <t xml:space="preserve">14.2173109054565</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3668222427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5489845275879</t>
+    <t xml:space="preserve">14.3668212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5489854812622</t>
   </si>
   <si>
     <t xml:space="preserve">14.7964515686035</t>
@@ -5273,10 +5273,10 @@
     <t xml:space="preserve">14.7500524520874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7586450576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4355630874634</t>
+    <t xml:space="preserve">14.7586460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4355621337891</t>
   </si>
   <si>
     <t xml:space="preserve">14.4493112564087</t>
@@ -5288,7 +5288,7 @@
     <t xml:space="preserve">14.5386743545532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5661697387695</t>
+    <t xml:space="preserve">14.5661706924438</t>
   </si>
   <si>
     <t xml:space="preserve">14.6074151992798</t>
@@ -5303,13 +5303,13 @@
     <t xml:space="preserve">15.2673263549805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1006298065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3859052658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2827930450439</t>
+    <t xml:space="preserve">15.1006288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3859033584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2827920913696</t>
   </si>
   <si>
     <t xml:space="preserve">15.5113563537598</t>
@@ -5318,43 +5318,43 @@
     <t xml:space="preserve">15.9959783554077</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6058759689331</t>
+    <t xml:space="preserve">15.6058750152588</t>
   </si>
   <si>
     <t xml:space="preserve">15.712423324585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5251054763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4512090682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.607593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6471185684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.55260181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999782562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.231237411499</t>
+    <t xml:space="preserve">15.5251045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4512071609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6075925827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6471195220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5526008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2312364578247</t>
   </si>
   <si>
     <t xml:space="preserve">15.3137273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4649562835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9444236755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2726612091064</t>
+    <t xml:space="preserve">15.464955329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9444227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2726593017578</t>
   </si>
   <si>
     <t xml:space="preserve">16.246883392334</t>
@@ -5366,25 +5366,25 @@
     <t xml:space="preserve">16.0681571960449</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2348537445068</t>
+    <t xml:space="preserve">16.2348518371582</t>
   </si>
   <si>
     <t xml:space="preserve">16.1300239562988</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5405721664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1642160415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4855785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2759189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1848382949829</t>
+    <t xml:space="preserve">15.5405702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1642150878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.485577583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.275918006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1848392486572</t>
   </si>
   <si>
     <t xml:space="preserve">14.8806600570679</t>
@@ -5393,16 +5393,16 @@
     <t xml:space="preserve">14.6417865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.122971534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4168376922607</t>
+    <t xml:space="preserve">15.1229705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4168367385864</t>
   </si>
   <si>
     <t xml:space="preserve">15.7553873062134</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0647201538086</t>
+    <t xml:space="preserve">16.06471824646</t>
   </si>
   <si>
     <t xml:space="preserve">15.7467937469482</t>
@@ -5414,16 +5414,16 @@
     <t xml:space="preserve">15.5749416351318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7364816665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0440998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2211036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.894585609436</t>
+    <t xml:space="preserve">15.7364826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0440979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2211055755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8945846557617</t>
   </si>
   <si>
     <t xml:space="preserve">15.8705272674561</t>
@@ -5438,7 +5438,7 @@
     <t xml:space="preserve">16.1094017028809</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0939350128174</t>
+    <t xml:space="preserve">16.0939331054688</t>
   </si>
   <si>
     <t xml:space="preserve">16.9394454956055</t>
@@ -5447,7 +5447,7 @@
     <t xml:space="preserve">17.1009864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2754154205322</t>
+    <t xml:space="preserve">17.2754173278809</t>
   </si>
   <si>
     <t xml:space="preserve">17.4472694396973</t>
@@ -5456,7 +5456,7 @@
     <t xml:space="preserve">17.5847511291504</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0960102081299</t>
+    <t xml:space="preserve">18.0960083007812</t>
   </si>
   <si>
     <t xml:space="preserve">17.9714183807373</t>
@@ -5468,7 +5468,7 @@
     <t xml:space="preserve">18.0530471801758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0186767578125</t>
+    <t xml:space="preserve">18.0186748504639</t>
   </si>
   <si>
     <t xml:space="preserve">17.9671211242676</t>
@@ -5486,28 +5486,28 @@
     <t xml:space="preserve">18.289342880249</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2506771087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2549743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2377891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2420845031738</t>
+    <t xml:space="preserve">18.250675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2549724578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2377872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2420825958252</t>
   </si>
   <si>
     <t xml:space="preserve">18.2034168243408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1733436584473</t>
+    <t xml:space="preserve">18.1733417510986</t>
   </si>
   <si>
     <t xml:space="preserve">18.19482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5718612670898</t>
+    <t xml:space="preserve">17.5718631744385</t>
   </si>
   <si>
     <t xml:space="preserve">17.5503787994385</t>
@@ -5519,7 +5519,7 @@
     <t xml:space="preserve">17.7608985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620845794678</t>
+    <t xml:space="preserve">17.6620826721191</t>
   </si>
   <si>
     <t xml:space="preserve">17.8554172515869</t>
@@ -5531,7 +5531,7 @@
     <t xml:space="preserve">17.5761566162109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3011951446533</t>
+    <t xml:space="preserve">17.3011932373047</t>
   </si>
   <si>
     <t xml:space="preserve">17.11301612854</t>
@@ -5540,13 +5540,13 @@
     <t xml:space="preserve">16.8741416931152</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0459938049316</t>
+    <t xml:space="preserve">17.045991897583</t>
   </si>
   <si>
     <t xml:space="preserve">16.9016380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9274158477783</t>
+    <t xml:space="preserve">16.927417755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.8122749328613</t>
@@ -5558,7 +5558,7 @@
     <t xml:space="preserve">16.6885433197021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7761859893799</t>
+    <t xml:space="preserve">16.7761878967285</t>
   </si>
   <si>
     <t xml:space="preserve">16.7332248687744</t>
@@ -5567,7 +5567,7 @@
     <t xml:space="preserve">17.374231338501</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6105289459229</t>
+    <t xml:space="preserve">17.6105270385742</t>
   </si>
   <si>
     <t xml:space="preserve">17.8468246459961</t>
@@ -5585,16 +5585,16 @@
     <t xml:space="preserve">18.624454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0197124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3032684326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4536380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2388229370117</t>
+    <t xml:space="preserve">19.0197143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3032703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4536399841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2388248443604</t>
   </si>
   <si>
     <t xml:space="preserve">19.3977890014648</t>
@@ -5618,10 +5618,10 @@
     <t xml:space="preserve">20.8198623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1463832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8843078613281</t>
+    <t xml:space="preserve">21.1463813781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8843059539795</t>
   </si>
   <si>
     <t xml:space="preserve">20.8327522277832</t>
@@ -5633,13 +5633,13 @@
     <t xml:space="preserve">20.7382335662842</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9960117340088</t>
+    <t xml:space="preserve">20.9960098266602</t>
   </si>
   <si>
     <t xml:space="preserve">21.1592712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2494926452637</t>
+    <t xml:space="preserve">21.249490737915</t>
   </si>
   <si>
     <t xml:space="preserve">21.4814929962158</t>
@@ -5660,7 +5660,7 @@
     <t xml:space="preserve">21.8552703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7994194030762</t>
+    <t xml:space="preserve">21.7994213104248</t>
   </si>
   <si>
     <t xml:space="preserve">22.3665313720703</t>
@@ -5669,7 +5669,7 @@
     <t xml:space="preserve">22.4696407318115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8649024963379</t>
+    <t xml:space="preserve">22.8649005889893</t>
   </si>
   <si>
     <t xml:space="preserve">22.9078636169434</t>
@@ -5678,19 +5678,19 @@
     <t xml:space="preserve">23.1269760131836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1441612243652</t>
+    <t xml:space="preserve">23.1441593170166</t>
   </si>
   <si>
     <t xml:space="preserve">23.3331985473633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8391227722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9293460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6371974945068</t>
+    <t xml:space="preserve">22.8391246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9293441772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6371955871582</t>
   </si>
   <si>
     <t xml:space="preserve">21.8939361572266</t>
@@ -5699,10 +5699,10 @@
     <t xml:space="preserve">21.4943809509277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5244541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1377906799316</t>
+    <t xml:space="preserve">21.5244560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.137788772583</t>
   </si>
   <si>
     <t xml:space="preserve">21.3912696838379</t>
@@ -5711,25 +5711,25 @@
     <t xml:space="preserve">21.5459365844727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6791210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6619358062744</t>
+    <t xml:space="preserve">21.6791229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.661937713623</t>
   </si>
   <si>
     <t xml:space="preserve">20.9530487060547</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4771957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8370494842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8542346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9229755401611</t>
+    <t xml:space="preserve">21.4771976470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8370475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8542327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9229736328125</t>
   </si>
   <si>
     <t xml:space="preserve">21.2375450134277</t>
@@ -6819,6 +6819,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.44499969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44299983978271</t>
   </si>
 </sst>
 </file>
@@ -72053,7 +72056,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6527199074</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>21656232</v>
@@ -72074,6 +72077,32 @@
         <v>2268</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6910416667</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>20425082</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>9.54899978637695</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>9.38099956512451</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>9.46199989318848</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>9.44299983978271</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>2269</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="2270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="2271">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02501392364502</t>
+    <t xml:space="preserve">4.02501344680786</t>
   </si>
   <si>
     <t xml:space="preserve">STLAM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13119459152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91636300086975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78795790672302</t>
+    <t xml:space="preserve">4.13119506835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91636276245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78795695304871</t>
   </si>
   <si>
     <t xml:space="preserve">3.63238978385925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61757349967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71881604194641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66943025588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37804841995239</t>
+    <t xml:space="preserve">3.61757326126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71881628036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66942977905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37804794311523</t>
   </si>
   <si>
     <t xml:space="preserve">3.28421354293823</t>
@@ -74,67 +74,67 @@
     <t xml:space="preserve">3.18790936470032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2693977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06197357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25705099105835</t>
+    <t xml:space="preserve">3.26939749717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06197333335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25705122947693</t>
   </si>
   <si>
     <t xml:space="preserve">3.32619261741638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26199007034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46200609207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43237352371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18544054031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16321659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16074657440186</t>
+    <t xml:space="preserve">3.26198983192444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46200561523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43237328529358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1854407787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16321682929993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16074681282043</t>
   </si>
   <si>
     <t xml:space="preserve">3.07678985595703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95332264900208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91628313064575</t>
+    <t xml:space="preserve">2.95332288742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91628289222717</t>
   </si>
   <si>
     <t xml:space="preserve">2.94838428497314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65700316429138</t>
+    <t xml:space="preserve">2.65700340270996</t>
   </si>
   <si>
     <t xml:space="preserve">2.58292293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73355269432068</t>
+    <t xml:space="preserve">2.73355221748352</t>
   </si>
   <si>
     <t xml:space="preserve">2.59280014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68416595458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80269360542297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75824522972107</t>
+    <t xml:space="preserve">2.68416547775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80269336700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75824570655823</t>
   </si>
   <si>
     <t xml:space="preserve">2.89899754524231</t>
@@ -146,49 +146,49 @@
     <t xml:space="preserve">2.81010150909424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92615985870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83973383903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72614455223083</t>
+    <t xml:space="preserve">2.92616009712219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83973360061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72614431381226</t>
   </si>
   <si>
     <t xml:space="preserve">3.00517916679382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13358426094055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2990300655365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45212817192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46447587013245</t>
+    <t xml:space="preserve">3.13358402252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29902982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45212864875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46447539329529</t>
   </si>
   <si>
     <t xml:space="preserve">3.44225072860718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28915238380432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30643820762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21013402938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35088539123535</t>
+    <t xml:space="preserve">3.2891526222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3064386844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21013355255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35088586807251</t>
   </si>
   <si>
     <t xml:space="preserve">3.44718980789185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36076331138611</t>
+    <t xml:space="preserve">3.36076354980469</t>
   </si>
   <si>
     <t xml:space="preserve">3.44472026824951</t>
@@ -197,13 +197,13 @@
     <t xml:space="preserve">3.42496609687805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51633095741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50151515007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386141777039</t>
+    <t xml:space="preserve">3.51633143424988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50151491165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386165618896</t>
   </si>
   <si>
     <t xml:space="preserve">3.47682189941406</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">3.33360075950623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57559514045715</t>
+    <t xml:space="preserve">3.57559490203857</t>
   </si>
   <si>
     <t xml:space="preserve">3.5064537525177</t>
@@ -221,73 +221,73 @@
     <t xml:space="preserve">3.33606958389282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34841632843018</t>
+    <t xml:space="preserve">3.34841656684875</t>
   </si>
   <si>
     <t xml:space="preserve">3.18050193786621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13852262496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01505637168884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13605380058289</t>
+    <t xml:space="preserve">3.13852286338806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01505613327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13605356216431</t>
   </si>
   <si>
     <t xml:space="preserve">3.21260285377502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16815495491028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31878399848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35335564613342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40274167060852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56571769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54596281051636</t>
+    <t xml:space="preserve">3.1681547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3187837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35335516929626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40274214744568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56571793556213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54596304893494</t>
   </si>
   <si>
     <t xml:space="preserve">3.56818747520447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47435283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53361630439758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41014957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38298654556274</t>
+    <t xml:space="preserve">3.47435259819031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53361654281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41015028953552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3829870223999</t>
   </si>
   <si>
     <t xml:space="preserve">3.29656004905701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26692843437195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36570167541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31631469726562</t>
+    <t xml:space="preserve">3.26692867279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36570191383362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3163149356842</t>
   </si>
   <si>
     <t xml:space="preserve">3.38051795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33113098144531</t>
+    <t xml:space="preserve">3.33113121986389</t>
   </si>
   <si>
     <t xml:space="preserve">3.108891248703</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">3.11629939079285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97801637649536</t>
+    <t xml:space="preserve">2.97801613807678</t>
   </si>
   <si>
     <t xml:space="preserve">3.06938219070435</t>
@@ -311,31 +311,31 @@
     <t xml:space="preserve">3.12370681762695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07185125350952</t>
+    <t xml:space="preserve">3.0718514919281</t>
   </si>
   <si>
     <t xml:space="preserve">3.15827775001526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07432055473328</t>
+    <t xml:space="preserve">3.07432007789612</t>
   </si>
   <si>
     <t xml:space="preserve">3.0422191619873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03974914550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14840030670166</t>
+    <t xml:space="preserve">3.03974938392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14840006828308</t>
   </si>
   <si>
     <t xml:space="preserve">3.1212375164032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93109822273254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87677383422852</t>
+    <t xml:space="preserve">2.9310986995697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87677407264709</t>
   </si>
   <si>
     <t xml:space="preserve">2.89652848243713</t>
@@ -347,16 +347,16 @@
     <t xml:space="preserve">2.93356847763062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09407472610474</t>
+    <t xml:space="preserve">3.09407496452332</t>
   </si>
   <si>
     <t xml:space="preserve">3.08666706085205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04962706565857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11136031150818</t>
+    <t xml:space="preserve">3.04962730407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11135983467102</t>
   </si>
   <si>
     <t xml:space="preserve">2.81997919082642</t>
@@ -365,55 +365,55 @@
     <t xml:space="preserve">2.64465594291687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66194176673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7137975692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77059245109558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.533536195755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52365851402283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54835176467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84714198112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96320009231567</t>
+    <t xml:space="preserve">2.66194152832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71379733085632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77059268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53353643417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52365875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54835200309753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8471417427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96319985389709</t>
   </si>
   <si>
     <t xml:space="preserve">2.91134452819824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99777150154114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00270915031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95826125144958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08913588523865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09901356697083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12617707252502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06691217422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84467244148254</t>
+    <t xml:space="preserve">2.99777126312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00270962715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95826148986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08913564682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0990138053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12617683410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06691193580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84467267990112</t>
   </si>
   <si>
     <t xml:space="preserve">2.81257104873657</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">2.69157338142395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91381335258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88665127754211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05703520774841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98789381980896</t>
+    <t xml:space="preserve">2.91381359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88665103912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05703496932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98789358139038</t>
   </si>
   <si>
     <t xml:space="preserve">2.96073126792908</t>
@@ -443,22 +443,22 @@
     <t xml:space="preserve">2.88418197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91875219345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0348105430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02987217903137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04468822479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99283194541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05950450897217</t>
+    <t xml:space="preserve">2.91875243186951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03481030464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02987241744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0446879863739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99283242225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05950403213501</t>
   </si>
   <si>
     <t xml:space="preserve">2.97554683685303</t>
@@ -479,31 +479,31 @@
     <t xml:space="preserve">2.8743040561676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81504034996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90146684646606</t>
+    <t xml:space="preserve">2.81504058837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90146660804749</t>
   </si>
   <si>
     <t xml:space="preserve">2.83232545852661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8668966293335</t>
+    <t xml:space="preserve">2.86689615249634</t>
   </si>
   <si>
     <t xml:space="preserve">2.74096012115479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70885896682739</t>
+    <t xml:space="preserve">2.70885920524597</t>
   </si>
   <si>
     <t xml:space="preserve">2.7903470993042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82491755485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84220314025879</t>
+    <t xml:space="preserve">2.82491779327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84220290184021</t>
   </si>
   <si>
     <t xml:space="preserve">2.8915901184082</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">2.87183475494385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90887451171875</t>
+    <t xml:space="preserve">2.90887475013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.76812314987183</t>
@@ -521,88 +521,88 @@
     <t xml:space="preserve">2.82244825363159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85948801040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93850755691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25211191177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29409193992615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25952053070068</t>
+    <t xml:space="preserve">2.85948824882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9385073184967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25211215019226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29409146308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25952076911926</t>
   </si>
   <si>
     <t xml:space="preserve">3.03234148025513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0274031162262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16568517684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5237398147583</t>
+    <t xml:space="preserve">3.02740335464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16568565368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52373933792114</t>
   </si>
   <si>
     <t xml:space="preserve">3.39780330657959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47188305854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4595365524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47929096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49410629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55584096908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58547210693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57065582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56077909469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60028839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62251281738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55830955505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72128558158875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81265115737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85709953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93364810943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93117952346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97315716743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525903701782</t>
+    <t xml:space="preserve">3.47188282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45953631401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4792914390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49410700798035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55584001541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58547282218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57065653800964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56077885627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60028862953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62251257896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55830931663513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72128534317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81265163421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8570990562439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93364882469177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93117904663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97315740585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525856018066</t>
   </si>
   <si>
     <t xml:space="preserve">3.99044322967529</t>
@@ -614,10 +614,10 @@
     <t xml:space="preserve">4.19539785385132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21762180328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29664039611816</t>
+    <t xml:space="preserve">4.21762132644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29664087295532</t>
   </si>
   <si>
     <t xml:space="preserve">4.30651760101318</t>
@@ -629,43 +629,43 @@
     <t xml:space="preserve">4.26453924179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31392621994019</t>
+    <t xml:space="preserve">4.31392669677734</t>
   </si>
   <si>
     <t xml:space="preserve">4.30898761749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27935457229614</t>
+    <t xml:space="preserve">4.27935552597046</t>
   </si>
   <si>
     <t xml:space="preserve">4.42257690429688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5065336227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53863525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5707368850708</t>
+    <t xml:space="preserve">4.50653409957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53863573074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57073640823364</t>
   </si>
   <si>
     <t xml:space="preserve">4.88928031921387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95842266082764</t>
+    <t xml:space="preserve">4.95842218399048</t>
   </si>
   <si>
     <t xml:space="preserve">5.01274824142456</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17078447341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3361496925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53616666793823</t>
+    <t xml:space="preserve">5.17078495025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33615016937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53616571426392</t>
   </si>
   <si>
     <t xml:space="preserve">4.34602737426758</t>
@@ -680,46 +680,46 @@
     <t xml:space="preserve">4.62753105163574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64234733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71889734268188</t>
+    <t xml:space="preserve">4.64234781265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71889686584473</t>
   </si>
   <si>
     <t xml:space="preserve">4.99793195724487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04237842559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10164403915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12633657455444</t>
+    <t xml:space="preserve">5.04237937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10164356231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12633609771729</t>
   </si>
   <si>
     <t xml:space="preserve">4.95348405838013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98805332183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99299287796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00287055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04731702804565</t>
+    <t xml:space="preserve">4.9880542755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99299240112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00287103652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04731750488281</t>
   </si>
   <si>
     <t xml:space="preserve">4.92385149002075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78062963485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89915895462036</t>
+    <t xml:space="preserve">4.78062915802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8991584777832</t>
   </si>
   <si>
     <t xml:space="preserve">5.02756309509277</t>
@@ -728,52 +728,52 @@
     <t xml:space="preserve">5.33869934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34363794326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32388353347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25474214553833</t>
+    <t xml:space="preserve">5.34363842010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32388305664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25474262237549</t>
   </si>
   <si>
     <t xml:space="preserve">5.32882213592529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1757230758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14609050750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18560075759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18066263198853</t>
+    <t xml:space="preserve">5.17572259902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14609003067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18560123443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18066215515137</t>
   </si>
   <si>
     <t xml:space="preserve">5.13127517700195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1362133026123</t>
+    <t xml:space="preserve">5.13621377944946</t>
   </si>
   <si>
     <t xml:space="preserve">5.16584634780884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09670448303223</t>
+    <t xml:space="preserve">5.09670495986938</t>
   </si>
   <si>
     <t xml:space="preserve">5.14115238189697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22511053085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30412864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21029424667358</t>
+    <t xml:space="preserve">5.22511005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30412769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21029472351074</t>
   </si>
   <si>
     <t xml:space="preserve">4.98311519622803</t>
@@ -794,82 +794,82 @@
     <t xml:space="preserve">5.07201147079468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06213331222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81026172637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83248662948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74358987808228</t>
+    <t xml:space="preserve">5.0621337890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81026220321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83248710632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74359035491943</t>
   </si>
   <si>
     <t xml:space="preserve">4.78556823730469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73371267318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71642732620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70654916763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69420337677002</t>
+    <t xml:space="preserve">4.73371315002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71642780303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70654964447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69420289993286</t>
   </si>
   <si>
     <t xml:space="preserve">4.51888036727905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45220899581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64728689193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70408058166504</t>
+    <t xml:space="preserve">4.45220851898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64728593826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70408010482788</t>
   </si>
   <si>
     <t xml:space="preserve">4.63000106811523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79297637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78803825378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23498773574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91644287109375</t>
+    <t xml:space="preserve">4.79297685623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78803777694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23498725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91644239425659</t>
   </si>
   <si>
     <t xml:space="preserve">4.97323799133301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05225706100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03744077682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91891241073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94854497909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02262449264526</t>
+    <t xml:space="preserve">5.0522575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03744029998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91891288757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94854545593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02262401580811</t>
   </si>
   <si>
     <t xml:space="preserve">4.76828384399414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62012434005737</t>
+    <t xml:space="preserve">4.62012386322021</t>
   </si>
   <si>
     <t xml:space="preserve">4.80038452148438</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">4.72383594512939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68926429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66210126876831</t>
+    <t xml:space="preserve">4.68926525115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66210222244263</t>
   </si>
   <si>
     <t xml:space="preserve">4.67197895050049</t>
@@ -893,31 +893,31 @@
     <t xml:space="preserve">4.583083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61518526077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84730195999146</t>
+    <t xml:space="preserve">4.61518573760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84730243682861</t>
   </si>
   <si>
     <t xml:space="preserve">4.83001661300659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75346660614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80532312393188</t>
+    <t xml:space="preserve">4.75346708297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80532360076904</t>
   </si>
   <si>
     <t xml:space="preserve">4.75099849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79544591903687</t>
+    <t xml:space="preserve">4.79544639587402</t>
   </si>
   <si>
     <t xml:space="preserve">4.8176703453064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78309917449951</t>
+    <t xml:space="preserve">4.78309965133667</t>
   </si>
   <si>
     <t xml:space="preserve">4.72136640548706</t>
@@ -926,37 +926,37 @@
     <t xml:space="preserve">4.68432569503784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85224008560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77816152572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76087522506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55839014053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85507774353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86003732681274</t>
+    <t xml:space="preserve">4.85224056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.778160572052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76087617874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55838966369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86003828048706</t>
   </si>
   <si>
     <t xml:space="preserve">4.78564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8253231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80548572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87243461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95922231674194</t>
+    <t xml:space="preserve">4.82532215118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80548524856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87243509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95922183990479</t>
   </si>
   <si>
     <t xml:space="preserve">4.99889516830444</t>
@@ -968,37 +968,37 @@
     <t xml:space="preserve">5.15263223648071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17246770858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10799884796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17742776870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97409915924072</t>
+    <t xml:space="preserve">5.1724681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10799837112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17742729187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97409963607788</t>
   </si>
   <si>
     <t xml:space="preserve">4.97905969619751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98897695541382</t>
+    <t xml:space="preserve">4.98897647857666</t>
   </si>
   <si>
     <t xml:space="preserve">5.03856897354126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03361034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05840635299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07328414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02865171432495</t>
+    <t xml:space="preserve">5.03360986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05840587615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07328367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02865123748779</t>
   </si>
   <si>
     <t xml:space="preserve">5.07824325561523</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">5.06336545944214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95178318023682</t>
+    <t xml:space="preserve">4.95178413391113</t>
   </si>
   <si>
     <t xml:space="preserve">4.95426273345947</t>
@@ -1016,22 +1016,22 @@
     <t xml:space="preserve">4.86995601654053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26669454574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40555238723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34604120254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30636739730835</t>
+    <t xml:space="preserve">5.26669502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40555191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34604167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30636787414551</t>
   </si>
   <si>
     <t xml:space="preserve">5.67334985733032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68822717666626</t>
+    <t xml:space="preserve">5.68822765350342</t>
   </si>
   <si>
     <t xml:space="preserve">6.01553678512573</t>
@@ -1040,46 +1040,46 @@
     <t xml:space="preserve">6.19406795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14943599700928</t>
+    <t xml:space="preserve">6.14943504333496</t>
   </si>
   <si>
     <t xml:space="preserve">6.16431331634521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07008838653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13951683044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27341604232788</t>
+    <t xml:space="preserve">6.07008743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13951730728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27341651916504</t>
   </si>
   <si>
     <t xml:space="preserve">6.61560249328613</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53129577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50649881362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78421545028687</t>
+    <t xml:space="preserve">6.53129482269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50649976730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78421640396118</t>
   </si>
   <si>
     <t xml:space="preserve">6.7098274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72470569610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76933860778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80405282974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96770763397217</t>
+    <t xml:space="preserve">6.72470617294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76933765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80405235290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96770715713501</t>
   </si>
   <si>
     <t xml:space="preserve">6.88340091705322</t>
@@ -1091,58 +1091,58 @@
     <t xml:space="preserve">7.07681035995483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14623975753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1809549331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46363019943237</t>
+    <t xml:space="preserve">7.14623928070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18095350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46362972259521</t>
   </si>
   <si>
     <t xml:space="preserve">7.31485271453857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33469009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38428163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36444568634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51818180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58265018463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56281423568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53801727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49338483810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40907859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52313995361328</t>
+    <t xml:space="preserve">7.33468961715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38428258895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36444520950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51818084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58265113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56281471252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53801822662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49338579177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40907764434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52313947677612</t>
   </si>
   <si>
     <t xml:space="preserve">7.41403770446777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50330352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42395639419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4586706161499</t>
+    <t xml:space="preserve">7.50330305099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42395687103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45867013931274</t>
   </si>
   <si>
     <t xml:space="preserve">7.41899633407593</t>
@@ -1151,22 +1151,22 @@
     <t xml:space="preserve">7.30989408493042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37932300567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93795204162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05697298049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02225875854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14128065109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34956741333008</t>
+    <t xml:space="preserve">7.37932348251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93795299530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0569748878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02225828170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14127969741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34956645965576</t>
   </si>
   <si>
     <t xml:space="preserve">7.3594856262207</t>
@@ -1178,10 +1178,10 @@
     <t xml:space="preserve">7.76614141464233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73142671585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66199779510498</t>
+    <t xml:space="preserve">7.73142623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66199827194214</t>
   </si>
   <si>
     <t xml:space="preserve">7.45371055603027</t>
@@ -1190,67 +1190,67 @@
     <t xml:space="preserve">7.28013753890991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33964776992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37436294555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25038290023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43387365341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55785512924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24046516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2007908821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17103481292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.151198387146</t>
+    <t xml:space="preserve">7.33964920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37436246871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2503833770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43387508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55785417556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24046421051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20078992843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1710352897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15119886398315</t>
   </si>
   <si>
     <t xml:space="preserve">7.00738143920898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23550415039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19087219238281</t>
+    <t xml:space="preserve">7.23550367355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19087171554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.53305912017822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52809953689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50826215744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43883323669434</t>
+    <t xml:space="preserve">7.52810001373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50826168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43883371353149</t>
   </si>
   <si>
     <t xml:space="preserve">7.44875192642212</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63720178604126</t>
+    <t xml:space="preserve">7.6372013092041</t>
   </si>
   <si>
     <t xml:space="preserve">7.6520791053772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64216041564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69175338745117</t>
+    <t xml:space="preserve">7.64216089248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69175291061401</t>
   </si>
   <si>
     <t xml:space="preserve">7.67191648483276</t>
@@ -1259,31 +1259,31 @@
     <t xml:space="preserve">7.54297685623169</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39420032501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71159029006958</t>
+    <t xml:space="preserve">7.39419984817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71159076690674</t>
   </si>
   <si>
     <t xml:space="preserve">8.35628986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88692474365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98115062713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15968322753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21423435211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42252159118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48699188232422</t>
+    <t xml:space="preserve">8.88692569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98115158081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15968418121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2142333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42252254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48699283599854</t>
   </si>
   <si>
     <t xml:space="preserve">9.69032001495361</t>
@@ -1301,19 +1301,19 @@
     <t xml:space="preserve">9.69528007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76470851898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70519733428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64072704315186</t>
+    <t xml:space="preserve">9.76470947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70519638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6407299041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.63080883026123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81926155090332</t>
+    <t xml:space="preserve">9.819260597229</t>
   </si>
   <si>
     <t xml:space="preserve">9.84108066558838</t>
@@ -1322,37 +1322,37 @@
     <t xml:space="preserve">9.68337726593018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65163898468018</t>
+    <t xml:space="preserve">9.65163803100586</t>
   </si>
   <si>
     <t xml:space="preserve">9.5385684967041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31936836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7579870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35110855102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89982128143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63698196411133</t>
+    <t xml:space="preserve">9.31936931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75798606872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35110950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89982032775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63698101043701</t>
   </si>
   <si>
     <t xml:space="preserve">8.75302696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57548713684082</t>
+    <t xml:space="preserve">8.57548809051514</t>
   </si>
   <si>
     <t xml:space="preserve">8.77782249450684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82741451263428</t>
+    <t xml:space="preserve">8.82741546630859</t>
   </si>
   <si>
     <t xml:space="preserve">9.0039644241333</t>
@@ -1364,37 +1364,37 @@
     <t xml:space="preserve">8.94643592834473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98908710479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80956363677979</t>
+    <t xml:space="preserve">8.98908615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80956268310547</t>
   </si>
   <si>
     <t xml:space="preserve">8.73814964294434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6905403137207</t>
+    <t xml:space="preserve">8.69054126739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.8055944442749</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71434497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47431945800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98930740356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01410293579102</t>
+    <t xml:space="preserve">8.71434593200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47431755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98930644989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0141019821167</t>
   </si>
   <si>
     <t xml:space="preserve">8.46836853027344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55664253234863</t>
+    <t xml:space="preserve">8.55664157867432</t>
   </si>
   <si>
     <t xml:space="preserve">8.56259250640869</t>
@@ -1409,28 +1409,28 @@
     <t xml:space="preserve">8.53085422515869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43266201019287</t>
+    <t xml:space="preserve">8.43266105651855</t>
   </si>
   <si>
     <t xml:space="preserve">8.53184604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52589416503906</t>
+    <t xml:space="preserve">8.52589511871338</t>
   </si>
   <si>
     <t xml:space="preserve">8.35926532745361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56457710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71731948852539</t>
+    <t xml:space="preserve">8.56457614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71732044219971</t>
   </si>
   <si>
     <t xml:space="preserve">8.42175102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25115299224854</t>
+    <t xml:space="preserve">8.25115489959717</t>
   </si>
   <si>
     <t xml:space="preserve">8.1886682510376</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">8.18370914459229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78278160095215</t>
+    <t xml:space="preserve">8.78278255462646</t>
   </si>
   <si>
     <t xml:space="preserve">8.73517322540283</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">9.15869045257568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07438373565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18943881988525</t>
+    <t xml:space="preserve">9.07438468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18943977355957</t>
   </si>
   <si>
     <t xml:space="preserve">9.31342029571533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22613620758057</t>
+    <t xml:space="preserve">9.22613716125488</t>
   </si>
   <si>
     <t xml:space="preserve">9.40764427185059</t>
@@ -1475,16 +1475,16 @@
     <t xml:space="preserve">9.36301136016846</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70916652679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76768398284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63180160522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55840492248535</t>
+    <t xml:space="preserve">9.70916557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76768493652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63180255889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55840396881104</t>
   </si>
   <si>
     <t xml:space="preserve">9.7597484588623</t>
@@ -1493,16 +1493,16 @@
     <t xml:space="preserve">9.79148769378662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393367767334</t>
+    <t xml:space="preserve">9.49393558502197</t>
   </si>
   <si>
     <t xml:space="preserve">9.68635272979736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41458606719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20927619934082</t>
+    <t xml:space="preserve">9.41458702087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2092752456665</t>
   </si>
   <si>
     <t xml:space="preserve">9.43739891052246</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">9.21820259094238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51674747467041</t>
+    <t xml:space="preserve">9.51674842834473</t>
   </si>
   <si>
     <t xml:space="preserve">9.5355920791626</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">9.29556560516357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3084602355957</t>
+    <t xml:space="preserve">9.30846118927002</t>
   </si>
   <si>
     <t xml:space="preserve">9.42946434020996</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">9.30746841430664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36797046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19935703277588</t>
+    <t xml:space="preserve">9.36796951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19935607910156</t>
   </si>
   <si>
     <t xml:space="preserve">9.4393835067749</t>
@@ -1550,22 +1550,22 @@
     <t xml:space="preserve">9.59609508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48600101470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31143569946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3054838180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1081075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06446647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42747974395752</t>
+    <t xml:space="preserve">9.48600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31143665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30548477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10810852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06446552276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42748069763184</t>
   </si>
   <si>
     <t xml:space="preserve">9.62089061737061</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">9.185471534729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85221195220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87601470947266</t>
+    <t xml:space="preserve">8.85221290588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87601661682129</t>
   </si>
   <si>
     <t xml:space="preserve">8.86213111877441</t>
@@ -1586,22 +1586,22 @@
     <t xml:space="preserve">9.13984775543213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90676307678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98313617706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92660045623779</t>
+    <t xml:space="preserve">8.90676212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98313522338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92659854888916</t>
   </si>
   <si>
     <t xml:space="preserve">8.85022830963135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04462814331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87403297424316</t>
+    <t xml:space="preserve">9.04462909698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87403202056885</t>
   </si>
   <si>
     <t xml:space="preserve">8.92461585998535</t>
@@ -1613,28 +1613,28 @@
     <t xml:space="preserve">8.75005149841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38505172729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18172550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92979526519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15296077728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24123668670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95558595657349</t>
+    <t xml:space="preserve">8.38505363464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18172454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92979764938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15296173095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24123573303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95558500289917</t>
   </si>
   <si>
     <t xml:space="preserve">8.10039329528809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10237884521484</t>
+    <t xml:space="preserve">8.10237598419189</t>
   </si>
   <si>
     <t xml:space="preserve">8.03889942169189</t>
@@ -1643,13 +1643,13 @@
     <t xml:space="preserve">8.50506687164307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40687370300293</t>
+    <t xml:space="preserve">8.40687274932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.46935939788818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52291965484619</t>
+    <t xml:space="preserve">8.52291870117188</t>
   </si>
   <si>
     <t xml:space="preserve">8.26305675506592</t>
@@ -1658,16 +1658,16 @@
     <t xml:space="preserve">8.21346378326416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25214672088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19957828521729</t>
+    <t xml:space="preserve">8.25214576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19957733154297</t>
   </si>
   <si>
     <t xml:space="preserve">8.24916934967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22239112854004</t>
+    <t xml:space="preserve">8.22239017486572</t>
   </si>
   <si>
     <t xml:space="preserve">8.33347606658936</t>
@@ -1682,34 +1682,34 @@
     <t xml:space="preserve">8.21048831939697</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1611156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26426935195923</t>
+    <t xml:space="preserve">7.16111707687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26426982879639</t>
   </si>
   <si>
     <t xml:space="preserve">7.23947334289551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04804611206055</t>
+    <t xml:space="preserve">7.04804563522339</t>
   </si>
   <si>
     <t xml:space="preserve">7.04209566116333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24344062805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23352098464966</t>
+    <t xml:space="preserve">7.2434401512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23352193832397</t>
   </si>
   <si>
     <t xml:space="preserve">7.20277500152588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24839925765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17500305175781</t>
+    <t xml:space="preserve">7.24839878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1750020980835</t>
   </si>
   <si>
     <t xml:space="preserve">7.04407978057861</t>
@@ -1724,46 +1724,46 @@
     <t xml:space="preserve">6.79909372329712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01730012893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12243509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03713703155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95977115631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18591260910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43486595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42693090438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36146926879883</t>
+    <t xml:space="preserve">7.01729965209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12243413925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03713655471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95977210998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1859130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4348669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42693185806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36147022247314</t>
   </si>
   <si>
     <t xml:space="preserve">7.22062683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26823568344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39320802688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22657918930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21566915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16706705093384</t>
+    <t xml:space="preserve">7.26823616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3932089805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22657823562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21566820144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.167067527771</t>
   </si>
   <si>
     <t xml:space="preserve">7.48247480392456</t>
@@ -1772,61 +1772,61 @@
     <t xml:space="preserve">7.40610218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42792224884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.457679271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48346662521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61934900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73341178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66001653671265</t>
+    <t xml:space="preserve">7.42792272567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45767736434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48346614837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61934852600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73341083526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66001462936401</t>
   </si>
   <si>
     <t xml:space="preserve">7.70266342163086</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66794919967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51024532318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68282556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69373750686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64017724990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57769155502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52016401290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34460735321045</t>
+    <t xml:space="preserve">7.66794872283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51024627685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68282651901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69373798370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64017772674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57769060134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52016496658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34460878372192</t>
   </si>
   <si>
     <t xml:space="preserve">7.42197179794312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01035737991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96274852752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92803335189819</t>
+    <t xml:space="preserve">7.01035642623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96274757385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92803192138672</t>
   </si>
   <si>
     <t xml:space="preserve">6.94588613510132</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">7.17797803878784</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87744951248169</t>
+    <t xml:space="preserve">6.87745046615601</t>
   </si>
   <si>
     <t xml:space="preserve">6.82587337493896</t>
@@ -1844,91 +1844,91 @@
     <t xml:space="preserve">6.66618680953979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86455583572388</t>
+    <t xml:space="preserve">6.86455488204956</t>
   </si>
   <si>
     <t xml:space="preserve">6.95183849334717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78024864196777</t>
+    <t xml:space="preserve">6.78025007247925</t>
   </si>
   <si>
     <t xml:space="preserve">7.04705476760864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81992244720459</t>
+    <t xml:space="preserve">6.81992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">6.67015361785889</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75247573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02920055389404</t>
+    <t xml:space="preserve">6.75247716903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02920198440552</t>
   </si>
   <si>
     <t xml:space="preserve">7.11251592636108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09664630889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26129293441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28708028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0867280960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30394172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23054647445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13334465026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1283860206604</t>
+    <t xml:space="preserve">7.09664583206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26129388809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28708219528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08672666549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30394268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23054599761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13334512710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12838554382324</t>
   </si>
   <si>
     <t xml:space="preserve">6.94291114807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01233959197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93001699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99051952362061</t>
+    <t xml:space="preserve">7.01234102249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93001747131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99051856994629</t>
   </si>
   <si>
     <t xml:space="preserve">7.33865737915039</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34758329391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30493402481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49635982513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34857559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23451375961304</t>
+    <t xml:space="preserve">7.34758424758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30493354797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49635934829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34857511520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23451280593872</t>
   </si>
   <si>
     <t xml:space="preserve">6.86554574966431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82488203048706</t>
+    <t xml:space="preserve">6.82488107681274</t>
   </si>
   <si>
     <t xml:space="preserve">6.6106424331665</t>
@@ -1937,37 +1937,37 @@
     <t xml:space="preserve">6.78322410583496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91613101959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92208194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86852312088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82884931564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82289791107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72272157669067</t>
+    <t xml:space="preserve">6.9161319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92208385467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86852264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82884979248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82289886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72272109985352</t>
   </si>
   <si>
     <t xml:space="preserve">6.50848340988159</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25754642486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28928661346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23175859451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15736961364746</t>
+    <t xml:space="preserve">6.25754690170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28928518295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23175954818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15737009048462</t>
   </si>
   <si>
     <t xml:space="preserve">6.50253248214722</t>
@@ -1976,40 +1976,40 @@
     <t xml:space="preserve">6.5511326789856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62849712371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87645721435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01134777069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16012573242188</t>
+    <t xml:space="preserve">6.6284966468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87645673751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01134729385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16012620925903</t>
   </si>
   <si>
     <t xml:space="preserve">7.24443101882935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21070909500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32080411911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10557270050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26724529266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18690490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18988084793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28509712219238</t>
+    <t xml:space="preserve">7.21070957183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32080364227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10557413101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26724338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1869044303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18987989425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28509902954102</t>
   </si>
   <si>
     <t xml:space="preserve">7.39816761016846</t>
@@ -2027,52 +2027,52 @@
     <t xml:space="preserve">6.44302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4182243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39739608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49757289886475</t>
+    <t xml:space="preserve">6.41822528839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39739656448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49757242202759</t>
   </si>
   <si>
     <t xml:space="preserve">6.40731477737427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45988321304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44897317886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45194864273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57692003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.501540184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51145839691162</t>
+    <t xml:space="preserve">6.45988368988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44897222518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45194721221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57692098617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50154113769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51145887374878</t>
   </si>
   <si>
     <t xml:space="preserve">6.54617309570312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4559154510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43806123733521</t>
+    <t xml:space="preserve">6.45591497421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43806171417236</t>
   </si>
   <si>
     <t xml:space="preserve">6.41227436065674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3626823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41525030136108</t>
+    <t xml:space="preserve">6.36268186569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41524982452393</t>
   </si>
   <si>
     <t xml:space="preserve">6.64932489395142</t>
@@ -2081,46 +2081,46 @@
     <t xml:space="preserve">6.32697629928589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36664962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35871410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30416297912598</t>
+    <t xml:space="preserve">6.36665058135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35871458053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30416345596313</t>
   </si>
   <si>
     <t xml:space="preserve">6.25853872299194</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26548004150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32003259658813</t>
+    <t xml:space="preserve">6.26548099517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32003355026245</t>
   </si>
   <si>
     <t xml:space="preserve">6.63643074035645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46980094909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49658107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33590221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46385145187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49162244796753</t>
+    <t xml:space="preserve">6.46980142593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49657964706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33590269088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46385097503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4916205406189</t>
   </si>
   <si>
     <t xml:space="preserve">6.66122770309448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52633619308472</t>
+    <t xml:space="preserve">6.52633666992188</t>
   </si>
   <si>
     <t xml:space="preserve">6.58188009262085</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">6.73958301544189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80603694915771</t>
+    <t xml:space="preserve">6.80603647232056</t>
   </si>
   <si>
     <t xml:space="preserve">6.80901288986206</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">6.81000280380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9389443397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86157989501953</t>
+    <t xml:space="preserve">6.93894338607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86158037185669</t>
   </si>
   <si>
     <t xml:space="preserve">6.89133405685425</t>
@@ -2153,85 +2153,85 @@
     <t xml:space="preserve">7.04308700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09367275238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607570648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29303169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28431129455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20211315155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14384746551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.209397315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19170999526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14488983154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04916667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3737907409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11263513565063</t>
+    <t xml:space="preserve">7.09367084503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29303216934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28431081771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20211410522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14384698867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20939779281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19170951843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14488840103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04916572570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11263608932495</t>
   </si>
   <si>
     <t xml:space="preserve">7.07205581665039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80673885345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73806667327881</t>
+    <t xml:space="preserve">6.80673789978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73806571960449</t>
   </si>
   <si>
     <t xml:space="preserve">6.61112928390503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71309471130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81401920318604</t>
+    <t xml:space="preserve">6.71309566497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81402015686035</t>
   </si>
   <si>
     <t xml:space="preserve">6.88997459411621</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95448303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93350124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88365411758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82684946060181</t>
+    <t xml:space="preserve">6.9544825553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93350076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88365364074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82684993743896</t>
   </si>
   <si>
     <t xml:space="preserve">6.62166261672974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64021062850952</t>
+    <t xml:space="preserve">6.64021015167236</t>
   </si>
   <si>
     <t xml:space="preserve">7.16999053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10623121261597</t>
+    <t xml:space="preserve">7.10623073577881</t>
   </si>
   <si>
     <t xml:space="preserve">7.019287109375</t>
@@ -2240,52 +2240,52 @@
     <t xml:space="preserve">6.96132373809814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62977695465088</t>
+    <t xml:space="preserve">6.62977647781372</t>
   </si>
   <si>
     <t xml:space="preserve">6.59268140792847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84771680831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78163909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78743410110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76425123214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88133525848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94625329971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83728408813477</t>
+    <t xml:space="preserve">6.84771728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78163957595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78743457794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7642502784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88133478164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94625377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83728313446045</t>
   </si>
   <si>
     <t xml:space="preserve">6.89524555206299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86278629302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92422676086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98566865921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0644965171814</t>
+    <t xml:space="preserve">6.86278581619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92422771453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98566818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06449699401855</t>
   </si>
   <si>
     <t xml:space="preserve">7.15028142929077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13521146774292</t>
+    <t xml:space="preserve">7.13521099090576</t>
   </si>
   <si>
     <t xml:space="preserve">7.14216709136963</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">7.02160501480103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03319835662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08072710037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10970830917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1572380065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13057470321655</t>
+    <t xml:space="preserve">7.03319692611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08072757720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10970783233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15723752975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13057422637939</t>
   </si>
   <si>
     <t xml:space="preserve">7.33112573623657</t>
@@ -2315,31 +2315,31 @@
     <t xml:space="preserve">7.35315132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3253288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28939294815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20940494537354</t>
+    <t xml:space="preserve">7.32532930374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28939342498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20940542221069</t>
   </si>
   <si>
     <t xml:space="preserve">7.20476722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28707408905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28591442108154</t>
+    <t xml:space="preserve">7.28707504272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28591537475586</t>
   </si>
   <si>
     <t xml:space="preserve">7.05986166000366</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07493114471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95900583267212</t>
+    <t xml:space="preserve">7.07493019104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95900535583496</t>
   </si>
   <si>
     <t xml:space="preserve">7.17578554153442</t>
@@ -2348,76 +2348,76 @@
     <t xml:space="preserve">7.3114185333252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19433450698853</t>
+    <t xml:space="preserve">7.19433403015137</t>
   </si>
   <si>
     <t xml:space="preserve">7.08768320083618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97639322280884</t>
+    <t xml:space="preserve">6.97639417648315</t>
   </si>
   <si>
     <t xml:space="preserve">6.99841928482056</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76540994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81873607635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8685827255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72715520858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72367668151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82569074630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58572483062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4072003364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52660322189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46632242202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194389343262</t>
+    <t xml:space="preserve">6.76541042327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81873512268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86858224868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72715425491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72367715835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82569122314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58572578430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40720081329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52660417556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46632289886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6819429397583</t>
   </si>
   <si>
     <t xml:space="preserve">6.6900577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5451512336731</t>
+    <t xml:space="preserve">6.54515075683594</t>
   </si>
   <si>
     <t xml:space="preserve">6.63557291030884</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74454355239868</t>
+    <t xml:space="preserve">6.74454259872437</t>
   </si>
   <si>
     <t xml:space="preserve">6.8048243522644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86162853240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86394739151001</t>
+    <t xml:space="preserve">6.86162805557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86394691467285</t>
   </si>
   <si>
     <t xml:space="preserve">7.08304595947266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29055213928223</t>
+    <t xml:space="preserve">7.29055309295654</t>
   </si>
   <si>
     <t xml:space="preserve">7.30562257766724</t>
@@ -2426,19 +2426,19 @@
     <t xml:space="preserve">7.37285947799683</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28243684768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28127813339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29287099838257</t>
+    <t xml:space="preserve">7.28243732452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28127765655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29287052154541</t>
   </si>
   <si>
     <t xml:space="preserve">7.18158197402954</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18737888336182</t>
+    <t xml:space="preserve">7.18737840652466</t>
   </si>
   <si>
     <t xml:space="preserve">7.07029342651367</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">6.92654657363892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83148765563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84539794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87785720825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63093566894531</t>
+    <t xml:space="preserve">6.83148813247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84539937973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87785768508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525754928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63093614578247</t>
   </si>
   <si>
     <t xml:space="preserve">6.54051399230957</t>
@@ -2468,28 +2468,28 @@
     <t xml:space="preserve">6.53239965438843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57529163360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50921392440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54862976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73410987854004</t>
+    <t xml:space="preserve">6.5752911567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50921440124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54862928390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73410940170288</t>
   </si>
   <si>
     <t xml:space="preserve">6.87553882598877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91843175888062</t>
+    <t xml:space="preserve">6.91843128204346</t>
   </si>
   <si>
     <t xml:space="preserve">7.07145214080811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03899431228638</t>
+    <t xml:space="preserve">7.03899383544922</t>
   </si>
   <si>
     <t xml:space="preserve">6.87206172943115</t>
@@ -2498,34 +2498,34 @@
     <t xml:space="preserve">6.95668697357178</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90915679931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87322044372559</t>
+    <t xml:space="preserve">6.90915727615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87321996688843</t>
   </si>
   <si>
     <t xml:space="preserve">6.86742401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90336036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81062030792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45980262756348</t>
+    <t xml:space="preserve">6.90336132049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81062078475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45980310440063</t>
   </si>
   <si>
     <t xml:space="preserve">8.07304859161377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12057876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32808589935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37561511993408</t>
+    <t xml:space="preserve">8.12057781219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32808494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37561321258545</t>
   </si>
   <si>
     <t xml:space="preserve">8.38025093078613</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">8.41039180755615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5112476348877</t>
+    <t xml:space="preserve">8.51124572753906</t>
   </si>
   <si>
     <t xml:space="preserve">8.41386985778809</t>
@@ -2549,16 +2549,16 @@
     <t xml:space="preserve">8.40807437896729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42198371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1843376159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19245147705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09623432159424</t>
+    <t xml:space="preserve">8.42198467254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18433666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1924524307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09623527526855</t>
   </si>
   <si>
     <t xml:space="preserve">7.79019212722778</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">7.88177299499512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87713527679443</t>
+    <t xml:space="preserve">7.87713479995728</t>
   </si>
   <si>
     <t xml:space="preserve">7.89104557037354</t>
@@ -2579,91 +2579,91 @@
     <t xml:space="preserve">7.82033205032349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77859830856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70440578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65224123001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74845695495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68238115310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68701696395874</t>
+    <t xml:space="preserve">7.77859973907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70440530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65224075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7484564781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68238067626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6870174407959</t>
   </si>
   <si>
     <t xml:space="preserve">7.62093830108643</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5792064666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46328163146973</t>
+    <t xml:space="preserve">7.57920694351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46328115463257</t>
   </si>
   <si>
     <t xml:space="preserve">7.64760255813599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72411251068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8075795173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88525009155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8840913772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91191244125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82844686508179</t>
+    <t xml:space="preserve">7.72411346435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80757999420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88524961471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88409090042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91191339492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82844591140747</t>
   </si>
   <si>
     <t xml:space="preserve">7.78439474105835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7415018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58036613464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47719192504883</t>
+    <t xml:space="preserve">7.74150085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5803656578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47719144821167</t>
   </si>
   <si>
     <t xml:space="preserve">7.51196908950806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41691160202026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43777751922607</t>
+    <t xml:space="preserve">7.41691064834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43777847290039</t>
   </si>
   <si>
     <t xml:space="preserve">7.43661880493164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39024686813354</t>
+    <t xml:space="preserve">7.39024782180786</t>
   </si>
   <si>
     <t xml:space="preserve">7.36822271347046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22911214828491</t>
+    <t xml:space="preserve">7.22911167144775</t>
   </si>
   <si>
     <t xml:space="preserve">7.21867799758911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20592546463013</t>
+    <t xml:space="preserve">7.2059268951416</t>
   </si>
   <si>
     <t xml:space="preserve">7.22099685668945</t>
@@ -2672,13 +2672,13 @@
     <t xml:space="preserve">7.14680433273315</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98218965530396</t>
+    <t xml:space="preserve">6.98219013214111</t>
   </si>
   <si>
     <t xml:space="preserve">7.03783464431763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96364164352417</t>
+    <t xml:space="preserve">6.96364259719849</t>
   </si>
   <si>
     <t xml:space="preserve">7.03087949752808</t>
@@ -2687,49 +2687,49 @@
     <t xml:space="preserve">6.91263484954834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80018711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85235357284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19317483901978</t>
+    <t xml:space="preserve">6.80018663406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85235404968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19317436218262</t>
   </si>
   <si>
     <t xml:space="preserve">7.07608985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03203868865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29403066635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10739040374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1410083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11086750030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11550521850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00189828872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57297325134277</t>
+    <t xml:space="preserve">7.03203916549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29402923583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10738945007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14100933074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11086702346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1155047416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00189733505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57297229766846</t>
   </si>
   <si>
     <t xml:space="preserve">6.52544355392456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70165157318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51616954803467</t>
+    <t xml:space="preserve">6.70165061950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51617002487183</t>
   </si>
   <si>
     <t xml:space="preserve">6.27620363235474</t>
@@ -2738,40 +2738,40 @@
     <t xml:space="preserve">6.3411226272583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37126302719116</t>
+    <t xml:space="preserve">6.37126350402832</t>
   </si>
   <si>
     <t xml:space="preserve">6.2843189239502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09651947021484</t>
+    <t xml:space="preserve">6.09651851654053</t>
   </si>
   <si>
     <t xml:space="preserve">5.438063621521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40676259994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51921033859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53326511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85785627365112</t>
+    <t xml:space="preserve">5.40676307678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51921081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53326463699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85785675048828</t>
   </si>
   <si>
     <t xml:space="preserve">4.15534782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9791419506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54731941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36531567573547</t>
+    <t xml:space="preserve">3.97914123535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54731917381287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36531591415405</t>
   </si>
   <si>
     <t xml:space="preserve">3.56123042106628</t>
@@ -2780,34 +2780,34 @@
     <t xml:space="preserve">3.40994739532471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84872484207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96117281913757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99421167373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75482487678528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65744805335999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80931043624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66498398780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64295721054077</t>
+    <t xml:space="preserve">3.84872508049011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96117305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99421119689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75482535362244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65744781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80930995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66498374938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64295768737793</t>
   </si>
   <si>
     <t xml:space="preserve">3.59368896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83481431007385</t>
+    <t xml:space="preserve">3.83481383323669</t>
   </si>
   <si>
     <t xml:space="preserve">4.08289480209351</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">4.12636661529541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33503198623657</t>
+    <t xml:space="preserve">4.33503246307373</t>
   </si>
   <si>
     <t xml:space="preserve">4.32401990890503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10434007644653</t>
+    <t xml:space="preserve">4.10434055328369</t>
   </si>
   <si>
     <t xml:space="preserve">4.12057018280029</t>
@@ -2831,10 +2831,10 @@
     <t xml:space="preserve">4.24403142929077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30663013458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11419439315796</t>
+    <t xml:space="preserve">4.30663061141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11419486999512</t>
   </si>
   <si>
     <t xml:space="preserve">4.20229768753052</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">4.35010194778442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26026105880737</t>
+    <t xml:space="preserve">4.26026010513306</t>
   </si>
   <si>
     <t xml:space="preserve">4.46197128295898</t>
@@ -2852,19 +2852,19 @@
     <t xml:space="preserve">4.57383871078491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74135208129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64629173278809</t>
+    <t xml:space="preserve">4.74135112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64629220962524</t>
   </si>
   <si>
     <t xml:space="preserve">4.38430070877075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44863939285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42139673233032</t>
+    <t xml:space="preserve">4.44863986968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42139720916748</t>
   </si>
   <si>
     <t xml:space="preserve">4.40516757965088</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">4.50370407104492</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42429494857788</t>
+    <t xml:space="preserve">4.42429447174072</t>
   </si>
   <si>
     <t xml:space="preserve">4.40053081512451</t>
@@ -2888,31 +2888,31 @@
     <t xml:space="preserve">4.17505502700806</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51703500747681</t>
+    <t xml:space="preserve">4.51703548431396</t>
   </si>
   <si>
     <t xml:space="preserve">4.31242704391479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25388431549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29851627349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59934186935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72859907150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78192472457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60340023040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76511573791504</t>
+    <t xml:space="preserve">4.25388383865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29851675033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59934234619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72859954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78192567825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60339975357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7651162147522</t>
   </si>
   <si>
     <t xml:space="preserve">4.83293151855469</t>
@@ -2924,22 +2924,22 @@
     <t xml:space="preserve">5.04449605941772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39748907089233</t>
+    <t xml:space="preserve">5.39748954772949</t>
   </si>
   <si>
     <t xml:space="preserve">5.45255327224731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21316766738892</t>
+    <t xml:space="preserve">5.21316814422607</t>
   </si>
   <si>
     <t xml:space="preserve">5.0723180770874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68165016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7488865852356</t>
+    <t xml:space="preserve">4.68164920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74888610839844</t>
   </si>
   <si>
     <t xml:space="preserve">4.7506251335144</t>
@@ -2948,22 +2948,22 @@
     <t xml:space="preserve">4.88625812530518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86770963668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85263967514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8995885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96624708175659</t>
+    <t xml:space="preserve">4.86771011352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85264015197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89958953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96624660491943</t>
   </si>
   <si>
     <t xml:space="preserve">5.25374174118042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02247047424316</t>
+    <t xml:space="preserve">5.02246999740601</t>
   </si>
   <si>
     <t xml:space="preserve">5.09550285339355</t>
@@ -2972,16 +2972,16 @@
     <t xml:space="preserve">5.00508165359497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1169490814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18418645858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09260559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21606588363647</t>
+    <t xml:space="preserve">5.11694955825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18418598175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09260511398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21606540679932</t>
   </si>
   <si>
     <t xml:space="preserve">5.15868234634399</t>
@@ -2990,67 +2990,67 @@
     <t xml:space="preserve">5.21896409988403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20679140090942</t>
+    <t xml:space="preserve">5.20679187774658</t>
   </si>
   <si>
     <t xml:space="preserve">5.09840154647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00276279449463</t>
+    <t xml:space="preserve">5.00276327133179</t>
   </si>
   <si>
     <t xml:space="preserve">5.11984825134277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24910497665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2044734954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2572193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31692123413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31054544448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34184503555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35401678085327</t>
+    <t xml:space="preserve">5.24910449981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20447301864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25721883773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3169207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31054592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34184455871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35401630401611</t>
   </si>
   <si>
     <t xml:space="preserve">5.30822658538818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34126567840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26069641113281</t>
+    <t xml:space="preserve">5.3412652015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26069688796997</t>
   </si>
   <si>
     <t xml:space="preserve">5.25895833969116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37488412857056</t>
+    <t xml:space="preserve">5.3748836517334</t>
   </si>
   <si>
     <t xml:space="preserve">5.30764722824097</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99638605117798</t>
+    <t xml:space="preserve">4.99638652801514</t>
   </si>
   <si>
     <t xml:space="preserve">5.23693227767944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44270133972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44733715057373</t>
+    <t xml:space="preserve">5.44270038604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44733667373657</t>
   </si>
   <si>
     <t xml:space="preserve">5.38937425613403</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">5.38183975219727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47457933425903</t>
+    <t xml:space="preserve">5.47457981109619</t>
   </si>
   <si>
     <t xml:space="preserve">5.76323366165161</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">5.74178791046143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65716171264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61658763885498</t>
+    <t xml:space="preserve">5.65716123580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61658811569214</t>
   </si>
   <si>
     <t xml:space="preserve">5.59340381622314</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">5.58065176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47631931304932</t>
+    <t xml:space="preserve">5.47631883621216</t>
   </si>
   <si>
     <t xml:space="preserve">5.40618371963501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58007287979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51631259918213</t>
+    <t xml:space="preserve">5.5800724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51631307601929</t>
   </si>
   <si>
     <t xml:space="preserve">5.54703330993652</t>
@@ -3101,16 +3101,16 @@
     <t xml:space="preserve">5.47747802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45719051361084</t>
+    <t xml:space="preserve">5.457190990448</t>
   </si>
   <si>
     <t xml:space="preserve">5.35053968429565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28736019134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31750059127808</t>
+    <t xml:space="preserve">5.28736066818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31750106811523</t>
   </si>
   <si>
     <t xml:space="preserve">5.37836217880249</t>
@@ -3125,28 +3125,28 @@
     <t xml:space="preserve">5.57079792022705</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57137775421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73019647598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74642467498779</t>
+    <t xml:space="preserve">5.57137727737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73019599914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74642515182495</t>
   </si>
   <si>
     <t xml:space="preserve">5.78641891479492</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30750417709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.266930103302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23910856246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01537179946899</t>
+    <t xml:space="preserve">6.30750465393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26693058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23910903930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01537227630615</t>
   </si>
   <si>
     <t xml:space="preserve">5.75975608825684</t>
@@ -3155,28 +3155,28 @@
     <t xml:space="preserve">5.92263126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02232789993286</t>
+    <t xml:space="preserve">6.02232837677002</t>
   </si>
   <si>
     <t xml:space="preserve">6.01189517974854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92958688735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16491508483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02116823196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06753778457642</t>
+    <t xml:space="preserve">5.92958641052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16491460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02116870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06753826141357</t>
   </si>
   <si>
     <t xml:space="preserve">5.99914216995239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07681322097778</t>
+    <t xml:space="preserve">6.07681274414062</t>
   </si>
   <si>
     <t xml:space="preserve">6.18578290939331</t>
@@ -3188,58 +3188,58 @@
     <t xml:space="preserve">6.19041967391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1046347618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16375637054443</t>
+    <t xml:space="preserve">6.10463523864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16375684738159</t>
   </si>
   <si>
     <t xml:space="preserve">6.06058263778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12666082382202</t>
+    <t xml:space="preserve">6.12666034698486</t>
   </si>
   <si>
     <t xml:space="preserve">5.99566507339478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24954128265381</t>
+    <t xml:space="preserve">6.24954175949097</t>
   </si>
   <si>
     <t xml:space="preserve">6.22867488861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24722242355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20548915863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35735130310059</t>
+    <t xml:space="preserve">6.24722290039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20548868179321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35735177993774</t>
   </si>
   <si>
     <t xml:space="preserve">6.43386268615723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48023366928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37242221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12550115585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12318277359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11043071746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27156734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37937784194946</t>
+    <t xml:space="preserve">6.48023414611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3724217414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12550067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12318229675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11043119430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27156782150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3793773651123</t>
   </si>
   <si>
     <t xml:space="preserve">6.47443723678589</t>
@@ -3248,28 +3248,28 @@
     <t xml:space="preserve">6.51269292831421</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91031694412231</t>
+    <t xml:space="preserve">6.91031789779663</t>
   </si>
   <si>
     <t xml:space="preserve">6.99146461486816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07840871810913</t>
+    <t xml:space="preserve">7.07840824127197</t>
   </si>
   <si>
     <t xml:space="preserve">7.29750776290894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3183741569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34851503372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50037717819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46559906005859</t>
+    <t xml:space="preserve">7.31837463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34851551055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5003776550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46560001373291</t>
   </si>
   <si>
     <t xml:space="preserve">7.44705104827881</t>
@@ -3278,46 +3278,46 @@
     <t xml:space="preserve">7.58964061737061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64180660247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58616065979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66615152359009</t>
+    <t xml:space="preserve">7.64180707931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58616161346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66615056991577</t>
   </si>
   <si>
     <t xml:space="preserve">7.573410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66730928421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63948774337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66846799850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85395050048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80294275283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77048301696777</t>
+    <t xml:space="preserve">7.66731023788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63948678970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66846895217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85395002365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80294322967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77048397064209</t>
   </si>
   <si>
     <t xml:space="preserve">7.98494529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01624584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9061164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01044940948486</t>
+    <t xml:space="preserve">8.0162467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90611600875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01044845581055</t>
   </si>
   <si>
     <t xml:space="preserve">8.18781471252441</t>
@@ -3326,10 +3326,10 @@
     <t xml:space="preserve">8.29678440093994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34895133972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42082595825195</t>
+    <t xml:space="preserve">8.348952293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42082500457764</t>
   </si>
   <si>
     <t xml:space="preserve">8.25968933105469</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">8.46139907836914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51588535308838</t>
+    <t xml:space="preserve">8.51588439941406</t>
   </si>
   <si>
     <t xml:space="preserve">8.57036876678467</t>
@@ -3353,55 +3353,55 @@
     <t xml:space="preserve">8.62485408782959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60166835784912</t>
+    <t xml:space="preserve">8.60167026519775</t>
   </si>
   <si>
     <t xml:space="preserve">8.57152843475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41271018981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33503913879395</t>
+    <t xml:space="preserve">8.41271114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33504104614258</t>
   </si>
   <si>
     <t xml:space="preserve">8.50545120239258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46951389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78281021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40054321289062</t>
+    <t xml:space="preserve">8.46951484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78280925750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40054225921631</t>
   </si>
   <si>
     <t xml:space="preserve">9.27200698852539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32146167755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1196346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84830379486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43663024902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60236930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30564308166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49945068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37381076812744</t>
+    <t xml:space="preserve">9.32146263122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11963367462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84830284118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43662929534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60236835479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30564212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49944972991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37380981445312</t>
   </si>
   <si>
     <t xml:space="preserve">8.42460060119629</t>
@@ -3410,22 +3410,22 @@
     <t xml:space="preserve">8.68122863769531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69726943969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76142406463623</t>
+    <t xml:space="preserve">8.69726848602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76142501831055</t>
   </si>
   <si>
     <t xml:space="preserve">8.93117332458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08889293670654</t>
+    <t xml:space="preserve">9.08889198303223</t>
   </si>
   <si>
     <t xml:space="preserve">9.01805114746094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84295654296875</t>
+    <t xml:space="preserve">8.84295749664307</t>
   </si>
   <si>
     <t xml:space="preserve">8.79483890533447</t>
@@ -3437,28 +3437,28 @@
     <t xml:space="preserve">8.95790481567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02206134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82825469970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87770938873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94186592102051</t>
+    <t xml:space="preserve">9.02206230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82825565338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87770843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94186496734619</t>
   </si>
   <si>
     <t xml:space="preserve">8.82424449920654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86968994140625</t>
+    <t xml:space="preserve">8.86969089508057</t>
   </si>
   <si>
     <t xml:space="preserve">9.07552623748779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06082344055176</t>
+    <t xml:space="preserve">9.06082248687744</t>
   </si>
   <si>
     <t xml:space="preserve">8.97795486450195</t>
@@ -3470,13 +3470,13 @@
     <t xml:space="preserve">9.28537178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2679967880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25061988830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14369297027588</t>
+    <t xml:space="preserve">9.26799774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25062084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14369201660156</t>
   </si>
   <si>
     <t xml:space="preserve">9.6796703338623</t>
@@ -3485,13 +3485,13 @@
     <t xml:space="preserve">9.85610103607178</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0579280853271</t>
+    <t xml:space="preserve">10.0579290390015</t>
   </si>
   <si>
     <t xml:space="preserve">10.1755485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3158922195435</t>
+    <t xml:space="preserve">10.3158931732178</t>
   </si>
   <si>
     <t xml:space="preserve">10.602707862854</t>
@@ -6822,6 +6822,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.44299983978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59700012207031</t>
   </si>
 </sst>
 </file>
@@ -72082,7 +72085,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6910416667</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>20425082</v>
@@ -72103,6 +72106,32 @@
         <v>2269</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6936111111</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>25677460</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>9.63899993896484</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>9.41699981689453</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>9.59700012207031</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>2270</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2273" uniqueCount="2273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="2274">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02501344680786</t>
+    <t xml:space="preserve">4.02501440048218</t>
   </si>
   <si>
     <t xml:space="preserve">STLAM.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">4.13119506835938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91636276245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78795838356018</t>
+    <t xml:space="preserve">3.91636323928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78795790672302</t>
   </si>
   <si>
     <t xml:space="preserve">3.63238978385925</t>
@@ -59,106 +59,106 @@
     <t xml:space="preserve">3.61757373809814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71881580352783</t>
+    <t xml:space="preserve">3.71881628036499</t>
   </si>
   <si>
     <t xml:space="preserve">3.66942977905273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37804818153381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28421354293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1879096031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26939749717712</t>
+    <t xml:space="preserve">3.37804865837097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28421401977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18790912628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26939725875854</t>
   </si>
   <si>
     <t xml:space="preserve">3.06197333335876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25705099105835</t>
+    <t xml:space="preserve">3.25705122947693</t>
   </si>
   <si>
     <t xml:space="preserve">3.3261923789978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26199007034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46200561523438</t>
+    <t xml:space="preserve">3.2619903087616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46200585365295</t>
   </si>
   <si>
     <t xml:space="preserve">3.43237328529358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18544006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16321659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16074681282043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07678985595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95332288742065</t>
+    <t xml:space="preserve">3.18544054031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16321635246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16074705123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07678961753845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95332264900208</t>
   </si>
   <si>
     <t xml:space="preserve">2.91628313064575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94838428497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65700316429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58292245864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7335524559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59280037879944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68416571617126</t>
+    <t xml:space="preserve">2.94838404655457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65700340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58292269706726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73355221748352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59280014038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68416595458984</t>
   </si>
   <si>
     <t xml:space="preserve">2.80269360542297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75824522972107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89899778366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87924313545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81010150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92616009712219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83973383903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72614455223083</t>
+    <t xml:space="preserve">2.75824570655823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89899730682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87924265861511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81010127067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92616033554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83973336219788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72614431381226</t>
   </si>
   <si>
     <t xml:space="preserve">3.00517892837524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13358402252197</t>
+    <t xml:space="preserve">3.13358378410339</t>
   </si>
   <si>
     <t xml:space="preserve">3.2990300655365</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">3.46447539329529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44225120544434</t>
+    <t xml:space="preserve">3.44225072860718</t>
   </si>
   <si>
     <t xml:space="preserve">3.2891526222229</t>
@@ -182,16 +182,16 @@
     <t xml:space="preserve">3.21013307571411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35088539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.447190284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36076307296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44472026824951</t>
+    <t xml:space="preserve">3.35088586807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44718980789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36076354980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472002983093</t>
   </si>
   <si>
     <t xml:space="preserve">3.42496609687805</t>
@@ -200,19 +200,19 @@
     <t xml:space="preserve">3.51633095741272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50151538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386117935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47682166099548</t>
+    <t xml:space="preserve">3.50151562690735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386189460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47682237625122</t>
   </si>
   <si>
     <t xml:space="preserve">3.33360075950623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57559490203857</t>
+    <t xml:space="preserve">3.57559537887573</t>
   </si>
   <si>
     <t xml:space="preserve">3.5064537525177</t>
@@ -224,31 +224,31 @@
     <t xml:space="preserve">3.34841656684875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18050146102905</t>
+    <t xml:space="preserve">3.18050169944763</t>
   </si>
   <si>
     <t xml:space="preserve">3.13852286338806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01505661010742</t>
+    <t xml:space="preserve">3.01505637168884</t>
   </si>
   <si>
     <t xml:space="preserve">3.13605380058289</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21260285377502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16815519332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3187837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35335493087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40274143218994</t>
+    <t xml:space="preserve">3.21260333061218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16815495491028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31878423690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35335516929626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4027419090271</t>
   </si>
   <si>
     <t xml:space="preserve">3.56571769714355</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">3.54596304893494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56818699836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47435307502747</t>
+    <t xml:space="preserve">3.56818747520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47435259819031</t>
   </si>
   <si>
     <t xml:space="preserve">3.53361654281616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41014957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3829870223999</t>
+    <t xml:space="preserve">3.41015005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38298654556274</t>
   </si>
   <si>
     <t xml:space="preserve">3.29656004905701</t>
@@ -281,40 +281,40 @@
     <t xml:space="preserve">3.3657021522522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31631517410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38051772117615</t>
+    <t xml:space="preserve">3.3163149356842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38051724433899</t>
   </si>
   <si>
     <t xml:space="preserve">3.33113074302673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10889053344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11382937431335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10148286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629915237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97801661491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06938195228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12370753288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07185077667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15827775001526</t>
+    <t xml:space="preserve">3.10889101028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11382985115051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10148334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629867553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97801637649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06938219070435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12370681762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07185101509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15827798843384</t>
   </si>
   <si>
     <t xml:space="preserve">3.07432055473328</t>
@@ -329,22 +329,22 @@
     <t xml:space="preserve">3.14840054512024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12123775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9310986995697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87677383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89652824401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86195778846741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93356776237488</t>
+    <t xml:space="preserve">3.1212375164032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93109893798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87677359580994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89652848243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86195755004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93356847763062</t>
   </si>
   <si>
     <t xml:space="preserve">3.09407520294189</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">3.1113600730896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.819979429245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64465641975403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66194128990173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7137975692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.770592212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.533536195755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52365875244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54835176467896</t>
+    <t xml:space="preserve">2.81997895240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64465618133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66194176673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71379780769348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77059245109558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53353595733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52365851402283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54835200309753</t>
   </si>
   <si>
     <t xml:space="preserve">2.84714150428772</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">2.95826125144958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08913564682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09901452064514</t>
+    <t xml:space="preserve">3.08913588523865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09901428222656</t>
   </si>
   <si>
     <t xml:space="preserve">3.12617659568787</t>
@@ -413,160 +413,160 @@
     <t xml:space="preserve">3.06691193580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84467220306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81257104873657</t>
+    <t xml:space="preserve">2.84467196464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81257128715515</t>
   </si>
   <si>
     <t xml:space="preserve">2.69157338142395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91381335258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88665080070496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05703473091125</t>
+    <t xml:space="preserve">2.91381359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88665127754211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05703449249268</t>
   </si>
   <si>
     <t xml:space="preserve">2.98789405822754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96073126792908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97307825088501</t>
+    <t xml:space="preserve">2.9607310295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97307753562927</t>
   </si>
   <si>
     <t xml:space="preserve">2.8841814994812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91875267028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03481030464172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02987194061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04468822479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99283242225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05950379371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97554707527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95085382461548</t>
+    <t xml:space="preserve">2.91875290870667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0348105430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02987217903137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04468846321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99283289909363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05950427055359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97554683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9508535861969</t>
   </si>
   <si>
     <t xml:space="preserve">2.96813941001892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90393614768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86442756652832</t>
+    <t xml:space="preserve">2.90393590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86442732810974</t>
   </si>
   <si>
     <t xml:space="preserve">2.87430453300476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81504058837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90146708488464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83232545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86689639091492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74096035957336</t>
+    <t xml:space="preserve">2.81504034996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90146732330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83232522010803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8668966293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74096012115479</t>
   </si>
   <si>
     <t xml:space="preserve">2.70885896682739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7903470993042</t>
+    <t xml:space="preserve">2.79034686088562</t>
   </si>
   <si>
     <t xml:space="preserve">2.82491779327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84220290184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89158964157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87183451652527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90887427330017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76812314987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82244825363159</t>
+    <t xml:space="preserve">2.84220314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89158987998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87183523178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90887475013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76812291145325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82244777679443</t>
   </si>
   <si>
     <t xml:space="preserve">2.85948777198792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93850684165955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25211191177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29409098625183</t>
+    <t xml:space="preserve">2.93850708007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25211262702942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29409122467041</t>
   </si>
   <si>
     <t xml:space="preserve">3.25952005386353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03234195709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02740335464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16568565368652</t>
+    <t xml:space="preserve">3.03234171867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0274031162262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16568541526794</t>
   </si>
   <si>
     <t xml:space="preserve">3.52373957633972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39780282974243</t>
+    <t xml:space="preserve">3.39780330657959</t>
   </si>
   <si>
     <t xml:space="preserve">3.47188282012939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45953583717346</t>
+    <t xml:space="preserve">3.45953607559204</t>
   </si>
   <si>
     <t xml:space="preserve">3.4792914390564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49410700798035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55584073066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58547210693359</t>
+    <t xml:space="preserve">3.49410676956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55584001541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58547258377075</t>
   </si>
   <si>
     <t xml:space="preserve">3.57065606117249</t>
@@ -581,19 +581,19 @@
     <t xml:space="preserve">3.62251257896423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55830979347229</t>
+    <t xml:space="preserve">3.55830931663513</t>
   </si>
   <si>
     <t xml:space="preserve">3.72128534317017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81265211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85709929466248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93364834785461</t>
+    <t xml:space="preserve">3.81265115737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85709977149963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93364882469177</t>
   </si>
   <si>
     <t xml:space="preserve">3.93117904663086</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">3.97315764427185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00525951385498</t>
+    <t xml:space="preserve">4.00525903701782</t>
   </si>
   <si>
     <t xml:space="preserve">3.99044322967529</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">4.15341854095459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19539737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21762132644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29664039611816</t>
+    <t xml:space="preserve">4.19539785385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21762228012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29664087295532</t>
   </si>
   <si>
     <t xml:space="preserve">4.30651807785034</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">4.30898714065552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27935457229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42257642745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50653409957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53863525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57073640823364</t>
+    <t xml:space="preserve">4.27935552597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42257690429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5065336227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53863573074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5707368850708</t>
   </si>
   <si>
     <t xml:space="preserve">4.88928031921387</t>
@@ -656,34 +656,34 @@
     <t xml:space="preserve">4.95842218399048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0127477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17078495025635</t>
+    <t xml:space="preserve">5.01274824142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17078447341919</t>
   </si>
   <si>
     <t xml:space="preserve">4.33615064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53616571426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34602689743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39047574996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41516828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62753105163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64234685897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71889686584473</t>
+    <t xml:space="preserve">4.53616619110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34602737426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39047479629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41516780853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6275315284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64234733581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71889734268188</t>
   </si>
   <si>
     <t xml:space="preserve">4.99793195724487</t>
@@ -692,31 +692,31 @@
     <t xml:space="preserve">5.0423789024353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10164403915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12633752822876</t>
+    <t xml:space="preserve">5.10164308547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1263370513916</t>
   </si>
   <si>
     <t xml:space="preserve">4.95348405838013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98805379867554</t>
+    <t xml:space="preserve">4.98805332183838</t>
   </si>
   <si>
     <t xml:space="preserve">4.99299240112305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00287055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04731750488281</t>
+    <t xml:space="preserve">5.00287008285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04731702804565</t>
   </si>
   <si>
     <t xml:space="preserve">4.92385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78062915802002</t>
+    <t xml:space="preserve">4.78062963485718</t>
   </si>
   <si>
     <t xml:space="preserve">4.8991584777832</t>
@@ -728,13 +728,13 @@
     <t xml:space="preserve">5.33869981765747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34363746643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32388257980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25474262237549</t>
+    <t xml:space="preserve">5.34363794326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32388353347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25474214553833</t>
   </si>
   <si>
     <t xml:space="preserve">5.32882213592529</t>
@@ -743,43 +743,43 @@
     <t xml:space="preserve">5.1757230758667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14609098434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18560075759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18066167831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13127517700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13621425628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16584587097168</t>
+    <t xml:space="preserve">5.14609003067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18560028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18066263198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13127565383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13621473312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16584634780884</t>
   </si>
   <si>
     <t xml:space="preserve">5.09670448303223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14115285873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22511005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30412912368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21029424667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98311567306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94360589981079</t>
+    <t xml:space="preserve">5.14115190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22511053085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2102952003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98311519622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94360542297363</t>
   </si>
   <si>
     <t xml:space="preserve">4.96336078643799</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">5.06213426589966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81026220321655</t>
+    <t xml:space="preserve">4.81026268005371</t>
   </si>
   <si>
     <t xml:space="preserve">4.83248567581177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74359035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78556776046753</t>
+    <t xml:space="preserve">4.74358987808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78556823730469</t>
   </si>
   <si>
     <t xml:space="preserve">4.73371267318726</t>
@@ -821,76 +821,76 @@
     <t xml:space="preserve">4.69420289993286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51888036727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45220851898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64728593826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70408058166504</t>
+    <t xml:space="preserve">4.51887989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45220899581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6472864151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70408010482788</t>
   </si>
   <si>
     <t xml:space="preserve">4.63000059127808</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79297733306885</t>
+    <t xml:space="preserve">4.79297685623169</t>
   </si>
   <si>
     <t xml:space="preserve">4.78803777694702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23498678207397</t>
+    <t xml:space="preserve">5.23498773574829</t>
   </si>
   <si>
     <t xml:space="preserve">4.91644334793091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97323799133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05225801467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03744077682495</t>
+    <t xml:space="preserve">4.97323751449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0522575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03744029998779</t>
   </si>
   <si>
     <t xml:space="preserve">4.91891288757324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94854497909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02262401580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76828384399414</t>
+    <t xml:space="preserve">4.9485445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02262496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76828336715698</t>
   </si>
   <si>
     <t xml:space="preserve">4.62012386322021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80038547515869</t>
+    <t xml:space="preserve">4.80038452148438</t>
   </si>
   <si>
     <t xml:space="preserve">4.72383546829224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68926477432251</t>
+    <t xml:space="preserve">4.68926525115967</t>
   </si>
   <si>
     <t xml:space="preserve">4.66210222244263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67197847366333</t>
+    <t xml:space="preserve">4.67197942733765</t>
   </si>
   <si>
     <t xml:space="preserve">4.59049129486084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58308362960815</t>
+    <t xml:space="preserve">4.583083152771</t>
   </si>
   <si>
     <t xml:space="preserve">4.61518526077271</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">4.84730195999146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83001661300659</t>
+    <t xml:space="preserve">4.83001613616943</t>
   </si>
   <si>
     <t xml:space="preserve">4.75346708297729</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">4.80532360076904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75099897384644</t>
+    <t xml:space="preserve">4.75099849700928</t>
   </si>
   <si>
     <t xml:space="preserve">4.79544687271118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81767082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78309917449951</t>
+    <t xml:space="preserve">4.8176703453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78309965133667</t>
   </si>
   <si>
     <t xml:space="preserve">4.7213659286499</t>
@@ -926,67 +926,67 @@
     <t xml:space="preserve">4.68432569503784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85224056243896</t>
+    <t xml:space="preserve">4.85224008560181</t>
   </si>
   <si>
     <t xml:space="preserve">4.778160572052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76087522506714</t>
+    <t xml:space="preserve">4.7608757019043</t>
   </si>
   <si>
     <t xml:space="preserve">4.55839014053345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85507822036743</t>
+    <t xml:space="preserve">4.85507869720459</t>
   </si>
   <si>
     <t xml:space="preserve">4.8600378036499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7856502532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82532262802124</t>
+    <t xml:space="preserve">4.78564929962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82532215118408</t>
   </si>
   <si>
     <t xml:space="preserve">4.80548572540283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87243509292603</t>
+    <t xml:space="preserve">4.87243556976318</t>
   </si>
   <si>
     <t xml:space="preserve">4.95922231674194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9988956451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19230461120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1526312828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17246866226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10799884796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17742729187012</t>
+    <t xml:space="preserve">4.99889612197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19230508804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15263223648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1724681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10799837112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17742776870728</t>
   </si>
   <si>
     <t xml:space="preserve">4.97409963607788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97905874252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98897790908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03856992721558</t>
+    <t xml:space="preserve">4.97905969619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98897743225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03856945037842</t>
   </si>
   <si>
     <t xml:space="preserve">5.03360986709595</t>
@@ -998,16 +998,16 @@
     <t xml:space="preserve">5.07328414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02865123748779</t>
+    <t xml:space="preserve">5.02865076065063</t>
   </si>
   <si>
     <t xml:space="preserve">5.07824277877808</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06336545944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95178318023682</t>
+    <t xml:space="preserve">5.06336498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95178365707397</t>
   </si>
   <si>
     <t xml:space="preserve">4.95426273345947</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">4.86995649337769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26669454574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40555191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34604215621948</t>
+    <t xml:space="preserve">5.26669406890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40555238723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34604167938232</t>
   </si>
   <si>
     <t xml:space="preserve">5.30636787414551</t>
@@ -1031,43 +1031,43 @@
     <t xml:space="preserve">5.67334985733032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68822813034058</t>
+    <t xml:space="preserve">5.68822765350342</t>
   </si>
   <si>
     <t xml:space="preserve">6.01553583145142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19406890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14943647384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16431331634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07008838653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13951635360718</t>
+    <t xml:space="preserve">6.19406843185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14943599700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1643123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07008790969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13951683044434</t>
   </si>
   <si>
     <t xml:space="preserve">6.27341651916504</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61560201644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53129529953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50650024414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78421592712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70982837677002</t>
+    <t xml:space="preserve">6.61560249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53129482269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50649929046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78421545028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70982885360718</t>
   </si>
   <si>
     <t xml:space="preserve">6.7247052192688</t>
@@ -1076,16 +1076,16 @@
     <t xml:space="preserve">6.76933813095093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80405282974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96770620346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88339996337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99250364303589</t>
+    <t xml:space="preserve">6.80405235290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96770763397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88340044021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99250268936157</t>
   </si>
   <si>
     <t xml:space="preserve">7.07681035995483</t>
@@ -1097,91 +1097,91 @@
     <t xml:space="preserve">7.18095397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46363019943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31485271453857</t>
+    <t xml:space="preserve">7.46362972259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31485366821289</t>
   </si>
   <si>
     <t xml:space="preserve">7.3346905708313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38428258895874</t>
+    <t xml:space="preserve">7.38428163528442</t>
   </si>
   <si>
     <t xml:space="preserve">7.36444520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51818084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58265018463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56281471252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53801870346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49338483810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40907907485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52314138412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41403770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50330209732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4239559173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45867109298706</t>
+    <t xml:space="preserve">7.51818180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58265113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5628137588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53801727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49338388442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4090781211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52313947677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4140362739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50330400466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42395496368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45867013931274</t>
   </si>
   <si>
     <t xml:space="preserve">7.41899633407593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3098931312561</t>
+    <t xml:space="preserve">7.30989456176758</t>
   </si>
   <si>
     <t xml:space="preserve">7.37932300567627</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93795299530029</t>
+    <t xml:space="preserve">6.93795204162598</t>
   </si>
   <si>
     <t xml:space="preserve">7.05697298049927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02225923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1412787437439</t>
+    <t xml:space="preserve">7.02225828170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14127969741821</t>
   </si>
   <si>
     <t xml:space="preserve">7.34956741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3594856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51322031021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76614189147949</t>
+    <t xml:space="preserve">7.35948657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5132212638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76614141464233</t>
   </si>
   <si>
     <t xml:space="preserve">7.73142719268799</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66199731826782</t>
+    <t xml:space="preserve">7.66199922561646</t>
   </si>
   <si>
     <t xml:space="preserve">7.45371150970459</t>
@@ -1190,28 +1190,28 @@
     <t xml:space="preserve">7.28013753890991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33964920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37436246871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25038242340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43387317657471</t>
+    <t xml:space="preserve">7.33964872360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3743634223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25038385391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43387413024902</t>
   </si>
   <si>
     <t xml:space="preserve">7.55785417556763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24046421051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20078992843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1710352897644</t>
+    <t xml:space="preserve">7.24046325683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20079040527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17103624343872</t>
   </si>
   <si>
     <t xml:space="preserve">7.15119886398315</t>
@@ -1220,25 +1220,25 @@
     <t xml:space="preserve">7.00738143920898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23550462722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19087171554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53305912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52810001373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50826263427734</t>
+    <t xml:space="preserve">7.2355055809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19087219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53305864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52809906005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50826358795166</t>
   </si>
   <si>
     <t xml:space="preserve">7.43883275985718</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4487509727478</t>
+    <t xml:space="preserve">7.44875192642212</t>
   </si>
   <si>
     <t xml:space="preserve">7.6372013092041</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">7.67191648483276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54297685623169</t>
+    <t xml:space="preserve">7.54297733306885</t>
   </si>
   <si>
     <t xml:space="preserve">7.39420080184937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71159076690674</t>
+    <t xml:space="preserve">7.71158981323242</t>
   </si>
   <si>
     <t xml:space="preserve">8.35628986358643</t>
@@ -1274,43 +1274,43 @@
     <t xml:space="preserve">8.98115062713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15968418121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21423435211182</t>
+    <t xml:space="preserve">9.15968322753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2142333984375</t>
   </si>
   <si>
     <t xml:space="preserve">9.42252254486084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48699188232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69032001495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28862380981445</t>
+    <t xml:space="preserve">9.48699378967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69032096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28862190246582</t>
   </si>
   <si>
     <t xml:space="preserve">9.32829761505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50186920166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69527912139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76470947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70519638061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64072799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63080883026123</t>
+    <t xml:space="preserve">9.50187110900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69528007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76470756530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7052001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64072704315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63080978393555</t>
   </si>
   <si>
     <t xml:space="preserve">9.819260597229</t>
@@ -1325,25 +1325,25 @@
     <t xml:space="preserve">9.65163993835449</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5385684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31937026977539</t>
+    <t xml:space="preserve">9.53856754302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31936931610107</t>
   </si>
   <si>
     <t xml:space="preserve">8.75798606872559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35111045837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89982032775879</t>
+    <t xml:space="preserve">9.35110950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89982223510742</t>
   </si>
   <si>
     <t xml:space="preserve">8.63698196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75302791595459</t>
+    <t xml:space="preserve">8.75302600860596</t>
   </si>
   <si>
     <t xml:space="preserve">8.57548713684082</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">8.77782249450684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82741546630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0039644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83733367919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94643783569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98908710479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80956268310547</t>
+    <t xml:space="preserve">8.82741641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00396537780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8373327255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94643688201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98908615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80956172943115</t>
   </si>
   <si>
     <t xml:space="preserve">8.73814964294434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6905403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80559539794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71434497833252</t>
+    <t xml:space="preserve">8.69054126739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80559635162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71434593200684</t>
   </si>
   <si>
     <t xml:space="preserve">8.47431945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98930644989014</t>
+    <t xml:space="preserve">7.98930835723877</t>
   </si>
   <si>
     <t xml:space="preserve">8.01410293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46836757659912</t>
+    <t xml:space="preserve">8.46836853027344</t>
   </si>
   <si>
     <t xml:space="preserve">8.556640625</t>
@@ -1403,28 +1403,28 @@
     <t xml:space="preserve">8.51597595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52787780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53085517883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43266105651855</t>
+    <t xml:space="preserve">8.52787685394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53085327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43266201019287</t>
   </si>
   <si>
     <t xml:space="preserve">8.53184604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52589416503906</t>
+    <t xml:space="preserve">8.52589321136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.35926532745361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56457614898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71732044219971</t>
+    <t xml:space="preserve">8.5645751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71732139587402</t>
   </si>
   <si>
     <t xml:space="preserve">8.42175197601318</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">8.25115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1886682510376</t>
+    <t xml:space="preserve">8.18866729736328</t>
   </si>
   <si>
     <t xml:space="preserve">8.32554244995117</t>
@@ -1442,10 +1442,10 @@
     <t xml:space="preserve">8.15791988372803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18370914459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78278350830078</t>
+    <t xml:space="preserve">8.18370723724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78278255462646</t>
   </si>
   <si>
     <t xml:space="preserve">8.73517322540283</t>
@@ -1457,19 +1457,19 @@
     <t xml:space="preserve">9.07438373565674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18943977355957</t>
+    <t xml:space="preserve">9.18943881988525</t>
   </si>
   <si>
     <t xml:space="preserve">9.31341934204102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22613620758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4076452255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4364070892334</t>
+    <t xml:space="preserve">9.22613716125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40764427185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43640804290771</t>
   </si>
   <si>
     <t xml:space="preserve">9.36301136016846</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">9.70916557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76768493652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63180160522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55840587615967</t>
+    <t xml:space="preserve">9.76768398284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63180255889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55840492248535</t>
   </si>
   <si>
     <t xml:space="preserve">9.7597484588623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79148960113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393463134766</t>
+    <t xml:space="preserve">9.79148769378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393558502197</t>
   </si>
   <si>
     <t xml:space="preserve">9.68635272979736</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">9.41458797454834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20927619934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43739986419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2182035446167</t>
+    <t xml:space="preserve">9.20927715301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43739891052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21820163726807</t>
   </si>
   <si>
     <t xml:space="preserve">9.51674747467041</t>
@@ -1517,46 +1517,46 @@
     <t xml:space="preserve">9.53559303283691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48004913330078</t>
+    <t xml:space="preserve">9.48005104064941</t>
   </si>
   <si>
     <t xml:space="preserve">9.29556560516357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30845832824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42946529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41756343841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36697864532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30746841430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36796951293945</t>
+    <t xml:space="preserve">9.30845928192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42946434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41756439208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36697959899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30746936798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36796855926514</t>
   </si>
   <si>
     <t xml:space="preserve">9.1993579864502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43938541412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59609413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48600101470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31143474578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30548572540283</t>
+    <t xml:space="preserve">9.43938446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59609508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31143665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3054838180542</t>
   </si>
   <si>
     <t xml:space="preserve">9.10810852050781</t>
@@ -1565,28 +1565,28 @@
     <t xml:space="preserve">9.06446552276611</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42748069763184</t>
+    <t xml:space="preserve">9.42747974395752</t>
   </si>
   <si>
     <t xml:space="preserve">9.62089061737061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.185471534729</t>
+    <t xml:space="preserve">9.18547058105469</t>
   </si>
   <si>
     <t xml:space="preserve">8.85221099853516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87601470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8621301651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13984680175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90676212310791</t>
+    <t xml:space="preserve">8.87601566314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86212921142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13984775543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90676307678223</t>
   </si>
   <si>
     <t xml:space="preserve">8.98313522338867</t>
@@ -1610,10 +1610,10 @@
     <t xml:space="preserve">8.79666900634766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75005054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38505458831787</t>
+    <t xml:space="preserve">8.75005149841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38505363464355</t>
   </si>
   <si>
     <t xml:space="preserve">8.18172454833984</t>
@@ -1625,64 +1625,64 @@
     <t xml:space="preserve">8.15296173095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24123573303223</t>
+    <t xml:space="preserve">8.24123668670654</t>
   </si>
   <si>
     <t xml:space="preserve">7.95558452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1003942489624</t>
+    <t xml:space="preserve">8.10039234161377</t>
   </si>
   <si>
     <t xml:space="preserve">8.10237693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03890037536621</t>
+    <t xml:space="preserve">8.03889942169189</t>
   </si>
   <si>
     <t xml:space="preserve">8.50506687164307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40687274932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46935939788818</t>
+    <t xml:space="preserve">8.40687370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4693603515625</t>
   </si>
   <si>
     <t xml:space="preserve">8.52291965484619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2630558013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21346378326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25214576721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19957733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24916934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22238922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33347797393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14105892181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01906108856201</t>
+    <t xml:space="preserve">8.26305675506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21346473693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25214672088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19957828521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24917030334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22239017486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33347702026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14105987548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01906204223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.21048831939697</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16111707687378</t>
+    <t xml:space="preserve">7.16111612319946</t>
   </si>
   <si>
     <t xml:space="preserve">7.26426839828491</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">7.23947334289551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04804658889771</t>
+    <t xml:space="preserve">7.04804563522339</t>
   </si>
   <si>
     <t xml:space="preserve">7.04209566116333</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">7.23352098464966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20277500152588</t>
+    <t xml:space="preserve">7.20277404785156</t>
   </si>
   <si>
     <t xml:space="preserve">7.24839878082275</t>
@@ -1715,22 +1715,22 @@
     <t xml:space="preserve">7.04407978057861</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97663402557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80802059173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79909420013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01729965209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12243509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03713607788086</t>
+    <t xml:space="preserve">6.97663259506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.808021068573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79909229278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01729869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12243413925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03713655471802</t>
   </si>
   <si>
     <t xml:space="preserve">6.95977210998535</t>
@@ -1742,16 +1742,16 @@
     <t xml:space="preserve">7.4348669052124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42693185806274</t>
+    <t xml:space="preserve">7.42693138122559</t>
   </si>
   <si>
     <t xml:space="preserve">7.36146926879883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.220627784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26823616027832</t>
+    <t xml:space="preserve">7.22062683105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.268235206604</t>
   </si>
   <si>
     <t xml:space="preserve">7.39320802688599</t>
@@ -1763,10 +1763,10 @@
     <t xml:space="preserve">7.21566820144653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16706657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48247575759888</t>
+    <t xml:space="preserve">7.167067527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48247480392456</t>
   </si>
   <si>
     <t xml:space="preserve">7.40610218048096</t>
@@ -1784,19 +1784,19 @@
     <t xml:space="preserve">7.61934852600098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7334098815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66001415252686</t>
+    <t xml:space="preserve">7.73341131210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66001462936401</t>
   </si>
   <si>
     <t xml:space="preserve">7.70266437530518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66794967651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51024675369263</t>
+    <t xml:space="preserve">7.66794872283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51024627685547</t>
   </si>
   <si>
     <t xml:space="preserve">7.68282651901245</t>
@@ -1808,52 +1808,52 @@
     <t xml:space="preserve">7.64017772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57769060134888</t>
+    <t xml:space="preserve">7.57769250869751</t>
   </si>
   <si>
     <t xml:space="preserve">7.52016448974609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34460878372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42197227478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01035737991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96274757385254</t>
+    <t xml:space="preserve">7.34460783004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42197179794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01035642623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96274852752686</t>
   </si>
   <si>
     <t xml:space="preserve">6.92803382873535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94588613510132</t>
+    <t xml:space="preserve">6.94588708877563</t>
   </si>
   <si>
     <t xml:space="preserve">7.17797803878784</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87744951248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82587385177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66618633270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8645544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95183849334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78024768829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04705429077148</t>
+    <t xml:space="preserve">6.87744998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82587432861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66618680953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86455631256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95183897018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78024816513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04705476760864</t>
   </si>
   <si>
     <t xml:space="preserve">6.81992197036743</t>
@@ -1865,13 +1865,13 @@
     <t xml:space="preserve">6.75247669219971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0292010307312</t>
+    <t xml:space="preserve">7.02920198440552</t>
   </si>
   <si>
     <t xml:space="preserve">7.11251592636108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09664678573608</t>
+    <t xml:space="preserve">7.09664583206177</t>
   </si>
   <si>
     <t xml:space="preserve">7.26129388809204</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">7.28708171844482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08672761917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30394268035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23054599761963</t>
+    <t xml:space="preserve">7.08672666549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30394172668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23054504394531</t>
   </si>
   <si>
     <t xml:space="preserve">7.1333441734314</t>
@@ -1895,22 +1895,22 @@
     <t xml:space="preserve">7.12838649749756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94291210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01234102249146</t>
+    <t xml:space="preserve">6.94291019439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01233911514282</t>
   </si>
   <si>
     <t xml:space="preserve">6.93001747131348</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99051952362061</t>
+    <t xml:space="preserve">6.99052000045776</t>
   </si>
   <si>
     <t xml:space="preserve">7.33865690231323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34758329391479</t>
+    <t xml:space="preserve">7.34758234024048</t>
   </si>
   <si>
     <t xml:space="preserve">7.30493354797363</t>
@@ -1919,37 +1919,37 @@
     <t xml:space="preserve">7.49636030197144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34857511520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23451375961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86554670333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82488203048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61064195632935</t>
+    <t xml:space="preserve">7.34857559204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2345118522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86554622650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8248815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61064291000366</t>
   </si>
   <si>
     <t xml:space="preserve">6.7832236289978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9161319732666</t>
+    <t xml:space="preserve">6.91613245010376</t>
   </si>
   <si>
     <t xml:space="preserve">6.92208194732666</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86852312088013</t>
+    <t xml:space="preserve">6.86852216720581</t>
   </si>
   <si>
     <t xml:space="preserve">6.82884883880615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82289886474609</t>
+    <t xml:space="preserve">6.82289838790894</t>
   </si>
   <si>
     <t xml:space="preserve">6.72272205352783</t>
@@ -1961,25 +1961,25 @@
     <t xml:space="preserve">6.25754642486572</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28928518295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23175859451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1573691368103</t>
+    <t xml:space="preserve">6.28928565979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23175811767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15737009048462</t>
   </si>
   <si>
     <t xml:space="preserve">6.50253295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55113220214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6284966468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87645721435547</t>
+    <t xml:space="preserve">6.55113172531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62849617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87645626068115</t>
   </si>
   <si>
     <t xml:space="preserve">7.01134824752808</t>
@@ -2003,79 +2003,79 @@
     <t xml:space="preserve">7.26724338531494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18690538406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18987894058228</t>
+    <t xml:space="preserve">7.1869044303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18988084793091</t>
   </si>
   <si>
     <t xml:space="preserve">7.28509712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39816665649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.473548412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52710628509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6354398727417</t>
+    <t xml:space="preserve">7.39816856384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47354793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52710723876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63544034957886</t>
   </si>
   <si>
     <t xml:space="preserve">6.44302177429199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41822528839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3973970413208</t>
+    <t xml:space="preserve">6.4182243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39739608764648</t>
   </si>
   <si>
     <t xml:space="preserve">6.4975733757019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40731477737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4598822593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44897222518921</t>
+    <t xml:space="preserve">6.40731430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45988321304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44897317886353</t>
   </si>
   <si>
     <t xml:space="preserve">6.45194721221924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57692050933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.501540184021</t>
+    <t xml:space="preserve">6.57691955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50154113769531</t>
   </si>
   <si>
     <t xml:space="preserve">6.51145887374878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54617309570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45591640472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43806171417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41227436065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3626823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41524887084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64932489395142</t>
+    <t xml:space="preserve">6.54617214202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4559154510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43806219100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41227340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36268186569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41524934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64932441711426</t>
   </si>
   <si>
     <t xml:space="preserve">6.32697534561157</t>
@@ -2084,58 +2084,58 @@
     <t xml:space="preserve">6.36664962768555</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35871362686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30416250228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25853824615479</t>
+    <t xml:space="preserve">6.35871458053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30416345596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2585391998291</t>
   </si>
   <si>
     <t xml:space="preserve">6.26548147201538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32003307342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63643074035645</t>
+    <t xml:space="preserve">6.32003164291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63643026351929</t>
   </si>
   <si>
     <t xml:space="preserve">6.469801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49658012390137</t>
+    <t xml:space="preserve">6.49658060073853</t>
   </si>
   <si>
     <t xml:space="preserve">6.33590221405029</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46384954452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4916205406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66122722625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52633476257324</t>
+    <t xml:space="preserve">6.4638500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49162197113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66122817993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52633666992188</t>
   </si>
   <si>
     <t xml:space="preserve">6.58188009262085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73958253860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8060359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80901145935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81000423431396</t>
+    <t xml:space="preserve">6.73958206176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80603504180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80901193618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81000375747681</t>
   </si>
   <si>
     <t xml:space="preserve">6.93894338607788</t>
@@ -2144,13 +2144,13 @@
     <t xml:space="preserve">6.86157941818237</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89133548736572</t>
+    <t xml:space="preserve">6.89133453369141</t>
   </si>
   <si>
     <t xml:space="preserve">6.89232778549194</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04308795928955</t>
+    <t xml:space="preserve">7.04308700561523</t>
   </si>
   <si>
     <t xml:space="preserve">7.0936713218689</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">7.29303216934204</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28431081771851</t>
+    <t xml:space="preserve">7.28431129455566</t>
   </si>
   <si>
     <t xml:space="preserve">7.20211410522461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14384889602661</t>
+    <t xml:space="preserve">7.14384794235229</t>
   </si>
   <si>
     <t xml:space="preserve">7.20939779281616</t>
@@ -2186,40 +2186,40 @@
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11263370513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07205581665039</t>
+    <t xml:space="preserve">7.11263465881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07205677032471</t>
   </si>
   <si>
     <t xml:space="preserve">6.80673742294312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73806571960449</t>
+    <t xml:space="preserve">6.73806667327881</t>
   </si>
   <si>
     <t xml:space="preserve">6.61112928390503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71309518814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81402015686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88997459411621</t>
+    <t xml:space="preserve">6.71309566497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81402063369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88997411727905</t>
   </si>
   <si>
     <t xml:space="preserve">6.9544825553894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93350124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88365411758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82685041427612</t>
+    <t xml:space="preserve">6.93350172042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88365364074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82684993743896</t>
   </si>
   <si>
     <t xml:space="preserve">6.62166213989258</t>
@@ -2228,70 +2228,70 @@
     <t xml:space="preserve">6.64021015167236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16998958587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10622978210449</t>
+    <t xml:space="preserve">7.16999053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10623168945312</t>
   </si>
   <si>
     <t xml:space="preserve">7.019287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96132326126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6297779083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59268140792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84771585464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78163957595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78743505477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7642502784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8813362121582</t>
+    <t xml:space="preserve">6.96132373809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62977743148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59268093109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84771728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78163909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78743457794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76425075531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88133478164673</t>
   </si>
   <si>
     <t xml:space="preserve">6.94625377655029</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83728408813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89524555206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8627872467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92422819137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98566818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06449699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15028238296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13521289825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14216661453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02160501480103</t>
+    <t xml:space="preserve">6.83728361129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89524507522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86278676986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92422866821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98566722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06449747085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15028142929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13521099090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14216709136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02160549163818</t>
   </si>
   <si>
     <t xml:space="preserve">7.03319787979126</t>
@@ -2300,46 +2300,46 @@
     <t xml:space="preserve">7.08072662353516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10970878601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15723752975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13057565689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33112573623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35315132141113</t>
+    <t xml:space="preserve">7.10970783233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15723848342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13057518005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33112668991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35315227508545</t>
   </si>
   <si>
     <t xml:space="preserve">7.32532930374146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28939342498779</t>
+    <t xml:space="preserve">7.28939247131348</t>
   </si>
   <si>
     <t xml:space="preserve">7.20940446853638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20476722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28707313537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28591537475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05986166000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07493209838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9590048789978</t>
+    <t xml:space="preserve">7.20476675033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28707504272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28591442108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05986070632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07493114471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95900535583496</t>
   </si>
   <si>
     <t xml:space="preserve">7.17578554153442</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">7.08768320083618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.976393699646</t>
+    <t xml:space="preserve">6.97639417648315</t>
   </si>
   <si>
     <t xml:space="preserve">6.99841928482056</t>
@@ -2363,43 +2363,43 @@
     <t xml:space="preserve">6.76541042327881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81873559951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86858320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72715330123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7236762046814</t>
+    <t xml:space="preserve">6.81873607635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8685827255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72715377807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72367668151855</t>
   </si>
   <si>
     <t xml:space="preserve">6.82569122314453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5857253074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40719985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52660226821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4663233757019</t>
+    <t xml:space="preserve">6.58572435379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40719938278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52660369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46632289886475</t>
   </si>
   <si>
     <t xml:space="preserve">6.68194389343262</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6900577545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54515075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.635573387146</t>
+    <t xml:space="preserve">6.69005727767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54515171051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63557291030884</t>
   </si>
   <si>
     <t xml:space="preserve">6.74454259872437</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">6.80482387542725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86162805557251</t>
+    <t xml:space="preserve">6.86162757873535</t>
   </si>
   <si>
     <t xml:space="preserve">6.86394691467285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08304452896118</t>
+    <t xml:space="preserve">7.0830454826355</t>
   </si>
   <si>
     <t xml:space="preserve">7.29055309295654</t>
@@ -2423,34 +2423,34 @@
     <t xml:space="preserve">7.30562257766724</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37285804748535</t>
+    <t xml:space="preserve">7.37285900115967</t>
   </si>
   <si>
     <t xml:space="preserve">7.28243637084961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28127765655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29287052154541</t>
+    <t xml:space="preserve">7.28127908706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29287147521973</t>
   </si>
   <si>
     <t xml:space="preserve">7.18158292770386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18737936019897</t>
+    <t xml:space="preserve">7.18737840652466</t>
   </si>
   <si>
     <t xml:space="preserve">7.07029342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92654705047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83148670196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84539842605591</t>
+    <t xml:space="preserve">6.92654657363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83148717880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84539890289307</t>
   </si>
   <si>
     <t xml:space="preserve">6.87785673141479</t>
@@ -2459,40 +2459,40 @@
     <t xml:space="preserve">6.81525754928589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63093566894531</t>
+    <t xml:space="preserve">6.63093614578247</t>
   </si>
   <si>
     <t xml:space="preserve">6.54051446914673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53239965438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57529163360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50921487808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54862976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7341103553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87553977966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91843175888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07145309448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03899383544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87206077575684</t>
+    <t xml:space="preserve">6.53239917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57529211044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50921392440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54862928390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73410987854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87553930282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91843128204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07145214080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03899431228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87206125259399</t>
   </si>
   <si>
     <t xml:space="preserve">6.95668601989746</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">6.90915632247925</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87322092056274</t>
+    <t xml:space="preserve">6.87321996688843</t>
   </si>
   <si>
     <t xml:space="preserve">6.86742353439331</t>
@@ -2510,19 +2510,19 @@
     <t xml:space="preserve">6.90336036682129</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81062030792236</t>
+    <t xml:space="preserve">6.81062126159668</t>
   </si>
   <si>
     <t xml:space="preserve">7.45980310440063</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07304859161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12057876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32808589935303</t>
+    <t xml:space="preserve">8.0730504989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12057781219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32808494567871</t>
   </si>
   <si>
     <t xml:space="preserve">8.37561511993408</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">8.41039180755615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51124668121338</t>
+    <t xml:space="preserve">8.5112476348877</t>
   </si>
   <si>
     <t xml:space="preserve">8.41386985778809</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">8.42198467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18433666229248</t>
+    <t xml:space="preserve">8.1843376159668</t>
   </si>
   <si>
     <t xml:space="preserve">8.19245147705078</t>
@@ -2561,25 +2561,25 @@
     <t xml:space="preserve">8.09623432159424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79019021987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7461404800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88177156448364</t>
+    <t xml:space="preserve">7.79019117355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74613952636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88177251815796</t>
   </si>
   <si>
     <t xml:space="preserve">7.87713479995728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89104557037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82033205032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77859878540039</t>
+    <t xml:space="preserve">7.89104604721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82033109664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77859783172607</t>
   </si>
   <si>
     <t xml:space="preserve">7.70440530776978</t>
@@ -2594,28 +2594,28 @@
     <t xml:space="preserve">7.68238067626953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6870174407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62094020843506</t>
+    <t xml:space="preserve">7.68701648712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62093925476074</t>
   </si>
   <si>
     <t xml:space="preserve">7.57920598983765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46328067779541</t>
+    <t xml:space="preserve">7.46328115463257</t>
   </si>
   <si>
     <t xml:space="preserve">7.64760255813599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72411346435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80757904052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88524961471558</t>
+    <t xml:space="preserve">7.72411298751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80757999420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88525056838989</t>
   </si>
   <si>
     <t xml:space="preserve">7.88409090042114</t>
@@ -2624,73 +2624,73 @@
     <t xml:space="preserve">7.91191244125366</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82844591140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78439521789551</t>
+    <t xml:space="preserve">7.82844686508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78439474105835</t>
   </si>
   <si>
     <t xml:space="preserve">7.7415018081665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5803656578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47719287872314</t>
+    <t xml:space="preserve">7.58036470413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47719192504883</t>
   </si>
   <si>
     <t xml:space="preserve">7.51197004318237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41691064834595</t>
+    <t xml:space="preserve">7.41691112518311</t>
   </si>
   <si>
     <t xml:space="preserve">7.43777751922607</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43661880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39024782180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36822128295898</t>
+    <t xml:space="preserve">7.43661785125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39024686813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36822271347046</t>
   </si>
   <si>
     <t xml:space="preserve">7.22911167144775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21867799758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20592546463013</t>
+    <t xml:space="preserve">7.21867752075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20592641830444</t>
   </si>
   <si>
     <t xml:space="preserve">7.22099733352661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14680433273315</t>
+    <t xml:space="preserve">7.14680337905884</t>
   </si>
   <si>
     <t xml:space="preserve">6.98219013214111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03783464431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96364164352417</t>
+    <t xml:space="preserve">7.03783416748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96364259719849</t>
   </si>
   <si>
     <t xml:space="preserve">7.03087854385376</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91263484954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80018758773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8523530960083</t>
+    <t xml:space="preserve">6.9126353263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8001880645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85235357284546</t>
   </si>
   <si>
     <t xml:space="preserve">7.19317531585693</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">7.07608985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03203916549683</t>
+    <t xml:space="preserve">7.03203821182251</t>
   </si>
   <si>
     <t xml:space="preserve">7.29403018951416</t>
@@ -2708,28 +2708,28 @@
     <t xml:space="preserve">7.10738945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1410083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11086702346802</t>
+    <t xml:space="preserve">7.14100790023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11086750030518</t>
   </si>
   <si>
     <t xml:space="preserve">7.1155047416687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00189733505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57297277450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52544403076172</t>
+    <t xml:space="preserve">7.00189828872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57297229766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52544450759888</t>
   </si>
   <si>
     <t xml:space="preserve">6.70165061950684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51616907119751</t>
+    <t xml:space="preserve">6.51616954803467</t>
   </si>
   <si>
     <t xml:space="preserve">6.27620410919189</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">6.3411226272583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37126302719116</t>
+    <t xml:space="preserve">6.37126350402832</t>
   </si>
   <si>
     <t xml:space="preserve">6.2843189239502</t>
@@ -2747,19 +2747,19 @@
     <t xml:space="preserve">6.09651899337769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.438063621521</t>
+    <t xml:space="preserve">5.43806314468384</t>
   </si>
   <si>
     <t xml:space="preserve">5.40676259994507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51921081542969</t>
+    <t xml:space="preserve">5.51921129226685</t>
   </si>
   <si>
     <t xml:space="preserve">4.53326463699341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85785627365112</t>
+    <t xml:space="preserve">4.85785579681396</t>
   </si>
   <si>
     <t xml:space="preserve">4.15534782409668</t>
@@ -2771,13 +2771,13 @@
     <t xml:space="preserve">3.54731917381287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36531567573547</t>
+    <t xml:space="preserve">3.36531591415405</t>
   </si>
   <si>
     <t xml:space="preserve">3.56122994422913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40994763374329</t>
+    <t xml:space="preserve">3.40994739532471</t>
   </si>
   <si>
     <t xml:space="preserve">3.84872460365295</t>
@@ -2786,34 +2786,34 @@
     <t xml:space="preserve">3.96117329597473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99421119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75482559204102</t>
+    <t xml:space="preserve">3.99421167373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75482535362244</t>
   </si>
   <si>
     <t xml:space="preserve">3.65744781494141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80930995941162</t>
+    <t xml:space="preserve">3.80931043624878</t>
   </si>
   <si>
     <t xml:space="preserve">3.66498351097107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64295768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368920326233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83481383323669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08289432525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12636709213257</t>
+    <t xml:space="preserve">3.64295721054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83481335639954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08289480209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12636661529541</t>
   </si>
   <si>
     <t xml:space="preserve">4.33503198623657</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">4.12057018280029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24403142929077</t>
+    <t xml:space="preserve">4.24403047561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.30663061141968</t>
@@ -2837,19 +2837,19 @@
     <t xml:space="preserve">4.11419486999512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20229721069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35010194778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26026058197021</t>
+    <t xml:space="preserve">4.20229768753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35010242462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26026010513306</t>
   </si>
   <si>
     <t xml:space="preserve">4.46197080612183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57383871078491</t>
+    <t xml:space="preserve">4.57383918762207</t>
   </si>
   <si>
     <t xml:space="preserve">4.74135112762451</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">4.44863986968994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42139673233032</t>
+    <t xml:space="preserve">4.42139720916748</t>
   </si>
   <si>
     <t xml:space="preserve">4.40516805648804</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">4.17505502700806</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51703548431396</t>
+    <t xml:space="preserve">4.51703596115112</t>
   </si>
   <si>
     <t xml:space="preserve">4.31242752075195</t>
@@ -2897,22 +2897,22 @@
     <t xml:space="preserve">4.25388431549072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29851579666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59934186935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.728600025177</t>
+    <t xml:space="preserve">4.29851627349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59934234619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72859954833984</t>
   </si>
   <si>
     <t xml:space="preserve">4.78192567825317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60339975357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76511526107788</t>
+    <t xml:space="preserve">4.6033992767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76511573791504</t>
   </si>
   <si>
     <t xml:space="preserve">4.83293199539185</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">5.04449558258057</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39748954772949</t>
+    <t xml:space="preserve">5.39748907089233</t>
   </si>
   <si>
     <t xml:space="preserve">5.45255279541016</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">5.07231855392456</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68164920806885</t>
+    <t xml:space="preserve">4.68164968490601</t>
   </si>
   <si>
     <t xml:space="preserve">4.74888610839844</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">4.7506251335144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88625812530518</t>
+    <t xml:space="preserve">4.88625764846802</t>
   </si>
   <si>
     <t xml:space="preserve">4.86771011352539</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">4.96624612808228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25374221801758</t>
+    <t xml:space="preserve">5.25374174118042</t>
   </si>
   <si>
     <t xml:space="preserve">5.02246999740601</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">5.09260559082031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21606588363647</t>
+    <t xml:space="preserve">5.21606540679932</t>
   </si>
   <si>
     <t xml:space="preserve">5.15868234634399</t>
@@ -2993,13 +2993,13 @@
     <t xml:space="preserve">5.20679235458374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09840154647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00276231765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11984872817993</t>
+    <t xml:space="preserve">5.09840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00276279449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11984825134277</t>
   </si>
   <si>
     <t xml:space="preserve">5.24910449981689</t>
@@ -3008,13 +3008,13 @@
     <t xml:space="preserve">5.20447301864624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25721883773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3169207572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31054496765137</t>
+    <t xml:space="preserve">5.25721979141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31692123413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31054449081421</t>
   </si>
   <si>
     <t xml:space="preserve">5.34184455871582</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">5.35401678085327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30822658538818</t>
+    <t xml:space="preserve">5.30822706222534</t>
   </si>
   <si>
     <t xml:space="preserve">5.3412652015686</t>
@@ -3032,31 +3032,31 @@
     <t xml:space="preserve">5.26069688796997</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25895881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37488412857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30764722824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99638652801514</t>
+    <t xml:space="preserve">5.258957862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37488460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30764675140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99638700485229</t>
   </si>
   <si>
     <t xml:space="preserve">5.23693227767944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44270038604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44733667373657</t>
+    <t xml:space="preserve">5.44270133972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44733715057373</t>
   </si>
   <si>
     <t xml:space="preserve">5.38937425613403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38183879852295</t>
+    <t xml:space="preserve">5.38183927536011</t>
   </si>
   <si>
     <t xml:space="preserve">5.47457885742188</t>
@@ -3068,22 +3068,22 @@
     <t xml:space="preserve">5.74178791046143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65716171264648</t>
+    <t xml:space="preserve">5.65716218948364</t>
   </si>
   <si>
     <t xml:space="preserve">5.61658811569214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5934042930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56848001480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58065223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.476318359375</t>
+    <t xml:space="preserve">5.59340286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56848049163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58065128326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47631931304932</t>
   </si>
   <si>
     <t xml:space="preserve">5.40618371963501</t>
@@ -3092,34 +3092,34 @@
     <t xml:space="preserve">5.5800724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51631307601929</t>
+    <t xml:space="preserve">5.51631259918213</t>
   </si>
   <si>
     <t xml:space="preserve">5.54703378677368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47747755050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.457190990448</t>
+    <t xml:space="preserve">5.47747802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45719051361084</t>
   </si>
   <si>
     <t xml:space="preserve">5.35054016113281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28736019134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31750106811523</t>
+    <t xml:space="preserve">5.28736066818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31750059127808</t>
   </si>
   <si>
     <t xml:space="preserve">5.37836217880249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46646499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58470869064331</t>
+    <t xml:space="preserve">5.46646451950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58470821380615</t>
   </si>
   <si>
     <t xml:space="preserve">5.57079744338989</t>
@@ -3128,13 +3128,13 @@
     <t xml:space="preserve">5.57137727737427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73019552230835</t>
+    <t xml:space="preserve">5.73019599914551</t>
   </si>
   <si>
     <t xml:space="preserve">5.74642467498779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78641939163208</t>
+    <t xml:space="preserve">5.78641891479492</t>
   </si>
   <si>
     <t xml:space="preserve">6.30750465393066</t>
@@ -3146,67 +3146,67 @@
     <t xml:space="preserve">6.23910856246948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01537179946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75975608825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92263174057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02232646942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01189517974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92958736419678</t>
+    <t xml:space="preserve">6.01537227630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75975656509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92263126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02232789993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01189470291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92958641052246</t>
   </si>
   <si>
     <t xml:space="preserve">6.16491508483887</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02116823196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06753873825073</t>
+    <t xml:space="preserve">6.02116870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06753921508789</t>
   </si>
   <si>
     <t xml:space="preserve">5.99914216995239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07681274414062</t>
+    <t xml:space="preserve">6.07681226730347</t>
   </si>
   <si>
     <t xml:space="preserve">6.18578195571899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20317125320435</t>
+    <t xml:space="preserve">6.2031717300415</t>
   </si>
   <si>
     <t xml:space="preserve">6.19041967391968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1046347618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16375589370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06058216094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12665987014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99566555023193</t>
+    <t xml:space="preserve">6.10463428497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16375637054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06058263778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12666082382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99566459655762</t>
   </si>
   <si>
     <t xml:space="preserve">6.24954080581665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22867441177368</t>
+    <t xml:space="preserve">6.22867488861084</t>
   </si>
   <si>
     <t xml:space="preserve">6.24722290039062</t>
@@ -3215,37 +3215,37 @@
     <t xml:space="preserve">6.20548963546753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3573522567749</t>
+    <t xml:space="preserve">6.35735130310059</t>
   </si>
   <si>
     <t xml:space="preserve">6.43386268615723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48023319244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37242364883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12550163269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12318325042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11043119430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27156686782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3793773651123</t>
+    <t xml:space="preserve">6.48023366928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37242269515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12550020217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12318277359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11043071746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27156734466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37937688827515</t>
   </si>
   <si>
     <t xml:space="preserve">6.47443723678589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51269245147705</t>
+    <t xml:space="preserve">6.51269197463989</t>
   </si>
   <si>
     <t xml:space="preserve">6.91031694412231</t>
@@ -3254,31 +3254,31 @@
     <t xml:space="preserve">6.99146461486816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07840824127197</t>
+    <t xml:space="preserve">7.07840919494629</t>
   </si>
   <si>
     <t xml:space="preserve">7.29750776290894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31837368011475</t>
+    <t xml:space="preserve">7.31837463378906</t>
   </si>
   <si>
     <t xml:space="preserve">7.34851551055908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50037574768066</t>
+    <t xml:space="preserve">7.5003776550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.46560001373291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44705057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58963966369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64180612564087</t>
+    <t xml:space="preserve">7.44705104827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58964061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64180707931519</t>
   </si>
   <si>
     <t xml:space="preserve">7.58616209030151</t>
@@ -3287,19 +3287,19 @@
     <t xml:space="preserve">7.66615056991577</t>
   </si>
   <si>
-    <t xml:space="preserve">7.573410987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66730928421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63948774337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66846895217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85395002365112</t>
+    <t xml:space="preserve">7.57341051101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66731023788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63948678970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66846990585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85395097732544</t>
   </si>
   <si>
     <t xml:space="preserve">7.80294322967529</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">7.77048397064209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98494625091553</t>
+    <t xml:space="preserve">7.98494529724121</t>
   </si>
   <si>
     <t xml:space="preserve">8.01624584197998</t>
@@ -3329,16 +3329,16 @@
     <t xml:space="preserve">8.348952293396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42082500457764</t>
+    <t xml:space="preserve">8.42082595825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.25968933105469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46140003204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51588344573975</t>
+    <t xml:space="preserve">8.46139907836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51588439941406</t>
   </si>
   <si>
     <t xml:space="preserve">8.57036876678467</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">8.51356506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49733448028564</t>
+    <t xml:space="preserve">8.49733543395996</t>
   </si>
   <si>
     <t xml:space="preserve">8.62485504150391</t>
@@ -3356,13 +3356,13 @@
     <t xml:space="preserve">8.60166931152344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5715274810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41271114349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33503913879395</t>
+    <t xml:space="preserve">8.57152843475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41271018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33504009246826</t>
   </si>
   <si>
     <t xml:space="preserve">8.50545120239258</t>
@@ -3371,25 +3371,25 @@
     <t xml:space="preserve">8.46951389312744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78281116485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40054225921631</t>
+    <t xml:space="preserve">8.78281021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40054130554199</t>
   </si>
   <si>
     <t xml:space="preserve">9.27200603485107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32146072387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1196346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84830379486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43662929534912</t>
+    <t xml:space="preserve">9.32146167755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11963367462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84830284118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43663024902344</t>
   </si>
   <si>
     <t xml:space="preserve">8.60236835479736</t>
@@ -3407,46 +3407,46 @@
     <t xml:space="preserve">8.42460155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68122863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69726848602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76142406463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93117427825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08889293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01805210113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84295749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79483795166016</t>
+    <t xml:space="preserve">8.681227684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69726753234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76142501831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93117332458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08889198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01805305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84295654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79483985900879</t>
   </si>
   <si>
     <t xml:space="preserve">8.86567878723145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95790386199951</t>
+    <t xml:space="preserve">8.95790481567383</t>
   </si>
   <si>
     <t xml:space="preserve">9.02206134796143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82825469970703</t>
+    <t xml:space="preserve">8.82825374603271</t>
   </si>
   <si>
     <t xml:space="preserve">8.87770843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94186592102051</t>
+    <t xml:space="preserve">8.94186687469482</t>
   </si>
   <si>
     <t xml:space="preserve">8.82424545288086</t>
@@ -3455,46 +3455,46 @@
     <t xml:space="preserve">8.86968994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07552623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06082248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97795486450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30542278289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28537178039551</t>
+    <t xml:space="preserve">9.07552719116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06082439422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97795391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30542087554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28537082672119</t>
   </si>
   <si>
     <t xml:space="preserve">9.2679967880249</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25061988830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14369201660156</t>
+    <t xml:space="preserve">9.25062084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14369297027588</t>
   </si>
   <si>
     <t xml:space="preserve">9.6796703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85610008239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0579290390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1755485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3158931732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6027088165283</t>
+    <t xml:space="preserve">9.85610103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0579280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1755495071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3158922195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.602707862854</t>
   </si>
   <si>
     <t xml:space="preserve">10.5399112701416</t>
@@ -3503,40 +3503,40 @@
     <t xml:space="preserve">10.6655044555664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.983772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5970001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4785413742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1288757324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1374397277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2801599502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4457149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4628429412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7754001617432</t>
+    <t xml:space="preserve">10.9837713241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.596999168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4785404205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1288747787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1374387741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.280158996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4457139968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4628419876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7753992080688</t>
   </si>
   <si>
     <t xml:space="preserve">10.7639818191528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8010883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9124126434326</t>
+    <t xml:space="preserve">10.8010892868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9124116897583</t>
   </si>
   <si>
     <t xml:space="preserve">10.9109840393066</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">10.7397193908691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7340097427368</t>
+    <t xml:space="preserve">10.7340106964111</t>
   </si>
   <si>
     <t xml:space="preserve">10.8910026550293</t>
@@ -3569,34 +3569,34 @@
     <t xml:space="preserve">10.3457975387573</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4551296234131</t>
+    <t xml:space="preserve">10.4551305770874</t>
   </si>
   <si>
     <t xml:space="preserve">10.481369972229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4886598587036</t>
+    <t xml:space="preserve">10.4886589050293</t>
   </si>
   <si>
     <t xml:space="preserve">10.4667921066284</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4288892745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4901170730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.09068775177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0761108398438</t>
+    <t xml:space="preserve">10.4288902282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4901161193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0906887054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0761098861694</t>
   </si>
   <si>
     <t xml:space="preserve">10.2204294204712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1227588653564</t>
+    <t xml:space="preserve">10.1227579116821</t>
   </si>
   <si>
     <t xml:space="preserve">10.8312349319458</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">10.8910036087036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0061674118042</t>
+    <t xml:space="preserve">11.0061683654785</t>
   </si>
   <si>
     <t xml:space="preserve">10.6869163513184</t>
@@ -3629,37 +3629,37 @@
     <t xml:space="preserve">11.0003366470337</t>
   </si>
   <si>
-    <t xml:space="preserve">10.736478805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9376525878906</t>
+    <t xml:space="preserve">10.7364797592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9376516342163</t>
   </si>
   <si>
     <t xml:space="preserve">11.1636066436768</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2160873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2787714004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2583618164062</t>
+    <t xml:space="preserve">11.2160863876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2787704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2583608627319</t>
   </si>
   <si>
     <t xml:space="preserve">11.7190160751343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739426612854</t>
+    <t xml:space="preserve">11.7394275665283</t>
   </si>
   <si>
     <t xml:space="preserve">11.8502159118652</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9143581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.033896446228</t>
+    <t xml:space="preserve">11.9143590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0338954925537</t>
   </si>
   <si>
     <t xml:space="preserve">12.1709260940552</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">12.7219638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7379989624023</t>
+    <t xml:space="preserve">12.737998008728</t>
   </si>
   <si>
     <t xml:space="preserve">12.5601511001587</t>
@@ -3686,19 +3686,19 @@
     <t xml:space="preserve">12.3677253723145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3167037963867</t>
+    <t xml:space="preserve">12.3167028427124</t>
   </si>
   <si>
     <t xml:space="preserve">12.3181610107422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3604364395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0003681182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4056272506714</t>
+    <t xml:space="preserve">12.3604373931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0003671646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4056282043457</t>
   </si>
   <si>
     <t xml:space="preserve">12.3808450698853</t>
@@ -3713,13 +3713,13 @@
     <t xml:space="preserve">12.436240196228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2758846282959</t>
+    <t xml:space="preserve">12.2758855819702</t>
   </si>
   <si>
     <t xml:space="preserve">12.2613077163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0659675598145</t>
+    <t xml:space="preserve">12.0659666061401</t>
   </si>
   <si>
     <t xml:space="preserve">12.1738414764404</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">12.3414850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1942510604858</t>
+    <t xml:space="preserve">12.1942491531372</t>
   </si>
   <si>
     <t xml:space="preserve">12.0936632156372</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">12.0164022445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429269790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8370971679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6679954528809</t>
+    <t xml:space="preserve">11.8429279327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8370962142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6679944992065</t>
   </si>
   <si>
     <t xml:space="preserve">11.4332942962646</t>
@@ -3758,10 +3758,10 @@
     <t xml:space="preserve">11.0499000549316</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4289216995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3633222579956</t>
+    <t xml:space="preserve">11.4289207458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3633213043213</t>
   </si>
   <si>
     <t xml:space="preserve">11.4814004898071</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">11.5790710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4347524642944</t>
+    <t xml:space="preserve">11.4347515106201</t>
   </si>
   <si>
     <t xml:space="preserve">11.5324220657349</t>
@@ -3779,31 +3779,31 @@
     <t xml:space="preserve">11.9201889038086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8006534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9318532943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7175903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.714674949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0280961990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.117018699646</t>
+    <t xml:space="preserve">11.8006525039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9318523406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7175893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7146739959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0280952453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1170196533203</t>
   </si>
   <si>
     <t xml:space="preserve">13.0834913253784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1330547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4829177856445</t>
+    <t xml:space="preserve">13.1330537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4829187393188</t>
   </si>
   <si>
     <t xml:space="preserve">13.5645551681519</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">13.369213104248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0062294006348</t>
+    <t xml:space="preserve">13.0062284469604</t>
   </si>
   <si>
     <t xml:space="preserve">13.105357170105</t>
@@ -3821,10 +3821,10 @@
     <t xml:space="preserve">12.6388702392578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4930934906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5411996841431</t>
+    <t xml:space="preserve">12.4930925369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5412006378174</t>
   </si>
   <si>
     <t xml:space="preserve">12.5732707977295</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">12.6024265289307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.485803604126</t>
+    <t xml:space="preserve">12.4858055114746</t>
   </si>
   <si>
     <t xml:space="preserve">12.5105857849121</t>
@@ -3848,25 +3848,25 @@
     <t xml:space="preserve">12.4814319610596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5674409866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4537334442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0980367660522</t>
+    <t xml:space="preserve">12.567440032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4537343978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0980377197266</t>
   </si>
   <si>
     <t xml:space="preserve">12.1636371612549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1753005981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2656803131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6898918151855</t>
+    <t xml:space="preserve">12.1752986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2656812667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6898927688599</t>
   </si>
   <si>
     <t xml:space="preserve">12.2525606155396</t>
@@ -3875,19 +3875,19 @@
     <t xml:space="preserve">11.7044401168823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6854877471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0645084381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2219486236572</t>
+    <t xml:space="preserve">11.6854887008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0645093917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2219467163086</t>
   </si>
   <si>
     <t xml:space="preserve">12.2365255355835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3444013595581</t>
+    <t xml:space="preserve">12.3444004058838</t>
   </si>
   <si>
     <t xml:space="preserve">11.9770412445068</t>
@@ -3905,19 +3905,19 @@
     <t xml:space="preserve">11.7627506256104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0674247741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6373815536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0790863037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1534337997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2642230987549</t>
+    <t xml:space="preserve">12.0674238204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6373825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0790872573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1534328460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2642240524292</t>
   </si>
   <si>
     <t xml:space="preserve">12.2860898971558</t>
@@ -3926,34 +3926,34 @@
     <t xml:space="preserve">12.2671384811401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4114580154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3123302459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2292356491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2598505020142</t>
+    <t xml:space="preserve">12.4114589691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3123292922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2292375564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2598485946655</t>
   </si>
   <si>
     <t xml:space="preserve">12.2846326828003</t>
   </si>
   <si>
-    <t xml:space="preserve">12.281717300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.765697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.80797290802</t>
+    <t xml:space="preserve">12.2817163467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7656965255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8079719543457</t>
   </si>
   <si>
     <t xml:space="preserve">12.7992248535156</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5995101928711</t>
+    <t xml:space="preserve">12.5995111465454</t>
   </si>
   <si>
     <t xml:space="preserve">12.719048500061</t>
@@ -3977,34 +3977,34 @@
     <t xml:space="preserve">12.7117605209351</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0339260101318</t>
+    <t xml:space="preserve">13.0339250564575</t>
   </si>
   <si>
     <t xml:space="preserve">13.0368413925171</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0295534133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1855335235596</t>
+    <t xml:space="preserve">13.0295524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1855344772339</t>
   </si>
   <si>
     <t xml:space="preserve">13.0878639221191</t>
   </si>
   <si>
-    <t xml:space="preserve">13.093695640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7248792648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3983383178711</t>
+    <t xml:space="preserve">13.0936946868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7248802185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3983392715454</t>
   </si>
   <si>
     <t xml:space="preserve">12.2511034011841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1782159805298</t>
+    <t xml:space="preserve">12.1782150268555</t>
   </si>
   <si>
     <t xml:space="preserve">11.3458280563354</t>
@@ -4016,28 +4016,28 @@
     <t xml:space="preserve">11.0353231430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6621646881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6096849441528</t>
+    <t xml:space="preserve">11.662163734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6096858978271</t>
   </si>
   <si>
     <t xml:space="preserve">11.4755706787109</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8749990463257</t>
+    <t xml:space="preserve">11.8749980926514</t>
   </si>
   <si>
     <t xml:space="preserve">12.2977523803711</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1592645645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9887037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0193185806274</t>
+    <t xml:space="preserve">12.1592626571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9887046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0193176269531</t>
   </si>
   <si>
     <t xml:space="preserve">11.9289360046387</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">11.8924913406372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9639225006104</t>
+    <t xml:space="preserve">11.963921546936</t>
   </si>
   <si>
     <t xml:space="preserve">11.5309648513794</t>
@@ -4061,7 +4061,7 @@
     <t xml:space="preserve">11.9916200637817</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2685985565186</t>
+    <t xml:space="preserve">12.2685966491699</t>
   </si>
   <si>
     <t xml:space="preserve">12.1621799468994</t>
@@ -4076,16 +4076,16 @@
     <t xml:space="preserve">13.4318971633911</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2992401123047</t>
+    <t xml:space="preserve">13.299241065979</t>
   </si>
   <si>
     <t xml:space="preserve">13.1213932037354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0208053588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1490907669067</t>
+    <t xml:space="preserve">13.020806312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1490898132324</t>
   </si>
   <si>
     <t xml:space="preserve">13.3969106674194</t>
@@ -4097,28 +4097,28 @@
     <t xml:space="preserve">13.8298692703247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9508638381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9173364639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8415307998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6986684799194</t>
+    <t xml:space="preserve">13.9508647918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9173345565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8415298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6986694335938</t>
   </si>
   <si>
     <t xml:space="preserve">13.2132320404053</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1009531021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6855182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7861051559448</t>
+    <t xml:space="preserve">12.1009521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6855192184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7861061096191</t>
   </si>
   <si>
     <t xml:space="preserve">12.4406147003174</t>
@@ -4130,19 +4130,19 @@
     <t xml:space="preserve">12.6417856216431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6636533737183</t>
+    <t xml:space="preserve">12.6636524200439</t>
   </si>
   <si>
     <t xml:space="preserve">11.998908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8822870254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9814167022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4683122634888</t>
+    <t xml:space="preserve">11.882287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9814157485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4683132171631</t>
   </si>
   <si>
     <t xml:space="preserve">12.3618927001953</t>
@@ -4154,52 +4154,52 @@
     <t xml:space="preserve">11.9099855422974</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3997964859009</t>
+    <t xml:space="preserve">12.3997955322266</t>
   </si>
   <si>
     <t xml:space="preserve">12.5149602890015</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665525436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8837461471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4391555786133</t>
+    <t xml:space="preserve">12.1665515899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8837451934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4391565322876</t>
   </si>
   <si>
     <t xml:space="preserve">11.6869468688965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3064994812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1052961349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2190027236938</t>
+    <t xml:space="preserve">12.3064985275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1052951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2190017700195</t>
   </si>
   <si>
     <t xml:space="preserve">10.9041242599487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0746517181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43031692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42594528198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5834131240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81808376312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83703517913818</t>
+    <t xml:space="preserve">10.0746507644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43031787872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42594337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5834150314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81808471679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8370361328125</t>
   </si>
   <si>
     <t xml:space="preserve">10.2043933868408</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">10.3180999755859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.977011680603</t>
+    <t xml:space="preserve">10.9770126342773</t>
   </si>
   <si>
     <t xml:space="preserve">10.7262754440308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6883726119995</t>
+    <t xml:space="preserve">10.6883735656738</t>
   </si>
   <si>
     <t xml:space="preserve">10.6475563049316</t>
@@ -4229,16 +4229,16 @@
     <t xml:space="preserve">10.5046939849854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5207290649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5323925018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2321224212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0542736053467</t>
+    <t xml:space="preserve">10.52073097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5323915481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2321214675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.054274559021</t>
   </si>
   <si>
     <t xml:space="preserve">10.7875022888184</t>
@@ -4247,43 +4247,43 @@
     <t xml:space="preserve">10.7802124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8516426086426</t>
+    <t xml:space="preserve">10.8516435623169</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522142410278</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98718547821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86910724639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0338344573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1475410461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1358785629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1854429244995</t>
+    <t xml:space="preserve">9.98718643188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86910629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0338354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1475400924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1358795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1854419708252</t>
   </si>
   <si>
     <t xml:space="preserve">10.2583312988281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5054616928101</t>
+    <t xml:space="preserve">10.5054626464844</t>
   </si>
   <si>
     <t xml:space="preserve">10.5621299743652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6644449234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3197212219238</t>
+    <t xml:space="preserve">10.6644458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3197202682495</t>
   </si>
   <si>
     <t xml:space="preserve">10.0741624832153</t>
@@ -4295,7 +4295,7 @@
     <t xml:space="preserve">9.94823551177979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0710144042969</t>
+    <t xml:space="preserve">10.0710134506226</t>
   </si>
   <si>
     <t xml:space="preserve">10.2174043655396</t>
@@ -4352,10 +4352,10 @@
     <t xml:space="preserve">10.3386087417603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5306482315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7903718948364</t>
+    <t xml:space="preserve">10.5306491851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7903728485107</t>
   </si>
   <si>
     <t xml:space="preserve">10.8202800750732</t>
@@ -4364,22 +4364,22 @@
     <t xml:space="preserve">11.0186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9666700363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1571340560913</t>
+    <t xml:space="preserve">10.9666709899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1571350097656</t>
   </si>
   <si>
     <t xml:space="preserve">11.2263946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8549098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9304666519165</t>
+    <t xml:space="preserve">10.8549108505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.064263343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9304656982422</t>
   </si>
   <si>
     <t xml:space="preserve">11.0249118804932</t>
@@ -4388,16 +4388,16 @@
     <t xml:space="preserve">10.7919464111328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2252740859985</t>
+    <t xml:space="preserve">10.2252750396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.82388305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0977745056152</t>
+    <t xml:space="preserve">9.82073497772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0977735519409</t>
   </si>
   <si>
     <t xml:space="preserve">9.56415843963623</t>
@@ -4406,25 +4406,25 @@
     <t xml:space="preserve">9.63027000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74989986419678</t>
+    <t xml:space="preserve">9.74990081787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.99388408660889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82230854034424</t>
+    <t xml:space="preserve">9.82230758666992</t>
   </si>
   <si>
     <t xml:space="preserve">9.61295509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78138160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77508640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86953067779541</t>
+    <t xml:space="preserve">9.78138256072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77508544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86953163146973</t>
   </si>
   <si>
     <t xml:space="preserve">9.59406566619873</t>
@@ -4451,16 +4451,16 @@
     <t xml:space="preserve">9.80499362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60193538665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67906665802002</t>
+    <t xml:space="preserve">9.60193634033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67906761169434</t>
   </si>
   <si>
     <t xml:space="preserve">9.4445276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20211887359619</t>
+    <t xml:space="preserve">9.20211791992188</t>
   </si>
   <si>
     <t xml:space="preserve">9.40989780426025</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">10.0348100662231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1764783859253</t>
+    <t xml:space="preserve">10.176477432251</t>
   </si>
   <si>
     <t xml:space="preserve">10.677038192749</t>
@@ -4499,10 +4499,10 @@
     <t xml:space="preserve">11.0548191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2405614852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3523225784302</t>
+    <t xml:space="preserve">11.2405605316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3523216247559</t>
   </si>
   <si>
     <t xml:space="preserve">11.2736177444458</t>
@@ -4511,31 +4511,31 @@
     <t xml:space="preserve">11.2799139022827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6340827941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.33815574646</t>
+    <t xml:space="preserve">11.6340837478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3381547927856</t>
   </si>
   <si>
     <t xml:space="preserve">11.4971380233765</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5585269927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6734352111816</t>
+    <t xml:space="preserve">11.5585279464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.673436164856</t>
   </si>
   <si>
     <t xml:space="preserve">11.726954460144</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7049169540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680629730225</t>
+    <t xml:space="preserve">11.5223245620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7049179077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3680639266968</t>
   </si>
   <si>
     <t xml:space="preserve">10.9021329879761</t>
@@ -4547,10 +4547,10 @@
     <t xml:space="preserve">11.1681537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0894498825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.813982963562</t>
+    <t xml:space="preserve">11.089448928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8139839172363</t>
   </si>
   <si>
     <t xml:space="preserve">10.8265762329102</t>
@@ -4562,25 +4562,25 @@
     <t xml:space="preserve">10.5101852416992</t>
   </si>
   <si>
-    <t xml:space="preserve">10.333888053894</t>
+    <t xml:space="preserve">10.3338871002197</t>
   </si>
   <si>
     <t xml:space="preserve">10.6046304702759</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0961999893188</t>
+    <t xml:space="preserve">10.0961990356445</t>
   </si>
   <si>
     <t xml:space="preserve">10.2315711975098</t>
   </si>
   <si>
-    <t xml:space="preserve">10.340184211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4613885879517</t>
+    <t xml:space="preserve">10.3401832580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3323125839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4613876342773</t>
   </si>
   <si>
     <t xml:space="preserve">10.8124103546143</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">10.5463886260986</t>
   </si>
   <si>
-    <t xml:space="preserve">10.632963180542</t>
+    <t xml:space="preserve">10.6329641342163</t>
   </si>
   <si>
     <t xml:space="preserve">10.4047212600708</t>
@@ -4607,31 +4607,31 @@
     <t xml:space="preserve">10.4912958145142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.237868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0111999511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1009225845337</t>
+    <t xml:space="preserve">10.2378673553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0111989974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1009216308594</t>
   </si>
   <si>
     <t xml:space="preserve">10.0946264266968</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65860366821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8490686416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93564319610596</t>
+    <t xml:space="preserve">9.65860462188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84906768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93564224243164</t>
   </si>
   <si>
     <t xml:space="preserve">9.86480903625488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68064117431641</t>
+    <t xml:space="preserve">9.68064022064209</t>
   </si>
   <si>
     <t xml:space="preserve">9.58934307098389</t>
@@ -4640,16 +4640,16 @@
     <t xml:space="preserve">9.69638156890869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59721374511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82703018188477</t>
+    <t xml:space="preserve">9.5972146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82703113555908</t>
   </si>
   <si>
     <t xml:space="preserve">9.83647537231445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0851821899414</t>
+    <t xml:space="preserve">10.0851812362671</t>
   </si>
   <si>
     <t xml:space="preserve">10.2488861083984</t>
@@ -4658,16 +4658,16 @@
     <t xml:space="preserve">10.2063865661621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3685169219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.289813041687</t>
+    <t xml:space="preserve">10.3685178756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2898120880127</t>
   </si>
   <si>
     <t xml:space="preserve">10.6487045288086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7447233200073</t>
+    <t xml:space="preserve">10.7447242736816</t>
   </si>
   <si>
     <t xml:space="preserve">10.7305574417114</t>
@@ -4676,19 +4676,19 @@
     <t xml:space="preserve">10.675464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7510194778442</t>
+    <t xml:space="preserve">10.7510204315186</t>
   </si>
   <si>
     <t xml:space="preserve">10.8092622756958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4566659927368</t>
+    <t xml:space="preserve">10.4566669464111</t>
   </si>
   <si>
     <t xml:space="preserve">10.8297252655029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7872257232666</t>
+    <t xml:space="preserve">10.7872247695923</t>
   </si>
   <si>
     <t xml:space="preserve">11.1429681777954</t>
@@ -4703,10 +4703,10 @@
     <t xml:space="preserve">11.4247303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2153768539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1036167144775</t>
+    <t xml:space="preserve">11.2153759002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1036157608032</t>
   </si>
   <si>
     <t xml:space="preserve">11.3413028717041</t>
@@ -4718,13 +4718,13 @@
     <t xml:space="preserve">11.5553789138794</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3838043212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5333423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5301933288574</t>
+    <t xml:space="preserve">11.3838033676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5333433151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5301942825317</t>
   </si>
   <si>
     <t xml:space="preserve">11.4546375274658</t>
@@ -4739,13 +4739,13 @@
     <t xml:space="preserve">11.7332515716553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4924154281616</t>
+    <t xml:space="preserve">11.4924163818359</t>
   </si>
   <si>
     <t xml:space="preserve">11.5364904403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3712110519409</t>
+    <t xml:space="preserve">11.3712120056152</t>
   </si>
   <si>
     <t xml:space="preserve">11.3979711532593</t>
@@ -4769,7 +4769,7 @@
     <t xml:space="preserve">10.6675939559937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3291635513306</t>
+    <t xml:space="preserve">10.3291645050049</t>
   </si>
   <si>
     <t xml:space="preserve">10.3811092376709</t>
@@ -4778,22 +4778,22 @@
     <t xml:space="preserve">10.3559246063232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3244428634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.52907371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4393510818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7415752410889</t>
+    <t xml:space="preserve">10.32444190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5290746688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4393520355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7415761947632</t>
   </si>
   <si>
     <t xml:space="preserve">10.8816699981689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1697282791138</t>
+    <t xml:space="preserve">11.1697273254395</t>
   </si>
   <si>
     <t xml:space="preserve">11.2862100601196</t>
@@ -4808,7 +4808,7 @@
     <t xml:space="preserve">11.5286197662354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6246395111084</t>
+    <t xml:space="preserve">11.6246404647827</t>
   </si>
   <si>
     <t xml:space="preserve">11.1996355056763</t>
@@ -4817,13 +4817,13 @@
     <t xml:space="preserve">11.2673206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3035259246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2295417785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9477815628052</t>
+    <t xml:space="preserve">11.3035249710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2295427322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9477806091309</t>
   </si>
   <si>
     <t xml:space="preserve">11.037504196167</t>
@@ -4838,28 +4838,28 @@
     <t xml:space="preserve">10.95250415802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0611162185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1728763580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3145446777344</t>
+    <t xml:space="preserve">11.0611152648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1728754043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3145437240601</t>
   </si>
   <si>
     <t xml:space="preserve">11.4026927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9693641662598</t>
+    <t xml:space="preserve">11.9693651199341</t>
   </si>
   <si>
     <t xml:space="preserve">11.9630680084229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8686237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8749189376831</t>
+    <t xml:space="preserve">11.8686218261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8749198913574</t>
   </si>
   <si>
     <t xml:space="preserve">11.9016780853271</t>
@@ -4868,31 +4868,31 @@
     <t xml:space="preserve">12.3392753601074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.129921913147</t>
+    <t xml:space="preserve">12.1299209594727</t>
   </si>
   <si>
     <t xml:space="preserve">12.2054777145386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.258996963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4903869628906</t>
+    <t xml:space="preserve">12.2589960098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4903879165649</t>
   </si>
   <si>
     <t xml:space="preserve">12.517147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5533504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7013149261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4888143539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7642784118652</t>
+    <t xml:space="preserve">12.5533514022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7013158798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4888134002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7642793655396</t>
   </si>
   <si>
     <t xml:space="preserve">13.2254867553711</t>
@@ -4904,7 +4904,7 @@
     <t xml:space="preserve">13.0901145935059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0287256240845</t>
+    <t xml:space="preserve">13.0287265777588</t>
   </si>
   <si>
     <t xml:space="preserve">13.4238214492798</t>
@@ -4913,16 +4913,16 @@
     <t xml:space="preserve">13.5151195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9054927825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8330860137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7968816757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7653980255127</t>
+    <t xml:space="preserve">13.9054918289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8330841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7968807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.765398979187</t>
   </si>
   <si>
     <t xml:space="preserve">13.5387306213379</t>
@@ -4937,7 +4937,7 @@
     <t xml:space="preserve">12.9027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4305715560913</t>
+    <t xml:space="preserve">12.4305725097656</t>
   </si>
   <si>
     <t xml:space="preserve">12.5265922546387</t>
@@ -4949,19 +4949,19 @@
     <t xml:space="preserve">12.7390937805176</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7469625473022</t>
+    <t xml:space="preserve">12.7469635009766</t>
   </si>
   <si>
     <t xml:space="preserve">12.7343711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155725479126</t>
+    <t xml:space="preserve">12.5155735015869</t>
   </si>
   <si>
     <t xml:space="preserve">12.7737226486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7910394668579</t>
+    <t xml:space="preserve">12.7910385131836</t>
   </si>
   <si>
     <t xml:space="preserve">12.9153909683228</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">12.9390029907227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.682427406311</t>
+    <t xml:space="preserve">12.6824264526367</t>
   </si>
   <si>
     <t xml:space="preserve">12.7878894805908</t>
@@ -4994,19 +4994,19 @@
     <t xml:space="preserve">13.2443752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5088224411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3624324798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4049320220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3545618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6320552825928</t>
+    <t xml:space="preserve">13.5088214874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3624334335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.404932975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3545627593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6320543289185</t>
   </si>
   <si>
     <t xml:space="preserve">12.5486288070679</t>
@@ -5054,13 +5054,13 @@
     <t xml:space="preserve">12.770318031311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6242437362671</t>
+    <t xml:space="preserve">12.6242446899414</t>
   </si>
   <si>
     <t xml:space="preserve">12.7514142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0143480300903</t>
+    <t xml:space="preserve">13.014347076416</t>
   </si>
   <si>
     <t xml:space="preserve">13.2600955963135</t>
@@ -5069,13 +5069,13 @@
     <t xml:space="preserve">13.1655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0934000015259</t>
+    <t xml:space="preserve">13.0933990478516</t>
   </si>
   <si>
     <t xml:space="preserve">12.5623769760132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4334878921509</t>
+    <t xml:space="preserve">12.4334888458252</t>
   </si>
   <si>
     <t xml:space="preserve">12.6929845809937</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">13.5470886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5178737640381</t>
+    <t xml:space="preserve">13.5178747177124</t>
   </si>
   <si>
     <t xml:space="preserve">13.6261405944824</t>
@@ -5132,13 +5132,13 @@
     <t xml:space="preserve">13.2033843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0813703536987</t>
+    <t xml:space="preserve">13.0813694000244</t>
   </si>
   <si>
     <t xml:space="preserve">12.9885702133179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0469999313354</t>
+    <t xml:space="preserve">13.0469989776611</t>
   </si>
   <si>
     <t xml:space="preserve">13.1587028503418</t>
@@ -5153,7 +5153,7 @@
     <t xml:space="preserve">13.8254890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.999059677124</t>
+    <t xml:space="preserve">13.9990587234497</t>
   </si>
   <si>
     <t xml:space="preserve">13.9681262969971</t>
@@ -5171,7 +5171,7 @@
     <t xml:space="preserve">13.9767189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0437412261963</t>
+    <t xml:space="preserve">14.043740272522</t>
   </si>
   <si>
     <t xml:space="preserve">14.3736963272095</t>
@@ -5180,52 +5180,52 @@
     <t xml:space="preserve">14.4458742141724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3547925949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2671489715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2551193237305</t>
+    <t xml:space="preserve">14.3547916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2671480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2551183700562</t>
   </si>
   <si>
     <t xml:space="preserve">14.3152666091919</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1863784790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4149408340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4235334396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8050441741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.593846321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650459289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0200386047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192983627319</t>
+    <t xml:space="preserve">14.1863775253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4149398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4235324859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8050451278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5938453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650449752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0200366973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192974090576</t>
   </si>
   <si>
     <t xml:space="preserve">15.5147933959961</t>
   </si>
   <si>
-    <t xml:space="preserve">15.373875617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3446598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2982606887817</t>
+    <t xml:space="preserve">15.3738746643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3446588516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2982597351074</t>
   </si>
   <si>
     <t xml:space="preserve">15.0834455490112</t>
@@ -5243,31 +5243,31 @@
     <t xml:space="preserve">14.5197706222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3221406936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1571636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0523338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3015184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3633852005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.378851890564</t>
+    <t xml:space="preserve">14.3221397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1571626663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0523328781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3015174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3633842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3788509368896</t>
   </si>
   <si>
     <t xml:space="preserve">14.2173109054565</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3668222427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5489845275879</t>
+    <t xml:space="preserve">14.3668212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5489854812622</t>
   </si>
   <si>
     <t xml:space="preserve">14.7964515686035</t>
@@ -5276,10 +5276,10 @@
     <t xml:space="preserve">14.7500524520874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7586450576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4355630874634</t>
+    <t xml:space="preserve">14.7586460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4355621337891</t>
   </si>
   <si>
     <t xml:space="preserve">14.4493112564087</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">14.5386743545532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5661697387695</t>
+    <t xml:space="preserve">14.5661706924438</t>
   </si>
   <si>
     <t xml:space="preserve">14.6074151992798</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">15.2673263549805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1006298065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3859052658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2827930450439</t>
+    <t xml:space="preserve">15.1006288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3859033584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2827920913696</t>
   </si>
   <si>
     <t xml:space="preserve">15.5113563537598</t>
@@ -5321,43 +5321,43 @@
     <t xml:space="preserve">15.9959783554077</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6058759689331</t>
+    <t xml:space="preserve">15.6058750152588</t>
   </si>
   <si>
     <t xml:space="preserve">15.712423324585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5251054763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4512090682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.607593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6471185684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.55260181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999782562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.231237411499</t>
+    <t xml:space="preserve">15.5251045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4512071609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6075925827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6471195220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5526008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2312364578247</t>
   </si>
   <si>
     <t xml:space="preserve">15.3137273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4649562835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9444236755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2726612091064</t>
+    <t xml:space="preserve">15.464955329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9444227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2726593017578</t>
   </si>
   <si>
     <t xml:space="preserve">16.246883392334</t>
@@ -5369,25 +5369,25 @@
     <t xml:space="preserve">16.0681571960449</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2348537445068</t>
+    <t xml:space="preserve">16.2348518371582</t>
   </si>
   <si>
     <t xml:space="preserve">16.1300239562988</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5405721664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1642160415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4855785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2759189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1848382949829</t>
+    <t xml:space="preserve">15.5405702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1642150878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.485577583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.275918006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1848392486572</t>
   </si>
   <si>
     <t xml:space="preserve">14.8806600570679</t>
@@ -5396,16 +5396,16 @@
     <t xml:space="preserve">14.6417865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.122971534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4168376922607</t>
+    <t xml:space="preserve">15.1229705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4168367385864</t>
   </si>
   <si>
     <t xml:space="preserve">15.7553873062134</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0647201538086</t>
+    <t xml:space="preserve">16.06471824646</t>
   </si>
   <si>
     <t xml:space="preserve">15.7467937469482</t>
@@ -5417,16 +5417,16 @@
     <t xml:space="preserve">15.5749416351318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7364816665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0440998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2211036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.894585609436</t>
+    <t xml:space="preserve">15.7364826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0440979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2211055755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8945846557617</t>
   </si>
   <si>
     <t xml:space="preserve">15.8705272674561</t>
@@ -5441,7 +5441,7 @@
     <t xml:space="preserve">16.1094017028809</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0939350128174</t>
+    <t xml:space="preserve">16.0939331054688</t>
   </si>
   <si>
     <t xml:space="preserve">16.9394454956055</t>
@@ -5450,7 +5450,7 @@
     <t xml:space="preserve">17.1009864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2754154205322</t>
+    <t xml:space="preserve">17.2754173278809</t>
   </si>
   <si>
     <t xml:space="preserve">17.4472694396973</t>
@@ -5459,7 +5459,7 @@
     <t xml:space="preserve">17.5847511291504</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0960102081299</t>
+    <t xml:space="preserve">18.0960083007812</t>
   </si>
   <si>
     <t xml:space="preserve">17.9714183807373</t>
@@ -5471,7 +5471,7 @@
     <t xml:space="preserve">18.0530471801758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0186767578125</t>
+    <t xml:space="preserve">18.0186748504639</t>
   </si>
   <si>
     <t xml:space="preserve">17.9671211242676</t>
@@ -5489,28 +5489,28 @@
     <t xml:space="preserve">18.289342880249</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2506771087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2549743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2377891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2420845031738</t>
+    <t xml:space="preserve">18.250675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2549724578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2377872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2420825958252</t>
   </si>
   <si>
     <t xml:space="preserve">18.2034168243408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1733436584473</t>
+    <t xml:space="preserve">18.1733417510986</t>
   </si>
   <si>
     <t xml:space="preserve">18.19482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5718612670898</t>
+    <t xml:space="preserve">17.5718631744385</t>
   </si>
   <si>
     <t xml:space="preserve">17.5503787994385</t>
@@ -5522,7 +5522,7 @@
     <t xml:space="preserve">17.7608985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620845794678</t>
+    <t xml:space="preserve">17.6620826721191</t>
   </si>
   <si>
     <t xml:space="preserve">17.8554172515869</t>
@@ -5534,7 +5534,7 @@
     <t xml:space="preserve">17.5761566162109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3011951446533</t>
+    <t xml:space="preserve">17.3011932373047</t>
   </si>
   <si>
     <t xml:space="preserve">17.11301612854</t>
@@ -5543,13 +5543,13 @@
     <t xml:space="preserve">16.8741416931152</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0459938049316</t>
+    <t xml:space="preserve">17.045991897583</t>
   </si>
   <si>
     <t xml:space="preserve">16.9016380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9274158477783</t>
+    <t xml:space="preserve">16.927417755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.8122749328613</t>
@@ -5561,7 +5561,7 @@
     <t xml:space="preserve">16.6885433197021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7761859893799</t>
+    <t xml:space="preserve">16.7761878967285</t>
   </si>
   <si>
     <t xml:space="preserve">16.7332248687744</t>
@@ -5570,7 +5570,7 @@
     <t xml:space="preserve">17.374231338501</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6105289459229</t>
+    <t xml:space="preserve">17.6105270385742</t>
   </si>
   <si>
     <t xml:space="preserve">17.8468246459961</t>
@@ -5588,16 +5588,16 @@
     <t xml:space="preserve">18.624454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0197124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3032684326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4536380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2388229370117</t>
+    <t xml:space="preserve">19.0197143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3032703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4536399841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2388248443604</t>
   </si>
   <si>
     <t xml:space="preserve">19.3977890014648</t>
@@ -5621,10 +5621,10 @@
     <t xml:space="preserve">20.8198623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1463832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8843078613281</t>
+    <t xml:space="preserve">21.1463813781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8843059539795</t>
   </si>
   <si>
     <t xml:space="preserve">20.8327522277832</t>
@@ -5636,13 +5636,13 @@
     <t xml:space="preserve">20.7382335662842</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9960117340088</t>
+    <t xml:space="preserve">20.9960098266602</t>
   </si>
   <si>
     <t xml:space="preserve">21.1592712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2494926452637</t>
+    <t xml:space="preserve">21.249490737915</t>
   </si>
   <si>
     <t xml:space="preserve">21.4814929962158</t>
@@ -5663,7 +5663,7 @@
     <t xml:space="preserve">21.8552703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7994194030762</t>
+    <t xml:space="preserve">21.7994213104248</t>
   </si>
   <si>
     <t xml:space="preserve">22.3665313720703</t>
@@ -5672,7 +5672,7 @@
     <t xml:space="preserve">22.4696407318115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8649024963379</t>
+    <t xml:space="preserve">22.8649005889893</t>
   </si>
   <si>
     <t xml:space="preserve">22.9078636169434</t>
@@ -5681,19 +5681,19 @@
     <t xml:space="preserve">23.1269760131836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1441612243652</t>
+    <t xml:space="preserve">23.1441593170166</t>
   </si>
   <si>
     <t xml:space="preserve">23.3331985473633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8391227722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9293460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6371974945068</t>
+    <t xml:space="preserve">22.8391246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9293441772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6371955871582</t>
   </si>
   <si>
     <t xml:space="preserve">21.8939361572266</t>
@@ -5702,10 +5702,10 @@
     <t xml:space="preserve">21.4943809509277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5244541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1377906799316</t>
+    <t xml:space="preserve">21.5244560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.137788772583</t>
   </si>
   <si>
     <t xml:space="preserve">21.3912696838379</t>
@@ -5714,25 +5714,25 @@
     <t xml:space="preserve">21.5459365844727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6791210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6619358062744</t>
+    <t xml:space="preserve">21.6791229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.661937713623</t>
   </si>
   <si>
     <t xml:space="preserve">20.9530487060547</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4771957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8370494842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8542346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9229755401611</t>
+    <t xml:space="preserve">21.4771976470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8370475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8542327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9229736328125</t>
   </si>
   <si>
     <t xml:space="preserve">21.2375450134277</t>
@@ -6831,6 +6831,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.70699977874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84500026702881</t>
   </si>
 </sst>
 </file>
@@ -72143,7 +72146,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6940625</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>35362928</v>
@@ -72164,6 +72167,32 @@
         <v>2272</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6942361111</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>76778104</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>9.66100025177002</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>8.61299991607666</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>9.63000011444092</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>8.84500026702881</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>2273</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="2274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2275" uniqueCount="2275">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02501440048218</t>
+    <t xml:space="preserve">4.02501392364502</t>
   </si>
   <si>
     <t xml:space="preserve">STLAM.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">4.13119506835938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91636323928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78795790672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63238978385925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757373809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71881628036499</t>
+    <t xml:space="preserve">3.91636347770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78795742988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63239002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757349967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71881651878357</t>
   </si>
   <si>
     <t xml:space="preserve">3.66942977905273</t>
@@ -68,64 +68,64 @@
     <t xml:space="preserve">3.37804865837097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28421401977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18790912628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26939725875854</t>
+    <t xml:space="preserve">3.28421354293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18790888786316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26939749717712</t>
   </si>
   <si>
     <t xml:space="preserve">3.06197333335876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25705122947693</t>
+    <t xml:space="preserve">3.25705099105835</t>
   </si>
   <si>
     <t xml:space="preserve">3.3261923789978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2619903087616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46200585365295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43237328529358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18544054031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16321635246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16074705123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07678961753845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95332264900208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91628313064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94838404655457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65700340270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58292269706726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73355221748352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59280014038086</t>
+    <t xml:space="preserve">3.26198959350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46200561523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.432373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18544006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16321587562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16074681282043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07679033279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95332217216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91628289222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94838452339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6570029258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58292317390442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73355269432068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59279990196228</t>
   </si>
   <si>
     <t xml:space="preserve">2.68416595458984</t>
@@ -134,79 +134,79 @@
     <t xml:space="preserve">2.80269360542297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75824570655823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89899730682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87924265861511</t>
+    <t xml:space="preserve">2.75824594497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89899778366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87924289703369</t>
   </si>
   <si>
     <t xml:space="preserve">2.81010127067566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92616033554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83973336219788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72614431381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00517892837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13358378410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2990300655365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45212841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46447539329529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44225072860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2891526222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30643749237061</t>
+    <t xml:space="preserve">2.92615985870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83973383903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72614407539368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00517868995667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13358449935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29902958869934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45212817192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46447563171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44225096702576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28915238380432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30643796920776</t>
   </si>
   <si>
     <t xml:space="preserve">3.21013307571411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35088586807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44718980789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36076354980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44472002983093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42496609687805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51633095741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50151562690735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386189460754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47682237625122</t>
+    <t xml:space="preserve">3.35088539123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44719004631042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36076331138611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44471979141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42496585845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5163311958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50151538848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386141777039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4768214225769</t>
   </si>
   <si>
     <t xml:space="preserve">3.33360075950623</t>
@@ -218,37 +218,37 @@
     <t xml:space="preserve">3.5064537525177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3360698223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841656684875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18050169944763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13852286338806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01505637168884</t>
+    <t xml:space="preserve">3.33607006072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841680526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18050193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13852310180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01505708694458</t>
   </si>
   <si>
     <t xml:space="preserve">3.13605380058289</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21260333061218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16815495491028</t>
+    <t xml:space="preserve">3.21260285377502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16815519332886</t>
   </si>
   <si>
     <t xml:space="preserve">3.31878423690796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35335516929626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4027419090271</t>
+    <t xml:space="preserve">3.35335540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40274167060852</t>
   </si>
   <si>
     <t xml:space="preserve">3.56571769714355</t>
@@ -257,25 +257,25 @@
     <t xml:space="preserve">3.54596304893494</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56818747520447</t>
+    <t xml:space="preserve">3.56818723678589</t>
   </si>
   <si>
     <t xml:space="preserve">3.47435259819031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53361654281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41015005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38298654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29656004905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26692867279053</t>
+    <t xml:space="preserve">3.53361630439758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41014981269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38298678398132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29656052589417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26692819595337</t>
   </si>
   <si>
     <t xml:space="preserve">3.3657021522522</t>
@@ -284,58 +284,58 @@
     <t xml:space="preserve">3.3163149356842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38051724433899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33113074302673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10889101028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11382985115051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10148334503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629867553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97801637649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06938219070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12370681762695</t>
+    <t xml:space="preserve">3.38051819801331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33113145828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.108891248703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11383008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10148310661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629915237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97801613807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06938171386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12370705604553</t>
   </si>
   <si>
     <t xml:space="preserve">3.07185101509094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15827798843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07432055473328</t>
+    <t xml:space="preserve">3.15827751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07432079315186</t>
   </si>
   <si>
     <t xml:space="preserve">3.04221892356873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03974962234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14840054512024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1212375164032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93109893798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87677359580994</t>
+    <t xml:space="preserve">3.03974986076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14839959144592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12123775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93109822273254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87677335739136</t>
   </si>
   <si>
     <t xml:space="preserve">2.89652848243713</t>
@@ -344,16 +344,16 @@
     <t xml:space="preserve">2.86195755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93356847763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09407520294189</t>
+    <t xml:space="preserve">2.93356823921204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09407472610474</t>
   </si>
   <si>
     <t xml:space="preserve">3.08666706085205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04962730407715</t>
+    <t xml:space="preserve">3.04962754249573</t>
   </si>
   <si>
     <t xml:space="preserve">3.1113600730896</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">2.81997895240784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64465618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66194176673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71379780769348</t>
+    <t xml:space="preserve">2.64465641975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66194200515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7137975692749</t>
   </si>
   <si>
     <t xml:space="preserve">2.77059245109558</t>
@@ -389,13 +389,13 @@
     <t xml:space="preserve">2.96320009231567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91134428977966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9977707862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00270962715149</t>
+    <t xml:space="preserve">2.91134452819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99777102470398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00270938873291</t>
   </si>
   <si>
     <t xml:space="preserve">2.95826125144958</t>
@@ -407,196 +407,196 @@
     <t xml:space="preserve">3.09901428222656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12617659568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06691193580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84467196464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81257128715515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69157338142395</t>
+    <t xml:space="preserve">3.12617707252502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06691241264343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84467244148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81257104873657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69157361984253</t>
   </si>
   <si>
     <t xml:space="preserve">2.91381359100342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88665127754211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05703449249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98789405822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9607310295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97307753562927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8841814994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91875290870667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0348105430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02987217903137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04468846321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99283289909363</t>
+    <t xml:space="preserve">2.88665080070496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05703473091125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98789358139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96073079109192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97307801246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88418197631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91875243186951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03481030464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02987194061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0446879863739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99283266067505</t>
   </si>
   <si>
     <t xml:space="preserve">3.05950427055359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97554683685303</t>
+    <t xml:space="preserve">2.97554659843445</t>
   </si>
   <si>
     <t xml:space="preserve">2.9508535861969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96813941001892</t>
+    <t xml:space="preserve">2.96813917160034</t>
   </si>
   <si>
     <t xml:space="preserve">2.90393590927124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86442732810974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87430453300476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81504034996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90146732330322</t>
+    <t xml:space="preserve">2.86442756652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87430477142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81504058837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90146660804749</t>
   </si>
   <si>
     <t xml:space="preserve">2.83232522010803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8668966293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74096012115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70885896682739</t>
+    <t xml:space="preserve">2.86689686775208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74096035957336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70885872840881</t>
   </si>
   <si>
     <t xml:space="preserve">2.79034686088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82491779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84220314025879</t>
+    <t xml:space="preserve">2.82491755485535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84220337867737</t>
   </si>
   <si>
     <t xml:space="preserve">2.89158987998962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87183523178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90887475013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76812291145325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82244777679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85948777198792</t>
+    <t xml:space="preserve">2.87183499336243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90887427330017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76812267303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82244825363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85948824882507</t>
   </si>
   <si>
     <t xml:space="preserve">2.93850708007812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25211262702942</t>
+    <t xml:space="preserve">3.25211238861084</t>
   </si>
   <si>
     <t xml:space="preserve">3.29409122467041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25952005386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03234171867371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0274031162262</t>
+    <t xml:space="preserve">3.25952053070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03234195709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02740287780762</t>
   </si>
   <si>
     <t xml:space="preserve">3.16568541526794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52373957633972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39780330657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47188282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45953607559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4792914390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49410676956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55584001541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58547258377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57065606117249</t>
+    <t xml:space="preserve">3.52373933792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39780306816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47188305854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45953631401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47929120063782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49410700798035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55584049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58547282218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57065629959106</t>
   </si>
   <si>
     <t xml:space="preserve">3.56077909469604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60028910636902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62251257896423</t>
+    <t xml:space="preserve">3.6002893447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62251234054565</t>
   </si>
   <si>
     <t xml:space="preserve">3.55830931663513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72128534317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81265115737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85709977149963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93364882469177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93117904663086</t>
+    <t xml:space="preserve">3.72128558158875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81265211105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85709953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93364858627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93117880821228</t>
   </si>
   <si>
     <t xml:space="preserve">3.97315764427185</t>
@@ -605,40 +605,40 @@
     <t xml:space="preserve">4.00525903701782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99044322967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15341854095459</t>
+    <t xml:space="preserve">3.99044275283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15341901779175</t>
   </si>
   <si>
     <t xml:space="preserve">4.19539785385132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21762228012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29664087295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30651807785034</t>
+    <t xml:space="preserve">4.21762180328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29664039611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30651760101318</t>
   </si>
   <si>
     <t xml:space="preserve">4.17564296722412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26453971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31392574310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30898714065552</t>
+    <t xml:space="preserve">4.26453924179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31392621994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30898761749268</t>
   </si>
   <si>
     <t xml:space="preserve">4.27935552597046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42257690429688</t>
+    <t xml:space="preserve">4.42257642745972</t>
   </si>
   <si>
     <t xml:space="preserve">4.5065336227417</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">4.88928031921387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95842218399048</t>
+    <t xml:space="preserve">4.95842266082764</t>
   </si>
   <si>
     <t xml:space="preserve">5.01274824142456</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17078447341919</t>
+    <t xml:space="preserve">5.17078495025635</t>
   </si>
   <si>
     <t xml:space="preserve">4.33615064620972</t>
@@ -668,52 +668,52 @@
     <t xml:space="preserve">4.53616619110107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34602737426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39047479629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41516780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6275315284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64234733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71889734268188</t>
+    <t xml:space="preserve">4.34602689743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39047574996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41516828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62753105163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64234828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71889638900757</t>
   </si>
   <si>
     <t xml:space="preserve">4.99793195724487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0423789024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10164308547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1263370513916</t>
+    <t xml:space="preserve">5.04237842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10164403915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12633657455444</t>
   </si>
   <si>
     <t xml:space="preserve">4.95348405838013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98805332183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99299240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00287008285522</t>
+    <t xml:space="preserve">4.98805379867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99299192428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00287055969238</t>
   </si>
   <si>
     <t xml:space="preserve">5.04731702804565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92385101318359</t>
+    <t xml:space="preserve">4.92385149002075</t>
   </si>
   <si>
     <t xml:space="preserve">4.78062963485718</t>
@@ -722,16 +722,16 @@
     <t xml:space="preserve">4.8991584777832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02756357192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33869981765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34363794326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32388353347778</t>
+    <t xml:space="preserve">5.02756309509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33869886398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34363698959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32388401031494</t>
   </si>
   <si>
     <t xml:space="preserve">5.25474214553833</t>
@@ -740,31 +740,31 @@
     <t xml:space="preserve">5.32882213592529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1757230758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14609003067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18560028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18066263198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13127565383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13621473312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16584634780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09670448303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14115190505981</t>
+    <t xml:space="preserve">5.17572402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14609146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18559980392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18066167831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13127517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13621377944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.165846824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09670400619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14115238189697</t>
   </si>
   <si>
     <t xml:space="preserve">5.22511053085327</t>
@@ -773,13 +773,13 @@
     <t xml:space="preserve">5.30412864685059</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2102952003479</t>
+    <t xml:space="preserve">5.21029472351074</t>
   </si>
   <si>
     <t xml:space="preserve">4.98311519622803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94360542297363</t>
+    <t xml:space="preserve">4.94360494613647</t>
   </si>
   <si>
     <t xml:space="preserve">4.96336078643799</t>
@@ -788,52 +788,52 @@
     <t xml:space="preserve">4.93372821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07695007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07201099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06213426589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81026268005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83248567581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74358987808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78556823730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73371267318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71642684936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70655012130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69420289993286</t>
+    <t xml:space="preserve">5.07694959640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07201147079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06213474273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81026220321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83248615264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74358940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78556776046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7337121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71642732620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70655059814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69420337677002</t>
   </si>
   <si>
     <t xml:space="preserve">4.51887989044189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45220899581909</t>
+    <t xml:space="preserve">4.45220804214478</t>
   </si>
   <si>
     <t xml:space="preserve">4.6472864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70408010482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63000059127808</t>
+    <t xml:space="preserve">4.70408058166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63000106811523</t>
   </si>
   <si>
     <t xml:space="preserve">4.79297685623169</t>
@@ -842,55 +842,55 @@
     <t xml:space="preserve">4.78803777694702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23498773574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91644334793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97323751449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0522575378418</t>
+    <t xml:space="preserve">5.23498725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91644287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97323799133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05225706100464</t>
   </si>
   <si>
     <t xml:space="preserve">5.03744029998779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91891288757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9485445022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02262496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76828336715698</t>
+    <t xml:space="preserve">4.91891241073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94854497909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02262449264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76828384399414</t>
   </si>
   <si>
     <t xml:space="preserve">4.62012386322021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80038452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72383546829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68926525115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66210222244263</t>
+    <t xml:space="preserve">4.80038499832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72383642196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68926429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66210174560547</t>
   </si>
   <si>
     <t xml:space="preserve">4.67197942733765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59049129486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.583083152771</t>
+    <t xml:space="preserve">4.590491771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58308362960815</t>
   </si>
   <si>
     <t xml:space="preserve">4.61518526077271</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">4.84730195999146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83001613616943</t>
+    <t xml:space="preserve">4.83001565933228</t>
   </si>
   <si>
     <t xml:space="preserve">4.75346708297729</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">4.80532360076904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75099849700928</t>
+    <t xml:space="preserve">4.75099802017212</t>
   </si>
   <si>
     <t xml:space="preserve">4.79544687271118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8176703453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78309965133667</t>
+    <t xml:space="preserve">4.81767082214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78309917449951</t>
   </si>
   <si>
     <t xml:space="preserve">4.7213659286499</t>
@@ -932,34 +932,34 @@
     <t xml:space="preserve">4.778160572052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7608757019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55839014053345</t>
+    <t xml:space="preserve">4.76087522506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55838966369629</t>
   </si>
   <si>
     <t xml:space="preserve">4.85507869720459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8600378036499</t>
+    <t xml:space="preserve">4.86003732681274</t>
   </si>
   <si>
     <t xml:space="preserve">4.78564929962158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82532215118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80548572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87243556976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95922231674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99889612197876</t>
+    <t xml:space="preserve">4.8253231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80548620223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87243461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95922136306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9988956451416</t>
   </si>
   <si>
     <t xml:space="preserve">5.19230508804321</t>
@@ -968,10 +968,10 @@
     <t xml:space="preserve">5.15263223648071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1724681854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10799837112427</t>
+    <t xml:space="preserve">5.17246866226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10799884796143</t>
   </si>
   <si>
     <t xml:space="preserve">5.17742776870728</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">4.97409963607788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97905969619751</t>
+    <t xml:space="preserve">4.97905921936035</t>
   </si>
   <si>
     <t xml:space="preserve">4.98897743225098</t>
@@ -989,127 +989,127 @@
     <t xml:space="preserve">5.03856945037842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03360986709595</t>
+    <t xml:space="preserve">5.03361034393311</t>
   </si>
   <si>
     <t xml:space="preserve">5.05840635299683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07328414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02865076065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07824277877808</t>
+    <t xml:space="preserve">5.07328462600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02865171432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07824325561523</t>
   </si>
   <si>
     <t xml:space="preserve">5.06336498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95178365707397</t>
+    <t xml:space="preserve">4.95178318023682</t>
   </si>
   <si>
     <t xml:space="preserve">4.95426273345947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86995649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26669406890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40555238723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34604167938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30636787414551</t>
+    <t xml:space="preserve">4.86995601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26669454574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40555191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34604120254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30636739730835</t>
   </si>
   <si>
     <t xml:space="preserve">5.67334985733032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68822765350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01553583145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19406843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14943599700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1643123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07008790969849</t>
+    <t xml:space="preserve">5.68822717666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01553773880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19406890869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14943552017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16431283950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07008838653564</t>
   </si>
   <si>
     <t xml:space="preserve">6.13951683044434</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27341651916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61560249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53129482269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50649929046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78421545028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70982885360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7247052192688</t>
+    <t xml:space="preserve">6.27341604232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61560297012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53129577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50649976730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78421688079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70982789993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72470474243164</t>
   </si>
   <si>
     <t xml:space="preserve">6.76933813095093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80405235290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96770763397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88340044021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99250268936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07681035995483</t>
+    <t xml:space="preserve">6.80405282974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96770715713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88340091705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99250364303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07680940628052</t>
   </si>
   <si>
     <t xml:space="preserve">7.14623928070068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18095397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46362972259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31485366821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3346905708313</t>
+    <t xml:space="preserve">7.18095445632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46362924575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31485271453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33468914031982</t>
   </si>
   <si>
     <t xml:space="preserve">7.38428163528442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36444520950317</t>
+    <t xml:space="preserve">7.36444473266602</t>
   </si>
   <si>
     <t xml:space="preserve">7.51818180084229</t>
@@ -1118,37 +1118,37 @@
     <t xml:space="preserve">7.58265113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5628137588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53801727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49338388442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4090781211853</t>
+    <t xml:space="preserve">7.56281328201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53801918029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49338483810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40907764434814</t>
   </si>
   <si>
     <t xml:space="preserve">7.52313947677612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4140362739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50330400466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42395496368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45867013931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41899633407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30989456176758</t>
+    <t xml:space="preserve">7.41403675079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50330352783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4239559173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45866966247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41899538040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3098931312561</t>
   </si>
   <si>
     <t xml:space="preserve">7.37932300567627</t>
@@ -1157,37 +1157,37 @@
     <t xml:space="preserve">6.93795204162598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05697298049927</t>
+    <t xml:space="preserve">7.05697345733643</t>
   </si>
   <si>
     <t xml:space="preserve">7.02225828170776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14127969741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34956741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35948657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5132212638855</t>
+    <t xml:space="preserve">7.14128065109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34956836700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35948610305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51322221755981</t>
   </si>
   <si>
     <t xml:space="preserve">7.76614141464233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73142719268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66199922561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45371150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28013753890991</t>
+    <t xml:space="preserve">7.73142766952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6619987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45371103286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28013706207275</t>
   </si>
   <si>
     <t xml:space="preserve">7.33964872360229</t>
@@ -1196,85 +1196,85 @@
     <t xml:space="preserve">7.3743634223938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25038385391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43387413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55785417556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24046325683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20079040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17103624343872</t>
+    <t xml:space="preserve">7.25038242340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43387365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55785512924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24046421051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20078992843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17103672027588</t>
   </si>
   <si>
     <t xml:space="preserve">7.15119886398315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00738143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2355055809021</t>
+    <t xml:space="preserve">7.00738096237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23550415039062</t>
   </si>
   <si>
     <t xml:space="preserve">7.19087219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53305864334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52809906005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50826358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43883275985718</t>
+    <t xml:space="preserve">7.53305959701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52809953689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50826263427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43883228302002</t>
   </si>
   <si>
     <t xml:space="preserve">7.44875192642212</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6372013092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65208005905151</t>
+    <t xml:space="preserve">7.63720178604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6520791053772</t>
   </si>
   <si>
     <t xml:space="preserve">7.64216184616089</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69175386428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67191648483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297733306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39420080184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71158981323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35628986358643</t>
+    <t xml:space="preserve">7.69175434112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67191743850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297780990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39419937133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71159172058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35628890991211</t>
   </si>
   <si>
     <t xml:space="preserve">8.88692665100098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98115062713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15968322753906</t>
+    <t xml:space="preserve">8.98115158081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15968418121338</t>
   </si>
   <si>
     <t xml:space="preserve">9.2142333984375</t>
@@ -1283,28 +1283,28 @@
     <t xml:space="preserve">9.42252254486084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48699378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69032096862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28862190246582</t>
+    <t xml:space="preserve">9.48699188232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69032001495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28862380981445</t>
   </si>
   <si>
     <t xml:space="preserve">9.32829761505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50187110900879</t>
+    <t xml:space="preserve">9.50186920166016</t>
   </si>
   <si>
     <t xml:space="preserve">9.69528007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76470756530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7052001953125</t>
+    <t xml:space="preserve">9.76470851898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70519733428955</t>
   </si>
   <si>
     <t xml:space="preserve">9.64072704315186</t>
@@ -1319,43 +1319,43 @@
     <t xml:space="preserve">9.84108066558838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68337821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65163993835449</t>
+    <t xml:space="preserve">9.68337631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65163898468018</t>
   </si>
   <si>
     <t xml:space="preserve">9.53856754302979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31936931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75798606872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35110950469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89982223510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63698196411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75302600860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57548713684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77782249450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82741641998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00396537780762</t>
+    <t xml:space="preserve">9.31937122344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7579870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35110855102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89982128143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63698291778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75302696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57548809051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77782344818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82741546630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0039644241333</t>
   </si>
   <si>
     <t xml:space="preserve">8.8373327255249</t>
@@ -1367,100 +1367,100 @@
     <t xml:space="preserve">8.98908615112305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80956172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73814964294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69054126739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80559635162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71434593200684</t>
+    <t xml:space="preserve">8.80956363677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73815155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6905403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80559539794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71434497833252</t>
   </si>
   <si>
     <t xml:space="preserve">8.47431945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98930835723877</t>
+    <t xml:space="preserve">7.98930644989014</t>
   </si>
   <si>
     <t xml:space="preserve">8.01410293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46836853027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.556640625</t>
+    <t xml:space="preserve">8.46836757659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55664157867432</t>
   </si>
   <si>
     <t xml:space="preserve">8.56259250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51597595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52787685394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53085327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43266201019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53184604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52589321136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35926532745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5645751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71732139587402</t>
+    <t xml:space="preserve">8.51597690582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5278787612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53085422515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43266105651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53184509277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52589416503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3592643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56457710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71732044219971</t>
   </si>
   <si>
     <t xml:space="preserve">8.42175197601318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25115394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18866729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32554244995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15791988372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18370723724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78278255462646</t>
+    <t xml:space="preserve">8.25115299224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1886682510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32554149627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15792179107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18370914459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78278350830078</t>
   </si>
   <si>
     <t xml:space="preserve">8.73517322540283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15869235992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07438373565674</t>
+    <t xml:space="preserve">9.15869045257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07438564300537</t>
   </si>
   <si>
     <t xml:space="preserve">9.18943881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31341934204102</t>
+    <t xml:space="preserve">9.31342124938965</t>
   </si>
   <si>
     <t xml:space="preserve">9.22613716125488</t>
@@ -1472,22 +1472,22 @@
     <t xml:space="preserve">9.43640804290771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36301136016846</t>
+    <t xml:space="preserve">9.36301231384277</t>
   </si>
   <si>
     <t xml:space="preserve">9.70916557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76768398284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63180255889893</t>
+    <t xml:space="preserve">9.7676830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63180160522461</t>
   </si>
   <si>
     <t xml:space="preserve">9.55840492248535</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7597484588623</t>
+    <t xml:space="preserve">9.75974941253662</t>
   </si>
   <si>
     <t xml:space="preserve">9.79148769378662</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">9.49393558502197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68635272979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41458797454834</t>
+    <t xml:space="preserve">9.68635368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41458702087402</t>
   </si>
   <si>
     <t xml:space="preserve">9.20927715301514</t>
@@ -1508,19 +1508,19 @@
     <t xml:space="preserve">9.43739891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21820163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51674747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53559303283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48005104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29556560516357</t>
+    <t xml:space="preserve">9.21820259094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51674652099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5355920791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48004817962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29556655883789</t>
   </si>
   <si>
     <t xml:space="preserve">9.30845928192139</t>
@@ -1532,46 +1532,46 @@
     <t xml:space="preserve">9.41756439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36697959899902</t>
+    <t xml:space="preserve">9.36697864532471</t>
   </si>
   <si>
     <t xml:space="preserve">9.30746936798096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36796855926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1993579864502</t>
+    <t xml:space="preserve">9.36797046661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19935703277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.43938446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59609508514404</t>
+    <t xml:space="preserve">9.59609413146973</t>
   </si>
   <si>
     <t xml:space="preserve">9.48600006103516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31143665313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3054838180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10810852050781</t>
+    <t xml:space="preserve">9.31143474578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30548477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1081075668335</t>
   </si>
   <si>
     <t xml:space="preserve">9.06446552276611</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42747974395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62089061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18547058105469</t>
+    <t xml:space="preserve">9.42748069763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62089157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.185471534729</t>
   </si>
   <si>
     <t xml:space="preserve">8.85221099853516</t>
@@ -1580,73 +1580,73 @@
     <t xml:space="preserve">8.87601566314697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86212921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13984775543213</t>
+    <t xml:space="preserve">8.86213111877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1398458480835</t>
   </si>
   <si>
     <t xml:space="preserve">8.90676307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98313522338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92659854888916</t>
+    <t xml:space="preserve">8.98313617706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92659950256348</t>
   </si>
   <si>
     <t xml:space="preserve">8.85022735595703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04462909698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87403202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92461585998535</t>
+    <t xml:space="preserve">9.04462814331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87403297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92461490631104</t>
   </si>
   <si>
     <t xml:space="preserve">8.79666900634766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75005149841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38505363464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18172454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92979574203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15296173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24123668670654</t>
+    <t xml:space="preserve">8.75005054473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38505268096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18172550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92979717254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15296077728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24123477935791</t>
   </si>
   <si>
     <t xml:space="preserve">7.95558452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10039234161377</t>
+    <t xml:space="preserve">8.10039329528809</t>
   </si>
   <si>
     <t xml:space="preserve">8.10237693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03889942169189</t>
+    <t xml:space="preserve">8.03889846801758</t>
   </si>
   <si>
     <t xml:space="preserve">8.50506687164307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40687370300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4693603515625</t>
+    <t xml:space="preserve">8.40687274932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46935844421387</t>
   </si>
   <si>
     <t xml:space="preserve">8.52291965484619</t>
@@ -1655,106 +1655,106 @@
     <t xml:space="preserve">8.26305675506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21346473693848</t>
+    <t xml:space="preserve">8.21346282958984</t>
   </si>
   <si>
     <t xml:space="preserve">8.25214672088623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19957828521729</t>
+    <t xml:space="preserve">8.19957733154297</t>
   </si>
   <si>
     <t xml:space="preserve">8.24917030334473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22239017486572</t>
+    <t xml:space="preserve">8.22239112854004</t>
   </si>
   <si>
     <t xml:space="preserve">8.33347702026367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14105987548828</t>
+    <t xml:space="preserve">8.14105892181396</t>
   </si>
   <si>
     <t xml:space="preserve">8.01906204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21048831939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16111612319946</t>
+    <t xml:space="preserve">8.21048736572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16111660003662</t>
   </si>
   <si>
     <t xml:space="preserve">7.26426839828491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23947334289551</t>
+    <t xml:space="preserve">7.23947238922119</t>
   </si>
   <si>
     <t xml:space="preserve">7.04804563522339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04209566116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2434401512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23352098464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20277404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24839878082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1750020980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04407978057861</t>
+    <t xml:space="preserve">7.0420970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24343967437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23352193832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20277500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24839925765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17500305175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0440788269043</t>
   </si>
   <si>
     <t xml:space="preserve">6.97663259506226</t>
   </si>
   <si>
-    <t xml:space="preserve">6.808021068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79909229278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01729869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12243413925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03713655471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95977210998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1859130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4348669052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42693138122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36146926879883</t>
+    <t xml:space="preserve">6.80801963806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7990927696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01729822158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12243461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0371356010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95977115631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18591260910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43486595153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42693185806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36146879196167</t>
   </si>
   <si>
     <t xml:space="preserve">7.22062683105469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.268235206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39320802688599</t>
+    <t xml:space="preserve">7.26823568344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39320755004883</t>
   </si>
   <si>
     <t xml:space="preserve">7.22657918930054</t>
@@ -1763,100 +1763,100 @@
     <t xml:space="preserve">7.21566820144653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.167067527771</t>
+    <t xml:space="preserve">7.16706705093384</t>
   </si>
   <si>
     <t xml:space="preserve">7.48247480392456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40610218048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42792272567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45767831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48346614837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61934852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73341131210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66001462936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70266437530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66794872283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51024627685547</t>
+    <t xml:space="preserve">7.40610313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42792224884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45768022537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48346662521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61934900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73341178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66001558303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70266342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66794919967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51024532318115</t>
   </si>
   <si>
     <t xml:space="preserve">7.68282651901245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6937370300293</t>
+    <t xml:space="preserve">7.69373750686646</t>
   </si>
   <si>
     <t xml:space="preserve">7.64017772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57769250869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52016448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34460783004761</t>
+    <t xml:space="preserve">7.57769060134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52016401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34460830688477</t>
   </si>
   <si>
     <t xml:space="preserve">7.42197179794312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01035642623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96274852752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92803382873535</t>
+    <t xml:space="preserve">7.01035690307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96274900436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92803287506104</t>
   </si>
   <si>
     <t xml:space="preserve">6.94588708877563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17797803878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87744998931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82587432861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66618680953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86455631256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95183897018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78024816513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04705476760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81992197036743</t>
+    <t xml:space="preserve">7.17797899246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87744951248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82587289810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66618585586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86455535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95183706283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78024911880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0470552444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81992244720459</t>
   </si>
   <si>
     <t xml:space="preserve">6.67015361785889</t>
@@ -1865,40 +1865,40 @@
     <t xml:space="preserve">6.75247669219971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02920198440552</t>
+    <t xml:space="preserve">7.02920055389404</t>
   </si>
   <si>
     <t xml:space="preserve">7.11251592636108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09664583206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26129388809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28708171844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08672666549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30394172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23054504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1333441734314</t>
+    <t xml:space="preserve">7.09664726257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26129293441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28708124160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08672904968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30394268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23054552078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13334465026855</t>
   </si>
   <si>
     <t xml:space="preserve">7.12838649749756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94291019439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01233911514282</t>
+    <t xml:space="preserve">6.94291114807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01234149932861</t>
   </si>
   <si>
     <t xml:space="preserve">6.93001747131348</t>
@@ -1907,217 +1907,217 @@
     <t xml:space="preserve">6.99052000045776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33865690231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34758234024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30493354797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49636030197144</t>
+    <t xml:space="preserve">7.33865642547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34758329391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30493402481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49635887145996</t>
   </si>
   <si>
     <t xml:space="preserve">7.34857559204102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2345118522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86554622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8248815536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61064291000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7832236289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91613245010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92208194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86852216720581</t>
+    <t xml:space="preserve">7.23451280593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86554670333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82488203048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61064386367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78322410583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91613149642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92208242416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86852264404297</t>
   </si>
   <si>
     <t xml:space="preserve">6.82884883880615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82289838790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72272205352783</t>
+    <t xml:space="preserve">6.82289791107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72272109985352</t>
   </si>
   <si>
     <t xml:space="preserve">6.50848340988159</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25754642486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28928565979004</t>
+    <t xml:space="preserve">6.25754690170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28928470611572</t>
   </si>
   <si>
     <t xml:space="preserve">6.23175811767578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15737009048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50253295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55113172531128</t>
+    <t xml:space="preserve">6.1573691368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50253248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55113220214844</t>
   </si>
   <si>
     <t xml:space="preserve">6.62849617004395</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87645626068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01134824752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16012525558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24443101882935</t>
+    <t xml:space="preserve">6.87645769119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01134872436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1601243019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24443244934082</t>
   </si>
   <si>
     <t xml:space="preserve">7.2107081413269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32080364227295</t>
+    <t xml:space="preserve">7.32080411911011</t>
   </si>
   <si>
     <t xml:space="preserve">7.10557317733765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26724338531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1869044303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18988084793091</t>
+    <t xml:space="preserve">7.26724433898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18690490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18987989425659</t>
   </si>
   <si>
     <t xml:space="preserve">7.28509712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39816856384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47354793548584</t>
+    <t xml:space="preserve">7.39816761016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47354698181152</t>
   </si>
   <si>
     <t xml:space="preserve">7.52710723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63544034957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44302177429199</t>
+    <t xml:space="preserve">6.6354398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44302129745483</t>
   </si>
   <si>
     <t xml:space="preserve">6.4182243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39739608764648</t>
+    <t xml:space="preserve">6.39739656448364</t>
   </si>
   <si>
     <t xml:space="preserve">6.4975733757019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40731430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45988321304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44897317886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45194721221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57691955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50154113769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51145887374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54617214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4559154510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43806219100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41227340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36268186569214</t>
+    <t xml:space="preserve">6.40731477737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45988273620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44897270202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45194816589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57692003250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50154066085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5114598274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54617404937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45591449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43806171417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41227436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36268138885498</t>
   </si>
   <si>
     <t xml:space="preserve">6.41524934768677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64932441711426</t>
+    <t xml:space="preserve">6.64932489395142</t>
   </si>
   <si>
     <t xml:space="preserve">6.32697534561157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36664962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35871458053589</t>
+    <t xml:space="preserve">6.36664867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35871505737305</t>
   </si>
   <si>
     <t xml:space="preserve">6.30416345596313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2585391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26548147201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32003164291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63643026351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.469801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49658060073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33590221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4638500213623</t>
+    <t xml:space="preserve">6.25853872299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26548051834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32003259658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6364312171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46980094909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49658107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33590269088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46385049819946</t>
   </si>
   <si>
     <t xml:space="preserve">6.49162197113037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66122817993164</t>
+    <t xml:space="preserve">6.66122722625732</t>
   </si>
   <si>
     <t xml:space="preserve">6.52633666992188</t>
@@ -2126,40 +2126,40 @@
     <t xml:space="preserve">6.58188009262085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73958206176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80603504180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80901193618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81000375747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93894338607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86157941818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89133453369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89232778549194</t>
+    <t xml:space="preserve">6.73958301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80603694915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80901098251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81000423431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93894481658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86158037185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89133501052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89232683181763</t>
   </si>
   <si>
     <t xml:space="preserve">7.04308700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0936713218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607666015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29303216934204</t>
+    <t xml:space="preserve">7.09367227554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607570648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2930326461792</t>
   </si>
   <si>
     <t xml:space="preserve">7.28431129455566</t>
@@ -2168,70 +2168,70 @@
     <t xml:space="preserve">7.20211410522461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14384794235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20939779281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19171047210693</t>
+    <t xml:space="preserve">7.14384889602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20939826965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19170951843262</t>
   </si>
   <si>
     <t xml:space="preserve">7.14488935470581</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04916667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11263465881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07205677032471</t>
+    <t xml:space="preserve">7.04916620254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3737907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11263513565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07205533981323</t>
   </si>
   <si>
     <t xml:space="preserve">6.80673742294312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73806667327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61112928390503</t>
+    <t xml:space="preserve">6.73806715011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61112976074219</t>
   </si>
   <si>
     <t xml:space="preserve">6.71309566497803</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81402063369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88997411727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9544825553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93350172042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88365364074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82684993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62166213989258</t>
+    <t xml:space="preserve">6.81401920318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88997459411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95448303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93350076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88365411758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82684898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62166309356689</t>
   </si>
   <si>
     <t xml:space="preserve">6.64021015167236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16999053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10623168945312</t>
+    <t xml:space="preserve">7.16998958587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10623073577881</t>
   </si>
   <si>
     <t xml:space="preserve">7.019287109375</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">6.96132373809814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62977743148804</t>
+    <t xml:space="preserve">6.6297779083252</t>
   </si>
   <si>
     <t xml:space="preserve">6.59268093109131</t>
@@ -2261,19 +2261,19 @@
     <t xml:space="preserve">6.88133478164673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94625377655029</t>
+    <t xml:space="preserve">6.94625282287598</t>
   </si>
   <si>
     <t xml:space="preserve">6.83728361129761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89524507522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86278676986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92422866821289</t>
+    <t xml:space="preserve">6.8952465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86278581619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92422771453857</t>
   </si>
   <si>
     <t xml:space="preserve">6.98566722869873</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">7.06449747085571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15028142929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13521099090576</t>
+    <t xml:space="preserve">7.15028238296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13521194458008</t>
   </si>
   <si>
     <t xml:space="preserve">7.14216709136963</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">7.02160549163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03319787979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08072662353516</t>
+    <t xml:space="preserve">7.03319692611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.080726146698</t>
   </si>
   <si>
     <t xml:space="preserve">7.10970783233643</t>
@@ -2309,16 +2309,16 @@
     <t xml:space="preserve">7.13057518005371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33112668991089</t>
+    <t xml:space="preserve">7.33112573623657</t>
   </si>
   <si>
     <t xml:space="preserve">7.35315227508545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32532930374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28939247131348</t>
+    <t xml:space="preserve">7.32532978057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28939342498779</t>
   </si>
   <si>
     <t xml:space="preserve">7.20940446853638</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">7.28707504272461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28591442108154</t>
+    <t xml:space="preserve">7.28591537475586</t>
   </si>
   <si>
     <t xml:space="preserve">7.05986070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07493114471436</t>
+    <t xml:space="preserve">7.07493019104004</t>
   </si>
   <si>
     <t xml:space="preserve">6.95900535583496</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">7.17578554153442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3114185333252</t>
+    <t xml:space="preserve">7.31141757965088</t>
   </si>
   <si>
     <t xml:space="preserve">7.19433403015137</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">7.08768320083618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97639417648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99841928482056</t>
+    <t xml:space="preserve">6.976393699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99842023849487</t>
   </si>
   <si>
     <t xml:space="preserve">6.76541042327881</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">6.81873607635498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8685827255249</t>
+    <t xml:space="preserve">6.86858320236206</t>
   </si>
   <si>
     <t xml:space="preserve">6.72715377807617</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">6.72367668151855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82569122314453</t>
+    <t xml:space="preserve">6.82569074630737</t>
   </si>
   <si>
     <t xml:space="preserve">6.58572435379028</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">6.68194389343262</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69005727767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54515171051025</t>
+    <t xml:space="preserve">6.6900577545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54515075683594</t>
   </si>
   <si>
     <t xml:space="preserve">6.63557291030884</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">7.0830454826355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29055309295654</t>
+    <t xml:space="preserve">7.29055213928223</t>
   </si>
   <si>
     <t xml:space="preserve">7.30562257766724</t>
@@ -2426,10 +2426,10 @@
     <t xml:space="preserve">7.37285900115967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28243637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28127908706665</t>
+    <t xml:space="preserve">7.28243732452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28127813339233</t>
   </si>
   <si>
     <t xml:space="preserve">7.29287147521973</t>
@@ -2456,22 +2456,22 @@
     <t xml:space="preserve">6.87785673141479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81525754928589</t>
+    <t xml:space="preserve">6.81525659561157</t>
   </si>
   <si>
     <t xml:space="preserve">6.63093614578247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54051446914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53239917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57529211044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50921392440796</t>
+    <t xml:space="preserve">6.54051351547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53239870071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5752911567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50921487808228</t>
   </si>
   <si>
     <t xml:space="preserve">6.54862928390503</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">6.73410987854004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87553930282593</t>
+    <t xml:space="preserve">6.87554025650024</t>
   </si>
   <si>
     <t xml:space="preserve">6.91843128204346</t>
@@ -2492,13 +2492,13 @@
     <t xml:space="preserve">7.03899431228638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87206125259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95668601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90915632247925</t>
+    <t xml:space="preserve">6.87206172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95668697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90915679931641</t>
   </si>
   <si>
     <t xml:space="preserve">6.87321996688843</t>
@@ -2510,25 +2510,25 @@
     <t xml:space="preserve">6.90336036682129</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81062126159668</t>
+    <t xml:space="preserve">6.81062030792236</t>
   </si>
   <si>
     <t xml:space="preserve">7.45980310440063</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0730504989624</t>
+    <t xml:space="preserve">8.07304859161377</t>
   </si>
   <si>
     <t xml:space="preserve">8.12057781219482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32808494567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37561511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38025188446045</t>
+    <t xml:space="preserve">8.32808399200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37561416625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38025093078613</t>
   </si>
   <si>
     <t xml:space="preserve">8.40691471099854</t>
@@ -2537,25 +2537,25 @@
     <t xml:space="preserve">8.48226547241211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41039180755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5112476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41386985778809</t>
+    <t xml:space="preserve">8.41039085388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51124668121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41386890411377</t>
   </si>
   <si>
     <t xml:space="preserve">8.40807437896729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42198467254639</t>
+    <t xml:space="preserve">8.42198371887207</t>
   </si>
   <si>
     <t xml:space="preserve">8.1843376159668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19245147705078</t>
+    <t xml:space="preserve">8.1924524307251</t>
   </si>
   <si>
     <t xml:space="preserve">8.09623432159424</t>
@@ -2564,22 +2564,22 @@
     <t xml:space="preserve">7.79019117355347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74613952636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88177251815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87713479995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89104604721069</t>
+    <t xml:space="preserve">7.7461404800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88177394866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87713527679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89104557037354</t>
   </si>
   <si>
     <t xml:space="preserve">7.82033109664917</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77859783172607</t>
+    <t xml:space="preserve">7.77859878540039</t>
   </si>
   <si>
     <t xml:space="preserve">7.70440530776978</t>
@@ -2609,31 +2609,31 @@
     <t xml:space="preserve">7.64760255813599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72411298751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80757999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88525056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88409090042114</t>
+    <t xml:space="preserve">7.72411346435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80757904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88524961471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88408994674683</t>
   </si>
   <si>
     <t xml:space="preserve">7.91191244125366</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82844686508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78439474105835</t>
+    <t xml:space="preserve">7.82844591140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78439378738403</t>
   </si>
   <si>
     <t xml:space="preserve">7.7415018081665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58036470413208</t>
+    <t xml:space="preserve">7.5803656578064</t>
   </si>
   <si>
     <t xml:space="preserve">7.47719192504883</t>
@@ -2642,7 +2642,7 @@
     <t xml:space="preserve">7.51197004318237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41691112518311</t>
+    <t xml:space="preserve">7.41691207885742</t>
   </si>
   <si>
     <t xml:space="preserve">7.43777751922607</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">7.22911167144775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21867752075195</t>
+    <t xml:space="preserve">7.21867799758911</t>
   </si>
   <si>
     <t xml:space="preserve">7.20592641830444</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">7.22099733352661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14680337905884</t>
+    <t xml:space="preserve">7.14680528640747</t>
   </si>
   <si>
     <t xml:space="preserve">6.98219013214111</t>
@@ -2681,13 +2681,13 @@
     <t xml:space="preserve">6.96364259719849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03087854385376</t>
+    <t xml:space="preserve">7.03088045120239</t>
   </si>
   <si>
     <t xml:space="preserve">6.9126353263855</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8001880645752</t>
+    <t xml:space="preserve">6.80018711090088</t>
   </si>
   <si>
     <t xml:space="preserve">6.85235357284546</t>
@@ -2702,13 +2702,13 @@
     <t xml:space="preserve">7.03203821182251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29403018951416</t>
+    <t xml:space="preserve">7.29402923583984</t>
   </si>
   <si>
     <t xml:space="preserve">7.10738945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14100790023804</t>
+    <t xml:space="preserve">7.1410083770752</t>
   </si>
   <si>
     <t xml:space="preserve">7.11086750030518</t>
@@ -2717,22 +2717,22 @@
     <t xml:space="preserve">7.1155047416687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00189828872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57297229766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52544450759888</t>
+    <t xml:space="preserve">7.00189733505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57297277450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52544355392456</t>
   </si>
   <si>
     <t xml:space="preserve">6.70165061950684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51616954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27620410919189</t>
+    <t xml:space="preserve">6.51616907119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27620458602905</t>
   </si>
   <si>
     <t xml:space="preserve">6.3411226272583</t>
@@ -2744,13 +2744,13 @@
     <t xml:space="preserve">6.2843189239502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09651899337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43806314468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40676259994507</t>
+    <t xml:space="preserve">6.096519947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.438063621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40676307678223</t>
   </si>
   <si>
     <t xml:space="preserve">5.51921129226685</t>
@@ -2759,19 +2759,19 @@
     <t xml:space="preserve">4.53326463699341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85785579681396</t>
+    <t xml:space="preserve">4.85785627365112</t>
   </si>
   <si>
     <t xml:space="preserve">4.15534782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97914123535156</t>
+    <t xml:space="preserve">3.9791407585144</t>
   </si>
   <si>
     <t xml:space="preserve">3.54731917381287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36531591415405</t>
+    <t xml:space="preserve">3.36531543731689</t>
   </si>
   <si>
     <t xml:space="preserve">3.56122994422913</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">3.40994739532471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84872460365295</t>
+    <t xml:space="preserve">3.84872508049011</t>
   </si>
   <si>
     <t xml:space="preserve">3.96117329597473</t>
@@ -2795,22 +2795,22 @@
     <t xml:space="preserve">3.65744781494141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80931043624878</t>
+    <t xml:space="preserve">3.80930995941162</t>
   </si>
   <si>
     <t xml:space="preserve">3.66498351097107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64295721054077</t>
+    <t xml:space="preserve">3.64295768737793</t>
   </si>
   <si>
     <t xml:space="preserve">3.59368896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83481335639954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08289480209351</t>
+    <t xml:space="preserve">3.83481383323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08289432525635</t>
   </si>
   <si>
     <t xml:space="preserve">4.12636661529541</t>
@@ -2822,19 +2822,19 @@
     <t xml:space="preserve">4.32401990890503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10434007644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12057018280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24403047561646</t>
+    <t xml:space="preserve">4.10434055328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12056970596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24403095245361</t>
   </si>
   <si>
     <t xml:space="preserve">4.30663061141968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11419486999512</t>
+    <t xml:space="preserve">4.11419439315796</t>
   </si>
   <si>
     <t xml:space="preserve">4.20229768753052</t>
@@ -2846,16 +2846,16 @@
     <t xml:space="preserve">4.26026010513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46197080612183</t>
+    <t xml:space="preserve">4.46197128295898</t>
   </si>
   <si>
     <t xml:space="preserve">4.57383918762207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74135112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64629220962524</t>
+    <t xml:space="preserve">4.74135208129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64629173278809</t>
   </si>
   <si>
     <t xml:space="preserve">4.38430070877075</t>
@@ -2873,10 +2873,10 @@
     <t xml:space="preserve">4.50370407104492</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42429494857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40053033828735</t>
+    <t xml:space="preserve">4.42429447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4005298614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.27475118637085</t>
@@ -2888,55 +2888,55 @@
     <t xml:space="preserve">4.17505502700806</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51703596115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31242752075195</t>
+    <t xml:space="preserve">4.51703548431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31242704391479</t>
   </si>
   <si>
     <t xml:space="preserve">4.25388431549072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29851627349854</t>
+    <t xml:space="preserve">4.29851675033569</t>
   </si>
   <si>
     <t xml:space="preserve">4.59934234619141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72859954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78192567825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6033992767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76511573791504</t>
+    <t xml:space="preserve">4.728600025177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78192520141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60339975357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7651162147522</t>
   </si>
   <si>
     <t xml:space="preserve">4.83293199539185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08217287063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04449558258057</t>
+    <t xml:space="preserve">5.08217144012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04449605941772</t>
   </si>
   <si>
     <t xml:space="preserve">5.39748907089233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45255279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21316862106323</t>
+    <t xml:space="preserve">5.45255327224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21316814422607</t>
   </si>
   <si>
     <t xml:space="preserve">5.07231855392456</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68164968490601</t>
+    <t xml:space="preserve">4.68164920806885</t>
   </si>
   <si>
     <t xml:space="preserve">4.74888610839844</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">4.88625764846802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86771011352539</t>
+    <t xml:space="preserve">4.86770963668823</t>
   </si>
   <si>
     <t xml:space="preserve">4.85263967514038</t>
@@ -2957,10 +2957,10 @@
     <t xml:space="preserve">4.89958906173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96624612808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25374174118042</t>
+    <t xml:space="preserve">4.96624660491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25374221801758</t>
   </si>
   <si>
     <t xml:space="preserve">5.02246999740601</t>
@@ -2969,10 +2969,10 @@
     <t xml:space="preserve">5.09550285339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00508117675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1169490814209</t>
+    <t xml:space="preserve">5.00508165359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11694955825806</t>
   </si>
   <si>
     <t xml:space="preserve">5.18418645858765</t>
@@ -2981,25 +2981,25 @@
     <t xml:space="preserve">5.09260559082031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21606540679932</t>
+    <t xml:space="preserve">5.21606588363647</t>
   </si>
   <si>
     <t xml:space="preserve">5.15868234634399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21896409988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20679235458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09840202331543</t>
+    <t xml:space="preserve">5.21896457672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20679187774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09840154647827</t>
   </si>
   <si>
     <t xml:space="preserve">5.00276279449463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11984825134277</t>
+    <t xml:space="preserve">5.11984872817993</t>
   </si>
   <si>
     <t xml:space="preserve">5.24910449981689</t>
@@ -3008,19 +3008,19 @@
     <t xml:space="preserve">5.20447301864624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25721979141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31692123413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31054449081421</t>
+    <t xml:space="preserve">5.2572193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31692171096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31054496765137</t>
   </si>
   <si>
     <t xml:space="preserve">5.34184455871582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35401678085327</t>
+    <t xml:space="preserve">5.35401630401611</t>
   </si>
   <si>
     <t xml:space="preserve">5.30822706222534</t>
@@ -3029,13 +3029,13 @@
     <t xml:space="preserve">5.3412652015686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26069688796997</t>
+    <t xml:space="preserve">5.26069736480713</t>
   </si>
   <si>
     <t xml:space="preserve">5.258957862854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37488460540771</t>
+    <t xml:space="preserve">5.37488412857056</t>
   </si>
   <si>
     <t xml:space="preserve">5.30764675140381</t>
@@ -3050,19 +3050,19 @@
     <t xml:space="preserve">5.44270133972168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44733715057373</t>
+    <t xml:space="preserve">5.44733667373657</t>
   </si>
   <si>
     <t xml:space="preserve">5.38937425613403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38183927536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47457885742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76323366165161</t>
+    <t xml:space="preserve">5.38183975219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47457981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76323270797729</t>
   </si>
   <si>
     <t xml:space="preserve">5.74178791046143</t>
@@ -3074,10 +3074,10 @@
     <t xml:space="preserve">5.61658811569214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59340286254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56848049163818</t>
+    <t xml:space="preserve">5.59340333938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56847953796387</t>
   </si>
   <si>
     <t xml:space="preserve">5.58065128326416</t>
@@ -3089,28 +3089,28 @@
     <t xml:space="preserve">5.40618371963501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5800724029541</t>
+    <t xml:space="preserve">5.58007287979126</t>
   </si>
   <si>
     <t xml:space="preserve">5.51631259918213</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54703378677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47747802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45719051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35054016113281</t>
+    <t xml:space="preserve">5.54703283309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47747755050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45719146728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35053968429565</t>
   </si>
   <si>
     <t xml:space="preserve">5.28736066818237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31750059127808</t>
+    <t xml:space="preserve">5.31750106811523</t>
   </si>
   <si>
     <t xml:space="preserve">5.37836217880249</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">5.58470821380615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57079744338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57137727737427</t>
+    <t xml:space="preserve">5.57079792022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57137823104858</t>
   </si>
   <si>
     <t xml:space="preserve">5.73019599914551</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">5.74642467498779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78641891479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30750465393066</t>
+    <t xml:space="preserve">5.78641939163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30750417709351</t>
   </si>
   <si>
     <t xml:space="preserve">6.26693058013916</t>
@@ -3158,100 +3158,100 @@
     <t xml:space="preserve">6.02232789993286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01189470291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92958641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16491508483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02116870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06753921508789</t>
+    <t xml:space="preserve">6.01189374923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92958736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16491603851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02116775512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06753778457642</t>
   </si>
   <si>
     <t xml:space="preserve">5.99914216995239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07681226730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18578195571899</t>
+    <t xml:space="preserve">6.07681274414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18578243255615</t>
   </si>
   <si>
     <t xml:space="preserve">6.2031717300415</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19041967391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10463428497314</t>
+    <t xml:space="preserve">6.19042062759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10463523864746</t>
   </si>
   <si>
     <t xml:space="preserve">6.16375637054443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06058263778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12666082382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99566459655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24954080581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22867488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24722290039062</t>
+    <t xml:space="preserve">6.06058216094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12665987014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99566507339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24954128265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22867441177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24722337722778</t>
   </si>
   <si>
     <t xml:space="preserve">6.20548963546753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35735130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43386268615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48023366928101</t>
+    <t xml:space="preserve">6.3573522567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43386173248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48023271560669</t>
   </si>
   <si>
     <t xml:space="preserve">6.37242269515991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12550020217896</t>
+    <t xml:space="preserve">6.12550067901611</t>
   </si>
   <si>
     <t xml:space="preserve">6.12318277359009</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11043071746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27156734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37937688827515</t>
+    <t xml:space="preserve">6.1104302406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27156686782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3793773651123</t>
   </si>
   <si>
     <t xml:space="preserve">6.47443723678589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51269197463989</t>
+    <t xml:space="preserve">6.51269149780273</t>
   </si>
   <si>
     <t xml:space="preserve">6.91031694412231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99146461486816</t>
+    <t xml:space="preserve">6.99146556854248</t>
   </si>
   <si>
     <t xml:space="preserve">7.07840919494629</t>
@@ -3263,25 +3263,25 @@
     <t xml:space="preserve">7.31837463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34851551055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5003776550293</t>
+    <t xml:space="preserve">7.34851598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50037670135498</t>
   </si>
   <si>
     <t xml:space="preserve">7.46560001373291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44705104827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58964061737061</t>
+    <t xml:space="preserve">7.44705057144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58963966369629</t>
   </si>
   <si>
     <t xml:space="preserve">7.64180707931519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58616209030151</t>
+    <t xml:space="preserve">7.58616161346436</t>
   </si>
   <si>
     <t xml:space="preserve">7.66615056991577</t>
@@ -3296,16 +3296,16 @@
     <t xml:space="preserve">7.63948678970337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66846990585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85395097732544</t>
+    <t xml:space="preserve">7.66846895217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85395002365112</t>
   </si>
   <si>
     <t xml:space="preserve">7.80294322967529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77048397064209</t>
+    <t xml:space="preserve">7.77048301696777</t>
   </si>
   <si>
     <t xml:space="preserve">7.98494529724121</t>
@@ -3314,19 +3314,19 @@
     <t xml:space="preserve">8.01624584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9061164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01044845581055</t>
+    <t xml:space="preserve">7.90611505508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01044940948486</t>
   </si>
   <si>
     <t xml:space="preserve">8.18781471252441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29678535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.348952293396</t>
+    <t xml:space="preserve">8.29678440093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34895133972168</t>
   </si>
   <si>
     <t xml:space="preserve">8.42082595825195</t>
@@ -3341,16 +3341,16 @@
     <t xml:space="preserve">8.51588439941406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57036876678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51356506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49733543395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62485504150391</t>
+    <t xml:space="preserve">8.57036972045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51356601715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49733638763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62485408782959</t>
   </si>
   <si>
     <t xml:space="preserve">8.60166931152344</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">8.57152843475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41271018981934</t>
+    <t xml:space="preserve">8.41271114349365</t>
   </si>
   <si>
     <t xml:space="preserve">8.33504009246826</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">8.78281021118164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40054130554199</t>
+    <t xml:space="preserve">8.40054225921631</t>
   </si>
   <si>
     <t xml:space="preserve">9.27200603485107</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">8.30564403533936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49945163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37380981445312</t>
+    <t xml:space="preserve">8.49945068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37381076812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.42460155487061</t>
@@ -3410,19 +3410,19 @@
     <t xml:space="preserve">8.681227684021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69726753234863</t>
+    <t xml:space="preserve">8.69726848602295</t>
   </si>
   <si>
     <t xml:space="preserve">8.76142501831055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93117332458496</t>
+    <t xml:space="preserve">8.93117427825928</t>
   </si>
   <si>
     <t xml:space="preserve">9.08889198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01805305480957</t>
+    <t xml:space="preserve">9.01805210113525</t>
   </si>
   <si>
     <t xml:space="preserve">8.84295654296875</t>
@@ -3437,13 +3437,13 @@
     <t xml:space="preserve">8.95790481567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02206134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82825374603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87770843505859</t>
+    <t xml:space="preserve">9.02206230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82825469970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87770938873291</t>
   </si>
   <si>
     <t xml:space="preserve">8.94186687469482</t>
@@ -3455,19 +3455,19 @@
     <t xml:space="preserve">8.86968994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07552719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06082439422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97795391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30542087554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28537082672119</t>
+    <t xml:space="preserve">9.07552623748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06082248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97795486450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30542182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28537178039551</t>
   </si>
   <si>
     <t xml:space="preserve">9.2679967880249</t>
@@ -3476,13 +3476,13 @@
     <t xml:space="preserve">9.25062084197998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14369297027588</t>
+    <t xml:space="preserve">9.14369201660156</t>
   </si>
   <si>
     <t xml:space="preserve">9.6796703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85610103607178</t>
+    <t xml:space="preserve">9.85610198974609</t>
   </si>
   <si>
     <t xml:space="preserve">10.0579280853271</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">10.1755495071411</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3158922195435</t>
+    <t xml:space="preserve">10.3158931732178</t>
   </si>
   <si>
     <t xml:space="preserve">10.602707862854</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">10.5399112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6655044555664</t>
+    <t xml:space="preserve">10.6655054092407</t>
   </si>
   <si>
     <t xml:space="preserve">10.9837713241577</t>
@@ -3512,16 +3512,16 @@
     <t xml:space="preserve">10.4785404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1288747787476</t>
+    <t xml:space="preserve">10.1288757324219</t>
   </si>
   <si>
     <t xml:space="preserve">10.1374387741089</t>
   </si>
   <si>
-    <t xml:space="preserve">10.280158996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4457139968872</t>
+    <t xml:space="preserve">10.2801599502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4457149505615</t>
   </si>
   <si>
     <t xml:space="preserve">10.4628419876099</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">10.7639818191528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8010892868042</t>
+    <t xml:space="preserve">10.8010902404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.9124116897583</t>
@@ -3542,13 +3542,13 @@
     <t xml:space="preserve">10.9109840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6526613235474</t>
+    <t xml:space="preserve">10.652660369873</t>
   </si>
   <si>
     <t xml:space="preserve">10.5613193511963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6597967147827</t>
+    <t xml:space="preserve">10.6597957611084</t>
   </si>
   <si>
     <t xml:space="preserve">10.8082256317139</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">10.7397193908691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7340106964111</t>
+    <t xml:space="preserve">10.7340116500854</t>
   </si>
   <si>
     <t xml:space="preserve">10.8910026550293</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">10.4551305770874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.481369972229</t>
+    <t xml:space="preserve">10.4813709259033</t>
   </si>
   <si>
     <t xml:space="preserve">10.4886589050293</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">10.0761098861694</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2204294204712</t>
+    <t xml:space="preserve">10.2204303741455</t>
   </si>
   <si>
     <t xml:space="preserve">10.1227579116821</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">10.8910036087036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0061683654785</t>
+    <t xml:space="preserve">11.0061674118042</t>
   </si>
   <si>
     <t xml:space="preserve">10.6869163513184</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">10.7306489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6781692504883</t>
+    <t xml:space="preserve">10.678168296814</t>
   </si>
   <si>
     <t xml:space="preserve">10.8283195495605</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">11.0047092437744</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0003366470337</t>
+    <t xml:space="preserve">11.000337600708</t>
   </si>
   <si>
     <t xml:space="preserve">10.7364797592163</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">10.9376516342163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1636066436768</t>
+    <t xml:space="preserve">11.1636056900024</t>
   </si>
   <si>
     <t xml:space="preserve">11.2160863876343</t>
@@ -3644,13 +3644,13 @@
     <t xml:space="preserve">11.2787704467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2583608627319</t>
+    <t xml:space="preserve">11.2583618164062</t>
   </si>
   <si>
     <t xml:space="preserve">11.7190160751343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7394275665283</t>
+    <t xml:space="preserve">11.739426612854</t>
   </si>
   <si>
     <t xml:space="preserve">11.8502159118652</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">12.3910493850708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5003824234009</t>
+    <t xml:space="preserve">12.5003814697266</t>
   </si>
   <si>
     <t xml:space="preserve">12.3677253723145</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">12.3167028427124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3181610107422</t>
+    <t xml:space="preserve">12.3181600570679</t>
   </si>
   <si>
     <t xml:space="preserve">12.3604373931885</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">12.3808450698853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3560628890991</t>
+    <t xml:space="preserve">12.3560619354248</t>
   </si>
   <si>
     <t xml:space="preserve">12.3852186203003</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">12.2613077163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0659666061401</t>
+    <t xml:space="preserve">12.0659675598145</t>
   </si>
   <si>
     <t xml:space="preserve">12.1738414764404</t>
@@ -3728,13 +3728,13 @@
     <t xml:space="preserve">12.3414850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1942491531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0936632156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.688404083252</t>
+    <t xml:space="preserve">12.1942501068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0936641693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6884031295776</t>
   </si>
   <si>
     <t xml:space="preserve">12.0164022445679</t>
@@ -3743,10 +3743,10 @@
     <t xml:space="preserve">11.8429279327393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8370962142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6679944992065</t>
+    <t xml:space="preserve">11.8370971679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6679935455322</t>
   </si>
   <si>
     <t xml:space="preserve">11.4332942962646</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">11.3633213043213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4814004898071</t>
+    <t xml:space="preserve">11.4813995361328</t>
   </si>
   <si>
     <t xml:space="preserve">11.5790710449219</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">11.5324220657349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9201889038086</t>
+    <t xml:space="preserve">11.9201898574829</t>
   </si>
   <si>
     <t xml:space="preserve">11.8006525039673</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">12.7146739959717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0280952453613</t>
+    <t xml:space="preserve">13.0280961990356</t>
   </si>
   <si>
     <t xml:space="preserve">13.1170196533203</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">13.1330537796021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4829187393188</t>
+    <t xml:space="preserve">13.4829177856445</t>
   </si>
   <si>
     <t xml:space="preserve">13.5645551681519</t>
@@ -3827,13 +3827,13 @@
     <t xml:space="preserve">12.5412006378174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5732707977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6024265289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4858055114746</t>
+    <t xml:space="preserve">12.5732698440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6024255752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4858045578003</t>
   </si>
   <si>
     <t xml:space="preserve">12.5105857849121</t>
@@ -3860,28 +3860,28 @@
     <t xml:space="preserve">12.1636371612549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1752986907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2656812667847</t>
+    <t xml:space="preserve">12.1752996444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2656803131104</t>
   </si>
   <si>
     <t xml:space="preserve">12.6898927688599</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2525606155396</t>
+    <t xml:space="preserve">12.2525615692139</t>
   </si>
   <si>
     <t xml:space="preserve">11.7044401168823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6854887008667</t>
+    <t xml:space="preserve">11.6854877471924</t>
   </si>
   <si>
     <t xml:space="preserve">12.0645093917847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2219467163086</t>
+    <t xml:space="preserve">12.2219476699829</t>
   </si>
   <si>
     <t xml:space="preserve">12.2365255355835</t>
@@ -3902,19 +3902,19 @@
     <t xml:space="preserve">11.8575048446655</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7627506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0674238204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6373825073242</t>
+    <t xml:space="preserve">11.7627515792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0674247741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6373815536499</t>
   </si>
   <si>
     <t xml:space="preserve">12.0790872573853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1534328460693</t>
+    <t xml:space="preserve">12.1534337997437</t>
   </si>
   <si>
     <t xml:space="preserve">12.2642240524292</t>
@@ -3923,25 +3923,25 @@
     <t xml:space="preserve">12.2860898971558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2671384811401</t>
+    <t xml:space="preserve">12.2671394348145</t>
   </si>
   <si>
     <t xml:space="preserve">12.4114589691162</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3123292922974</t>
+    <t xml:space="preserve">12.3123302459717</t>
   </si>
   <si>
     <t xml:space="preserve">12.2292375564575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2598485946655</t>
+    <t xml:space="preserve">12.2598495483398</t>
   </si>
   <si>
     <t xml:space="preserve">12.2846326828003</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2817163467407</t>
+    <t xml:space="preserve">12.281717300415</t>
   </si>
   <si>
     <t xml:space="preserve">12.7656965255737</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">12.8079719543457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7992248535156</t>
+    <t xml:space="preserve">12.7992258071899</t>
   </si>
   <si>
     <t xml:space="preserve">12.5995111465454</t>
@@ -3959,19 +3959,19 @@
     <t xml:space="preserve">12.719048500061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7321672439575</t>
+    <t xml:space="preserve">12.7321662902832</t>
   </si>
   <si>
     <t xml:space="preserve">12.7904777526855</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8575353622437</t>
+    <t xml:space="preserve">12.857536315918</t>
   </si>
   <si>
     <t xml:space="preserve">12.9143896102905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7817316055298</t>
+    <t xml:space="preserve">12.7817325592041</t>
   </si>
   <si>
     <t xml:space="preserve">12.7117605209351</t>
@@ -3983,28 +3983,28 @@
     <t xml:space="preserve">13.0368413925171</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0295524597168</t>
+    <t xml:space="preserve">13.0295534133911</t>
   </si>
   <si>
     <t xml:space="preserve">13.1855344772339</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0878639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0936946868896</t>
+    <t xml:space="preserve">13.0878648757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.093695640564</t>
   </si>
   <si>
     <t xml:space="preserve">12.7248802185059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3983392715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2511034011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1782150268555</t>
+    <t xml:space="preserve">12.3983383178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2511043548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1782159805298</t>
   </si>
   <si>
     <t xml:space="preserve">11.3458280563354</t>
@@ -4019,10 +4019,10 @@
     <t xml:space="preserve">11.662163734436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6096858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4755706787109</t>
+    <t xml:space="preserve">11.6096849441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4755697250366</t>
   </si>
   <si>
     <t xml:space="preserve">11.8749980926514</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">11.9887046813965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0193176269531</t>
+    <t xml:space="preserve">12.0193185806274</t>
   </si>
   <si>
     <t xml:space="preserve">11.9289360046387</t>
@@ -4046,13 +4046,13 @@
     <t xml:space="preserve">11.8589639663696</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8924913406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.963921546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5309648513794</t>
+    <t xml:space="preserve">11.8924922943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9639225006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5309638977051</t>
   </si>
   <si>
     <t xml:space="preserve">11.886661529541</t>
@@ -4061,13 +4061,13 @@
     <t xml:space="preserve">11.9916200637817</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2685966491699</t>
+    <t xml:space="preserve">12.2685976028442</t>
   </si>
   <si>
     <t xml:space="preserve">12.1621799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301231384277</t>
+    <t xml:space="preserve">12.6301221847534</t>
   </si>
   <si>
     <t xml:space="preserve">12.9114742279053</t>
@@ -4094,22 +4094,22 @@
     <t xml:space="preserve">13.8561096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8298692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9508647918701</t>
+    <t xml:space="preserve">13.829870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9508638381958</t>
   </si>
   <si>
     <t xml:space="preserve">13.9173345565796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8415298461914</t>
+    <t xml:space="preserve">13.8415307998657</t>
   </si>
   <si>
     <t xml:space="preserve">13.6986694335938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2132320404053</t>
+    <t xml:space="preserve">13.2132329940796</t>
   </si>
   <si>
     <t xml:space="preserve">12.1009521484375</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">12.3618927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2234058380127</t>
+    <t xml:space="preserve">12.223406791687</t>
   </si>
   <si>
     <t xml:space="preserve">11.9099855422974</t>
@@ -4160,7 +4160,7 @@
     <t xml:space="preserve">12.5149602890015</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665515899658</t>
+    <t xml:space="preserve">12.1665525436401</t>
   </si>
   <si>
     <t xml:space="preserve">11.8837451934814</t>
@@ -4169,10 +4169,10 @@
     <t xml:space="preserve">12.4391565322876</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6869468688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3064985275269</t>
+    <t xml:space="preserve">11.6869459152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3064994812012</t>
   </si>
   <si>
     <t xml:space="preserve">11.1052951812744</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">11.2190017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9041242599487</t>
+    <t xml:space="preserve">10.9041233062744</t>
   </si>
   <si>
     <t xml:space="preserve">10.0746507644653</t>
@@ -4217,10 +4217,10 @@
     <t xml:space="preserve">10.6883735656738</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6475563049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8035373687744</t>
+    <t xml:space="preserve">10.6475553512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8035364151001</t>
   </si>
   <si>
     <t xml:space="preserve">10.6373510360718</t>
@@ -4229,13 +4229,13 @@
     <t xml:space="preserve">10.5046939849854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.52073097229</t>
+    <t xml:space="preserve">10.5207300186157</t>
   </si>
   <si>
     <t xml:space="preserve">10.5323915481567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2321214675903</t>
+    <t xml:space="preserve">11.2321224212646</t>
   </si>
   <si>
     <t xml:space="preserve">11.054274559021</t>
@@ -4247,10 +4247,10 @@
     <t xml:space="preserve">10.7802124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8516435623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4522142410278</t>
+    <t xml:space="preserve">10.8516426086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522151947021</t>
   </si>
   <si>
     <t xml:space="preserve">9.98718643188477</t>
@@ -6834,6 +6834,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.84500026702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77799987792969</t>
   </si>
 </sst>
 </file>
@@ -72172,7 +72175,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6942361111</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>76778104</v>
@@ -72193,6 +72196,32 @@
         <v>2273</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6940972222</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>20034417</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>8.99199962615967</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>8.76700019836426</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>8.82900047302246</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>8.77799987792969</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>2274</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2275" uniqueCount="2275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="2276">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,46 +44,46 @@
     <t xml:space="preserve">STLAM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13119506835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91636347770691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78795742988586</t>
+    <t xml:space="preserve">4.13119459152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91636395454407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78795790672302</t>
   </si>
   <si>
     <t xml:space="preserve">3.63239002227783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61757349967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71881651878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66942977905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37804865837097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28421354293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18790888786316</t>
+    <t xml:space="preserve">3.61757302284241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71881604194641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66942954063416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37804841995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28421401977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18790936470032</t>
   </si>
   <si>
     <t xml:space="preserve">3.26939749717712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06197333335876</t>
+    <t xml:space="preserve">3.06197309494019</t>
   </si>
   <si>
     <t xml:space="preserve">3.25705099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3261923789978</t>
+    <t xml:space="preserve">3.32619214057922</t>
   </si>
   <si>
     <t xml:space="preserve">3.26198959350586</t>
@@ -92,22 +92,22 @@
     <t xml:space="preserve">3.46200561523438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.432373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18544006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16321587562561</t>
+    <t xml:space="preserve">3.43237352371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18544030189514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16321635246277</t>
   </si>
   <si>
     <t xml:space="preserve">3.16074681282043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07679033279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95332217216492</t>
+    <t xml:space="preserve">3.07678985595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95332264900208</t>
   </si>
   <si>
     <t xml:space="preserve">2.91628289222717</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">2.94838452339172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6570029258728</t>
+    <t xml:space="preserve">2.65700316429138</t>
   </si>
   <si>
     <t xml:space="preserve">2.58292317390442</t>
@@ -125,10 +125,10 @@
     <t xml:space="preserve">2.73355269432068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59279990196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68416595458984</t>
+    <t xml:space="preserve">2.59280014038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68416619300842</t>
   </si>
   <si>
     <t xml:space="preserve">2.80269360542297</t>
@@ -146,127 +146,127 @@
     <t xml:space="preserve">2.81010127067566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92615985870361</t>
+    <t xml:space="preserve">2.92616009712219</t>
   </si>
   <si>
     <t xml:space="preserve">2.83973383903503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72614407539368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00517868995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13358449935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29902958869934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45212817192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46447563171387</t>
+    <t xml:space="preserve">2.72614431381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00517916679382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13358402252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29902982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45212864875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46447467803955</t>
   </si>
   <si>
     <t xml:space="preserve">3.44225096702576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28915238380432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30643796920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21013307571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35088539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44719004631042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36076331138611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44471979141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42496585845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5163311958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50151538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51386141777039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4768214225769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33360075950623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57559537887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5064537525177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33607006072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841680526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18050193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13852310180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01505708694458</t>
+    <t xml:space="preserve">3.28915214538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30643749237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21013331413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35088562965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44718980789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36076307296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472002983093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42496633529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51633095741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50151515007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51386117935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47682189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33360028266907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57559466362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50645399093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33606910705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841632843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18050169944763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13852286338806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01505661010742</t>
   </si>
   <si>
     <t xml:space="preserve">3.13605380058289</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21260285377502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16815519332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31878423690796</t>
+    <t xml:space="preserve">3.21260333061218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16815495491028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31878447532654</t>
   </si>
   <si>
     <t xml:space="preserve">3.35335540771484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40274167060852</t>
+    <t xml:space="preserve">3.40274214744568</t>
   </si>
   <si>
     <t xml:space="preserve">3.56571769714355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54596304893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56818723678589</t>
+    <t xml:space="preserve">3.54596352577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56818699836731</t>
   </si>
   <si>
     <t xml:space="preserve">3.47435259819031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53361630439758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41014981269836</t>
+    <t xml:space="preserve">3.53361701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41014957427979</t>
   </si>
   <si>
     <t xml:space="preserve">3.38298678398132</t>
@@ -275,85 +275,85 @@
     <t xml:space="preserve">3.29656052589417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26692819595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3657021522522</t>
+    <t xml:space="preserve">3.26692867279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36570167541504</t>
   </si>
   <si>
     <t xml:space="preserve">3.3163149356842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38051819801331</t>
+    <t xml:space="preserve">3.38051795959473</t>
   </si>
   <si>
     <t xml:space="preserve">3.33113145828247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.108891248703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11383008956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10148310661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629915237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97801613807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06938171386719</t>
+    <t xml:space="preserve">3.10889101028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11382961273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.101482629776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629843711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97801637649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06938195228577</t>
   </si>
   <si>
     <t xml:space="preserve">3.12370705604553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07185101509094</t>
+    <t xml:space="preserve">3.07185077667236</t>
   </si>
   <si>
     <t xml:space="preserve">3.15827751159668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07432079315186</t>
+    <t xml:space="preserve">3.0743203163147</t>
   </si>
   <si>
     <t xml:space="preserve">3.04221892356873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03974986076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14839959144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12123775482178</t>
+    <t xml:space="preserve">3.03974962234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14840030670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1212375164032</t>
   </si>
   <si>
     <t xml:space="preserve">2.93109822273254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87677335739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89652848243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86195755004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93356823921204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09407472610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08666706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04962754249573</t>
+    <t xml:space="preserve">2.87677359580994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89652824401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86195778846741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93356871604919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09407496452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08666658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04962706565857</t>
   </si>
   <si>
     <t xml:space="preserve">3.1113600730896</t>
@@ -362,34 +362,34 @@
     <t xml:space="preserve">2.81997895240784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64465641975403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66194200515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7137975692749</t>
+    <t xml:space="preserve">2.64465618133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66194176673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71379780769348</t>
   </si>
   <si>
     <t xml:space="preserve">2.77059245109558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53353595733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52365851402283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54835200309753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84714150428772</t>
+    <t xml:space="preserve">2.53353571891785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52365827560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54835224151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8471417427063</t>
   </si>
   <si>
     <t xml:space="preserve">2.96320009231567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91134452819824</t>
+    <t xml:space="preserve">2.91134476661682</t>
   </si>
   <si>
     <t xml:space="preserve">2.99777102470398</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">3.08913588523865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09901428222656</t>
+    <t xml:space="preserve">3.0990138053894</t>
   </si>
   <si>
     <t xml:space="preserve">3.12617707252502</t>
@@ -413,58 +413,58 @@
     <t xml:space="preserve">3.06691241264343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84467244148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81257104873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69157361984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91381359100342</t>
+    <t xml:space="preserve">2.84467196464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81257081031799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69157338142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91381335258484</t>
   </si>
   <si>
     <t xml:space="preserve">2.88665080070496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05703473091125</t>
+    <t xml:space="preserve">3.05703520774841</t>
   </si>
   <si>
     <t xml:space="preserve">2.98789358139038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96073079109192</t>
+    <t xml:space="preserve">2.96073126792908</t>
   </si>
   <si>
     <t xml:space="preserve">2.97307801246643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88418197631836</t>
+    <t xml:space="preserve">2.88418173789978</t>
   </si>
   <si>
     <t xml:space="preserve">2.91875243186951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03481030464172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02987194061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0446879863739</t>
+    <t xml:space="preserve">3.0348105430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02987217903137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04468822479248</t>
   </si>
   <si>
     <t xml:space="preserve">2.99283266067505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05950427055359</t>
+    <t xml:space="preserve">3.05950403213501</t>
   </si>
   <si>
     <t xml:space="preserve">2.97554659843445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9508535861969</t>
+    <t xml:space="preserve">2.95085382461548</t>
   </si>
   <si>
     <t xml:space="preserve">2.96813917160034</t>
@@ -476,67 +476,67 @@
     <t xml:space="preserve">2.86442756652832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87430477142334</t>
+    <t xml:space="preserve">2.87430500984192</t>
   </si>
   <si>
     <t xml:space="preserve">2.81504058837891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90146660804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83232522010803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86689686775208</t>
+    <t xml:space="preserve">2.90146708488464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83232498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86689615249634</t>
   </si>
   <si>
     <t xml:space="preserve">2.74096035957336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70885872840881</t>
+    <t xml:space="preserve">2.70885896682739</t>
   </si>
   <si>
     <t xml:space="preserve">2.79034686088562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82491755485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84220337867737</t>
+    <t xml:space="preserve">2.82491779327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84220314025879</t>
   </si>
   <si>
     <t xml:space="preserve">2.89158987998962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87183499336243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90887427330017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76812267303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82244825363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85948824882507</t>
+    <t xml:space="preserve">2.87183451652527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90887498855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76812291145325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82244801521301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85948801040649</t>
   </si>
   <si>
     <t xml:space="preserve">2.93850708007812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25211238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29409122467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25952053070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03234195709229</t>
+    <t xml:space="preserve">3.25211191177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29409146308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2595202922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03234171867371</t>
   </si>
   <si>
     <t xml:space="preserve">3.02740287780762</t>
@@ -545,16 +545,16 @@
     <t xml:space="preserve">3.16568541526794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52373933792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39780306816101</t>
+    <t xml:space="preserve">3.52373957633972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39780330657959</t>
   </si>
   <si>
     <t xml:space="preserve">3.47188305854797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45953631401062</t>
+    <t xml:space="preserve">3.4595365524292</t>
   </si>
   <si>
     <t xml:space="preserve">3.47929120063782</t>
@@ -563,19 +563,19 @@
     <t xml:space="preserve">3.49410700798035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55584049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58547282218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57065629959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56077909469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6002893447876</t>
+    <t xml:space="preserve">3.55584096908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58547234535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57065582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56077933311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60028886795044</t>
   </si>
   <si>
     <t xml:space="preserve">3.62251234054565</t>
@@ -587,40 +587,40 @@
     <t xml:space="preserve">3.72128558158875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81265211105347</t>
+    <t xml:space="preserve">3.81265139579773</t>
   </si>
   <si>
     <t xml:space="preserve">3.85709953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93364858627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93117880821228</t>
+    <t xml:space="preserve">3.93364882469177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93117904663086</t>
   </si>
   <si>
     <t xml:space="preserve">3.97315764427185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00525903701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99044275283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15341901779175</t>
+    <t xml:space="preserve">4.00525856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99044346809387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15341854095459</t>
   </si>
   <si>
     <t xml:space="preserve">4.19539785385132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21762180328369</t>
+    <t xml:space="preserve">4.21762275695801</t>
   </si>
   <si>
     <t xml:space="preserve">4.29664039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30651760101318</t>
+    <t xml:space="preserve">4.30651807785034</t>
   </si>
   <si>
     <t xml:space="preserve">4.17564296722412</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">4.26453924179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31392621994019</t>
+    <t xml:space="preserve">4.31392669677734</t>
   </si>
   <si>
     <t xml:space="preserve">4.30898761749268</t>
@@ -638,40 +638,40 @@
     <t xml:space="preserve">4.27935552597046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42257642745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5065336227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53863573074341</t>
+    <t xml:space="preserve">4.42257738113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50653409957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53863620758057</t>
   </si>
   <si>
     <t xml:space="preserve">4.5707368850708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88928031921387</t>
+    <t xml:space="preserve">4.88928079605103</t>
   </si>
   <si>
     <t xml:space="preserve">4.95842266082764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01274824142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17078495025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33615064620972</t>
+    <t xml:space="preserve">5.0127477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17078447341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33615016937256</t>
   </si>
   <si>
     <t xml:space="preserve">4.53616619110107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34602689743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39047574996948</t>
+    <t xml:space="preserve">4.34602737426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39047527313232</t>
   </si>
   <si>
     <t xml:space="preserve">4.41516828536987</t>
@@ -680,46 +680,46 @@
     <t xml:space="preserve">4.62753105163574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64234828948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71889638900757</t>
+    <t xml:space="preserve">4.64234733581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71889686584473</t>
   </si>
   <si>
     <t xml:space="preserve">4.99793195724487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04237842559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10164403915405</t>
+    <t xml:space="preserve">5.0423789024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10164356231689</t>
   </si>
   <si>
     <t xml:space="preserve">5.12633657455444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95348405838013</t>
+    <t xml:space="preserve">4.95348358154297</t>
   </si>
   <si>
     <t xml:space="preserve">4.98805379867554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99299192428589</t>
+    <t xml:space="preserve">4.99299144744873</t>
   </si>
   <si>
     <t xml:space="preserve">5.00287055969238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04731702804565</t>
+    <t xml:space="preserve">5.0473165512085</t>
   </si>
   <si>
     <t xml:space="preserve">4.92385149002075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78062963485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8991584777832</t>
+    <t xml:space="preserve">4.78062915802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89915800094604</t>
   </si>
   <si>
     <t xml:space="preserve">5.02756309509277</t>
@@ -728,40 +728,40 @@
     <t xml:space="preserve">5.33869886398315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34363698959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32388401031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25474214553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32882213592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17572402954102</t>
+    <t xml:space="preserve">5.34363794326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32388353347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25474166870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32882165908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17572355270386</t>
   </si>
   <si>
     <t xml:space="preserve">5.14609146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18559980392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18066167831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13127517700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13621377944946</t>
+    <t xml:space="preserve">5.18560028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18066215515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13127613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1362133026123</t>
   </si>
   <si>
     <t xml:space="preserve">5.165846824646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09670400619507</t>
+    <t xml:space="preserve">5.09670448303223</t>
   </si>
   <si>
     <t xml:space="preserve">5.14115238189697</t>
@@ -770,61 +770,61 @@
     <t xml:space="preserve">5.22511053085327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30412864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21029472351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98311519622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94360494613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96336078643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93372821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07694959640503</t>
+    <t xml:space="preserve">5.30412769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21029376983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98311567306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94360542297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96336126327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93372869491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0769510269165</t>
   </si>
   <si>
     <t xml:space="preserve">5.07201147079468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06213474273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81026220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83248615264893</t>
+    <t xml:space="preserve">5.06213426589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81026172637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83248662948608</t>
   </si>
   <si>
     <t xml:space="preserve">4.74358940124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78556776046753</t>
+    <t xml:space="preserve">4.78556823730469</t>
   </si>
   <si>
     <t xml:space="preserve">4.7337121963501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71642732620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70655059814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69420337677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51887989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45220804214478</t>
+    <t xml:space="preserve">4.71642684936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70655012130737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69420289993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51888036727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45220899581909</t>
   </si>
   <si>
     <t xml:space="preserve">4.6472864151001</t>
@@ -842,22 +842,22 @@
     <t xml:space="preserve">4.78803777694702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23498725891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91644287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97323799133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05225706100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03744029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91891241073608</t>
+    <t xml:space="preserve">5.23498678207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91644334793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97323703765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05225658416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03744077682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91891193389893</t>
   </si>
   <si>
     <t xml:space="preserve">4.94854497909546</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">5.02262449264526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76828384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62012386322021</t>
+    <t xml:space="preserve">4.76828336715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62012338638306</t>
   </si>
   <si>
     <t xml:space="preserve">4.80038499832153</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">4.72383642196655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68926429748535</t>
+    <t xml:space="preserve">4.68926477432251</t>
   </si>
   <si>
     <t xml:space="preserve">4.66210174560547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67197942733765</t>
+    <t xml:space="preserve">4.67197895050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.590491771698</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">4.58308362960815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61518526077271</t>
+    <t xml:space="preserve">4.61518478393555</t>
   </si>
   <si>
     <t xml:space="preserve">4.84730195999146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83001565933228</t>
+    <t xml:space="preserve">4.83001613616943</t>
   </si>
   <si>
     <t xml:space="preserve">4.75346708297729</t>
@@ -917,13 +917,13 @@
     <t xml:space="preserve">4.81767082214355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78309917449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7213659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68432569503784</t>
+    <t xml:space="preserve">4.78309965133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72136545181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.684326171875</t>
   </si>
   <si>
     <t xml:space="preserve">4.85224008560181</t>
@@ -932,34 +932,34 @@
     <t xml:space="preserve">4.778160572052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76087522506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55838966369629</t>
+    <t xml:space="preserve">4.7608757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55839014053345</t>
   </si>
   <si>
     <t xml:space="preserve">4.85507869720459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86003732681274</t>
+    <t xml:space="preserve">4.8600378036499</t>
   </si>
   <si>
     <t xml:space="preserve">4.78564929962158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8253231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80548620223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87243461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95922136306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9988956451416</t>
+    <t xml:space="preserve">4.82532358169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80548572540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87243509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95922183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99889612197876</t>
   </si>
   <si>
     <t xml:space="preserve">5.19230508804321</t>
@@ -971,13 +971,13 @@
     <t xml:space="preserve">5.17246866226196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10799884796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17742776870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97409963607788</t>
+    <t xml:space="preserve">5.10799837112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17742824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97410011291504</t>
   </si>
   <si>
     <t xml:space="preserve">4.97905921936035</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">4.98897743225098</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03856945037842</t>
+    <t xml:space="preserve">5.03856992721558</t>
   </si>
   <si>
     <t xml:space="preserve">5.03361034393311</t>
@@ -998,49 +998,49 @@
     <t xml:space="preserve">5.07328462600708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02865171432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07824325561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06336498260498</t>
+    <t xml:space="preserve">5.02865076065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07824373245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06336545944214</t>
   </si>
   <si>
     <t xml:space="preserve">4.95178318023682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95426273345947</t>
+    <t xml:space="preserve">4.95426321029663</t>
   </si>
   <si>
     <t xml:space="preserve">4.86995601654053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26669454574585</t>
+    <t xml:space="preserve">5.26669406890869</t>
   </si>
   <si>
     <t xml:space="preserve">5.40555191040039</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34604120254517</t>
+    <t xml:space="preserve">5.34604167938232</t>
   </si>
   <si>
     <t xml:space="preserve">5.30636739730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67334985733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68822717666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01553773880005</t>
+    <t xml:space="preserve">5.67335033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68822813034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01553678512573</t>
   </si>
   <si>
     <t xml:space="preserve">6.19406890869141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14943552017212</t>
+    <t xml:space="preserve">6.14943599700928</t>
   </si>
   <si>
     <t xml:space="preserve">6.16431283950806</t>
@@ -1049,25 +1049,25 @@
     <t xml:space="preserve">6.07008838653564</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13951683044434</t>
+    <t xml:space="preserve">6.13951635360718</t>
   </si>
   <si>
     <t xml:space="preserve">6.27341604232788</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61560297012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53129577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50649976730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78421688079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70982789993286</t>
+    <t xml:space="preserve">6.61560249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53129529953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50649881362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78421640396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70982837677002</t>
   </si>
   <si>
     <t xml:space="preserve">6.72470474243164</t>
@@ -1082,70 +1082,70 @@
     <t xml:space="preserve">6.96770715713501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88340091705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99250364303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07680940628052</t>
+    <t xml:space="preserve">6.88340139389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99250316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07680988311768</t>
   </si>
   <si>
     <t xml:space="preserve">7.14623928070068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18095445632935</t>
+    <t xml:space="preserve">7.18095397949219</t>
   </si>
   <si>
     <t xml:space="preserve">7.46362924575806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31485271453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33468914031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38428163528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36444473266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51818180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58265113830566</t>
+    <t xml:space="preserve">7.31485319137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33469009399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38428211212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36444520950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51818084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58265066146851</t>
   </si>
   <si>
     <t xml:space="preserve">7.56281328201294</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53801918029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49338483810425</t>
+    <t xml:space="preserve">7.53801774978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49338531494141</t>
   </si>
   <si>
     <t xml:space="preserve">7.40907764434814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52313947677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41403675079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50330352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4239559173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45866966247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41899538040161</t>
+    <t xml:space="preserve">7.52313899993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41403770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50330305099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42395544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4586706161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41899681091309</t>
   </si>
   <si>
     <t xml:space="preserve">7.3098931312561</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">7.37932300567627</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93795204162598</t>
+    <t xml:space="preserve">6.93795108795166</t>
   </si>
   <si>
     <t xml:space="preserve">7.05697345733643</t>
@@ -1163,61 +1163,61 @@
     <t xml:space="preserve">7.02225828170776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14128065109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34956836700439</t>
+    <t xml:space="preserve">7.14127969741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34956741333008</t>
   </si>
   <si>
     <t xml:space="preserve">7.35948610305786</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51322221755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76614141464233</t>
+    <t xml:space="preserve">7.51322174072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76614093780518</t>
   </si>
   <si>
     <t xml:space="preserve">7.73142766952515</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6619987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45371103286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28013706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33964872360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3743634223938</t>
+    <t xml:space="preserve">7.66199827194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45371150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28013753890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33964824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37436199188232</t>
   </si>
   <si>
     <t xml:space="preserve">7.25038242340088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43387365341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55785512924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24046421051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20078992843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17103672027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15119886398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00738096237183</t>
+    <t xml:space="preserve">7.43387460708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55785465240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24046468734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20079040527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1710352897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15119743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00738048553467</t>
   </si>
   <si>
     <t xml:space="preserve">7.23550415039062</t>
@@ -1226,28 +1226,28 @@
     <t xml:space="preserve">7.19087219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53305959701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52809953689575</t>
+    <t xml:space="preserve">7.53305864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52809906005859</t>
   </si>
   <si>
     <t xml:space="preserve">7.50826263427734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43883228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44875192642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63720178604126</t>
+    <t xml:space="preserve">7.43883323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44875240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6372013092041</t>
   </si>
   <si>
     <t xml:space="preserve">7.6520791053772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64216184616089</t>
+    <t xml:space="preserve">7.64216136932373</t>
   </si>
   <si>
     <t xml:space="preserve">7.69175434112549</t>
@@ -1256,31 +1256,31 @@
     <t xml:space="preserve">7.67191743850708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54297780990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39419937133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71159172058105</t>
+    <t xml:space="preserve">7.54297637939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39419984817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7115912437439</t>
   </si>
   <si>
     <t xml:space="preserve">8.35628890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88692665100098</t>
+    <t xml:space="preserve">8.88692760467529</t>
   </si>
   <si>
     <t xml:space="preserve">8.98115158081055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15968418121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2142333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42252254486084</t>
+    <t xml:space="preserve">9.15968322753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21423435211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42252349853516</t>
   </si>
   <si>
     <t xml:space="preserve">9.48699188232422</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">9.69032001495361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28862380981445</t>
+    <t xml:space="preserve">9.28862285614014</t>
   </si>
   <si>
     <t xml:space="preserve">9.32829761505127</t>
@@ -1331,19 +1331,19 @@
     <t xml:space="preserve">9.31937122344971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7579870223999</t>
+    <t xml:space="preserve">8.75798511505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.35110855102539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89982128143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63698291778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75302696228027</t>
+    <t xml:space="preserve">8.89982032775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63698101043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75302600860596</t>
   </si>
   <si>
     <t xml:space="preserve">8.57548809051514</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">8.77782344818115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82741546630859</t>
+    <t xml:space="preserve">8.82741451263428</t>
   </si>
   <si>
     <t xml:space="preserve">9.0039644241333</t>
@@ -1364,40 +1364,40 @@
     <t xml:space="preserve">8.94643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98908615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80956363677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73815155029297</t>
+    <t xml:space="preserve">8.98908710479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80956172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73814964294434</t>
   </si>
   <si>
     <t xml:space="preserve">8.6905403137207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80559539794922</t>
+    <t xml:space="preserve">8.80559635162354</t>
   </si>
   <si>
     <t xml:space="preserve">8.71434497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47431945800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98930644989014</t>
+    <t xml:space="preserve">8.4743185043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98930692672729</t>
   </si>
   <si>
     <t xml:space="preserve">8.01410293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46836757659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55664157867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56259250640869</t>
+    <t xml:space="preserve">8.46836853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55664253234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56259155273438</t>
   </si>
   <si>
     <t xml:space="preserve">8.51597690582275</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">8.5278787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53085422515869</t>
+    <t xml:space="preserve">8.53085517883301</t>
   </si>
   <si>
     <t xml:space="preserve">8.43266105651855</t>
@@ -1415,31 +1415,31 @@
     <t xml:space="preserve">8.53184509277344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52589416503906</t>
+    <t xml:space="preserve">8.52589511871338</t>
   </si>
   <si>
     <t xml:space="preserve">8.3592643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56457710266113</t>
+    <t xml:space="preserve">8.56457614898682</t>
   </si>
   <si>
     <t xml:space="preserve">8.71732044219971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42175197601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25115299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1886682510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32554149627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15792179107666</t>
+    <t xml:space="preserve">8.42175006866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25115394592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18866729736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32554244995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15791988372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.18370914459229</t>
@@ -1448,22 +1448,22 @@
     <t xml:space="preserve">8.78278350830078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73517322540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15869045257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07438564300537</t>
+    <t xml:space="preserve">8.73517227172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07438468933105</t>
   </si>
   <si>
     <t xml:space="preserve">9.18943881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31342124938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22613716125488</t>
+    <t xml:space="preserve">9.31342029571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22613620758057</t>
   </si>
   <si>
     <t xml:space="preserve">9.40764427185059</t>
@@ -1478,64 +1478,64 @@
     <t xml:space="preserve">9.70916557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7676830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63180160522461</t>
+    <t xml:space="preserve">9.76768398284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63180065155029</t>
   </si>
   <si>
     <t xml:space="preserve">9.55840492248535</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75974941253662</t>
+    <t xml:space="preserve">9.7597484588623</t>
   </si>
   <si>
     <t xml:space="preserve">9.79148769378662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393558502197</t>
+    <t xml:space="preserve">9.49393653869629</t>
   </si>
   <si>
     <t xml:space="preserve">9.68635368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41458702087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20927715301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43739891052246</t>
+    <t xml:space="preserve">9.41458606719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20927619934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43739986419678</t>
   </si>
   <si>
     <t xml:space="preserve">9.21820259094238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51674652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5355920791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48004817962646</t>
+    <t xml:space="preserve">9.51674747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53559303283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48004913330078</t>
   </si>
   <si>
     <t xml:space="preserve">9.29556655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30845928192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42946434020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41756439208984</t>
+    <t xml:space="preserve">9.3084602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42946529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41756343841553</t>
   </si>
   <si>
     <t xml:space="preserve">9.36697864532471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30746936798096</t>
+    <t xml:space="preserve">9.30746841430664</t>
   </si>
   <si>
     <t xml:space="preserve">9.36797046661377</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">9.19935703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43938446044922</t>
+    <t xml:space="preserve">9.4393835067749</t>
   </si>
   <si>
     <t xml:space="preserve">9.59609413146973</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">9.06446552276611</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42748069763184</t>
+    <t xml:space="preserve">9.42748165130615</t>
   </si>
   <si>
     <t xml:space="preserve">9.62089157104492</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">8.85221099853516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87601566314697</t>
+    <t xml:space="preserve">8.87601470947266</t>
   </si>
   <si>
     <t xml:space="preserve">8.86213111877441</t>
@@ -1586,67 +1586,67 @@
     <t xml:space="preserve">9.1398458480835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90676307678223</t>
+    <t xml:space="preserve">8.90676403045654</t>
   </si>
   <si>
     <t xml:space="preserve">8.98313617706299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92659950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85022735595703</t>
+    <t xml:space="preserve">8.92660045623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85022830963135</t>
   </si>
   <si>
     <t xml:space="preserve">9.04462814331055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87403297424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92461490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79666900634766</t>
+    <t xml:space="preserve">8.87403202056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92461681365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79666996002197</t>
   </si>
   <si>
     <t xml:space="preserve">8.75005054473877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38505268096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18172550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92979717254639</t>
+    <t xml:space="preserve">8.38505363464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18172454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92979669570923</t>
   </si>
   <si>
     <t xml:space="preserve">8.15296077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24123477935791</t>
+    <t xml:space="preserve">8.24123573303223</t>
   </si>
   <si>
     <t xml:space="preserve">7.95558452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10039329528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10237693786621</t>
+    <t xml:space="preserve">8.10039234161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10237789154053</t>
   </si>
   <si>
     <t xml:space="preserve">8.03889846801758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50506687164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40687274932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46935844421387</t>
+    <t xml:space="preserve">8.50506591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40687370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4693603515625</t>
   </si>
   <si>
     <t xml:space="preserve">8.52291965484619</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">8.26305675506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21346282958984</t>
+    <t xml:space="preserve">8.21346378326416</t>
   </si>
   <si>
     <t xml:space="preserve">8.25214672088623</t>
@@ -1667,22 +1667,22 @@
     <t xml:space="preserve">8.24917030334473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22239112854004</t>
+    <t xml:space="preserve">8.22239017486572</t>
   </si>
   <si>
     <t xml:space="preserve">8.33347702026367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14105892181396</t>
+    <t xml:space="preserve">8.14105796813965</t>
   </si>
   <si>
     <t xml:space="preserve">8.01906204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21048736572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16111660003662</t>
+    <t xml:space="preserve">8.21048831939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16111755371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.26426839828491</t>
@@ -1694,37 +1694,37 @@
     <t xml:space="preserve">7.04804563522339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0420970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24343967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23352193832397</t>
+    <t xml:space="preserve">7.04209518432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24343919754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23352241516113</t>
   </si>
   <si>
     <t xml:space="preserve">7.20277500152588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24839925765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17500305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0440788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97663259506226</t>
+    <t xml:space="preserve">7.24839973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1750020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04407930374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97663354873657</t>
   </si>
   <si>
     <t xml:space="preserve">6.80801963806152</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7990927696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01729822158813</t>
+    <t xml:space="preserve">6.79909372329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01729917526245</t>
   </si>
   <si>
     <t xml:space="preserve">7.12243461608887</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">7.0371356010437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95977115631104</t>
+    <t xml:space="preserve">6.95977210998535</t>
   </si>
   <si>
     <t xml:space="preserve">7.18591260910034</t>
@@ -1742,52 +1742,52 @@
     <t xml:space="preserve">7.43486595153809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42693185806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36146879196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22062683105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26823568344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39320755004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22657918930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21566820144653</t>
+    <t xml:space="preserve">7.42692995071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36146974563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22062730789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26823616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39320850372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22657871246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21566772460938</t>
   </si>
   <si>
     <t xml:space="preserve">7.16706705093384</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48247480392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40610313415527</t>
+    <t xml:space="preserve">7.48247528076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40610265731812</t>
   </si>
   <si>
     <t xml:space="preserve">7.42792224884033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45768022537231</t>
+    <t xml:space="preserve">7.457679271698</t>
   </si>
   <si>
     <t xml:space="preserve">7.48346662521362</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61934900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73341178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66001558303833</t>
+    <t xml:space="preserve">7.61934995651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73341035842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66001462936401</t>
   </si>
   <si>
     <t xml:space="preserve">7.70266342163086</t>
@@ -1799,94 +1799,94 @@
     <t xml:space="preserve">7.51024532318115</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68282651901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69373750686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64017772674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57769060134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52016401290894</t>
+    <t xml:space="preserve">7.68282604217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69373798370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64017677307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57769155502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52016496658325</t>
   </si>
   <si>
     <t xml:space="preserve">7.34460830688477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42197179794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01035690307617</t>
+    <t xml:space="preserve">7.42197275161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01035594940186</t>
   </si>
   <si>
     <t xml:space="preserve">6.96274900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92803287506104</t>
+    <t xml:space="preserve">6.92803382873535</t>
   </si>
   <si>
     <t xml:space="preserve">6.94588708877563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17797899246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87744951248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82587289810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66618585586548</t>
+    <t xml:space="preserve">7.17797803878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87744998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82587432861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66618680953979</t>
   </si>
   <si>
     <t xml:space="preserve">6.86455535888672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95183706283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78024911880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0470552444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81992244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67015361785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75247669219971</t>
+    <t xml:space="preserve">6.95183658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78024959564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04705429077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81992197036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67015409469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75247573852539</t>
   </si>
   <si>
     <t xml:space="preserve">7.02920055389404</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11251592636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09664726257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26129293441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28708124160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08672904968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30394268035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23054552078247</t>
+    <t xml:space="preserve">7.11251640319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09664630889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2612943649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28708171844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08672761917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30394220352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23054695129395</t>
   </si>
   <si>
     <t xml:space="preserve">7.13334465026855</t>
@@ -1898,28 +1898,28 @@
     <t xml:space="preserve">6.94291114807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01234149932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93001747131348</t>
+    <t xml:space="preserve">7.0123405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93001794815063</t>
   </si>
   <si>
     <t xml:space="preserve">6.99052000045776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33865642547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34758329391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30493402481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49635887145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34857559204102</t>
+    <t xml:space="preserve">7.33865690231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34758281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30493307113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49636030197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34857511520386</t>
   </si>
   <si>
     <t xml:space="preserve">7.23451280593872</t>
@@ -1928,13 +1928,13 @@
     <t xml:space="preserve">6.86554670333862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82488203048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61064386367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78322410583496</t>
+    <t xml:space="preserve">6.8248815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61064338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78322458267212</t>
   </si>
   <si>
     <t xml:space="preserve">6.91613149642944</t>
@@ -1943,31 +1943,31 @@
     <t xml:space="preserve">6.92208242416382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86852264404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82884883880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82289791107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72272109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50848340988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25754690170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28928470611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23175811767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1573691368103</t>
+    <t xml:space="preserve">6.86852169036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82884931564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82289886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72272157669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50848388671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25754594802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28928518295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2317590713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15736961364746</t>
   </si>
   <si>
     <t xml:space="preserve">6.50253248214722</t>
@@ -1976,124 +1976,124 @@
     <t xml:space="preserve">6.55113220214844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62849617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87645769119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01134872436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1601243019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24443244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2107081413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32080411911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10557317733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26724433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18690490722656</t>
+    <t xml:space="preserve">6.6284966468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87645673751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01134824752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16012525558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24443054199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21070909500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32080507278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10557270050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26724338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18690395355225</t>
   </si>
   <si>
     <t xml:space="preserve">7.18987989425659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28509712219238</t>
+    <t xml:space="preserve">7.28509664535522</t>
   </si>
   <si>
     <t xml:space="preserve">7.39816761016846</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47354698181152</t>
+    <t xml:space="preserve">7.47354793548584</t>
   </si>
   <si>
     <t xml:space="preserve">7.52710723876953</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6354398727417</t>
+    <t xml:space="preserve">6.63543939590454</t>
   </si>
   <si>
     <t xml:space="preserve">6.44302129745483</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4182243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39739656448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4975733757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40731477737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45988273620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44897270202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45194816589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57692003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50154066085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5114598274231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54617404937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45591449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43806171417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41227436065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36268138885498</t>
+    <t xml:space="preserve">6.41822481155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3973970413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49757242202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40731430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45988178253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44897317886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4519476890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57692050933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.501540184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51145887374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54617357254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4559154510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43806266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4122748374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3626823425293</t>
   </si>
   <si>
     <t xml:space="preserve">6.41524934768677</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64932489395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32697534561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36664867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35871505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30416345596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25853872299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26548051834106</t>
+    <t xml:space="preserve">6.64932441711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32697582244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36665010452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35871410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30416297912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25853776931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26548099517822</t>
   </si>
   <si>
     <t xml:space="preserve">6.32003259658813</t>
@@ -2102,61 +2102,61 @@
     <t xml:space="preserve">6.6364312171936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46980094909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49658107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33590269088745</t>
+    <t xml:space="preserve">6.46980237960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49658060073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33590221405029</t>
   </si>
   <si>
     <t xml:space="preserve">6.46385049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49162197113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66122722625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52633666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58188009262085</t>
+    <t xml:space="preserve">6.49162149429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66122817993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52633619308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58188056945801</t>
   </si>
   <si>
     <t xml:space="preserve">6.73958301544189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80603694915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80901098251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81000423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93894481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86158037185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89133501052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89232683181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04308700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09367227554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607570648193</t>
+    <t xml:space="preserve">6.80603790283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8090124130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81000375747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9389443397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86157989501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89133405685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89232778549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04308795928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09367179870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607522964478</t>
   </si>
   <si>
     <t xml:space="preserve">7.2930326461792</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">7.20211410522461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14384889602661</t>
+    <t xml:space="preserve">7.14384841918945</t>
   </si>
   <si>
     <t xml:space="preserve">7.20939826965332</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">7.19170951843262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14488935470581</t>
+    <t xml:space="preserve">7.14488887786865</t>
   </si>
   <si>
     <t xml:space="preserve">7.04916620254517</t>
@@ -2186,160 +2186,160 @@
     <t xml:space="preserve">7.3737907409668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11263513565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07205533981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80673742294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73806715011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61112976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71309566497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81401920318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88997459411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95448303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93350076675415</t>
+    <t xml:space="preserve">7.11263561248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07205629348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80673837661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73806667327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61112928390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71309471130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81402015686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88997507095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95448350906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93350172042847</t>
   </si>
   <si>
     <t xml:space="preserve">6.88365411758423</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82684898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62166309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64021015167236</t>
+    <t xml:space="preserve">6.82684946060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62166261672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64020967483521</t>
   </si>
   <si>
     <t xml:space="preserve">7.16998958587646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10623073577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.019287109375</t>
+    <t xml:space="preserve">7.10623025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01928663253784</t>
   </si>
   <si>
     <t xml:space="preserve">6.96132373809814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6297779083252</t>
+    <t xml:space="preserve">6.62977743148804</t>
   </si>
   <si>
     <t xml:space="preserve">6.59268093109131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84771728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78163909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78743457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76425075531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88133478164673</t>
+    <t xml:space="preserve">6.84771585464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78163862228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78743505477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7642502784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88133525848389</t>
   </si>
   <si>
     <t xml:space="preserve">6.94625282287598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83728361129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8952465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86278581619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92422771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98566722869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06449747085571</t>
+    <t xml:space="preserve">6.83728408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89524602890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8627872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92422676086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98566770553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0644965171814</t>
   </si>
   <si>
     <t xml:space="preserve">7.15028238296509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13521194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14216709136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02160549163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03319692611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.080726146698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10970783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15723848342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13057518005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33112573623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35315227508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32532978057861</t>
+    <t xml:space="preserve">7.13521146774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14216804504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02160596847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0331974029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08072566986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10970735549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15723752975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13057470321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33112668991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35315275192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32532930374146</t>
   </si>
   <si>
     <t xml:space="preserve">7.28939342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20940446853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20476675033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28707504272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28591537475586</t>
+    <t xml:space="preserve">7.20940399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20476722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28707361221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28591442108154</t>
   </si>
   <si>
     <t xml:space="preserve">7.05986070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07493019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95900535583496</t>
+    <t xml:space="preserve">7.07493114471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95900583267212</t>
   </si>
   <si>
     <t xml:space="preserve">7.17578554153442</t>
@@ -2348,67 +2348,67 @@
     <t xml:space="preserve">7.31141757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19433403015137</t>
+    <t xml:space="preserve">7.19433355331421</t>
   </si>
   <si>
     <t xml:space="preserve">7.08768320083618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.976393699646</t>
+    <t xml:space="preserve">6.97639322280884</t>
   </si>
   <si>
     <t xml:space="preserve">6.99842023849487</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76541042327881</t>
+    <t xml:space="preserve">6.76540994644165</t>
   </si>
   <si>
     <t xml:space="preserve">6.81873607635498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86858320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72715377807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72367668151855</t>
+    <t xml:space="preserve">6.8685827255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72715473175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7236762046814</t>
   </si>
   <si>
     <t xml:space="preserve">6.82569074630737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58572435379028</t>
+    <t xml:space="preserve">6.58572483062744</t>
   </si>
   <si>
     <t xml:space="preserve">6.40719938278198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52660369873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46632289886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194389343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6900577545166</t>
+    <t xml:space="preserve">6.52660274505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46632242202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194437026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69005823135376</t>
   </si>
   <si>
     <t xml:space="preserve">6.54515075683594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63557291030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74454259872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80482387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86162757873535</t>
+    <t xml:space="preserve">6.635573387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74454307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80482339859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86162805557251</t>
   </si>
   <si>
     <t xml:space="preserve">6.86394691467285</t>
@@ -2423,97 +2423,97 @@
     <t xml:space="preserve">7.30562257766724</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37285900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28243732452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28127813339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29287147521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18158292770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18737840652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07029342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92654657363892</t>
+    <t xml:space="preserve">7.37285947799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28243684768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28127765655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29287052154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1815824508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18737888336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07029390335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92654705047607</t>
   </si>
   <si>
     <t xml:space="preserve">6.83148717880249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84539890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87785673141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525659561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63093614578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54051351547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53239870071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5752911567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50921487808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54862928390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73410987854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87554025650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91843128204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07145214080811</t>
+    <t xml:space="preserve">6.84539794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87785720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525802612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63093662261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54051399230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53239965438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57529163360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50921535491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54862976074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73410940170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87553882598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91843175888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07145309448242</t>
   </si>
   <si>
     <t xml:space="preserve">7.03899431228638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87206172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95668697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90915679931641</t>
+    <t xml:space="preserve">6.87206125259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95668649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90915727615356</t>
   </si>
   <si>
     <t xml:space="preserve">6.87321996688843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86742353439331</t>
+    <t xml:space="preserve">6.86742401123047</t>
   </si>
   <si>
     <t xml:space="preserve">6.90336036682129</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81062030792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45980310440063</t>
+    <t xml:space="preserve">6.81062126159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45980358123779</t>
   </si>
   <si>
     <t xml:space="preserve">8.07304859161377</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">8.12057781219482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32808399200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37561416625977</t>
+    <t xml:space="preserve">8.32808494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37561321258545</t>
   </si>
   <si>
     <t xml:space="preserve">8.38025093078613</t>
@@ -2537,13 +2537,13 @@
     <t xml:space="preserve">8.48226547241211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41039085388184</t>
+    <t xml:space="preserve">8.41039180755615</t>
   </si>
   <si>
     <t xml:space="preserve">8.51124668121338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41386890411377</t>
+    <t xml:space="preserve">8.41386985778809</t>
   </si>
   <si>
     <t xml:space="preserve">8.40807437896729</t>
@@ -2555,25 +2555,25 @@
     <t xml:space="preserve">8.1843376159668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1924524307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09623432159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79019117355347</t>
+    <t xml:space="preserve">8.19245147705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09623336791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79019165039062</t>
   </si>
   <si>
     <t xml:space="preserve">7.7461404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88177394866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87713527679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89104557037354</t>
+    <t xml:space="preserve">7.88177299499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87713479995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89104604721069</t>
   </si>
   <si>
     <t xml:space="preserve">7.82033109664917</t>
@@ -2588,28 +2588,28 @@
     <t xml:space="preserve">7.65223979949951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74845695495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68238067626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68701648712158</t>
+    <t xml:space="preserve">7.74845743179321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68237972259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68701696395874</t>
   </si>
   <si>
     <t xml:space="preserve">7.62093925476074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57920598983765</t>
+    <t xml:space="preserve">7.5792064666748</t>
   </si>
   <si>
     <t xml:space="preserve">7.46328115463257</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64760255813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72411346435547</t>
+    <t xml:space="preserve">7.64760208129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72411394119263</t>
   </si>
   <si>
     <t xml:space="preserve">7.80757904052734</t>
@@ -2618,73 +2618,73 @@
     <t xml:space="preserve">7.88524961471558</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88408994674683</t>
+    <t xml:space="preserve">7.88409042358398</t>
   </si>
   <si>
     <t xml:space="preserve">7.91191244125366</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82844591140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78439378738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7415018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5803656578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47719192504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51197004318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41691207885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43777751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43661785125732</t>
+    <t xml:space="preserve">7.82844638824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78439426422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74150228500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58036613464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47719287872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51197052001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41691160202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43777704238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43661880493164</t>
   </si>
   <si>
     <t xml:space="preserve">7.39024686813354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36822271347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22911167144775</t>
+    <t xml:space="preserve">7.3682222366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22911071777344</t>
   </si>
   <si>
     <t xml:space="preserve">7.21867799758911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20592641830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22099733352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14680528640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98219013214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03783416748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96364259719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03088045120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9126353263855</t>
+    <t xml:space="preserve">7.20592594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22099637985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14680480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98219108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03783464431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96364164352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03087902069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91263437271118</t>
   </si>
   <si>
     <t xml:space="preserve">6.80018711090088</t>
@@ -2693,43 +2693,43 @@
     <t xml:space="preserve">6.85235357284546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19317531585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07608985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03203821182251</t>
+    <t xml:space="preserve">7.19317483901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07609081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03203773498535</t>
   </si>
   <si>
     <t xml:space="preserve">7.29402923583984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10738945007324</t>
+    <t xml:space="preserve">7.10739040374756</t>
   </si>
   <si>
     <t xml:space="preserve">7.1410083770752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11086750030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1155047416687</t>
+    <t xml:space="preserve">7.11086797714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11550521850586</t>
   </si>
   <si>
     <t xml:space="preserve">7.00189733505249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57297277450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52544355392456</t>
+    <t xml:space="preserve">6.57297229766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52544403076172</t>
   </si>
   <si>
     <t xml:space="preserve">6.70165061950684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51616907119751</t>
+    <t xml:space="preserve">6.51617002487183</t>
   </si>
   <si>
     <t xml:space="preserve">6.27620458602905</t>
@@ -2738,25 +2738,25 @@
     <t xml:space="preserve">6.3411226272583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37126350402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2843189239502</t>
+    <t xml:space="preserve">6.37126302719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28431940078735</t>
   </si>
   <si>
     <t xml:space="preserve">6.096519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.438063621521</t>
+    <t xml:space="preserve">5.43806314468384</t>
   </si>
   <si>
     <t xml:space="preserve">5.40676307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51921129226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53326463699341</t>
+    <t xml:space="preserve">5.51921081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53326511383057</t>
   </si>
   <si>
     <t xml:space="preserve">4.85785627365112</t>
@@ -2765,49 +2765,49 @@
     <t xml:space="preserve">4.15534782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9791407585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54731917381287</t>
+    <t xml:space="preserve">3.97914147377014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54731941223145</t>
   </si>
   <si>
     <t xml:space="preserve">3.36531543731689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56122994422913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40994739532471</t>
+    <t xml:space="preserve">3.56123018264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40994763374329</t>
   </si>
   <si>
     <t xml:space="preserve">3.84872508049011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96117329597473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99421167373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75482535362244</t>
+    <t xml:space="preserve">3.96117305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99421095848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75482511520386</t>
   </si>
   <si>
     <t xml:space="preserve">3.65744781494141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80930995941162</t>
+    <t xml:space="preserve">3.8093101978302</t>
   </si>
   <si>
     <t xml:space="preserve">3.66498351097107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64295768737793</t>
+    <t xml:space="preserve">3.64295721054077</t>
   </si>
   <si>
     <t xml:space="preserve">3.59368896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83481383323669</t>
+    <t xml:space="preserve">3.83481431007385</t>
   </si>
   <si>
     <t xml:space="preserve">4.08289432525635</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">4.12636661529541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33503198623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32401990890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10434055328369</t>
+    <t xml:space="preserve">4.33503246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32402038574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10434103012085</t>
   </si>
   <si>
     <t xml:space="preserve">4.12056970596313</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">4.30663061141968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11419439315796</t>
+    <t xml:space="preserve">4.11419486999512</t>
   </si>
   <si>
     <t xml:space="preserve">4.20229768753052</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">4.57383918762207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74135208129883</t>
+    <t xml:space="preserve">4.74135160446167</t>
   </si>
   <si>
     <t xml:space="preserve">4.64629173278809</t>
@@ -2864,82 +2864,82 @@
     <t xml:space="preserve">4.44863986968994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42139720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40516805648804</t>
+    <t xml:space="preserve">4.42139673233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40516757965088</t>
   </si>
   <si>
     <t xml:space="preserve">4.50370407104492</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42429447174072</t>
+    <t xml:space="preserve">4.42429494857788</t>
   </si>
   <si>
     <t xml:space="preserve">4.4005298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27475118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15476846694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17505502700806</t>
+    <t xml:space="preserve">4.27475166320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1547679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1750545501709</t>
   </si>
   <si>
     <t xml:space="preserve">4.51703548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31242704391479</t>
+    <t xml:space="preserve">4.31242752075195</t>
   </si>
   <si>
     <t xml:space="preserve">4.25388431549072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29851675033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59934234619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.728600025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78192520141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60339975357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7651162147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83293199539185</t>
+    <t xml:space="preserve">4.29851627349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59934282302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72859954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78192567825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60340023040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76511573791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.832932472229</t>
   </si>
   <si>
     <t xml:space="preserve">5.08217144012451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04449605941772</t>
+    <t xml:space="preserve">5.04449558258057</t>
   </si>
   <si>
     <t xml:space="preserve">5.39748907089233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45255327224731</t>
+    <t xml:space="preserve">5.45255279541016</t>
   </si>
   <si>
     <t xml:space="preserve">5.21316814422607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07231855392456</t>
+    <t xml:space="preserve">5.0723180770874</t>
   </si>
   <si>
     <t xml:space="preserve">4.68164920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74888610839844</t>
+    <t xml:space="preserve">4.74888563156128</t>
   </si>
   <si>
     <t xml:space="preserve">4.7506251335144</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">4.85263967514038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89958906173706</t>
+    <t xml:space="preserve">4.8995885848999</t>
   </si>
   <si>
     <t xml:space="preserve">4.96624660491943</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">5.02246999740601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09550285339355</t>
+    <t xml:space="preserve">5.09550333023071</t>
   </si>
   <si>
     <t xml:space="preserve">5.00508165359497</t>
@@ -2978,28 +2978,28 @@
     <t xml:space="preserve">5.18418645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09260559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21606588363647</t>
+    <t xml:space="preserve">5.09260511398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21606540679932</t>
   </si>
   <si>
     <t xml:space="preserve">5.15868234634399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21896457672119</t>
+    <t xml:space="preserve">5.21896409988403</t>
   </si>
   <si>
     <t xml:space="preserve">5.20679187774658</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09840154647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00276279449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11984872817993</t>
+    <t xml:space="preserve">5.09840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00276327133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11984825134277</t>
   </si>
   <si>
     <t xml:space="preserve">5.24910449981689</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">5.2572193145752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31692171096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31054496765137</t>
+    <t xml:space="preserve">5.3169207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31054544448853</t>
   </si>
   <si>
     <t xml:space="preserve">5.34184455871582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35401630401611</t>
+    <t xml:space="preserve">5.35401678085327</t>
   </si>
   <si>
     <t xml:space="preserve">5.30822706222534</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">5.26069736480713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.258957862854</t>
+    <t xml:space="preserve">5.25895881652832</t>
   </si>
   <si>
     <t xml:space="preserve">5.37488412857056</t>
@@ -3041,28 +3041,28 @@
     <t xml:space="preserve">5.30764675140381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99638700485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23693227767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44270133972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44733667373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38937425613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38183975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47457981109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76323270797729</t>
+    <t xml:space="preserve">4.99638652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2369327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44270086288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44733715057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38937473297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38183927536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47457933425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76323318481445</t>
   </si>
   <si>
     <t xml:space="preserve">5.74178791046143</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">5.65716218948364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61658811569214</t>
+    <t xml:space="preserve">5.61658763885498</t>
   </si>
   <si>
     <t xml:space="preserve">5.59340333938599</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">5.56847953796387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58065128326416</t>
+    <t xml:space="preserve">5.58065176010132</t>
   </si>
   <si>
     <t xml:space="preserve">5.47631931304932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40618371963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58007287979126</t>
+    <t xml:space="preserve">5.40618324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5800724029541</t>
   </si>
   <si>
     <t xml:space="preserve">5.51631259918213</t>
@@ -3101,19 +3101,19 @@
     <t xml:space="preserve">5.47747755050659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45719146728516</t>
+    <t xml:space="preserve">5.457190990448</t>
   </si>
   <si>
     <t xml:space="preserve">5.35053968429565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28736066818237</t>
+    <t xml:space="preserve">5.28735971450806</t>
   </si>
   <si>
     <t xml:space="preserve">5.31750106811523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37836217880249</t>
+    <t xml:space="preserve">5.37836265563965</t>
   </si>
   <si>
     <t xml:space="preserve">5.46646451950073</t>
@@ -3122,31 +3122,31 @@
     <t xml:space="preserve">5.58470821380615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57079792022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57137823104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73019599914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74642467498779</t>
+    <t xml:space="preserve">5.57079839706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57137775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73019552230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74642515182495</t>
   </si>
   <si>
     <t xml:space="preserve">5.78641939163208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30750417709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26693058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23910856246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01537227630615</t>
+    <t xml:space="preserve">6.30750513076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.266930103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23910808563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01537179946899</t>
   </si>
   <si>
     <t xml:space="preserve">5.75975656509399</t>
@@ -3158,73 +3158,73 @@
     <t xml:space="preserve">6.02232789993286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01189374923706</t>
+    <t xml:space="preserve">6.01189470291138</t>
   </si>
   <si>
     <t xml:space="preserve">5.92958736419678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16491603851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02116775512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06753778457642</t>
+    <t xml:space="preserve">6.16491556167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02116727828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06753826141357</t>
   </si>
   <si>
     <t xml:space="preserve">5.99914216995239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07681274414062</t>
+    <t xml:space="preserve">6.07681226730347</t>
   </si>
   <si>
     <t xml:space="preserve">6.18578243255615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2031717300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19042062759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10463523864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16375637054443</t>
+    <t xml:space="preserve">6.20317125320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19042015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1046347618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16375732421875</t>
   </si>
   <si>
     <t xml:space="preserve">6.06058216094971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12665987014771</t>
+    <t xml:space="preserve">6.12666082382202</t>
   </si>
   <si>
     <t xml:space="preserve">5.99566507339478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24954128265381</t>
+    <t xml:space="preserve">6.24954080581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.22867441177368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24722337722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20548963546753</t>
+    <t xml:space="preserve">6.24722242355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20548868179321</t>
   </si>
   <si>
     <t xml:space="preserve">6.3573522567749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43386173248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48023271560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37242269515991</t>
+    <t xml:space="preserve">6.43386268615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48023319244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37242317199707</t>
   </si>
   <si>
     <t xml:space="preserve">6.12550067901611</t>
@@ -3242,28 +3242,28 @@
     <t xml:space="preserve">6.3793773651123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47443723678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51269149780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91031694412231</t>
+    <t xml:space="preserve">6.47443580627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51269245147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91031789779663</t>
   </si>
   <si>
     <t xml:space="preserve">6.99146556854248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07840919494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29750776290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31837463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34851598739624</t>
+    <t xml:space="preserve">7.07840871810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29750728607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3183741569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34851551055908</t>
   </si>
   <si>
     <t xml:space="preserve">7.50037670135498</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">7.46560001373291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44705057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58963966369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64180707931519</t>
+    <t xml:space="preserve">7.44705152511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58964014053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64180660247803</t>
   </si>
   <si>
     <t xml:space="preserve">7.58616161346436</t>
@@ -3287,10 +3287,10 @@
     <t xml:space="preserve">7.66615056991577</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57341051101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66731023788452</t>
+    <t xml:space="preserve">7.57341003417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66730976104736</t>
   </si>
   <si>
     <t xml:space="preserve">7.63948678970337</t>
@@ -3302,37 +3302,37 @@
     <t xml:space="preserve">7.85395002365112</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80294322967529</t>
+    <t xml:space="preserve">7.80294275283813</t>
   </si>
   <si>
     <t xml:space="preserve">7.77048301696777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98494529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01624584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90611505508423</t>
+    <t xml:space="preserve">7.98494577407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01624488830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90611600875854</t>
   </si>
   <si>
     <t xml:space="preserve">8.01044940948486</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18781471252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29678440093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34895133972168</t>
+    <t xml:space="preserve">8.18781661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29678535461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.348952293396</t>
   </si>
   <si>
     <t xml:space="preserve">8.42082595825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25968933105469</t>
+    <t xml:space="preserve">8.25968837738037</t>
   </si>
   <si>
     <t xml:space="preserve">8.46139907836914</t>
@@ -3341,16 +3341,16 @@
     <t xml:space="preserve">8.51588439941406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57036972045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51356601715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49733638763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62485408782959</t>
+    <t xml:space="preserve">8.57036876678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51356506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49733543395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62485504150391</t>
   </si>
   <si>
     <t xml:space="preserve">8.60166931152344</t>
@@ -3374,16 +3374,16 @@
     <t xml:space="preserve">8.78281021118164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40054225921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27200603485107</t>
+    <t xml:space="preserve">8.40054130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27200698852539</t>
   </si>
   <si>
     <t xml:space="preserve">9.32146167755127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11963367462158</t>
+    <t xml:space="preserve">9.1196346282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.84830284118652</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">8.43663024902344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60236835479736</t>
+    <t xml:space="preserve">8.60236930847168</t>
   </si>
   <si>
     <t xml:space="preserve">8.30564403533936</t>
@@ -3407,10 +3407,10 @@
     <t xml:space="preserve">8.42460155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.681227684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69726848602295</t>
+    <t xml:space="preserve">8.68122863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69726753234863</t>
   </si>
   <si>
     <t xml:space="preserve">8.76142501831055</t>
@@ -3419,46 +3419,46 @@
     <t xml:space="preserve">8.93117427825928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08889198303223</t>
+    <t xml:space="preserve">9.08889293670654</t>
   </si>
   <si>
     <t xml:space="preserve">9.01805210113525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84295654296875</t>
+    <t xml:space="preserve">8.84295749664307</t>
   </si>
   <si>
     <t xml:space="preserve">8.79483985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86567878723145</t>
+    <t xml:space="preserve">8.86567974090576</t>
   </si>
   <si>
     <t xml:space="preserve">8.95790481567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02206230163574</t>
+    <t xml:space="preserve">9.02206134796143</t>
   </si>
   <si>
     <t xml:space="preserve">8.82825469970703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87770938873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94186687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82424545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86968994140625</t>
+    <t xml:space="preserve">8.87770843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94186592102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82424640655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86969089508057</t>
   </si>
   <si>
     <t xml:space="preserve">9.07552623748779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06082248687744</t>
+    <t xml:space="preserve">9.06082344055176</t>
   </si>
   <si>
     <t xml:space="preserve">8.97795486450195</t>
@@ -3476,16 +3476,16 @@
     <t xml:space="preserve">9.25062084197998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14369201660156</t>
+    <t xml:space="preserve">9.14369297027588</t>
   </si>
   <si>
     <t xml:space="preserve">9.6796703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85610198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0579280853271</t>
+    <t xml:space="preserve">9.85610103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0579271316528</t>
   </si>
   <si>
     <t xml:space="preserve">10.1755495071411</t>
@@ -3497,10 +3497,10 @@
     <t xml:space="preserve">10.602707862854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5399112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6655054092407</t>
+    <t xml:space="preserve">10.5399103164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6655044555664</t>
   </si>
   <si>
     <t xml:space="preserve">10.9837713241577</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">10.4785404205322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1288757324219</t>
+    <t xml:space="preserve">10.1288766860962</t>
   </si>
   <si>
     <t xml:space="preserve">10.1374387741089</t>
@@ -3521,16 +3521,16 @@
     <t xml:space="preserve">10.2801599502563</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4457149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4628419876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7753992080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7639818191528</t>
+    <t xml:space="preserve">10.4457139968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4628410339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7754001617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7639827728271</t>
   </si>
   <si>
     <t xml:space="preserve">10.8010902404785</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">10.5613193511963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6597957611084</t>
+    <t xml:space="preserve">10.6597967147827</t>
   </si>
   <si>
     <t xml:space="preserve">10.8082256317139</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">10.7397193908691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7340116500854</t>
+    <t xml:space="preserve">10.7340106964111</t>
   </si>
   <si>
     <t xml:space="preserve">10.8910026550293</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">10.4551305770874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4813709259033</t>
+    <t xml:space="preserve">10.481369972229</t>
   </si>
   <si>
     <t xml:space="preserve">10.4886589050293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4667921066284</t>
+    <t xml:space="preserve">10.4667911529541</t>
   </si>
   <si>
     <t xml:space="preserve">10.4288902282715</t>
@@ -3587,13 +3587,13 @@
     <t xml:space="preserve">10.4901161193848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0906887054443</t>
+    <t xml:space="preserve">10.0906867980957</t>
   </si>
   <si>
     <t xml:space="preserve">10.0761098861694</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2204303741455</t>
+    <t xml:space="preserve">10.2204294204712</t>
   </si>
   <si>
     <t xml:space="preserve">10.1227579116821</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">10.8312349319458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8705949783325</t>
+    <t xml:space="preserve">10.8705940246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.8910036087036</t>
@@ -3611,13 +3611,13 @@
     <t xml:space="preserve">11.0061674118042</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6869163513184</t>
+    <t xml:space="preserve">10.686915397644</t>
   </si>
   <si>
     <t xml:space="preserve">10.7306489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.678168296814</t>
+    <t xml:space="preserve">10.6781692504883</t>
   </si>
   <si>
     <t xml:space="preserve">10.8283195495605</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">11.0047092437744</t>
   </si>
   <si>
-    <t xml:space="preserve">11.000337600708</t>
+    <t xml:space="preserve">11.0003366470337</t>
   </si>
   <si>
     <t xml:space="preserve">10.7364797592163</t>
@@ -3635,13 +3635,13 @@
     <t xml:space="preserve">10.9376516342163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1636056900024</t>
+    <t xml:space="preserve">11.1636066436768</t>
   </si>
   <si>
     <t xml:space="preserve">11.2160863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2787704467773</t>
+    <t xml:space="preserve">11.2787714004517</t>
   </si>
   <si>
     <t xml:space="preserve">11.2583618164062</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">11.739426612854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502159118652</t>
+    <t xml:space="preserve">11.8502168655396</t>
   </si>
   <si>
     <t xml:space="preserve">11.9143590927124</t>
@@ -3665,13 +3665,13 @@
     <t xml:space="preserve">12.1709260940552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5120449066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7219638824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.737998008728</t>
+    <t xml:space="preserve">12.5120439529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.721962928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7379989624023</t>
   </si>
   <si>
     <t xml:space="preserve">12.5601511001587</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">12.3910493850708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5003814697266</t>
+    <t xml:space="preserve">12.5003824234009</t>
   </si>
   <si>
     <t xml:space="preserve">12.3677253723145</t>
@@ -3689,10 +3689,10 @@
     <t xml:space="preserve">12.3167028427124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3181600570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3604373931885</t>
+    <t xml:space="preserve">12.3181610107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3604364395142</t>
   </si>
   <si>
     <t xml:space="preserve">12.0003671646118</t>
@@ -3701,10 +3701,10 @@
     <t xml:space="preserve">12.4056282043457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3808450698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3560619354248</t>
+    <t xml:space="preserve">12.3808441162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3560628890991</t>
   </si>
   <si>
     <t xml:space="preserve">12.3852186203003</t>
@@ -3713,16 +3713,16 @@
     <t xml:space="preserve">12.436240196228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2758855819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2613077163696</t>
+    <t xml:space="preserve">12.2758846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2613086700439</t>
   </si>
   <si>
     <t xml:space="preserve">12.0659675598145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1738414764404</t>
+    <t xml:space="preserve">12.1738405227661</t>
   </si>
   <si>
     <t xml:space="preserve">12.3414850234985</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">12.1942501068115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0936641693115</t>
+    <t xml:space="preserve">12.0936632156372</t>
   </si>
   <si>
     <t xml:space="preserve">11.6884031295776</t>
@@ -3743,13 +3743,13 @@
     <t xml:space="preserve">11.8429279327393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8370971679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6679935455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4332942962646</t>
+    <t xml:space="preserve">11.8370952606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6679944992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4332933425903</t>
   </si>
   <si>
     <t xml:space="preserve">11.0222024917603</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">11.0499000549316</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4289207458496</t>
+    <t xml:space="preserve">11.4289216995239</t>
   </si>
   <si>
     <t xml:space="preserve">11.3633213043213</t>
@@ -3794,13 +3794,13 @@
     <t xml:space="preserve">13.0280961990356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1170196533203</t>
+    <t xml:space="preserve">13.117018699646</t>
   </si>
   <si>
     <t xml:space="preserve">13.0834913253784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1330537796021</t>
+    <t xml:space="preserve">13.1330547332764</t>
   </si>
   <si>
     <t xml:space="preserve">13.4829177856445</t>
@@ -3809,10 +3809,10 @@
     <t xml:space="preserve">13.5645551681519</t>
   </si>
   <si>
-    <t xml:space="preserve">13.369213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0062284469604</t>
+    <t xml:space="preserve">13.3692140579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0062294006348</t>
   </si>
   <si>
     <t xml:space="preserve">13.105357170105</t>
@@ -3827,10 +3827,10 @@
     <t xml:space="preserve">12.5412006378174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5732698440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6024255752563</t>
+    <t xml:space="preserve">12.5732707977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6024265289307</t>
   </si>
   <si>
     <t xml:space="preserve">12.4858045578003</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">12.4814319610596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.567440032959</t>
+    <t xml:space="preserve">12.5674390792847</t>
   </si>
   <si>
     <t xml:space="preserve">12.4537343978882</t>
@@ -3866,19 +3866,19 @@
     <t xml:space="preserve">12.2656803131104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6898927688599</t>
+    <t xml:space="preserve">12.6898918151855</t>
   </si>
   <si>
     <t xml:space="preserve">12.2525615692139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7044401168823</t>
+    <t xml:space="preserve">11.704439163208</t>
   </si>
   <si>
     <t xml:space="preserve">11.6854877471924</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0645093917847</t>
+    <t xml:space="preserve">12.0645084381104</t>
   </si>
   <si>
     <t xml:space="preserve">12.2219476699829</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">12.2365255355835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3444004058838</t>
+    <t xml:space="preserve">12.3444013595581</t>
   </si>
   <si>
     <t xml:space="preserve">11.9770412445068</t>
@@ -3896,13 +3896,13 @@
     <t xml:space="preserve">12.1432285308838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0426416397095</t>
+    <t xml:space="preserve">12.0426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">11.8575048446655</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7627515792847</t>
+    <t xml:space="preserve">11.762749671936</t>
   </si>
   <si>
     <t xml:space="preserve">12.0674247741699</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">12.0790872573853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1534337997437</t>
+    <t xml:space="preserve">12.1534328460693</t>
   </si>
   <si>
     <t xml:space="preserve">12.2642240524292</t>
@@ -3926,16 +3926,16 @@
     <t xml:space="preserve">12.2671394348145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4114589691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3123302459717</t>
+    <t xml:space="preserve">12.4114580154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3123292922974</t>
   </si>
   <si>
     <t xml:space="preserve">12.2292375564575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2598495483398</t>
+    <t xml:space="preserve">12.2598505020142</t>
   </si>
   <si>
     <t xml:space="preserve">12.2846326828003</t>
@@ -3944,10 +3944,10 @@
     <t xml:space="preserve">12.281717300415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7656965255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8079719543457</t>
+    <t xml:space="preserve">12.765697479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8079710006714</t>
   </si>
   <si>
     <t xml:space="preserve">12.7992258071899</t>
@@ -3956,13 +3956,13 @@
     <t xml:space="preserve">12.5995111465454</t>
   </si>
   <si>
-    <t xml:space="preserve">12.719048500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7321662902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7904777526855</t>
+    <t xml:space="preserve">12.7190475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7321672439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7904787063599</t>
   </si>
   <si>
     <t xml:space="preserve">12.857536315918</t>
@@ -3971,13 +3971,13 @@
     <t xml:space="preserve">12.9143896102905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7817325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7117605209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0339250564575</t>
+    <t xml:space="preserve">12.7817316055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7117595672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0339260101318</t>
   </si>
   <si>
     <t xml:space="preserve">13.0368413925171</t>
@@ -3989,22 +3989,22 @@
     <t xml:space="preserve">13.1855344772339</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0878648757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.093695640564</t>
+    <t xml:space="preserve">13.0878639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0936946868896</t>
   </si>
   <si>
     <t xml:space="preserve">12.7248802185059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3983383178711</t>
+    <t xml:space="preserve">12.3983392715454</t>
   </si>
   <si>
     <t xml:space="preserve">12.2511043548584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1782159805298</t>
+    <t xml:space="preserve">12.1782150268555</t>
   </si>
   <si>
     <t xml:space="preserve">11.3458280563354</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">11.0353231430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.662163734436</t>
+    <t xml:space="preserve">11.6621646881104</t>
   </si>
   <si>
     <t xml:space="preserve">11.6096849441528</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">11.8749980926514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2977523803711</t>
+    <t xml:space="preserve">12.2977514266968</t>
   </si>
   <si>
     <t xml:space="preserve">12.1592626571655</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">11.9887046813965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0193185806274</t>
+    <t xml:space="preserve">12.0193176269531</t>
   </si>
   <si>
     <t xml:space="preserve">11.9289360046387</t>
@@ -4046,37 +4046,37 @@
     <t xml:space="preserve">11.8589639663696</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8924922943115</t>
+    <t xml:space="preserve">11.8924913406372</t>
   </si>
   <si>
     <t xml:space="preserve">11.9639225006104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5309638977051</t>
+    <t xml:space="preserve">11.5309648513794</t>
   </si>
   <si>
     <t xml:space="preserve">11.886661529541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9916200637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2685976028442</t>
+    <t xml:space="preserve">11.9916210174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2685966491699</t>
   </si>
   <si>
     <t xml:space="preserve">12.1621799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301221847534</t>
+    <t xml:space="preserve">12.6301231384277</t>
   </si>
   <si>
     <t xml:space="preserve">12.9114742279053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4318971633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.299241065979</t>
+    <t xml:space="preserve">13.4318962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2992401123047</t>
   </si>
   <si>
     <t xml:space="preserve">13.1213932037354</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">13.020806312561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1490898132324</t>
+    <t xml:space="preserve">13.1490907669067</t>
   </si>
   <si>
     <t xml:space="preserve">13.3969106674194</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">13.8561096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.829870223999</t>
+    <t xml:space="preserve">13.8298692703247</t>
   </si>
   <si>
     <t xml:space="preserve">13.9508638381958</t>
@@ -4103,10 +4103,10 @@
     <t xml:space="preserve">13.9173345565796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8415307998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6986694335938</t>
+    <t xml:space="preserve">13.8415298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6986703872681</t>
   </si>
   <si>
     <t xml:space="preserve">13.2132329940796</t>
@@ -4115,22 +4115,22 @@
     <t xml:space="preserve">12.1009521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6855192184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7861061096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4406147003174</t>
+    <t xml:space="preserve">12.6855182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7861051559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4406137466431</t>
   </si>
   <si>
     <t xml:space="preserve">12.3691825866699</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6417856216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6636524200439</t>
+    <t xml:space="preserve">12.6417846679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6636533737183</t>
   </si>
   <si>
     <t xml:space="preserve">11.998908996582</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">11.882287979126</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9814157485962</t>
+    <t xml:space="preserve">11.9814167022705</t>
   </si>
   <si>
     <t xml:space="preserve">12.4683132171631</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">12.3618927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.223406791687</t>
+    <t xml:space="preserve">12.2234058380127</t>
   </si>
   <si>
     <t xml:space="preserve">11.9099855422974</t>
@@ -4157,22 +4157,22 @@
     <t xml:space="preserve">12.3997955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5149602890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1665525436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8837451934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4391565322876</t>
+    <t xml:space="preserve">12.5149593353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1665515899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8837461471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4391555786133</t>
   </si>
   <si>
     <t xml:space="preserve">11.6869459152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3064994812012</t>
+    <t xml:space="preserve">12.3064985275269</t>
   </si>
   <si>
     <t xml:space="preserve">11.1052951812744</t>
@@ -4181,16 +4181,16 @@
     <t xml:space="preserve">11.2190017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9041233062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0746507644653</t>
+    <t xml:space="preserve">10.9041242599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0746517181396</t>
   </si>
   <si>
     <t xml:space="preserve">9.43031787872314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42594337463379</t>
+    <t xml:space="preserve">9.42594432830811</t>
   </si>
   <si>
     <t xml:space="preserve">10.5834150314331</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">10.2043933868408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3180999755859</t>
+    <t xml:space="preserve">10.3180990219116</t>
   </si>
   <si>
     <t xml:space="preserve">10.9770126342773</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">10.6475553512573</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8035364151001</t>
+    <t xml:space="preserve">10.8035373687744</t>
   </si>
   <si>
     <t xml:space="preserve">10.6373510360718</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">10.5323915481567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2321224212646</t>
+    <t xml:space="preserve">11.2321214675903</t>
   </si>
   <si>
     <t xml:space="preserve">11.054274559021</t>
@@ -4244,10 +4244,10 @@
     <t xml:space="preserve">10.7875022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7802124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8516426086426</t>
+    <t xml:space="preserve">10.7802133560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8516435623169</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522151947021</t>
@@ -4271,19 +4271,19 @@
     <t xml:space="preserve">10.1854419708252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2583312988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5054626464844</t>
+    <t xml:space="preserve">10.2583322525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5054616928101</t>
   </si>
   <si>
     <t xml:space="preserve">10.5621299743652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6644458770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3197202682495</t>
+    <t xml:space="preserve">10.6644449234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3197212219238</t>
   </si>
   <si>
     <t xml:space="preserve">10.0741624832153</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">10.2174043655396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9088830947876</t>
+    <t xml:space="preserve">9.90888404846191</t>
   </si>
   <si>
     <t xml:space="preserve">10.2237005233765</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">10.091477394104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0190687179565</t>
+    <t xml:space="preserve">10.0190696716309</t>
   </si>
   <si>
     <t xml:space="preserve">10.3449058532715</t>
@@ -4325,10 +4325,10 @@
     <t xml:space="preserve">10.4125909805298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4314804077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8375949859619</t>
+    <t xml:space="preserve">10.4314794540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8375959396362</t>
   </si>
   <si>
     <t xml:space="preserve">10.7683353424072</t>
@@ -4349,10 +4349,10 @@
     <t xml:space="preserve">10.6817607879639</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3386087417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5306491851807</t>
+    <t xml:space="preserve">10.3386096954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5306482315063</t>
   </si>
   <si>
     <t xml:space="preserve">10.7903728485107</t>
@@ -4364,7 +4364,7 @@
     <t xml:space="preserve">11.0186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9666709899902</t>
+    <t xml:space="preserve">10.9666700363159</t>
   </si>
   <si>
     <t xml:space="preserve">11.1571350097656</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">9.56415843963623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63027000427246</t>
+    <t xml:space="preserve">9.63026905059814</t>
   </si>
   <si>
     <t xml:space="preserve">9.74990081787109</t>
@@ -4415,16 +4415,16 @@
     <t xml:space="preserve">9.82230758666992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61295509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78138256072998</t>
+    <t xml:space="preserve">9.61295413970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78138160705566</t>
   </si>
   <si>
     <t xml:space="preserve">9.77508544921875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86953163146973</t>
+    <t xml:space="preserve">9.86953067779541</t>
   </si>
   <si>
     <t xml:space="preserve">9.59406566619873</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">9.28082180023193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22415447235107</t>
+    <t xml:space="preserve">9.22415542602539</t>
   </si>
   <si>
     <t xml:space="preserve">9.12656116485596</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">9.40989780426025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64443683624268</t>
+    <t xml:space="preserve">9.64443588256836</t>
   </si>
   <si>
     <t xml:space="preserve">10.014347076416</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">9.94981002807617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89156818389893</t>
+    <t xml:space="preserve">9.89156913757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.9545316696167</t>
@@ -4487,13 +4487,13 @@
     <t xml:space="preserve">10.0348100662231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.176477432251</t>
+    <t xml:space="preserve">10.1764783859253</t>
   </si>
   <si>
     <t xml:space="preserve">10.677038192749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9572257995605</t>
+    <t xml:space="preserve">10.9572248458862</t>
   </si>
   <si>
     <t xml:space="preserve">11.0548191070557</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">11.6340837478638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3381547927856</t>
+    <t xml:space="preserve">11.33815574646</t>
   </si>
   <si>
     <t xml:space="preserve">11.4971380233765</t>
@@ -4529,19 +4529,19 @@
     <t xml:space="preserve">11.726954460144</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223245620728</t>
+    <t xml:space="preserve">11.5223236083984</t>
   </si>
   <si>
     <t xml:space="preserve">11.7049179077148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680639266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9021329879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0500965118408</t>
+    <t xml:space="preserve">11.3680629730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9021339416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0500974655151</t>
   </si>
   <si>
     <t xml:space="preserve">11.1681537628174</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">10.6046304702759</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0961990356445</t>
+    <t xml:space="preserve">10.0961999893188</t>
   </si>
   <si>
     <t xml:space="preserve">10.2315711975098</t>
@@ -4577,13 +4577,13 @@
     <t xml:space="preserve">10.3401832580566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3323125839233</t>
+    <t xml:space="preserve">10.3323135375977</t>
   </si>
   <si>
     <t xml:space="preserve">10.4613876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8124103546143</t>
+    <t xml:space="preserve">10.8124094009399</t>
   </si>
   <si>
     <t xml:space="preserve">10.6597232818604</t>
@@ -4613,13 +4613,13 @@
     <t xml:space="preserve">10.0111989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1009216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0946264266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65860462188721</t>
+    <t xml:space="preserve">10.1009225845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0946254730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65860366821289</t>
   </si>
   <si>
     <t xml:space="preserve">9.84906768798828</t>
@@ -4652,13 +4652,13 @@
     <t xml:space="preserve">10.0851812362671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2488861083984</t>
+    <t xml:space="preserve">10.2488870620728</t>
   </si>
   <si>
     <t xml:space="preserve">10.2063865661621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3685178756714</t>
+    <t xml:space="preserve">10.3685169219971</t>
   </si>
   <si>
     <t xml:space="preserve">10.2898120880127</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">10.6487045288086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7447242736816</t>
+    <t xml:space="preserve">10.7447233200073</t>
   </si>
   <si>
     <t xml:space="preserve">10.7305574417114</t>
@@ -4679,10 +4679,10 @@
     <t xml:space="preserve">10.7510204315186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8092622756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4566669464111</t>
+    <t xml:space="preserve">10.8092613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4566659927368</t>
   </si>
   <si>
     <t xml:space="preserve">10.8297252655029</t>
@@ -4694,37 +4694,37 @@
     <t xml:space="preserve">11.1429681777954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1980609893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.339729309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4247303009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2153759002686</t>
+    <t xml:space="preserve">11.1980619430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3397302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.424729347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2153768539429</t>
   </si>
   <si>
     <t xml:space="preserve">11.1036157608032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3413028717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4451932907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5553789138794</t>
+    <t xml:space="preserve">11.3413038253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4451923370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5553798675537</t>
   </si>
   <si>
     <t xml:space="preserve">11.3838033676147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5333433151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5301942825317</t>
+    <t xml:space="preserve">11.5333423614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5301933288574</t>
   </si>
   <si>
     <t xml:space="preserve">11.4546375274658</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">11.5774164199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206583023071</t>
+    <t xml:space="preserve">11.7206592559814</t>
   </si>
   <si>
     <t xml:space="preserve">11.7332515716553</t>
@@ -4742,13 +4742,13 @@
     <t xml:space="preserve">11.4924163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5364904403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3712120056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3979711532593</t>
+    <t xml:space="preserve">11.5364894866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3712110519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.397970199585</t>
   </si>
   <si>
     <t xml:space="preserve">11.0831527709961</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">10.933614730835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6675939559937</t>
+    <t xml:space="preserve">10.6675930023193</t>
   </si>
   <si>
     <t xml:space="preserve">10.3291645050049</t>
@@ -4778,16 +4778,16 @@
     <t xml:space="preserve">10.3559246063232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.32444190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5290746688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4393520355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7415761947632</t>
+    <t xml:space="preserve">10.3244428634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.52907371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4393510818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7415752410889</t>
   </si>
   <si>
     <t xml:space="preserve">10.8816699981689</t>
@@ -4796,25 +4796,25 @@
     <t xml:space="preserve">11.1697273254395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2862100601196</t>
+    <t xml:space="preserve">11.2862110137939</t>
   </si>
   <si>
     <t xml:space="preserve">11.3696374893188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5427875518799</t>
+    <t xml:space="preserve">11.5427865982056</t>
   </si>
   <si>
     <t xml:space="preserve">11.5286197662354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6246404647827</t>
+    <t xml:space="preserve">11.6246395111084</t>
   </si>
   <si>
     <t xml:space="preserve">11.1996355056763</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2673206329346</t>
+    <t xml:space="preserve">11.2673215866089</t>
   </si>
   <si>
     <t xml:space="preserve">11.3035249710083</t>
@@ -4826,13 +4826,13 @@
     <t xml:space="preserve">10.9477806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">11.037504196167</t>
+    <t xml:space="preserve">11.0375032424927</t>
   </si>
   <si>
     <t xml:space="preserve">11.0312070846558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0343570709229</t>
+    <t xml:space="preserve">11.0343561172485</t>
   </si>
   <si>
     <t xml:space="preserve">10.95250415802</t>
@@ -4856,7 +4856,7 @@
     <t xml:space="preserve">11.9630680084229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8686218261719</t>
+    <t xml:space="preserve">11.8686227798462</t>
   </si>
   <si>
     <t xml:space="preserve">11.8749198913574</t>
@@ -4874,22 +4874,22 @@
     <t xml:space="preserve">12.2054777145386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2589960098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4903879165649</t>
+    <t xml:space="preserve">12.258996963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4903869628906</t>
   </si>
   <si>
     <t xml:space="preserve">12.517147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5533514022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7013158798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4888134002686</t>
+    <t xml:space="preserve">12.5533504486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7013149261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4888124465942</t>
   </si>
   <si>
     <t xml:space="preserve">12.7642793655396</t>
@@ -4901,7 +4901,7 @@
     <t xml:space="preserve">12.946873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0901145935059</t>
+    <t xml:space="preserve">13.0901155471802</t>
   </si>
   <si>
     <t xml:space="preserve">13.0287265777588</t>
@@ -4913,7 +4913,7 @@
     <t xml:space="preserve">13.5151195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9054918289185</t>
+    <t xml:space="preserve">13.9054927825928</t>
   </si>
   <si>
     <t xml:space="preserve">13.8330841064453</t>
@@ -4970,7 +4970,7 @@
     <t xml:space="preserve">13.050763130188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1719675064087</t>
+    <t xml:space="preserve">13.171968460083</t>
   </si>
   <si>
     <t xml:space="preserve">13.1200227737427</t>
@@ -4982,7 +4982,7 @@
     <t xml:space="preserve">12.6824264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7878894805908</t>
+    <t xml:space="preserve">12.7878904342651</t>
   </si>
   <si>
     <t xml:space="preserve">13.1829862594604</t>
@@ -4997,13 +4997,13 @@
     <t xml:space="preserve">13.5088214874268</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3624334335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.404932975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3545627593994</t>
+    <t xml:space="preserve">13.3624324798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4049320220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3545618057251</t>
   </si>
   <si>
     <t xml:space="preserve">12.6320543289185</t>
@@ -6837,6 +6837,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.77799987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85499954223633</t>
   </si>
 </sst>
 </file>
@@ -72201,7 +72204,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6940972222</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>20034417</v>
@@ -72222,6 +72225,32 @@
         <v>2274</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6938425926</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>22151911</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>9.05700016021729</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>8.76099967956543</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>8.85499954223633</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>2275</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -44,31 +44,31 @@
     <t xml:space="preserve">STLAM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13119411468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91636300086975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78795766830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63238978385925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757349967957</t>
+    <t xml:space="preserve">4.13119459152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91636347770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7879581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63239002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757302284241</t>
   </si>
   <si>
     <t xml:space="preserve">3.71881651878357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66943001747131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37804818153381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28421449661255</t>
+    <t xml:space="preserve">3.66942954063416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37804841995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28421401977539</t>
   </si>
   <si>
     <t xml:space="preserve">3.18790912628174</t>
@@ -80,55 +80,55 @@
     <t xml:space="preserve">3.06197333335876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25705099105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32619261741638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26198959350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4620053768158</t>
+    <t xml:space="preserve">3.25705075263977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3261923789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26199007034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46200513839722</t>
   </si>
   <si>
     <t xml:space="preserve">3.43237352371216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18543982505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16321611404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16074681282043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07678985595703</t>
+    <t xml:space="preserve">3.18544030189514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16321706771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16074705123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07679009437561</t>
   </si>
   <si>
     <t xml:space="preserve">2.95332264900208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91628336906433</t>
+    <t xml:space="preserve">2.91628289222717</t>
   </si>
   <si>
     <t xml:space="preserve">2.94838428497314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65700316429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58292317390442</t>
+    <t xml:space="preserve">2.65700340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58292269706726</t>
   </si>
   <si>
     <t xml:space="preserve">2.73355269432068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59279990196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68416595458984</t>
+    <t xml:space="preserve">2.59280014038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68416571617126</t>
   </si>
   <si>
     <t xml:space="preserve">2.80269384384155</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">2.75824570655823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89899778366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87924289703369</t>
+    <t xml:space="preserve">2.89899754524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87924337387085</t>
   </si>
   <si>
     <t xml:space="preserve">2.81010127067566</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">2.92615985870361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83973336219788</t>
+    <t xml:space="preserve">2.83973360061646</t>
   </si>
   <si>
     <t xml:space="preserve">2.72614455223083</t>
@@ -161,151 +161,151 @@
     <t xml:space="preserve">3.13358426094055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29902982711792</t>
+    <t xml:space="preserve">3.29902958869934</t>
   </si>
   <si>
     <t xml:space="preserve">3.45212888717651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46447491645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44225120544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28915214538574</t>
+    <t xml:space="preserve">3.46447563171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44225072860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2891526222229</t>
   </si>
   <si>
     <t xml:space="preserve">3.30643749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21013402938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35088539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44719004631042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36076331138611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44472026824951</t>
+    <t xml:space="preserve">3.21013355255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35088562965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44718980789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36076307296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44472002983093</t>
   </si>
   <si>
     <t xml:space="preserve">3.42496585845947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51633071899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50151491165161</t>
+    <t xml:space="preserve">3.5163311958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50151515007019</t>
   </si>
   <si>
     <t xml:space="preserve">3.51386117935181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4768214225769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33360052108765</t>
+    <t xml:space="preserve">3.47682237625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33360075950623</t>
   </si>
   <si>
     <t xml:space="preserve">3.57559466362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50645351409912</t>
+    <t xml:space="preserve">3.50645399093628</t>
   </si>
   <si>
     <t xml:space="preserve">3.33607006072998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34841656684875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18050193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1385223865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01505637168884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13605380058289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2126030921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1681547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31878447532654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35335445404053</t>
+    <t xml:space="preserve">3.34841704368591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18050146102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13852286338806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01505613327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13605356216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21260261535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16815519332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31878423690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35335564613342</t>
   </si>
   <si>
     <t xml:space="preserve">3.40274214744568</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5657172203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54596328735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56818747520447</t>
+    <t xml:space="preserve">3.56571745872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54596352577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56818699836731</t>
   </si>
   <si>
     <t xml:space="preserve">3.47435283660889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5336172580719</t>
+    <t xml:space="preserve">3.53361630439758</t>
   </si>
   <si>
     <t xml:space="preserve">3.41014981269836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38298630714417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29656052589417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26692819595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3657021522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3163149356842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38051772117615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33113145828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10889101028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11382985115051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10148334503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629915237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97801661491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06938171386719</t>
+    <t xml:space="preserve">3.38298678398132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29656076431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26692843437195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36570167541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31631517410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38051748275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33113121986389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10889077186584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11383008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.101482629776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629891395569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97801637649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06938195228577</t>
   </si>
   <si>
     <t xml:space="preserve">3.12370681762695</t>
@@ -314,46 +314,46 @@
     <t xml:space="preserve">3.07185125350952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15827751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07432007789612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0422191619873</t>
+    <t xml:space="preserve">3.15827822685242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0743203163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04221940040588</t>
   </si>
   <si>
     <t xml:space="preserve">3.03974962234497</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1483998298645</t>
+    <t xml:space="preserve">3.14840006828308</t>
   </si>
   <si>
     <t xml:space="preserve">3.12123727798462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93109846115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87677359580994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89652872085571</t>
+    <t xml:space="preserve">2.93109893798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87677311897278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89652824401855</t>
   </si>
   <si>
     <t xml:space="preserve">2.86195755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93356800079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09407448768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08666682243347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04962754249573</t>
+    <t xml:space="preserve">2.93356823921204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09407496452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08666729927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04962706565857</t>
   </si>
   <si>
     <t xml:space="preserve">3.1113600730896</t>
@@ -362,103 +362,103 @@
     <t xml:space="preserve">2.81997919082642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64465618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66194200515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71379780769348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.770592212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.533536195755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52365899085999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54835176467896</t>
+    <t xml:space="preserve">2.64465641975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66194152832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7137975692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77059245109558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53353595733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52365875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54835224151611</t>
   </si>
   <si>
     <t xml:space="preserve">2.8471417427063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96319985389709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91134452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99777126312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00270986557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95826148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08913588523865</t>
+    <t xml:space="preserve">2.96320009231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91134428977966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99777054786682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00270938873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95826125144958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08913612365723</t>
   </si>
   <si>
     <t xml:space="preserve">3.0990138053894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12617683410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06691241264343</t>
+    <t xml:space="preserve">3.12617611885071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06691217422485</t>
   </si>
   <si>
     <t xml:space="preserve">2.84467220306396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81257081031799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69157361984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91381359100342</t>
+    <t xml:space="preserve">2.81257128715515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69157338142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.913813829422</t>
   </si>
   <si>
     <t xml:space="preserve">2.88665080070496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05703473091125</t>
+    <t xml:space="preserve">3.05703520774841</t>
   </si>
   <si>
     <t xml:space="preserve">2.98789405822754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96073126792908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97307777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88418173789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91875243186951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0348105430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02987217903137</t>
+    <t xml:space="preserve">2.96073150634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97307801246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88418197631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91875267028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03481078147888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02987194061279</t>
   </si>
   <si>
     <t xml:space="preserve">3.04468774795532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99283242225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05950427055359</t>
+    <t xml:space="preserve">2.99283218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05950450897217</t>
   </si>
   <si>
     <t xml:space="preserve">2.97554707527161</t>
@@ -467,49 +467,49 @@
     <t xml:space="preserve">2.95085382461548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96813893318176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90393590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86442685127258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87430429458618</t>
+    <t xml:space="preserve">2.96813917160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90393614768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86442732810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87430477142334</t>
   </si>
   <si>
     <t xml:space="preserve">2.81504034996033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90146732330322</t>
+    <t xml:space="preserve">2.90146708488464</t>
   </si>
   <si>
     <t xml:space="preserve">2.83232545852661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86689615249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74095988273621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70885896682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79034733772278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82491779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84220337867737</t>
+    <t xml:space="preserve">2.86689591407776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74096012115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70885848999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79034686088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82491755485535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84220314025879</t>
   </si>
   <si>
     <t xml:space="preserve">2.89158987998962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87183475494385</t>
+    <t xml:space="preserve">2.87183523178101</t>
   </si>
   <si>
     <t xml:space="preserve">2.90887475013733</t>
@@ -518,52 +518,52 @@
     <t xml:space="preserve">2.76812267303467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82244825363159</t>
+    <t xml:space="preserve">2.82244849205017</t>
   </si>
   <si>
     <t xml:space="preserve">2.85948801040649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93850660324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25211191177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29409098625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25952005386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03234148025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02740335464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16568541526794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52373957633972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39780306816101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47188258171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45953607559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47929096221924</t>
+    <t xml:space="preserve">2.93850708007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25211238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29409122467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2595202922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03234195709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02740287780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16568565368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52373933792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39780330657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47188305854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45953631401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47929120063782</t>
   </si>
   <si>
     <t xml:space="preserve">3.49410700798035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55584025382996</t>
+    <t xml:space="preserve">3.55584049224854</t>
   </si>
   <si>
     <t xml:space="preserve">3.58547234535217</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">3.57065629959106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56077933311462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60028862953186</t>
+    <t xml:space="preserve">3.56077909469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60028839111328</t>
   </si>
   <si>
     <t xml:space="preserve">3.62251257896423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55830979347229</t>
+    <t xml:space="preserve">3.55830955505371</t>
   </si>
   <si>
     <t xml:space="preserve">3.72128558158875</t>
@@ -590,19 +590,19 @@
     <t xml:space="preserve">3.81265115737915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85710000991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93364882469177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9311785697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97315740585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525903701782</t>
+    <t xml:space="preserve">3.85709929466248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93364906311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93117833137512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97315764427185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525856018066</t>
   </si>
   <si>
     <t xml:space="preserve">3.99044299125671</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">4.15341949462891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19539785385132</t>
+    <t xml:space="preserve">4.19539833068848</t>
   </si>
   <si>
     <t xml:space="preserve">4.21762180328369</t>
@@ -620,49 +620,49 @@
     <t xml:space="preserve">4.29664039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30651807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17564344406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26453971862793</t>
+    <t xml:space="preserve">4.30651760101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17564296722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26453924179077</t>
   </si>
   <si>
     <t xml:space="preserve">4.31392621994019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30898761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2793550491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42257690429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50653457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53863573074341</t>
+    <t xml:space="preserve">4.30898714065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27935457229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42257642745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5065336227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53863525390625</t>
   </si>
   <si>
     <t xml:space="preserve">4.5707368850708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88928079605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95842218399048</t>
+    <t xml:space="preserve">4.88928031921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95842266082764</t>
   </si>
   <si>
     <t xml:space="preserve">5.0127477645874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17078447341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3361496925354</t>
+    <t xml:space="preserve">5.17078495025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33615016937256</t>
   </si>
   <si>
     <t xml:space="preserve">4.53616571426392</t>
@@ -674,34 +674,34 @@
     <t xml:space="preserve">4.39047574996948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41516876220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62753057479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64234733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71889638900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99793195724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0423789024353</t>
+    <t xml:space="preserve">4.41516828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62753105163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64234781265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71889686584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99793148040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04237842559814</t>
   </si>
   <si>
     <t xml:space="preserve">5.10164308547974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1263370513916</t>
+    <t xml:space="preserve">5.12633657455444</t>
   </si>
   <si>
     <t xml:space="preserve">4.95348358154297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9880542755127</t>
+    <t xml:space="preserve">4.98805379867554</t>
   </si>
   <si>
     <t xml:space="preserve">4.99299240112305</t>
@@ -710,79 +710,79 @@
     <t xml:space="preserve">5.00287055969238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04731798171997</t>
+    <t xml:space="preserve">5.04731750488281</t>
   </si>
   <si>
     <t xml:space="preserve">4.92385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78062963485718</t>
+    <t xml:space="preserve">4.78062915802002</t>
   </si>
   <si>
     <t xml:space="preserve">4.89915800094604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02756309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33869886398315</t>
+    <t xml:space="preserve">5.02756357192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33869934082031</t>
   </si>
   <si>
     <t xml:space="preserve">5.34363746643066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32388401031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25474166870117</t>
+    <t xml:space="preserve">5.32388305664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25474214553833</t>
   </si>
   <si>
     <t xml:space="preserve">5.32882261276245</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1757230758667</t>
+    <t xml:space="preserve">5.17572355270386</t>
   </si>
   <si>
     <t xml:space="preserve">5.14609098434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18559980392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18066120147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13127565383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13621425628662</t>
+    <t xml:space="preserve">5.18560075759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18066167831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13127470016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13621377944946</t>
   </si>
   <si>
     <t xml:space="preserve">5.16584634780884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09670400619507</t>
+    <t xml:space="preserve">5.09670448303223</t>
   </si>
   <si>
     <t xml:space="preserve">5.14115238189697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22511005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30412817001343</t>
+    <t xml:space="preserve">5.22511053085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30412769317627</t>
   </si>
   <si>
     <t xml:space="preserve">5.21029472351074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98311519622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94360542297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96336030960083</t>
+    <t xml:space="preserve">4.98311567306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94360589981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96336078643799</t>
   </si>
   <si>
     <t xml:space="preserve">4.93372821807861</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">5.06213426589966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81026220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83248615264893</t>
+    <t xml:space="preserve">4.81026268005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83248662948608</t>
   </si>
   <si>
     <t xml:space="preserve">4.74358987808228</t>
@@ -809,28 +809,28 @@
     <t xml:space="preserve">4.78556823730469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73371267318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71642637252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70655012130737</t>
+    <t xml:space="preserve">4.73371315002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71642732620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70655059814453</t>
   </si>
   <si>
     <t xml:space="preserve">4.69420337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51887989044189</t>
+    <t xml:space="preserve">4.51888036727905</t>
   </si>
   <si>
     <t xml:space="preserve">4.45220851898193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6472864151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70408010482788</t>
+    <t xml:space="preserve">4.64728689193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7040810585022</t>
   </si>
   <si>
     <t xml:space="preserve">4.63000059127808</t>
@@ -851,55 +851,55 @@
     <t xml:space="preserve">4.97323799133301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05225658416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03744029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91891288757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94854497909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02262401580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76828289031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62012434005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80038547515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72383546829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68926429748535</t>
+    <t xml:space="preserve">5.05225706100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03743982315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91891241073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94854545593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02262496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76828336715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62012386322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80038452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72383499145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68926477432251</t>
   </si>
   <si>
     <t xml:space="preserve">4.66210174560547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6719799041748</t>
+    <t xml:space="preserve">4.67197895050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.59049129486084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.583083152771</t>
+    <t xml:space="preserve">4.58308362960815</t>
   </si>
   <si>
     <t xml:space="preserve">4.61518478393555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84730100631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83001708984375</t>
+    <t xml:space="preserve">4.8473014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83001661300659</t>
   </si>
   <si>
     <t xml:space="preserve">4.75346708297729</t>
@@ -908,22 +908,22 @@
     <t xml:space="preserve">4.8053240776062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75099849700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79544639587402</t>
+    <t xml:space="preserve">4.75099802017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79544591903687</t>
   </si>
   <si>
     <t xml:space="preserve">4.8176703453064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78309965133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7213659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.684326171875</t>
+    <t xml:space="preserve">4.78309917449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72136545181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68432569503784</t>
   </si>
   <si>
     <t xml:space="preserve">4.85224056243896</t>
@@ -935,13 +935,13 @@
     <t xml:space="preserve">4.76087522506714</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55838966369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85507869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8600378036499</t>
+    <t xml:space="preserve">4.55839014053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86003732681274</t>
   </si>
   <si>
     <t xml:space="preserve">4.78564929962158</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">4.8253231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80548524856567</t>
+    <t xml:space="preserve">4.80548620223999</t>
   </si>
   <si>
     <t xml:space="preserve">4.87243556976318</t>
@@ -971,13 +971,13 @@
     <t xml:space="preserve">5.1724681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10799884796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17742729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97410011291504</t>
+    <t xml:space="preserve">5.10799789428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17742776870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97409915924072</t>
   </si>
   <si>
     <t xml:space="preserve">4.97905921936035</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">4.98897695541382</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03856945037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03361082077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05840587615967</t>
+    <t xml:space="preserve">5.03856992721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03360986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05840635299683</t>
   </si>
   <si>
     <t xml:space="preserve">5.07328414916992</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">5.02865123748779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07824277877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06336545944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95178365707397</t>
+    <t xml:space="preserve">5.07824325561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0633659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95178270339966</t>
   </si>
   <si>
     <t xml:space="preserve">4.95426225662231</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">5.26669454574585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40555286407471</t>
+    <t xml:space="preserve">5.40555143356323</t>
   </si>
   <si>
     <t xml:space="preserve">5.34604167938232</t>
@@ -1028,22 +1028,22 @@
     <t xml:space="preserve">5.30636835098267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67335081100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68822717666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01553678512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19406843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14943552017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16431283950806</t>
+    <t xml:space="preserve">5.67335033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68822765350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01553630828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19406938552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14943504333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16431331634521</t>
   </si>
   <si>
     <t xml:space="preserve">6.07008790969849</t>
@@ -1052,52 +1052,52 @@
     <t xml:space="preserve">6.13951683044434</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27341508865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61560344696045</t>
+    <t xml:space="preserve">6.27341604232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61560297012329</t>
   </si>
   <si>
     <t xml:space="preserve">6.53129482269287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50649881362915</t>
+    <t xml:space="preserve">6.50649976730347</t>
   </si>
   <si>
     <t xml:space="preserve">6.78421545028687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70982837677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72470569610596</t>
+    <t xml:space="preserve">6.70982789993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72470617294312</t>
   </si>
   <si>
     <t xml:space="preserve">6.76933813095093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80405282974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96770715713501</t>
+    <t xml:space="preserve">6.80405330657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96770763397217</t>
   </si>
   <si>
     <t xml:space="preserve">6.88340091705322</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99250316619873</t>
+    <t xml:space="preserve">6.99250268936157</t>
   </si>
   <si>
     <t xml:space="preserve">7.07681083679199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14623928070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18095397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46362829208374</t>
+    <t xml:space="preserve">7.14623880386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18095350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46362924575806</t>
   </si>
   <si>
     <t xml:space="preserve">7.31485271453857</t>
@@ -1106,55 +1106,55 @@
     <t xml:space="preserve">7.33468914031982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38428211212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36444473266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51818132400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58265018463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56281328201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53801727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49338531494141</t>
+    <t xml:space="preserve">7.38428068161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36444568634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51818037033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58265113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56281423568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53801918029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49338483810425</t>
   </si>
   <si>
     <t xml:space="preserve">7.4090781211853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5231409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41403675079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50330305099487</t>
+    <t xml:space="preserve">7.52313852310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41403722763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50330257415771</t>
   </si>
   <si>
     <t xml:space="preserve">7.42395544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45867109298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41899681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30989265441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37932300567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93795204162598</t>
+    <t xml:space="preserve">7.45866918563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41899728775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3098931312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37932348251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93795108795166</t>
   </si>
   <si>
     <t xml:space="preserve">7.05697345733643</t>
@@ -1163,46 +1163,46 @@
     <t xml:space="preserve">7.02225875854492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14128017425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34956789016724</t>
+    <t xml:space="preserve">7.14128065109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34956693649292</t>
   </si>
   <si>
     <t xml:space="preserve">7.3594856262207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5132212638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76614236831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73142719268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66199731826782</t>
+    <t xml:space="preserve">7.51322174072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76614141464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73142623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66199827194214</t>
   </si>
   <si>
     <t xml:space="preserve">7.45371103286743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28013801574707</t>
+    <t xml:space="preserve">7.28013706207275</t>
   </si>
   <si>
     <t xml:space="preserve">7.33964872360229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37436389923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2503833770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43387413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55785465240479</t>
+    <t xml:space="preserve">7.37436294555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25038290023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43387508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55785512924194</t>
   </si>
   <si>
     <t xml:space="preserve">7.24046421051025</t>
@@ -1211,76 +1211,76 @@
     <t xml:space="preserve">7.20078945159912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17103576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15119791030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00738096237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23550415039062</t>
+    <t xml:space="preserve">7.1710352897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15119743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00738000869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23550462722778</t>
   </si>
   <si>
     <t xml:space="preserve">7.19087219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53305912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52809906005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50826215744019</t>
+    <t xml:space="preserve">7.53305864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52809953689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50826263427734</t>
   </si>
   <si>
     <t xml:space="preserve">7.43883228302002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44875288009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6372013092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65208053588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64216184616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69175291061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67191696166992</t>
+    <t xml:space="preserve">7.4487509727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63720273971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65207958221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64216136932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69175338745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67191648483276</t>
   </si>
   <si>
     <t xml:space="preserve">7.54297733306885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39420080184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71159076690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35628890991211</t>
+    <t xml:space="preserve">7.39420032501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71158981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35628986358643</t>
   </si>
   <si>
     <t xml:space="preserve">8.88692665100098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98115158081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15968322753906</t>
+    <t xml:space="preserve">8.98115253448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15968418121338</t>
   </si>
   <si>
     <t xml:space="preserve">9.21423530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42252159118652</t>
+    <t xml:space="preserve">9.42252254486084</t>
   </si>
   <si>
     <t xml:space="preserve">9.48699283599854</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">9.69032001495361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2886209487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32829761505127</t>
+    <t xml:space="preserve">9.28862285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32829666137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.50186920166016</t>
@@ -1301,19 +1301,19 @@
     <t xml:space="preserve">9.69528007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76470851898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70519828796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64072799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63080787658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.819260597229</t>
+    <t xml:space="preserve">9.76470756530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70519733428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64072704315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63080883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81925964355469</t>
   </si>
   <si>
     <t xml:space="preserve">9.84107971191406</t>
@@ -1322,55 +1322,55 @@
     <t xml:space="preserve">9.68337726593018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65163803100586</t>
+    <t xml:space="preserve">9.65163993835449</t>
   </si>
   <si>
     <t xml:space="preserve">9.53856754302979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31936931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7579870223999</t>
+    <t xml:space="preserve">9.31937026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75798606872559</t>
   </si>
   <si>
     <t xml:space="preserve">9.35110950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89981937408447</t>
+    <t xml:space="preserve">8.89982032775879</t>
   </si>
   <si>
     <t xml:space="preserve">8.63698291778564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75302696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57548809051514</t>
+    <t xml:space="preserve">8.75302791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5754861831665</t>
   </si>
   <si>
     <t xml:space="preserve">8.77782344818115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82741451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00396347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83733367919922</t>
+    <t xml:space="preserve">8.82741546630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00396537780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8373327255249</t>
   </si>
   <si>
     <t xml:space="preserve">8.94643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98908710479736</t>
+    <t xml:space="preserve">8.98908615112305</t>
   </si>
   <si>
     <t xml:space="preserve">8.80956363677979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73814964294434</t>
+    <t xml:space="preserve">8.73814868927002</t>
   </si>
   <si>
     <t xml:space="preserve">8.69054126739502</t>
@@ -1379,22 +1379,22 @@
     <t xml:space="preserve">8.8055944442749</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71434497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4743185043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98930692672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01410293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4683666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55664253234863</t>
+    <t xml:space="preserve">8.71434593200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47431945800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98930740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01410388946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46836853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55664157867432</t>
   </si>
   <si>
     <t xml:space="preserve">8.56259155273438</t>
@@ -1403,19 +1403,19 @@
     <t xml:space="preserve">8.51597690582275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52787685394287</t>
+    <t xml:space="preserve">8.52787780761719</t>
   </si>
   <si>
     <t xml:space="preserve">8.53085422515869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43266105651855</t>
+    <t xml:space="preserve">8.43266201019287</t>
   </si>
   <si>
     <t xml:space="preserve">8.53184604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52589416503906</t>
+    <t xml:space="preserve">8.52589511871338</t>
   </si>
   <si>
     <t xml:space="preserve">8.35926532745361</t>
@@ -1424,31 +1424,31 @@
     <t xml:space="preserve">8.56457614898682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71732044219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42175006866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25115394592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18866634368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32554340362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15791988372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18370819091797</t>
+    <t xml:space="preserve">8.71732139587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42175197601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25115299224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18866729736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32554244995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15792083740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18370914459229</t>
   </si>
   <si>
     <t xml:space="preserve">8.78278350830078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73517417907715</t>
+    <t xml:space="preserve">8.73517322540283</t>
   </si>
   <si>
     <t xml:space="preserve">9.15869140625</t>
@@ -1460,79 +1460,79 @@
     <t xml:space="preserve">9.18943881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3134183883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22613716125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40764427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43640804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36301231384277</t>
+    <t xml:space="preserve">9.31342029571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22613620758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4076452255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4364070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36301136016846</t>
   </si>
   <si>
     <t xml:space="preserve">9.7091646194458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76768493652344</t>
+    <t xml:space="preserve">9.76768398284912</t>
   </si>
   <si>
     <t xml:space="preserve">9.63180160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55840587615967</t>
+    <t xml:space="preserve">9.55840492248535</t>
   </si>
   <si>
     <t xml:space="preserve">9.75974941253662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79148960113525</t>
+    <t xml:space="preserve">9.79148864746094</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393558502197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68635368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41458797454834</t>
+    <t xml:space="preserve">9.686354637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41458702087402</t>
   </si>
   <si>
     <t xml:space="preserve">9.20927619934082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43739891052246</t>
+    <t xml:space="preserve">9.43739986419678</t>
   </si>
   <si>
     <t xml:space="preserve">9.21820259094238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51674747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53559303283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48004913330078</t>
+    <t xml:space="preserve">9.51674842834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5355920791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4800500869751</t>
   </si>
   <si>
     <t xml:space="preserve">9.29556655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3084602355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42946434020996</t>
+    <t xml:space="preserve">9.30845928192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42946529388428</t>
   </si>
   <si>
     <t xml:space="preserve">9.41756343841553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36697959899902</t>
+    <t xml:space="preserve">9.36697769165039</t>
   </si>
   <si>
     <t xml:space="preserve">9.30746841430664</t>
@@ -1544,67 +1544,67 @@
     <t xml:space="preserve">9.19935703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43938446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59609603881836</t>
+    <t xml:space="preserve">9.4393835067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59609508514404</t>
   </si>
   <si>
     <t xml:space="preserve">9.48600101470947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31143569946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30548572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10810661315918</t>
+    <t xml:space="preserve">9.31143665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30548477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1081075668335</t>
   </si>
   <si>
     <t xml:space="preserve">9.06446552276611</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42748069763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62089061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.185471534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85221290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87601566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86212921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13984680175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90676403045654</t>
+    <t xml:space="preserve">9.42748165130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62089157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18547058105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85221195220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87601661682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8621301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13984775543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90676212310791</t>
   </si>
   <si>
     <t xml:space="preserve">8.98313522338867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92659950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85022735595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04463005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87403202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92461585998535</t>
+    <t xml:space="preserve">8.92660045623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85022830963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04462909698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87403297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92461681365967</t>
   </si>
   <si>
     <t xml:space="preserve">8.79666900634766</t>
@@ -1616,58 +1616,58 @@
     <t xml:space="preserve">8.38505268096924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18172359466553</t>
+    <t xml:space="preserve">8.18172550201416</t>
   </si>
   <si>
     <t xml:space="preserve">7.92979621887207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15296173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24123573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95558404922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1003942489624</t>
+    <t xml:space="preserve">8.15296268463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24123477935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95558452606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10039329528809</t>
   </si>
   <si>
     <t xml:space="preserve">8.10237693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03889942169189</t>
+    <t xml:space="preserve">8.03889846801758</t>
   </si>
   <si>
     <t xml:space="preserve">8.50506687164307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40687274932861</t>
+    <t xml:space="preserve">8.40687370300293</t>
   </si>
   <si>
     <t xml:space="preserve">8.46935939788818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52291870117188</t>
+    <t xml:space="preserve">8.52291965484619</t>
   </si>
   <si>
     <t xml:space="preserve">8.26305675506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21346473693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25214672088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19957637786865</t>
+    <t xml:space="preserve">8.21346282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25214576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19957828521729</t>
   </si>
   <si>
     <t xml:space="preserve">8.24916934967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22239017486572</t>
+    <t xml:space="preserve">8.22239112854004</t>
   </si>
   <si>
     <t xml:space="preserve">8.33347797393799</t>
@@ -1682,37 +1682,37 @@
     <t xml:space="preserve">8.21048831939697</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16111516952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26426887512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23947334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04804706573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04209518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24343919754028</t>
+    <t xml:space="preserve">7.16111660003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26426792144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23947238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04804611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04209566116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2434401512146</t>
   </si>
   <si>
     <t xml:space="preserve">7.23352146148682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20277500152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2483983039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17500257492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04407978057861</t>
+    <t xml:space="preserve">7.2027735710144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24839878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1750020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04407930374146</t>
   </si>
   <si>
     <t xml:space="preserve">6.97663354873657</t>
@@ -1724,34 +1724,34 @@
     <t xml:space="preserve">6.79909372329712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01729869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12243413925171</t>
+    <t xml:space="preserve">7.01729917526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12243461608887</t>
   </si>
   <si>
     <t xml:space="preserve">7.03713607788086</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95977258682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1859130859375</t>
+    <t xml:space="preserve">6.95977067947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18591260910034</t>
   </si>
   <si>
     <t xml:space="preserve">7.43486642837524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42693042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36146974563599</t>
+    <t xml:space="preserve">7.4269323348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36146879196167</t>
   </si>
   <si>
     <t xml:space="preserve">7.22062730789185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.268235206604</t>
+    <t xml:space="preserve">7.26823616027832</t>
   </si>
   <si>
     <t xml:space="preserve">7.39320802688599</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">7.16706705093384</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48247480392456</t>
+    <t xml:space="preserve">7.48247528076172</t>
   </si>
   <si>
     <t xml:space="preserve">7.40610218048096</t>
@@ -1775,16 +1775,16 @@
     <t xml:space="preserve">7.42792272567749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45767784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48346614837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61934995651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73341178894043</t>
+    <t xml:space="preserve">7.457679271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48346662521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61935043334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73341083526611</t>
   </si>
   <si>
     <t xml:space="preserve">7.66001462936401</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">7.70266437530518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66795015335083</t>
+    <t xml:space="preserve">7.66795063018799</t>
   </si>
   <si>
     <t xml:space="preserve">7.51024532318115</t>
@@ -1802,61 +1802,61 @@
     <t xml:space="preserve">7.68282651901245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69373798370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64017820358276</t>
+    <t xml:space="preserve">7.6937370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64017868041992</t>
   </si>
   <si>
     <t xml:space="preserve">7.57769107818604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52016305923462</t>
+    <t xml:space="preserve">7.52016448974609</t>
   </si>
   <si>
     <t xml:space="preserve">7.34460878372192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42197179794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01035737991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96274757385254</t>
+    <t xml:space="preserve">7.42197132110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01035642623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9627480506897</t>
   </si>
   <si>
     <t xml:space="preserve">6.92803382873535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94588708877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.177978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87744903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82587337493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66618680953979</t>
+    <t xml:space="preserve">6.94588613510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17797803878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87744855880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82587242126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66618585586548</t>
   </si>
   <si>
     <t xml:space="preserve">6.86455535888672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95183801651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78024911880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04705476760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81992149353027</t>
+    <t xml:space="preserve">6.95183753967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78024864196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04705429077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81992244720459</t>
   </si>
   <si>
     <t xml:space="preserve">6.67015361785889</t>
@@ -1865,31 +1865,31 @@
     <t xml:space="preserve">6.75247669219971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0292010307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11251497268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09664630889893</t>
+    <t xml:space="preserve">7.02920055389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11251592636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09664678573608</t>
   </si>
   <si>
     <t xml:space="preserve">7.26129341125488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28708076477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08672761917114</t>
+    <t xml:space="preserve">7.28708171844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0867280960083</t>
   </si>
   <si>
     <t xml:space="preserve">7.30394124984741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23054695129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13334560394287</t>
+    <t xml:space="preserve">7.23054552078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13334512710571</t>
   </si>
   <si>
     <t xml:space="preserve">7.1283860206604</t>
@@ -1898,13 +1898,13 @@
     <t xml:space="preserve">6.94291114807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0123405456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93001699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99052000045776</t>
+    <t xml:space="preserve">7.01233959197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93001747131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99051952362061</t>
   </si>
   <si>
     <t xml:space="preserve">7.33865594863892</t>
@@ -1913,10 +1913,10 @@
     <t xml:space="preserve">7.34758329391479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30493497848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49636030197144</t>
+    <t xml:space="preserve">7.30493354797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49635982513428</t>
   </si>
   <si>
     <t xml:space="preserve">7.34857559204102</t>
@@ -1925,109 +1925,109 @@
     <t xml:space="preserve">7.23451280593872</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86554718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82488203048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61064338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78322410583496</t>
+    <t xml:space="preserve">6.86554765701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82488107681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61064291000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78322505950928</t>
   </si>
   <si>
     <t xml:space="preserve">6.91613149642944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92208242416382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86852169036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82884883880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82289934158325</t>
+    <t xml:space="preserve">6.92208290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86852264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82884931564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82289743423462</t>
   </si>
   <si>
     <t xml:space="preserve">6.72272109985352</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50848388671875</t>
+    <t xml:space="preserve">6.50848293304443</t>
   </si>
   <si>
     <t xml:space="preserve">6.25754594802856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2892861366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23175859451294</t>
+    <t xml:space="preserve">6.28928470611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2317590713501</t>
   </si>
   <si>
     <t xml:space="preserve">6.15737009048462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50253248214722</t>
+    <t xml:space="preserve">6.5025315284729</t>
   </si>
   <si>
     <t xml:space="preserve">6.55113220214844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6284966468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87645769119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01134920120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16012477874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24443197250366</t>
+    <t xml:space="preserve">6.62849617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87645673751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01134777069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16012525558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24443292617798</t>
   </si>
   <si>
     <t xml:space="preserve">7.2107081413269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32080364227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10557270050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26724481582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1869044303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18987989425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28509712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39816761016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47354793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52710723876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6354398727417</t>
+    <t xml:space="preserve">7.32080316543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10557413101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2672438621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18690490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18988037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28509759902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3981671333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47354888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52710819244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63543939590454</t>
   </si>
   <si>
     <t xml:space="preserve">6.44302177429199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41822481155396</t>
+    <t xml:space="preserve">6.4182243347168</t>
   </si>
   <si>
     <t xml:space="preserve">6.39739608764648</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">6.49757289886475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40731477737427</t>
+    <t xml:space="preserve">6.40731430053711</t>
   </si>
   <si>
     <t xml:space="preserve">6.45988321304321</t>
@@ -2045,16 +2045,16 @@
     <t xml:space="preserve">6.44897222518921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45194816589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57692003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50153970718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51145839691162</t>
+    <t xml:space="preserve">6.4519476890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57692098617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50154066085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51145887374878</t>
   </si>
   <si>
     <t xml:space="preserve">6.54617309570312</t>
@@ -2063,103 +2063,103 @@
     <t xml:space="preserve">6.4559154510498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43806219100952</t>
+    <t xml:space="preserve">6.43806123733521</t>
   </si>
   <si>
     <t xml:space="preserve">6.41227436065674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36268281936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41525077819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64932537078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32697629928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36664962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35871362686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30416250228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25853872299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26548051834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32003259658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63643026351929</t>
+    <t xml:space="preserve">6.36268186569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41524982452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64932489395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32697534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36665010452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35871410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30416297912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2585391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26548147201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32003211975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63643074035645</t>
   </si>
   <si>
     <t xml:space="preserve">6.469801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49658060073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33590221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46385097503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49162149429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66122817993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52633666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58188009262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73958253860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80603647232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80901193618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81000328063965</t>
+    <t xml:space="preserve">6.49658155441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33590173721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4638500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49162244796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66122722625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52633714675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58187961578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73958301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80603551864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8090124130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81000423431396</t>
   </si>
   <si>
     <t xml:space="preserve">6.9389443397522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86157941818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89133548736572</t>
+    <t xml:space="preserve">6.86157894134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89133501052856</t>
   </si>
   <si>
     <t xml:space="preserve">6.89232730865479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04308748245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0936713218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607522964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29303216934204</t>
+    <t xml:space="preserve">7.04308700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09367179870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607570648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2930326461792</t>
   </si>
   <si>
     <t xml:space="preserve">7.28431081771851</t>
@@ -2171,67 +2171,67 @@
     <t xml:space="preserve">7.14384841918945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20939874649048</t>
+    <t xml:space="preserve">7.20939826965332</t>
   </si>
   <si>
     <t xml:space="preserve">7.19170999526978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14488935470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04916667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11263513565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07205677032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80673789978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73806619644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61112976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71309566497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81402015686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88997411727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95448350906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93350076675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88365411758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82684946060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62166261672974</t>
+    <t xml:space="preserve">7.14488983154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04916524887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3737907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11263418197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07205486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80673742294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73806667327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61112880706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71309518814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81401968002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88997364044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95448303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93350172042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88365364074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82684993743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62166213989258</t>
   </si>
   <si>
     <t xml:space="preserve">6.64021015167236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16999006271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10623121261597</t>
+    <t xml:space="preserve">7.16999053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10623073577881</t>
   </si>
   <si>
     <t xml:space="preserve">7.01928663253784</t>
@@ -2243,28 +2243,28 @@
     <t xml:space="preserve">6.62977695465088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59267997741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84771633148193</t>
+    <t xml:space="preserve">6.59268093109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84771728515625</t>
   </si>
   <si>
     <t xml:space="preserve">6.78163909912109</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78743505477905</t>
+    <t xml:space="preserve">6.78743553161621</t>
   </si>
   <si>
     <t xml:space="preserve">6.7642502784729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88133478164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94625282287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83728265762329</t>
+    <t xml:space="preserve">6.88133573532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94625425338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83728361129761</t>
   </si>
   <si>
     <t xml:space="preserve">6.89524555206299</t>
@@ -2273,16 +2273,16 @@
     <t xml:space="preserve">6.86278676986694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92422723770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98566865921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06449699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15028142929077</t>
+    <t xml:space="preserve">6.92422771453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98566818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06449794769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15028190612793</t>
   </si>
   <si>
     <t xml:space="preserve">7.13521194458008</t>
@@ -2291,67 +2291,67 @@
     <t xml:space="preserve">7.14216756820679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02160501480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03319692611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08072710037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10970783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15723752975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13057518005371</t>
+    <t xml:space="preserve">7.02160453796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03319835662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08072519302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10970735549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1572380065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13057470321655</t>
   </si>
   <si>
     <t xml:space="preserve">7.33112621307373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35315227508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32533025741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28939342498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20940446853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20476627349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28707408905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28591537475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0598611831665</t>
+    <t xml:space="preserve">7.35315179824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32532930374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28939294815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20940399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20476722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28707456588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28591442108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05986070632935</t>
   </si>
   <si>
     <t xml:space="preserve">7.07493019104004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95900583267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17578506469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31141805648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19433403015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08768177032471</t>
+    <t xml:space="preserve">6.95900440216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17578649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31141757965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19433450698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08768320083618</t>
   </si>
   <si>
     <t xml:space="preserve">6.976393699646</t>
@@ -2360,43 +2360,43 @@
     <t xml:space="preserve">6.99841976165771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76541042327881</t>
+    <t xml:space="preserve">6.76541090011597</t>
   </si>
   <si>
     <t xml:space="preserve">6.81873559951782</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86858320236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72715425491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7236762046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82569074630737</t>
+    <t xml:space="preserve">6.8685827255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72715377807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72367572784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82569169998169</t>
   </si>
   <si>
     <t xml:space="preserve">6.58572483062744</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40719890594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52660274505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46632194519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68194389343262</t>
+    <t xml:space="preserve">6.40719985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52660226821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46632289886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68194484710693</t>
   </si>
   <si>
     <t xml:space="preserve">6.6900577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54515171051025</t>
+    <t xml:space="preserve">6.54515075683594</t>
   </si>
   <si>
     <t xml:space="preserve">6.63557291030884</t>
@@ -2405,31 +2405,31 @@
     <t xml:space="preserve">6.74454307556152</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80482339859009</t>
+    <t xml:space="preserve">6.8048243522644</t>
   </si>
   <si>
     <t xml:space="preserve">6.86162757873535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86394691467285</t>
+    <t xml:space="preserve">6.86394596099854</t>
   </si>
   <si>
     <t xml:space="preserve">7.08304595947266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29055309295654</t>
+    <t xml:space="preserve">7.29055213928223</t>
   </si>
   <si>
     <t xml:space="preserve">7.30562162399292</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37285900115967</t>
+    <t xml:space="preserve">7.37285947799683</t>
   </si>
   <si>
     <t xml:space="preserve">7.28243637084961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28127765655518</t>
+    <t xml:space="preserve">7.28127813339233</t>
   </si>
   <si>
     <t xml:space="preserve">7.29287052154541</t>
@@ -2438,43 +2438,43 @@
     <t xml:space="preserve">7.1815824508667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18737888336182</t>
+    <t xml:space="preserve">7.18737745285034</t>
   </si>
   <si>
     <t xml:space="preserve">7.07029294967651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92654657363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83148622512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84539890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87785673141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525754928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63093614578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54051351547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53239917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57529211044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50921440124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54862833023071</t>
+    <t xml:space="preserve">6.92654752731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83148813247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84539699554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87785768508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525707244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63093566894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54051399230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53239870071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5752911567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50921487808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54862928390503</t>
   </si>
   <si>
     <t xml:space="preserve">6.73410892486572</t>
@@ -2483,16 +2483,16 @@
     <t xml:space="preserve">6.87553834915161</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9184308052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07145309448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03899383544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87206172943115</t>
+    <t xml:space="preserve">6.91843128204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07145214080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03899431228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87206077575684</t>
   </si>
   <si>
     <t xml:space="preserve">6.95668697357178</t>
@@ -2501,19 +2501,19 @@
     <t xml:space="preserve">6.90915679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87321996688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86742353439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90336179733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81061983108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45980262756348</t>
+    <t xml:space="preserve">6.87322092056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86742448806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90336084365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81062078475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45980310440063</t>
   </si>
   <si>
     <t xml:space="preserve">8.07304954528809</t>
@@ -2525,10 +2525,10 @@
     <t xml:space="preserve">8.32808494567871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37561416625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38025093078613</t>
+    <t xml:space="preserve">8.37561511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38025188446045</t>
   </si>
   <si>
     <t xml:space="preserve">8.40691471099854</t>
@@ -2537,22 +2537,22 @@
     <t xml:space="preserve">8.48226547241211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41039085388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51124477386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41386890411377</t>
+    <t xml:space="preserve">8.41039276123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5112476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41386985778809</t>
   </si>
   <si>
     <t xml:space="preserve">8.40807342529297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42198467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18433856964111</t>
+    <t xml:space="preserve">8.42198371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1843376159668</t>
   </si>
   <si>
     <t xml:space="preserve">8.19245147705078</t>
@@ -2561,55 +2561,55 @@
     <t xml:space="preserve">8.09623432159424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79019069671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74613857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88177299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87713384628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89104557037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82033252716064</t>
+    <t xml:space="preserve">7.79019165039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74613952636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88177251815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87713575363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89104604721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82033157348633</t>
   </si>
   <si>
     <t xml:space="preserve">7.77859878540039</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70440530776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65223979949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74845743179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68238067626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68701648712158</t>
+    <t xml:space="preserve">7.70440626144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65223932266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74845790863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68238019943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68701696395874</t>
   </si>
   <si>
     <t xml:space="preserve">7.62093925476074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57920598983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46328067779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64760303497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72411441802979</t>
+    <t xml:space="preserve">7.57920503616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46328115463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64760255813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72411394119263</t>
   </si>
   <si>
     <t xml:space="preserve">7.80757999420166</t>
@@ -2618,55 +2618,55 @@
     <t xml:space="preserve">7.88524913787842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8840913772583</t>
+    <t xml:space="preserve">7.88409090042114</t>
   </si>
   <si>
     <t xml:space="preserve">7.91191244125366</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82844591140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78439426422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74150228500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58036470413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47719097137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51196908950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41691017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43777751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43661832809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39024639129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3682222366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2291111946106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21867704391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2059268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22099685668945</t>
+    <t xml:space="preserve">7.82844734191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78439474105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74150276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5803656578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47719144821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51197004318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41691112518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4377760887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43661785125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39024782180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36822271347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22911214828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21867799758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20592594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22099733352661</t>
   </si>
   <si>
     <t xml:space="preserve">7.14680433273315</t>
@@ -2675,91 +2675,91 @@
     <t xml:space="preserve">6.98219013214111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03783464431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96364212036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03087949752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9126353263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80018758773804</t>
+    <t xml:space="preserve">7.03783512115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96364116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03087854385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91263628005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8001880645752</t>
   </si>
   <si>
     <t xml:space="preserve">6.85235404968262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19317579269409</t>
+    <t xml:space="preserve">7.19317531585693</t>
   </si>
   <si>
     <t xml:space="preserve">7.07609033584595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03203821182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29403018951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10738945007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14100885391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11086797714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11550521850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00189828872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57297277450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52544355392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70165061950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51617002487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27620315551758</t>
+    <t xml:space="preserve">7.03203868865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29403066635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10739040374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1410083770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11086750030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11550426483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00189781188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57297325134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52544450759888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70165109634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51616954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27620410919189</t>
   </si>
   <si>
     <t xml:space="preserve">6.3411226272583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37126302719116</t>
+    <t xml:space="preserve">6.37126350402832</t>
   </si>
   <si>
     <t xml:space="preserve">6.2843189239502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09651899337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.438063621521</t>
+    <t xml:space="preserve">6.09651947021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43806314468384</t>
   </si>
   <si>
     <t xml:space="preserve">5.40676307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51921081542969</t>
+    <t xml:space="preserve">5.51921033859253</t>
   </si>
   <si>
     <t xml:space="preserve">4.53326463699341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85785579681396</t>
+    <t xml:space="preserve">4.85785627365112</t>
   </si>
   <si>
     <t xml:space="preserve">4.15534782409668</t>
@@ -2768,13 +2768,13 @@
     <t xml:space="preserve">3.97914123535156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54731917381287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36531591415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56122994422913</t>
+    <t xml:space="preserve">3.54731869697571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36531615257263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56123018264771</t>
   </si>
   <si>
     <t xml:space="preserve">3.40994715690613</t>
@@ -2783,58 +2783,58 @@
     <t xml:space="preserve">3.84872460365295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96117305755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99421119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75482511520386</t>
+    <t xml:space="preserve">3.96117329597473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99421191215515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75482583045959</t>
   </si>
   <si>
     <t xml:space="preserve">3.65744805335999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80930972099304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66498327255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64295768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368944168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83481431007385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08289432525635</t>
+    <t xml:space="preserve">3.80930995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66498351097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64295721054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368872642517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83481335639954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08289480209351</t>
   </si>
   <si>
     <t xml:space="preserve">4.12636661529541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33503198623657</t>
+    <t xml:space="preserve">4.33503246307373</t>
   </si>
   <si>
     <t xml:space="preserve">4.32401990890503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10434055328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12057065963745</t>
+    <t xml:space="preserve">4.10434103012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12056970596313</t>
   </si>
   <si>
     <t xml:space="preserve">4.24403142929077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30663061141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11419343948364</t>
+    <t xml:space="preserve">4.30663013458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11419486999512</t>
   </si>
   <si>
     <t xml:space="preserve">4.20229721069336</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">4.46197080612183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57383871078491</t>
+    <t xml:space="preserve">4.57383823394775</t>
   </si>
   <si>
     <t xml:space="preserve">4.74135160446167</t>
@@ -2858,10 +2858,10 @@
     <t xml:space="preserve">4.64629173278809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38430070877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44863939285278</t>
+    <t xml:space="preserve">4.38430118560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4486403465271</t>
   </si>
   <si>
     <t xml:space="preserve">4.42139673233032</t>
@@ -2870,28 +2870,28 @@
     <t xml:space="preserve">4.40516757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50370407104492</t>
+    <t xml:space="preserve">4.50370359420776</t>
   </si>
   <si>
     <t xml:space="preserve">4.42429494857788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40053033828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27475070953369</t>
+    <t xml:space="preserve">4.40052938461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27475118637085</t>
   </si>
   <si>
     <t xml:space="preserve">4.15476846694946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17505550384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51703643798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31242752075195</t>
+    <t xml:space="preserve">4.17505502700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51703596115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31242704391479</t>
   </si>
   <si>
     <t xml:space="preserve">4.25388431549072</t>
@@ -2906,46 +2906,46 @@
     <t xml:space="preserve">4.72859954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78192567825317</t>
+    <t xml:space="preserve">4.78192520141602</t>
   </si>
   <si>
     <t xml:space="preserve">4.60339975357056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76511573791504</t>
+    <t xml:space="preserve">4.76511526107788</t>
   </si>
   <si>
     <t xml:space="preserve">4.83293151855469</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08217191696167</t>
+    <t xml:space="preserve">5.08217239379883</t>
   </si>
   <si>
     <t xml:space="preserve">5.04449605941772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39748907089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45255374908447</t>
+    <t xml:space="preserve">5.39748954772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45255327224731</t>
   </si>
   <si>
     <t xml:space="preserve">5.21316814422607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0723180770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68164920806885</t>
+    <t xml:space="preserve">5.07231855392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68164968490601</t>
   </si>
   <si>
     <t xml:space="preserve">4.74888610839844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75062465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88625764846802</t>
+    <t xml:space="preserve">4.7506251335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88625860214233</t>
   </si>
   <si>
     <t xml:space="preserve">4.86771011352539</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">4.89958906173706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96624612808228</t>
+    <t xml:space="preserve">4.96624660491943</t>
   </si>
   <si>
     <t xml:space="preserve">5.25374221801758</t>
@@ -2966,43 +2966,43 @@
     <t xml:space="preserve">5.02247047424316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09550285339355</t>
+    <t xml:space="preserve">5.09550333023071</t>
   </si>
   <si>
     <t xml:space="preserve">5.00508165359497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11695003509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18418598175049</t>
+    <t xml:space="preserve">5.11694955825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1841869354248</t>
   </si>
   <si>
     <t xml:space="preserve">5.09260559082031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21606540679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15868234634399</t>
+    <t xml:space="preserve">5.21606588363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15868186950684</t>
   </si>
   <si>
     <t xml:space="preserve">5.21896457672119</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2067928314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09840154647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00276279449463</t>
+    <t xml:space="preserve">5.20679235458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09840202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00276327133179</t>
   </si>
   <si>
     <t xml:space="preserve">5.11984825134277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24910449981689</t>
+    <t xml:space="preserve">5.24910497665405</t>
   </si>
   <si>
     <t xml:space="preserve">5.20447301864624</t>
@@ -3011,73 +3011,73 @@
     <t xml:space="preserve">5.2572193145752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31692123413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31054496765137</t>
+    <t xml:space="preserve">5.3169207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31054544448853</t>
   </si>
   <si>
     <t xml:space="preserve">5.34184455871582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35401678085327</t>
+    <t xml:space="preserve">5.35401725769043</t>
   </si>
   <si>
     <t xml:space="preserve">5.30822658538818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3412652015686</t>
+    <t xml:space="preserve">5.34126567840576</t>
   </si>
   <si>
     <t xml:space="preserve">5.26069736480713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25895833969116</t>
+    <t xml:space="preserve">5.25895881652832</t>
   </si>
   <si>
     <t xml:space="preserve">5.37488412857056</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30764675140381</t>
+    <t xml:space="preserve">5.30764770507812</t>
   </si>
   <si>
     <t xml:space="preserve">4.99638652801514</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23693180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44270038604736</t>
+    <t xml:space="preserve">5.23693227767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44270086288452</t>
   </si>
   <si>
     <t xml:space="preserve">5.44733715057373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38937425613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38183975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47457981109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76323366165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74178791046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65716171264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61658811569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59340333938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56847953796387</t>
+    <t xml:space="preserve">5.38937473297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38183927536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47458028793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76323318481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74178886413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65716218948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61658763885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59340381622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56847906112671</t>
   </si>
   <si>
     <t xml:space="preserve">5.58065176010132</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">5.47631883621216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40618324279785</t>
+    <t xml:space="preserve">5.40618371963501</t>
   </si>
   <si>
     <t xml:space="preserve">5.5800724029541</t>
@@ -3095,28 +3095,28 @@
     <t xml:space="preserve">5.51631259918213</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54703330993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47747802734375</t>
+    <t xml:space="preserve">5.54703283309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47747850418091</t>
   </si>
   <si>
     <t xml:space="preserve">5.457190990448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35053968429565</t>
+    <t xml:space="preserve">5.35054016113281</t>
   </si>
   <si>
     <t xml:space="preserve">5.28735971450806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31750011444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37836170196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46646451950073</t>
+    <t xml:space="preserve">5.31750059127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37836122512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46646404266357</t>
   </si>
   <si>
     <t xml:space="preserve">5.58470869064331</t>
@@ -3125,49 +3125,49 @@
     <t xml:space="preserve">5.57079792022705</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57137680053711</t>
+    <t xml:space="preserve">5.57137632369995</t>
   </si>
   <si>
     <t xml:space="preserve">5.73019552230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74642419815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78641939163208</t>
+    <t xml:space="preserve">5.74642515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641891479492</t>
   </si>
   <si>
     <t xml:space="preserve">6.30750417709351</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26693058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23910808563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01537132263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75975656509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92263078689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0223274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01189470291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92958736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16491508483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02116775512695</t>
+    <t xml:space="preserve">6.26692962646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23910903930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01537227630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75975561141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92263174057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02232789993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01189422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92958688735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16491460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02116870880127</t>
   </si>
   <si>
     <t xml:space="preserve">6.06753826141357</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">5.99914216995239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07681274414062</t>
+    <t xml:space="preserve">6.07681226730347</t>
   </si>
   <si>
     <t xml:space="preserve">6.18578290939331</t>
@@ -3185,22 +3185,22 @@
     <t xml:space="preserve">6.20317077636719</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19041967391968</t>
+    <t xml:space="preserve">6.19041919708252</t>
   </si>
   <si>
     <t xml:space="preserve">6.10463523864746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16375684738159</t>
+    <t xml:space="preserve">6.16375637054443</t>
   </si>
   <si>
     <t xml:space="preserve">6.06058263778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12666034698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99566459655762</t>
+    <t xml:space="preserve">6.12666082382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99566555023193</t>
   </si>
   <si>
     <t xml:space="preserve">6.24954128265381</t>
@@ -3209,10 +3209,10 @@
     <t xml:space="preserve">6.22867488861084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24722290039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20548915863037</t>
+    <t xml:space="preserve">6.24722242355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20548963546753</t>
   </si>
   <si>
     <t xml:space="preserve">6.3573522567749</t>
@@ -3221,16 +3221,16 @@
     <t xml:space="preserve">6.43386268615723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48023319244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37242317199707</t>
+    <t xml:space="preserve">6.48023414611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37242269515991</t>
   </si>
   <si>
     <t xml:space="preserve">6.12550115585327</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12318277359009</t>
+    <t xml:space="preserve">6.12318325042725</t>
   </si>
   <si>
     <t xml:space="preserve">6.11043119430542</t>
@@ -3242,73 +3242,73 @@
     <t xml:space="preserve">6.3793773651123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47443771362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51269292831421</t>
+    <t xml:space="preserve">6.47443675994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51269149780273</t>
   </si>
   <si>
     <t xml:space="preserve">6.91031694412231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99146509170532</t>
+    <t xml:space="preserve">6.99146413803101</t>
   </si>
   <si>
     <t xml:space="preserve">7.07840871810913</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29750680923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3183741569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34851598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50037717819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46559953689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705104827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58964014053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64180660247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58616161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66615152359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57341051101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66730976104736</t>
+    <t xml:space="preserve">7.29750776290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31837463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34851503372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50037813186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46560049057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705057144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58963918685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64180707931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58616256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66615104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57341003417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66730928421021</t>
   </si>
   <si>
     <t xml:space="preserve">7.63948774337769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66846895217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85395050048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80294370651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77048349380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98494482040405</t>
+    <t xml:space="preserve">7.6684684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85395002365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80294322967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77048206329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98494529724121</t>
   </si>
   <si>
     <t xml:space="preserve">8.01624488830566</t>
@@ -3317,46 +3317,46 @@
     <t xml:space="preserve">7.90611600875854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01045036315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18781566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29678440093994</t>
+    <t xml:space="preserve">8.01044845581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1878137588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29678535461426</t>
   </si>
   <si>
     <t xml:space="preserve">8.34895133972168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42082595825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.259690284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46140003204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51588439941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57036876678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51356506347656</t>
+    <t xml:space="preserve">8.42082691192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25968837738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46139907836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51588535308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57036972045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51356601715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.49733543395996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62485504150391</t>
+    <t xml:space="preserve">8.62485408782959</t>
   </si>
   <si>
     <t xml:space="preserve">8.60166931152344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57152938842773</t>
+    <t xml:space="preserve">8.57152843475342</t>
   </si>
   <si>
     <t xml:space="preserve">8.41271018981934</t>
@@ -3365,28 +3365,28 @@
     <t xml:space="preserve">8.33504009246826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50545024871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46951484680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78281021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40054035186768</t>
+    <t xml:space="preserve">8.50545120239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46951389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78281116485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40054130554199</t>
   </si>
   <si>
     <t xml:space="preserve">9.27200603485107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32146167755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11963367462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84830379486084</t>
+    <t xml:space="preserve">9.32146072387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11963272094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84830284118652</t>
   </si>
   <si>
     <t xml:space="preserve">8.43662929534912</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">8.60236835479736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30564403533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49944972991943</t>
+    <t xml:space="preserve">8.30564308166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49945163726807</t>
   </si>
   <si>
     <t xml:space="preserve">8.37380981445312</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">8.681227684021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69726943969727</t>
+    <t xml:space="preserve">8.69726753234863</t>
   </si>
   <si>
     <t xml:space="preserve">8.76142501831055</t>
@@ -3422,16 +3422,16 @@
     <t xml:space="preserve">9.08889198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01805114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84295845031738</t>
+    <t xml:space="preserve">9.01805305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84295654296875</t>
   </si>
   <si>
     <t xml:space="preserve">8.79483985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86567974090576</t>
+    <t xml:space="preserve">8.86567878723145</t>
   </si>
   <si>
     <t xml:space="preserve">8.95790481567383</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">9.02206134796143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82825565338135</t>
+    <t xml:space="preserve">8.82825469970703</t>
   </si>
   <si>
     <t xml:space="preserve">8.87770938873291</t>
@@ -3449,22 +3449,22 @@
     <t xml:space="preserve">8.94186592102051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82424640655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86969089508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07552623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06082248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97795391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30542278289795</t>
+    <t xml:space="preserve">8.82424449920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86968994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07552528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06082344055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97795486450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30542087554932</t>
   </si>
   <si>
     <t xml:space="preserve">9.28537178039551</t>
@@ -3479,16 +3479,16 @@
     <t xml:space="preserve">9.14369201660156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67966938018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85610103607178</t>
+    <t xml:space="preserve">9.67967128753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85610198974609</t>
   </si>
   <si>
     <t xml:space="preserve">10.0579280853271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1755495071411</t>
+    <t xml:space="preserve">10.1755485534668</t>
   </si>
   <si>
     <t xml:space="preserve">10.3158922195435</t>
@@ -3497,22 +3497,22 @@
     <t xml:space="preserve">10.602707862854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5399122238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6655044555664</t>
+    <t xml:space="preserve">10.5399112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6655054092407</t>
   </si>
   <si>
     <t xml:space="preserve">10.9837713241577</t>
   </si>
   <si>
-    <t xml:space="preserve">10.596999168396</t>
+    <t xml:space="preserve">10.5970001220703</t>
   </si>
   <si>
     <t xml:space="preserve">10.4785413742065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1288757324219</t>
+    <t xml:space="preserve">10.1288766860962</t>
   </si>
   <si>
     <t xml:space="preserve">10.1374387741089</t>
@@ -3524,49 +3524,49 @@
     <t xml:space="preserve">10.4457149505615</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4628410339355</t>
+    <t xml:space="preserve">10.4628419876099</t>
   </si>
   <si>
     <t xml:space="preserve">10.7754001617432</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7639818191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8010902404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.912410736084</t>
+    <t xml:space="preserve">10.7639827728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8010892868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9124116897583</t>
   </si>
   <si>
     <t xml:space="preserve">10.9109840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">10.652660369873</t>
+    <t xml:space="preserve">10.6526613235474</t>
   </si>
   <si>
     <t xml:space="preserve">10.5613193511963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6597967147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8082246780396</t>
+    <t xml:space="preserve">10.6597957611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8082256317139</t>
   </si>
   <si>
     <t xml:space="preserve">10.7397193908691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7340106964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8910026550293</t>
+    <t xml:space="preserve">10.7340116500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8910036087036</t>
   </si>
   <si>
     <t xml:space="preserve">10.7816705703735</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3457975387573</t>
+    <t xml:space="preserve">10.3457984924316</t>
   </si>
   <si>
     <t xml:space="preserve">10.4551305770874</t>
@@ -3575,40 +3575,40 @@
     <t xml:space="preserve">10.481369972229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4886589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4667911529541</t>
+    <t xml:space="preserve">10.4886598587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4667921066284</t>
   </si>
   <si>
     <t xml:space="preserve">10.4288902282715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4901170730591</t>
+    <t xml:space="preserve">10.4901161193848</t>
   </si>
   <si>
     <t xml:space="preserve">10.09068775177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0761098861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2204303741455</t>
+    <t xml:space="preserve">10.0761089324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2204294204712</t>
   </si>
   <si>
     <t xml:space="preserve">10.1227579116821</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8312349319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8705940246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8910036087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0061674118042</t>
+    <t xml:space="preserve">10.8312339782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8705949783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8910045623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0061683654785</t>
   </si>
   <si>
     <t xml:space="preserve">10.686915397644</t>
@@ -3617,46 +3617,46 @@
     <t xml:space="preserve">10.7306489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6781692504883</t>
+    <t xml:space="preserve">10.678168296814</t>
   </si>
   <si>
     <t xml:space="preserve">10.8283195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0047101974487</t>
+    <t xml:space="preserve">11.0047092437744</t>
   </si>
   <si>
     <t xml:space="preserve">11.0003366470337</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7364807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9376516342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1636066436768</t>
+    <t xml:space="preserve">10.7364797592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9376525878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1636056900024</t>
   </si>
   <si>
     <t xml:space="preserve">11.2160863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2787714004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2583618164062</t>
+    <t xml:space="preserve">11.2787704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2583608627319</t>
   </si>
   <si>
     <t xml:space="preserve">11.7190160751343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739426612854</t>
+    <t xml:space="preserve">11.7394275665283</t>
   </si>
   <si>
     <t xml:space="preserve">11.8502159118652</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9143590927124</t>
+    <t xml:space="preserve">11.9143600463867</t>
   </si>
   <si>
     <t xml:space="preserve">12.0338954925537</t>
@@ -3665,13 +3665,13 @@
     <t xml:space="preserve">12.1709260940552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5120449066162</t>
+    <t xml:space="preserve">12.5120439529419</t>
   </si>
   <si>
     <t xml:space="preserve">12.7219638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7379989624023</t>
+    <t xml:space="preserve">12.737998008728</t>
   </si>
   <si>
     <t xml:space="preserve">12.5601511001587</t>
@@ -3680,10 +3680,10 @@
     <t xml:space="preserve">12.3910493850708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5003824234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3677253723145</t>
+    <t xml:space="preserve">12.5003814697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677244186401</t>
   </si>
   <si>
     <t xml:space="preserve">12.3167028427124</t>
@@ -3695,25 +3695,25 @@
     <t xml:space="preserve">12.3604364395142</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0003671646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4056282043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3808441162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3560628890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3852195739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4362411499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2758846282959</t>
+    <t xml:space="preserve">12.0003681182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4056272506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3808450698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3560619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3852186203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.436240196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2758855819702</t>
   </si>
   <si>
     <t xml:space="preserve">12.2613077163696</t>
@@ -3722,25 +3722,25 @@
     <t xml:space="preserve">12.0659675598145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1738405227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3414850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1942491531372</t>
+    <t xml:space="preserve">12.1738414764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3414840698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1942510604858</t>
   </si>
   <si>
     <t xml:space="preserve">12.0936641693115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6884031295776</t>
+    <t xml:space="preserve">11.688404083252</t>
   </si>
   <si>
     <t xml:space="preserve">12.0164022445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429279327393</t>
+    <t xml:space="preserve">11.8429269790649</t>
   </si>
   <si>
     <t xml:space="preserve">11.8370962142944</t>
@@ -3749,22 +3749,22 @@
     <t xml:space="preserve">11.6679944992065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4332933425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0222024917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0499000549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4289216995239</t>
+    <t xml:space="preserve">11.4332942962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0222034454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.049901008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4289207458496</t>
   </si>
   <si>
     <t xml:space="preserve">11.3633213043213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4813995361328</t>
+    <t xml:space="preserve">11.4814004898071</t>
   </si>
   <si>
     <t xml:space="preserve">11.5790710449219</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">11.9201898574829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8006525039673</t>
+    <t xml:space="preserve">11.8006534576416</t>
   </si>
   <si>
     <t xml:space="preserve">11.9318523406982</t>
@@ -3794,46 +3794,46 @@
     <t xml:space="preserve">13.0280961990356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1170196533203</t>
+    <t xml:space="preserve">13.1170206069946</t>
   </si>
   <si>
     <t xml:space="preserve">13.0834913253784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1330537796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4829168319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5645551681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3692140579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0062294006348</t>
+    <t xml:space="preserve">13.1330547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4829196929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5645561218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.369213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0062284469604</t>
   </si>
   <si>
     <t xml:space="preserve">13.105357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6388702392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4930934906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5412006378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5732707977295</t>
+    <t xml:space="preserve">12.6388711929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4930925369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5411987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5732698440552</t>
   </si>
   <si>
     <t xml:space="preserve">12.6024265289307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4858045578003</t>
+    <t xml:space="preserve">12.485803604126</t>
   </si>
   <si>
     <t xml:space="preserve">12.5105857849121</t>
@@ -3845,13 +3845,13 @@
     <t xml:space="preserve">12.2744283676147</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4814319610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.567440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4537343978882</t>
+    <t xml:space="preserve">12.4814310073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5674390792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4537334442139</t>
   </si>
   <si>
     <t xml:space="preserve">12.0980377197266</t>
@@ -3860,13 +3860,13 @@
     <t xml:space="preserve">12.1636371612549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1752996444702</t>
+    <t xml:space="preserve">12.1752986907959</t>
   </si>
   <si>
     <t xml:space="preserve">12.2656803131104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6898918151855</t>
+    <t xml:space="preserve">12.6898927688599</t>
   </si>
   <si>
     <t xml:space="preserve">12.2525615692139</t>
@@ -3878,40 +3878,40 @@
     <t xml:space="preserve">11.6854877471924</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0645084381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2219476699829</t>
+    <t xml:space="preserve">12.0645093917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2219486236572</t>
   </si>
   <si>
     <t xml:space="preserve">12.2365255355835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3444013595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9770412445068</t>
+    <t xml:space="preserve">12.3444004058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9770421981812</t>
   </si>
   <si>
     <t xml:space="preserve">12.1432285308838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0426416397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8575048446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7627506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0674247741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6373815536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0790863037109</t>
+    <t xml:space="preserve">12.0426425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8575057983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7627515792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0674238204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6373825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0790872573853</t>
   </si>
   <si>
     <t xml:space="preserve">12.1534328460693</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">12.2860898971558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2671394348145</t>
+    <t xml:space="preserve">12.2671384811401</t>
   </si>
   <si>
     <t xml:space="preserve">12.4114580154419</t>
@@ -3932,22 +3932,22 @@
     <t xml:space="preserve">12.3123292922974</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2292375564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2598505020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2846326828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.281717300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.765697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8079719543457</t>
+    <t xml:space="preserve">12.2292366027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2598485946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.284631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2817163467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7656955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.80797290802</t>
   </si>
   <si>
     <t xml:space="preserve">12.7992248535156</t>
@@ -3962,61 +3962,61 @@
     <t xml:space="preserve">12.7321672439575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7904777526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.857536315918</t>
+    <t xml:space="preserve">12.7904787063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8575353622437</t>
   </si>
   <si>
     <t xml:space="preserve">12.9143896102905</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7817325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7117605209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0339260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368413925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0295534133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1855344772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0878648757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0936946868896</t>
+    <t xml:space="preserve">12.7817316055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7117595672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0339269638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368423461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0295524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1855354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0878639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.093695640564</t>
   </si>
   <si>
     <t xml:space="preserve">12.7248802185059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3983392715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2511034011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1782159805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3458271026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3472862243652</t>
+    <t xml:space="preserve">12.3983383178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2511043548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1782150268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3458280563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3472852706909</t>
   </si>
   <si>
     <t xml:space="preserve">11.0353231430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6621646881104</t>
+    <t xml:space="preserve">11.662163734436</t>
   </si>
   <si>
     <t xml:space="preserve">11.6096849441528</t>
@@ -4025,13 +4025,13 @@
     <t xml:space="preserve">11.4755697250366</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8749980926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2977514266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1592626571655</t>
+    <t xml:space="preserve">11.8749990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2977523803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1592636108398</t>
   </si>
   <si>
     <t xml:space="preserve">11.9887046813965</t>
@@ -4058,16 +4058,16 @@
     <t xml:space="preserve">11.886661529541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9916210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2685966491699</t>
+    <t xml:space="preserve">11.9916200637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2685976028442</t>
   </si>
   <si>
     <t xml:space="preserve">12.1621799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301231384277</t>
+    <t xml:space="preserve">12.6301221847534</t>
   </si>
   <si>
     <t xml:space="preserve">12.9114742279053</t>
@@ -4076,34 +4076,34 @@
     <t xml:space="preserve">13.4318971633911</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2992401123047</t>
+    <t xml:space="preserve">13.299241065979</t>
   </si>
   <si>
     <t xml:space="preserve">13.1213932037354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.020806312561</t>
+    <t xml:space="preserve">13.0208072662354</t>
   </si>
   <si>
     <t xml:space="preserve">13.1490907669067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3969106674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8561096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.829870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9508638381958</t>
+    <t xml:space="preserve">13.3969116210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.856107711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8298692703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9508628845215</t>
   </si>
   <si>
     <t xml:space="preserve">13.9173345565796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.84153175354</t>
+    <t xml:space="preserve">13.8415307998657</t>
   </si>
   <si>
     <t xml:space="preserve">13.6986703872681</t>
@@ -4112,10 +4112,10 @@
     <t xml:space="preserve">13.2132329940796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1009531021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6855182647705</t>
+    <t xml:space="preserve">12.1009521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6855192184448</t>
   </si>
   <si>
     <t xml:space="preserve">12.7861061096191</t>
@@ -4124,13 +4124,13 @@
     <t xml:space="preserve">12.4406147003174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3691825866699</t>
+    <t xml:space="preserve">12.3691816329956</t>
   </si>
   <si>
     <t xml:space="preserve">12.6417856216431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6636533737183</t>
+    <t xml:space="preserve">12.6636524200439</t>
   </si>
   <si>
     <t xml:space="preserve">11.9989099502563</t>
@@ -4145,13 +4145,13 @@
     <t xml:space="preserve">12.4683122634888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3618936538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2234058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9099864959717</t>
+    <t xml:space="preserve">12.3618927001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.223406791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9099855422974</t>
   </si>
   <si>
     <t xml:space="preserve">12.3997945785522</t>
@@ -4160,40 +4160,40 @@
     <t xml:space="preserve">12.5149602890015</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665515899658</t>
+    <t xml:space="preserve">12.1665534973145</t>
   </si>
   <si>
     <t xml:space="preserve">11.8837461471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4391565322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869459152222</t>
+    <t xml:space="preserve">12.4391555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869468688965</t>
   </si>
   <si>
     <t xml:space="preserve">12.3064994812012</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1052951812744</t>
+    <t xml:space="preserve">11.1052961349487</t>
   </si>
   <si>
     <t xml:space="preserve">11.2190017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9041233062744</t>
+    <t xml:space="preserve">10.9041242599487</t>
   </si>
   <si>
     <t xml:space="preserve">10.0746517181396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43031787872314</t>
+    <t xml:space="preserve">9.43031692504883</t>
   </si>
   <si>
     <t xml:space="preserve">9.42594337463379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5834150314331</t>
+    <t xml:space="preserve">10.5834140777588</t>
   </si>
   <si>
     <t xml:space="preserve">9.81808471679688</t>
@@ -4202,10 +4202,10 @@
     <t xml:space="preserve">9.8370361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2043933868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3180990219116</t>
+    <t xml:space="preserve">10.2043943405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3180999755859</t>
   </si>
   <si>
     <t xml:space="preserve">10.9770126342773</t>
@@ -4217,10 +4217,10 @@
     <t xml:space="preserve">10.6883735656738</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6475553512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8035373687744</t>
+    <t xml:space="preserve">10.6475563049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8035364151001</t>
   </si>
   <si>
     <t xml:space="preserve">10.6373510360718</t>
@@ -4229,31 +4229,31 @@
     <t xml:space="preserve">10.5046939849854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5207300186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5323925018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2321224212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.054274559021</t>
+    <t xml:space="preserve">10.5207290649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5323915481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2321214675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0542736053467</t>
   </si>
   <si>
     <t xml:space="preserve">10.7875022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7802133560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8516426086426</t>
+    <t xml:space="preserve">10.7802124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8516445159912</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522151947021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98718643188477</t>
+    <t xml:space="preserve">9.98718547821045</t>
   </si>
   <si>
     <t xml:space="preserve">9.86910629272461</t>
@@ -4262,25 +4262,25 @@
     <t xml:space="preserve">10.0338354110718</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475400924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1358795166016</t>
+    <t xml:space="preserve">10.1475410461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1358785629272</t>
   </si>
   <si>
     <t xml:space="preserve">10.1854419708252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2583322525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5054616928101</t>
+    <t xml:space="preserve">10.2583312988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5054626464844</t>
   </si>
   <si>
     <t xml:space="preserve">10.5621299743652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6644449234009</t>
+    <t xml:space="preserve">10.6644458770752</t>
   </si>
   <si>
     <t xml:space="preserve">10.3197212219238</t>
@@ -4298,10 +4298,10 @@
     <t xml:space="preserve">10.0710134506226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2174043655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90888404846191</t>
+    <t xml:space="preserve">10.2174053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9088830947876</t>
   </si>
   <si>
     <t xml:space="preserve">10.2237005233765</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">10.091477394104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0190696716309</t>
+    <t xml:space="preserve">10.0190687179565</t>
   </si>
   <si>
     <t xml:space="preserve">10.3449058532715</t>
@@ -4325,10 +4325,10 @@
     <t xml:space="preserve">10.4125909805298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4314794540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8375959396362</t>
+    <t xml:space="preserve">10.4314804077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8375949859619</t>
   </si>
   <si>
     <t xml:space="preserve">10.7683353424072</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">10.6817607879639</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3386096954346</t>
+    <t xml:space="preserve">10.3386087417603</t>
   </si>
   <si>
     <t xml:space="preserve">10.5306482315063</t>
@@ -4394,7 +4394,7 @@
     <t xml:space="preserve">9.82388305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82073497772217</t>
+    <t xml:space="preserve">9.82073402404785</t>
   </si>
   <si>
     <t xml:space="preserve">10.0977735519409</t>
@@ -4403,22 +4403,22 @@
     <t xml:space="preserve">9.56415843963623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63026905059814</t>
+    <t xml:space="preserve">9.63027095794678</t>
   </si>
   <si>
     <t xml:space="preserve">9.74990081787109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99388408660889</t>
+    <t xml:space="preserve">9.99388313293457</t>
   </si>
   <si>
     <t xml:space="preserve">9.82230758666992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61295413970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78138160705566</t>
+    <t xml:space="preserve">9.61295509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78138256072998</t>
   </si>
   <si>
     <t xml:space="preserve">9.77508544921875</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">9.40989780426025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64443588256836</t>
+    <t xml:space="preserve">9.64443683624268</t>
   </si>
   <si>
     <t xml:space="preserve">10.014347076416</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">9.94981002807617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89156913757324</t>
+    <t xml:space="preserve">9.89156723022461</t>
   </si>
   <si>
     <t xml:space="preserve">9.9545316696167</t>
@@ -4493,13 +4493,13 @@
     <t xml:space="preserve">10.677038192749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9572248458862</t>
+    <t xml:space="preserve">10.9572257995605</t>
   </si>
   <si>
     <t xml:space="preserve">11.0548191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2405605316162</t>
+    <t xml:space="preserve">11.2405614852905</t>
   </si>
   <si>
     <t xml:space="preserve">11.3523216247559</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">11.6340837478638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.33815574646</t>
+    <t xml:space="preserve">11.3381547927856</t>
   </si>
   <si>
     <t xml:space="preserve">11.4971380233765</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">11.673436164856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.726954460144</t>
+    <t xml:space="preserve">11.7269554138184</t>
   </si>
   <si>
     <t xml:space="preserve">11.5223236083984</t>
@@ -4538,10 +4538,10 @@
     <t xml:space="preserve">11.3680629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9021339416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0500974655151</t>
+    <t xml:space="preserve">10.9021320343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0500965118408</t>
   </si>
   <si>
     <t xml:space="preserve">11.1681537628174</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">10.8139839172363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8265762329102</t>
+    <t xml:space="preserve">10.8265771865845</t>
   </si>
   <si>
     <t xml:space="preserve">10.7195386886597</t>
@@ -4583,13 +4583,13 @@
     <t xml:space="preserve">10.4613876342773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8124094009399</t>
+    <t xml:space="preserve">10.8124103546143</t>
   </si>
   <si>
     <t xml:space="preserve">10.6597232818604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7557430267334</t>
+    <t xml:space="preserve">10.7557439804077</t>
   </si>
   <si>
     <t xml:space="preserve">10.7699098587036</t>
@@ -4607,19 +4607,19 @@
     <t xml:space="preserve">10.4912958145142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2378673553467</t>
+    <t xml:space="preserve">10.237868309021</t>
   </si>
   <si>
     <t xml:space="preserve">10.0111989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1009225845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0946254730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65860366821289</t>
+    <t xml:space="preserve">10.1009216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0946264266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65860462188721</t>
   </si>
   <si>
     <t xml:space="preserve">9.84906768798828</t>
@@ -4631,10 +4631,10 @@
     <t xml:space="preserve">9.86480903625488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68064022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58934307098389</t>
+    <t xml:space="preserve">9.68064117431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5893440246582</t>
   </si>
   <si>
     <t xml:space="preserve">9.69638156890869</t>
@@ -4661,13 +4661,13 @@
     <t xml:space="preserve">10.3685169219971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2898120880127</t>
+    <t xml:space="preserve">10.289813041687</t>
   </si>
   <si>
     <t xml:space="preserve">10.6487045288086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7447233200073</t>
+    <t xml:space="preserve">10.744725227356</t>
   </si>
   <si>
     <t xml:space="preserve">10.7305574417114</t>
@@ -4679,43 +4679,43 @@
     <t xml:space="preserve">10.7510204315186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8092613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4566659927368</t>
+    <t xml:space="preserve">10.8092622756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4566669464111</t>
   </si>
   <si>
     <t xml:space="preserve">10.8297252655029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7872247695923</t>
+    <t xml:space="preserve">10.7872257232666</t>
   </si>
   <si>
     <t xml:space="preserve">11.1429681777954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1980619430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3397302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.424729347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2153768539429</t>
+    <t xml:space="preserve">11.1980609893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.339729309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4247303009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2153759002686</t>
   </si>
   <si>
     <t xml:space="preserve">11.1036157608032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3413038253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4451923370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5553798675537</t>
+    <t xml:space="preserve">11.3413028717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4451932907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5553789138794</t>
   </si>
   <si>
     <t xml:space="preserve">11.3838033676147</t>
@@ -4724,7 +4724,7 @@
     <t xml:space="preserve">11.5333423614502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5301933288574</t>
+    <t xml:space="preserve">11.5301942825317</t>
   </si>
   <si>
     <t xml:space="preserve">11.4546375274658</t>
@@ -4733,16 +4733,16 @@
     <t xml:space="preserve">11.5774164199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7206592559814</t>
+    <t xml:space="preserve">11.7206583023071</t>
   </si>
   <si>
     <t xml:space="preserve">11.7332515716553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4924163818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5364894866943</t>
+    <t xml:space="preserve">11.4924154281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5364904403687</t>
   </si>
   <si>
     <t xml:space="preserve">11.3712110519409</t>
@@ -4760,13 +4760,13 @@
     <t xml:space="preserve">10.8486137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8612070083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.933614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6675930023193</t>
+    <t xml:space="preserve">10.8612060546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9336137771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6675939559937</t>
   </si>
   <si>
     <t xml:space="preserve">10.3291645050049</t>
@@ -4775,31 +4775,31 @@
     <t xml:space="preserve">10.3811092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3559246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3244428634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.52907371521</t>
+    <t xml:space="preserve">10.3559236526489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.32444190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5290746688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4393510818481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7415752410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8816699981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1697273254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2862110137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3696374893188</t>
+    <t xml:space="preserve">10.7415761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8816690444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1697282791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2862100601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3696365356445</t>
   </si>
   <si>
     <t xml:space="preserve">11.5427865982056</t>
@@ -4814,10 +4814,10 @@
     <t xml:space="preserve">11.1996355056763</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2673215866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3035249710083</t>
+    <t xml:space="preserve">11.2673206329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3035259246826</t>
   </si>
   <si>
     <t xml:space="preserve">11.2295427322388</t>
@@ -4826,13 +4826,13 @@
     <t xml:space="preserve">10.9477806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0375032424927</t>
+    <t xml:space="preserve">11.037504196167</t>
   </si>
   <si>
     <t xml:space="preserve">11.0312070846558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0343561172485</t>
+    <t xml:space="preserve">11.0343570709229</t>
   </si>
   <si>
     <t xml:space="preserve">10.95250415802</t>
@@ -4844,7 +4844,7 @@
     <t xml:space="preserve">11.1728754043579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3145437240601</t>
+    <t xml:space="preserve">11.3145446777344</t>
   </si>
   <si>
     <t xml:space="preserve">11.4026927947998</t>
@@ -4853,7 +4853,7 @@
     <t xml:space="preserve">11.9693651199341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9630680084229</t>
+    <t xml:space="preserve">11.9630689620972</t>
   </si>
   <si>
     <t xml:space="preserve">11.8686227798462</t>
@@ -4862,7 +4862,7 @@
     <t xml:space="preserve">11.8749198913574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9016780853271</t>
+    <t xml:space="preserve">11.9016790390015</t>
   </si>
   <si>
     <t xml:space="preserve">12.3392753601074</t>
@@ -4874,22 +4874,22 @@
     <t xml:space="preserve">12.2054777145386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.258996963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4903869628906</t>
+    <t xml:space="preserve">12.2589960098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4903879165649</t>
   </si>
   <si>
     <t xml:space="preserve">12.517147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5533504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7013149261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4888124465942</t>
+    <t xml:space="preserve">12.5533514022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7013158798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4888134002686</t>
   </si>
   <si>
     <t xml:space="preserve">12.7642793655396</t>
@@ -4907,25 +4907,25 @@
     <t xml:space="preserve">13.0287265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4238214492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5151195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9054927825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8330841064453</t>
+    <t xml:space="preserve">13.4238204956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.515118598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9054918289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8330850601196</t>
   </si>
   <si>
     <t xml:space="preserve">13.7968807220459</t>
   </si>
   <si>
-    <t xml:space="preserve">13.765398979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5387306213379</t>
+    <t xml:space="preserve">13.7653980255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5387296676636</t>
   </si>
   <si>
     <t xml:space="preserve">13.2915983200073</t>
@@ -4934,19 +4934,19 @@
     <t xml:space="preserve">12.7532606124878</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9027976989746</t>
+    <t xml:space="preserve">12.9027986526489</t>
   </si>
   <si>
     <t xml:space="preserve">12.4305725097656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265922546387</t>
+    <t xml:space="preserve">12.5265913009644</t>
   </si>
   <si>
     <t xml:space="preserve">12.4714984893799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7390937805176</t>
+    <t xml:space="preserve">12.7390947341919</t>
   </si>
   <si>
     <t xml:space="preserve">12.7469635009766</t>
@@ -4961,19 +4961,19 @@
     <t xml:space="preserve">12.7737226486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7910385131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9153909683228</t>
+    <t xml:space="preserve">12.7910394668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9153919219971</t>
   </si>
   <si>
     <t xml:space="preserve">13.050763130188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.171968460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1200227737427</t>
+    <t xml:space="preserve">13.1719675064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.120023727417</t>
   </si>
   <si>
     <t xml:space="preserve">12.9390029907227</t>
@@ -4982,7 +4982,7 @@
     <t xml:space="preserve">12.6824264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7878904342651</t>
+    <t xml:space="preserve">12.7878894805908</t>
   </si>
   <si>
     <t xml:space="preserve">13.1829862594604</t>
@@ -5054,13 +5054,13 @@
     <t xml:space="preserve">12.770318031311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6242446899414</t>
+    <t xml:space="preserve">12.6242437362671</t>
   </si>
   <si>
     <t xml:space="preserve">12.7514142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.014347076416</t>
+    <t xml:space="preserve">13.0143480300903</t>
   </si>
   <si>
     <t xml:space="preserve">13.2600955963135</t>
@@ -5069,13 +5069,13 @@
     <t xml:space="preserve">13.1655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0933990478516</t>
+    <t xml:space="preserve">13.0934000015259</t>
   </si>
   <si>
     <t xml:space="preserve">12.5623769760132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4334888458252</t>
+    <t xml:space="preserve">12.4334878921509</t>
   </si>
   <si>
     <t xml:space="preserve">12.6929845809937</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">13.5470886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5178747177124</t>
+    <t xml:space="preserve">13.5178737640381</t>
   </si>
   <si>
     <t xml:space="preserve">13.6261405944824</t>
@@ -5132,13 +5132,13 @@
     <t xml:space="preserve">13.2033843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0813694000244</t>
+    <t xml:space="preserve">13.0813703536987</t>
   </si>
   <si>
     <t xml:space="preserve">12.9885702133179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0469989776611</t>
+    <t xml:space="preserve">13.0469999313354</t>
   </si>
   <si>
     <t xml:space="preserve">13.1587028503418</t>
@@ -5153,7 +5153,7 @@
     <t xml:space="preserve">13.8254890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9990587234497</t>
+    <t xml:space="preserve">13.999059677124</t>
   </si>
   <si>
     <t xml:space="preserve">13.9681262969971</t>
@@ -5171,7 +5171,7 @@
     <t xml:space="preserve">13.9767189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">14.043740272522</t>
+    <t xml:space="preserve">14.0437412261963</t>
   </si>
   <si>
     <t xml:space="preserve">14.3736963272095</t>
@@ -5180,52 +5180,52 @@
     <t xml:space="preserve">14.4458742141724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3547916412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2671480178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2551183700562</t>
+    <t xml:space="preserve">14.3547925949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2671489715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2551193237305</t>
   </si>
   <si>
     <t xml:space="preserve">14.3152666091919</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1863775253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4149398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4235324859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8050451278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5938453674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650449752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0200366973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192974090576</t>
+    <t xml:space="preserve">14.1863784790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4149408340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4235334396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8050441741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.593846321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650459289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0200386047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192983627319</t>
   </si>
   <si>
     <t xml:space="preserve">15.5147933959961</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3738746643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3446588516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2982597351074</t>
+    <t xml:space="preserve">15.373875617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3446598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2982606887817</t>
   </si>
   <si>
     <t xml:space="preserve">15.0834455490112</t>
@@ -5243,31 +5243,31 @@
     <t xml:space="preserve">14.5197706222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3221397399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1571626663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0523328781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3015174865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3633842468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3788509368896</t>
+    <t xml:space="preserve">14.3221406936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1571636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0523338317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3015184402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3633852005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.378851890564</t>
   </si>
   <si>
     <t xml:space="preserve">14.2173109054565</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3668212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5489854812622</t>
+    <t xml:space="preserve">14.3668222427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5489845275879</t>
   </si>
   <si>
     <t xml:space="preserve">14.7964515686035</t>
@@ -5276,10 +5276,10 @@
     <t xml:space="preserve">14.7500524520874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7586460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4355621337891</t>
+    <t xml:space="preserve">14.7586450576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4355630874634</t>
   </si>
   <si>
     <t xml:space="preserve">14.4493112564087</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">14.5386743545532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5661706924438</t>
+    <t xml:space="preserve">14.5661697387695</t>
   </si>
   <si>
     <t xml:space="preserve">14.6074151992798</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">15.2673263549805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1006288528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3859033584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2827920913696</t>
+    <t xml:space="preserve">15.1006298065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3859052658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2827930450439</t>
   </si>
   <si>
     <t xml:space="preserve">15.5113563537598</t>
@@ -5321,43 +5321,43 @@
     <t xml:space="preserve">15.9959783554077</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6058750152588</t>
+    <t xml:space="preserve">15.6058759689331</t>
   </si>
   <si>
     <t xml:space="preserve">15.712423324585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5251045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4512071609497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6075925827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6471195220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5526008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999773025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2312364578247</t>
+    <t xml:space="preserve">15.5251054763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4512090682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.607593536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6471185684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.55260181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999782562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.231237411499</t>
   </si>
   <si>
     <t xml:space="preserve">15.3137273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.464955329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9444227218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2726593017578</t>
+    <t xml:space="preserve">15.4649562835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9444236755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2726612091064</t>
   </si>
   <si>
     <t xml:space="preserve">16.246883392334</t>
@@ -5369,25 +5369,25 @@
     <t xml:space="preserve">16.0681571960449</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2348518371582</t>
+    <t xml:space="preserve">16.2348537445068</t>
   </si>
   <si>
     <t xml:space="preserve">16.1300239562988</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5405702590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1642150878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.485577583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.275918006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1848392486572</t>
+    <t xml:space="preserve">15.5405721664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1642160415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4855785369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2759189605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1848382949829</t>
   </si>
   <si>
     <t xml:space="preserve">14.8806600570679</t>
@@ -5396,16 +5396,16 @@
     <t xml:space="preserve">14.6417865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1229705810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4168367385864</t>
+    <t xml:space="preserve">15.122971534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4168376922607</t>
   </si>
   <si>
     <t xml:space="preserve">15.7553873062134</t>
   </si>
   <si>
-    <t xml:space="preserve">16.06471824646</t>
+    <t xml:space="preserve">16.0647201538086</t>
   </si>
   <si>
     <t xml:space="preserve">15.7467937469482</t>
@@ -5417,16 +5417,16 @@
     <t xml:space="preserve">15.5749416351318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7364826202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0440979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2211055755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8945846557617</t>
+    <t xml:space="preserve">15.7364816665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0440998077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2211036682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.894585609436</t>
   </si>
   <si>
     <t xml:space="preserve">15.8705272674561</t>
@@ -5441,7 +5441,7 @@
     <t xml:space="preserve">16.1094017028809</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0939331054688</t>
+    <t xml:space="preserve">16.0939350128174</t>
   </si>
   <si>
     <t xml:space="preserve">16.9394454956055</t>
@@ -5450,7 +5450,7 @@
     <t xml:space="preserve">17.1009864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2754173278809</t>
+    <t xml:space="preserve">17.2754154205322</t>
   </si>
   <si>
     <t xml:space="preserve">17.4472694396973</t>
@@ -5459,7 +5459,7 @@
     <t xml:space="preserve">17.5847511291504</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0960083007812</t>
+    <t xml:space="preserve">18.0960102081299</t>
   </si>
   <si>
     <t xml:space="preserve">17.9714183807373</t>
@@ -5471,7 +5471,7 @@
     <t xml:space="preserve">18.0530471801758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0186748504639</t>
+    <t xml:space="preserve">18.0186767578125</t>
   </si>
   <si>
     <t xml:space="preserve">17.9671211242676</t>
@@ -5489,28 +5489,28 @@
     <t xml:space="preserve">18.289342880249</t>
   </si>
   <si>
-    <t xml:space="preserve">18.250675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2549724578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2377872467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2420825958252</t>
+    <t xml:space="preserve">18.2506771087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2549743652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2377891540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2420845031738</t>
   </si>
   <si>
     <t xml:space="preserve">18.2034168243408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1733417510986</t>
+    <t xml:space="preserve">18.1733436584473</t>
   </si>
   <si>
     <t xml:space="preserve">18.19482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5718631744385</t>
+    <t xml:space="preserve">17.5718612670898</t>
   </si>
   <si>
     <t xml:space="preserve">17.5503787994385</t>
@@ -5522,7 +5522,7 @@
     <t xml:space="preserve">17.7608985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620826721191</t>
+    <t xml:space="preserve">17.6620845794678</t>
   </si>
   <si>
     <t xml:space="preserve">17.8554172515869</t>
@@ -5534,7 +5534,7 @@
     <t xml:space="preserve">17.5761566162109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3011932373047</t>
+    <t xml:space="preserve">17.3011951446533</t>
   </si>
   <si>
     <t xml:space="preserve">17.11301612854</t>
@@ -5543,13 +5543,13 @@
     <t xml:space="preserve">16.8741416931152</t>
   </si>
   <si>
-    <t xml:space="preserve">17.045991897583</t>
+    <t xml:space="preserve">17.0459938049316</t>
   </si>
   <si>
     <t xml:space="preserve">16.9016380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.927417755127</t>
+    <t xml:space="preserve">16.9274158477783</t>
   </si>
   <si>
     <t xml:space="preserve">16.8122749328613</t>
@@ -5561,7 +5561,7 @@
     <t xml:space="preserve">16.6885433197021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7761878967285</t>
+    <t xml:space="preserve">16.7761859893799</t>
   </si>
   <si>
     <t xml:space="preserve">16.7332248687744</t>
@@ -5570,7 +5570,7 @@
     <t xml:space="preserve">17.374231338501</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6105270385742</t>
+    <t xml:space="preserve">17.6105289459229</t>
   </si>
   <si>
     <t xml:space="preserve">17.8468246459961</t>
@@ -5588,16 +5588,16 @@
     <t xml:space="preserve">18.624454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0197143554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3032703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4536399841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2388248443604</t>
+    <t xml:space="preserve">19.0197124481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3032684326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4536380767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2388229370117</t>
   </si>
   <si>
     <t xml:space="preserve">19.3977890014648</t>
@@ -5621,10 +5621,10 @@
     <t xml:space="preserve">20.8198623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1463813781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8843059539795</t>
+    <t xml:space="preserve">21.1463832855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8843078613281</t>
   </si>
   <si>
     <t xml:space="preserve">20.8327522277832</t>
@@ -5636,13 +5636,13 @@
     <t xml:space="preserve">20.7382335662842</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9960098266602</t>
+    <t xml:space="preserve">20.9960117340088</t>
   </si>
   <si>
     <t xml:space="preserve">21.1592712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.249490737915</t>
+    <t xml:space="preserve">21.2494926452637</t>
   </si>
   <si>
     <t xml:space="preserve">21.4814929962158</t>
@@ -5663,7 +5663,7 @@
     <t xml:space="preserve">21.8552703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7994213104248</t>
+    <t xml:space="preserve">21.7994194030762</t>
   </si>
   <si>
     <t xml:space="preserve">22.3665313720703</t>
@@ -5672,7 +5672,7 @@
     <t xml:space="preserve">22.4696407318115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8649005889893</t>
+    <t xml:space="preserve">22.8649024963379</t>
   </si>
   <si>
     <t xml:space="preserve">22.9078636169434</t>
@@ -5681,19 +5681,19 @@
     <t xml:space="preserve">23.1269760131836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1441593170166</t>
+    <t xml:space="preserve">23.1441612243652</t>
   </si>
   <si>
     <t xml:space="preserve">23.3331985473633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8391246795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9293441772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6371955871582</t>
+    <t xml:space="preserve">22.8391227722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9293460845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6371974945068</t>
   </si>
   <si>
     <t xml:space="preserve">21.8939361572266</t>
@@ -5702,10 +5702,10 @@
     <t xml:space="preserve">21.4943809509277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5244560241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.137788772583</t>
+    <t xml:space="preserve">21.5244541168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1377906799316</t>
   </si>
   <si>
     <t xml:space="preserve">21.3912696838379</t>
@@ -5714,25 +5714,25 @@
     <t xml:space="preserve">21.5459365844727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6791229248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.661937713623</t>
+    <t xml:space="preserve">21.6791210174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6619358062744</t>
   </si>
   <si>
     <t xml:space="preserve">20.9530487060547</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4771976470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8370475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8542327880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9229736328125</t>
+    <t xml:space="preserve">21.4771957397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8370494842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8542346954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9229755401611</t>
   </si>
   <si>
     <t xml:space="preserve">21.2375450134277</t>
@@ -6842,7 +6842,7 @@
     <t xml:space="preserve">8.85499954223633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8100004196167</t>
+    <t xml:space="preserve">8.73799991607666</t>
   </si>
 </sst>
 </file>
@@ -72285,22 +72285,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6911574074</v>
+        <v>45967.6910763889</v>
       </c>
       <c r="B2505" t="n">
-        <v>25658508</v>
+        <v>18231894</v>
       </c>
       <c r="C2505" t="n">
-        <v>8.91199970245361</v>
+        <v>8.9709997177124</v>
       </c>
       <c r="D2505" t="n">
-        <v>8.30000019073486</v>
+        <v>8.68299961090088</v>
       </c>
       <c r="E2505" t="n">
-        <v>8.5</v>
+        <v>8.89999961853027</v>
       </c>
       <c r="F2505" t="n">
-        <v>8.8100004196167</v>
+        <v>8.73799991607666</v>
       </c>
       <c r="G2505" t="s">
         <v>2276</v>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2280" uniqueCount="2280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2281" uniqueCount="2281">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">4.13119506835938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91636395454407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78795766830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63238954544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757349967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71881628036499</t>
+    <t xml:space="preserve">3.91636347770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7879581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63238978385925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757373809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71881699562073</t>
   </si>
   <si>
     <t xml:space="preserve">3.66942954063416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37804865837097</t>
+    <t xml:space="preserve">3.37804794311523</t>
   </si>
   <si>
     <t xml:space="preserve">3.28421378135681</t>
@@ -80,58 +80,58 @@
     <t xml:space="preserve">3.06197333335876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25705170631409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32619214057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26198983192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46200609207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43237328529358</t>
+    <t xml:space="preserve">3.25705146789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32619261741638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26198959350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46200633049011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.432373046875</t>
   </si>
   <si>
     <t xml:space="preserve">3.18544030189514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16321659088135</t>
+    <t xml:space="preserve">3.16321587562561</t>
   </si>
   <si>
     <t xml:space="preserve">3.16074681282043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07678937911987</t>
+    <t xml:space="preserve">3.07679009437561</t>
   </si>
   <si>
     <t xml:space="preserve">2.95332288742065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91628289222717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94838404655457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65700268745422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58292269706726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73355221748352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59279990196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68416619300842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80269360542297</t>
+    <t xml:space="preserve">2.91628313064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94838452339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65700316429138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58292245864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73355269432068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59280037879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68416571617126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80269384384155</t>
   </si>
   <si>
     <t xml:space="preserve">2.75824546813965</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">2.89899754524231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87924242019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81010150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92616009712219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83973336219788</t>
+    <t xml:space="preserve">2.87924313545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81010103225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92615985870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83973360061646</t>
   </si>
   <si>
     <t xml:space="preserve">2.72614407539368</t>
@@ -161,76 +161,76 @@
     <t xml:space="preserve">3.13358426094055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29902958869934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45212841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46447515487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44225144386292</t>
+    <t xml:space="preserve">3.29902982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45212864875793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46447491645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44225072860718</t>
   </si>
   <si>
     <t xml:space="preserve">3.2891526222229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30643773078918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21013355255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35088539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44719052314758</t>
+    <t xml:space="preserve">3.30643749237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21013379096985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35088610649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.447190284729</t>
   </si>
   <si>
     <t xml:space="preserve">3.36076354980469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44472026824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42496585845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51633071899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50151538848877</t>
+    <t xml:space="preserve">3.44472002983093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42496633529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51633048057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50151515007019</t>
   </si>
   <si>
     <t xml:space="preserve">3.51386117935181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47682213783264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33360028266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57559537887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5064537525177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33606958389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841656684875</t>
+    <t xml:space="preserve">3.47682166099548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33360075950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57559514045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50645399093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3360698223114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841704368591</t>
   </si>
   <si>
     <t xml:space="preserve">3.18050169944763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13852286338806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01505613327026</t>
+    <t xml:space="preserve">3.13852262496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01505661010742</t>
   </si>
   <si>
     <t xml:space="preserve">3.13605356216431</t>
@@ -239,25 +239,25 @@
     <t xml:space="preserve">3.2126030921936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16815447807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31878399848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35335469245911</t>
+    <t xml:space="preserve">3.16815519332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31878423690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35335493087769</t>
   </si>
   <si>
     <t xml:space="preserve">3.4027419090271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56571793556213</t>
+    <t xml:space="preserve">3.5657172203064</t>
   </si>
   <si>
     <t xml:space="preserve">3.54596328735352</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56818771362305</t>
+    <t xml:space="preserve">3.56818723678589</t>
   </si>
   <si>
     <t xml:space="preserve">3.47435235977173</t>
@@ -269,64 +269,64 @@
     <t xml:space="preserve">3.41015005111694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3829870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29656004905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26692843437195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36570167541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31631517410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38051843643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33113098144531</t>
+    <t xml:space="preserve">3.38298678398132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29656028747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26692867279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36570191383362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3163149356842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38051772117615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33113050460815</t>
   </si>
   <si>
     <t xml:space="preserve">3.108891248703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11382985115051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10148310661316</t>
+    <t xml:space="preserve">3.11383008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.101482629776</t>
   </si>
   <si>
     <t xml:space="preserve">3.11629867553711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9780158996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06938195228577</t>
+    <t xml:space="preserve">2.97801613807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06938171386719</t>
   </si>
   <si>
     <t xml:space="preserve">3.12370729446411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0718514919281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15827798843384</t>
+    <t xml:space="preserve">3.07185173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15827775001526</t>
   </si>
   <si>
     <t xml:space="preserve">3.0743203163147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0422191619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03974938392639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1483998298645</t>
+    <t xml:space="preserve">3.04221892356873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03974986076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14840006828308</t>
   </si>
   <si>
     <t xml:space="preserve">3.12123775482178</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">2.93109846115112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87677311897278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89652824401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86195731163025</t>
+    <t xml:space="preserve">2.87677335739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89652848243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86195778846741</t>
   </si>
   <si>
     <t xml:space="preserve">2.93356823921204</t>
@@ -350,25 +350,25 @@
     <t xml:space="preserve">3.09407472610474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08666706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04962730407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11136031150818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81997871398926</t>
+    <t xml:space="preserve">3.08666682243347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04962682723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1113600730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81997919082642</t>
   </si>
   <si>
     <t xml:space="preserve">2.64465641975403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66194224357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7137975692749</t>
+    <t xml:space="preserve">2.66194176673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71379780769348</t>
   </si>
   <si>
     <t xml:space="preserve">2.77059268951416</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">2.533536195755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52365899085999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54835176467896</t>
+    <t xml:space="preserve">2.52365875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54835224151611</t>
   </si>
   <si>
     <t xml:space="preserve">2.8471417427063</t>
@@ -389,73 +389,73 @@
     <t xml:space="preserve">2.96320009231567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91134452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9977707862854</t>
+    <t xml:space="preserve">2.91134428977966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99777126312256</t>
   </si>
   <si>
     <t xml:space="preserve">3.00270962715149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95826148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08913636207581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09901356697083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12617707252502</t>
+    <t xml:space="preserve">2.95826125144958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08913588523865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09901404380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12617683410645</t>
   </si>
   <si>
     <t xml:space="preserve">3.06691265106201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84467267990112</t>
+    <t xml:space="preserve">2.84467220306396</t>
   </si>
   <si>
     <t xml:space="preserve">2.81257104873657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69157338142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.913813829422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88665080070496</t>
+    <t xml:space="preserve">2.69157361984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91381359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88665103912354</t>
   </si>
   <si>
     <t xml:space="preserve">3.05703496932983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98789429664612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96073079109192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97307801246643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88418221473694</t>
+    <t xml:space="preserve">2.98789381980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96073126792908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97307753562927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88418173789978</t>
   </si>
   <si>
     <t xml:space="preserve">2.91875243186951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03481101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02987217903137</t>
+    <t xml:space="preserve">3.0348105430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02987265586853</t>
   </si>
   <si>
     <t xml:space="preserve">3.0446879863739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99283242225647</t>
+    <t xml:space="preserve">2.99283218383789</t>
   </si>
   <si>
     <t xml:space="preserve">3.05950427055359</t>
@@ -464,85 +464,85 @@
     <t xml:space="preserve">2.97554683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95085406303406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96813941001892</t>
+    <t xml:space="preserve">2.95085382461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96813917160034</t>
   </si>
   <si>
     <t xml:space="preserve">2.9039363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86442708969116</t>
+    <t xml:space="preserve">2.86442732810974</t>
   </si>
   <si>
     <t xml:space="preserve">2.87430453300476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81504058837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90146660804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83232498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86689686775208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74095988273621</t>
+    <t xml:space="preserve">2.81504034996033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90146708488464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83232545852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86689639091492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74096012115479</t>
   </si>
   <si>
     <t xml:space="preserve">2.70885896682739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7903470993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8249180316925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84220314025879</t>
+    <t xml:space="preserve">2.79034686088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82491779327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84220337867737</t>
   </si>
   <si>
     <t xml:space="preserve">2.89158987998962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87183499336243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90887451171875</t>
+    <t xml:space="preserve">2.87183475494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90887475013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.76812267303467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82244825363159</t>
+    <t xml:space="preserve">2.82244801521301</t>
   </si>
   <si>
     <t xml:space="preserve">2.85948801040649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93850708007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25211191177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29409122467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25952053070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03234195709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02740335464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16568541526794</t>
+    <t xml:space="preserve">2.93850755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25211238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29409146308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2595202922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03234171867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0274031162262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16568565368652</t>
   </si>
   <si>
     <t xml:space="preserve">3.52373933792114</t>
@@ -551,85 +551,85 @@
     <t xml:space="preserve">3.39780306816101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47188234329224</t>
+    <t xml:space="preserve">3.47188305854797</t>
   </si>
   <si>
     <t xml:space="preserve">3.4595365524292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47929167747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49410676956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55584001541138</t>
+    <t xml:space="preserve">3.47929096221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49410724639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55584049224854</t>
   </si>
   <si>
     <t xml:space="preserve">3.58547234535217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57065606117249</t>
+    <t xml:space="preserve">3.57065629959106</t>
   </si>
   <si>
     <t xml:space="preserve">3.5607795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60028862953186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62251281738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55830955505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72128534317017</t>
+    <t xml:space="preserve">3.60028839111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62251257896423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55830931663513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72128558158875</t>
   </si>
   <si>
     <t xml:space="preserve">3.81265115737915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85710024833679</t>
+    <t xml:space="preserve">3.85709929466248</t>
   </si>
   <si>
     <t xml:space="preserve">3.93364906311035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93117928504944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97315788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525856018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99044299125671</t>
+    <t xml:space="preserve">3.93117880821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97315764427185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525903701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99044346809387</t>
   </si>
   <si>
     <t xml:space="preserve">4.15341901779175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19539737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21762228012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29664087295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30651760101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17564296722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26453971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31392621994019</t>
+    <t xml:space="preserve">4.19539833068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21762180328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29664039611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30651807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17564249038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26453876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31392574310303</t>
   </si>
   <si>
     <t xml:space="preserve">4.30898714065552</t>
@@ -638,70 +638,70 @@
     <t xml:space="preserve">4.2793550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42257738113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50653409957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53863573074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57073736190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88927984237671</t>
+    <t xml:space="preserve">4.42257690429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5065336227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53863525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57073640823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88928079605103</t>
   </si>
   <si>
     <t xml:space="preserve">4.95842218399048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01274728775024</t>
+    <t xml:space="preserve">5.0127477645874</t>
   </si>
   <si>
     <t xml:space="preserve">5.17078495025635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33615064620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53616523742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34602737426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39047574996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41516780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6275315284729</t>
+    <t xml:space="preserve">4.3361496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53616571426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34602689743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39047527313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41516828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62753105163574</t>
   </si>
   <si>
     <t xml:space="preserve">4.64234781265259</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71889734268188</t>
+    <t xml:space="preserve">4.71889686584473</t>
   </si>
   <si>
     <t xml:space="preserve">4.99793195724487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0423789024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10164308547974</t>
+    <t xml:space="preserve">5.04237842559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10164260864258</t>
   </si>
   <si>
     <t xml:space="preserve">5.12633657455444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95348405838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98805379867554</t>
+    <t xml:space="preserve">4.95348358154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9880542755127</t>
   </si>
   <si>
     <t xml:space="preserve">4.99299240112305</t>
@@ -710,40 +710,40 @@
     <t xml:space="preserve">5.00287055969238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04731798171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92385101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78063011169434</t>
+    <t xml:space="preserve">5.04731750488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92385053634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78062963485718</t>
   </si>
   <si>
     <t xml:space="preserve">4.8991584777832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02756309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33869981765747</t>
+    <t xml:space="preserve">5.02756261825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33869934082031</t>
   </si>
   <si>
     <t xml:space="preserve">5.34363794326782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3238844871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25474166870117</t>
+    <t xml:space="preserve">5.32388353347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25474262237549</t>
   </si>
   <si>
     <t xml:space="preserve">5.32882213592529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1757230758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14609146118164</t>
+    <t xml:space="preserve">5.17572259902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14609050750732</t>
   </si>
   <si>
     <t xml:space="preserve">5.18560075759888</t>
@@ -758,175 +758,175 @@
     <t xml:space="preserve">5.13621377944946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16584634780884</t>
+    <t xml:space="preserve">5.16584587097168</t>
   </si>
   <si>
     <t xml:space="preserve">5.09670448303223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14115285873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22511005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30412817001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21029424667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98311519622803</t>
+    <t xml:space="preserve">5.14115238189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22511100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21029472351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98311567306519</t>
   </si>
   <si>
     <t xml:space="preserve">4.94360589981079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96336126327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93372821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07694911956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07201099395752</t>
+    <t xml:space="preserve">4.96336078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93372774124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07695055007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07201194763184</t>
   </si>
   <si>
     <t xml:space="preserve">5.06213426589966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81026220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83248662948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74358987808228</t>
+    <t xml:space="preserve">4.81026172637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83248615264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74359035491943</t>
   </si>
   <si>
     <t xml:space="preserve">4.78556823730469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73371315002441</t>
+    <t xml:space="preserve">4.73371267318726</t>
   </si>
   <si>
     <t xml:space="preserve">4.71642732620239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70654964447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69420337677002</t>
+    <t xml:space="preserve">4.70655012130737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69420289993286</t>
   </si>
   <si>
     <t xml:space="preserve">4.51888036727905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45220851898193</t>
+    <t xml:space="preserve">4.45220947265625</t>
   </si>
   <si>
     <t xml:space="preserve">4.6472864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70408058166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63000059127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79297685623169</t>
+    <t xml:space="preserve">4.70407962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63000011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79297637939453</t>
   </si>
   <si>
     <t xml:space="preserve">4.78803777694702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23498773574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91644287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97323799133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05225801467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03744077682495</t>
+    <t xml:space="preserve">5.23498725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91644334793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97323846817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05225706100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03744029998779</t>
   </si>
   <si>
     <t xml:space="preserve">4.91891241073608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94854545593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02262496948242</t>
+    <t xml:space="preserve">4.94854497909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02262401580811</t>
   </si>
   <si>
     <t xml:space="preserve">4.76828384399414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62012338638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80038452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72383499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68926477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66210126876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67197942733765</t>
+    <t xml:space="preserve">4.62012386322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80038547515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72383594512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68926429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66210174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67197895050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.59049081802368</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58308362960815</t>
+    <t xml:space="preserve">4.58308267593384</t>
   </si>
   <si>
     <t xml:space="preserve">4.61518526077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8473014831543</t>
+    <t xml:space="preserve">4.84730243682861</t>
   </si>
   <si>
     <t xml:space="preserve">4.83001661300659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75346660614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80532312393188</t>
+    <t xml:space="preserve">4.75346708297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8053240776062</t>
   </si>
   <si>
     <t xml:space="preserve">4.75099802017212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79544734954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81767082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78309869766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72136545181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68432521820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85224056243896</t>
+    <t xml:space="preserve">4.79544639587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8176703453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78309965133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72136640548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68432569503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85224103927612</t>
   </si>
   <si>
     <t xml:space="preserve">4.77816104888916</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">4.7608757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55838918685913</t>
+    <t xml:space="preserve">4.55838966369629</t>
   </si>
   <si>
     <t xml:space="preserve">4.85507822036743</t>
@@ -950,22 +950,22 @@
     <t xml:space="preserve">4.8253231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80548667907715</t>
+    <t xml:space="preserve">4.80548572540283</t>
   </si>
   <si>
     <t xml:space="preserve">4.87243556976318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95922183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9988956451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19230604171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1526312828064</t>
+    <t xml:space="preserve">4.95922231674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99889516830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19230461120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15263175964355</t>
   </si>
   <si>
     <t xml:space="preserve">5.1724681854248</t>
@@ -977,28 +977,28 @@
     <t xml:space="preserve">5.17742824554443</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9741005897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97905969619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98897743225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03856992721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03360986709595</t>
+    <t xml:space="preserve">4.97409963607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97905921936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98897647857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03856945037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03361034393311</t>
   </si>
   <si>
     <t xml:space="preserve">5.05840635299683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07328414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02865076065063</t>
+    <t xml:space="preserve">5.07328367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02865123748779</t>
   </si>
   <si>
     <t xml:space="preserve">5.07824325561523</t>
@@ -1010,250 +1010,250 @@
     <t xml:space="preserve">4.95178318023682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.954261302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86995601654053</t>
+    <t xml:space="preserve">4.95426273345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86995697021484</t>
   </si>
   <si>
     <t xml:space="preserve">5.26669454574585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40555238723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34604120254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30636835098267</t>
+    <t xml:space="preserve">5.40555191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34604072570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30636739730835</t>
   </si>
   <si>
     <t xml:space="preserve">5.67335033416748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68822813034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01553678512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19406843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14943552017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16431331634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07008838653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13951587677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27341556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61560249328613</t>
+    <t xml:space="preserve">5.68822717666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01553726196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19406747817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14943599700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1643123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07008790969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13951730728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27341651916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61560297012329</t>
   </si>
   <si>
     <t xml:space="preserve">6.53129482269287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50650072097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78421640396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70982885360718</t>
+    <t xml:space="preserve">6.50649976730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78421688079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70982789993286</t>
   </si>
   <si>
     <t xml:space="preserve">6.7247052192688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76933717727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80405330657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96770668029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88339996337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99250316619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07681035995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14623928070068</t>
+    <t xml:space="preserve">6.76933860778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80405235290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96770715713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88340091705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99250364303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07680940628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14623880386353</t>
   </si>
   <si>
     <t xml:space="preserve">7.18095350265503</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46362972259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31485271453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33468961715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38428211212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36444568634033</t>
+    <t xml:space="preserve">7.46362924575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31485223770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33469009399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38428163528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36444473266602</t>
   </si>
   <si>
     <t xml:space="preserve">7.51818037033081</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58265066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56281518936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53801822662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49338388442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40907764434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52313995361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41403770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50330305099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4239559173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4586706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41899681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30989360809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37932205200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93795156478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05697250366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02225923538208</t>
+    <t xml:space="preserve">7.58265113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56281423568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53801727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49338483810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40907669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52314138412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41403818130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50330257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42395544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45867013931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41899728775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30989503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37932348251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93795204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05697345733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02225828170776</t>
   </si>
   <si>
     <t xml:space="preserve">7.14128017425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34956693649292</t>
+    <t xml:space="preserve">7.34956789016724</t>
   </si>
   <si>
     <t xml:space="preserve">7.3594856262207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51322031021118</t>
+    <t xml:space="preserve">7.51322174072266</t>
   </si>
   <si>
     <t xml:space="preserve">7.76614236831665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73142719268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6619987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45371055603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28013610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33964872360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37436389923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25038290023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43387460708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55785417556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24046468734741</t>
+    <t xml:space="preserve">7.73142671585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66199827194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45371103286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28013849258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33964967727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3743634223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2503833770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43387413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55785512924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24046516418457</t>
   </si>
   <si>
     <t xml:space="preserve">7.20079040527344</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17103433609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.151198387146</t>
+    <t xml:space="preserve">7.17103576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15119743347168</t>
   </si>
   <si>
     <t xml:space="preserve">7.00738096237183</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23550462722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19087171554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53305912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52809906005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50826215744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43883371353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44875192642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63720178604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65208005905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64216184616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69175386428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67191600799561</t>
+    <t xml:space="preserve">7.23550510406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19087219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53305864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52809953689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50826168060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43883323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44875288009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63720273971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65207862854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64216232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69175243377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67191648483276</t>
   </si>
   <si>
     <t xml:space="preserve">7.54297733306885</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">7.39419984817505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71159029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35628890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88692665100098</t>
+    <t xml:space="preserve">7.71158981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35629081726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88692760467529</t>
   </si>
   <si>
     <t xml:space="preserve">8.98115062713623</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">9.21423530578613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42252254486084</t>
+    <t xml:space="preserve">9.42252159118652</t>
   </si>
   <si>
     <t xml:space="preserve">9.48699283599854</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">9.28862380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32829570770264</t>
+    <t xml:space="preserve">9.32829666137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.50187015533447</t>
@@ -1301,52 +1301,52 @@
     <t xml:space="preserve">9.69527912139893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76470756530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70519733428955</t>
+    <t xml:space="preserve">9.76470851898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70519828796387</t>
   </si>
   <si>
     <t xml:space="preserve">9.64072799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63080787658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81925868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84108066558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68337726593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65163898468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53856754302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31937026977539</t>
+    <t xml:space="preserve">9.63080978393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81925964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8410816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68337631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65163803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5385684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31936931610107</t>
   </si>
   <si>
     <t xml:space="preserve">8.75798606872559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35111045837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89982032775879</t>
+    <t xml:space="preserve">9.35110950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89982128143311</t>
   </si>
   <si>
     <t xml:space="preserve">8.63698196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75302696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57548809051514</t>
+    <t xml:space="preserve">8.75302600860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57548713684082</t>
   </si>
   <si>
     <t xml:space="preserve">8.77782344818115</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">8.82741546630859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00396347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83733463287354</t>
+    <t xml:space="preserve">9.0039644241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8373327255249</t>
   </si>
   <si>
     <t xml:space="preserve">8.94643592834473</t>
@@ -1367,16 +1367,16 @@
     <t xml:space="preserve">8.98908710479736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80956268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73814868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6905403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8055944442749</t>
+    <t xml:space="preserve">8.80956172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73814964294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69054126739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80559539794922</t>
   </si>
   <si>
     <t xml:space="preserve">8.71434497833252</t>
@@ -1385,52 +1385,52 @@
     <t xml:space="preserve">8.47431945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98930835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01410293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46836853027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55664253234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56259346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51597690582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52787780761719</t>
+    <t xml:space="preserve">7.98930692672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01410388946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46836757659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55664157867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56259155273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51597595214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52787685394287</t>
   </si>
   <si>
     <t xml:space="preserve">8.53085422515869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43266296386719</t>
+    <t xml:space="preserve">8.43266201019287</t>
   </si>
   <si>
     <t xml:space="preserve">8.53184509277344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52589511871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35926532745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56457710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71732044219971</t>
+    <t xml:space="preserve">8.52589416503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35926628112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56457614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71732139587402</t>
   </si>
   <si>
     <t xml:space="preserve">8.42175102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25115394592285</t>
+    <t xml:space="preserve">8.25115299224854</t>
   </si>
   <si>
     <t xml:space="preserve">8.1886682510376</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">8.15792083740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1837100982666</t>
+    <t xml:space="preserve">8.18370819091797</t>
   </si>
   <si>
     <t xml:space="preserve">8.78278255462646</t>
@@ -1463,85 +1463,85 @@
     <t xml:space="preserve">9.31342029571533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2261381149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40764427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43640804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36301326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70916652679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76768398284912</t>
+    <t xml:space="preserve">9.22613620758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4076452255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4364070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36301136016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70916557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7676830291748</t>
   </si>
   <si>
     <t xml:space="preserve">9.63180255889893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55840587615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75975036621094</t>
+    <t xml:space="preserve">9.55840492248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7597484588623</t>
   </si>
   <si>
     <t xml:space="preserve">9.7914867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393558502197</t>
+    <t xml:space="preserve">9.49393653869629</t>
   </si>
   <si>
     <t xml:space="preserve">9.68635368347168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41458797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20927619934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43739891052246</t>
+    <t xml:space="preserve">9.41458702087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20927715301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43739986419678</t>
   </si>
   <si>
     <t xml:space="preserve">9.2182035446167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51674652099609</t>
+    <t xml:space="preserve">9.51674747467041</t>
   </si>
   <si>
     <t xml:space="preserve">9.5355920791626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4800500869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29556655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30845928192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42946434020996</t>
+    <t xml:space="preserve">9.48004913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29556560516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30846118927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42946529388428</t>
   </si>
   <si>
     <t xml:space="preserve">9.41756343841553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36697769165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30747032165527</t>
+    <t xml:space="preserve">9.36697864532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30746746063232</t>
   </si>
   <si>
     <t xml:space="preserve">9.36797046661377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19935703277588</t>
+    <t xml:space="preserve">9.19935512542725</t>
   </si>
   <si>
     <t xml:space="preserve">9.43938255310059</t>
@@ -1550,13 +1550,13 @@
     <t xml:space="preserve">9.59609508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48600101470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31143569946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3054838180542</t>
+    <t xml:space="preserve">9.48600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31143665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30548477172852</t>
   </si>
   <si>
     <t xml:space="preserve">9.1081075668335</t>
@@ -1571,25 +1571,25 @@
     <t xml:space="preserve">9.62089157104492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18547058105469</t>
+    <t xml:space="preserve">9.185471534729</t>
   </si>
   <si>
     <t xml:space="preserve">8.85221195220947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87601566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86212825775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13984680175781</t>
+    <t xml:space="preserve">8.87601470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8621301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13984775543213</t>
   </si>
   <si>
     <t xml:space="preserve">8.90676212310791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98313426971436</t>
+    <t xml:space="preserve">8.98313617706299</t>
   </si>
   <si>
     <t xml:space="preserve">8.92659950256348</t>
@@ -1598,13 +1598,13 @@
     <t xml:space="preserve">8.85022830963135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04462909698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87403202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92461585998535</t>
+    <t xml:space="preserve">9.04463005065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87403106689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92461681365967</t>
   </si>
   <si>
     <t xml:space="preserve">8.79666900634766</t>
@@ -1628,10 +1628,10 @@
     <t xml:space="preserve">8.24123573303223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95558404922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10039329528809</t>
+    <t xml:space="preserve">7.95558547973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10039234161377</t>
   </si>
   <si>
     <t xml:space="preserve">8.10237693786621</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">8.40687370300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46935844421387</t>
+    <t xml:space="preserve">8.46935939788818</t>
   </si>
   <si>
     <t xml:space="preserve">8.52291870117188</t>
@@ -1655,73 +1655,73 @@
     <t xml:space="preserve">8.26305675506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21346378326416</t>
+    <t xml:space="preserve">8.21346473693848</t>
   </si>
   <si>
     <t xml:space="preserve">8.25214672088623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19957733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24917030334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22239017486572</t>
+    <t xml:space="preserve">8.19957828521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24916934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22239112854004</t>
   </si>
   <si>
     <t xml:space="preserve">8.33347702026367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14105796813965</t>
+    <t xml:space="preserve">8.14105892181396</t>
   </si>
   <si>
     <t xml:space="preserve">8.01906299591064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21048736572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16111612319946</t>
+    <t xml:space="preserve">8.21048927307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1611156463623</t>
   </si>
   <si>
     <t xml:space="preserve">7.26426839828491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23947191238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04804611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04209613800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24343967437744</t>
+    <t xml:space="preserve">7.23947238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04804658889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04209470748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24344110488892</t>
   </si>
   <si>
     <t xml:space="preserve">7.23352146148682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20277547836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24839782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17500257492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04407930374146</t>
+    <t xml:space="preserve">7.20277452468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2483983039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17500305175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04407978057861</t>
   </si>
   <si>
     <t xml:space="preserve">6.97663402557373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.808021068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79909324645996</t>
+    <t xml:space="preserve">6.80802011489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7990927696228</t>
   </si>
   <si>
     <t xml:space="preserve">7.01729917526245</t>
@@ -1730,91 +1730,91 @@
     <t xml:space="preserve">7.12243461608887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03713607788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95977163314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18591356277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43486738204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42693090438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36146974563599</t>
+    <t xml:space="preserve">7.03713655471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95977210998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18591213226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43486642837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42693138122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36146879196167</t>
   </si>
   <si>
     <t xml:space="preserve">7.220627784729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26823568344116</t>
+    <t xml:space="preserve">7.26823616027832</t>
   </si>
   <si>
     <t xml:space="preserve">7.39320802688599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22657871246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21566772460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.167067527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48247528076172</t>
+    <t xml:space="preserve">7.22657823562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21566867828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16706705093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4824743270874</t>
   </si>
   <si>
     <t xml:space="preserve">7.40610218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42792272567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45767831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48346519470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61934900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73341083526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66001510620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70266389846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66794967651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51024580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68282699584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69373750686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64017820358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57769155502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52016401290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34460878372192</t>
+    <t xml:space="preserve">7.42792177200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45767879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48346662521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61934947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73341131210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66001462936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70266437530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66794872283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51024627685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68282651901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6937370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64017868041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57769107818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52016544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34460783004761</t>
   </si>
   <si>
     <t xml:space="preserve">7.42197227478027</t>
@@ -1826,13 +1826,13 @@
     <t xml:space="preserve">6.9627480506897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92803382873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94588661193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17797756195068</t>
+    <t xml:space="preserve">6.92803335189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94588613510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17797803878784</t>
   </si>
   <si>
     <t xml:space="preserve">6.87744951248169</t>
@@ -1841,181 +1841,181 @@
     <t xml:space="preserve">6.82587337493896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66618633270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86455583572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95183706283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78024816513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04705429077148</t>
+    <t xml:space="preserve">6.66618680953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86455488204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95183849334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78024911880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04705476760864</t>
   </si>
   <si>
     <t xml:space="preserve">6.81992244720459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67015504837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75247573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0292010307312</t>
+    <t xml:space="preserve">6.67015361785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75247669219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02920198440552</t>
   </si>
   <si>
     <t xml:space="preserve">7.11251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09664726257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26129484176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28708076477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08672761917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30394268035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23054647445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13334512710571</t>
+    <t xml:space="preserve">7.0966477394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26129293441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28708171844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0867280960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30394172668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23054552078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13334560394287</t>
   </si>
   <si>
     <t xml:space="preserve">7.1283860206604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94291067123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01234102249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93001651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99052000045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33865690231323</t>
+    <t xml:space="preserve">6.94291114807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01234006881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93001699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99052047729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33865642547607</t>
   </si>
   <si>
     <t xml:space="preserve">7.34758329391479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30493450164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49635934829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34857606887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2345142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86554718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82488250732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61064291000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78322505950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91613101959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92208194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86852264404297</t>
+    <t xml:space="preserve">7.30493402481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49635982513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34857559204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23451232910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86554574966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8248815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61064338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78322458267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91613149642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92208290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86852121353149</t>
   </si>
   <si>
     <t xml:space="preserve">6.82884883880615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82289838790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72272062301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50848340988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25754737854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28928470611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23175859451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15737056732178</t>
+    <t xml:space="preserve">6.82289791107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72272109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50848245620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25754594802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28928518295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2317590713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15737009048462</t>
   </si>
   <si>
     <t xml:space="preserve">6.50253248214722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5511326789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62849617004395</t>
+    <t xml:space="preserve">6.55113220214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6284966468811</t>
   </si>
   <si>
     <t xml:space="preserve">6.87645673751831</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01134872436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16012477874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2444314956665</t>
+    <t xml:space="preserve">7.01134777069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16012525558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24443244934082</t>
   </si>
   <si>
     <t xml:space="preserve">7.21070861816406</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32080411911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10557413101196</t>
+    <t xml:space="preserve">7.32080364227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1055736541748</t>
   </si>
   <si>
     <t xml:space="preserve">7.26724433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1869044303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18987989425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28509616851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39816808700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47354698181152</t>
+    <t xml:space="preserve">7.18690395355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18987941741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28509664535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3981671333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47354793548584</t>
   </si>
   <si>
     <t xml:space="preserve">7.52710819244385</t>
@@ -2024,79 +2024,79 @@
     <t xml:space="preserve">6.63543891906738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44302177429199</t>
+    <t xml:space="preserve">6.44302129745483</t>
   </si>
   <si>
     <t xml:space="preserve">6.41822481155396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39739608764648</t>
+    <t xml:space="preserve">6.3973970413208</t>
   </si>
   <si>
     <t xml:space="preserve">6.49757289886475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40731477737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45988273620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44897317886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4519476890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5769214630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50154066085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51145935058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54617357254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4559154510498</t>
+    <t xml:space="preserve">6.40731430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45988321304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44897174835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45194864273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57692050933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.501540184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51145887374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54617404937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45591592788696</t>
   </si>
   <si>
     <t xml:space="preserve">6.43806171417236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41227436065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36268186569214</t>
+    <t xml:space="preserve">6.41227388381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3626823425293</t>
   </si>
   <si>
     <t xml:space="preserve">6.41524982452393</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6493239402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32697582244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36664915084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35871458053589</t>
+    <t xml:space="preserve">6.64932489395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32697629928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36664867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35871410369873</t>
   </si>
   <si>
     <t xml:space="preserve">6.30416297912598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25853729248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26548051834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32003355026245</t>
+    <t xml:space="preserve">6.25853967666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26548099517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32003259658813</t>
   </si>
   <si>
     <t xml:space="preserve">6.6364312171936</t>
@@ -2105,115 +2105,115 @@
     <t xml:space="preserve">6.46980142593384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49658060073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33590173721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46384954452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49162149429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66122722625732</t>
+    <t xml:space="preserve">6.49658012390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33590221405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46385049819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49162197113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66122674942017</t>
   </si>
   <si>
     <t xml:space="preserve">6.52633666992188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58188056945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73958349227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80603551864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80901145935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81000328063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9389443397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86157989501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89133501052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8923282623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04308795928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0936713218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16607618331909</t>
+    <t xml:space="preserve">6.58187913894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73958301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80603694915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8090124130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81000423431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93894386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86157941818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89133453369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89232730865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04308700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09367179870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16607522964478</t>
   </si>
   <si>
     <t xml:space="preserve">7.29303169250488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28431224822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20211458206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14384794235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20939779281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19170999526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14488887786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04916620254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11263418197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07205581665039</t>
+    <t xml:space="preserve">7.28431177139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20211410522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14384841918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20939826965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19171047210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14488935470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04916715621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11263465881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07205629348755</t>
   </si>
   <si>
     <t xml:space="preserve">6.80673789978027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73806571960449</t>
+    <t xml:space="preserve">6.73806762695312</t>
   </si>
   <si>
     <t xml:space="preserve">6.61112976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71309566497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81402063369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88997459411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9544825553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93350076675415</t>
+    <t xml:space="preserve">6.71309518814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81401968002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88997411727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95448303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93350124359131</t>
   </si>
   <si>
     <t xml:space="preserve">6.88365411758423</t>
@@ -2222,166 +2222,166 @@
     <t xml:space="preserve">6.82684946060181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62166166305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64020919799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16998910903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10623025894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.019287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96132373809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62977695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59268093109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84771633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78163909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78743553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7642502784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88133573532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94625282287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83728361129761</t>
+    <t xml:space="preserve">6.62166213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64021015167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16999006271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10622978210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01928615570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96132326126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62977647781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59268188476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84771585464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78163862228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78743457794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76424980163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88133478164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94625234603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83728313446045</t>
   </si>
   <si>
     <t xml:space="preserve">6.89524555206299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86278772354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92422771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98566818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06449699401855</t>
+    <t xml:space="preserve">6.86278629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92422819137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98566770553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06449794769287</t>
   </si>
   <si>
     <t xml:space="preserve">7.15028190612793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13521242141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14216804504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02160501480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03319787979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08072710037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10970735549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1572380065918</t>
+    <t xml:space="preserve">7.13521146774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14216709136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02160406112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0331974029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.080726146698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10970783233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15723848342896</t>
   </si>
   <si>
     <t xml:space="preserve">7.13057518005371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33112621307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35315179824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3253288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28939294815063</t>
+    <t xml:space="preserve">7.33112525939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35315084457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32532930374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28939390182495</t>
   </si>
   <si>
     <t xml:space="preserve">7.20940494537354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20476722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28707504272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2859148979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0598611831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07493162155151</t>
+    <t xml:space="preserve">7.20476675033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28707408905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28591442108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05986070632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07493019104004</t>
   </si>
   <si>
     <t xml:space="preserve">6.95900583267212</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17578554153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31141805648804</t>
+    <t xml:space="preserve">7.1757869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3114185333252</t>
   </si>
   <si>
     <t xml:space="preserve">7.19433450698853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08768320083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97639417648315</t>
+    <t xml:space="preserve">7.08768224716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97639465332031</t>
   </si>
   <si>
     <t xml:space="preserve">6.99841976165771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76540994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81873607635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8685827255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72715425491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7236762046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82569169998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58572483062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40719985961914</t>
+    <t xml:space="preserve">6.76541137695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81873559951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86858367919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72715473175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72367715835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82569074630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58572578430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4072003364563</t>
   </si>
   <si>
     <t xml:space="preserve">6.52660322189331</t>
@@ -2396,43 +2396,43 @@
     <t xml:space="preserve">6.6900577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54515171051025</t>
+    <t xml:space="preserve">6.5451512336731</t>
   </si>
   <si>
     <t xml:space="preserve">6.635573387146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74454307556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8048243522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86162805557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86394596099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0830454826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29055213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30562353134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37285947799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28243684768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28127861022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29287099838257</t>
+    <t xml:space="preserve">6.74454355239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80482387542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86162757873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86394691467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08304595947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29055261611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30562162399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37286043167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28243732452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28127813339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29287004470825</t>
   </si>
   <si>
     <t xml:space="preserve">7.18158197402954</t>
@@ -2441,40 +2441,40 @@
     <t xml:space="preserve">7.1873779296875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07029342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92654705047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83148765563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84539794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87785768508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81525754928589</t>
+    <t xml:space="preserve">7.07029294967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92654657363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83148860931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84539937973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87785720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81525659561157</t>
   </si>
   <si>
     <t xml:space="preserve">6.63093614578247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54051399230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53239965438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57529258728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50921535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54862833023071</t>
+    <t xml:space="preserve">6.54051446914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53239917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57529163360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50921392440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54862976074219</t>
   </si>
   <si>
     <t xml:space="preserve">6.73410987854004</t>
@@ -2486,49 +2486,49 @@
     <t xml:space="preserve">6.91843128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07145261764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03899431228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87206125259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95668697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90915727615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87322092056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86742448806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90336084365845</t>
+    <t xml:space="preserve">7.07145309448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0389928817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87206172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95668649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90915679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87321949005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86742305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90336132049561</t>
   </si>
   <si>
     <t xml:space="preserve">6.81062078475952</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45980262756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07304954528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12057876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32808589935303</t>
+    <t xml:space="preserve">7.45980310440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07304859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12057781219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32808494567871</t>
   </si>
   <si>
     <t xml:space="preserve">8.37561511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38025188446045</t>
+    <t xml:space="preserve">8.38025093078613</t>
   </si>
   <si>
     <t xml:space="preserve">8.40691471099854</t>
@@ -2537,22 +2537,22 @@
     <t xml:space="preserve">8.48226547241211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41039085388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5112476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4138708114624</t>
+    <t xml:space="preserve">8.41039180755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51124668121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41386985778809</t>
   </si>
   <si>
     <t xml:space="preserve">8.40807437896729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42198467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18433570861816</t>
+    <t xml:space="preserve">8.42198371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18433666229248</t>
   </si>
   <si>
     <t xml:space="preserve">8.19245147705078</t>
@@ -2561,31 +2561,31 @@
     <t xml:space="preserve">8.09623527526855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79019117355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74613952636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8817720413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87713527679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89104557037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82033109664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77859830856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70440483093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65223932266235</t>
+    <t xml:space="preserve">7.79019069671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74613857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88177251815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87713479995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89104509353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82033252716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77859878540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70440530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65224027633667</t>
   </si>
   <si>
     <t xml:space="preserve">7.74845695495605</t>
@@ -2597,142 +2597,142 @@
     <t xml:space="preserve">7.68701696395874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62093925476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5792064666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46328163146973</t>
+    <t xml:space="preserve">7.62094020843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57920598983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46328067779541</t>
   </si>
   <si>
     <t xml:space="preserve">7.64760255813599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72411251068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8075795173645</t>
+    <t xml:space="preserve">7.72411298751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80757904052734</t>
   </si>
   <si>
     <t xml:space="preserve">7.88525009155273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8840913772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91191148757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82844686508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78439378738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7415018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58036518096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47719192504883</t>
+    <t xml:space="preserve">7.88409090042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91191244125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82844543457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78439474105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74150228500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5803656578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47719240188599</t>
   </si>
   <si>
     <t xml:space="preserve">7.51196908950806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41691160202026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43777751922607</t>
+    <t xml:space="preserve">7.41691017150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43777704238892</t>
   </si>
   <si>
     <t xml:space="preserve">7.43661785125732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39024877548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36822319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22911214828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21867752075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20592546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22099637985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14680528640747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98219060897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03783464431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96364164352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03087902069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91263484954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80018758773804</t>
+    <t xml:space="preserve">7.39024782180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36822175979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2291111946106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21867704391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20592594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22099828720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14680433273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98218965530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03783512115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96364116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03087997436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91263437271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80018711090088</t>
   </si>
   <si>
     <t xml:space="preserve">6.85235404968262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19317531585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07608938217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03203964233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29402875900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10738945007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14100885391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11086797714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11550378799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00189828872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57297229766846</t>
+    <t xml:space="preserve">7.19317579269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07609081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03203868865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.294029712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10739040374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1410083770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11086845397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1155047416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00189733505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57297325134277</t>
   </si>
   <si>
     <t xml:space="preserve">6.52544403076172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70164966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51616907119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27620315551758</t>
+    <t xml:space="preserve">6.70165061950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51616954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27620363235474</t>
   </si>
   <si>
     <t xml:space="preserve">6.3411226272583</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">6.09651899337769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43806314468384</t>
+    <t xml:space="preserve">5.43806266784668</t>
   </si>
   <si>
     <t xml:space="preserve">5.40676307678223</t>
@@ -2756,40 +2756,40 @@
     <t xml:space="preserve">5.51921033859253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53326511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85785579681396</t>
+    <t xml:space="preserve">4.53326416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85785627365112</t>
   </si>
   <si>
     <t xml:space="preserve">4.15534830093384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97914147377014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54731917381287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36531519889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56123042106628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40994787216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84872484207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96117329597473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99421119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75482535362244</t>
+    <t xml:space="preserve">3.97914123535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54731869697571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36531591415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56122994422913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40994715690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84872460365295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96117305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99421143531799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75482583045959</t>
   </si>
   <si>
     <t xml:space="preserve">3.65744805335999</t>
@@ -2798,37 +2798,37 @@
     <t xml:space="preserve">3.80930995941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66498351097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64295744895935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368872642517</t>
+    <t xml:space="preserve">3.66498374938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64295721054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368896484375</t>
   </si>
   <si>
     <t xml:space="preserve">3.83481383323669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08289480209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12636661529541</t>
+    <t xml:space="preserve">4.08289432525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12636613845825</t>
   </si>
   <si>
     <t xml:space="preserve">4.33503198623657</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32401990890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10434007644653</t>
+    <t xml:space="preserve">4.32402038574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10434055328369</t>
   </si>
   <si>
     <t xml:space="preserve">4.12057018280029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24403047561646</t>
+    <t xml:space="preserve">4.24403142929077</t>
   </si>
   <si>
     <t xml:space="preserve">4.30663061141968</t>
@@ -2840,25 +2840,25 @@
     <t xml:space="preserve">4.20229721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35010194778442</t>
+    <t xml:space="preserve">4.35010242462158</t>
   </si>
   <si>
     <t xml:space="preserve">4.26026058197021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46197128295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57383823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74135208129883</t>
+    <t xml:space="preserve">4.46197080612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57383871078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74135160446167</t>
   </si>
   <si>
     <t xml:space="preserve">4.64629173278809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38430070877075</t>
+    <t xml:space="preserve">4.38430118560791</t>
   </si>
   <si>
     <t xml:space="preserve">4.44863891601562</t>
@@ -2873,10 +2873,10 @@
     <t xml:space="preserve">4.50370359420776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42429494857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40053033828735</t>
+    <t xml:space="preserve">4.42429447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4005298614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.27475118637085</t>
@@ -2888,16 +2888,16 @@
     <t xml:space="preserve">4.17505502700806</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51703548431396</t>
+    <t xml:space="preserve">4.51703596115112</t>
   </si>
   <si>
     <t xml:space="preserve">4.31242704391479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25388479232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29851579666138</t>
+    <t xml:space="preserve">4.25388383865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29851627349854</t>
   </si>
   <si>
     <t xml:space="preserve">4.59934234619141</t>
@@ -2906,16 +2906,16 @@
     <t xml:space="preserve">4.72859954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78192567825317</t>
+    <t xml:space="preserve">4.78192520141602</t>
   </si>
   <si>
     <t xml:space="preserve">4.60339975357056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76511526107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.832932472229</t>
+    <t xml:space="preserve">4.7651162147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83293151855469</t>
   </si>
   <si>
     <t xml:space="preserve">5.08217191696167</t>
@@ -2924,16 +2924,16 @@
     <t xml:space="preserve">5.04449605941772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39748859405518</t>
+    <t xml:space="preserve">5.39749002456665</t>
   </si>
   <si>
     <t xml:space="preserve">5.45255327224731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21316766738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0723180770874</t>
+    <t xml:space="preserve">5.21316862106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07231855392456</t>
   </si>
   <si>
     <t xml:space="preserve">4.68164968490601</t>
@@ -2942,76 +2942,76 @@
     <t xml:space="preserve">4.7488865852356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7506251335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88625812530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86770963668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85263967514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89958953857422</t>
+    <t xml:space="preserve">4.75062465667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88625860214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86771011352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85264015197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89958906173706</t>
   </si>
   <si>
     <t xml:space="preserve">4.96624612808228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25374221801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02247047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09550333023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00508165359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11694955825806</t>
+    <t xml:space="preserve">5.25374174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02247095108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09550380706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00508213043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1169490814209</t>
   </si>
   <si>
     <t xml:space="preserve">5.18418645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09260606765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21606588363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15868282318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21896409988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20679140090942</t>
+    <t xml:space="preserve">5.09260511398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21606540679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15868234634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21896457672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20679187774658</t>
   </si>
   <si>
     <t xml:space="preserve">5.09840154647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00276279449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11984825134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24910449981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20447301864624</t>
+    <t xml:space="preserve">5.00276231765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11984777450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24910497665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2044734954834</t>
   </si>
   <si>
     <t xml:space="preserve">5.2572193145752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31692123413086</t>
+    <t xml:space="preserve">5.3169207572937</t>
   </si>
   <si>
     <t xml:space="preserve">5.31054544448853</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">5.35401725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30822706222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3412652015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26069641113281</t>
+    <t xml:space="preserve">5.30822658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34126567840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26069688796997</t>
   </si>
   <si>
     <t xml:space="preserve">5.25895833969116</t>
@@ -3038,37 +3038,37 @@
     <t xml:space="preserve">5.37488412857056</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30764722824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99638652801514</t>
+    <t xml:space="preserve">5.30764770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99638700485229</t>
   </si>
   <si>
     <t xml:space="preserve">5.23693227767944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44270133972168</t>
+    <t xml:space="preserve">5.44270038604736</t>
   </si>
   <si>
     <t xml:space="preserve">5.44733715057373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38937425613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38183975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47457933425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76323318481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74178886413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65716218948364</t>
+    <t xml:space="preserve">5.38937473297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38183927536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47457981109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76323413848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74178838729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65716171264648</t>
   </si>
   <si>
     <t xml:space="preserve">5.61658811569214</t>
@@ -3083,22 +3083,22 @@
     <t xml:space="preserve">5.58065176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47631931304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40618324279785</t>
+    <t xml:space="preserve">5.476318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40618371963501</t>
   </si>
   <si>
     <t xml:space="preserve">5.5800724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51631212234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54703235626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47747755050659</t>
+    <t xml:space="preserve">5.51631307601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54703283309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47747802734375</t>
   </si>
   <si>
     <t xml:space="preserve">5.457190990448</t>
@@ -3116,40 +3116,40 @@
     <t xml:space="preserve">5.37836170196533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46646547317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58470869064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57079696655273</t>
+    <t xml:space="preserve">5.46646451950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58470821380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57079792022705</t>
   </si>
   <si>
     <t xml:space="preserve">5.57137727737427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73019552230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74642467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78641891479492</t>
+    <t xml:space="preserve">5.73019599914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74642515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78641843795776</t>
   </si>
   <si>
     <t xml:space="preserve">6.30750465393066</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26692962646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23910903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01537132263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75975608825684</t>
+    <t xml:space="preserve">6.266930103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23910856246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01537179946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75975561141968</t>
   </si>
   <si>
     <t xml:space="preserve">5.92263174057007</t>
@@ -3158,40 +3158,40 @@
     <t xml:space="preserve">6.0223274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01189422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92958736419678</t>
+    <t xml:space="preserve">6.01189470291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92958688735962</t>
   </si>
   <si>
     <t xml:space="preserve">6.16491508483887</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02116823196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06753778457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99914264678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07681226730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18578243255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20317125320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19042015075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1046347618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16375637054443</t>
+    <t xml:space="preserve">6.02116870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06753826141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99914216995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07681274414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18578338623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2031717300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19041919708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10463523864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16375589370728</t>
   </si>
   <si>
     <t xml:space="preserve">6.06058311462402</t>
@@ -3200,112 +3200,112 @@
     <t xml:space="preserve">6.12666082382202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99566555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24954128265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22867441177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24722242355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20549011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3573522567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43386173248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48023319244385</t>
+    <t xml:space="preserve">5.99566507339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24954032897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22867488861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24722290039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20548963546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35735177993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43386316299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48023414611816</t>
   </si>
   <si>
     <t xml:space="preserve">6.37242269515991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12550115585327</t>
+    <t xml:space="preserve">6.12550067901611</t>
   </si>
   <si>
     <t xml:space="preserve">6.12318277359009</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1104302406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27156686782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37937688827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47443723678589</t>
+    <t xml:space="preserve">6.11043071746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27156782150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3793773651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47443675994873</t>
   </si>
   <si>
     <t xml:space="preserve">6.51269245147705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91031694412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99146461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07840871810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29750728607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31837511062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34851551055908</t>
+    <t xml:space="preserve">6.91031789779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99146509170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07840824127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29750776290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31837463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34851503372192</t>
   </si>
   <si>
     <t xml:space="preserve">7.50037717819214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46559906005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44705200195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58963966369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64180660247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58616256713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66615056991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57341146469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66730928421021</t>
+    <t xml:space="preserve">7.46559858322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44705057144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58963918685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64180707931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58616161346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66615104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.573410987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66731023788452</t>
   </si>
   <si>
     <t xml:space="preserve">7.63948774337769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66846895217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85394954681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80294179916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77048397064209</t>
+    <t xml:space="preserve">7.66846942901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85395097732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80294322967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77048301696777</t>
   </si>
   <si>
     <t xml:space="preserve">7.98494434356689</t>
@@ -3314,40 +3314,40 @@
     <t xml:space="preserve">8.01624584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90611505508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01044845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18781566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29678440093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34895038604736</t>
+    <t xml:space="preserve">7.90611696243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01044940948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18781471252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29678535461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34895133972168</t>
   </si>
   <si>
     <t xml:space="preserve">8.42082500457764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25968933105469</t>
+    <t xml:space="preserve">8.25968837738037</t>
   </si>
   <si>
     <t xml:space="preserve">8.46139907836914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51588439941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57036876678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51356601715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49733638763428</t>
+    <t xml:space="preserve">8.51588535308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57036972045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5135669708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49733543395996</t>
   </si>
   <si>
     <t xml:space="preserve">8.62485408782959</t>
@@ -3356,43 +3356,43 @@
     <t xml:space="preserve">8.60166931152344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57152938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41271114349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33504009246826</t>
+    <t xml:space="preserve">8.57152843475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41271018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33503913879395</t>
   </si>
   <si>
     <t xml:space="preserve">8.50545120239258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46951389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78281116485596</t>
+    <t xml:space="preserve">8.46951293945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78280925750732</t>
   </si>
   <si>
     <t xml:space="preserve">8.40054130554199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27200698852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32146072387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1196346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84830284118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43663120269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60236740112305</t>
+    <t xml:space="preserve">9.27200603485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32146167755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11963367462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84830379486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43663024902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60236835479736</t>
   </si>
   <si>
     <t xml:space="preserve">8.30564403533936</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">8.42460060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.681227684021</t>
+    <t xml:space="preserve">8.68122863769531</t>
   </si>
   <si>
     <t xml:space="preserve">8.69726848602295</t>
@@ -3416,58 +3416,58 @@
     <t xml:space="preserve">8.76142501831055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93117332458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08889198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01805210113525</t>
+    <t xml:space="preserve">8.93117427825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08889102935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01805305480957</t>
   </si>
   <si>
     <t xml:space="preserve">8.84295654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79483890533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86567974090576</t>
+    <t xml:space="preserve">8.79483985900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86567878723145</t>
   </si>
   <si>
     <t xml:space="preserve">8.95790481567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02206134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82825374603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87770748138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94186592102051</t>
+    <t xml:space="preserve">9.02206230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82825469970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87770938873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94186496734619</t>
   </si>
   <si>
     <t xml:space="preserve">8.82424545288086</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86969089508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07552719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06082344055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97795391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30542087554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28537273406982</t>
+    <t xml:space="preserve">8.86968994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07552528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06082248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97795486450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30542182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28537178039551</t>
   </si>
   <si>
     <t xml:space="preserve">9.2679967880249</t>
@@ -3497,25 +3497,25 @@
     <t xml:space="preserve">10.602707862854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5399122238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.665506362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.983772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.596999168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4785413742065</t>
+    <t xml:space="preserve">10.5399112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6655054092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9837713241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5969982147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4785404205322</t>
   </si>
   <si>
     <t xml:space="preserve">10.1288757324219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1374397277832</t>
+    <t xml:space="preserve">10.1374387741089</t>
   </si>
   <si>
     <t xml:space="preserve">10.2801599502563</t>
@@ -3533,10 +3533,10 @@
     <t xml:space="preserve">10.7639818191528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8010892868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9124116897583</t>
+    <t xml:space="preserve">10.8010902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.912410736084</t>
   </si>
   <si>
     <t xml:space="preserve">10.9109840393066</t>
@@ -3548,16 +3548,16 @@
     <t xml:space="preserve">10.5613193511963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6597967147827</t>
+    <t xml:space="preserve">10.6597957611084</t>
   </si>
   <si>
     <t xml:space="preserve">10.8082246780396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7397193908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7340097427368</t>
+    <t xml:space="preserve">10.7397203445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7340106964111</t>
   </si>
   <si>
     <t xml:space="preserve">10.8910026550293</t>
@@ -3569,10 +3569,10 @@
     <t xml:space="preserve">10.3457975387573</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4551296234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.481369972229</t>
+    <t xml:space="preserve">10.4551305770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4813709259033</t>
   </si>
   <si>
     <t xml:space="preserve">10.4886589050293</t>
@@ -3581,22 +3581,22 @@
     <t xml:space="preserve">10.4667921066284</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4288892745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4901170730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0906867980957</t>
+    <t xml:space="preserve">10.4288902282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4901161193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0906887054443</t>
   </si>
   <si>
     <t xml:space="preserve">10.0761098861694</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2204294204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1227588653564</t>
+    <t xml:space="preserve">10.2204303741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1227579116821</t>
   </si>
   <si>
     <t xml:space="preserve">10.8312349319458</t>
@@ -3608,25 +3608,25 @@
     <t xml:space="preserve">10.8910036087036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0061683654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.686915397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7306480407715</t>
+    <t xml:space="preserve">11.0061674118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6869163513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7306489944458</t>
   </si>
   <si>
     <t xml:space="preserve">10.678168296814</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8283205032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0047101974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0003356933594</t>
+    <t xml:space="preserve">10.8283195495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0047092437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.000337600708</t>
   </si>
   <si>
     <t xml:space="preserve">10.7364797592163</t>
@@ -3635,13 +3635,13 @@
     <t xml:space="preserve">10.9376516342163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1636066436768</t>
+    <t xml:space="preserve">11.1636056900024</t>
   </si>
   <si>
     <t xml:space="preserve">11.2160863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2787714004517</t>
+    <t xml:space="preserve">11.2787704467773</t>
   </si>
   <si>
     <t xml:space="preserve">11.2583618164062</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">11.739426612854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502149581909</t>
+    <t xml:space="preserve">11.8502159118652</t>
   </si>
   <si>
     <t xml:space="preserve">11.9143590927124</t>
@@ -3671,31 +3671,31 @@
     <t xml:space="preserve">12.7219638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7379989624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.560152053833</t>
+    <t xml:space="preserve">12.737998008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5601511001587</t>
   </si>
   <si>
     <t xml:space="preserve">12.3910493850708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5003824234009</t>
+    <t xml:space="preserve">12.5003814697266</t>
   </si>
   <si>
     <t xml:space="preserve">12.3677253723145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3167037963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3181610107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3604364395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0003681182861</t>
+    <t xml:space="preserve">12.3167028427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3181600570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3604373931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0003671646118</t>
   </si>
   <si>
     <t xml:space="preserve">12.4056282043457</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">12.3808450698853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3560628890991</t>
+    <t xml:space="preserve">12.3560619354248</t>
   </si>
   <si>
     <t xml:space="preserve">12.3852186203003</t>
@@ -3713,40 +3713,40 @@
     <t xml:space="preserve">12.436240196228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2758846282959</t>
+    <t xml:space="preserve">12.2758855819702</t>
   </si>
   <si>
     <t xml:space="preserve">12.2613077163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0659666061401</t>
+    <t xml:space="preserve">12.0659675598145</t>
   </si>
   <si>
     <t xml:space="preserve">12.1738414764404</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3414840698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1942510604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0936632156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.688404083252</t>
+    <t xml:space="preserve">12.3414850234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1942501068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0936641693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6884031295776</t>
   </si>
   <si>
     <t xml:space="preserve">12.0164022445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429269790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8370962142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6679954528809</t>
+    <t xml:space="preserve">11.8429279327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8370971679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6679935455322</t>
   </si>
   <si>
     <t xml:space="preserve">11.4332942962646</t>
@@ -3755,10 +3755,10 @@
     <t xml:space="preserve">11.0222024917603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.049901008606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4289216995239</t>
+    <t xml:space="preserve">11.0499000549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4289207458496</t>
   </si>
   <si>
     <t xml:space="preserve">11.3633213043213</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">11.4813995361328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5790700912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4347524642944</t>
+    <t xml:space="preserve">11.5790710449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4347515106201</t>
   </si>
   <si>
     <t xml:space="preserve">11.5324220657349</t>
@@ -3785,34 +3785,34 @@
     <t xml:space="preserve">11.9318523406982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7175912857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.714674949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0280952453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.117018699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0834922790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1330547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4829187393188</t>
+    <t xml:space="preserve">12.7175893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7146739959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0280961990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1170196533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0834913253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1330537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4829177856445</t>
   </si>
   <si>
     <t xml:space="preserve">13.5645551681519</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3692121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0062294006348</t>
+    <t xml:space="preserve">13.369213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0062284469604</t>
   </si>
   <si>
     <t xml:space="preserve">13.105357170105</t>
@@ -3821,22 +3821,22 @@
     <t xml:space="preserve">12.6388702392578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4930934906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5411996841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5732707977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6024265289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.485803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5105867385864</t>
+    <t xml:space="preserve">12.4930925369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5412006378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5732698440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6024255752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4858045578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5105857849121</t>
   </si>
   <si>
     <t xml:space="preserve">12.4041690826416</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">12.567440032959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4537334442139</t>
+    <t xml:space="preserve">12.4537343978882</t>
   </si>
   <si>
     <t xml:space="preserve">12.0980377197266</t>
@@ -3863,34 +3863,34 @@
     <t xml:space="preserve">12.1752996444702</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2656812667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6898918151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2525606155396</t>
+    <t xml:space="preserve">12.2656803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6898927688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2525615692139</t>
   </si>
   <si>
     <t xml:space="preserve">11.7044401168823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6854887008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0645084381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2219486236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2365264892578</t>
+    <t xml:space="preserve">11.6854877471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0645093917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2219476699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2365255355835</t>
   </si>
   <si>
     <t xml:space="preserve">12.3444004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9770421981812</t>
+    <t xml:space="preserve">11.9770412445068</t>
   </si>
   <si>
     <t xml:space="preserve">12.1432285308838</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">11.8575048446655</t>
   </si>
   <si>
-    <t xml:space="preserve">11.762749671936</t>
+    <t xml:space="preserve">11.7627515792847</t>
   </si>
   <si>
     <t xml:space="preserve">12.0674247741699</t>
@@ -3911,13 +3911,13 @@
     <t xml:space="preserve">11.6373815536499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0790863037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1534328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2642230987549</t>
+    <t xml:space="preserve">12.0790872573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1534337997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2642240524292</t>
   </si>
   <si>
     <t xml:space="preserve">12.2860898971558</t>
@@ -3926,13 +3926,13 @@
     <t xml:space="preserve">12.2671394348145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4114580154419</t>
+    <t xml:space="preserve">12.4114589691162</t>
   </si>
   <si>
     <t xml:space="preserve">12.3123302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2292366027832</t>
+    <t xml:space="preserve">12.2292375564575</t>
   </si>
   <si>
     <t xml:space="preserve">12.2598495483398</t>
@@ -3944,22 +3944,22 @@
     <t xml:space="preserve">12.281717300415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.765697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.80797290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7992248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5995101928711</t>
+    <t xml:space="preserve">12.7656965255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8079719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7992258071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5995111465454</t>
   </si>
   <si>
     <t xml:space="preserve">12.719048500061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7321681976318</t>
+    <t xml:space="preserve">12.7321662902832</t>
   </si>
   <si>
     <t xml:space="preserve">12.7904777526855</t>
@@ -3968,34 +3968,34 @@
     <t xml:space="preserve">12.857536315918</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9143905639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7817316055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7117595672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0339260101318</t>
+    <t xml:space="preserve">12.9143896102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7817325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7117605209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0339250564575</t>
   </si>
   <si>
     <t xml:space="preserve">13.0368413925171</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0295524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1855335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0878639221191</t>
+    <t xml:space="preserve">13.0295534133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1855344772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0878648757935</t>
   </si>
   <si>
     <t xml:space="preserve">13.093695640564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7248792648315</t>
+    <t xml:space="preserve">12.7248802185059</t>
   </si>
   <si>
     <t xml:space="preserve">12.3983383178711</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">11.0353231430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6621646881104</t>
+    <t xml:space="preserve">11.662163734436</t>
   </si>
   <si>
     <t xml:space="preserve">11.6096849441528</t>
@@ -4025,40 +4025,40 @@
     <t xml:space="preserve">11.4755697250366</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8749990463257</t>
+    <t xml:space="preserve">11.8749980926514</t>
   </si>
   <si>
     <t xml:space="preserve">12.2977523803711</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1592636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9887037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0193176269531</t>
+    <t xml:space="preserve">12.1592626571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9887046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0193185806274</t>
   </si>
   <si>
     <t xml:space="preserve">11.9289360046387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8589630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8924913406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9639234542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5309648513794</t>
+    <t xml:space="preserve">11.8589639663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8924922943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9639225006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5309638977051</t>
   </si>
   <si>
     <t xml:space="preserve">11.886661529541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9916191101074</t>
+    <t xml:space="preserve">11.9916200637817</t>
   </si>
   <si>
     <t xml:space="preserve">12.2685976028442</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">12.1621799468994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301231384277</t>
+    <t xml:space="preserve">12.6301221847534</t>
   </si>
   <si>
     <t xml:space="preserve">12.9114742279053</t>
@@ -4076,13 +4076,13 @@
     <t xml:space="preserve">13.4318971633911</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2992401123047</t>
+    <t xml:space="preserve">13.299241065979</t>
   </si>
   <si>
     <t xml:space="preserve">13.1213932037354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0208053588867</t>
+    <t xml:space="preserve">13.020806312561</t>
   </si>
   <si>
     <t xml:space="preserve">13.1490898132324</t>
@@ -4091,22 +4091,22 @@
     <t xml:space="preserve">13.3969106674194</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8561086654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8298692703247</t>
+    <t xml:space="preserve">13.8561096191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.829870223999</t>
   </si>
   <si>
     <t xml:space="preserve">13.9508638381958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9173364639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.84153175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6986684799194</t>
+    <t xml:space="preserve">13.9173345565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8415307998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6986694335938</t>
   </si>
   <si>
     <t xml:space="preserve">13.2132329940796</t>
@@ -4118,19 +4118,19 @@
     <t xml:space="preserve">12.6855192184448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7861051559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4406137466431</t>
+    <t xml:space="preserve">12.7861061096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4406147003174</t>
   </si>
   <si>
     <t xml:space="preserve">12.3691825866699</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6417865753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6636533737183</t>
+    <t xml:space="preserve">12.6417856216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6636524200439</t>
   </si>
   <si>
     <t xml:space="preserve">11.998908996582</t>
@@ -4142,10 +4142,10 @@
     <t xml:space="preserve">11.9814157485962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4683122634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3618936538696</t>
+    <t xml:space="preserve">12.4683132171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3618927001953</t>
   </si>
   <si>
     <t xml:space="preserve">12.223406791687</t>
@@ -4154,49 +4154,49 @@
     <t xml:space="preserve">11.9099855422974</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3997964859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5149593353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1665515899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8837461471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4391555786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869468688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3064985275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1052961349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2190027236938</t>
+    <t xml:space="preserve">12.3997955322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5149602890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1665525436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8837451934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4391565322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869459152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3064994812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1052951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2190017700195</t>
   </si>
   <si>
     <t xml:space="preserve">10.9041233062744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0746517181396</t>
+    <t xml:space="preserve">10.0746507644653</t>
   </si>
   <si>
     <t xml:space="preserve">9.43031787872314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42594432830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5834131240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81808376312256</t>
+    <t xml:space="preserve">9.42594337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5834150314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81808471679688</t>
   </si>
   <si>
     <t xml:space="preserve">9.8370361328125</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">10.6883735656738</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6475563049316</t>
+    <t xml:space="preserve">10.6475553512573</t>
   </si>
   <si>
     <t xml:space="preserve">10.8035364151001</t>
@@ -4244,28 +4244,28 @@
     <t xml:space="preserve">10.7875022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7802133560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8516435623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4522142410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98718547821045</t>
+    <t xml:space="preserve">10.7802124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8516426086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4522151947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98718643188477</t>
   </si>
   <si>
     <t xml:space="preserve">9.86910629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0338344573975</t>
+    <t xml:space="preserve">10.0338354110718</t>
   </si>
   <si>
     <t xml:space="preserve">10.1475400924683</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1358785629272</t>
+    <t xml:space="preserve">10.1358795166016</t>
   </si>
   <si>
     <t xml:space="preserve">10.1854419708252</t>
@@ -4274,16 +4274,16 @@
     <t xml:space="preserve">10.2583312988281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5054616928101</t>
+    <t xml:space="preserve">10.5054626464844</t>
   </si>
   <si>
     <t xml:space="preserve">10.5621299743652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6644449234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3197212219238</t>
+    <t xml:space="preserve">10.6644458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3197202682495</t>
   </si>
   <si>
     <t xml:space="preserve">10.0741624832153</t>
@@ -4295,7 +4295,7 @@
     <t xml:space="preserve">9.94823551177979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0710144042969</t>
+    <t xml:space="preserve">10.0710134506226</t>
   </si>
   <si>
     <t xml:space="preserve">10.2174043655396</t>
@@ -4352,10 +4352,10 @@
     <t xml:space="preserve">10.3386087417603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5306482315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7903718948364</t>
+    <t xml:space="preserve">10.5306491851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7903728485107</t>
   </si>
   <si>
     <t xml:space="preserve">10.8202800750732</t>
@@ -4364,22 +4364,22 @@
     <t xml:space="preserve">11.0186147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9666700363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1571340560913</t>
+    <t xml:space="preserve">10.9666709899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1571350097656</t>
   </si>
   <si>
     <t xml:space="preserve">11.2263946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8549098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9304666519165</t>
+    <t xml:space="preserve">10.8549108505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.064263343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9304656982422</t>
   </si>
   <si>
     <t xml:space="preserve">11.0249118804932</t>
@@ -4388,16 +4388,16 @@
     <t xml:space="preserve">10.7919464111328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2252740859985</t>
+    <t xml:space="preserve">10.2252750396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.82388305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0977745056152</t>
+    <t xml:space="preserve">9.82073497772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0977735519409</t>
   </si>
   <si>
     <t xml:space="preserve">9.56415843963623</t>
@@ -4406,25 +4406,25 @@
     <t xml:space="preserve">9.63027000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74989986419678</t>
+    <t xml:space="preserve">9.74990081787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.99388408660889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82230854034424</t>
+    <t xml:space="preserve">9.82230758666992</t>
   </si>
   <si>
     <t xml:space="preserve">9.61295509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78138160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77508640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86953067779541</t>
+    <t xml:space="preserve">9.78138256072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77508544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86953163146973</t>
   </si>
   <si>
     <t xml:space="preserve">9.59406566619873</t>
@@ -4451,16 +4451,16 @@
     <t xml:space="preserve">9.80499362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60193538665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67906665802002</t>
+    <t xml:space="preserve">9.60193634033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67906761169434</t>
   </si>
   <si>
     <t xml:space="preserve">9.4445276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20211887359619</t>
+    <t xml:space="preserve">9.20211791992188</t>
   </si>
   <si>
     <t xml:space="preserve">9.40989780426025</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">10.0348100662231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1764783859253</t>
+    <t xml:space="preserve">10.176477432251</t>
   </si>
   <si>
     <t xml:space="preserve">10.677038192749</t>
@@ -4499,10 +4499,10 @@
     <t xml:space="preserve">11.0548191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2405614852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3523225784302</t>
+    <t xml:space="preserve">11.2405605316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3523216247559</t>
   </si>
   <si>
     <t xml:space="preserve">11.2736177444458</t>
@@ -4511,31 +4511,31 @@
     <t xml:space="preserve">11.2799139022827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6340827941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.33815574646</t>
+    <t xml:space="preserve">11.6340837478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3381547927856</t>
   </si>
   <si>
     <t xml:space="preserve">11.4971380233765</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5585269927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6734352111816</t>
+    <t xml:space="preserve">11.5585279464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.673436164856</t>
   </si>
   <si>
     <t xml:space="preserve">11.726954460144</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7049169540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680629730225</t>
+    <t xml:space="preserve">11.5223245620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7049179077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3680639266968</t>
   </si>
   <si>
     <t xml:space="preserve">10.9021329879761</t>
@@ -4547,10 +4547,10 @@
     <t xml:space="preserve">11.1681537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0894498825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.813982963562</t>
+    <t xml:space="preserve">11.089448928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8139839172363</t>
   </si>
   <si>
     <t xml:space="preserve">10.8265762329102</t>
@@ -4562,25 +4562,25 @@
     <t xml:space="preserve">10.5101852416992</t>
   </si>
   <si>
-    <t xml:space="preserve">10.333888053894</t>
+    <t xml:space="preserve">10.3338871002197</t>
   </si>
   <si>
     <t xml:space="preserve">10.6046304702759</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0961999893188</t>
+    <t xml:space="preserve">10.0961990356445</t>
   </si>
   <si>
     <t xml:space="preserve">10.2315711975098</t>
   </si>
   <si>
-    <t xml:space="preserve">10.340184211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4613885879517</t>
+    <t xml:space="preserve">10.3401832580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3323125839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4613876342773</t>
   </si>
   <si>
     <t xml:space="preserve">10.8124103546143</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">10.5463886260986</t>
   </si>
   <si>
-    <t xml:space="preserve">10.632963180542</t>
+    <t xml:space="preserve">10.6329641342163</t>
   </si>
   <si>
     <t xml:space="preserve">10.4047212600708</t>
@@ -4607,31 +4607,31 @@
     <t xml:space="preserve">10.4912958145142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.237868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0111999511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1009225845337</t>
+    <t xml:space="preserve">10.2378673553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0111989974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1009216308594</t>
   </si>
   <si>
     <t xml:space="preserve">10.0946264266968</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65860366821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8490686416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93564319610596</t>
+    <t xml:space="preserve">9.65860462188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84906768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93564224243164</t>
   </si>
   <si>
     <t xml:space="preserve">9.86480903625488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68064117431641</t>
+    <t xml:space="preserve">9.68064022064209</t>
   </si>
   <si>
     <t xml:space="preserve">9.58934307098389</t>
@@ -4640,16 +4640,16 @@
     <t xml:space="preserve">9.69638156890869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59721374511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82703018188477</t>
+    <t xml:space="preserve">9.5972146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82703113555908</t>
   </si>
   <si>
     <t xml:space="preserve">9.83647537231445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0851821899414</t>
+    <t xml:space="preserve">10.0851812362671</t>
   </si>
   <si>
     <t xml:space="preserve">10.2488861083984</t>
@@ -4658,16 +4658,16 @@
     <t xml:space="preserve">10.2063865661621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3685169219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.289813041687</t>
+    <t xml:space="preserve">10.3685178756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2898120880127</t>
   </si>
   <si>
     <t xml:space="preserve">10.6487045288086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7447233200073</t>
+    <t xml:space="preserve">10.7447242736816</t>
   </si>
   <si>
     <t xml:space="preserve">10.7305574417114</t>
@@ -4676,19 +4676,19 @@
     <t xml:space="preserve">10.675464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7510194778442</t>
+    <t xml:space="preserve">10.7510204315186</t>
   </si>
   <si>
     <t xml:space="preserve">10.8092622756958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4566659927368</t>
+    <t xml:space="preserve">10.4566669464111</t>
   </si>
   <si>
     <t xml:space="preserve">10.8297252655029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7872257232666</t>
+    <t xml:space="preserve">10.7872247695923</t>
   </si>
   <si>
     <t xml:space="preserve">11.1429681777954</t>
@@ -4703,10 +4703,10 @@
     <t xml:space="preserve">11.4247303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2153768539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1036167144775</t>
+    <t xml:space="preserve">11.2153759002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1036157608032</t>
   </si>
   <si>
     <t xml:space="preserve">11.3413028717041</t>
@@ -4718,13 +4718,13 @@
     <t xml:space="preserve">11.5553789138794</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3838043212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5333423614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5301933288574</t>
+    <t xml:space="preserve">11.3838033676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5333433151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5301942825317</t>
   </si>
   <si>
     <t xml:space="preserve">11.4546375274658</t>
@@ -4739,13 +4739,13 @@
     <t xml:space="preserve">11.7332515716553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4924154281616</t>
+    <t xml:space="preserve">11.4924163818359</t>
   </si>
   <si>
     <t xml:space="preserve">11.5364904403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3712110519409</t>
+    <t xml:space="preserve">11.3712120056152</t>
   </si>
   <si>
     <t xml:space="preserve">11.3979711532593</t>
@@ -4769,7 +4769,7 @@
     <t xml:space="preserve">10.6675939559937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3291635513306</t>
+    <t xml:space="preserve">10.3291645050049</t>
   </si>
   <si>
     <t xml:space="preserve">10.3811092376709</t>
@@ -4778,22 +4778,22 @@
     <t xml:space="preserve">10.3559246063232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3244428634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.52907371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4393510818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7415752410889</t>
+    <t xml:space="preserve">10.32444190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5290746688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4393520355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7415761947632</t>
   </si>
   <si>
     <t xml:space="preserve">10.8816699981689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1697282791138</t>
+    <t xml:space="preserve">11.1697273254395</t>
   </si>
   <si>
     <t xml:space="preserve">11.2862100601196</t>
@@ -4808,7 +4808,7 @@
     <t xml:space="preserve">11.5286197662354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6246395111084</t>
+    <t xml:space="preserve">11.6246404647827</t>
   </si>
   <si>
     <t xml:space="preserve">11.1996355056763</t>
@@ -4817,13 +4817,13 @@
     <t xml:space="preserve">11.2673206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3035259246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2295417785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9477815628052</t>
+    <t xml:space="preserve">11.3035249710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2295427322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9477806091309</t>
   </si>
   <si>
     <t xml:space="preserve">11.037504196167</t>
@@ -4838,28 +4838,28 @@
     <t xml:space="preserve">10.95250415802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0611162185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1728763580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3145446777344</t>
+    <t xml:space="preserve">11.0611152648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1728754043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3145437240601</t>
   </si>
   <si>
     <t xml:space="preserve">11.4026927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9693641662598</t>
+    <t xml:space="preserve">11.9693651199341</t>
   </si>
   <si>
     <t xml:space="preserve">11.9630680084229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8686237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8749189376831</t>
+    <t xml:space="preserve">11.8686218261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8749198913574</t>
   </si>
   <si>
     <t xml:space="preserve">11.9016780853271</t>
@@ -4868,31 +4868,31 @@
     <t xml:space="preserve">12.3392753601074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.129921913147</t>
+    <t xml:space="preserve">12.1299209594727</t>
   </si>
   <si>
     <t xml:space="preserve">12.2054777145386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.258996963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4903869628906</t>
+    <t xml:space="preserve">12.2589960098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4903879165649</t>
   </si>
   <si>
     <t xml:space="preserve">12.517147064209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5533504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7013149261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4888143539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7642784118652</t>
+    <t xml:space="preserve">12.5533514022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7013158798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4888134002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7642793655396</t>
   </si>
   <si>
     <t xml:space="preserve">13.2254867553711</t>
@@ -4904,7 +4904,7 @@
     <t xml:space="preserve">13.0901145935059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0287256240845</t>
+    <t xml:space="preserve">13.0287265777588</t>
   </si>
   <si>
     <t xml:space="preserve">13.4238214492798</t>
@@ -4913,16 +4913,16 @@
     <t xml:space="preserve">13.5151195526123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9054927825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8330860137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7968816757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7653980255127</t>
+    <t xml:space="preserve">13.9054918289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8330841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7968807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.765398979187</t>
   </si>
   <si>
     <t xml:space="preserve">13.5387306213379</t>
@@ -4937,7 +4937,7 @@
     <t xml:space="preserve">12.9027976989746</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4305715560913</t>
+    <t xml:space="preserve">12.4305725097656</t>
   </si>
   <si>
     <t xml:space="preserve">12.5265922546387</t>
@@ -4949,19 +4949,19 @@
     <t xml:space="preserve">12.7390937805176</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7469625473022</t>
+    <t xml:space="preserve">12.7469635009766</t>
   </si>
   <si>
     <t xml:space="preserve">12.7343711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5155725479126</t>
+    <t xml:space="preserve">12.5155735015869</t>
   </si>
   <si>
     <t xml:space="preserve">12.7737226486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7910394668579</t>
+    <t xml:space="preserve">12.7910385131836</t>
   </si>
   <si>
     <t xml:space="preserve">12.9153909683228</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">12.9390029907227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.682427406311</t>
+    <t xml:space="preserve">12.6824264526367</t>
   </si>
   <si>
     <t xml:space="preserve">12.7878894805908</t>
@@ -4994,19 +4994,19 @@
     <t xml:space="preserve">13.2443752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5088224411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3624324798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4049320220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3545618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6320552825928</t>
+    <t xml:space="preserve">13.5088214874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3624334335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.404932975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3545627593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6320543289185</t>
   </si>
   <si>
     <t xml:space="preserve">12.5486288070679</t>
@@ -5054,13 +5054,13 @@
     <t xml:space="preserve">12.770318031311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6242437362671</t>
+    <t xml:space="preserve">12.6242446899414</t>
   </si>
   <si>
     <t xml:space="preserve">12.7514142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0143480300903</t>
+    <t xml:space="preserve">13.014347076416</t>
   </si>
   <si>
     <t xml:space="preserve">13.2600955963135</t>
@@ -5069,13 +5069,13 @@
     <t xml:space="preserve">13.1655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0934000015259</t>
+    <t xml:space="preserve">13.0933990478516</t>
   </si>
   <si>
     <t xml:space="preserve">12.5623769760132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4334878921509</t>
+    <t xml:space="preserve">12.4334888458252</t>
   </si>
   <si>
     <t xml:space="preserve">12.6929845809937</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">13.5470886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5178737640381</t>
+    <t xml:space="preserve">13.5178747177124</t>
   </si>
   <si>
     <t xml:space="preserve">13.6261405944824</t>
@@ -5132,13 +5132,13 @@
     <t xml:space="preserve">13.2033843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0813703536987</t>
+    <t xml:space="preserve">13.0813694000244</t>
   </si>
   <si>
     <t xml:space="preserve">12.9885702133179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0469999313354</t>
+    <t xml:space="preserve">13.0469989776611</t>
   </si>
   <si>
     <t xml:space="preserve">13.1587028503418</t>
@@ -5153,7 +5153,7 @@
     <t xml:space="preserve">13.8254890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.999059677124</t>
+    <t xml:space="preserve">13.9990587234497</t>
   </si>
   <si>
     <t xml:space="preserve">13.9681262969971</t>
@@ -5171,7 +5171,7 @@
     <t xml:space="preserve">13.9767189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0437412261963</t>
+    <t xml:space="preserve">14.043740272522</t>
   </si>
   <si>
     <t xml:space="preserve">14.3736963272095</t>
@@ -5180,52 +5180,52 @@
     <t xml:space="preserve">14.4458742141724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3547925949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2671489715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2551193237305</t>
+    <t xml:space="preserve">14.3547916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2671480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2551183700562</t>
   </si>
   <si>
     <t xml:space="preserve">14.3152666091919</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1863784790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4149408340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4235334396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8050441741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.593846321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9650459289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0200386047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7192983627319</t>
+    <t xml:space="preserve">14.1863775253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4149398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4235324859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8050451278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5938453674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9650449752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0200366973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7192974090576</t>
   </si>
   <si>
     <t xml:space="preserve">15.5147933959961</t>
   </si>
   <si>
-    <t xml:space="preserve">15.373875617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3446598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2982606887817</t>
+    <t xml:space="preserve">15.3738746643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3446588516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2982597351074</t>
   </si>
   <si>
     <t xml:space="preserve">15.0834455490112</t>
@@ -5243,31 +5243,31 @@
     <t xml:space="preserve">14.5197706222534</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3221406936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1571636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0523338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3015184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3633852005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.378851890564</t>
+    <t xml:space="preserve">14.3221397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1571626663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0523328781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3015174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3633842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3788509368896</t>
   </si>
   <si>
     <t xml:space="preserve">14.2173109054565</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3668222427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5489845275879</t>
+    <t xml:space="preserve">14.3668212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5489854812622</t>
   </si>
   <si>
     <t xml:space="preserve">14.7964515686035</t>
@@ -5276,10 +5276,10 @@
     <t xml:space="preserve">14.7500524520874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7586450576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4355630874634</t>
+    <t xml:space="preserve">14.7586460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4355621337891</t>
   </si>
   <si>
     <t xml:space="preserve">14.4493112564087</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">14.5386743545532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5661697387695</t>
+    <t xml:space="preserve">14.5661706924438</t>
   </si>
   <si>
     <t xml:space="preserve">14.6074151992798</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">15.2673263549805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1006298065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3859052658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2827930450439</t>
+    <t xml:space="preserve">15.1006288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3859033584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2827920913696</t>
   </si>
   <si>
     <t xml:space="preserve">15.5113563537598</t>
@@ -5321,43 +5321,43 @@
     <t xml:space="preserve">15.9959783554077</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6058759689331</t>
+    <t xml:space="preserve">15.6058750152588</t>
   </si>
   <si>
     <t xml:space="preserve">15.712423324585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5251054763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4512090682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.607593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6471185684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.55260181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2999782562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.231237411499</t>
+    <t xml:space="preserve">15.5251045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4512071609497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6075925827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6471195220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5526008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2999773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2312364578247</t>
   </si>
   <si>
     <t xml:space="preserve">15.3137273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4649562835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9444236755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2726612091064</t>
+    <t xml:space="preserve">15.464955329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9444227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2726593017578</t>
   </si>
   <si>
     <t xml:space="preserve">16.246883392334</t>
@@ -5369,25 +5369,25 @@
     <t xml:space="preserve">16.0681571960449</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2348537445068</t>
+    <t xml:space="preserve">16.2348518371582</t>
   </si>
   <si>
     <t xml:space="preserve">16.1300239562988</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5405721664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1642160415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4855785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2759189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1848382949829</t>
+    <t xml:space="preserve">15.5405702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1642150878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.485577583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.275918006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1848392486572</t>
   </si>
   <si>
     <t xml:space="preserve">14.8806600570679</t>
@@ -5396,16 +5396,16 @@
     <t xml:space="preserve">14.6417865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.122971534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4168376922607</t>
+    <t xml:space="preserve">15.1229705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4168367385864</t>
   </si>
   <si>
     <t xml:space="preserve">15.7553873062134</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0647201538086</t>
+    <t xml:space="preserve">16.06471824646</t>
   </si>
   <si>
     <t xml:space="preserve">15.7467937469482</t>
@@ -5417,16 +5417,16 @@
     <t xml:space="preserve">15.5749416351318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7364816665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0440998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2211036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.894585609436</t>
+    <t xml:space="preserve">15.7364826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0440979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2211055755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8945846557617</t>
   </si>
   <si>
     <t xml:space="preserve">15.8705272674561</t>
@@ -5441,7 +5441,7 @@
     <t xml:space="preserve">16.1094017028809</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0939350128174</t>
+    <t xml:space="preserve">16.0939331054688</t>
   </si>
   <si>
     <t xml:space="preserve">16.9394454956055</t>
@@ -5450,7 +5450,7 @@
     <t xml:space="preserve">17.1009864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2754154205322</t>
+    <t xml:space="preserve">17.2754173278809</t>
   </si>
   <si>
     <t xml:space="preserve">17.4472694396973</t>
@@ -5459,7 +5459,7 @@
     <t xml:space="preserve">17.5847511291504</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0960102081299</t>
+    <t xml:space="preserve">18.0960083007812</t>
   </si>
   <si>
     <t xml:space="preserve">17.9714183807373</t>
@@ -5471,7 +5471,7 @@
     <t xml:space="preserve">18.0530471801758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0186767578125</t>
+    <t xml:space="preserve">18.0186748504639</t>
   </si>
   <si>
     <t xml:space="preserve">17.9671211242676</t>
@@ -5489,28 +5489,28 @@
     <t xml:space="preserve">18.289342880249</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2506771087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2549743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2377891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2420845031738</t>
+    <t xml:space="preserve">18.250675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2549724578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2377872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2420825958252</t>
   </si>
   <si>
     <t xml:space="preserve">18.2034168243408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1733436584473</t>
+    <t xml:space="preserve">18.1733417510986</t>
   </si>
   <si>
     <t xml:space="preserve">18.19482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5718612670898</t>
+    <t xml:space="preserve">17.5718631744385</t>
   </si>
   <si>
     <t xml:space="preserve">17.5503787994385</t>
@@ -5522,7 +5522,7 @@
     <t xml:space="preserve">17.7608985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620845794678</t>
+    <t xml:space="preserve">17.6620826721191</t>
   </si>
   <si>
     <t xml:space="preserve">17.8554172515869</t>
@@ -5534,7 +5534,7 @@
     <t xml:space="preserve">17.5761566162109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3011951446533</t>
+    <t xml:space="preserve">17.3011932373047</t>
   </si>
   <si>
     <t xml:space="preserve">17.11301612854</t>
@@ -5543,13 +5543,13 @@
     <t xml:space="preserve">16.8741416931152</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0459938049316</t>
+    <t xml:space="preserve">17.045991897583</t>
   </si>
   <si>
     <t xml:space="preserve">16.9016380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9274158477783</t>
+    <t xml:space="preserve">16.927417755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.8122749328613</t>
@@ -5561,7 +5561,7 @@
     <t xml:space="preserve">16.6885433197021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7761859893799</t>
+    <t xml:space="preserve">16.7761878967285</t>
   </si>
   <si>
     <t xml:space="preserve">16.7332248687744</t>
@@ -5570,7 +5570,7 @@
     <t xml:space="preserve">17.374231338501</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6105289459229</t>
+    <t xml:space="preserve">17.6105270385742</t>
   </si>
   <si>
     <t xml:space="preserve">17.8468246459961</t>
@@ -5588,16 +5588,16 @@
     <t xml:space="preserve">18.624454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0197124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3032684326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4536380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2388229370117</t>
+    <t xml:space="preserve">19.0197143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3032703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4536399841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2388248443604</t>
   </si>
   <si>
     <t xml:space="preserve">19.3977890014648</t>
@@ -5621,10 +5621,10 @@
     <t xml:space="preserve">20.8198623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1463832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8843078613281</t>
+    <t xml:space="preserve">21.1463813781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8843059539795</t>
   </si>
   <si>
     <t xml:space="preserve">20.8327522277832</t>
@@ -5636,13 +5636,13 @@
     <t xml:space="preserve">20.7382335662842</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9960117340088</t>
+    <t xml:space="preserve">20.9960098266602</t>
   </si>
   <si>
     <t xml:space="preserve">21.1592712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2494926452637</t>
+    <t xml:space="preserve">21.249490737915</t>
   </si>
   <si>
     <t xml:space="preserve">21.4814929962158</t>
@@ -5663,7 +5663,7 @@
     <t xml:space="preserve">21.8552703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7994194030762</t>
+    <t xml:space="preserve">21.7994213104248</t>
   </si>
   <si>
     <t xml:space="preserve">22.3665313720703</t>
@@ -5672,7 +5672,7 @@
     <t xml:space="preserve">22.4696407318115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8649024963379</t>
+    <t xml:space="preserve">22.8649005889893</t>
   </si>
   <si>
     <t xml:space="preserve">22.9078636169434</t>
@@ -5681,19 +5681,19 @@
     <t xml:space="preserve">23.1269760131836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1441612243652</t>
+    <t xml:space="preserve">23.1441593170166</t>
   </si>
   <si>
     <t xml:space="preserve">23.3331985473633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8391227722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9293460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6371974945068</t>
+    <t xml:space="preserve">22.8391246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9293441772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6371955871582</t>
   </si>
   <si>
     <t xml:space="preserve">21.8939361572266</t>
@@ -5702,10 +5702,10 @@
     <t xml:space="preserve">21.4943809509277</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5244541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1377906799316</t>
+    <t xml:space="preserve">21.5244560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.137788772583</t>
   </si>
   <si>
     <t xml:space="preserve">21.3912696838379</t>
@@ -5714,25 +5714,25 @@
     <t xml:space="preserve">21.5459365844727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6791210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6619358062744</t>
+    <t xml:space="preserve">21.6791229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.661937713623</t>
   </si>
   <si>
     <t xml:space="preserve">20.9530487060547</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4771957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8370494842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8542346954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9229755401611</t>
+    <t xml:space="preserve">21.4771976470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8370475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8542327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9229736328125</t>
   </si>
   <si>
     <t xml:space="preserve">21.2375450134277</t>
@@ -6852,6 +6852,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.91600036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28400039672852</t>
   </si>
 </sst>
 </file>
@@ -72372,7 +72375,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6942476852</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>18287013</v>
@@ -72393,6 +72396,32 @@
         <v>2279</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6941203704</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>27274295</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>9.39200019836426</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>8.91300010681152</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>8.93099975585938</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>9.28400039672852</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>2280</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/STLAM.MI.xlsx
+++ b/data/STLAM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2281" uniqueCount="2281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="2282">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">STLAM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13119459152222</t>
+    <t xml:space="preserve">4.13119506835938</t>
   </si>
   <si>
     <t xml:space="preserve">3.91636371612549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78795862197876</t>
+    <t xml:space="preserve">3.78795742988586</t>
   </si>
   <si>
     <t xml:space="preserve">3.63238978385925</t>
@@ -65,82 +65,82 @@
     <t xml:space="preserve">3.66942977905273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37804770469666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28421354293823</t>
+    <t xml:space="preserve">3.37804818153381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28421401977539</t>
   </si>
   <si>
     <t xml:space="preserve">3.1879096031189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26939797401428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06197333335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25705146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3261923789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26198983192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46200633049011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43237352371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18544054031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16321587562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16074705123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07678961753845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9533224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91628313064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94838404655457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6570029258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5829222202301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7335524559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59279990196228</t>
+    <t xml:space="preserve">3.26939725875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06197309494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25705170631409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32619261741638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26199007034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46200561523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43237328529358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1854407787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16321635246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16074681282043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07679009437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95332288742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91628289222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94838428497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65700340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58292293548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73355293273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59280037879944</t>
   </si>
   <si>
     <t xml:space="preserve">2.68416571617126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80269360542297</t>
+    <t xml:space="preserve">2.80269336700439</t>
   </si>
   <si>
     <t xml:space="preserve">2.75824594497681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89899754524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87924313545227</t>
+    <t xml:space="preserve">2.89899730682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87924289703369</t>
   </si>
   <si>
     <t xml:space="preserve">2.81010150909424</t>
@@ -149,52 +149,52 @@
     <t xml:space="preserve">2.92616009712219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83973360061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72614455223083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00517892837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13358426094055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29902982711792</t>
+    <t xml:space="preserve">2.83973383903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72614407539368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00517916679382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13358402252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2990300655365</t>
   </si>
   <si>
     <t xml:space="preserve">3.45212817192078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46447491645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44225120544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28915214538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30643844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21013331413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35088586807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44718956947327</t>
+    <t xml:space="preserve">3.46447539329529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44225144386292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2891526222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30643820762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21013402938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35088562965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44719004631042</t>
   </si>
   <si>
     <t xml:space="preserve">3.36076354980469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44472002983093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42496657371521</t>
+    <t xml:space="preserve">3.44472026824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42496585845947</t>
   </si>
   <si>
     <t xml:space="preserve">3.51633071899414</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">3.50151515007019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51386141777039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4768214225769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33360052108765</t>
+    <t xml:space="preserve">3.51386165618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47682166099548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33360075950623</t>
   </si>
   <si>
     <t xml:space="preserve">3.57559466362</t>
@@ -218,55 +218,55 @@
     <t xml:space="preserve">3.50645351409912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3360698223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841632843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18050217628479</t>
+    <t xml:space="preserve">3.33606958389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841656684875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18050169944763</t>
   </si>
   <si>
     <t xml:space="preserve">3.13852286338806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01505613327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13605380058289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21260333061218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16815519332886</t>
+    <t xml:space="preserve">3.01505637168884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13605356216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2126030921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16815543174744</t>
   </si>
   <si>
     <t xml:space="preserve">3.31878423690796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35335469245911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40274167060852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56571769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54596257209778</t>
+    <t xml:space="preserve">3.35335516929626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4027419090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56571745872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54596376419067</t>
   </si>
   <si>
     <t xml:space="preserve">3.56818723678589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47435283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53361630439758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41014933586121</t>
+    <t xml:space="preserve">3.47435307502747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.533616065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4101505279541</t>
   </si>
   <si>
     <t xml:space="preserve">3.38298654556274</t>
@@ -290,52 +290,52 @@
     <t xml:space="preserve">3.33113098144531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.108891248703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11383008956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10148286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11629939079285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97801613807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06938171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12370753288269</t>
+    <t xml:space="preserve">3.10889053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11382961273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10148310661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11629915237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97801637649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06938219070435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12370729446411</t>
   </si>
   <si>
     <t xml:space="preserve">3.07185101509094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15827822685242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07432055473328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0422191619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03974914550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14840054512024</t>
+    <t xml:space="preserve">3.15827775001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07432079315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04221868515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03974962234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14840006828308</t>
   </si>
   <si>
     <t xml:space="preserve">3.12123775482178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9310986995697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87677311897278</t>
+    <t xml:space="preserve">2.93109893798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87677335739136</t>
   </si>
   <si>
     <t xml:space="preserve">2.89652824401855</t>
@@ -344,34 +344,34 @@
     <t xml:space="preserve">2.86195778846741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93356800079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09407496452332</t>
+    <t xml:space="preserve">2.93356823921204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09407472610474</t>
   </si>
   <si>
     <t xml:space="preserve">3.08666682243347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04962706565857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11136054992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81997919082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64465594291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66194152832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71379780769348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.770592212677</t>
+    <t xml:space="preserve">3.04962730407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11136031150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81997895240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64465641975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66194200515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7137975692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77059245109558</t>
   </si>
   <si>
     <t xml:space="preserve">2.533536195755</t>
@@ -380,25 +380,25 @@
     <t xml:space="preserve">2.52365875244141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54835176467896</t>
+    <t xml:space="preserve">2.54835200309753</t>
   </si>
   <si>
     <t xml:space="preserve">2.8471417427063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96320033073425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91134452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9977707862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00270938873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95826125144958</t>
+    <t xml:space="preserve">2.96320009231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91134476661682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99777126312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00270962715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95826148986816</t>
   </si>
   <si>
     <t xml:space="preserve">3.08913588523865</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">3.12617659568787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06691193580627</t>
+    <t xml:space="preserve">3.06691217422485</t>
   </si>
   <si>
     <t xml:space="preserve">2.84467196464539</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">2.91381359100342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88665080070496</t>
+    <t xml:space="preserve">2.88665103912354</t>
   </si>
   <si>
     <t xml:space="preserve">3.05703496932983</t>
@@ -434,76 +434,76 @@
     <t xml:space="preserve">2.98789358139038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9607310295105</t>
+    <t xml:space="preserve">2.96073126792908</t>
   </si>
   <si>
     <t xml:space="preserve">2.97307753562927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88418173789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91875243186951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03481078147888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02987194061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04468822479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99283242225647</t>
+    <t xml:space="preserve">2.88418221473694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91875219345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0348105430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02987217903137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0446879863739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99283218383789</t>
   </si>
   <si>
     <t xml:space="preserve">3.05950450897217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97554683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9508535861969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96813941001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90393567085266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86442756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87430453300476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81504082679749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90146732330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83232545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86689591407776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74096035957336</t>
+    <t xml:space="preserve">2.97554731369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95085406303406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96813917160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9039363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86442732810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87430429458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81504058837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90146660804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83232569694519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86689639091492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74096012115479</t>
   </si>
   <si>
     <t xml:space="preserve">2.70885896682739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7903470993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82491779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84220314025879</t>
+    <t xml:space="preserve">2.79034686088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82491755485535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84220337867737</t>
   </si>
   <si>
     <t xml:space="preserve">2.89158964157104</t>
@@ -512,52 +512,52 @@
     <t xml:space="preserve">2.87183451652527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90887427330017</t>
+    <t xml:space="preserve">2.90887451171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.76812267303467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82244801521301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85948777198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93850708007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25211238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29409146308899</t>
+    <t xml:space="preserve">2.82244825363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85948824882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9385073184967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25211215019226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29409170150757</t>
   </si>
   <si>
     <t xml:space="preserve">3.25952005386353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03234171867371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02740335464478</t>
+    <t xml:space="preserve">3.03234148025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02740287780762</t>
   </si>
   <si>
     <t xml:space="preserve">3.16568541526794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5237398147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39780330657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47188258171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45953607559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47929096221924</t>
+    <t xml:space="preserve">3.52373933792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39780306816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47188305854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45953631401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4792914390564</t>
   </si>
   <si>
     <t xml:space="preserve">3.49410700798035</t>
@@ -569,43 +569,43 @@
     <t xml:space="preserve">3.58547234535217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57065606117249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5607795715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60028886795044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62251257896423</t>
+    <t xml:space="preserve">3.57065582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56077909469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60028910636902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62251210212708</t>
   </si>
   <si>
     <t xml:space="preserve">3.55830955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72128510475159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81265139579773</t>
+    <t xml:space="preserve">3.72128582000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81265115737915</t>
   </si>
   <si>
     <t xml:space="preserve">3.8570990562439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93364834785461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93117904663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97315812110901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99044275283813</t>
+    <t xml:space="preserve">3.93364882469177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93117880821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97315740585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99044370651245</t>
   </si>
   <si>
     <t xml:space="preserve">4.15341901779175</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">4.19539785385132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21762228012085</t>
+    <t xml:space="preserve">4.21762180328369</t>
   </si>
   <si>
     <t xml:space="preserve">4.29664039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30651807785034</t>
+    <t xml:space="preserve">4.30651760101318</t>
   </si>
   <si>
     <t xml:space="preserve">4.17564296722412</t>
@@ -635,76 +635,76 @@
     <t xml:space="preserve">4.30898761749268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27935552597046</t>
+    <t xml:space="preserve">4.2793550491333</t>
   </si>
   <si>
     <t xml:space="preserve">4.42257642745972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5065336227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53863573074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5707368850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88928031921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95842266082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0127477645874</t>
+    <t xml:space="preserve">4.50653409957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53863525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57073640823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88927984237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95842218399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01274728775024</t>
   </si>
   <si>
     <t xml:space="preserve">5.17078447341919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33615064620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53616523742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34602689743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39047527313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41516780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62753057479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64234733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71889638900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99793243408203</t>
+    <t xml:space="preserve">4.3361496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53616666793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34602785110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39047574996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41516828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62753105163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64234781265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71889734268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99793195724487</t>
   </si>
   <si>
     <t xml:space="preserve">5.0423789024353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10164308547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1263370513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95348453521729</t>
+    <t xml:space="preserve">5.10164260864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12633657455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95348405838013</t>
   </si>
   <si>
     <t xml:space="preserve">4.98805379867554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99299192428589</t>
+    <t xml:space="preserve">4.99299240112305</t>
   </si>
   <si>
     <t xml:space="preserve">5.00287055969238</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">4.92385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78062963485718</t>
+    <t xml:space="preserve">4.78062915802002</t>
   </si>
   <si>
     <t xml:space="preserve">4.8991584777832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02756357192993</t>
+    <t xml:space="preserve">5.02756309509277</t>
   </si>
   <si>
     <t xml:space="preserve">5.33869934082031</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">5.34363794326782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32388305664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25474309921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32882261276245</t>
+    <t xml:space="preserve">5.32388401031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25474214553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32882213592529</t>
   </si>
   <si>
     <t xml:space="preserve">5.1757230758667</t>
@@ -746,22 +746,22 @@
     <t xml:space="preserve">5.14609098434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18560075759888</t>
+    <t xml:space="preserve">5.18560123443604</t>
   </si>
   <si>
     <t xml:space="preserve">5.18066263198853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13127517700195</t>
+    <t xml:space="preserve">5.13127470016479</t>
   </si>
   <si>
     <t xml:space="preserve">5.13621377944946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16584539413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09670400619507</t>
+    <t xml:space="preserve">5.16584634780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09670495986938</t>
   </si>
   <si>
     <t xml:space="preserve">5.14115238189697</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">5.22511005401611</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30412864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21029567718506</t>
+    <t xml:space="preserve">5.30412817001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21029472351074</t>
   </si>
   <si>
     <t xml:space="preserve">4.98311519622803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94360542297363</t>
+    <t xml:space="preserve">4.94360494613647</t>
   </si>
   <si>
     <t xml:space="preserve">4.96336078643799</t>
@@ -791,28 +791,28 @@
     <t xml:space="preserve">5.07695007324219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07201147079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06213426589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81026220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83248615264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74358940124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78556871414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7337121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71642637252808</t>
+    <t xml:space="preserve">5.07201242446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0621337890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81026172637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83248710632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74358987808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78556823730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73371267318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71642732620239</t>
   </si>
   <si>
     <t xml:space="preserve">4.70655012130737</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">4.69420337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51887989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45220804214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64728593826294</t>
+    <t xml:space="preserve">4.51888036727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45220851898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6472864151001</t>
   </si>
   <si>
     <t xml:space="preserve">4.70408010482788</t>
@@ -836,19 +836,19 @@
     <t xml:space="preserve">4.63000106811523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79297685623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78803777694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23498678207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91644287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97323846817017</t>
+    <t xml:space="preserve">4.79297637939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78803825378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23498773574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91644239425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97323799133301</t>
   </si>
   <si>
     <t xml:space="preserve">5.0522575378418</t>
@@ -860,61 +860,61 @@
     <t xml:space="preserve">4.91891288757324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94854497909546</t>
+    <t xml:space="preserve">4.9485445022583</t>
   </si>
   <si>
     <t xml:space="preserve">5.02262496948242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76828384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6201229095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80038499832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72383642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68926477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66210222244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67197847366333</t>
+    <t xml:space="preserve">4.7682843208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62012434005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80038452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72383689880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68926429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66210174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67197895050049</t>
   </si>
   <si>
     <t xml:space="preserve">4.59049129486084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.583083152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61518478393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84730195999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83001708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75346708297729</t>
+    <t xml:space="preserve">4.58308362960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61518526077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8473014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83001661300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75346660614014</t>
   </si>
   <si>
     <t xml:space="preserve">4.80532360076904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75099802017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79544544219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8176703453064</t>
+    <t xml:space="preserve">4.75099897384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79544687271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81766986846924</t>
   </si>
   <si>
     <t xml:space="preserve">4.78309917449951</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">4.68432521820068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85224103927612</t>
+    <t xml:space="preserve">4.85224056243896</t>
   </si>
   <si>
     <t xml:space="preserve">4.77816104888916</t>
@@ -935,13 +935,13 @@
     <t xml:space="preserve">4.7608757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55838966369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85507917404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86003732681274</t>
+    <t xml:space="preserve">4.55838918685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8600378036499</t>
   </si>
   <si>
     <t xml:space="preserve">4.78564977645874</t>
@@ -953,88 +953,88 @@
     <t xml:space="preserve">4.80548572540283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87243509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95922183990479</t>
+    <t xml:space="preserve">4.87243461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95922231674194</t>
   </si>
   <si>
     <t xml:space="preserve">4.99889516830444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19230461120605</t>
+    <t xml:space="preserve">5.19230508804321</t>
   </si>
   <si>
     <t xml:space="preserve">5.15263223648071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17246866226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10799932479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17742681503296</t>
+    <t xml:space="preserve">5.17246770858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10799884796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17742824554443</t>
   </si>
   <si>
     <t xml:space="preserve">4.97409963607788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97905921936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98897743225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03856945037842</t>
+    <t xml:space="preserve">4.97905969619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9889760017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03856897354126</t>
   </si>
   <si>
     <t xml:space="preserve">5.03361082077026</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05840635299683</t>
+    <t xml:space="preserve">5.05840587615967</t>
   </si>
   <si>
     <t xml:space="preserve">5.07328414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02865171432495</t>
+    <t xml:space="preserve">5.02865123748779</t>
   </si>
   <si>
     <t xml:space="preserve">5.07824277877808</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0633659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95178413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95426273345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86995601654053</t>
+    <t xml:space="preserve">5.06336545944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95178365707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95426225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86995649337769</t>
   </si>
   <si>
     <t xml:space="preserve">5.26669454574585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40555238723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34604215621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30636835098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67334985733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68822765350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01553678512573</t>
+    <t xml:space="preserve">5.40555191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34604120254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30636787414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67335033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6882266998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01553630828857</t>
   </si>
   <si>
     <t xml:space="preserve">6.19406795501709</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">6.14943599700928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1643123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07008695602417</t>
+    <t xml:space="preserve">6.16431283950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07008743286133</t>
   </si>
   <si>
     <t xml:space="preserve">6.13951683044434</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27341604232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61560201644897</t>
+    <t xml:space="preserve">6.27341651916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61560297012329</t>
   </si>
   <si>
     <t xml:space="preserve">6.53129577636719</t>
@@ -1064,73 +1064,73 @@
     <t xml:space="preserve">6.50649929046631</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78421592712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70982837677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7247052192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76933860778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80405330657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96770715713501</t>
+    <t xml:space="preserve">6.78421640396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7098274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72470569610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76933813095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80405282974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96770763397217</t>
   </si>
   <si>
     <t xml:space="preserve">6.88340044021606</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99250364303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07681083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14623880386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18095397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46362829208374</t>
+    <t xml:space="preserve">6.99250316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07680940628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14623785018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18095350265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46362972259521</t>
   </si>
   <si>
     <t xml:space="preserve">7.31485271453857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3346905708313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38428163528442</t>
+    <t xml:space="preserve">7.33468914031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38428258895874</t>
   </si>
   <si>
     <t xml:space="preserve">7.36444616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51818084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58265018463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56281423568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53801870346069</t>
+    <t xml:space="preserve">7.51817989349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58265066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56281328201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53801822662354</t>
   </si>
   <si>
     <t xml:space="preserve">7.49338531494141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40907764434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52313947677612</t>
+    <t xml:space="preserve">7.4090781211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52313995361328</t>
   </si>
   <si>
     <t xml:space="preserve">7.41403722763062</t>
@@ -1139,55 +1139,55 @@
     <t xml:space="preserve">7.50330352783203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42395544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4586706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41899681091309</t>
+    <t xml:space="preserve">7.42395639419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45867013931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41899633407593</t>
   </si>
   <si>
     <t xml:space="preserve">7.30989360809326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37932205200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93795156478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05697393417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02225875854492</t>
+    <t xml:space="preserve">7.37932252883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93795204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05697441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02225780487061</t>
   </si>
   <si>
     <t xml:space="preserve">7.14128017425537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34956789016724</t>
+    <t xml:space="preserve">7.34956836700439</t>
   </si>
   <si>
     <t xml:space="preserve">7.3594856262207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51322221755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76614189147949</t>
+    <t xml:space="preserve">7.51322174072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76614141464233</t>
   </si>
   <si>
     <t xml:space="preserve">7.73142719268799</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66199827194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45371150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28013801574707</t>
+    <t xml:space="preserve">7.66199779510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45371198654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28013706207275</t>
   </si>
   <si>
     <t xml:space="preserve">7.33964920043945</t>
@@ -1196,73 +1196,73 @@
     <t xml:space="preserve">7.3743634223938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25038242340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43387413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55785465240479</t>
+    <t xml:space="preserve">7.2503833770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43387365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55785417556763</t>
   </si>
   <si>
     <t xml:space="preserve">7.24046468734741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20078992843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17103481292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15119886398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00738143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2355055809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19087171554565</t>
+    <t xml:space="preserve">7.20079040527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1710352897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15119743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00738096237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23550510406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19087076187134</t>
   </si>
   <si>
     <t xml:space="preserve">7.53305912017822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52809810638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50826263427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43883275985718</t>
+    <t xml:space="preserve">7.52809906005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50826215744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43883371353149</t>
   </si>
   <si>
     <t xml:space="preserve">7.44875192642212</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63720178604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65208005905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64216232299805</t>
+    <t xml:space="preserve">7.63720273971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65207862854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64215993881226</t>
   </si>
   <si>
     <t xml:space="preserve">7.69175338745117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67191743850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54297637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39420127868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71159029006958</t>
+    <t xml:space="preserve">7.67191600799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54297733306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39419937133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71159076690674</t>
   </si>
   <si>
     <t xml:space="preserve">8.35628890991211</t>
@@ -1271,46 +1271,46 @@
     <t xml:space="preserve">8.88692665100098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98115158081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15968418121338</t>
+    <t xml:space="preserve">8.98115062713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1596851348877</t>
   </si>
   <si>
     <t xml:space="preserve">9.21423435211182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42252159118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48699188232422</t>
+    <t xml:space="preserve">9.42252254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48699283599854</t>
   </si>
   <si>
     <t xml:space="preserve">9.69032001495361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28862380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32829761505127</t>
+    <t xml:space="preserve">9.28862285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32829666137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.50187015533447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69527912139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76470851898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70519924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64072704315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63080978393555</t>
+    <t xml:space="preserve">9.69528007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76470947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70519733428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64072895050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63080883026123</t>
   </si>
   <si>
     <t xml:space="preserve">9.81925964355469</t>
@@ -1319,64 +1319,64 @@
     <t xml:space="preserve">9.84107971191406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68337821960449</t>
+    <t xml:space="preserve">9.68337726593018</t>
   </si>
   <si>
     <t xml:space="preserve">9.65163803100586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53856754302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31936931610107</t>
+    <t xml:space="preserve">9.5385684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31937026977539</t>
   </si>
   <si>
     <t xml:space="preserve">8.75798606872559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35111045837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89982128143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63698291778564</t>
+    <t xml:space="preserve">9.35110950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89981937408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63698196411133</t>
   </si>
   <si>
     <t xml:space="preserve">8.75302696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57548809051514</t>
+    <t xml:space="preserve">8.57548713684082</t>
   </si>
   <si>
     <t xml:space="preserve">8.77782344818115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82741546630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0039644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83733177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94643783569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98908615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80956268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73814868927002</t>
+    <t xml:space="preserve">8.82741641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00396347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83733367919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94643592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98908710479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80956363677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73815059661865</t>
   </si>
   <si>
     <t xml:space="preserve">8.6905403137207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80559635162354</t>
+    <t xml:space="preserve">8.80559539794922</t>
   </si>
   <si>
     <t xml:space="preserve">8.71434497833252</t>
@@ -1394,22 +1394,22 @@
     <t xml:space="preserve">8.46836853027344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.556640625</t>
+    <t xml:space="preserve">8.55664157867432</t>
   </si>
   <si>
     <t xml:space="preserve">8.56259250640869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51597595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5278787612915</t>
+    <t xml:space="preserve">8.51597690582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52787780761719</t>
   </si>
   <si>
     <t xml:space="preserve">8.53085422515869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43266105651855</t>
+    <t xml:space="preserve">8.43266201019287</t>
   </si>
   <si>
     <t xml:space="preserve">8.53184509277344</t>
@@ -1418,28 +1418,28 @@
     <t xml:space="preserve">8.52589416503906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35926532745361</t>
+    <t xml:space="preserve">8.3592643737793</t>
   </si>
   <si>
     <t xml:space="preserve">8.56457614898682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71732044219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42175102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25115394592285</t>
+    <t xml:space="preserve">8.71732139587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42175006866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25115299224854</t>
   </si>
   <si>
     <t xml:space="preserve">8.18866729736328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32554340362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15791988372803</t>
+    <t xml:space="preserve">8.32554149627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15791893005371</t>
   </si>
   <si>
     <t xml:space="preserve">8.18370914459229</t>
@@ -1448,76 +1448,76 @@
     <t xml:space="preserve">8.78278255462646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73517322540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07438468933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18943977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31341934204102</t>
+    <t xml:space="preserve">8.73517417907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15869045257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07438564300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18943881988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31342029571533</t>
   </si>
   <si>
     <t xml:space="preserve">9.22613716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4076452255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4364070892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36301040649414</t>
+    <t xml:space="preserve">9.40764617919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43640804290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36301136016846</t>
   </si>
   <si>
     <t xml:space="preserve">9.7091646194458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7676830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63180255889893</t>
+    <t xml:space="preserve">9.76768207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63180160522461</t>
   </si>
   <si>
     <t xml:space="preserve">9.55840492248535</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7597484588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79148769378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68635368347168</t>
+    <t xml:space="preserve">9.75974941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79148864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393558502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68635272979736</t>
   </si>
   <si>
     <t xml:space="preserve">9.41458702087402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20927715301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43739986419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21820259094238</t>
+    <t xml:space="preserve">9.2092752456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43740081787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2182035446167</t>
   </si>
   <si>
     <t xml:space="preserve">9.51674747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53559303283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4800500869751</t>
+    <t xml:space="preserve">9.53559112548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48004913330078</t>
   </si>
   <si>
     <t xml:space="preserve">9.29556560516357</t>
@@ -1535,40 +1535,40 @@
     <t xml:space="preserve">9.36697864532471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30746936798096</t>
+    <t xml:space="preserve">9.30746746063232</t>
   </si>
   <si>
     <t xml:space="preserve">9.36797046661377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19935703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4393835067749</t>
+    <t xml:space="preserve">9.1993579864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43938255310059</t>
   </si>
   <si>
     <t xml:space="preserve">9.59609508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48600101470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31143474578857</t>
+    <t xml:space="preserve">9.48600006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31143569946289</t>
   </si>
   <si>
     <t xml:space="preserve">9.30548477172852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10810852050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06446552276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42748069763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62089157104492</t>
+    <t xml:space="preserve">9.1081075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06446647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42748165130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62089061737061</t>
   </si>
   <si>
     <t xml:space="preserve">9.185471534729</t>
@@ -1580,28 +1580,28 @@
     <t xml:space="preserve">8.87601566314697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86212921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1398458480835</t>
+    <t xml:space="preserve">8.86213111877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13984775543213</t>
   </si>
   <si>
     <t xml:space="preserve">8.90676307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98313617706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92659854888916</t>
+    <t xml:space="preserve">8.98313522338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92659950256348</t>
   </si>
   <si>
     <t xml:space="preserve">8.85022735595703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04462909698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87403202056885</t>
+    <t xml:space="preserve">9.04462814331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87403297424316</t>
   </si>
   <si>
     <t xml:space="preserve">8.92461585998535</t>
@@ -1610,136 +1610,136 @@
     <t xml:space="preserve">8.79666900634766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75005149841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38505363464355</t>
+    <t xml:space="preserve">8.7500524520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38505268096924</t>
   </si>
   <si>
     <t xml:space="preserve">8.18172454833984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92979526519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15296077728271</t>
+    <t xml:space="preserve">7.92979574203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15296268463135</t>
   </si>
   <si>
     <t xml:space="preserve">8.24123573303223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9555835723877</t>
+    <t xml:space="preserve">7.95558452606201</t>
   </si>
   <si>
     <t xml:space="preserve">8.1003942489624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10237693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03889942169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50506591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40687274932861</t>
+    <t xml:space="preserve">8.10237598419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03890037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50506782531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40687370300293</t>
   </si>
   <si>
     <t xml:space="preserve">8.46935844421387</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52291965484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2630558013916</t>
+    <t xml:space="preserve">8.52291870117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26305675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.21346378326416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25214672088623</t>
+    <t xml:space="preserve">8.25214576721191</t>
   </si>
   <si>
     <t xml:space="preserve">8.19957828521729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24917030334473</t>
+    <t xml:space="preserve">8.24916934967041</t>
   </si>
   <si>
     <t xml:space="preserve">8.22239112854004</t>
   </si>
   <si>
-    <t xml:s